--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -491,22 +491,22 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>51483</v>
+        <v>51501</v>
       </c>
       <c r="F4">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="G4">
-        <v>20620</v>
+        <v>21961</v>
       </c>
       <c r="H4">
-        <v>21133</v>
+        <v>20289</v>
       </c>
       <c r="I4">
         <v>29</v>
       </c>
       <c r="J4">
-        <v>5702</v>
+        <v>6034</v>
       </c>
       <c r="K4">
         <v>2371</v>
@@ -518,10 +518,10 @@
         <v>6</v>
       </c>
       <c r="N4">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="O4">
-        <v>14296</v>
+        <v>15381</v>
       </c>
       <c r="P4">
         <v>53812</v>
@@ -556,31 +556,31 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>32973</v>
+        <v>34764</v>
       </c>
       <c r="H5">
-        <v>13715</v>
+        <v>12612</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>3239</v>
+        <v>3363</v>
       </c>
       <c r="K5">
         <v>1341</v>
       </c>
       <c r="L5">
-        <v>2515</v>
+        <v>2713</v>
       </c>
       <c r="M5">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="N5">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="O5">
-        <v>28736</v>
+        <v>30211</v>
       </c>
       <c r="P5">
         <v>54384</v>
@@ -615,34 +615,34 @@
         <v>2</v>
       </c>
       <c r="G6">
-        <v>18439</v>
+        <v>18745</v>
       </c>
       <c r="H6">
-        <v>11435</v>
+        <v>11356</v>
       </c>
       <c r="I6">
         <v>154</v>
       </c>
       <c r="J6">
-        <v>1576</v>
+        <v>1601</v>
       </c>
       <c r="K6">
         <v>939</v>
       </c>
       <c r="L6">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="M6">
         <v>26</v>
       </c>
       <c r="N6">
-        <v>587</v>
+        <v>623</v>
       </c>
       <c r="O6">
-        <v>15426</v>
+        <v>15671</v>
       </c>
       <c r="P6">
-        <v>42611</v>
+        <v>42630</v>
       </c>
       <c r="Q6">
         <v>17918</v>
@@ -674,34 +674,34 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>23139</v>
+        <v>23446</v>
       </c>
       <c r="H7">
-        <v>15175</v>
+        <v>14891</v>
       </c>
       <c r="I7">
         <v>364</v>
       </c>
       <c r="J7">
-        <v>4347</v>
+        <v>4182</v>
       </c>
       <c r="K7">
-        <v>3084</v>
+        <v>2858</v>
       </c>
       <c r="L7">
-        <v>797</v>
+        <v>1023</v>
       </c>
       <c r="M7">
         <v>28</v>
       </c>
       <c r="N7">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="O7">
-        <v>17827</v>
+        <v>18297</v>
       </c>
       <c r="P7">
-        <v>75226</v>
+        <v>77581</v>
       </c>
       <c r="Q7">
         <v>20905</v>
@@ -727,37 +727,37 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>40518</v>
+        <v>40539</v>
       </c>
       <c r="F8">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="G8">
-        <v>19697</v>
+        <v>20594</v>
       </c>
       <c r="H8">
-        <v>20837</v>
+        <v>19940</v>
       </c>
       <c r="I8">
         <v>18</v>
       </c>
       <c r="J8">
-        <v>7592</v>
+        <v>7832</v>
       </c>
       <c r="K8">
-        <v>3781</v>
+        <v>3640</v>
       </c>
       <c r="L8">
-        <v>2846</v>
+        <v>2999</v>
       </c>
       <c r="M8">
         <v>16</v>
       </c>
       <c r="N8">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="O8">
-        <v>8955</v>
+        <v>9425</v>
       </c>
       <c r="P8">
         <v>13958</v>
@@ -792,22 +792,22 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>26858</v>
+        <v>28479</v>
       </c>
       <c r="H9">
-        <v>14992</v>
+        <v>13678</v>
       </c>
       <c r="I9">
-        <v>457</v>
+        <v>389</v>
       </c>
       <c r="J9">
-        <v>4485</v>
+        <v>4710</v>
       </c>
       <c r="K9">
-        <v>3191</v>
+        <v>3131</v>
       </c>
       <c r="L9">
-        <v>474</v>
+        <v>536</v>
       </c>
       <c r="M9">
         <v>7</v>
@@ -816,7 +816,7 @@
         <v>147</v>
       </c>
       <c r="O9">
-        <v>21644</v>
+        <v>22975</v>
       </c>
       <c r="P9">
         <v>50354</v>
@@ -851,16 +851,16 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>25283</v>
+        <v>26066</v>
       </c>
       <c r="H10">
-        <v>10857</v>
+        <v>10129</v>
       </c>
       <c r="I10">
         <v>38</v>
       </c>
       <c r="J10">
-        <v>7358</v>
+        <v>7432</v>
       </c>
       <c r="K10">
         <v>4664</v>
@@ -872,13 +872,13 @@
         <v>9</v>
       </c>
       <c r="N10">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="O10">
-        <v>16880</v>
+        <v>17558</v>
       </c>
       <c r="P10">
-        <v>10399</v>
+        <v>11669</v>
       </c>
       <c r="Q10">
         <v>9525</v>
@@ -910,34 +910,34 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>28474</v>
+        <v>29717</v>
       </c>
       <c r="H11">
-        <v>18558</v>
+        <v>17488</v>
       </c>
       <c r="I11">
-        <v>571</v>
+        <v>551</v>
       </c>
       <c r="J11">
-        <v>3350</v>
+        <v>3443</v>
       </c>
       <c r="K11">
-        <v>1747</v>
+        <v>1675</v>
       </c>
       <c r="L11">
-        <v>447</v>
+        <v>532</v>
       </c>
       <c r="M11">
         <v>1</v>
       </c>
       <c r="N11">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="O11">
-        <v>24504</v>
+        <v>25541</v>
       </c>
       <c r="P11">
-        <v>61167</v>
+        <v>72059</v>
       </c>
       <c r="Q11">
         <v>23805</v>
@@ -963,22 +963,22 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>40546</v>
+        <v>40620</v>
       </c>
       <c r="F12">
-        <v>193</v>
+        <v>119</v>
       </c>
       <c r="G12">
-        <v>18244</v>
+        <v>19016</v>
       </c>
       <c r="H12">
-        <v>21759</v>
+        <v>20990</v>
       </c>
       <c r="I12">
         <v>56</v>
       </c>
       <c r="J12">
-        <v>7481</v>
+        <v>7623</v>
       </c>
       <c r="K12">
         <v>4598</v>
@@ -990,13 +990,13 @@
         <v>2</v>
       </c>
       <c r="N12">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="O12">
-        <v>10399</v>
+        <v>11015</v>
       </c>
       <c r="P12">
-        <v>38176</v>
+        <v>41963</v>
       </c>
       <c r="Q12">
         <v>17907</v>
@@ -1022,22 +1022,22 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>36856</v>
+        <v>36860</v>
       </c>
       <c r="F13">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="G13">
-        <v>21075</v>
+        <v>21417</v>
       </c>
       <c r="H13">
-        <v>13065</v>
+        <v>12723</v>
       </c>
       <c r="I13">
         <v>6</v>
       </c>
       <c r="J13">
-        <v>2982</v>
+        <v>3197</v>
       </c>
       <c r="K13">
         <v>1251</v>
@@ -1049,13 +1049,13 @@
         <v>0</v>
       </c>
       <c r="N13">
-        <v>1531</v>
+        <v>1587</v>
       </c>
       <c r="O13">
-        <v>16555</v>
+        <v>16626</v>
       </c>
       <c r="P13">
-        <v>52889</v>
+        <v>54271</v>
       </c>
       <c r="Q13">
         <v>16822</v>
@@ -1087,16 +1087,16 @@
         <v>4</v>
       </c>
       <c r="G14">
-        <v>25803</v>
+        <v>26496</v>
       </c>
       <c r="H14">
-        <v>11852</v>
+        <v>11645</v>
       </c>
       <c r="I14">
         <v>722</v>
       </c>
       <c r="J14">
-        <v>7155</v>
+        <v>7509</v>
       </c>
       <c r="K14">
         <v>4580</v>
@@ -1108,13 +1108,13 @@
         <v>27</v>
       </c>
       <c r="N14">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="O14">
-        <v>17616</v>
+        <v>17951</v>
       </c>
       <c r="P14">
-        <v>34138</v>
+        <v>36774</v>
       </c>
       <c r="Q14">
         <v>20044</v>
@@ -1146,31 +1146,31 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>35275</v>
+        <v>36385</v>
       </c>
       <c r="H15">
-        <v>7287</v>
+        <v>6200</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>133</v>
+        <v>15</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15">
-        <v>7604</v>
+        <v>7801</v>
       </c>
       <c r="M15">
         <v>0</v>
       </c>
       <c r="N15">
-        <v>758</v>
+        <v>982</v>
       </c>
       <c r="O15">
-        <v>32322</v>
+        <v>33186</v>
       </c>
       <c r="P15">
         <v>67178</v>
@@ -1199,40 +1199,40 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>25288</v>
+        <v>25302</v>
       </c>
       <c r="F16">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="G16">
-        <v>16387</v>
+        <v>17068</v>
       </c>
       <c r="H16">
-        <v>8197</v>
+        <v>7296</v>
       </c>
       <c r="I16">
         <v>78</v>
       </c>
       <c r="J16">
-        <v>358</v>
+        <v>149</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
       <c r="L16">
-        <v>8884</v>
+        <v>9522</v>
       </c>
       <c r="M16">
         <v>0</v>
       </c>
       <c r="N16">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="O16">
-        <v>9951</v>
+        <v>10289</v>
       </c>
       <c r="P16">
-        <v>66432</v>
+        <v>67034</v>
       </c>
       <c r="Q16">
         <v>5208</v>
@@ -1264,34 +1264,34 @@
         <v>13</v>
       </c>
       <c r="G17">
-        <v>22271</v>
+        <v>22826</v>
       </c>
       <c r="H17">
-        <v>4254</v>
+        <v>3551</v>
       </c>
       <c r="I17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17">
-        <v>290</v>
+        <v>152</v>
       </c>
       <c r="K17">
         <v>0</v>
       </c>
       <c r="L17">
-        <v>6715</v>
+        <v>7103</v>
       </c>
       <c r="M17">
         <v>2</v>
       </c>
       <c r="N17">
-        <v>104</v>
+        <v>155</v>
       </c>
       <c r="O17">
-        <v>20341</v>
+        <v>20701</v>
       </c>
       <c r="P17">
-        <v>65450</v>
+        <v>65453</v>
       </c>
       <c r="Q17">
         <v>5444</v>
@@ -1317,37 +1317,37 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>47690</v>
+        <v>47722</v>
       </c>
       <c r="F18">
-        <v>146</v>
+        <v>114</v>
       </c>
       <c r="G18">
-        <v>39560</v>
+        <v>41278</v>
       </c>
       <c r="H18">
-        <v>4994</v>
+        <v>3948</v>
       </c>
       <c r="I18">
-        <v>1236</v>
+        <v>1022</v>
       </c>
       <c r="J18">
-        <v>125</v>
+        <v>26</v>
       </c>
       <c r="K18">
         <v>0</v>
       </c>
       <c r="L18">
-        <v>5987</v>
+        <v>6437</v>
       </c>
       <c r="M18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N18">
-        <v>971</v>
+        <v>1128</v>
       </c>
       <c r="O18">
-        <v>35701</v>
+        <v>37190</v>
       </c>
       <c r="P18">
         <v>69692</v>
@@ -1376,37 +1376,37 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>56303</v>
+        <v>56313</v>
       </c>
       <c r="F19">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="G19">
-        <v>44104</v>
+        <v>46242</v>
       </c>
       <c r="H19">
-        <v>11639</v>
+        <v>9644</v>
       </c>
       <c r="I19">
-        <v>131</v>
+        <v>53</v>
       </c>
       <c r="J19">
-        <v>65</v>
+        <v>139</v>
       </c>
       <c r="K19">
         <v>0</v>
       </c>
       <c r="L19">
-        <v>11565</v>
+        <v>11810</v>
       </c>
       <c r="M19">
         <v>1</v>
       </c>
       <c r="N19">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="O19">
-        <v>38716</v>
+        <v>40553</v>
       </c>
       <c r="P19">
         <v>105570</v>
@@ -1435,40 +1435,40 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>34983</v>
+        <v>34984</v>
       </c>
       <c r="F20">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G20">
-        <v>30609</v>
+        <v>31346</v>
       </c>
       <c r="H20">
-        <v>2748</v>
+        <v>2555</v>
       </c>
       <c r="I20">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="J20">
-        <v>143</v>
+        <v>3</v>
       </c>
       <c r="K20">
         <v>0</v>
       </c>
       <c r="L20">
-        <v>5116</v>
+        <v>5380</v>
       </c>
       <c r="M20">
         <v>5</v>
       </c>
       <c r="N20">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="O20">
-        <v>26493</v>
+        <v>28538</v>
       </c>
       <c r="P20">
-        <v>75236</v>
+        <v>75257</v>
       </c>
       <c r="Q20">
         <v>9020</v>
@@ -1509,13 +1509,13 @@
         <v>0</v>
       </c>
       <c r="J21">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K21">
         <v>0</v>
       </c>
       <c r="L21">
-        <v>3879</v>
+        <v>3885</v>
       </c>
       <c r="M21">
         <v>3</v>
@@ -1524,7 +1524,7 @@
         <v>169</v>
       </c>
       <c r="O21">
-        <v>16210</v>
+        <v>16645</v>
       </c>
       <c r="P21">
         <v>62460</v>
@@ -1559,22 +1559,22 @@
         <v>0</v>
       </c>
       <c r="G22">
-        <v>17437</v>
+        <v>17766</v>
       </c>
       <c r="H22">
-        <v>901</v>
+        <v>619</v>
       </c>
       <c r="I22">
         <v>0</v>
       </c>
       <c r="J22">
-        <v>225</v>
+        <v>36</v>
       </c>
       <c r="K22">
         <v>0</v>
       </c>
       <c r="L22">
-        <v>6844</v>
+        <v>7183</v>
       </c>
       <c r="M22">
         <v>0</v>
@@ -1583,10 +1583,10 @@
         <v>151</v>
       </c>
       <c r="O22">
-        <v>16748</v>
+        <v>16992</v>
       </c>
       <c r="P22">
-        <v>63942</v>
+        <v>64099</v>
       </c>
       <c r="Q22">
         <v>4866</v>
@@ -1618,31 +1618,31 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>11722</v>
+        <v>11796</v>
       </c>
       <c r="H23">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="I23">
         <v>0</v>
       </c>
       <c r="J23">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="K23">
         <v>0</v>
       </c>
       <c r="L23">
-        <v>1952</v>
+        <v>2058</v>
       </c>
       <c r="M23">
         <v>0</v>
       </c>
       <c r="N23">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O23">
-        <v>11479</v>
+        <v>11580</v>
       </c>
       <c r="P23">
         <v>57093</v>
@@ -1677,31 +1677,31 @@
         <v>0</v>
       </c>
       <c r="G24">
-        <v>13434</v>
+        <v>13532</v>
       </c>
       <c r="H24">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I24">
         <v>0</v>
       </c>
       <c r="J24">
-        <v>92</v>
+        <v>4</v>
       </c>
       <c r="K24">
         <v>0</v>
       </c>
       <c r="L24">
-        <v>3237</v>
+        <v>3350</v>
       </c>
       <c r="M24">
         <v>0</v>
       </c>
       <c r="N24">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="O24">
-        <v>13145</v>
+        <v>13227</v>
       </c>
       <c r="P24">
         <v>65629</v>
@@ -1736,31 +1736,31 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>18505</v>
+        <v>18633</v>
       </c>
       <c r="H25">
-        <v>227</v>
+        <v>194</v>
       </c>
       <c r="I25">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="J25">
-        <v>154</v>
+        <v>49</v>
       </c>
       <c r="K25">
         <v>0</v>
       </c>
       <c r="L25">
-        <v>4127</v>
+        <v>4317</v>
       </c>
       <c r="M25">
         <v>0</v>
       </c>
       <c r="N25">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="O25">
-        <v>16308</v>
+        <v>18191</v>
       </c>
       <c r="P25">
         <v>57533</v>
@@ -1795,31 +1795,31 @@
         <v>0</v>
       </c>
       <c r="G26">
-        <v>16148</v>
+        <v>16383</v>
       </c>
       <c r="H26">
-        <v>1045</v>
+        <v>897</v>
       </c>
       <c r="I26">
         <v>0</v>
       </c>
       <c r="J26">
-        <v>187</v>
+        <v>31</v>
       </c>
       <c r="K26">
         <v>0</v>
       </c>
       <c r="L26">
-        <v>3071</v>
+        <v>3238</v>
       </c>
       <c r="M26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N26">
         <v>130</v>
       </c>
       <c r="O26">
-        <v>14765</v>
+        <v>15130</v>
       </c>
       <c r="P26">
         <v>66594</v>
@@ -1854,34 +1854,34 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>18681</v>
+        <v>21357</v>
       </c>
       <c r="H27">
-        <v>20446</v>
+        <v>17770</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27">
-        <v>482</v>
+        <v>323</v>
       </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="L27">
-        <v>3158</v>
+        <v>3755</v>
       </c>
       <c r="M27">
         <v>0</v>
       </c>
       <c r="N27">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="O27">
-        <v>16968</v>
+        <v>20052</v>
       </c>
       <c r="P27">
-        <v>39635</v>
+        <v>40115</v>
       </c>
       <c r="Q27">
         <v>12669</v>
@@ -1907,37 +1907,37 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>53611</v>
+        <v>53690</v>
       </c>
       <c r="F28">
-        <v>738</v>
+        <v>659</v>
       </c>
       <c r="G28">
-        <v>21794</v>
+        <v>22265</v>
       </c>
       <c r="H28">
-        <v>22698</v>
+        <v>22250</v>
       </c>
       <c r="I28">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J28">
-        <v>138</v>
+        <v>110</v>
       </c>
       <c r="K28">
         <v>0</v>
       </c>
       <c r="L28">
-        <v>2944</v>
+        <v>3072</v>
       </c>
       <c r="M28">
         <v>11</v>
       </c>
       <c r="N28">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="O28">
-        <v>18850</v>
+        <v>19189</v>
       </c>
       <c r="P28">
         <v>80640</v>
@@ -1972,31 +1972,31 @@
         <v>0</v>
       </c>
       <c r="G29">
-        <v>28086</v>
+        <v>29198</v>
       </c>
       <c r="H29">
-        <v>15988</v>
+        <v>15207</v>
       </c>
       <c r="I29">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="J29">
-        <v>357</v>
+        <v>226</v>
       </c>
       <c r="K29">
         <v>0</v>
       </c>
       <c r="L29">
-        <v>4011</v>
+        <v>4656</v>
       </c>
       <c r="M29">
         <v>2</v>
       </c>
       <c r="N29">
-        <v>266</v>
+        <v>322</v>
       </c>
       <c r="O29">
-        <v>25482</v>
+        <v>25992</v>
       </c>
       <c r="P29">
         <v>83837</v>
@@ -2025,37 +2025,37 @@
         <v>0</v>
       </c>
       <c r="E30">
-        <v>52590</v>
+        <v>52595</v>
       </c>
       <c r="F30">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="G30">
-        <v>22009</v>
+        <v>23744</v>
       </c>
       <c r="H30">
-        <v>27243</v>
+        <v>24912</v>
       </c>
       <c r="I30">
         <v>10</v>
       </c>
       <c r="J30">
-        <v>390</v>
+        <v>138</v>
       </c>
       <c r="K30">
         <v>0</v>
       </c>
       <c r="L30">
-        <v>1771</v>
+        <v>2196</v>
       </c>
       <c r="M30">
         <v>0</v>
       </c>
       <c r="N30">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O30">
-        <v>19424</v>
+        <v>20895</v>
       </c>
       <c r="P30">
         <v>86935</v>
@@ -2090,31 +2090,31 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>82380</v>
+        <v>84177</v>
       </c>
       <c r="H31">
-        <v>1763</v>
+        <v>900</v>
       </c>
       <c r="I31">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="J31">
-        <v>3087</v>
+        <v>146</v>
       </c>
       <c r="K31">
         <v>0</v>
       </c>
       <c r="L31">
-        <v>34613</v>
+        <v>38454</v>
       </c>
       <c r="M31">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N31">
-        <v>1218</v>
+        <v>1514</v>
       </c>
       <c r="O31">
-        <v>72615</v>
+        <v>74637</v>
       </c>
       <c r="P31">
         <v>81642</v>
@@ -2143,37 +2143,37 @@
         <v>0</v>
       </c>
       <c r="E32">
-        <v>46689</v>
+        <v>46692</v>
       </c>
       <c r="F32">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G32">
-        <v>18459</v>
+        <v>19674</v>
       </c>
       <c r="H32">
-        <v>19796</v>
+        <v>18621</v>
       </c>
       <c r="I32">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="J32">
-        <v>861</v>
+        <v>661</v>
       </c>
       <c r="K32">
         <v>0</v>
       </c>
       <c r="L32">
-        <v>2642</v>
+        <v>3411</v>
       </c>
       <c r="M32">
         <v>0</v>
       </c>
       <c r="N32">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O32">
-        <v>16103</v>
+        <v>17126</v>
       </c>
       <c r="P32">
         <v>10221</v>
@@ -2202,28 +2202,28 @@
         <v>0</v>
       </c>
       <c r="E33">
-        <v>40088</v>
+        <v>40096</v>
       </c>
       <c r="F33">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="G33">
-        <v>15202</v>
+        <v>16306</v>
       </c>
       <c r="H33">
-        <v>17294</v>
+        <v>16476</v>
       </c>
       <c r="I33">
         <v>10</v>
       </c>
       <c r="J33">
-        <v>374</v>
+        <v>148</v>
       </c>
       <c r="K33">
         <v>0</v>
       </c>
       <c r="L33">
-        <v>2116</v>
+        <v>2437</v>
       </c>
       <c r="M33">
         <v>1</v>
@@ -2232,10 +2232,10 @@
         <v>6</v>
       </c>
       <c r="O33">
-        <v>14057</v>
+        <v>15061</v>
       </c>
       <c r="P33">
-        <v>49857</v>
+        <v>56152</v>
       </c>
       <c r="Q33">
         <v>6678</v>
@@ -2261,28 +2261,28 @@
         <v>0</v>
       </c>
       <c r="E34">
-        <v>36180</v>
+        <v>36244</v>
       </c>
       <c r="F34">
-        <v>362</v>
+        <v>298</v>
       </c>
       <c r="G34">
-        <v>12483</v>
+        <v>14156</v>
       </c>
       <c r="H34">
-        <v>22547</v>
+        <v>20919</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
       <c r="J34">
-        <v>783</v>
+        <v>195</v>
       </c>
       <c r="K34">
         <v>0</v>
       </c>
       <c r="L34">
-        <v>5864</v>
+        <v>6570</v>
       </c>
       <c r="M34">
         <v>0</v>
@@ -2291,10 +2291,10 @@
         <v>0</v>
       </c>
       <c r="O34">
-        <v>10536</v>
+        <v>12130</v>
       </c>
       <c r="P34">
-        <v>67969</v>
+        <v>74626</v>
       </c>
       <c r="Q34">
         <v>7152</v>
@@ -2320,40 +2320,40 @@
         <v>0</v>
       </c>
       <c r="E35">
-        <v>33112</v>
+        <v>33132</v>
       </c>
       <c r="F35">
-        <v>452</v>
+        <v>432</v>
       </c>
       <c r="G35">
-        <v>15596</v>
+        <v>17250</v>
       </c>
       <c r="H35">
-        <v>14184</v>
+        <v>12998</v>
       </c>
       <c r="I35">
         <v>15</v>
       </c>
       <c r="J35">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="K35">
         <v>0</v>
       </c>
       <c r="L35">
-        <v>1152</v>
+        <v>1314</v>
       </c>
       <c r="M35">
         <v>0</v>
       </c>
       <c r="N35">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O35">
-        <v>14117</v>
+        <v>15555</v>
       </c>
       <c r="P35">
-        <v>52265</v>
+        <v>54855</v>
       </c>
       <c r="Q35">
         <v>8879</v>
@@ -2394,13 +2394,13 @@
         <v>0</v>
       </c>
       <c r="J36">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="K36">
         <v>0</v>
       </c>
       <c r="L36">
-        <v>7228</v>
+        <v>7279</v>
       </c>
       <c r="M36">
         <v>0</v>
@@ -2453,22 +2453,22 @@
         <v>0</v>
       </c>
       <c r="J37">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K37">
         <v>0</v>
       </c>
       <c r="L37">
-        <v>2251</v>
+        <v>2268</v>
       </c>
       <c r="M37">
         <v>0</v>
       </c>
       <c r="N37">
-        <v>497</v>
+        <v>515</v>
       </c>
       <c r="O37">
-        <v>17097</v>
+        <v>17113</v>
       </c>
       <c r="P37">
         <v>57832</v>
@@ -2503,34 +2503,34 @@
         <v>0</v>
       </c>
       <c r="G38">
-        <v>28424</v>
+        <v>28611</v>
       </c>
       <c r="H38">
-        <v>343</v>
+        <v>280</v>
       </c>
       <c r="I38">
         <v>13</v>
       </c>
       <c r="J38">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="K38">
         <v>0</v>
       </c>
       <c r="L38">
-        <v>4544</v>
+        <v>4666</v>
       </c>
       <c r="M38">
         <v>2</v>
       </c>
       <c r="N38">
-        <v>309</v>
+        <v>351</v>
       </c>
       <c r="O38">
-        <v>24463</v>
+        <v>24509</v>
       </c>
       <c r="P38">
-        <v>59982</v>
+        <v>60278</v>
       </c>
       <c r="Q38">
         <v>5160</v>
@@ -2571,22 +2571,22 @@
         <v>0</v>
       </c>
       <c r="J39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K39">
         <v>0</v>
       </c>
       <c r="L39">
-        <v>4479</v>
+        <v>4493</v>
       </c>
       <c r="M39">
         <v>1</v>
       </c>
       <c r="N39">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="O39">
-        <v>18545</v>
+        <v>18590</v>
       </c>
       <c r="P39">
         <v>71133</v>
@@ -2621,31 +2621,31 @@
         <v>0</v>
       </c>
       <c r="G40">
-        <v>13955</v>
+        <v>14262</v>
       </c>
       <c r="H40">
-        <v>488</v>
+        <v>279</v>
       </c>
       <c r="I40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J40">
-        <v>569</v>
+        <v>586</v>
       </c>
       <c r="K40">
         <v>0</v>
       </c>
       <c r="L40">
-        <v>574</v>
+        <v>596</v>
       </c>
       <c r="M40">
         <v>0</v>
       </c>
       <c r="N40">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="O40">
-        <v>12812</v>
+        <v>13080</v>
       </c>
       <c r="P40">
         <v>73242</v>
@@ -2680,16 +2680,16 @@
         <v>0</v>
       </c>
       <c r="G41">
-        <v>19163</v>
+        <v>19562</v>
       </c>
       <c r="H41">
-        <v>357</v>
+        <v>303</v>
       </c>
       <c r="I41">
         <v>0</v>
       </c>
       <c r="J41">
-        <v>488</v>
+        <v>529</v>
       </c>
       <c r="K41">
         <v>0</v>
@@ -2704,7 +2704,7 @@
         <v>27</v>
       </c>
       <c r="O41">
-        <v>18073</v>
+        <v>18443</v>
       </c>
       <c r="P41">
         <v>85249</v>
@@ -2748,13 +2748,13 @@
         <v>0</v>
       </c>
       <c r="J42">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="K42">
         <v>0</v>
       </c>
       <c r="L42">
-        <v>6119</v>
+        <v>6156</v>
       </c>
       <c r="M42">
         <v>0</v>
@@ -2763,7 +2763,7 @@
         <v>416</v>
       </c>
       <c r="O42">
-        <v>23538</v>
+        <v>24102</v>
       </c>
       <c r="P42">
         <v>41861</v>
@@ -2798,34 +2798,34 @@
         <v>0</v>
       </c>
       <c r="G43">
-        <v>29027</v>
+        <v>29390</v>
       </c>
       <c r="H43">
-        <v>320</v>
+        <v>120</v>
       </c>
       <c r="I43">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J43">
-        <v>125</v>
+        <v>94</v>
       </c>
       <c r="K43">
         <v>0</v>
       </c>
       <c r="L43">
-        <v>6300</v>
+        <v>6486</v>
       </c>
       <c r="M43">
         <v>1</v>
       </c>
       <c r="N43">
-        <v>647</v>
+        <v>785</v>
       </c>
       <c r="O43">
-        <v>22692</v>
+        <v>23351</v>
       </c>
       <c r="P43">
-        <v>39766</v>
+        <v>41231</v>
       </c>
       <c r="Q43">
         <v>5277</v>
@@ -2851,37 +2851,37 @@
         <v>0</v>
       </c>
       <c r="E44">
-        <v>21880</v>
+        <v>21882</v>
       </c>
       <c r="F44">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G44">
-        <v>19229</v>
+        <v>19739</v>
       </c>
       <c r="H44">
-        <v>1493</v>
+        <v>1045</v>
       </c>
       <c r="I44">
         <v>0</v>
       </c>
       <c r="J44">
-        <v>841</v>
+        <v>1028</v>
       </c>
       <c r="K44">
         <v>0</v>
       </c>
       <c r="L44">
-        <v>4577</v>
+        <v>4606</v>
       </c>
       <c r="M44">
         <v>0</v>
       </c>
       <c r="N44">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O44">
-        <v>15126</v>
+        <v>15465</v>
       </c>
       <c r="P44">
         <v>68393</v>
@@ -2910,22 +2910,22 @@
         <v>0</v>
       </c>
       <c r="E45">
-        <v>19928</v>
+        <v>19934</v>
       </c>
       <c r="F45">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G45">
-        <v>14347</v>
+        <v>14501</v>
       </c>
       <c r="H45">
-        <v>2381</v>
+        <v>2299</v>
       </c>
       <c r="I45">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J45">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="K45">
         <v>0</v>
@@ -2937,10 +2937,10 @@
         <v>1</v>
       </c>
       <c r="N45">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="O45">
-        <v>12832</v>
+        <v>12972</v>
       </c>
       <c r="P45">
         <v>76002</v>
@@ -2969,37 +2969,37 @@
         <v>0</v>
       </c>
       <c r="E46">
-        <v>21511</v>
+        <v>21512</v>
       </c>
       <c r="F46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G46">
-        <v>18995</v>
+        <v>19510</v>
       </c>
       <c r="H46">
-        <v>2517</v>
+        <v>2002</v>
       </c>
       <c r="I46">
         <v>0</v>
       </c>
       <c r="J46">
-        <v>1089</v>
+        <v>972</v>
       </c>
       <c r="K46">
         <v>0</v>
       </c>
       <c r="L46">
-        <v>5535</v>
+        <v>6032</v>
       </c>
       <c r="M46">
         <v>0</v>
       </c>
       <c r="N46">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="O46">
-        <v>14599</v>
+        <v>15211</v>
       </c>
       <c r="P46">
         <v>64160</v>
@@ -3034,7 +3034,7 @@
         <v>5</v>
       </c>
       <c r="G47">
-        <v>19221</v>
+        <v>19381</v>
       </c>
       <c r="H47">
         <v>2090</v>
@@ -3043,13 +3043,13 @@
         <v>70</v>
       </c>
       <c r="J47">
-        <v>270</v>
+        <v>205</v>
       </c>
       <c r="K47">
         <v>0</v>
       </c>
       <c r="L47">
-        <v>1511</v>
+        <v>1587</v>
       </c>
       <c r="M47">
         <v>1</v>
@@ -3058,7 +3058,7 @@
         <v>64</v>
       </c>
       <c r="O47">
-        <v>17657</v>
+        <v>17815</v>
       </c>
       <c r="P47">
         <v>49875</v>
@@ -3093,16 +3093,16 @@
         <v>47</v>
       </c>
       <c r="G48">
-        <v>19356</v>
+        <v>19370</v>
       </c>
       <c r="H48">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="I48">
         <v>6</v>
       </c>
       <c r="J48">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="K48">
         <v>0</v>
@@ -3117,7 +3117,7 @@
         <v>212</v>
       </c>
       <c r="O48">
-        <v>18590</v>
+        <v>18595</v>
       </c>
       <c r="P48">
         <v>54142</v>
@@ -3152,16 +3152,16 @@
         <v>23</v>
       </c>
       <c r="G49">
-        <v>16450</v>
+        <v>16908</v>
       </c>
       <c r="H49">
-        <v>1033</v>
+        <v>927</v>
       </c>
       <c r="I49">
         <v>67</v>
       </c>
       <c r="J49">
-        <v>169</v>
+        <v>217</v>
       </c>
       <c r="K49">
         <v>0</v>
@@ -3173,10 +3173,10 @@
         <v>0</v>
       </c>
       <c r="N49">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="O49">
-        <v>14396</v>
+        <v>14908</v>
       </c>
       <c r="P49">
         <v>49949</v>
@@ -3211,31 +3211,31 @@
         <v>0</v>
       </c>
       <c r="G50">
-        <v>19376</v>
+        <v>19686</v>
       </c>
       <c r="H50">
-        <v>1712</v>
+        <v>1538</v>
       </c>
       <c r="I50">
         <v>4</v>
       </c>
       <c r="J50">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="K50">
         <v>0</v>
       </c>
       <c r="L50">
-        <v>3214</v>
+        <v>3254</v>
       </c>
       <c r="M50">
         <v>5</v>
       </c>
       <c r="N50">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O50">
-        <v>17721</v>
+        <v>18209</v>
       </c>
       <c r="P50">
         <v>63298</v>
@@ -3270,31 +3270,31 @@
         <v>0</v>
       </c>
       <c r="G51">
-        <v>20638</v>
+        <v>21030</v>
       </c>
       <c r="H51">
-        <v>1420</v>
+        <v>1107</v>
       </c>
       <c r="I51">
         <v>0</v>
       </c>
       <c r="J51">
-        <v>153</v>
+        <v>70</v>
       </c>
       <c r="K51">
         <v>0</v>
       </c>
       <c r="L51">
-        <v>3597</v>
+        <v>3924</v>
       </c>
       <c r="M51">
         <v>11</v>
       </c>
       <c r="N51">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="O51">
-        <v>16749</v>
+        <v>17316</v>
       </c>
       <c r="P51">
         <v>71754</v>
@@ -3329,22 +3329,22 @@
         <v>0</v>
       </c>
       <c r="G52">
-        <v>20355</v>
+        <v>20534</v>
       </c>
       <c r="H52">
-        <v>195</v>
+        <v>142</v>
       </c>
       <c r="I52">
         <v>0</v>
       </c>
       <c r="J52">
-        <v>266</v>
+        <v>353</v>
       </c>
       <c r="K52">
         <v>1</v>
       </c>
       <c r="L52">
-        <v>2245</v>
+        <v>2246</v>
       </c>
       <c r="M52">
         <v>1</v>
@@ -3353,7 +3353,7 @@
         <v>18</v>
       </c>
       <c r="O52">
-        <v>19677</v>
+        <v>19928</v>
       </c>
       <c r="P52">
         <v>63986</v>
@@ -3397,19 +3397,19 @@
         <v>0</v>
       </c>
       <c r="J53">
-        <v>782</v>
+        <v>816</v>
       </c>
       <c r="K53">
         <v>0</v>
       </c>
       <c r="L53">
-        <v>2607</v>
+        <v>2615</v>
       </c>
       <c r="M53">
         <v>1</v>
       </c>
       <c r="N53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O53">
         <v>18140</v>
@@ -3447,31 +3447,31 @@
         <v>0</v>
       </c>
       <c r="G54">
-        <v>19880</v>
+        <v>20053</v>
       </c>
       <c r="H54">
-        <v>694</v>
+        <v>524</v>
       </c>
       <c r="I54">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="J54">
-        <v>581</v>
+        <v>549</v>
       </c>
       <c r="K54">
-        <v>225</v>
+        <v>203</v>
       </c>
       <c r="L54">
-        <v>1441</v>
+        <v>1494</v>
       </c>
       <c r="M54">
         <v>3</v>
       </c>
       <c r="N54">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="O54">
-        <v>17419</v>
+        <v>17557</v>
       </c>
       <c r="P54">
         <v>58440</v>
@@ -3506,31 +3506,31 @@
         <v>0</v>
       </c>
       <c r="G55">
-        <v>15748</v>
+        <v>15789</v>
       </c>
       <c r="H55">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="I55">
         <v>5</v>
       </c>
       <c r="J55">
-        <v>681</v>
+        <v>627</v>
       </c>
       <c r="K55">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="L55">
-        <v>1291</v>
+        <v>1340</v>
       </c>
       <c r="M55">
         <v>0</v>
       </c>
       <c r="N55">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="O55">
-        <v>14877</v>
+        <v>14972</v>
       </c>
       <c r="P55">
         <v>58215</v>
@@ -3565,16 +3565,16 @@
         <v>0</v>
       </c>
       <c r="G56">
-        <v>17895</v>
+        <v>18179</v>
       </c>
       <c r="H56">
-        <v>370</v>
+        <v>197</v>
       </c>
       <c r="I56">
         <v>0</v>
       </c>
       <c r="J56">
-        <v>1201</v>
+        <v>1278</v>
       </c>
       <c r="K56">
         <v>359</v>
@@ -3586,10 +3586,10 @@
         <v>1</v>
       </c>
       <c r="N56">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="O56">
-        <v>13770</v>
+        <v>13971</v>
       </c>
       <c r="P56">
         <v>46365</v>
@@ -3624,22 +3624,22 @@
         <v>0</v>
       </c>
       <c r="G57">
-        <v>21004</v>
+        <v>21025</v>
       </c>
       <c r="H57">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="I57">
         <v>0</v>
       </c>
       <c r="J57">
-        <v>445</v>
+        <v>284</v>
       </c>
       <c r="K57">
-        <v>170</v>
+        <v>48</v>
       </c>
       <c r="L57">
-        <v>1435</v>
+        <v>1598</v>
       </c>
       <c r="M57">
         <v>0</v>
@@ -3648,7 +3648,7 @@
         <v>35</v>
       </c>
       <c r="O57">
-        <v>20361</v>
+        <v>20441</v>
       </c>
       <c r="P57">
         <v>61556</v>
@@ -3683,31 +3683,31 @@
         <v>0</v>
       </c>
       <c r="G58">
-        <v>19609</v>
+        <v>20296</v>
       </c>
       <c r="H58">
-        <v>2429</v>
+        <v>1974</v>
       </c>
       <c r="I58">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="J58">
-        <v>1768</v>
+        <v>1894</v>
       </c>
       <c r="K58">
-        <v>750</v>
+        <v>585</v>
       </c>
       <c r="L58">
-        <v>4373</v>
+        <v>4571</v>
       </c>
       <c r="M58">
         <v>2</v>
       </c>
       <c r="N58">
-        <v>171</v>
+        <v>204</v>
       </c>
       <c r="O58">
-        <v>14255</v>
+        <v>14812</v>
       </c>
       <c r="P58">
         <v>57577</v>
@@ -3742,31 +3742,31 @@
         <v>0</v>
       </c>
       <c r="G59">
-        <v>18722</v>
+        <v>18755</v>
       </c>
       <c r="H59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I59">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="J59">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="K59">
         <v>0</v>
       </c>
       <c r="L59">
-        <v>2470</v>
+        <v>2485</v>
       </c>
       <c r="M59">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N59">
-        <v>235</v>
+        <v>263</v>
       </c>
       <c r="O59">
-        <v>15989</v>
+        <v>15990</v>
       </c>
       <c r="P59">
         <v>60495</v>
@@ -3801,16 +3801,16 @@
         <v>0</v>
       </c>
       <c r="G60">
-        <v>21755</v>
+        <v>22032</v>
       </c>
       <c r="H60">
-        <v>830</v>
+        <v>691</v>
       </c>
       <c r="I60">
         <v>0</v>
       </c>
       <c r="J60">
-        <v>934</v>
+        <v>1005</v>
       </c>
       <c r="K60">
         <v>75</v>
@@ -3822,10 +3822,10 @@
         <v>0</v>
       </c>
       <c r="N60">
-        <v>137</v>
+        <v>195</v>
       </c>
       <c r="O60">
-        <v>20279</v>
+        <v>20428</v>
       </c>
       <c r="P60">
         <v>70140</v>
@@ -3869,16 +3869,16 @@
         <v>0</v>
       </c>
       <c r="J61">
-        <v>554</v>
+        <v>500</v>
       </c>
       <c r="K61">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="L61">
-        <v>9429</v>
+        <v>9496</v>
       </c>
       <c r="M61">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N61">
         <v>1</v>
@@ -3919,31 +3919,31 @@
         <v>0</v>
       </c>
       <c r="G62">
-        <v>14791</v>
+        <v>15009</v>
       </c>
       <c r="H62">
-        <v>590</v>
+        <v>569</v>
       </c>
       <c r="I62">
         <v>200</v>
       </c>
       <c r="J62">
-        <v>580</v>
+        <v>603</v>
       </c>
       <c r="K62">
         <v>0</v>
       </c>
       <c r="L62">
-        <v>3416</v>
+        <v>3426</v>
       </c>
       <c r="M62">
         <v>1</v>
       </c>
       <c r="N62">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="O62">
-        <v>14038</v>
+        <v>14200</v>
       </c>
       <c r="P62">
         <v>51334</v>
@@ -3978,31 +3978,31 @@
         <v>0</v>
       </c>
       <c r="G63">
-        <v>36329</v>
+        <v>36417</v>
       </c>
       <c r="H63">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="I63">
-        <v>119</v>
+        <v>94</v>
       </c>
       <c r="J63">
-        <v>182</v>
+        <v>117</v>
       </c>
       <c r="K63">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="L63">
-        <v>10149</v>
+        <v>10271</v>
       </c>
       <c r="M63">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N63">
-        <v>714</v>
+        <v>748</v>
       </c>
       <c r="O63">
-        <v>30645</v>
+        <v>31053</v>
       </c>
       <c r="P63">
         <v>68691</v>
@@ -4037,31 +4037,31 @@
         <v>0</v>
       </c>
       <c r="G64">
-        <v>38252</v>
+        <v>38577</v>
       </c>
       <c r="H64">
-        <v>2185</v>
+        <v>1950</v>
       </c>
       <c r="I64">
         <v>7</v>
       </c>
       <c r="J64">
-        <v>182</v>
+        <v>87</v>
       </c>
       <c r="K64">
         <v>0</v>
       </c>
       <c r="L64">
-        <v>8672</v>
+        <v>8795</v>
       </c>
       <c r="M64">
         <v>8</v>
       </c>
       <c r="N64">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O64">
-        <v>33210</v>
+        <v>34250</v>
       </c>
       <c r="P64">
         <v>60527</v>
@@ -4096,31 +4096,31 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>31449</v>
+        <v>32454</v>
       </c>
       <c r="H65">
-        <v>8512</v>
+        <v>7101</v>
       </c>
       <c r="I65">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="J65">
-        <v>737</v>
+        <v>932</v>
       </c>
       <c r="K65">
         <v>0</v>
       </c>
       <c r="L65">
-        <v>8462</v>
+        <v>8678</v>
       </c>
       <c r="M65">
         <v>1</v>
       </c>
       <c r="N65">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="O65">
-        <v>22301</v>
+        <v>22882</v>
       </c>
       <c r="P65">
         <v>34607</v>
@@ -4155,31 +4155,31 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>43046</v>
+        <v>44579</v>
       </c>
       <c r="H66">
-        <v>12903</v>
+        <v>11802</v>
       </c>
       <c r="I66">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="J66">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="K66">
         <v>0</v>
       </c>
       <c r="L66">
-        <v>8174</v>
+        <v>8436</v>
       </c>
       <c r="M66">
         <v>2</v>
       </c>
       <c r="N66">
-        <v>226</v>
+        <v>309</v>
       </c>
       <c r="O66">
-        <v>36756</v>
+        <v>38187</v>
       </c>
       <c r="P66">
         <v>93810</v>
@@ -4208,37 +4208,37 @@
         <v>0</v>
       </c>
       <c r="E67">
-        <v>68799</v>
+        <v>68811</v>
       </c>
       <c r="F67">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G67">
-        <v>57884</v>
+        <v>58474</v>
       </c>
       <c r="H67">
-        <v>4077</v>
+        <v>3341</v>
       </c>
       <c r="I67">
-        <v>2018</v>
+        <v>1982</v>
       </c>
       <c r="J67">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="K67">
         <v>0</v>
       </c>
       <c r="L67">
-        <v>16159</v>
+        <v>16425</v>
       </c>
       <c r="M67">
         <v>9</v>
       </c>
       <c r="N67">
-        <v>623</v>
+        <v>646</v>
       </c>
       <c r="O67">
-        <v>45047</v>
+        <v>45463</v>
       </c>
       <c r="P67">
         <v>78022</v>
@@ -4267,40 +4267,40 @@
         <v>0</v>
       </c>
       <c r="E68">
-        <v>65352</v>
+        <v>65358</v>
       </c>
       <c r="F68">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="G68">
-        <v>57099</v>
+        <v>57842</v>
       </c>
       <c r="H68">
-        <v>7088</v>
+        <v>6392</v>
       </c>
       <c r="I68">
-        <v>696</v>
+        <v>666</v>
       </c>
       <c r="J68">
-        <v>245</v>
+        <v>267</v>
       </c>
       <c r="K68">
         <v>0</v>
       </c>
       <c r="L68">
-        <v>13636</v>
+        <v>13972</v>
       </c>
       <c r="M68">
         <v>2</v>
       </c>
       <c r="N68">
-        <v>231</v>
+        <v>279</v>
       </c>
       <c r="O68">
-        <v>47763</v>
+        <v>48532</v>
       </c>
       <c r="P68">
-        <v>61098</v>
+        <v>61125</v>
       </c>
       <c r="Q68">
         <v>7850</v>
@@ -4332,34 +4332,34 @@
         <v>0</v>
       </c>
       <c r="G69">
-        <v>34272</v>
+        <v>35040</v>
       </c>
       <c r="H69">
-        <v>6484</v>
+        <v>5772</v>
       </c>
       <c r="I69">
         <v>84</v>
       </c>
       <c r="J69">
-        <v>160</v>
+        <v>326</v>
       </c>
       <c r="K69">
         <v>0</v>
       </c>
       <c r="L69">
-        <v>12342</v>
+        <v>12664</v>
       </c>
       <c r="M69">
         <v>2</v>
       </c>
       <c r="N69">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="O69">
-        <v>25874</v>
+        <v>26182</v>
       </c>
       <c r="P69">
-        <v>32963</v>
+        <v>33788</v>
       </c>
       <c r="Q69">
         <v>6528</v>
@@ -4391,31 +4391,31 @@
         <v>0</v>
       </c>
       <c r="G70">
-        <v>41889</v>
+        <v>42378</v>
       </c>
       <c r="H70">
-        <v>2642</v>
+        <v>1938</v>
       </c>
       <c r="I70">
-        <v>2033</v>
+        <v>1954</v>
       </c>
       <c r="J70">
-        <v>410</v>
+        <v>73</v>
       </c>
       <c r="K70">
         <v>0</v>
       </c>
       <c r="L70">
-        <v>16230</v>
+        <v>16726</v>
       </c>
       <c r="M70">
         <v>2</v>
       </c>
       <c r="N70">
-        <v>259</v>
+        <v>411</v>
       </c>
       <c r="O70">
-        <v>33658</v>
+        <v>33965</v>
       </c>
       <c r="P70">
         <v>42040</v>
@@ -4450,31 +4450,31 @@
         <v>0</v>
       </c>
       <c r="G71">
-        <v>43235</v>
+        <v>43982</v>
       </c>
       <c r="H71">
-        <v>4957</v>
+        <v>4731</v>
       </c>
       <c r="I71">
-        <v>1457</v>
+        <v>1020</v>
       </c>
       <c r="J71">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="K71">
         <v>0</v>
       </c>
       <c r="L71">
-        <v>19812</v>
+        <v>19916</v>
       </c>
       <c r="M71">
         <v>1</v>
       </c>
       <c r="N71">
-        <v>1289</v>
+        <v>1845</v>
       </c>
       <c r="O71">
-        <v>30963</v>
+        <v>31054</v>
       </c>
       <c r="P71">
         <v>48896</v>
@@ -4503,37 +4503,37 @@
         <v>0</v>
       </c>
       <c r="E72">
-        <v>61541</v>
+        <v>61542</v>
       </c>
       <c r="F72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G72">
-        <v>48571</v>
+        <v>49552</v>
       </c>
       <c r="H72">
-        <v>10534</v>
+        <v>9683</v>
       </c>
       <c r="I72">
-        <v>1587</v>
+        <v>1475</v>
       </c>
       <c r="J72">
-        <v>154</v>
+        <v>27</v>
       </c>
       <c r="K72">
         <v>0</v>
       </c>
       <c r="L72">
-        <v>14069</v>
+        <v>14402</v>
       </c>
       <c r="M72">
         <v>9</v>
       </c>
       <c r="N72">
-        <v>174</v>
+        <v>238</v>
       </c>
       <c r="O72">
-        <v>37542</v>
+        <v>38281</v>
       </c>
       <c r="P72">
         <v>85505</v>
@@ -4562,37 +4562,37 @@
         <v>0</v>
       </c>
       <c r="E73">
-        <v>58911</v>
+        <v>58915</v>
       </c>
       <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73">
+        <v>42150</v>
+      </c>
+      <c r="H73">
+        <v>15172</v>
+      </c>
+      <c r="I73">
+        <v>220</v>
+      </c>
+      <c r="J73">
+        <v>267</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+      <c r="L73">
+        <v>8020</v>
+      </c>
+      <c r="M73">
         <v>4</v>
       </c>
-      <c r="G73">
-        <v>39717</v>
-      </c>
-      <c r="H73">
-        <v>17418</v>
-      </c>
-      <c r="I73">
-        <v>313</v>
-      </c>
-      <c r="J73">
-        <v>150</v>
-      </c>
-      <c r="K73">
-        <v>0</v>
-      </c>
-      <c r="L73">
-        <v>7632</v>
-      </c>
-      <c r="M73">
-        <v>3</v>
-      </c>
       <c r="N73">
-        <v>131</v>
+        <v>244</v>
       </c>
       <c r="O73">
-        <v>34797</v>
+        <v>36661</v>
       </c>
       <c r="P73">
         <v>67550</v>
@@ -4618,40 +4618,40 @@
         <v>0</v>
       </c>
       <c r="E74">
-        <v>2427309</v>
+        <v>2427694</v>
       </c>
       <c r="F74">
-        <v>3073</v>
+        <v>2688</v>
       </c>
       <c r="G74">
-        <v>1786121</v>
+        <v>1832841</v>
       </c>
       <c r="H74">
-        <v>473395</v>
+        <v>435241</v>
       </c>
       <c r="I74">
-        <v>14170</v>
+        <v>12813</v>
       </c>
       <c r="J74">
-        <v>78550</v>
+        <v>74463</v>
       </c>
       <c r="K74">
-        <v>33280</v>
+        <v>32410</v>
       </c>
       <c r="L74">
-        <v>368237</v>
+        <v>384609</v>
       </c>
       <c r="M74">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="N74">
-        <v>18540</v>
+        <v>21179</v>
       </c>
       <c r="O74">
-        <v>1492135</v>
+        <v>1536853</v>
       </c>
       <c r="P74">
-        <v>4163342</v>
+        <v>4205101</v>
       </c>
       <c r="Q74">
         <v>629720</v>

--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -491,25 +491,25 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>51501</v>
+        <v>51528</v>
       </c>
       <c r="F4">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>21961</v>
+        <v>22368</v>
       </c>
       <c r="H4">
-        <v>20289</v>
+        <v>21971</v>
       </c>
       <c r="I4">
         <v>29</v>
       </c>
       <c r="J4">
-        <v>6034</v>
+        <v>6217</v>
       </c>
       <c r="K4">
-        <v>2371</v>
+        <v>3203</v>
       </c>
       <c r="L4">
         <v>1621</v>
@@ -521,7 +521,7 @@
         <v>95</v>
       </c>
       <c r="O4">
-        <v>15381</v>
+        <v>15605</v>
       </c>
       <c r="P4">
         <v>53812</v>
@@ -556,22 +556,22 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>34764</v>
+        <v>35689</v>
       </c>
       <c r="H5">
-        <v>12612</v>
+        <v>13209</v>
       </c>
       <c r="I5">
         <v>7</v>
       </c>
       <c r="J5">
-        <v>3363</v>
+        <v>3461</v>
       </c>
       <c r="K5">
-        <v>1341</v>
+        <v>1671</v>
       </c>
       <c r="L5">
-        <v>2713</v>
+        <v>2761</v>
       </c>
       <c r="M5">
         <v>40</v>
@@ -580,7 +580,7 @@
         <v>297</v>
       </c>
       <c r="O5">
-        <v>30211</v>
+        <v>31122</v>
       </c>
       <c r="P5">
         <v>54384</v>
@@ -615,19 +615,19 @@
         <v>2</v>
       </c>
       <c r="G6">
-        <v>18745</v>
+        <v>19286</v>
       </c>
       <c r="H6">
-        <v>11356</v>
+        <v>12738</v>
       </c>
       <c r="I6">
-        <v>154</v>
+        <v>246</v>
       </c>
       <c r="J6">
-        <v>1601</v>
+        <v>1611</v>
       </c>
       <c r="K6">
-        <v>939</v>
+        <v>1045</v>
       </c>
       <c r="L6">
         <v>1358</v>
@@ -636,13 +636,13 @@
         <v>26</v>
       </c>
       <c r="N6">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="O6">
-        <v>15671</v>
+        <v>16202</v>
       </c>
       <c r="P6">
-        <v>42630</v>
+        <v>43508</v>
       </c>
       <c r="Q6">
         <v>17918</v>
@@ -674,31 +674,31 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>23446</v>
+        <v>23987</v>
       </c>
       <c r="H7">
-        <v>14891</v>
+        <v>14812</v>
       </c>
       <c r="I7">
         <v>364</v>
       </c>
       <c r="J7">
-        <v>4182</v>
+        <v>4187</v>
       </c>
       <c r="K7">
-        <v>2858</v>
+        <v>3031</v>
       </c>
       <c r="L7">
-        <v>1023</v>
+        <v>1027</v>
       </c>
       <c r="M7">
         <v>28</v>
       </c>
       <c r="N7">
-        <v>336</v>
+        <v>384</v>
       </c>
       <c r="O7">
-        <v>18297</v>
+        <v>18869</v>
       </c>
       <c r="P7">
         <v>77581</v>
@@ -727,25 +727,25 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>40539</v>
+        <v>40548</v>
       </c>
       <c r="F8">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G8">
-        <v>20594</v>
+        <v>21243</v>
       </c>
       <c r="H8">
-        <v>19940</v>
+        <v>19291</v>
       </c>
       <c r="I8">
         <v>18</v>
       </c>
       <c r="J8">
-        <v>7832</v>
+        <v>8137</v>
       </c>
       <c r="K8">
-        <v>3640</v>
+        <v>3930</v>
       </c>
       <c r="L8">
         <v>2999</v>
@@ -754,13 +754,13 @@
         <v>16</v>
       </c>
       <c r="N8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O8">
-        <v>9425</v>
+        <v>9768</v>
       </c>
       <c r="P8">
-        <v>13958</v>
+        <v>14385</v>
       </c>
       <c r="Q8">
         <v>20902</v>
@@ -792,19 +792,19 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>28479</v>
+        <v>29149</v>
       </c>
       <c r="H9">
-        <v>13678</v>
+        <v>13518</v>
       </c>
       <c r="I9">
         <v>389</v>
       </c>
       <c r="J9">
-        <v>4710</v>
+        <v>4795</v>
       </c>
       <c r="K9">
-        <v>3131</v>
+        <v>3736</v>
       </c>
       <c r="L9">
         <v>536</v>
@@ -816,7 +816,7 @@
         <v>147</v>
       </c>
       <c r="O9">
-        <v>22975</v>
+        <v>23560</v>
       </c>
       <c r="P9">
         <v>50354</v>
@@ -851,19 +851,19 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>26066</v>
+        <v>26506</v>
       </c>
       <c r="H10">
-        <v>10129</v>
+        <v>9990</v>
       </c>
       <c r="I10">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J10">
-        <v>7432</v>
+        <v>7585</v>
       </c>
       <c r="K10">
-        <v>4664</v>
+        <v>5113</v>
       </c>
       <c r="L10">
         <v>1091</v>
@@ -872,16 +872,16 @@
         <v>9</v>
       </c>
       <c r="N10">
-        <v>185</v>
+        <v>240</v>
       </c>
       <c r="O10">
-        <v>17558</v>
+        <v>17790</v>
       </c>
       <c r="P10">
-        <v>11669</v>
+        <v>12194</v>
       </c>
       <c r="Q10">
-        <v>9525</v>
+        <v>9518</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -910,19 +910,19 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>29717</v>
+        <v>30640</v>
       </c>
       <c r="H11">
-        <v>17488</v>
+        <v>17221</v>
       </c>
       <c r="I11">
-        <v>551</v>
+        <v>611</v>
       </c>
       <c r="J11">
-        <v>3443</v>
+        <v>3579</v>
       </c>
       <c r="K11">
-        <v>1675</v>
+        <v>1841</v>
       </c>
       <c r="L11">
         <v>532</v>
@@ -931,13 +931,13 @@
         <v>1</v>
       </c>
       <c r="N11">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="O11">
-        <v>25541</v>
+        <v>26303</v>
       </c>
       <c r="P11">
-        <v>72059</v>
+        <v>75787</v>
       </c>
       <c r="Q11">
         <v>23805</v>
@@ -969,34 +969,34 @@
         <v>119</v>
       </c>
       <c r="G12">
-        <v>19016</v>
+        <v>19975</v>
       </c>
       <c r="H12">
-        <v>20990</v>
+        <v>20031</v>
       </c>
       <c r="I12">
-        <v>56</v>
+        <v>204</v>
       </c>
       <c r="J12">
-        <v>7623</v>
+        <v>7775</v>
       </c>
       <c r="K12">
-        <v>4598</v>
+        <v>5099</v>
       </c>
       <c r="L12">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="M12">
         <v>2</v>
       </c>
       <c r="N12">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="O12">
-        <v>11015</v>
+        <v>11780</v>
       </c>
       <c r="P12">
-        <v>41963</v>
+        <v>42636</v>
       </c>
       <c r="Q12">
         <v>17907</v>
@@ -1022,25 +1022,25 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>36860</v>
+        <v>36863</v>
       </c>
       <c r="F13">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G13">
-        <v>21417</v>
+        <v>22084</v>
       </c>
       <c r="H13">
-        <v>12723</v>
+        <v>12709</v>
       </c>
       <c r="I13">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J13">
-        <v>3197</v>
+        <v>3296</v>
       </c>
       <c r="K13">
-        <v>1251</v>
+        <v>1477</v>
       </c>
       <c r="L13">
         <v>13</v>
@@ -1049,13 +1049,13 @@
         <v>0</v>
       </c>
       <c r="N13">
-        <v>1587</v>
+        <v>1661</v>
       </c>
       <c r="O13">
-        <v>16626</v>
+        <v>17120</v>
       </c>
       <c r="P13">
-        <v>54271</v>
+        <v>54599</v>
       </c>
       <c r="Q13">
         <v>16822</v>
@@ -1087,19 +1087,19 @@
         <v>4</v>
       </c>
       <c r="G14">
-        <v>26496</v>
+        <v>27110</v>
       </c>
       <c r="H14">
-        <v>11645</v>
+        <v>12739</v>
       </c>
       <c r="I14">
-        <v>722</v>
+        <v>769</v>
       </c>
       <c r="J14">
-        <v>7509</v>
+        <v>7663</v>
       </c>
       <c r="K14">
-        <v>4580</v>
+        <v>4888</v>
       </c>
       <c r="L14">
         <v>1138</v>
@@ -1108,13 +1108,13 @@
         <v>27</v>
       </c>
       <c r="N14">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="O14">
-        <v>17951</v>
+        <v>18397</v>
       </c>
       <c r="P14">
-        <v>36774</v>
+        <v>38577</v>
       </c>
       <c r="Q14">
         <v>20044</v>
@@ -1146,37 +1146,37 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>36385</v>
+        <v>37076</v>
       </c>
       <c r="H15">
-        <v>6200</v>
+        <v>5514</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J15">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15">
-        <v>7801</v>
+        <v>7914</v>
       </c>
       <c r="M15">
         <v>0</v>
       </c>
       <c r="N15">
-        <v>982</v>
+        <v>1015</v>
       </c>
       <c r="O15">
-        <v>33186</v>
+        <v>33703</v>
       </c>
       <c r="P15">
         <v>67178</v>
       </c>
       <c r="Q15">
-        <v>5009</v>
+        <v>5008</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -1199,37 +1199,37 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>25302</v>
+        <v>25324</v>
       </c>
       <c r="F16">
-        <v>247</v>
+        <v>225</v>
       </c>
       <c r="G16">
-        <v>17068</v>
+        <v>17672</v>
       </c>
       <c r="H16">
-        <v>7296</v>
+        <v>6764</v>
       </c>
       <c r="I16">
-        <v>78</v>
+        <v>223</v>
       </c>
       <c r="J16">
-        <v>149</v>
+        <v>217</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
       <c r="L16">
-        <v>9522</v>
+        <v>9923</v>
       </c>
       <c r="M16">
         <v>0</v>
       </c>
       <c r="N16">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="O16">
-        <v>10289</v>
+        <v>10509</v>
       </c>
       <c r="P16">
         <v>67034</v>
@@ -1264,31 +1264,31 @@
         <v>13</v>
       </c>
       <c r="G17">
-        <v>22826</v>
+        <v>23754</v>
       </c>
       <c r="H17">
-        <v>3551</v>
+        <v>3287</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J17">
-        <v>152</v>
+        <v>228</v>
       </c>
       <c r="K17">
         <v>0</v>
       </c>
       <c r="L17">
-        <v>7103</v>
+        <v>7420</v>
       </c>
       <c r="M17">
         <v>2</v>
       </c>
       <c r="N17">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="O17">
-        <v>20701</v>
+        <v>21293</v>
       </c>
       <c r="P17">
         <v>65453</v>
@@ -1317,43 +1317,43 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>47722</v>
+        <v>47725</v>
       </c>
       <c r="F18">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="G18">
-        <v>41278</v>
+        <v>41933</v>
       </c>
       <c r="H18">
-        <v>3948</v>
+        <v>4742</v>
       </c>
       <c r="I18">
-        <v>1022</v>
+        <v>1110</v>
       </c>
       <c r="J18">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="K18">
         <v>0</v>
       </c>
       <c r="L18">
-        <v>6437</v>
+        <v>6477</v>
       </c>
       <c r="M18">
         <v>3</v>
       </c>
       <c r="N18">
-        <v>1128</v>
+        <v>1140</v>
       </c>
       <c r="O18">
-        <v>37190</v>
+        <v>37812</v>
       </c>
       <c r="P18">
         <v>69692</v>
       </c>
       <c r="Q18">
-        <v>6901</v>
+        <v>6892</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -1376,37 +1376,37 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>56313</v>
+        <v>56345</v>
       </c>
       <c r="F19">
-        <v>177</v>
+        <v>145</v>
       </c>
       <c r="G19">
-        <v>46242</v>
+        <v>46950</v>
       </c>
       <c r="H19">
-        <v>9644</v>
+        <v>8903</v>
       </c>
       <c r="I19">
-        <v>53</v>
+        <v>161</v>
       </c>
       <c r="J19">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="K19">
         <v>0</v>
       </c>
       <c r="L19">
-        <v>11810</v>
+        <v>11978</v>
       </c>
       <c r="M19">
         <v>1</v>
       </c>
       <c r="N19">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="O19">
-        <v>40553</v>
+        <v>41150</v>
       </c>
       <c r="P19">
         <v>105570</v>
@@ -1435,28 +1435,28 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>34984</v>
+        <v>34985</v>
       </c>
       <c r="F20">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G20">
-        <v>31346</v>
+        <v>31715</v>
       </c>
       <c r="H20">
-        <v>2555</v>
+        <v>2817</v>
       </c>
       <c r="I20">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J20">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="K20">
         <v>0</v>
       </c>
       <c r="L20">
-        <v>5380</v>
+        <v>5385</v>
       </c>
       <c r="M20">
         <v>5</v>
@@ -1465,7 +1465,7 @@
         <v>178</v>
       </c>
       <c r="O20">
-        <v>28538</v>
+        <v>29447</v>
       </c>
       <c r="P20">
         <v>75257</v>
@@ -1509,13 +1509,13 @@
         <v>0</v>
       </c>
       <c r="J21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21">
         <v>0</v>
       </c>
       <c r="L21">
-        <v>3885</v>
+        <v>3886</v>
       </c>
       <c r="M21">
         <v>3</v>
@@ -1559,31 +1559,31 @@
         <v>0</v>
       </c>
       <c r="G22">
-        <v>17766</v>
+        <v>17928</v>
       </c>
       <c r="H22">
-        <v>619</v>
+        <v>457</v>
       </c>
       <c r="I22">
         <v>0</v>
       </c>
       <c r="J22">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="K22">
         <v>0</v>
       </c>
       <c r="L22">
-        <v>7183</v>
+        <v>7212</v>
       </c>
       <c r="M22">
         <v>0</v>
       </c>
       <c r="N22">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O22">
-        <v>16992</v>
+        <v>17131</v>
       </c>
       <c r="P22">
         <v>64099</v>
@@ -1621,19 +1621,19 @@
         <v>11796</v>
       </c>
       <c r="H23">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I23">
         <v>0</v>
       </c>
       <c r="J23">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K23">
         <v>0</v>
       </c>
       <c r="L23">
-        <v>2058</v>
+        <v>2069</v>
       </c>
       <c r="M23">
         <v>0</v>
@@ -1677,31 +1677,31 @@
         <v>0</v>
       </c>
       <c r="G24">
-        <v>13532</v>
+        <v>13562</v>
       </c>
       <c r="H24">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J24">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="K24">
         <v>0</v>
       </c>
       <c r="L24">
-        <v>3350</v>
+        <v>3361</v>
       </c>
       <c r="M24">
         <v>0</v>
       </c>
       <c r="N24">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="O24">
-        <v>13227</v>
+        <v>13341</v>
       </c>
       <c r="P24">
         <v>65629</v>
@@ -1736,31 +1736,31 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>18633</v>
+        <v>18684</v>
       </c>
       <c r="H25">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="I25">
+        <v>35</v>
+      </c>
+      <c r="J25">
         <v>28</v>
       </c>
-      <c r="J25">
-        <v>49</v>
-      </c>
       <c r="K25">
         <v>0</v>
       </c>
       <c r="L25">
-        <v>4317</v>
+        <v>4376</v>
       </c>
       <c r="M25">
         <v>0</v>
       </c>
       <c r="N25">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="O25">
-        <v>18191</v>
+        <v>18194</v>
       </c>
       <c r="P25">
         <v>57533</v>
@@ -1795,16 +1795,16 @@
         <v>0</v>
       </c>
       <c r="G26">
-        <v>16383</v>
+        <v>16514</v>
       </c>
       <c r="H26">
-        <v>897</v>
+        <v>918</v>
       </c>
       <c r="I26">
         <v>0</v>
       </c>
       <c r="J26">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="K26">
         <v>0</v>
@@ -1816,10 +1816,10 @@
         <v>3</v>
       </c>
       <c r="N26">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="O26">
-        <v>15130</v>
+        <v>15226</v>
       </c>
       <c r="P26">
         <v>66594</v>
@@ -1854,31 +1854,31 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>21357</v>
+        <v>21864</v>
       </c>
       <c r="H27">
-        <v>17770</v>
+        <v>18983</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27">
-        <v>323</v>
+        <v>216</v>
       </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="L27">
-        <v>3755</v>
+        <v>3981</v>
       </c>
       <c r="M27">
         <v>0</v>
       </c>
       <c r="N27">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O27">
-        <v>20052</v>
+        <v>20666</v>
       </c>
       <c r="P27">
         <v>40115</v>
@@ -1907,37 +1907,37 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>53690</v>
+        <v>53845</v>
       </c>
       <c r="F28">
-        <v>659</v>
+        <v>504</v>
       </c>
       <c r="G28">
-        <v>22265</v>
+        <v>22986</v>
       </c>
       <c r="H28">
-        <v>22250</v>
+        <v>24189</v>
       </c>
       <c r="I28">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="J28">
-        <v>110</v>
+        <v>188</v>
       </c>
       <c r="K28">
         <v>0</v>
       </c>
       <c r="L28">
-        <v>3072</v>
+        <v>3088</v>
       </c>
       <c r="M28">
         <v>11</v>
       </c>
       <c r="N28">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O28">
-        <v>19189</v>
+        <v>19860</v>
       </c>
       <c r="P28">
         <v>80640</v>
@@ -1972,31 +1972,31 @@
         <v>0</v>
       </c>
       <c r="G29">
-        <v>29198</v>
+        <v>31309</v>
       </c>
       <c r="H29">
-        <v>15207</v>
+        <v>14026</v>
       </c>
       <c r="I29">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="J29">
-        <v>226</v>
+        <v>492</v>
       </c>
       <c r="K29">
         <v>0</v>
       </c>
       <c r="L29">
-        <v>4656</v>
+        <v>4686</v>
       </c>
       <c r="M29">
         <v>2</v>
       </c>
       <c r="N29">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="O29">
-        <v>25992</v>
+        <v>27754</v>
       </c>
       <c r="P29">
         <v>83837</v>
@@ -2031,22 +2031,22 @@
         <v>58</v>
       </c>
       <c r="G30">
-        <v>23744</v>
+        <v>24386</v>
       </c>
       <c r="H30">
-        <v>24912</v>
+        <v>24691</v>
       </c>
       <c r="I30">
-        <v>10</v>
+        <v>515</v>
       </c>
       <c r="J30">
-        <v>138</v>
+        <v>205</v>
       </c>
       <c r="K30">
         <v>0</v>
       </c>
       <c r="L30">
-        <v>2196</v>
+        <v>2249</v>
       </c>
       <c r="M30">
         <v>0</v>
@@ -2055,7 +2055,7 @@
         <v>140</v>
       </c>
       <c r="O30">
-        <v>20895</v>
+        <v>21444</v>
       </c>
       <c r="P30">
         <v>86935</v>
@@ -2090,31 +2090,31 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>84177</v>
+        <v>84364</v>
       </c>
       <c r="H31">
-        <v>900</v>
+        <v>1122</v>
       </c>
       <c r="I31">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="J31">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="K31">
         <v>0</v>
       </c>
       <c r="L31">
-        <v>38454</v>
+        <v>38587</v>
       </c>
       <c r="M31">
         <v>24</v>
       </c>
       <c r="N31">
-        <v>1514</v>
+        <v>1520</v>
       </c>
       <c r="O31">
-        <v>74637</v>
+        <v>75638</v>
       </c>
       <c r="P31">
         <v>81642</v>
@@ -2149,22 +2149,22 @@
         <v>36</v>
       </c>
       <c r="G32">
-        <v>19674</v>
+        <v>20693</v>
       </c>
       <c r="H32">
-        <v>18621</v>
+        <v>19878</v>
       </c>
       <c r="I32">
-        <v>702</v>
+        <v>764</v>
       </c>
       <c r="J32">
-        <v>661</v>
+        <v>1048</v>
       </c>
       <c r="K32">
         <v>0</v>
       </c>
       <c r="L32">
-        <v>3411</v>
+        <v>3505</v>
       </c>
       <c r="M32">
         <v>0</v>
@@ -2173,7 +2173,7 @@
         <v>9</v>
       </c>
       <c r="O32">
-        <v>17126</v>
+        <v>17747</v>
       </c>
       <c r="P32">
         <v>10221</v>
@@ -2202,22 +2202,22 @@
         <v>0</v>
       </c>
       <c r="E33">
-        <v>40096</v>
+        <v>40100</v>
       </c>
       <c r="F33">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="G33">
-        <v>16306</v>
+        <v>17068</v>
       </c>
       <c r="H33">
-        <v>16476</v>
+        <v>17383</v>
       </c>
       <c r="I33">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J33">
-        <v>148</v>
+        <v>292</v>
       </c>
       <c r="K33">
         <v>0</v>
@@ -2229,13 +2229,13 @@
         <v>1</v>
       </c>
       <c r="N33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O33">
-        <v>15061</v>
+        <v>15788</v>
       </c>
       <c r="P33">
-        <v>56152</v>
+        <v>57686</v>
       </c>
       <c r="Q33">
         <v>6678</v>
@@ -2261,28 +2261,28 @@
         <v>0</v>
       </c>
       <c r="E34">
-        <v>36244</v>
+        <v>36259</v>
       </c>
       <c r="F34">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="G34">
-        <v>14156</v>
+        <v>15775</v>
       </c>
       <c r="H34">
-        <v>20919</v>
+        <v>19694</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
       <c r="J34">
-        <v>195</v>
+        <v>126</v>
       </c>
       <c r="K34">
         <v>0</v>
       </c>
       <c r="L34">
-        <v>6570</v>
+        <v>6692</v>
       </c>
       <c r="M34">
         <v>0</v>
@@ -2291,7 +2291,7 @@
         <v>0</v>
       </c>
       <c r="O34">
-        <v>12130</v>
+        <v>13965</v>
       </c>
       <c r="P34">
         <v>74626</v>
@@ -2320,40 +2320,40 @@
         <v>0</v>
       </c>
       <c r="E35">
-        <v>33132</v>
+        <v>33160</v>
       </c>
       <c r="F35">
-        <v>432</v>
+        <v>404</v>
       </c>
       <c r="G35">
-        <v>17250</v>
+        <v>18457</v>
       </c>
       <c r="H35">
-        <v>12998</v>
+        <v>12627</v>
       </c>
       <c r="I35">
         <v>15</v>
       </c>
       <c r="J35">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="K35">
         <v>0</v>
       </c>
       <c r="L35">
-        <v>1314</v>
+        <v>1454</v>
       </c>
       <c r="M35">
         <v>0</v>
       </c>
       <c r="N35">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O35">
-        <v>15555</v>
+        <v>16534</v>
       </c>
       <c r="P35">
-        <v>54855</v>
+        <v>55533</v>
       </c>
       <c r="Q35">
         <v>8879</v>
@@ -2453,22 +2453,22 @@
         <v>0</v>
       </c>
       <c r="J37">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K37">
         <v>0</v>
       </c>
       <c r="L37">
-        <v>2268</v>
+        <v>2277</v>
       </c>
       <c r="M37">
         <v>0</v>
       </c>
       <c r="N37">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="O37">
-        <v>17113</v>
+        <v>17120</v>
       </c>
       <c r="P37">
         <v>57832</v>
@@ -2503,34 +2503,34 @@
         <v>0</v>
       </c>
       <c r="G38">
-        <v>28611</v>
+        <v>28786</v>
       </c>
       <c r="H38">
-        <v>280</v>
+        <v>141</v>
       </c>
       <c r="I38">
         <v>13</v>
       </c>
       <c r="J38">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="K38">
         <v>0</v>
       </c>
       <c r="L38">
-        <v>4666</v>
+        <v>4696</v>
       </c>
       <c r="M38">
         <v>2</v>
       </c>
       <c r="N38">
-        <v>351</v>
+        <v>456</v>
       </c>
       <c r="O38">
-        <v>24509</v>
+        <v>24535</v>
       </c>
       <c r="P38">
-        <v>60278</v>
+        <v>60540</v>
       </c>
       <c r="Q38">
         <v>5160</v>
@@ -2571,13 +2571,13 @@
         <v>0</v>
       </c>
       <c r="J39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39">
         <v>0</v>
       </c>
       <c r="L39">
-        <v>4493</v>
+        <v>4494</v>
       </c>
       <c r="M39">
         <v>1</v>
@@ -2592,7 +2592,7 @@
         <v>71133</v>
       </c>
       <c r="Q39">
-        <v>5909</v>
+        <v>5903</v>
       </c>
       <c r="R39">
         <v>0</v>
@@ -2621,22 +2621,22 @@
         <v>0</v>
       </c>
       <c r="G40">
-        <v>14262</v>
+        <v>14567</v>
       </c>
       <c r="H40">
-        <v>279</v>
+        <v>517</v>
       </c>
       <c r="I40">
         <v>2</v>
       </c>
       <c r="J40">
-        <v>586</v>
+        <v>599</v>
       </c>
       <c r="K40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L40">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="M40">
         <v>0</v>
@@ -2645,7 +2645,7 @@
         <v>20</v>
       </c>
       <c r="O40">
-        <v>13080</v>
+        <v>13415</v>
       </c>
       <c r="P40">
         <v>73242</v>
@@ -2680,31 +2680,31 @@
         <v>0</v>
       </c>
       <c r="G41">
-        <v>19562</v>
+        <v>19799</v>
       </c>
       <c r="H41">
-        <v>303</v>
+        <v>872</v>
       </c>
       <c r="I41">
         <v>0</v>
       </c>
       <c r="J41">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="K41">
         <v>0</v>
       </c>
       <c r="L41">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="M41">
         <v>0</v>
       </c>
       <c r="N41">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O41">
-        <v>18443</v>
+        <v>18674</v>
       </c>
       <c r="P41">
         <v>85249</v>
@@ -2748,13 +2748,13 @@
         <v>0</v>
       </c>
       <c r="J42">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="K42">
         <v>0</v>
       </c>
       <c r="L42">
-        <v>6156</v>
+        <v>6166</v>
       </c>
       <c r="M42">
         <v>0</v>
@@ -2763,10 +2763,10 @@
         <v>416</v>
       </c>
       <c r="O42">
-        <v>24102</v>
+        <v>24234</v>
       </c>
       <c r="P42">
-        <v>41861</v>
+        <v>42193</v>
       </c>
       <c r="Q42">
         <v>4713</v>
@@ -2798,37 +2798,37 @@
         <v>0</v>
       </c>
       <c r="G43">
-        <v>29390</v>
+        <v>29626</v>
       </c>
       <c r="H43">
-        <v>120</v>
+        <v>27</v>
       </c>
       <c r="I43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43">
-        <v>94</v>
+        <v>164</v>
       </c>
       <c r="K43">
         <v>0</v>
       </c>
       <c r="L43">
-        <v>6486</v>
+        <v>6531</v>
       </c>
       <c r="M43">
         <v>1</v>
       </c>
       <c r="N43">
-        <v>785</v>
+        <v>861</v>
       </c>
       <c r="O43">
-        <v>23351</v>
+        <v>23405</v>
       </c>
       <c r="P43">
-        <v>41231</v>
+        <v>41498</v>
       </c>
       <c r="Q43">
-        <v>5277</v>
+        <v>5271</v>
       </c>
       <c r="R43">
         <v>0</v>
@@ -2851,28 +2851,28 @@
         <v>0</v>
       </c>
       <c r="E44">
-        <v>21882</v>
+        <v>21890</v>
       </c>
       <c r="F44">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G44">
-        <v>19739</v>
+        <v>19842</v>
       </c>
       <c r="H44">
-        <v>1045</v>
+        <v>1111</v>
       </c>
       <c r="I44">
         <v>0</v>
       </c>
       <c r="J44">
-        <v>1028</v>
+        <v>1044</v>
       </c>
       <c r="K44">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L44">
-        <v>4606</v>
+        <v>4679</v>
       </c>
       <c r="M44">
         <v>0</v>
@@ -2881,7 +2881,7 @@
         <v>56</v>
       </c>
       <c r="O44">
-        <v>15465</v>
+        <v>15554</v>
       </c>
       <c r="P44">
         <v>68393</v>
@@ -2916,19 +2916,19 @@
         <v>1</v>
       </c>
       <c r="G45">
-        <v>14501</v>
+        <v>14669</v>
       </c>
       <c r="H45">
-        <v>2299</v>
+        <v>2697</v>
       </c>
       <c r="I45">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J45">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="K45">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L45">
         <v>1474</v>
@@ -2940,7 +2940,7 @@
         <v>39</v>
       </c>
       <c r="O45">
-        <v>12972</v>
+        <v>13125</v>
       </c>
       <c r="P45">
         <v>76002</v>
@@ -2975,31 +2975,31 @@
         <v>0</v>
       </c>
       <c r="G46">
-        <v>19510</v>
+        <v>19671</v>
       </c>
       <c r="H46">
-        <v>2002</v>
+        <v>1841</v>
       </c>
       <c r="I46">
         <v>0</v>
       </c>
       <c r="J46">
-        <v>972</v>
+        <v>1058</v>
       </c>
       <c r="K46">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L46">
-        <v>6032</v>
+        <v>6063</v>
       </c>
       <c r="M46">
         <v>0</v>
       </c>
       <c r="N46">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="O46">
-        <v>15211</v>
+        <v>15250</v>
       </c>
       <c r="P46">
         <v>64160</v>
@@ -3028,16 +3028,16 @@
         <v>0</v>
       </c>
       <c r="E47">
-        <v>22421</v>
+        <v>22423</v>
       </c>
       <c r="F47">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G47">
-        <v>19381</v>
+        <v>19383</v>
       </c>
       <c r="H47">
-        <v>2090</v>
+        <v>2128</v>
       </c>
       <c r="I47">
         <v>70</v>
@@ -3058,7 +3058,7 @@
         <v>64</v>
       </c>
       <c r="O47">
-        <v>17815</v>
+        <v>17817</v>
       </c>
       <c r="P47">
         <v>49875</v>
@@ -3093,19 +3093,19 @@
         <v>47</v>
       </c>
       <c r="G48">
-        <v>19370</v>
+        <v>19494</v>
       </c>
       <c r="H48">
-        <v>265</v>
+        <v>141</v>
       </c>
       <c r="I48">
         <v>6</v>
       </c>
       <c r="J48">
-        <v>323</v>
+        <v>364</v>
       </c>
       <c r="K48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L48">
         <v>3383</v>
@@ -3114,16 +3114,16 @@
         <v>4</v>
       </c>
       <c r="N48">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="O48">
-        <v>18595</v>
+        <v>18675</v>
       </c>
       <c r="P48">
         <v>54142</v>
       </c>
       <c r="Q48">
-        <v>4627</v>
+        <v>4623</v>
       </c>
       <c r="R48">
         <v>0</v>
@@ -3152,16 +3152,16 @@
         <v>23</v>
       </c>
       <c r="G49">
-        <v>16908</v>
+        <v>17532</v>
       </c>
       <c r="H49">
-        <v>927</v>
+        <v>1076</v>
       </c>
       <c r="I49">
-        <v>67</v>
+        <v>111</v>
       </c>
       <c r="J49">
-        <v>217</v>
+        <v>333</v>
       </c>
       <c r="K49">
         <v>0</v>
@@ -3173,10 +3173,10 @@
         <v>0</v>
       </c>
       <c r="N49">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="O49">
-        <v>14908</v>
+        <v>15754</v>
       </c>
       <c r="P49">
         <v>49949</v>
@@ -3211,16 +3211,16 @@
         <v>0</v>
       </c>
       <c r="G50">
-        <v>19686</v>
+        <v>19849</v>
       </c>
       <c r="H50">
-        <v>1538</v>
+        <v>1389</v>
       </c>
       <c r="I50">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J50">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="K50">
         <v>0</v>
@@ -3232,10 +3232,10 @@
         <v>5</v>
       </c>
       <c r="N50">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O50">
-        <v>18209</v>
+        <v>18357</v>
       </c>
       <c r="P50">
         <v>63298</v>
@@ -3270,16 +3270,16 @@
         <v>0</v>
       </c>
       <c r="G51">
-        <v>21030</v>
+        <v>21307</v>
       </c>
       <c r="H51">
-        <v>1107</v>
+        <v>1186</v>
       </c>
       <c r="I51">
         <v>0</v>
       </c>
       <c r="J51">
-        <v>70</v>
+        <v>159</v>
       </c>
       <c r="K51">
         <v>0</v>
@@ -3294,7 +3294,7 @@
         <v>49</v>
       </c>
       <c r="O51">
-        <v>17316</v>
+        <v>18171</v>
       </c>
       <c r="P51">
         <v>71754</v>
@@ -3329,16 +3329,16 @@
         <v>0</v>
       </c>
       <c r="G52">
-        <v>20534</v>
+        <v>20602</v>
       </c>
       <c r="H52">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="I52">
         <v>0</v>
       </c>
       <c r="J52">
-        <v>353</v>
+        <v>370</v>
       </c>
       <c r="K52">
         <v>1</v>
@@ -3350,10 +3350,10 @@
         <v>1</v>
       </c>
       <c r="N52">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="O52">
-        <v>19928</v>
+        <v>19975</v>
       </c>
       <c r="P52">
         <v>63986</v>
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="J53">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="K53">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="L53">
         <v>2615</v>
@@ -3447,19 +3447,19 @@
         <v>0</v>
       </c>
       <c r="G54">
-        <v>20053</v>
+        <v>20087</v>
       </c>
       <c r="H54">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="I54">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="J54">
-        <v>549</v>
+        <v>566</v>
       </c>
       <c r="K54">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="L54">
         <v>1494</v>
@@ -3468,10 +3468,10 @@
         <v>3</v>
       </c>
       <c r="N54">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="O54">
-        <v>17557</v>
+        <v>17568</v>
       </c>
       <c r="P54">
         <v>58440</v>
@@ -3506,16 +3506,16 @@
         <v>0</v>
       </c>
       <c r="G55">
-        <v>15789</v>
+        <v>15806</v>
       </c>
       <c r="H55">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="I55">
         <v>5</v>
       </c>
       <c r="J55">
-        <v>627</v>
+        <v>661</v>
       </c>
       <c r="K55">
         <v>19</v>
@@ -3527,10 +3527,10 @@
         <v>0</v>
       </c>
       <c r="N55">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="O55">
-        <v>14972</v>
+        <v>14973</v>
       </c>
       <c r="P55">
         <v>58215</v>
@@ -3565,19 +3565,19 @@
         <v>0</v>
       </c>
       <c r="G56">
-        <v>18179</v>
+        <v>18260</v>
       </c>
       <c r="H56">
-        <v>197</v>
+        <v>271</v>
       </c>
       <c r="I56">
         <v>0</v>
       </c>
       <c r="J56">
-        <v>1278</v>
+        <v>1298</v>
       </c>
       <c r="K56">
-        <v>359</v>
+        <v>411</v>
       </c>
       <c r="L56">
         <v>2268</v>
@@ -3589,7 +3589,7 @@
         <v>336</v>
       </c>
       <c r="O56">
-        <v>13971</v>
+        <v>14032</v>
       </c>
       <c r="P56">
         <v>46365</v>
@@ -3624,10 +3624,10 @@
         <v>0</v>
       </c>
       <c r="G57">
-        <v>21025</v>
+        <v>21029</v>
       </c>
       <c r="H57">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -3636,7 +3636,7 @@
         <v>284</v>
       </c>
       <c r="K57">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="L57">
         <v>1598</v>
@@ -3648,7 +3648,7 @@
         <v>35</v>
       </c>
       <c r="O57">
-        <v>20441</v>
+        <v>20445</v>
       </c>
       <c r="P57">
         <v>61556</v>
@@ -3683,19 +3683,19 @@
         <v>0</v>
       </c>
       <c r="G58">
-        <v>20296</v>
+        <v>20686</v>
       </c>
       <c r="H58">
-        <v>1974</v>
+        <v>1830</v>
       </c>
       <c r="I58">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="J58">
-        <v>1894</v>
+        <v>2100</v>
       </c>
       <c r="K58">
-        <v>585</v>
+        <v>722</v>
       </c>
       <c r="L58">
         <v>4571</v>
@@ -3704,10 +3704,10 @@
         <v>2</v>
       </c>
       <c r="N58">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="O58">
-        <v>14812</v>
+        <v>14976</v>
       </c>
       <c r="P58">
         <v>57577</v>
@@ -3742,16 +3742,16 @@
         <v>0</v>
       </c>
       <c r="G59">
-        <v>18755</v>
+        <v>18762</v>
       </c>
       <c r="H59">
         <v>0</v>
       </c>
       <c r="I59">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J59">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K59">
         <v>0</v>
@@ -3763,7 +3763,7 @@
         <v>2</v>
       </c>
       <c r="N59">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="O59">
         <v>15990</v>
@@ -3801,19 +3801,19 @@
         <v>0</v>
       </c>
       <c r="G60">
-        <v>22032</v>
+        <v>22344</v>
       </c>
       <c r="H60">
-        <v>691</v>
+        <v>733</v>
       </c>
       <c r="I60">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J60">
-        <v>1005</v>
+        <v>1024</v>
       </c>
       <c r="K60">
-        <v>75</v>
+        <v>107</v>
       </c>
       <c r="L60">
         <v>4335</v>
@@ -3825,7 +3825,7 @@
         <v>195</v>
       </c>
       <c r="O60">
-        <v>20428</v>
+        <v>20721</v>
       </c>
       <c r="P60">
         <v>70140</v>
@@ -3869,13 +3869,13 @@
         <v>0</v>
       </c>
       <c r="J61">
-        <v>500</v>
+        <v>436</v>
       </c>
       <c r="K61">
-        <v>72</v>
+        <v>172</v>
       </c>
       <c r="L61">
-        <v>9496</v>
+        <v>9551</v>
       </c>
       <c r="M61">
         <v>17</v>
@@ -3919,31 +3919,31 @@
         <v>0</v>
       </c>
       <c r="G62">
-        <v>15009</v>
+        <v>15115</v>
       </c>
       <c r="H62">
-        <v>569</v>
+        <v>493</v>
       </c>
       <c r="I62">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="J62">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="K62">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="L62">
-        <v>3426</v>
+        <v>3449</v>
       </c>
       <c r="M62">
         <v>1</v>
       </c>
       <c r="N62">
-        <v>174</v>
+        <v>233</v>
       </c>
       <c r="O62">
-        <v>14200</v>
+        <v>14217</v>
       </c>
       <c r="P62">
         <v>51334</v>
@@ -3978,37 +3978,37 @@
         <v>0</v>
       </c>
       <c r="G63">
-        <v>36417</v>
+        <v>36419</v>
       </c>
       <c r="H63">
         <v>134</v>
       </c>
       <c r="I63">
-        <v>94</v>
+        <v>200</v>
       </c>
       <c r="J63">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="K63">
         <v>0</v>
       </c>
       <c r="L63">
-        <v>10271</v>
+        <v>10368</v>
       </c>
       <c r="M63">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N63">
         <v>748</v>
       </c>
       <c r="O63">
-        <v>31053</v>
+        <v>31420</v>
       </c>
       <c r="P63">
         <v>68691</v>
       </c>
       <c r="Q63">
-        <v>9812</v>
+        <v>9810</v>
       </c>
       <c r="R63">
         <v>0</v>
@@ -4037,22 +4037,22 @@
         <v>0</v>
       </c>
       <c r="G64">
-        <v>38577</v>
+        <v>38753</v>
       </c>
       <c r="H64">
-        <v>1950</v>
+        <v>2513</v>
       </c>
       <c r="I64">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J64">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="K64">
         <v>0</v>
       </c>
       <c r="L64">
-        <v>8795</v>
+        <v>8804</v>
       </c>
       <c r="M64">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>207</v>
       </c>
       <c r="O64">
-        <v>34250</v>
+        <v>35461</v>
       </c>
       <c r="P64">
         <v>60527</v>
@@ -4096,31 +4096,31 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>32454</v>
+        <v>32950</v>
       </c>
       <c r="H65">
-        <v>7101</v>
+        <v>6639</v>
       </c>
       <c r="I65">
-        <v>175</v>
+        <v>477</v>
       </c>
       <c r="J65">
-        <v>932</v>
+        <v>6</v>
       </c>
       <c r="K65">
         <v>0</v>
       </c>
       <c r="L65">
-        <v>8678</v>
+        <v>9683</v>
       </c>
       <c r="M65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N65">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O65">
-        <v>22882</v>
+        <v>23543</v>
       </c>
       <c r="P65">
         <v>34607</v>
@@ -4155,31 +4155,31 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>44579</v>
+        <v>46370</v>
       </c>
       <c r="H66">
-        <v>11802</v>
+        <v>12936</v>
       </c>
       <c r="I66">
-        <v>134</v>
+        <v>166</v>
       </c>
       <c r="J66">
-        <v>322</v>
+        <v>128</v>
       </c>
       <c r="K66">
         <v>0</v>
       </c>
       <c r="L66">
-        <v>8436</v>
+        <v>9053</v>
       </c>
       <c r="M66">
         <v>2</v>
       </c>
       <c r="N66">
-        <v>309</v>
+        <v>388</v>
       </c>
       <c r="O66">
-        <v>38187</v>
+        <v>39584</v>
       </c>
       <c r="P66">
         <v>93810</v>
@@ -4208,22 +4208,22 @@
         <v>0</v>
       </c>
       <c r="E67">
-        <v>68811</v>
+        <v>68826</v>
       </c>
       <c r="F67">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="G67">
-        <v>58474</v>
+        <v>58823</v>
       </c>
       <c r="H67">
-        <v>3341</v>
+        <v>3875</v>
       </c>
       <c r="I67">
-        <v>1982</v>
+        <v>2160</v>
       </c>
       <c r="J67">
-        <v>85</v>
+        <v>154</v>
       </c>
       <c r="K67">
         <v>0</v>
@@ -4235,10 +4235,10 @@
         <v>9</v>
       </c>
       <c r="N67">
-        <v>646</v>
+        <v>656</v>
       </c>
       <c r="O67">
-        <v>45463</v>
+        <v>46007</v>
       </c>
       <c r="P67">
         <v>78022</v>
@@ -4267,22 +4267,22 @@
         <v>0</v>
       </c>
       <c r="E68">
-        <v>65358</v>
+        <v>65360</v>
       </c>
       <c r="F68">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G68">
-        <v>57842</v>
+        <v>58074</v>
       </c>
       <c r="H68">
-        <v>6392</v>
+        <v>6190</v>
       </c>
       <c r="I68">
-        <v>666</v>
+        <v>796</v>
       </c>
       <c r="J68">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="K68">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>2</v>
       </c>
       <c r="N68">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="O68">
-        <v>48532</v>
+        <v>48762</v>
       </c>
       <c r="P68">
-        <v>61125</v>
+        <v>61338</v>
       </c>
       <c r="Q68">
         <v>7850</v>
@@ -4332,16 +4332,16 @@
         <v>0</v>
       </c>
       <c r="G69">
-        <v>35040</v>
+        <v>35302</v>
       </c>
       <c r="H69">
-        <v>5772</v>
+        <v>5825</v>
       </c>
       <c r="I69">
-        <v>84</v>
+        <v>195</v>
       </c>
       <c r="J69">
-        <v>326</v>
+        <v>511</v>
       </c>
       <c r="K69">
         <v>0</v>
@@ -4356,10 +4356,10 @@
         <v>128</v>
       </c>
       <c r="O69">
-        <v>26182</v>
+        <v>26350</v>
       </c>
       <c r="P69">
-        <v>33788</v>
+        <v>33793</v>
       </c>
       <c r="Q69">
         <v>6528</v>
@@ -4391,16 +4391,16 @@
         <v>0</v>
       </c>
       <c r="G70">
-        <v>42378</v>
+        <v>42525</v>
       </c>
       <c r="H70">
-        <v>1938</v>
+        <v>1841</v>
       </c>
       <c r="I70">
-        <v>1954</v>
+        <v>2403</v>
       </c>
       <c r="J70">
-        <v>73</v>
+        <v>139</v>
       </c>
       <c r="K70">
         <v>0</v>
@@ -4412,10 +4412,10 @@
         <v>2</v>
       </c>
       <c r="N70">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="O70">
-        <v>33965</v>
+        <v>34499</v>
       </c>
       <c r="P70">
         <v>42040</v>
@@ -4450,16 +4450,16 @@
         <v>0</v>
       </c>
       <c r="G71">
-        <v>43982</v>
+        <v>44172</v>
       </c>
       <c r="H71">
-        <v>4731</v>
+        <v>4727</v>
       </c>
       <c r="I71">
-        <v>1020</v>
+        <v>1766</v>
       </c>
       <c r="J71">
-        <v>78</v>
+        <v>124</v>
       </c>
       <c r="K71">
         <v>0</v>
@@ -4471,7 +4471,7 @@
         <v>1</v>
       </c>
       <c r="N71">
-        <v>1845</v>
+        <v>1989</v>
       </c>
       <c r="O71">
         <v>31054</v>
@@ -4509,16 +4509,16 @@
         <v>1</v>
       </c>
       <c r="G72">
-        <v>49552</v>
+        <v>50024</v>
       </c>
       <c r="H72">
-        <v>9683</v>
+        <v>9270</v>
       </c>
       <c r="I72">
-        <v>1475</v>
+        <v>1783</v>
       </c>
       <c r="J72">
-        <v>27</v>
+        <v>158</v>
       </c>
       <c r="K72">
         <v>0</v>
@@ -4530,10 +4530,10 @@
         <v>9</v>
       </c>
       <c r="N72">
-        <v>238</v>
+        <v>257</v>
       </c>
       <c r="O72">
-        <v>38281</v>
+        <v>38899</v>
       </c>
       <c r="P72">
         <v>85505</v>
@@ -4568,16 +4568,16 @@
         <v>0</v>
       </c>
       <c r="G73">
-        <v>42150</v>
+        <v>43520</v>
       </c>
       <c r="H73">
-        <v>15172</v>
+        <v>14352</v>
       </c>
       <c r="I73">
-        <v>220</v>
+        <v>331</v>
       </c>
       <c r="J73">
-        <v>267</v>
+        <v>629</v>
       </c>
       <c r="K73">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>4</v>
       </c>
       <c r="N73">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O73">
-        <v>36661</v>
+        <v>37987</v>
       </c>
       <c r="P73">
         <v>67550</v>
@@ -4618,43 +4618,43 @@
         <v>0</v>
       </c>
       <c r="E74">
-        <v>2427694</v>
+        <v>2428020</v>
       </c>
       <c r="F74">
-        <v>2688</v>
+        <v>2362</v>
       </c>
       <c r="G74">
-        <v>1832841</v>
+        <v>1862362</v>
       </c>
       <c r="H74">
-        <v>435241</v>
+        <v>439963</v>
       </c>
       <c r="I74">
-        <v>12813</v>
+        <v>16586</v>
       </c>
       <c r="J74">
-        <v>74463</v>
+        <v>77338</v>
       </c>
       <c r="K74">
-        <v>32410</v>
+        <v>37135</v>
       </c>
       <c r="L74">
-        <v>384609</v>
+        <v>388649</v>
       </c>
       <c r="M74">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="N74">
-        <v>21179</v>
+        <v>22156</v>
       </c>
       <c r="O74">
-        <v>1536853</v>
+        <v>1565937</v>
       </c>
       <c r="P74">
-        <v>4205101</v>
+        <v>4216754</v>
       </c>
       <c r="Q74">
-        <v>629720</v>
+        <v>629685</v>
       </c>
       <c r="R74">
         <v>1</v>

--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -497,31 +497,31 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>22368</v>
+        <v>24686</v>
       </c>
       <c r="H4">
-        <v>21971</v>
+        <v>20291</v>
       </c>
       <c r="I4">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>6217</v>
+        <v>6086</v>
       </c>
       <c r="K4">
-        <v>3203</v>
+        <v>3057</v>
       </c>
       <c r="L4">
-        <v>1621</v>
+        <v>2022</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="O4">
-        <v>15605</v>
+        <v>17611</v>
       </c>
       <c r="P4">
         <v>53812</v>
@@ -556,34 +556,34 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>35689</v>
+        <v>37082</v>
       </c>
       <c r="H5">
-        <v>13209</v>
+        <v>12253</v>
       </c>
       <c r="I5">
         <v>7</v>
       </c>
       <c r="J5">
-        <v>3461</v>
+        <v>3669</v>
       </c>
       <c r="K5">
-        <v>1671</v>
+        <v>1662</v>
       </c>
       <c r="L5">
-        <v>2761</v>
+        <v>2772</v>
       </c>
       <c r="M5">
         <v>40</v>
       </c>
       <c r="N5">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="O5">
-        <v>31122</v>
+        <v>32428</v>
       </c>
       <c r="P5">
-        <v>54384</v>
+        <v>55484</v>
       </c>
       <c r="Q5">
         <v>16108</v>
@@ -615,22 +615,22 @@
         <v>2</v>
       </c>
       <c r="G6">
-        <v>19286</v>
+        <v>19832</v>
       </c>
       <c r="H6">
-        <v>12738</v>
+        <v>12693</v>
       </c>
       <c r="I6">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="J6">
-        <v>1611</v>
+        <v>1632</v>
       </c>
       <c r="K6">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="L6">
-        <v>1358</v>
+        <v>1382</v>
       </c>
       <c r="M6">
         <v>26</v>
@@ -639,7 +639,7 @@
         <v>624</v>
       </c>
       <c r="O6">
-        <v>16202</v>
+        <v>16703</v>
       </c>
       <c r="P6">
         <v>43508</v>
@@ -674,31 +674,31 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>23987</v>
+        <v>24550</v>
       </c>
       <c r="H7">
-        <v>14812</v>
+        <v>14340</v>
       </c>
       <c r="I7">
-        <v>364</v>
+        <v>294</v>
       </c>
       <c r="J7">
-        <v>4187</v>
+        <v>4273</v>
       </c>
       <c r="K7">
-        <v>3031</v>
+        <v>3028</v>
       </c>
       <c r="L7">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="M7">
         <v>28</v>
       </c>
       <c r="N7">
-        <v>384</v>
+        <v>593</v>
       </c>
       <c r="O7">
-        <v>18869</v>
+        <v>19234</v>
       </c>
       <c r="P7">
         <v>77581</v>
@@ -727,40 +727,40 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>40548</v>
+        <v>40550</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G8">
-        <v>21243</v>
+        <v>22375</v>
       </c>
       <c r="H8">
-        <v>19291</v>
+        <v>18176</v>
       </c>
       <c r="I8">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>8137</v>
+        <v>8356</v>
       </c>
       <c r="K8">
-        <v>3930</v>
+        <v>3883</v>
       </c>
       <c r="L8">
-        <v>2999</v>
+        <v>3229</v>
       </c>
       <c r="M8">
         <v>16</v>
       </c>
       <c r="N8">
-        <v>141</v>
+        <v>168</v>
       </c>
       <c r="O8">
-        <v>9768</v>
+        <v>10406</v>
       </c>
       <c r="P8">
-        <v>14385</v>
+        <v>19800</v>
       </c>
       <c r="Q8">
         <v>20902</v>
@@ -792,31 +792,31 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>29149</v>
+        <v>29947</v>
       </c>
       <c r="H9">
-        <v>13518</v>
+        <v>12728</v>
       </c>
       <c r="I9">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="J9">
-        <v>4795</v>
+        <v>5069</v>
       </c>
       <c r="K9">
         <v>3736</v>
       </c>
       <c r="L9">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M9">
         <v>7</v>
       </c>
       <c r="N9">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="O9">
-        <v>23560</v>
+        <v>24071</v>
       </c>
       <c r="P9">
         <v>50354</v>
@@ -851,22 +851,22 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>26506</v>
+        <v>27734</v>
       </c>
       <c r="H10">
-        <v>9990</v>
+        <v>8763</v>
       </c>
       <c r="I10">
         <v>37</v>
       </c>
       <c r="J10">
-        <v>7585</v>
+        <v>7463</v>
       </c>
       <c r="K10">
-        <v>5113</v>
+        <v>4912</v>
       </c>
       <c r="L10">
-        <v>1091</v>
+        <v>1411</v>
       </c>
       <c r="M10">
         <v>9</v>
@@ -875,10 +875,10 @@
         <v>240</v>
       </c>
       <c r="O10">
-        <v>17790</v>
+        <v>18807</v>
       </c>
       <c r="P10">
-        <v>12194</v>
+        <v>12983</v>
       </c>
       <c r="Q10">
         <v>9518</v>
@@ -910,16 +910,16 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>30640</v>
+        <v>32503</v>
       </c>
       <c r="H11">
-        <v>17221</v>
+        <v>15971</v>
       </c>
       <c r="I11">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="J11">
-        <v>3579</v>
+        <v>3877</v>
       </c>
       <c r="K11">
         <v>1841</v>
@@ -931,13 +931,13 @@
         <v>1</v>
       </c>
       <c r="N11">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="O11">
-        <v>26303</v>
+        <v>27866</v>
       </c>
       <c r="P11">
-        <v>75787</v>
+        <v>76980</v>
       </c>
       <c r="Q11">
         <v>23805</v>
@@ -963,22 +963,22 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>40620</v>
+        <v>40703</v>
       </c>
       <c r="F12">
-        <v>119</v>
+        <v>36</v>
       </c>
       <c r="G12">
-        <v>19975</v>
+        <v>21360</v>
       </c>
       <c r="H12">
-        <v>20031</v>
+        <v>18758</v>
       </c>
       <c r="I12">
-        <v>204</v>
+        <v>161</v>
       </c>
       <c r="J12">
-        <v>7775</v>
+        <v>7999</v>
       </c>
       <c r="K12">
         <v>5099</v>
@@ -990,13 +990,13 @@
         <v>2</v>
       </c>
       <c r="N12">
-        <v>253</v>
+        <v>311</v>
       </c>
       <c r="O12">
-        <v>11780</v>
+        <v>12884</v>
       </c>
       <c r="P12">
-        <v>42636</v>
+        <v>42640</v>
       </c>
       <c r="Q12">
         <v>17907</v>
@@ -1022,37 +1022,37 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>36863</v>
+        <v>36894</v>
       </c>
       <c r="F13">
-        <v>168</v>
+        <v>137</v>
       </c>
       <c r="G13">
-        <v>22084</v>
+        <v>22927</v>
       </c>
       <c r="H13">
-        <v>12709</v>
+        <v>11868</v>
       </c>
       <c r="I13">
         <v>12</v>
       </c>
       <c r="J13">
-        <v>3296</v>
+        <v>3452</v>
       </c>
       <c r="K13">
-        <v>1477</v>
+        <v>1419</v>
       </c>
       <c r="L13">
-        <v>13</v>
+        <v>102</v>
       </c>
       <c r="M13">
         <v>0</v>
       </c>
       <c r="N13">
-        <v>1661</v>
+        <v>1719</v>
       </c>
       <c r="O13">
-        <v>17120</v>
+        <v>17641</v>
       </c>
       <c r="P13">
         <v>54599</v>
@@ -1081,40 +1081,40 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>48962</v>
+        <v>48964</v>
       </c>
       <c r="F14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G14">
-        <v>27110</v>
+        <v>27843</v>
       </c>
       <c r="H14">
-        <v>12739</v>
+        <v>12419</v>
       </c>
       <c r="I14">
-        <v>769</v>
+        <v>674</v>
       </c>
       <c r="J14">
-        <v>7663</v>
+        <v>7852</v>
       </c>
       <c r="K14">
-        <v>4888</v>
+        <v>4693</v>
       </c>
       <c r="L14">
-        <v>1138</v>
+        <v>1327</v>
       </c>
       <c r="M14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N14">
-        <v>325</v>
+        <v>385</v>
       </c>
       <c r="O14">
-        <v>18397</v>
+        <v>18683</v>
       </c>
       <c r="P14">
-        <v>38577</v>
+        <v>39802</v>
       </c>
       <c r="Q14">
         <v>20044</v>
@@ -1146,31 +1146,31 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>37076</v>
+        <v>38081</v>
       </c>
       <c r="H15">
-        <v>5514</v>
+        <v>4534</v>
       </c>
       <c r="I15">
         <v>4</v>
       </c>
       <c r="J15">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15">
-        <v>7914</v>
+        <v>8170</v>
       </c>
       <c r="M15">
         <v>0</v>
       </c>
       <c r="N15">
-        <v>1015</v>
+        <v>1281</v>
       </c>
       <c r="O15">
-        <v>33703</v>
+        <v>34420</v>
       </c>
       <c r="P15">
         <v>67178</v>
@@ -1199,40 +1199,40 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>25324</v>
+        <v>25363</v>
       </c>
       <c r="F16">
-        <v>225</v>
+        <v>186</v>
       </c>
       <c r="G16">
-        <v>17672</v>
+        <v>18537</v>
       </c>
       <c r="H16">
-        <v>6764</v>
+        <v>5930</v>
       </c>
       <c r="I16">
         <v>223</v>
       </c>
       <c r="J16">
-        <v>217</v>
+        <v>112</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
       <c r="L16">
-        <v>9923</v>
+        <v>10418</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="O16">
-        <v>10509</v>
+        <v>11594</v>
       </c>
       <c r="P16">
-        <v>67034</v>
+        <v>67082</v>
       </c>
       <c r="Q16">
         <v>5208</v>
@@ -1264,34 +1264,34 @@
         <v>13</v>
       </c>
       <c r="G17">
-        <v>23754</v>
+        <v>25260</v>
       </c>
       <c r="H17">
-        <v>3287</v>
+        <v>2224</v>
       </c>
       <c r="I17">
         <v>2</v>
       </c>
       <c r="J17">
-        <v>228</v>
+        <v>336</v>
       </c>
       <c r="K17">
         <v>0</v>
       </c>
       <c r="L17">
-        <v>7420</v>
+        <v>7800</v>
       </c>
       <c r="M17">
         <v>2</v>
       </c>
       <c r="N17">
-        <v>185</v>
+        <v>235</v>
       </c>
       <c r="O17">
-        <v>21293</v>
+        <v>22974</v>
       </c>
       <c r="P17">
-        <v>65453</v>
+        <v>65454</v>
       </c>
       <c r="Q17">
         <v>5444</v>
@@ -1317,37 +1317,37 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>47725</v>
+        <v>47757</v>
       </c>
       <c r="F18">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="G18">
-        <v>41933</v>
+        <v>43836</v>
       </c>
       <c r="H18">
-        <v>4742</v>
+        <v>3225</v>
       </c>
       <c r="I18">
-        <v>1110</v>
+        <v>695</v>
       </c>
       <c r="J18">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K18">
         <v>0</v>
       </c>
       <c r="L18">
-        <v>6477</v>
+        <v>6938</v>
       </c>
       <c r="M18">
         <v>3</v>
       </c>
       <c r="N18">
-        <v>1140</v>
+        <v>1208</v>
       </c>
       <c r="O18">
-        <v>37812</v>
+        <v>39212</v>
       </c>
       <c r="P18">
         <v>69692</v>
@@ -1376,37 +1376,37 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>56345</v>
+        <v>56350</v>
       </c>
       <c r="F19">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="G19">
-        <v>46950</v>
+        <v>48528</v>
       </c>
       <c r="H19">
-        <v>8903</v>
+        <v>7473</v>
       </c>
       <c r="I19">
-        <v>161</v>
+        <v>117</v>
       </c>
       <c r="J19">
-        <v>161</v>
+        <v>88</v>
       </c>
       <c r="K19">
         <v>0</v>
       </c>
       <c r="L19">
-        <v>11978</v>
+        <v>12691</v>
       </c>
       <c r="M19">
         <v>1</v>
       </c>
       <c r="N19">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="O19">
-        <v>41150</v>
+        <v>42256</v>
       </c>
       <c r="P19">
         <v>105570</v>
@@ -1435,37 +1435,37 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>34985</v>
+        <v>34993</v>
       </c>
       <c r="F20">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G20">
-        <v>31715</v>
+        <v>32691</v>
       </c>
       <c r="H20">
-        <v>2817</v>
+        <v>2077</v>
       </c>
       <c r="I20">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J20">
-        <v>14</v>
+        <v>78</v>
       </c>
       <c r="K20">
         <v>0</v>
       </c>
       <c r="L20">
-        <v>5385</v>
+        <v>5458</v>
       </c>
       <c r="M20">
         <v>5</v>
       </c>
       <c r="N20">
-        <v>178</v>
+        <v>209</v>
       </c>
       <c r="O20">
-        <v>29447</v>
+        <v>31163</v>
       </c>
       <c r="P20">
         <v>75257</v>
@@ -1509,19 +1509,19 @@
         <v>0</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="K21">
         <v>0</v>
       </c>
       <c r="L21">
-        <v>3886</v>
+        <v>3893</v>
       </c>
       <c r="M21">
         <v>3</v>
       </c>
       <c r="N21">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="O21">
         <v>16645</v>
@@ -1559,31 +1559,31 @@
         <v>0</v>
       </c>
       <c r="G22">
-        <v>17928</v>
+        <v>18048</v>
       </c>
       <c r="H22">
-        <v>457</v>
+        <v>337</v>
       </c>
       <c r="I22">
         <v>0</v>
       </c>
       <c r="J22">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="K22">
         <v>0</v>
       </c>
       <c r="L22">
-        <v>7212</v>
+        <v>7303</v>
       </c>
       <c r="M22">
         <v>0</v>
       </c>
       <c r="N22">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O22">
-        <v>17131</v>
+        <v>17180</v>
       </c>
       <c r="P22">
         <v>64099</v>
@@ -1618,31 +1618,31 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>11796</v>
+        <v>12005</v>
       </c>
       <c r="H23">
+        <v>13</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
         <v>21</v>
       </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
       <c r="K23">
         <v>0</v>
       </c>
       <c r="L23">
-        <v>2069</v>
+        <v>2079</v>
       </c>
       <c r="M23">
         <v>0</v>
       </c>
       <c r="N23">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="O23">
-        <v>11580</v>
+        <v>11868</v>
       </c>
       <c r="P23">
         <v>57093</v>
@@ -1677,31 +1677,31 @@
         <v>0</v>
       </c>
       <c r="G24">
-        <v>13562</v>
+        <v>13745</v>
       </c>
       <c r="H24">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I24">
         <v>8</v>
       </c>
       <c r="J24">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K24">
         <v>0</v>
       </c>
       <c r="L24">
-        <v>3361</v>
+        <v>3398</v>
       </c>
       <c r="M24">
         <v>0</v>
       </c>
       <c r="N24">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="O24">
-        <v>13341</v>
+        <v>13499</v>
       </c>
       <c r="P24">
         <v>65629</v>
@@ -1736,31 +1736,31 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>18684</v>
+        <v>18765</v>
       </c>
       <c r="H25">
-        <v>179</v>
+        <v>146</v>
       </c>
       <c r="I25">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J25">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="K25">
         <v>0</v>
       </c>
       <c r="L25">
-        <v>4376</v>
+        <v>4439</v>
       </c>
       <c r="M25">
         <v>0</v>
       </c>
       <c r="N25">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="O25">
-        <v>18194</v>
+        <v>18199</v>
       </c>
       <c r="P25">
         <v>57533</v>
@@ -1795,31 +1795,31 @@
         <v>0</v>
       </c>
       <c r="G26">
-        <v>16514</v>
+        <v>16646</v>
       </c>
       <c r="H26">
-        <v>918</v>
+        <v>786</v>
       </c>
       <c r="I26">
         <v>0</v>
       </c>
       <c r="J26">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="K26">
         <v>0</v>
       </c>
       <c r="L26">
-        <v>3238</v>
+        <v>3294</v>
       </c>
       <c r="M26">
         <v>3</v>
       </c>
       <c r="N26">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="O26">
-        <v>15226</v>
+        <v>15335</v>
       </c>
       <c r="P26">
         <v>66594</v>
@@ -1854,22 +1854,22 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>21864</v>
+        <v>24261</v>
       </c>
       <c r="H27">
-        <v>18983</v>
+        <v>16619</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27">
-        <v>216</v>
+        <v>262</v>
       </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="L27">
-        <v>3981</v>
+        <v>4626</v>
       </c>
       <c r="M27">
         <v>0</v>
@@ -1878,7 +1878,7 @@
         <v>56</v>
       </c>
       <c r="O27">
-        <v>20666</v>
+        <v>22803</v>
       </c>
       <c r="P27">
         <v>40115</v>
@@ -1907,37 +1907,37 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>53845</v>
+        <v>54128</v>
       </c>
       <c r="F28">
-        <v>504</v>
+        <v>221</v>
       </c>
       <c r="G28">
-        <v>22986</v>
+        <v>23763</v>
       </c>
       <c r="H28">
-        <v>24189</v>
+        <v>23487</v>
       </c>
       <c r="I28">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="J28">
-        <v>188</v>
+        <v>113</v>
       </c>
       <c r="K28">
         <v>0</v>
       </c>
       <c r="L28">
-        <v>3088</v>
+        <v>3425</v>
       </c>
       <c r="M28">
         <v>11</v>
       </c>
       <c r="N28">
-        <v>233</v>
+        <v>280</v>
       </c>
       <c r="O28">
-        <v>19860</v>
+        <v>20432</v>
       </c>
       <c r="P28">
         <v>80640</v>
@@ -1972,31 +1972,31 @@
         <v>0</v>
       </c>
       <c r="G29">
-        <v>31309</v>
+        <v>32561</v>
       </c>
       <c r="H29">
-        <v>14026</v>
+        <v>12843</v>
       </c>
       <c r="I29">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="J29">
-        <v>492</v>
+        <v>96</v>
       </c>
       <c r="K29">
         <v>0</v>
       </c>
       <c r="L29">
-        <v>4686</v>
+        <v>5160</v>
       </c>
       <c r="M29">
         <v>2</v>
       </c>
       <c r="N29">
-        <v>337</v>
+        <v>363</v>
       </c>
       <c r="O29">
-        <v>27754</v>
+        <v>28868</v>
       </c>
       <c r="P29">
         <v>83837</v>
@@ -2031,22 +2031,22 @@
         <v>58</v>
       </c>
       <c r="G30">
-        <v>24386</v>
+        <v>25545</v>
       </c>
       <c r="H30">
-        <v>24691</v>
+        <v>23379</v>
       </c>
       <c r="I30">
         <v>515</v>
       </c>
       <c r="J30">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K30">
         <v>0</v>
       </c>
       <c r="L30">
-        <v>2249</v>
+        <v>2495</v>
       </c>
       <c r="M30">
         <v>0</v>
@@ -2055,7 +2055,7 @@
         <v>140</v>
       </c>
       <c r="O30">
-        <v>21444</v>
+        <v>22339</v>
       </c>
       <c r="P30">
         <v>86935</v>
@@ -2090,31 +2090,31 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>84364</v>
+        <v>85423</v>
       </c>
       <c r="H31">
-        <v>1122</v>
+        <v>894</v>
       </c>
       <c r="I31">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="J31">
-        <v>131</v>
+        <v>290</v>
       </c>
       <c r="K31">
         <v>0</v>
       </c>
       <c r="L31">
-        <v>38587</v>
+        <v>39631</v>
       </c>
       <c r="M31">
         <v>24</v>
       </c>
       <c r="N31">
-        <v>1520</v>
+        <v>1551</v>
       </c>
       <c r="O31">
-        <v>75638</v>
+        <v>79764</v>
       </c>
       <c r="P31">
         <v>81642</v>
@@ -2143,40 +2143,40 @@
         <v>0</v>
       </c>
       <c r="E32">
-        <v>46692</v>
+        <v>46700</v>
       </c>
       <c r="F32">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="G32">
-        <v>20693</v>
+        <v>22126</v>
       </c>
       <c r="H32">
-        <v>19878</v>
+        <v>18446</v>
       </c>
       <c r="I32">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="J32">
-        <v>1048</v>
+        <v>288</v>
       </c>
       <c r="K32">
         <v>0</v>
       </c>
       <c r="L32">
-        <v>3505</v>
+        <v>4805</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N32">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="O32">
-        <v>17747</v>
+        <v>18795</v>
       </c>
       <c r="P32">
-        <v>10221</v>
+        <v>11022</v>
       </c>
       <c r="Q32">
         <v>11379</v>
@@ -2202,40 +2202,40 @@
         <v>0</v>
       </c>
       <c r="E33">
-        <v>40100</v>
+        <v>40120</v>
       </c>
       <c r="F33">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="G33">
-        <v>17068</v>
+        <v>18499</v>
       </c>
       <c r="H33">
-        <v>17383</v>
+        <v>16675</v>
       </c>
       <c r="I33">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J33">
-        <v>292</v>
+        <v>144</v>
       </c>
       <c r="K33">
         <v>0</v>
       </c>
       <c r="L33">
-        <v>2437</v>
+        <v>2613</v>
       </c>
       <c r="M33">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N33">
         <v>7</v>
       </c>
       <c r="O33">
-        <v>15788</v>
+        <v>17161</v>
       </c>
       <c r="P33">
-        <v>57686</v>
+        <v>63531</v>
       </c>
       <c r="Q33">
         <v>6678</v>
@@ -2261,28 +2261,28 @@
         <v>0</v>
       </c>
       <c r="E34">
-        <v>36259</v>
+        <v>36317</v>
       </c>
       <c r="F34">
-        <v>283</v>
+        <v>225</v>
       </c>
       <c r="G34">
-        <v>15775</v>
+        <v>17429</v>
       </c>
       <c r="H34">
-        <v>19694</v>
+        <v>18157</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
       <c r="J34">
-        <v>126</v>
+        <v>393</v>
       </c>
       <c r="K34">
         <v>0</v>
       </c>
       <c r="L34">
-        <v>6692</v>
+        <v>6856</v>
       </c>
       <c r="M34">
         <v>0</v>
@@ -2291,7 +2291,7 @@
         <v>0</v>
       </c>
       <c r="O34">
-        <v>13965</v>
+        <v>15225</v>
       </c>
       <c r="P34">
         <v>74626</v>
@@ -2320,40 +2320,40 @@
         <v>0</v>
       </c>
       <c r="E35">
-        <v>33160</v>
+        <v>33192</v>
       </c>
       <c r="F35">
-        <v>404</v>
+        <v>372</v>
       </c>
       <c r="G35">
-        <v>18457</v>
+        <v>20077</v>
       </c>
       <c r="H35">
-        <v>12627</v>
+        <v>11116</v>
       </c>
       <c r="I35">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J35">
-        <v>196</v>
+        <v>65</v>
       </c>
       <c r="K35">
         <v>0</v>
       </c>
       <c r="L35">
-        <v>1454</v>
+        <v>1982</v>
       </c>
       <c r="M35">
         <v>0</v>
       </c>
       <c r="N35">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="O35">
-        <v>16534</v>
+        <v>17699</v>
       </c>
       <c r="P35">
-        <v>55533</v>
+        <v>62346</v>
       </c>
       <c r="Q35">
         <v>8879</v>
@@ -2394,13 +2394,13 @@
         <v>0</v>
       </c>
       <c r="J36">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K36">
         <v>0</v>
       </c>
       <c r="L36">
-        <v>7279</v>
+        <v>7288</v>
       </c>
       <c r="M36">
         <v>0</v>
@@ -2453,7 +2453,7 @@
         <v>0</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K37">
         <v>0</v>
@@ -2465,7 +2465,7 @@
         <v>0</v>
       </c>
       <c r="N37">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O37">
         <v>17120</v>
@@ -2503,34 +2503,34 @@
         <v>0</v>
       </c>
       <c r="G38">
-        <v>28786</v>
+        <v>28892</v>
       </c>
       <c r="H38">
-        <v>141</v>
+        <v>98</v>
       </c>
       <c r="I38">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J38">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="K38">
         <v>0</v>
       </c>
       <c r="L38">
-        <v>4696</v>
+        <v>4845</v>
       </c>
       <c r="M38">
         <v>2</v>
       </c>
       <c r="N38">
-        <v>456</v>
+        <v>474</v>
       </c>
       <c r="O38">
-        <v>24535</v>
+        <v>24561</v>
       </c>
       <c r="P38">
-        <v>60540</v>
+        <v>61242</v>
       </c>
       <c r="Q38">
         <v>5160</v>
@@ -2577,16 +2577,16 @@
         <v>0</v>
       </c>
       <c r="L39">
-        <v>4494</v>
+        <v>4509</v>
       </c>
       <c r="M39">
         <v>1</v>
       </c>
       <c r="N39">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="O39">
-        <v>18590</v>
+        <v>19483</v>
       </c>
       <c r="P39">
         <v>71133</v>
@@ -2621,31 +2621,31 @@
         <v>0</v>
       </c>
       <c r="G40">
-        <v>14567</v>
+        <v>14851</v>
       </c>
       <c r="H40">
-        <v>517</v>
+        <v>355</v>
       </c>
       <c r="I40">
         <v>2</v>
       </c>
       <c r="J40">
-        <v>599</v>
+        <v>549</v>
       </c>
       <c r="K40">
         <v>2</v>
       </c>
       <c r="L40">
-        <v>600</v>
+        <v>666</v>
       </c>
       <c r="M40">
         <v>0</v>
       </c>
       <c r="N40">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O40">
-        <v>13415</v>
+        <v>13696</v>
       </c>
       <c r="P40">
         <v>73242</v>
@@ -2680,22 +2680,22 @@
         <v>0</v>
       </c>
       <c r="G41">
-        <v>19799</v>
+        <v>20575</v>
       </c>
       <c r="H41">
-        <v>872</v>
+        <v>534</v>
       </c>
       <c r="I41">
         <v>0</v>
       </c>
       <c r="J41">
-        <v>528</v>
+        <v>469</v>
       </c>
       <c r="K41">
         <v>0</v>
       </c>
       <c r="L41">
-        <v>476</v>
+        <v>557</v>
       </c>
       <c r="M41">
         <v>0</v>
@@ -2704,7 +2704,7 @@
         <v>28</v>
       </c>
       <c r="O41">
-        <v>18674</v>
+        <v>19410</v>
       </c>
       <c r="P41">
         <v>85249</v>
@@ -2748,25 +2748,25 @@
         <v>0</v>
       </c>
       <c r="J42">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="K42">
         <v>0</v>
       </c>
       <c r="L42">
-        <v>6166</v>
+        <v>6178</v>
       </c>
       <c r="M42">
         <v>0</v>
       </c>
       <c r="N42">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O42">
-        <v>24234</v>
+        <v>25756</v>
       </c>
       <c r="P42">
-        <v>42193</v>
+        <v>46029</v>
       </c>
       <c r="Q42">
         <v>4713</v>
@@ -2798,34 +2798,34 @@
         <v>0</v>
       </c>
       <c r="G43">
-        <v>29626</v>
+        <v>29699</v>
       </c>
       <c r="H43">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="I43">
         <v>0</v>
       </c>
       <c r="J43">
-        <v>164</v>
+        <v>6</v>
       </c>
       <c r="K43">
         <v>0</v>
       </c>
       <c r="L43">
-        <v>6531</v>
+        <v>6713</v>
       </c>
       <c r="M43">
         <v>1</v>
       </c>
       <c r="N43">
-        <v>861</v>
+        <v>900</v>
       </c>
       <c r="O43">
-        <v>23405</v>
+        <v>24092</v>
       </c>
       <c r="P43">
-        <v>41498</v>
+        <v>42801</v>
       </c>
       <c r="Q43">
         <v>5271</v>
@@ -2851,37 +2851,37 @@
         <v>0</v>
       </c>
       <c r="E44">
-        <v>21890</v>
+        <v>21900</v>
       </c>
       <c r="F44">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G44">
-        <v>19842</v>
+        <v>20193</v>
       </c>
       <c r="H44">
-        <v>1111</v>
+        <v>802</v>
       </c>
       <c r="I44">
         <v>0</v>
       </c>
       <c r="J44">
-        <v>1044</v>
+        <v>1035</v>
       </c>
       <c r="K44">
         <v>7</v>
       </c>
       <c r="L44">
-        <v>4679</v>
+        <v>4865</v>
       </c>
       <c r="M44">
         <v>0</v>
       </c>
       <c r="N44">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="O44">
-        <v>15554</v>
+        <v>15730</v>
       </c>
       <c r="P44">
         <v>68393</v>
@@ -2910,37 +2910,37 @@
         <v>0</v>
       </c>
       <c r="E45">
-        <v>19934</v>
+        <v>19935</v>
       </c>
       <c r="F45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45">
-        <v>14669</v>
+        <v>15081</v>
       </c>
       <c r="H45">
-        <v>2697</v>
+        <v>2508</v>
       </c>
       <c r="I45">
         <v>13</v>
       </c>
       <c r="J45">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="K45">
         <v>6</v>
       </c>
       <c r="L45">
-        <v>1474</v>
+        <v>1494</v>
       </c>
       <c r="M45">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N45">
         <v>39</v>
       </c>
       <c r="O45">
-        <v>13125</v>
+        <v>13500</v>
       </c>
       <c r="P45">
         <v>76002</v>
@@ -2975,31 +2975,31 @@
         <v>0</v>
       </c>
       <c r="G46">
-        <v>19671</v>
+        <v>20173</v>
       </c>
       <c r="H46">
-        <v>1841</v>
+        <v>1339</v>
       </c>
       <c r="I46">
         <v>0</v>
       </c>
       <c r="J46">
-        <v>1058</v>
+        <v>83</v>
       </c>
       <c r="K46">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L46">
-        <v>6063</v>
+        <v>7310</v>
       </c>
       <c r="M46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N46">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="O46">
-        <v>15250</v>
+        <v>15906</v>
       </c>
       <c r="P46">
         <v>64160</v>
@@ -3028,22 +3028,22 @@
         <v>0</v>
       </c>
       <c r="E47">
-        <v>22423</v>
+        <v>22426</v>
       </c>
       <c r="F47">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G47">
-        <v>19383</v>
+        <v>19667</v>
       </c>
       <c r="H47">
-        <v>2128</v>
+        <v>1862</v>
       </c>
       <c r="I47">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J47">
-        <v>205</v>
+        <v>249</v>
       </c>
       <c r="K47">
         <v>0</v>
@@ -3055,10 +3055,10 @@
         <v>1</v>
       </c>
       <c r="N47">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="O47">
-        <v>17817</v>
+        <v>18239</v>
       </c>
       <c r="P47">
         <v>49875</v>
@@ -3093,31 +3093,31 @@
         <v>47</v>
       </c>
       <c r="G48">
-        <v>19494</v>
+        <v>19515</v>
       </c>
       <c r="H48">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="I48">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J48">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="K48">
         <v>2</v>
       </c>
       <c r="L48">
-        <v>3383</v>
+        <v>3396</v>
       </c>
       <c r="M48">
         <v>4</v>
       </c>
       <c r="N48">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="O48">
-        <v>18675</v>
+        <v>18717</v>
       </c>
       <c r="P48">
         <v>54142</v>
@@ -3152,16 +3152,16 @@
         <v>23</v>
       </c>
       <c r="G49">
-        <v>17532</v>
+        <v>17943</v>
       </c>
       <c r="H49">
-        <v>1076</v>
+        <v>959</v>
       </c>
       <c r="I49">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="J49">
-        <v>333</v>
+        <v>470</v>
       </c>
       <c r="K49">
         <v>0</v>
@@ -3173,10 +3173,10 @@
         <v>0</v>
       </c>
       <c r="N49">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="O49">
-        <v>15754</v>
+        <v>16011</v>
       </c>
       <c r="P49">
         <v>49949</v>
@@ -3211,22 +3211,22 @@
         <v>0</v>
       </c>
       <c r="G50">
-        <v>19849</v>
+        <v>20306</v>
       </c>
       <c r="H50">
-        <v>1389</v>
+        <v>1225</v>
       </c>
       <c r="I50">
         <v>1</v>
       </c>
       <c r="J50">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="K50">
         <v>0</v>
       </c>
       <c r="L50">
-        <v>3254</v>
+        <v>3269</v>
       </c>
       <c r="M50">
         <v>5</v>
@@ -3235,7 +3235,7 @@
         <v>11</v>
       </c>
       <c r="O50">
-        <v>18357</v>
+        <v>18998</v>
       </c>
       <c r="P50">
         <v>63298</v>
@@ -3270,22 +3270,22 @@
         <v>0</v>
       </c>
       <c r="G51">
-        <v>21307</v>
+        <v>21674</v>
       </c>
       <c r="H51">
-        <v>1186</v>
+        <v>826</v>
       </c>
       <c r="I51">
         <v>0</v>
       </c>
       <c r="J51">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="K51">
         <v>0</v>
       </c>
       <c r="L51">
-        <v>3924</v>
+        <v>4118</v>
       </c>
       <c r="M51">
         <v>11</v>
@@ -3294,7 +3294,7 @@
         <v>49</v>
       </c>
       <c r="O51">
-        <v>18171</v>
+        <v>18706</v>
       </c>
       <c r="P51">
         <v>71754</v>
@@ -3329,31 +3329,31 @@
         <v>0</v>
       </c>
       <c r="G52">
-        <v>20602</v>
+        <v>20659</v>
       </c>
       <c r="H52">
-        <v>134</v>
+        <v>101</v>
       </c>
       <c r="I52">
         <v>0</v>
       </c>
       <c r="J52">
-        <v>370</v>
+        <v>338</v>
       </c>
       <c r="K52">
         <v>1</v>
       </c>
       <c r="L52">
-        <v>2246</v>
+        <v>2309</v>
       </c>
       <c r="M52">
         <v>1</v>
       </c>
       <c r="N52">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O52">
-        <v>19975</v>
+        <v>20075</v>
       </c>
       <c r="P52">
         <v>63986</v>
@@ -3397,13 +3397,13 @@
         <v>0</v>
       </c>
       <c r="J53">
-        <v>817</v>
+        <v>660</v>
       </c>
       <c r="K53">
-        <v>319</v>
+        <v>148</v>
       </c>
       <c r="L53">
-        <v>2615</v>
+        <v>2733</v>
       </c>
       <c r="M53">
         <v>1</v>
@@ -3447,31 +3447,31 @@
         <v>0</v>
       </c>
       <c r="G54">
-        <v>20087</v>
+        <v>20192</v>
       </c>
       <c r="H54">
-        <v>520</v>
+        <v>416</v>
       </c>
       <c r="I54">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J54">
-        <v>566</v>
+        <v>668</v>
       </c>
       <c r="K54">
-        <v>216</v>
+        <v>180</v>
       </c>
       <c r="L54">
-        <v>1494</v>
+        <v>1533</v>
       </c>
       <c r="M54">
         <v>3</v>
       </c>
       <c r="N54">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="O54">
-        <v>17568</v>
+        <v>17635</v>
       </c>
       <c r="P54">
         <v>58440</v>
@@ -3506,31 +3506,31 @@
         <v>0</v>
       </c>
       <c r="G55">
-        <v>15806</v>
+        <v>15930</v>
       </c>
       <c r="H55">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="I55">
         <v>5</v>
       </c>
       <c r="J55">
-        <v>661</v>
+        <v>580</v>
       </c>
       <c r="K55">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="L55">
-        <v>1340</v>
+        <v>1413</v>
       </c>
       <c r="M55">
         <v>0</v>
       </c>
       <c r="N55">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="O55">
-        <v>14973</v>
+        <v>15156</v>
       </c>
       <c r="P55">
         <v>58215</v>
@@ -3565,16 +3565,16 @@
         <v>0</v>
       </c>
       <c r="G56">
-        <v>18260</v>
+        <v>18505</v>
       </c>
       <c r="H56">
-        <v>271</v>
+        <v>237</v>
       </c>
       <c r="I56">
         <v>0</v>
       </c>
       <c r="J56">
-        <v>1298</v>
+        <v>1368</v>
       </c>
       <c r="K56">
         <v>411</v>
@@ -3586,10 +3586,10 @@
         <v>1</v>
       </c>
       <c r="N56">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="O56">
-        <v>14032</v>
+        <v>14206</v>
       </c>
       <c r="P56">
         <v>46365</v>
@@ -3624,22 +3624,22 @@
         <v>0</v>
       </c>
       <c r="G57">
-        <v>21029</v>
+        <v>21105</v>
       </c>
       <c r="H57">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="I57">
         <v>0</v>
       </c>
       <c r="J57">
-        <v>284</v>
+        <v>216</v>
       </c>
       <c r="K57">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="L57">
-        <v>1598</v>
+        <v>1666</v>
       </c>
       <c r="M57">
         <v>0</v>
@@ -3648,7 +3648,7 @@
         <v>35</v>
       </c>
       <c r="O57">
-        <v>20445</v>
+        <v>20842</v>
       </c>
       <c r="P57">
         <v>61556</v>
@@ -3683,31 +3683,31 @@
         <v>0</v>
       </c>
       <c r="G58">
-        <v>20686</v>
+        <v>21092</v>
       </c>
       <c r="H58">
-        <v>1830</v>
+        <v>1504</v>
       </c>
       <c r="I58">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="J58">
-        <v>2100</v>
+        <v>1973</v>
       </c>
       <c r="K58">
-        <v>722</v>
+        <v>483</v>
       </c>
       <c r="L58">
-        <v>4571</v>
+        <v>4829</v>
       </c>
       <c r="M58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N58">
-        <v>224</v>
+        <v>272</v>
       </c>
       <c r="O58">
-        <v>14976</v>
+        <v>15152</v>
       </c>
       <c r="P58">
         <v>57577</v>
@@ -3742,31 +3742,31 @@
         <v>0</v>
       </c>
       <c r="G59">
-        <v>18762</v>
+        <v>18771</v>
       </c>
       <c r="H59">
         <v>0</v>
       </c>
       <c r="I59">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J59">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K59">
         <v>0</v>
       </c>
       <c r="L59">
-        <v>2485</v>
+        <v>2488</v>
       </c>
       <c r="M59">
         <v>2</v>
       </c>
       <c r="N59">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="O59">
-        <v>15990</v>
+        <v>15993</v>
       </c>
       <c r="P59">
         <v>60495</v>
@@ -3801,31 +3801,31 @@
         <v>0</v>
       </c>
       <c r="G60">
-        <v>22344</v>
+        <v>22579</v>
       </c>
       <c r="H60">
-        <v>733</v>
+        <v>631</v>
       </c>
       <c r="I60">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J60">
-        <v>1024</v>
+        <v>914</v>
       </c>
       <c r="K60">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="L60">
-        <v>4335</v>
+        <v>4531</v>
       </c>
       <c r="M60">
         <v>0</v>
       </c>
       <c r="N60">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="O60">
-        <v>20721</v>
+        <v>20865</v>
       </c>
       <c r="P60">
         <v>70140</v>
@@ -3869,13 +3869,13 @@
         <v>0</v>
       </c>
       <c r="J61">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="K61">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L61">
-        <v>9551</v>
+        <v>9558</v>
       </c>
       <c r="M61">
         <v>17</v>
@@ -3884,7 +3884,7 @@
         <v>1</v>
       </c>
       <c r="O61">
-        <v>13847</v>
+        <v>13948</v>
       </c>
       <c r="P61">
         <v>55240</v>
@@ -3919,16 +3919,16 @@
         <v>0</v>
       </c>
       <c r="G62">
-        <v>15115</v>
+        <v>15191</v>
       </c>
       <c r="H62">
-        <v>493</v>
+        <v>451</v>
       </c>
       <c r="I62">
-        <v>176</v>
+        <v>146</v>
       </c>
       <c r="J62">
-        <v>601</v>
+        <v>611</v>
       </c>
       <c r="K62">
         <v>40</v>
@@ -3940,7 +3940,7 @@
         <v>1</v>
       </c>
       <c r="N62">
-        <v>233</v>
+        <v>302</v>
       </c>
       <c r="O62">
         <v>14217</v>
@@ -3978,16 +3978,16 @@
         <v>0</v>
       </c>
       <c r="G63">
-        <v>36419</v>
+        <v>36533</v>
       </c>
       <c r="H63">
-        <v>134</v>
+        <v>46</v>
       </c>
       <c r="I63">
-        <v>200</v>
+        <v>174</v>
       </c>
       <c r="J63">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="K63">
         <v>0</v>
@@ -3999,10 +3999,10 @@
         <v>34</v>
       </c>
       <c r="N63">
-        <v>748</v>
+        <v>809</v>
       </c>
       <c r="O63">
-        <v>31420</v>
+        <v>31546</v>
       </c>
       <c r="P63">
         <v>68691</v>
@@ -4037,10 +4037,10 @@
         <v>0</v>
       </c>
       <c r="G64">
-        <v>38753</v>
+        <v>38964</v>
       </c>
       <c r="H64">
-        <v>2513</v>
+        <v>2310</v>
       </c>
       <c r="I64">
         <v>13</v>
@@ -4052,16 +4052,16 @@
         <v>0</v>
       </c>
       <c r="L64">
-        <v>8804</v>
+        <v>8857</v>
       </c>
       <c r="M64">
         <v>8</v>
       </c>
       <c r="N64">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="O64">
-        <v>35461</v>
+        <v>35634</v>
       </c>
       <c r="P64">
         <v>60527</v>
@@ -4096,31 +4096,31 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>32950</v>
+        <v>33911</v>
       </c>
       <c r="H65">
-        <v>6639</v>
+        <v>5822</v>
       </c>
       <c r="I65">
-        <v>477</v>
+        <v>428</v>
       </c>
       <c r="J65">
-        <v>6</v>
+        <v>359</v>
       </c>
       <c r="K65">
         <v>0</v>
       </c>
       <c r="L65">
-        <v>9683</v>
+        <v>9843</v>
       </c>
       <c r="M65">
         <v>2</v>
       </c>
       <c r="N65">
-        <v>428</v>
+        <v>487</v>
       </c>
       <c r="O65">
-        <v>23543</v>
+        <v>24359</v>
       </c>
       <c r="P65">
         <v>34607</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>46370</v>
+        <v>48573</v>
       </c>
       <c r="H66">
-        <v>12936</v>
+        <v>11039</v>
       </c>
       <c r="I66">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="J66">
-        <v>128</v>
+        <v>633</v>
       </c>
       <c r="K66">
         <v>0</v>
@@ -4176,10 +4176,10 @@
         <v>2</v>
       </c>
       <c r="N66">
-        <v>388</v>
+        <v>546</v>
       </c>
       <c r="O66">
-        <v>39584</v>
+        <v>41225</v>
       </c>
       <c r="P66">
         <v>93810</v>
@@ -4208,37 +4208,37 @@
         <v>0</v>
       </c>
       <c r="E67">
-        <v>68826</v>
+        <v>68828</v>
       </c>
       <c r="F67">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G67">
-        <v>58823</v>
+        <v>60533</v>
       </c>
       <c r="H67">
-        <v>3875</v>
+        <v>2339</v>
       </c>
       <c r="I67">
-        <v>2160</v>
+        <v>2040</v>
       </c>
       <c r="J67">
-        <v>154</v>
+        <v>629</v>
       </c>
       <c r="K67">
         <v>0</v>
       </c>
       <c r="L67">
-        <v>16425</v>
+        <v>16701</v>
       </c>
       <c r="M67">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N67">
-        <v>656</v>
+        <v>769</v>
       </c>
       <c r="O67">
-        <v>46007</v>
+        <v>46872</v>
       </c>
       <c r="P67">
         <v>78022</v>
@@ -4267,37 +4267,37 @@
         <v>0</v>
       </c>
       <c r="E68">
-        <v>65360</v>
+        <v>65362</v>
       </c>
       <c r="F68">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G68">
-        <v>58074</v>
+        <v>58665</v>
       </c>
       <c r="H68">
-        <v>6190</v>
+        <v>5649</v>
       </c>
       <c r="I68">
-        <v>796</v>
+        <v>765</v>
       </c>
       <c r="J68">
-        <v>331</v>
+        <v>463</v>
       </c>
       <c r="K68">
         <v>0</v>
       </c>
       <c r="L68">
-        <v>13972</v>
+        <v>14166</v>
       </c>
       <c r="M68">
         <v>2</v>
       </c>
       <c r="N68">
-        <v>281</v>
+        <v>304</v>
       </c>
       <c r="O68">
-        <v>48762</v>
+        <v>49254</v>
       </c>
       <c r="P68">
         <v>61338</v>
@@ -4332,34 +4332,34 @@
         <v>0</v>
       </c>
       <c r="G69">
-        <v>35302</v>
+        <v>35843</v>
       </c>
       <c r="H69">
-        <v>5825</v>
+        <v>5472</v>
       </c>
       <c r="I69">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="J69">
-        <v>511</v>
+        <v>225</v>
       </c>
       <c r="K69">
         <v>0</v>
       </c>
       <c r="L69">
-        <v>12664</v>
+        <v>13264</v>
       </c>
       <c r="M69">
         <v>2</v>
       </c>
       <c r="N69">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="O69">
-        <v>26350</v>
+        <v>26602</v>
       </c>
       <c r="P69">
-        <v>33793</v>
+        <v>33969</v>
       </c>
       <c r="Q69">
         <v>6528</v>
@@ -4391,31 +4391,31 @@
         <v>0</v>
       </c>
       <c r="G70">
-        <v>42525</v>
+        <v>42918</v>
       </c>
       <c r="H70">
-        <v>1841</v>
+        <v>1688</v>
       </c>
       <c r="I70">
-        <v>2403</v>
+        <v>2208</v>
       </c>
       <c r="J70">
-        <v>139</v>
+        <v>193</v>
       </c>
       <c r="K70">
         <v>0</v>
       </c>
       <c r="L70">
-        <v>16726</v>
+        <v>16834</v>
       </c>
       <c r="M70">
         <v>2</v>
       </c>
       <c r="N70">
-        <v>415</v>
+        <v>450</v>
       </c>
       <c r="O70">
-        <v>34499</v>
+        <v>34998</v>
       </c>
       <c r="P70">
         <v>42040</v>
@@ -4450,31 +4450,31 @@
         <v>0</v>
       </c>
       <c r="G71">
-        <v>44172</v>
+        <v>44856</v>
       </c>
       <c r="H71">
-        <v>4727</v>
+        <v>4381</v>
       </c>
       <c r="I71">
-        <v>1766</v>
+        <v>1431</v>
       </c>
       <c r="J71">
-        <v>124</v>
+        <v>50</v>
       </c>
       <c r="K71">
         <v>0</v>
       </c>
       <c r="L71">
-        <v>19916</v>
+        <v>20037</v>
       </c>
       <c r="M71">
         <v>1</v>
       </c>
       <c r="N71">
-        <v>1989</v>
+        <v>2495</v>
       </c>
       <c r="O71">
-        <v>31054</v>
+        <v>31257</v>
       </c>
       <c r="P71">
         <v>48896</v>
@@ -4509,31 +4509,31 @@
         <v>1</v>
       </c>
       <c r="G72">
-        <v>50024</v>
+        <v>51375</v>
       </c>
       <c r="H72">
-        <v>9270</v>
+        <v>8101</v>
       </c>
       <c r="I72">
-        <v>1783</v>
+        <v>1659</v>
       </c>
       <c r="J72">
-        <v>158</v>
+        <v>325</v>
       </c>
       <c r="K72">
         <v>0</v>
       </c>
       <c r="L72">
-        <v>14402</v>
+        <v>14612</v>
       </c>
       <c r="M72">
         <v>9</v>
       </c>
       <c r="N72">
-        <v>257</v>
+        <v>346</v>
       </c>
       <c r="O72">
-        <v>38899</v>
+        <v>39880</v>
       </c>
       <c r="P72">
         <v>85505</v>
@@ -4568,31 +4568,31 @@
         <v>0</v>
       </c>
       <c r="G73">
-        <v>43520</v>
+        <v>44837</v>
       </c>
       <c r="H73">
-        <v>14352</v>
+        <v>13083</v>
       </c>
       <c r="I73">
-        <v>331</v>
+        <v>267</v>
       </c>
       <c r="J73">
-        <v>629</v>
+        <v>389</v>
       </c>
       <c r="K73">
         <v>0</v>
       </c>
       <c r="L73">
-        <v>8020</v>
+        <v>8596</v>
       </c>
       <c r="M73">
         <v>4</v>
       </c>
       <c r="N73">
-        <v>245</v>
+        <v>400</v>
       </c>
       <c r="O73">
-        <v>37987</v>
+        <v>38947</v>
       </c>
       <c r="P73">
         <v>67550</v>
@@ -4618,40 +4618,40 @@
         <v>0</v>
       </c>
       <c r="E74">
-        <v>2428020</v>
+        <v>2428641</v>
       </c>
       <c r="F74">
-        <v>2362</v>
+        <v>1741</v>
       </c>
       <c r="G74">
-        <v>1862362</v>
+        <v>1911957</v>
       </c>
       <c r="H74">
-        <v>439963</v>
+        <v>400625</v>
       </c>
       <c r="I74">
-        <v>16586</v>
+        <v>14727</v>
       </c>
       <c r="J74">
-        <v>77338</v>
+        <v>77303</v>
       </c>
       <c r="K74">
-        <v>37135</v>
+        <v>35826</v>
       </c>
       <c r="L74">
-        <v>388649</v>
+        <v>402785</v>
       </c>
       <c r="M74">
-        <v>346</v>
+        <v>366</v>
       </c>
       <c r="N74">
-        <v>22156</v>
+        <v>24703</v>
       </c>
       <c r="O74">
-        <v>1565937</v>
+        <v>1613361</v>
       </c>
       <c r="P74">
-        <v>4216754</v>
+        <v>4246005</v>
       </c>
       <c r="Q74">
         <v>629685</v>

--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -1,41 +1,317 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\FormProcess\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5AB4BFD-4D2B-4BEE-A77B-E0796CDFE301}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
+  <si>
+    <t>S. No.</t>
+  </si>
+  <si>
+    <t>AC No. - AC Name</t>
+  </si>
+  <si>
+    <t>Notice Generated</t>
+  </si>
+  <si>
+    <t>Pending for Notice Generation</t>
+  </si>
+  <si>
+    <t>Notice Delivered</t>
+  </si>
+  <si>
+    <t>Notices pending delivery</t>
+  </si>
+  <si>
+    <t>Hearing</t>
+  </si>
+  <si>
+    <t>DEO Status</t>
+  </si>
+  <si>
+    <t>ERO/AERO Status</t>
+  </si>
+  <si>
+    <t>DSE with UP</t>
+  </si>
+  <si>
+    <t>Hearing Held</t>
+  </si>
+  <si>
+    <t>Hearing Date Lapsed</t>
+  </si>
+  <si>
+    <t>Reschedule Date Lapsed</t>
+  </si>
+  <si>
+    <t>Total Pending</t>
+  </si>
+  <si>
+    <t>Pending &gt; 5 days</t>
+  </si>
+  <si>
+    <t>Verified</t>
+  </si>
+  <si>
+    <t>Not Verified</t>
+  </si>
+  <si>
+    <t>Found Ineligible for Final</t>
+  </si>
+  <si>
+    <t>Parked for Final Publication w.r.t. Notices Generated</t>
+  </si>
+  <si>
+    <t>Parked For Final Publication w.r.t. Others</t>
+  </si>
+  <si>
+    <t>Electors having DSE with UP</t>
+  </si>
+  <si>
+    <t>Form 7 Generated</t>
+  </si>
+  <si>
+    <t>No Action Required</t>
+  </si>
+  <si>
+    <t>25 - Haridwar</t>
+  </si>
+  <si>
+    <t>26 - BHEL Ranipur</t>
+  </si>
+  <si>
+    <t>27 - Jwalapur</t>
+  </si>
+  <si>
+    <t>28 - Bhagwanpur</t>
+  </si>
+  <si>
+    <t>29 - Jhabrera</t>
+  </si>
+  <si>
+    <t>30 - Piran Kaliyar</t>
+  </si>
+  <si>
+    <t>31 - Roorkee</t>
+  </si>
+  <si>
+    <t>32 - Khanpur</t>
+  </si>
+  <si>
+    <t>33 - Manglore</t>
+  </si>
+  <si>
+    <t>34 - Laksar</t>
+  </si>
+  <si>
+    <t>35 - Haridwar Rural</t>
+  </si>
+  <si>
+    <t>56 - Lalkuan</t>
+  </si>
+  <si>
+    <t>57 - Bhimtal</t>
+  </si>
+  <si>
+    <t>58 - Nainital</t>
+  </si>
+  <si>
+    <t>59 - Haldwani</t>
+  </si>
+  <si>
+    <t>60 - Kaladhungi</t>
+  </si>
+  <si>
+    <t>61 - Ramnagar</t>
+  </si>
+  <si>
+    <t>48 - Dwarahat</t>
+  </si>
+  <si>
+    <t>49 - Salt</t>
+  </si>
+  <si>
+    <t>50 - Ranikhet</t>
+  </si>
+  <si>
+    <t>51 - Someshwar</t>
+  </si>
+  <si>
+    <t>52 - Almora</t>
+  </si>
+  <si>
+    <t>53 - Jageshwar</t>
+  </si>
+  <si>
+    <t>62 - Jaspur</t>
+  </si>
+  <si>
+    <t>63 - Kashipur</t>
+  </si>
+  <si>
+    <t>64 - Bajpur</t>
+  </si>
+  <si>
+    <t>65 - Gadarpur</t>
+  </si>
+  <si>
+    <t>66 - Rudrapur</t>
+  </si>
+  <si>
+    <t>67 - Kichha</t>
+  </si>
+  <si>
+    <t>68 - Sitarganj</t>
+  </si>
+  <si>
+    <t>69 - Nanakmatta</t>
+  </si>
+  <si>
+    <t>70 - Khatima</t>
+  </si>
+  <si>
+    <t>42 - Dharchula</t>
+  </si>
+  <si>
+    <t>43 - Didihat</t>
+  </si>
+  <si>
+    <t>44 - Pithoragarh</t>
+  </si>
+  <si>
+    <t>45 - Gangolihat</t>
+  </si>
+  <si>
+    <t>46 - Kapkot</t>
+  </si>
+  <si>
+    <t>47 - Bageshwar</t>
+  </si>
+  <si>
+    <t>54 - Lohaghat</t>
+  </si>
+  <si>
+    <t>55 - Champawat</t>
+  </si>
+  <si>
+    <t>4 - Badrinath</t>
+  </si>
+  <si>
+    <t>5 - Tharali</t>
+  </si>
+  <si>
+    <t>6 - Karanprayag</t>
+  </si>
+  <si>
+    <t>1 - Purola</t>
+  </si>
+  <si>
+    <t>2 - Yamunotri</t>
+  </si>
+  <si>
+    <t>3 - Gangotri</t>
+  </si>
+  <si>
+    <t>7 - Kedarnath</t>
+  </si>
+  <si>
+    <t>8 - Rudraprayag</t>
+  </si>
+  <si>
+    <t>9 - Ghansali</t>
+  </si>
+  <si>
+    <t>10 - Devprayag</t>
+  </si>
+  <si>
+    <t>11 - Narendranagar</t>
+  </si>
+  <si>
+    <t>12 - Pratapnagar</t>
+  </si>
+  <si>
+    <t>13 - Tehri</t>
+  </si>
+  <si>
+    <t>14 - Dhanolti</t>
+  </si>
+  <si>
+    <t>36 - Yamkeshwar</t>
+  </si>
+  <si>
+    <t>37 - Pauri</t>
+  </si>
+  <si>
+    <t>38 - Srinagar</t>
+  </si>
+  <si>
+    <t>39 - Chaubattakhal</t>
+  </si>
+  <si>
+    <t>40 - Lansdowne</t>
+  </si>
+  <si>
+    <t>41 - Kotdwar</t>
+  </si>
+  <si>
+    <t>15 - Chakrata</t>
+  </si>
+  <si>
+    <t>16 - Vikasnagar</t>
+  </si>
+  <si>
+    <t>17 - Sahaspur</t>
+  </si>
+  <si>
+    <t>18 - Dharmpur</t>
+  </si>
+  <si>
+    <t>19 - Raipur</t>
+  </si>
+  <si>
+    <t>20 - Rajpur Road</t>
+  </si>
+  <si>
+    <t>21 - Dehradun Cantonment</t>
+  </si>
+  <si>
+    <t>22 - Mussoorie</t>
+  </si>
+  <si>
+    <t>23 - Doiwala</t>
+  </si>
+  <si>
+    <t>24 - Rishikesh</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Notice &amp; Hearing Report Last Updated On : 25-08-2026 13:57:23</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -64,14 +340,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,93 +681,128 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S74"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:T74"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Notice &amp; Hearing Report</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>S. No.</v>
-      </c>
-      <c r="B2" t="str">
-        <v>AC No. - AC Name</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Notice Generated</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Pending for Notice Generation</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Notice Delivered</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Notices pending delivery</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Hearing</v>
-      </c>
-      <c r="J2" t="str">
-        <v>DEO Status</v>
-      </c>
-      <c r="N2" t="str">
-        <v>ERO/AERO Status</v>
-      </c>
-      <c r="Q2" t="str">
-        <v>DSE with UP</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="G3" t="str">
-        <v>Hearing Held</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Hearing Date Lapsed</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Reschedule Date Lapsed</v>
-      </c>
-      <c r="J3" t="str">
-        <v>Total Pending</v>
-      </c>
-      <c r="K3" t="str">
-        <v>Pending &gt; 5 days</v>
-      </c>
-      <c r="L3" t="str">
-        <v>Verified</v>
-      </c>
-      <c r="M3" t="str">
-        <v>Not Verified</v>
-      </c>
-      <c r="N3" t="str">
-        <v>Found Ineligible for Final</v>
-      </c>
-      <c r="O3" t="str">
-        <v>Parked for Final Publication w.r.t. Notices Generated</v>
-      </c>
-      <c r="P3" t="str">
-        <v>Parked For Final Publication w.r.t. Others</v>
-      </c>
-      <c r="Q3" t="str">
-        <v>Electors having DSE with UP</v>
-      </c>
-      <c r="R3" t="str">
-        <v>Form 7 Generated</v>
-      </c>
-      <c r="S3" t="str">
-        <v>No Action Required</v>
-      </c>
-    </row>
-    <row r="4">
+    <row r="1" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+    </row>
+    <row r="2" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+    </row>
+    <row r="3" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N3" t="s">
+        <v>17</v>
+      </c>
+      <c r="O3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R3" t="s">
+        <v>21</v>
+      </c>
+      <c r="S3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" t="str">
-        <v>25 - Haridwar</v>
+      <c r="B4" t="s">
+        <v>23</v>
       </c>
       <c r="C4">
         <v>51528</v>
@@ -536,12 +856,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
-      <c r="B5" t="str">
-        <v>26 - BHEL Ranipur</v>
+      <c r="B5" t="s">
+        <v>24</v>
       </c>
       <c r="C5">
         <v>53911</v>
@@ -595,12 +915,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
-      <c r="B6" t="str">
-        <v>27 - Jwalapur</v>
+      <c r="B6" t="s">
+        <v>25</v>
       </c>
       <c r="C6">
         <v>39773</v>
@@ -654,12 +974,12 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4</v>
       </c>
-      <c r="B7" t="str">
-        <v>28 - Bhagwanpur</v>
+      <c r="B7" t="s">
+        <v>26</v>
       </c>
       <c r="C7">
         <v>39463</v>
@@ -713,12 +1033,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
-      <c r="B8" t="str">
-        <v>29 - Jhabrera</v>
+      <c r="B8" t="s">
+        <v>27</v>
       </c>
       <c r="C8">
         <v>40552</v>
@@ -772,12 +1092,12 @@
         <v>110</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6</v>
       </c>
-      <c r="B9" t="str">
-        <v>30 - Piran Kaliyar</v>
+      <c r="B9" t="s">
+        <v>28</v>
       </c>
       <c r="C9">
         <v>43273</v>
@@ -831,12 +1151,12 @@
         <v>110</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>7</v>
       </c>
-      <c r="B10" t="str">
-        <v>31 - Roorkee</v>
+      <c r="B10" t="s">
+        <v>29</v>
       </c>
       <c r="C10">
         <v>36576</v>
@@ -890,12 +1210,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>8</v>
       </c>
-      <c r="B11" t="str">
-        <v>32 - Khanpur</v>
+      <c r="B11" t="s">
+        <v>30</v>
       </c>
       <c r="C11">
         <v>50998</v>
@@ -949,12 +1269,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
-      <c r="B12" t="str">
-        <v>33 - Manglore</v>
+      <c r="B12" t="s">
+        <v>31</v>
       </c>
       <c r="C12">
         <v>40739</v>
@@ -1008,12 +1328,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
-      <c r="B13" t="str">
-        <v>34 - Laksar</v>
+      <c r="B13" t="s">
+        <v>32</v>
       </c>
       <c r="C13">
         <v>37031</v>
@@ -1067,12 +1387,12 @@
         <v>109</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>11</v>
       </c>
-      <c r="B14" t="str">
-        <v>35 - Haridwar Rural</v>
+      <c r="B14" t="s">
+        <v>33</v>
       </c>
       <c r="C14">
         <v>48966</v>
@@ -1126,12 +1446,12 @@
         <v>174</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12</v>
       </c>
-      <c r="B15" t="str">
-        <v>56 - Lalkuan</v>
+      <c r="B15" t="s">
+        <v>34</v>
       </c>
       <c r="C15">
         <v>42703</v>
@@ -1185,12 +1505,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13</v>
       </c>
-      <c r="B16" t="str">
-        <v>57 - Bhimtal</v>
+      <c r="B16" t="s">
+        <v>35</v>
       </c>
       <c r="C16">
         <v>25549</v>
@@ -1244,12 +1564,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>14</v>
       </c>
-      <c r="B17" t="str">
-        <v>58 - Nainital</v>
+      <c r="B17" t="s">
+        <v>36</v>
       </c>
       <c r="C17">
         <v>27707</v>
@@ -1303,12 +1623,12 @@
         <v>105</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>15</v>
       </c>
-      <c r="B18" t="str">
-        <v>59 - Haldwani</v>
+      <c r="B18" t="s">
+        <v>37</v>
       </c>
       <c r="C18">
         <v>47836</v>
@@ -1362,12 +1682,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>16</v>
       </c>
-      <c r="B19" t="str">
-        <v>60 - Kaladhungi</v>
+      <c r="B19" t="s">
+        <v>38</v>
       </c>
       <c r="C19">
         <v>56490</v>
@@ -1421,12 +1741,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>17</v>
       </c>
-      <c r="B20" t="str">
-        <v>61 - Ramnagar</v>
+      <c r="B20" t="s">
+        <v>39</v>
       </c>
       <c r="C20">
         <v>35017</v>
@@ -1480,12 +1800,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>18</v>
       </c>
-      <c r="B21" t="str">
-        <v>48 - Dwarahat</v>
+      <c r="B21" t="s">
+        <v>40</v>
       </c>
       <c r="C21">
         <v>16962</v>
@@ -1539,12 +1859,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>19</v>
       </c>
-      <c r="B22" t="str">
-        <v>49 - Salt</v>
+      <c r="B22" t="s">
+        <v>41</v>
       </c>
       <c r="C22">
         <v>18668</v>
@@ -1598,12 +1918,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>20</v>
       </c>
-      <c r="B23" t="str">
-        <v>50 - Ranikhet</v>
+      <c r="B23" t="s">
+        <v>42</v>
       </c>
       <c r="C23">
         <v>12020</v>
@@ -1657,12 +1977,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>21</v>
       </c>
-      <c r="B24" t="str">
-        <v>51 - Someshwar</v>
+      <c r="B24" t="s">
+        <v>43</v>
       </c>
       <c r="C24">
         <v>14056</v>
@@ -1716,12 +2036,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>22</v>
       </c>
-      <c r="B25" t="str">
-        <v>52 - Almora</v>
+      <c r="B25" t="s">
+        <v>44</v>
       </c>
       <c r="C25">
         <v>19266</v>
@@ -1775,12 +2095,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23</v>
       </c>
-      <c r="B26" t="str">
-        <v>53 - Jageshwar</v>
+      <c r="B26" t="s">
+        <v>45</v>
       </c>
       <c r="C26">
         <v>17557</v>
@@ -1834,12 +2154,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>24</v>
       </c>
-      <c r="B27" t="str">
-        <v>62 - Jaspur</v>
+      <c r="B27" t="s">
+        <v>46</v>
       </c>
       <c r="C27">
         <v>44276</v>
@@ -1893,12 +2213,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25</v>
       </c>
-      <c r="B28" t="str">
-        <v>63 - Kashipur</v>
+      <c r="B28" t="s">
+        <v>47</v>
       </c>
       <c r="C28">
         <v>54349</v>
@@ -1952,12 +2272,12 @@
         <v>134</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26</v>
       </c>
-      <c r="B29" t="str">
-        <v>64 - Bajpur</v>
+      <c r="B29" t="s">
+        <v>48</v>
       </c>
       <c r="C29">
         <v>47111</v>
@@ -2011,12 +2331,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>27</v>
       </c>
-      <c r="B30" t="str">
-        <v>65 - Gadarpur</v>
+      <c r="B30" t="s">
+        <v>49</v>
       </c>
       <c r="C30">
         <v>52653</v>
@@ -2070,12 +2390,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>28</v>
       </c>
-      <c r="B31" t="str">
-        <v>66 - Rudrapur</v>
+      <c r="B31" t="s">
+        <v>50</v>
       </c>
       <c r="C31">
         <v>91162</v>
@@ -2129,12 +2449,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>29</v>
       </c>
-      <c r="B32" t="str">
-        <v>67 - Kichha</v>
+      <c r="B32" t="s">
+        <v>51</v>
       </c>
       <c r="C32">
         <v>46728</v>
@@ -2188,12 +2508,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>30</v>
       </c>
-      <c r="B33" t="str">
-        <v>68 - Sitarganj</v>
+      <c r="B33" t="s">
+        <v>52</v>
       </c>
       <c r="C33">
         <v>40230</v>
@@ -2247,12 +2567,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>31</v>
       </c>
-      <c r="B34" t="str">
-        <v>69 - Nanakmatta</v>
+      <c r="B34" t="s">
+        <v>53</v>
       </c>
       <c r="C34">
         <v>36542</v>
@@ -2306,12 +2626,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32</v>
       </c>
-      <c r="B35" t="str">
-        <v>70 - Khatima</v>
+      <c r="B35" t="s">
+        <v>54</v>
       </c>
       <c r="C35">
         <v>33564</v>
@@ -2365,12 +2685,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>33</v>
       </c>
-      <c r="B36" t="str">
-        <v>42 - Dharchula</v>
+      <c r="B36" t="s">
+        <v>55</v>
       </c>
       <c r="C36">
         <v>20905</v>
@@ -2424,12 +2744,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>34</v>
       </c>
-      <c r="B37" t="str">
-        <v>43 - Didihat</v>
+      <c r="B37" t="s">
+        <v>56</v>
       </c>
       <c r="C37">
         <v>17692</v>
@@ -2483,12 +2803,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>35</v>
       </c>
-      <c r="B38" t="str">
-        <v>44 - Pithoragarh</v>
+      <c r="B38" t="s">
+        <v>57</v>
       </c>
       <c r="C38">
         <v>29110</v>
@@ -2542,12 +2862,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>36</v>
       </c>
-      <c r="B39" t="str">
-        <v>45 - Gangolihat</v>
+      <c r="B39" t="s">
+        <v>58</v>
       </c>
       <c r="C39">
         <v>21367</v>
@@ -2601,12 +2921,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>37</v>
       </c>
-      <c r="B40" t="str">
-        <v>46 - Kapkot</v>
+      <c r="B40" t="s">
+        <v>59</v>
       </c>
       <c r="C40">
         <v>18905</v>
@@ -2660,12 +2980,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>38</v>
       </c>
-      <c r="B41" t="str">
-        <v>47 - Bageshwar</v>
+      <c r="B41" t="s">
+        <v>60</v>
       </c>
       <c r="C41">
         <v>23521</v>
@@ -2719,12 +3039,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>39</v>
       </c>
-      <c r="B42" t="str">
-        <v>54 - Lohaghat</v>
+      <c r="B42" t="s">
+        <v>61</v>
       </c>
       <c r="C42">
         <v>27565</v>
@@ -2778,12 +3098,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>40</v>
       </c>
-      <c r="B43" t="str">
-        <v>55 - Champawat</v>
+      <c r="B43" t="s">
+        <v>62</v>
       </c>
       <c r="C43">
         <v>29700</v>
@@ -2837,12 +3157,12 @@
         <v>121</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>41</v>
       </c>
-      <c r="B44" t="str">
-        <v>4 - Badrinath</v>
+      <c r="B44" t="s">
+        <v>63</v>
       </c>
       <c r="C44">
         <v>21900</v>
@@ -2896,12 +3216,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>42</v>
       </c>
-      <c r="B45" t="str">
-        <v>5 - Tharali</v>
+      <c r="B45" t="s">
+        <v>64</v>
       </c>
       <c r="C45">
         <v>19935</v>
@@ -2955,12 +3275,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>43</v>
       </c>
-      <c r="B46" t="str">
-        <v>6 - Karanprayag</v>
+      <c r="B46" t="s">
+        <v>65</v>
       </c>
       <c r="C46">
         <v>21512</v>
@@ -3014,12 +3334,12 @@
         <v>152</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>44</v>
       </c>
-      <c r="B47" t="str">
-        <v>1 - Purola</v>
+      <c r="B47" t="s">
+        <v>66</v>
       </c>
       <c r="C47">
         <v>22426</v>
@@ -3073,12 +3393,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>45</v>
       </c>
-      <c r="B48" t="str">
-        <v>2 - Yamunotri</v>
+      <c r="B48" t="s">
+        <v>67</v>
       </c>
       <c r="C48">
         <v>19641</v>
@@ -3132,12 +3452,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>46</v>
       </c>
-      <c r="B49" t="str">
-        <v>3 - Gangotri</v>
+      <c r="B49" t="s">
+        <v>68</v>
       </c>
       <c r="C49">
         <v>21651</v>
@@ -3191,12 +3511,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>47</v>
       </c>
-      <c r="B50" t="str">
-        <v>7 - Kedarnath</v>
+      <c r="B50" t="s">
+        <v>69</v>
       </c>
       <c r="C50">
         <v>21936</v>
@@ -3250,12 +3570,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>48</v>
       </c>
-      <c r="B51" t="str">
-        <v>8 - Rudraprayag</v>
+      <c r="B51" t="s">
+        <v>70</v>
       </c>
       <c r="C51">
         <v>23798</v>
@@ -3309,12 +3629,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>49</v>
       </c>
-      <c r="B52" t="str">
-        <v>9 - Ghansali</v>
+      <c r="B52" t="s">
+        <v>71</v>
       </c>
       <c r="C52">
         <v>21094</v>
@@ -3368,12 +3688,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>50</v>
       </c>
-      <c r="B53" t="str">
-        <v>10 - Devprayag</v>
+      <c r="B53" t="s">
+        <v>72</v>
       </c>
       <c r="C53">
         <v>19131</v>
@@ -3427,12 +3747,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>51</v>
       </c>
-      <c r="B54" t="str">
-        <v>11 - Narendranagar</v>
+      <c r="B54" t="s">
+        <v>73</v>
       </c>
       <c r="C54">
         <v>20758</v>
@@ -3486,12 +3806,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>52</v>
       </c>
-      <c r="B55" t="str">
-        <v>12 - Pratapnagar</v>
+      <c r="B55" t="s">
+        <v>74</v>
       </c>
       <c r="C55">
         <v>16022</v>
@@ -3545,12 +3865,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>53</v>
       </c>
-      <c r="B56" t="str">
-        <v>13 - Tehri</v>
+      <c r="B56" t="s">
+        <v>75</v>
       </c>
       <c r="C56">
         <v>19256</v>
@@ -3604,12 +3924,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>54</v>
       </c>
-      <c r="B57" t="str">
-        <v>14 - Dhanolti</v>
+      <c r="B57" t="s">
+        <v>76</v>
       </c>
       <c r="C57">
         <v>21240</v>
@@ -3663,12 +3983,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>55</v>
       </c>
-      <c r="B58" t="str">
-        <v>36 - Yamkeshwar</v>
+      <c r="B58" t="s">
+        <v>77</v>
       </c>
       <c r="C58">
         <v>22819</v>
@@ -3722,12 +4042,12 @@
         <v>64</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>56</v>
       </c>
-      <c r="B59" t="str">
-        <v>37 - Pauri</v>
+      <c r="B59" t="s">
+        <v>78</v>
       </c>
       <c r="C59">
         <v>18776</v>
@@ -3781,12 +4101,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>57</v>
       </c>
-      <c r="B60" t="str">
-        <v>38 - Srinagar</v>
+      <c r="B60" t="s">
+        <v>79</v>
       </c>
       <c r="C60">
         <v>23749</v>
@@ -3840,12 +4160,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>58</v>
       </c>
-      <c r="B61" t="str">
-        <v>39 - Chaubattakhal</v>
+      <c r="B61" t="s">
+        <v>80</v>
       </c>
       <c r="C61">
         <v>22069</v>
@@ -3899,12 +4219,12 @@
         <v>268</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>59</v>
       </c>
-      <c r="B62" t="str">
-        <v>40 - Lansdowne</v>
+      <c r="B62" t="s">
+        <v>81</v>
       </c>
       <c r="C62">
         <v>15800</v>
@@ -3958,12 +4278,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>60</v>
       </c>
-      <c r="B63" t="str">
-        <v>41 - Kotdwar</v>
+      <c r="B63" t="s">
+        <v>82</v>
       </c>
       <c r="C63">
         <v>36754</v>
@@ -4017,12 +4337,12 @@
         <v>153</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>61</v>
       </c>
-      <c r="B64" t="str">
-        <v>15 - Chakrata</v>
+      <c r="B64" t="s">
+        <v>83</v>
       </c>
       <c r="C64">
         <v>42048</v>
@@ -4076,12 +4396,12 @@
         <v>101</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>62</v>
       </c>
-      <c r="B65" t="str">
-        <v>16 - Vikasnagar</v>
+      <c r="B65" t="s">
+        <v>84</v>
       </c>
       <c r="C65">
         <v>41389</v>
@@ -4135,12 +4455,12 @@
         <v>138</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>63</v>
       </c>
-      <c r="B66" t="str">
-        <v>17 - Sahaspur</v>
+      <c r="B66" t="s">
+        <v>85</v>
       </c>
       <c r="C66">
         <v>67362</v>
@@ -4194,12 +4514,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>64</v>
       </c>
-      <c r="B67" t="str">
-        <v>18 - Dharmpur</v>
+      <c r="B67" t="s">
+        <v>86</v>
       </c>
       <c r="C67">
         <v>68828</v>
@@ -4253,12 +4573,12 @@
         <v>116</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>65</v>
       </c>
-      <c r="B68" t="str">
-        <v>19 - Raipur</v>
+      <c r="B68" t="s">
+        <v>87</v>
       </c>
       <c r="C68">
         <v>65397</v>
@@ -4312,12 +4632,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>66</v>
       </c>
-      <c r="B69" t="str">
-        <v>20 - Rajpur Road</v>
+      <c r="B69" t="s">
+        <v>88</v>
       </c>
       <c r="C69">
         <v>43938</v>
@@ -4371,12 +4691,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>67</v>
       </c>
-      <c r="B70" t="str">
-        <v>21 - Dehradun Cantonment</v>
+      <c r="B70" t="s">
+        <v>89</v>
       </c>
       <c r="C70">
         <v>47711</v>
@@ -4430,12 +4750,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>68</v>
       </c>
-      <c r="B71" t="str">
-        <v>22 - Mussoorie</v>
+      <c r="B71" t="s">
+        <v>90</v>
       </c>
       <c r="C71">
         <v>50963</v>
@@ -4489,12 +4809,12 @@
         <v>235</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>69</v>
       </c>
-      <c r="B72" t="str">
-        <v>23 - Doiwala</v>
+      <c r="B72" t="s">
+        <v>91</v>
       </c>
       <c r="C72">
         <v>61543</v>
@@ -4548,12 +4868,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>70</v>
       </c>
-      <c r="B73" t="str">
-        <v>24 - Rishikesh</v>
+      <c r="B73" t="s">
+        <v>92</v>
       </c>
       <c r="C73">
         <v>58915</v>
@@ -4607,10 +4927,11 @@
         <v>74</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="str">
-        <v>Total</v>
-      </c>
+    <row r="74" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B74" s="1"/>
       <c r="C74">
         <v>2430382</v>
       </c>
@@ -4665,6 +4986,7 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A74:B74"/>
     <mergeCell ref="A1:T1"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
@@ -4676,10 +4998,10 @@
     <mergeCell ref="J2:M2"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="A74:B74"/>
   </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S74"/>
+    <ignoredError sqref="A2:S74 B1:S1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -1,317 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\FormProcess\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5AB4BFD-4D2B-4BEE-A77B-E0796CDFE301}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
-  <si>
-    <t>S. No.</t>
-  </si>
-  <si>
-    <t>AC No. - AC Name</t>
-  </si>
-  <si>
-    <t>Notice Generated</t>
-  </si>
-  <si>
-    <t>Pending for Notice Generation</t>
-  </si>
-  <si>
-    <t>Notice Delivered</t>
-  </si>
-  <si>
-    <t>Notices pending delivery</t>
-  </si>
-  <si>
-    <t>Hearing</t>
-  </si>
-  <si>
-    <t>DEO Status</t>
-  </si>
-  <si>
-    <t>ERO/AERO Status</t>
-  </si>
-  <si>
-    <t>DSE with UP</t>
-  </si>
-  <si>
-    <t>Hearing Held</t>
-  </si>
-  <si>
-    <t>Hearing Date Lapsed</t>
-  </si>
-  <si>
-    <t>Reschedule Date Lapsed</t>
-  </si>
-  <si>
-    <t>Total Pending</t>
-  </si>
-  <si>
-    <t>Pending &gt; 5 days</t>
-  </si>
-  <si>
-    <t>Verified</t>
-  </si>
-  <si>
-    <t>Not Verified</t>
-  </si>
-  <si>
-    <t>Found Ineligible for Final</t>
-  </si>
-  <si>
-    <t>Parked for Final Publication w.r.t. Notices Generated</t>
-  </si>
-  <si>
-    <t>Parked For Final Publication w.r.t. Others</t>
-  </si>
-  <si>
-    <t>Electors having DSE with UP</t>
-  </si>
-  <si>
-    <t>Form 7 Generated</t>
-  </si>
-  <si>
-    <t>No Action Required</t>
-  </si>
-  <si>
-    <t>25 - Haridwar</t>
-  </si>
-  <si>
-    <t>26 - BHEL Ranipur</t>
-  </si>
-  <si>
-    <t>27 - Jwalapur</t>
-  </si>
-  <si>
-    <t>28 - Bhagwanpur</t>
-  </si>
-  <si>
-    <t>29 - Jhabrera</t>
-  </si>
-  <si>
-    <t>30 - Piran Kaliyar</t>
-  </si>
-  <si>
-    <t>31 - Roorkee</t>
-  </si>
-  <si>
-    <t>32 - Khanpur</t>
-  </si>
-  <si>
-    <t>33 - Manglore</t>
-  </si>
-  <si>
-    <t>34 - Laksar</t>
-  </si>
-  <si>
-    <t>35 - Haridwar Rural</t>
-  </si>
-  <si>
-    <t>56 - Lalkuan</t>
-  </si>
-  <si>
-    <t>57 - Bhimtal</t>
-  </si>
-  <si>
-    <t>58 - Nainital</t>
-  </si>
-  <si>
-    <t>59 - Haldwani</t>
-  </si>
-  <si>
-    <t>60 - Kaladhungi</t>
-  </si>
-  <si>
-    <t>61 - Ramnagar</t>
-  </si>
-  <si>
-    <t>48 - Dwarahat</t>
-  </si>
-  <si>
-    <t>49 - Salt</t>
-  </si>
-  <si>
-    <t>50 - Ranikhet</t>
-  </si>
-  <si>
-    <t>51 - Someshwar</t>
-  </si>
-  <si>
-    <t>52 - Almora</t>
-  </si>
-  <si>
-    <t>53 - Jageshwar</t>
-  </si>
-  <si>
-    <t>62 - Jaspur</t>
-  </si>
-  <si>
-    <t>63 - Kashipur</t>
-  </si>
-  <si>
-    <t>64 - Bajpur</t>
-  </si>
-  <si>
-    <t>65 - Gadarpur</t>
-  </si>
-  <si>
-    <t>66 - Rudrapur</t>
-  </si>
-  <si>
-    <t>67 - Kichha</t>
-  </si>
-  <si>
-    <t>68 - Sitarganj</t>
-  </si>
-  <si>
-    <t>69 - Nanakmatta</t>
-  </si>
-  <si>
-    <t>70 - Khatima</t>
-  </si>
-  <si>
-    <t>42 - Dharchula</t>
-  </si>
-  <si>
-    <t>43 - Didihat</t>
-  </si>
-  <si>
-    <t>44 - Pithoragarh</t>
-  </si>
-  <si>
-    <t>45 - Gangolihat</t>
-  </si>
-  <si>
-    <t>46 - Kapkot</t>
-  </si>
-  <si>
-    <t>47 - Bageshwar</t>
-  </si>
-  <si>
-    <t>54 - Lohaghat</t>
-  </si>
-  <si>
-    <t>55 - Champawat</t>
-  </si>
-  <si>
-    <t>4 - Badrinath</t>
-  </si>
-  <si>
-    <t>5 - Tharali</t>
-  </si>
-  <si>
-    <t>6 - Karanprayag</t>
-  </si>
-  <si>
-    <t>1 - Purola</t>
-  </si>
-  <si>
-    <t>2 - Yamunotri</t>
-  </si>
-  <si>
-    <t>3 - Gangotri</t>
-  </si>
-  <si>
-    <t>7 - Kedarnath</t>
-  </si>
-  <si>
-    <t>8 - Rudraprayag</t>
-  </si>
-  <si>
-    <t>9 - Ghansali</t>
-  </si>
-  <si>
-    <t>10 - Devprayag</t>
-  </si>
-  <si>
-    <t>11 - Narendranagar</t>
-  </si>
-  <si>
-    <t>12 - Pratapnagar</t>
-  </si>
-  <si>
-    <t>13 - Tehri</t>
-  </si>
-  <si>
-    <t>14 - Dhanolti</t>
-  </si>
-  <si>
-    <t>36 - Yamkeshwar</t>
-  </si>
-  <si>
-    <t>37 - Pauri</t>
-  </si>
-  <si>
-    <t>38 - Srinagar</t>
-  </si>
-  <si>
-    <t>39 - Chaubattakhal</t>
-  </si>
-  <si>
-    <t>40 - Lansdowne</t>
-  </si>
-  <si>
-    <t>41 - Kotdwar</t>
-  </si>
-  <si>
-    <t>15 - Chakrata</t>
-  </si>
-  <si>
-    <t>16 - Vikasnagar</t>
-  </si>
-  <si>
-    <t>17 - Sahaspur</t>
-  </si>
-  <si>
-    <t>18 - Dharmpur</t>
-  </si>
-  <si>
-    <t>19 - Raipur</t>
-  </si>
-  <si>
-    <t>20 - Rajpur Road</t>
-  </si>
-  <si>
-    <t>21 - Dehradun Cantonment</t>
-  </si>
-  <si>
-    <t>22 - Mussoorie</t>
-  </si>
-  <si>
-    <t>23 - Doiwala</t>
-  </si>
-  <si>
-    <t>24 - Rishikesh</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Notice &amp; Hearing Report Last Updated On : 25-08-2026 13:57:23</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -340,23 +64,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -681,128 +396,93 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T74"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S74"/>
   <sheetData>
-    <row r="1" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-    </row>
-    <row r="2" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-    </row>
-    <row r="3" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K3" t="s">
-        <v>14</v>
-      </c>
-      <c r="L3" t="s">
-        <v>15</v>
-      </c>
-      <c r="M3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N3" t="s">
-        <v>17</v>
-      </c>
-      <c r="O3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P3" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R3" t="s">
-        <v>21</v>
-      </c>
-      <c r="S3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Notice &amp; Hearing Report</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>S. No.</v>
+      </c>
+      <c r="B2" t="str">
+        <v>AC No. - AC Name</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Notice Generated</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Pending for Notice Generation</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Notice Delivered</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Notices pending delivery</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Hearing</v>
+      </c>
+      <c r="J2" t="str">
+        <v>DEO Status</v>
+      </c>
+      <c r="N2" t="str">
+        <v>ERO/AERO Status</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>DSE with UP</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="G3" t="str">
+        <v>Hearing Held</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Hearing Date Lapsed</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Reschedule Date Lapsed</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Total Pending</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Pending &gt; 5 days</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Verified</v>
+      </c>
+      <c r="M3" t="str">
+        <v>Not Verified</v>
+      </c>
+      <c r="N3" t="str">
+        <v>Found Ineligible for Final</v>
+      </c>
+      <c r="O3" t="str">
+        <v>Parked for Final Publication w.r.t. Notices Generated</v>
+      </c>
+      <c r="P3" t="str">
+        <v>Parked For Final Publication w.r.t. Others</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>Electors having DSE with UP</v>
+      </c>
+      <c r="R3" t="str">
+        <v>Form 7 Generated</v>
+      </c>
+      <c r="S3" t="str">
+        <v>No Action Required</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" t="s">
-        <v>23</v>
+      <c r="B4" t="str">
+        <v>25 - Haridwar</v>
       </c>
       <c r="C4">
         <v>51528</v>
@@ -817,31 +497,31 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>24686</v>
+        <v>29665</v>
       </c>
       <c r="H4">
-        <v>20291</v>
+        <v>17738</v>
       </c>
       <c r="I4">
         <v>10</v>
       </c>
       <c r="J4">
-        <v>6086</v>
+        <v>5691</v>
       </c>
       <c r="K4">
-        <v>3057</v>
+        <v>2902</v>
       </c>
       <c r="L4">
-        <v>2022</v>
+        <v>2870</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>107</v>
+        <v>158</v>
       </c>
       <c r="O4">
-        <v>17611</v>
+        <v>22187</v>
       </c>
       <c r="P4">
         <v>53812</v>
@@ -856,12 +536,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5">
         <v>2</v>
       </c>
-      <c r="B5" t="s">
-        <v>24</v>
+      <c r="B5" t="str">
+        <v>26 - BHEL Ranipur</v>
       </c>
       <c r="C5">
         <v>53911</v>
@@ -876,31 +556,31 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>37082</v>
+        <v>40511</v>
       </c>
       <c r="H5">
-        <v>12253</v>
+        <v>10295</v>
       </c>
       <c r="I5">
         <v>7</v>
       </c>
       <c r="J5">
-        <v>3669</v>
+        <v>3912</v>
       </c>
       <c r="K5">
-        <v>1662</v>
+        <v>1962</v>
       </c>
       <c r="L5">
-        <v>2772</v>
+        <v>2911</v>
       </c>
       <c r="M5">
         <v>40</v>
       </c>
       <c r="N5">
-        <v>311</v>
+        <v>331</v>
       </c>
       <c r="O5">
-        <v>32428</v>
+        <v>35695</v>
       </c>
       <c r="P5">
         <v>55484</v>
@@ -915,12 +595,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6">
         <v>3</v>
       </c>
-      <c r="B6" t="s">
-        <v>25</v>
+      <c r="B6" t="str">
+        <v>27 - Jwalapur</v>
       </c>
       <c r="C6">
         <v>39773</v>
@@ -935,34 +615,34 @@
         <v>2</v>
       </c>
       <c r="G6">
-        <v>19832</v>
+        <v>21051</v>
       </c>
       <c r="H6">
-        <v>12693</v>
+        <v>13460</v>
       </c>
       <c r="I6">
-        <v>227</v>
+        <v>194</v>
       </c>
       <c r="J6">
-        <v>1632</v>
+        <v>1450</v>
       </c>
       <c r="K6">
-        <v>1043</v>
+        <v>1077</v>
       </c>
       <c r="L6">
-        <v>1382</v>
+        <v>1613</v>
       </c>
       <c r="M6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N6">
-        <v>624</v>
+        <v>652</v>
       </c>
       <c r="O6">
-        <v>16703</v>
+        <v>17848</v>
       </c>
       <c r="P6">
-        <v>43508</v>
+        <v>44466</v>
       </c>
       <c r="Q6">
         <v>17918</v>
@@ -974,12 +654,12 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7">
         <v>4</v>
       </c>
-      <c r="B7" t="s">
-        <v>26</v>
+      <c r="B7" t="str">
+        <v>28 - Bhagwanpur</v>
       </c>
       <c r="C7">
         <v>39463</v>
@@ -994,31 +674,31 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>24550</v>
+        <v>28254</v>
       </c>
       <c r="H7">
-        <v>14340</v>
+        <v>10925</v>
       </c>
       <c r="I7">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="J7">
-        <v>4273</v>
+        <v>4245</v>
       </c>
       <c r="K7">
-        <v>3028</v>
+        <v>3226</v>
       </c>
       <c r="L7">
-        <v>1030</v>
+        <v>1146</v>
       </c>
       <c r="M7">
         <v>28</v>
       </c>
       <c r="N7">
-        <v>593</v>
+        <v>702</v>
       </c>
       <c r="O7">
-        <v>19234</v>
+        <v>22862</v>
       </c>
       <c r="P7">
         <v>77581</v>
@@ -1033,12 +713,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8">
         <v>5</v>
       </c>
-      <c r="B8" t="s">
-        <v>27</v>
+      <c r="B8" t="str">
+        <v>29 - Jhabrera</v>
       </c>
       <c r="C8">
         <v>40552</v>
@@ -1047,40 +727,40 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>40550</v>
+        <v>40552</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>22375</v>
+        <v>23537</v>
       </c>
       <c r="H8">
-        <v>18176</v>
+        <v>17014</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>8356</v>
+        <v>8983</v>
       </c>
       <c r="K8">
-        <v>3883</v>
+        <v>3915</v>
       </c>
       <c r="L8">
-        <v>3229</v>
+        <v>3327</v>
       </c>
       <c r="M8">
         <v>16</v>
       </c>
       <c r="N8">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="O8">
-        <v>10406</v>
+        <v>10812</v>
       </c>
       <c r="P8">
-        <v>19800</v>
+        <v>21334</v>
       </c>
       <c r="Q8">
         <v>20902</v>
@@ -1092,12 +772,12 @@
         <v>110</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9">
         <v>6</v>
       </c>
-      <c r="B9" t="s">
-        <v>28</v>
+      <c r="B9" t="str">
+        <v>30 - Piran Kaliyar</v>
       </c>
       <c r="C9">
         <v>43273</v>
@@ -1112,31 +792,31 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>29947</v>
+        <v>31661</v>
       </c>
       <c r="H9">
-        <v>12728</v>
+        <v>11197</v>
       </c>
       <c r="I9">
-        <v>386</v>
+        <v>403</v>
       </c>
       <c r="J9">
-        <v>5069</v>
+        <v>5135</v>
       </c>
       <c r="K9">
-        <v>3736</v>
+        <v>3792</v>
       </c>
       <c r="L9">
-        <v>537</v>
+        <v>561</v>
       </c>
       <c r="M9">
         <v>7</v>
       </c>
       <c r="N9">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="O9">
-        <v>24071</v>
+        <v>25676</v>
       </c>
       <c r="P9">
         <v>50354</v>
@@ -1151,12 +831,12 @@
         <v>110</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10">
         <v>7</v>
       </c>
-      <c r="B10" t="s">
-        <v>29</v>
+      <c r="B10" t="str">
+        <v>31 - Roorkee</v>
       </c>
       <c r="C10">
         <v>36576</v>
@@ -1171,37 +851,37 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>27734</v>
+        <v>28175</v>
       </c>
       <c r="H10">
-        <v>8763</v>
+        <v>8331</v>
       </c>
       <c r="I10">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="J10">
-        <v>7463</v>
+        <v>7377</v>
       </c>
       <c r="K10">
-        <v>4912</v>
+        <v>5239</v>
       </c>
       <c r="L10">
-        <v>1411</v>
+        <v>1729</v>
       </c>
       <c r="M10">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="N10">
-        <v>240</v>
+        <v>268</v>
       </c>
       <c r="O10">
-        <v>18807</v>
+        <v>18979</v>
       </c>
       <c r="P10">
-        <v>12983</v>
+        <v>19376</v>
       </c>
       <c r="Q10">
-        <v>9518</v>
+        <v>9516</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -1210,12 +890,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11">
         <v>8</v>
       </c>
-      <c r="B11" t="s">
-        <v>30</v>
+      <c r="B11" t="str">
+        <v>32 - Khanpur</v>
       </c>
       <c r="C11">
         <v>50998</v>
@@ -1230,19 +910,19 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>32503</v>
+        <v>36214</v>
       </c>
       <c r="H11">
-        <v>15971</v>
+        <v>12960</v>
       </c>
       <c r="I11">
-        <v>608</v>
+        <v>756</v>
       </c>
       <c r="J11">
-        <v>3877</v>
+        <v>5099</v>
       </c>
       <c r="K11">
-        <v>1841</v>
+        <v>2173</v>
       </c>
       <c r="L11">
         <v>532</v>
@@ -1251,13 +931,13 @@
         <v>1</v>
       </c>
       <c r="N11">
-        <v>179</v>
+        <v>236</v>
       </c>
       <c r="O11">
-        <v>27866</v>
+        <v>30298</v>
       </c>
       <c r="P11">
-        <v>76980</v>
+        <v>77667</v>
       </c>
       <c r="Q11">
         <v>23805</v>
@@ -1269,12 +949,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12">
         <v>9</v>
       </c>
-      <c r="B12" t="s">
-        <v>31</v>
+      <c r="B12" t="str">
+        <v>33 - Manglore</v>
       </c>
       <c r="C12">
         <v>40739</v>
@@ -1289,19 +969,19 @@
         <v>36</v>
       </c>
       <c r="G12">
-        <v>21360</v>
+        <v>23582</v>
       </c>
       <c r="H12">
-        <v>18758</v>
+        <v>16681</v>
       </c>
       <c r="I12">
-        <v>161</v>
+        <v>243</v>
       </c>
       <c r="J12">
-        <v>7999</v>
+        <v>8233</v>
       </c>
       <c r="K12">
-        <v>5099</v>
+        <v>5709</v>
       </c>
       <c r="L12">
         <v>316</v>
@@ -1310,13 +990,13 @@
         <v>2</v>
       </c>
       <c r="N12">
-        <v>311</v>
+        <v>341</v>
       </c>
       <c r="O12">
-        <v>12884</v>
+        <v>14842</v>
       </c>
       <c r="P12">
-        <v>42640</v>
+        <v>49539</v>
       </c>
       <c r="Q12">
         <v>17907</v>
@@ -1328,12 +1008,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13">
         <v>10</v>
       </c>
-      <c r="B13" t="s">
-        <v>32</v>
+      <c r="B13" t="str">
+        <v>34 - Laksar</v>
       </c>
       <c r="C13">
         <v>37031</v>
@@ -1342,37 +1022,37 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>36894</v>
+        <v>36896</v>
       </c>
       <c r="F13">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G13">
-        <v>22927</v>
+        <v>24217</v>
       </c>
       <c r="H13">
-        <v>11868</v>
+        <v>11105</v>
       </c>
       <c r="I13">
         <v>12</v>
       </c>
       <c r="J13">
-        <v>3452</v>
+        <v>3541</v>
       </c>
       <c r="K13">
-        <v>1419</v>
+        <v>1854</v>
       </c>
       <c r="L13">
-        <v>102</v>
+        <v>275</v>
       </c>
       <c r="M13">
         <v>0</v>
       </c>
       <c r="N13">
-        <v>1719</v>
+        <v>1839</v>
       </c>
       <c r="O13">
-        <v>17641</v>
+        <v>18544</v>
       </c>
       <c r="P13">
         <v>54599</v>
@@ -1387,12 +1067,12 @@
         <v>109</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14">
         <v>11</v>
       </c>
-      <c r="B14" t="s">
-        <v>33</v>
+      <c r="B14" t="str">
+        <v>35 - Haridwar Rural</v>
       </c>
       <c r="C14">
         <v>48966</v>
@@ -1407,34 +1087,34 @@
         <v>2</v>
       </c>
       <c r="G14">
-        <v>27843</v>
+        <v>28778</v>
       </c>
       <c r="H14">
-        <v>12419</v>
+        <v>13680</v>
       </c>
       <c r="I14">
-        <v>674</v>
+        <v>698</v>
       </c>
       <c r="J14">
-        <v>7852</v>
+        <v>7971</v>
       </c>
       <c r="K14">
-        <v>4693</v>
+        <v>5016</v>
       </c>
       <c r="L14">
-        <v>1327</v>
+        <v>1519</v>
       </c>
       <c r="M14">
         <v>28</v>
       </c>
       <c r="N14">
-        <v>385</v>
+        <v>400</v>
       </c>
       <c r="O14">
-        <v>18683</v>
+        <v>19291</v>
       </c>
       <c r="P14">
-        <v>39802</v>
+        <v>44013</v>
       </c>
       <c r="Q14">
         <v>20044</v>
@@ -1446,12 +1126,12 @@
         <v>174</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15">
         <v>12</v>
       </c>
-      <c r="B15" t="s">
-        <v>34</v>
+      <c r="B15" t="str">
+        <v>56 - Lalkuan</v>
       </c>
       <c r="C15">
         <v>42703</v>
@@ -1466,37 +1146,37 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>38081</v>
+        <v>39104</v>
       </c>
       <c r="H15">
-        <v>4534</v>
+        <v>3540</v>
       </c>
       <c r="I15">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="J15">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15">
-        <v>8170</v>
+        <v>8446</v>
       </c>
       <c r="M15">
         <v>0</v>
       </c>
       <c r="N15">
-        <v>1281</v>
+        <v>1518</v>
       </c>
       <c r="O15">
-        <v>34420</v>
+        <v>36825</v>
       </c>
       <c r="P15">
         <v>67178</v>
       </c>
       <c r="Q15">
-        <v>5008</v>
+        <v>4952</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -1505,12 +1185,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16">
         <v>13</v>
       </c>
-      <c r="B16" t="s">
-        <v>35</v>
+      <c r="B16" t="str">
+        <v>57 - Bhimtal</v>
       </c>
       <c r="C16">
         <v>25549</v>
@@ -1519,40 +1199,40 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>25363</v>
+        <v>25477</v>
       </c>
       <c r="F16">
-        <v>186</v>
+        <v>72</v>
       </c>
       <c r="G16">
-        <v>18537</v>
+        <v>19585</v>
       </c>
       <c r="H16">
-        <v>5930</v>
+        <v>4901</v>
       </c>
       <c r="I16">
-        <v>223</v>
+        <v>245</v>
       </c>
       <c r="J16">
-        <v>112</v>
+        <v>20</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
       <c r="L16">
-        <v>10418</v>
+        <v>11060</v>
       </c>
       <c r="M16">
         <v>1</v>
       </c>
       <c r="N16">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="O16">
-        <v>11594</v>
+        <v>12966</v>
       </c>
       <c r="P16">
-        <v>67082</v>
+        <v>67240</v>
       </c>
       <c r="Q16">
         <v>5208</v>
@@ -1564,12 +1244,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17">
         <v>14</v>
       </c>
-      <c r="B17" t="s">
-        <v>36</v>
+      <c r="B17" t="str">
+        <v>58 - Nainital</v>
       </c>
       <c r="C17">
         <v>27707</v>
@@ -1578,43 +1258,43 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>27694</v>
+        <v>27707</v>
       </c>
       <c r="F17">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G17">
-        <v>25260</v>
+        <v>26577</v>
       </c>
       <c r="H17">
-        <v>2224</v>
+        <v>972</v>
       </c>
       <c r="I17">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="J17">
-        <v>336</v>
+        <v>5</v>
       </c>
       <c r="K17">
         <v>0</v>
       </c>
       <c r="L17">
-        <v>7800</v>
+        <v>8775</v>
       </c>
       <c r="M17">
         <v>2</v>
       </c>
       <c r="N17">
-        <v>235</v>
+        <v>326</v>
       </c>
       <c r="O17">
-        <v>22974</v>
+        <v>24312</v>
       </c>
       <c r="P17">
-        <v>65454</v>
+        <v>65457</v>
       </c>
       <c r="Q17">
-        <v>5444</v>
+        <v>5441</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -1623,12 +1303,12 @@
         <v>105</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="A18">
         <v>15</v>
       </c>
-      <c r="B18" t="s">
-        <v>37</v>
+      <c r="B18" t="str">
+        <v>59 - Haldwani</v>
       </c>
       <c r="C18">
         <v>47836</v>
@@ -1637,43 +1317,43 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>47757</v>
+        <v>47783</v>
       </c>
       <c r="F18">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="G18">
-        <v>43836</v>
+        <v>45652</v>
       </c>
       <c r="H18">
-        <v>3225</v>
+        <v>1750</v>
       </c>
       <c r="I18">
-        <v>695</v>
+        <v>323</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18">
         <v>0</v>
       </c>
       <c r="L18">
-        <v>6938</v>
+        <v>7267</v>
       </c>
       <c r="M18">
         <v>3</v>
       </c>
       <c r="N18">
-        <v>1208</v>
+        <v>1579</v>
       </c>
       <c r="O18">
-        <v>39212</v>
+        <v>41097</v>
       </c>
       <c r="P18">
         <v>69692</v>
       </c>
       <c r="Q18">
-        <v>6892</v>
+        <v>6867</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -1682,12 +1362,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19">
       <c r="A19">
         <v>16</v>
       </c>
-      <c r="B19" t="s">
-        <v>38</v>
+      <c r="B19" t="str">
+        <v>60 - Kaladhungi</v>
       </c>
       <c r="C19">
         <v>56490</v>
@@ -1696,37 +1376,37 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>56350</v>
+        <v>56364</v>
       </c>
       <c r="F19">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="G19">
-        <v>48528</v>
+        <v>50998</v>
       </c>
       <c r="H19">
-        <v>7473</v>
+        <v>5059</v>
       </c>
       <c r="I19">
-        <v>117</v>
+        <v>430</v>
       </c>
       <c r="J19">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="K19">
         <v>0</v>
       </c>
       <c r="L19">
-        <v>12691</v>
+        <v>13591</v>
       </c>
       <c r="M19">
         <v>1</v>
       </c>
       <c r="N19">
-        <v>381</v>
+        <v>476</v>
       </c>
       <c r="O19">
-        <v>42256</v>
+        <v>44245</v>
       </c>
       <c r="P19">
         <v>105570</v>
@@ -1741,12 +1421,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20">
       <c r="A20">
         <v>17</v>
       </c>
-      <c r="B20" t="s">
-        <v>39</v>
+      <c r="B20" t="str">
+        <v>61 - Ramnagar</v>
       </c>
       <c r="C20">
         <v>35017</v>
@@ -1755,43 +1435,43 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>34993</v>
+        <v>34994</v>
       </c>
       <c r="F20">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G20">
-        <v>32691</v>
+        <v>33496</v>
       </c>
       <c r="H20">
-        <v>2077</v>
+        <v>1509</v>
       </c>
       <c r="I20">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J20">
-        <v>78</v>
+        <v>4</v>
       </c>
       <c r="K20">
         <v>0</v>
       </c>
       <c r="L20">
-        <v>5458</v>
+        <v>5605</v>
       </c>
       <c r="M20">
         <v>5</v>
       </c>
       <c r="N20">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="O20">
-        <v>31163</v>
+        <v>32520</v>
       </c>
       <c r="P20">
-        <v>75257</v>
+        <v>75694</v>
       </c>
       <c r="Q20">
-        <v>9020</v>
+        <v>9014</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -1800,12 +1480,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21">
       <c r="A21">
         <v>18</v>
       </c>
-      <c r="B21" t="s">
-        <v>40</v>
+      <c r="B21" t="str">
+        <v>48 - Dwarahat</v>
       </c>
       <c r="C21">
         <v>16962</v>
@@ -1829,13 +1509,13 @@
         <v>0</v>
       </c>
       <c r="J21">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="K21">
         <v>0</v>
       </c>
       <c r="L21">
-        <v>3893</v>
+        <v>4018</v>
       </c>
       <c r="M21">
         <v>3</v>
@@ -1844,7 +1524,7 @@
         <v>171</v>
       </c>
       <c r="O21">
-        <v>16645</v>
+        <v>16779</v>
       </c>
       <c r="P21">
         <v>62460</v>
@@ -1859,12 +1539,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22">
       <c r="A22">
         <v>19</v>
       </c>
-      <c r="B22" t="s">
-        <v>41</v>
+      <c r="B22" t="str">
+        <v>49 - Salt</v>
       </c>
       <c r="C22">
         <v>18668</v>
@@ -1879,31 +1559,31 @@
         <v>0</v>
       </c>
       <c r="G22">
-        <v>18048</v>
+        <v>18186</v>
       </c>
       <c r="H22">
-        <v>337</v>
+        <v>300</v>
       </c>
       <c r="I22">
         <v>0</v>
       </c>
       <c r="J22">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K22">
         <v>0</v>
       </c>
       <c r="L22">
-        <v>7303</v>
+        <v>7342</v>
       </c>
       <c r="M22">
         <v>0</v>
       </c>
       <c r="N22">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="O22">
-        <v>17180</v>
+        <v>17272</v>
       </c>
       <c r="P22">
         <v>64099</v>
@@ -1918,12 +1598,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23">
       <c r="A23">
         <v>20</v>
       </c>
-      <c r="B23" t="s">
-        <v>42</v>
+      <c r="B23" t="str">
+        <v>50 - Ranikhet</v>
       </c>
       <c r="C23">
         <v>12020</v>
@@ -1938,37 +1618,37 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>12005</v>
+        <v>12018</v>
       </c>
       <c r="H23">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I23">
         <v>0</v>
       </c>
       <c r="J23">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="K23">
         <v>0</v>
       </c>
       <c r="L23">
-        <v>2079</v>
+        <v>2103</v>
       </c>
       <c r="M23">
         <v>0</v>
       </c>
       <c r="N23">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="O23">
-        <v>11868</v>
+        <v>11902</v>
       </c>
       <c r="P23">
         <v>57093</v>
       </c>
       <c r="Q23">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -1977,12 +1657,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24">
       <c r="A24">
         <v>21</v>
       </c>
-      <c r="B24" t="s">
-        <v>43</v>
+      <c r="B24" t="str">
+        <v>51 - Someshwar</v>
       </c>
       <c r="C24">
         <v>14056</v>
@@ -1997,37 +1677,37 @@
         <v>0</v>
       </c>
       <c r="G24">
-        <v>13745</v>
+        <v>13820</v>
       </c>
       <c r="H24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I24">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J24">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="K24">
         <v>0</v>
       </c>
       <c r="L24">
-        <v>3398</v>
+        <v>3425</v>
       </c>
       <c r="M24">
         <v>0</v>
       </c>
       <c r="N24">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="O24">
-        <v>13499</v>
+        <v>13534</v>
       </c>
       <c r="P24">
         <v>65629</v>
       </c>
       <c r="Q24">
-        <v>3499</v>
+        <v>3497</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -2036,12 +1716,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25">
       <c r="A25">
         <v>22</v>
       </c>
-      <c r="B25" t="s">
-        <v>44</v>
+      <c r="B25" t="str">
+        <v>52 - Almora</v>
       </c>
       <c r="C25">
         <v>19266</v>
@@ -2056,37 +1736,37 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>18765</v>
+        <v>18928</v>
       </c>
       <c r="H25">
-        <v>146</v>
+        <v>98</v>
       </c>
       <c r="I25">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="J25">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="K25">
         <v>0</v>
       </c>
       <c r="L25">
-        <v>4439</v>
+        <v>4569</v>
       </c>
       <c r="M25">
         <v>0</v>
       </c>
       <c r="N25">
-        <v>215</v>
+        <v>244</v>
       </c>
       <c r="O25">
-        <v>18199</v>
+        <v>18243</v>
       </c>
       <c r="P25">
         <v>57533</v>
       </c>
       <c r="Q25">
-        <v>3240</v>
+        <v>3236</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -2095,12 +1775,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26">
       <c r="A26">
         <v>23</v>
       </c>
-      <c r="B26" t="s">
-        <v>45</v>
+      <c r="B26" t="str">
+        <v>53 - Jageshwar</v>
       </c>
       <c r="C26">
         <v>17557</v>
@@ -2115,31 +1795,31 @@
         <v>0</v>
       </c>
       <c r="G26">
-        <v>16646</v>
+        <v>16873</v>
       </c>
       <c r="H26">
-        <v>786</v>
+        <v>633</v>
       </c>
       <c r="I26">
         <v>0</v>
       </c>
       <c r="J26">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K26">
         <v>0</v>
       </c>
       <c r="L26">
-        <v>3294</v>
+        <v>3310</v>
       </c>
       <c r="M26">
         <v>3</v>
       </c>
       <c r="N26">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="O26">
-        <v>15335</v>
+        <v>15821</v>
       </c>
       <c r="P26">
         <v>66594</v>
@@ -2154,12 +1834,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27">
       <c r="A27">
         <v>24</v>
       </c>
-      <c r="B27" t="s">
-        <v>46</v>
+      <c r="B27" t="str">
+        <v>62 - Jaspur</v>
       </c>
       <c r="C27">
         <v>44276</v>
@@ -2174,22 +1854,22 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>24261</v>
+        <v>27129</v>
       </c>
       <c r="H27">
-        <v>16619</v>
+        <v>14854</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27">
-        <v>262</v>
+        <v>192</v>
       </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="L27">
-        <v>4626</v>
+        <v>5221</v>
       </c>
       <c r="M27">
         <v>0</v>
@@ -2198,10 +1878,10 @@
         <v>56</v>
       </c>
       <c r="O27">
-        <v>22803</v>
+        <v>25587</v>
       </c>
       <c r="P27">
-        <v>40115</v>
+        <v>40558</v>
       </c>
       <c r="Q27">
         <v>12669</v>
@@ -2213,12 +1893,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28">
       <c r="A28">
         <v>25</v>
       </c>
-      <c r="B28" t="s">
-        <v>47</v>
+      <c r="B28" t="str">
+        <v>63 - Kashipur</v>
       </c>
       <c r="C28">
         <v>54349</v>
@@ -2227,43 +1907,43 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>54128</v>
+        <v>54240</v>
       </c>
       <c r="F28">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="G28">
-        <v>23763</v>
+        <v>25443</v>
       </c>
       <c r="H28">
-        <v>23487</v>
+        <v>24526</v>
       </c>
       <c r="I28">
         <v>37</v>
       </c>
       <c r="J28">
-        <v>113</v>
+        <v>286</v>
       </c>
       <c r="K28">
         <v>0</v>
       </c>
       <c r="L28">
-        <v>3425</v>
+        <v>3549</v>
       </c>
       <c r="M28">
         <v>11</v>
       </c>
       <c r="N28">
-        <v>280</v>
+        <v>349</v>
       </c>
       <c r="O28">
-        <v>20432</v>
+        <v>21999</v>
       </c>
       <c r="P28">
-        <v>80640</v>
+        <v>80639</v>
       </c>
       <c r="Q28">
-        <v>14118</v>
+        <v>14117</v>
       </c>
       <c r="R28">
         <v>0</v>
@@ -2272,12 +1952,12 @@
         <v>134</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29">
       <c r="A29">
         <v>26</v>
       </c>
-      <c r="B29" t="s">
-        <v>48</v>
+      <c r="B29" t="str">
+        <v>64 - Bajpur</v>
       </c>
       <c r="C29">
         <v>47111</v>
@@ -2292,31 +1972,31 @@
         <v>0</v>
       </c>
       <c r="G29">
-        <v>32561</v>
+        <v>35478</v>
       </c>
       <c r="H29">
-        <v>12843</v>
+        <v>10820</v>
       </c>
       <c r="I29">
-        <v>89</v>
+        <v>353</v>
       </c>
       <c r="J29">
-        <v>96</v>
+        <v>406</v>
       </c>
       <c r="K29">
         <v>0</v>
       </c>
       <c r="L29">
-        <v>5160</v>
+        <v>5361</v>
       </c>
       <c r="M29">
         <v>2</v>
       </c>
       <c r="N29">
-        <v>363</v>
+        <v>441</v>
       </c>
       <c r="O29">
-        <v>28868</v>
+        <v>31262</v>
       </c>
       <c r="P29">
         <v>83837</v>
@@ -2331,12 +2011,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30">
       <c r="A30">
         <v>27</v>
       </c>
-      <c r="B30" t="s">
-        <v>49</v>
+      <c r="B30" t="str">
+        <v>65 - Gadarpur</v>
       </c>
       <c r="C30">
         <v>52653</v>
@@ -2351,22 +2031,22 @@
         <v>58</v>
       </c>
       <c r="G30">
-        <v>25545</v>
+        <v>28012</v>
       </c>
       <c r="H30">
-        <v>23379</v>
+        <v>20183</v>
       </c>
       <c r="I30">
-        <v>515</v>
+        <v>1239</v>
       </c>
       <c r="J30">
-        <v>207</v>
+        <v>508</v>
       </c>
       <c r="K30">
         <v>0</v>
       </c>
       <c r="L30">
-        <v>2495</v>
+        <v>2869</v>
       </c>
       <c r="M30">
         <v>0</v>
@@ -2375,7 +2055,7 @@
         <v>140</v>
       </c>
       <c r="O30">
-        <v>22339</v>
+        <v>25710</v>
       </c>
       <c r="P30">
         <v>86935</v>
@@ -2390,12 +2070,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31">
       <c r="A31">
         <v>28</v>
       </c>
-      <c r="B31" t="s">
-        <v>50</v>
+      <c r="B31" t="str">
+        <v>66 - Rudrapur</v>
       </c>
       <c r="C31">
         <v>91162</v>
@@ -2410,31 +2090,31 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>85423</v>
+        <v>86571</v>
       </c>
       <c r="H31">
-        <v>894</v>
+        <v>1324</v>
       </c>
       <c r="I31">
         <v>77</v>
       </c>
       <c r="J31">
-        <v>290</v>
+        <v>441</v>
       </c>
       <c r="K31">
         <v>0</v>
       </c>
       <c r="L31">
-        <v>39631</v>
+        <v>40384</v>
       </c>
       <c r="M31">
         <v>24</v>
       </c>
       <c r="N31">
-        <v>1551</v>
+        <v>1609</v>
       </c>
       <c r="O31">
-        <v>79764</v>
+        <v>80828</v>
       </c>
       <c r="P31">
         <v>81642</v>
@@ -2449,12 +2129,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32">
       <c r="A32">
         <v>29</v>
       </c>
-      <c r="B32" t="s">
-        <v>51</v>
+      <c r="B32" t="str">
+        <v>67 - Kichha</v>
       </c>
       <c r="C32">
         <v>46728</v>
@@ -2463,40 +2143,40 @@
         <v>0</v>
       </c>
       <c r="E32">
-        <v>46700</v>
+        <v>46705</v>
       </c>
       <c r="F32">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G32">
-        <v>22126</v>
+        <v>24494</v>
       </c>
       <c r="H32">
-        <v>18446</v>
+        <v>17769</v>
       </c>
       <c r="I32">
-        <v>760</v>
+        <v>680</v>
       </c>
       <c r="J32">
-        <v>288</v>
+        <v>551</v>
       </c>
       <c r="K32">
         <v>0</v>
       </c>
       <c r="L32">
-        <v>4805</v>
+        <v>5185</v>
       </c>
       <c r="M32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N32">
-        <v>20</v>
+        <v>216</v>
       </c>
       <c r="O32">
-        <v>18795</v>
+        <v>20642</v>
       </c>
       <c r="P32">
-        <v>11022</v>
+        <v>16303</v>
       </c>
       <c r="Q32">
         <v>11379</v>
@@ -2508,12 +2188,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33">
       <c r="A33">
         <v>30</v>
       </c>
-      <c r="B33" t="s">
-        <v>52</v>
+      <c r="B33" t="str">
+        <v>68 - Sitarganj</v>
       </c>
       <c r="C33">
         <v>40230</v>
@@ -2522,28 +2202,28 @@
         <v>0</v>
       </c>
       <c r="E33">
-        <v>40120</v>
+        <v>40149</v>
       </c>
       <c r="F33">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="G33">
-        <v>18499</v>
+        <v>21884</v>
       </c>
       <c r="H33">
-        <v>16675</v>
+        <v>14359</v>
       </c>
       <c r="I33">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="J33">
-        <v>144</v>
+        <v>323</v>
       </c>
       <c r="K33">
         <v>0</v>
       </c>
       <c r="L33">
-        <v>2613</v>
+        <v>2748</v>
       </c>
       <c r="M33">
         <v>5</v>
@@ -2552,10 +2232,10 @@
         <v>7</v>
       </c>
       <c r="O33">
-        <v>17161</v>
+        <v>20551</v>
       </c>
       <c r="P33">
-        <v>63531</v>
+        <v>69510</v>
       </c>
       <c r="Q33">
         <v>6678</v>
@@ -2567,12 +2247,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="34" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34">
       <c r="A34">
         <v>31</v>
       </c>
-      <c r="B34" t="s">
-        <v>53</v>
+      <c r="B34" t="str">
+        <v>69 - Nanakmatta</v>
       </c>
       <c r="C34">
         <v>36542</v>
@@ -2581,28 +2261,28 @@
         <v>0</v>
       </c>
       <c r="E34">
-        <v>36317</v>
+        <v>36368</v>
       </c>
       <c r="F34">
-        <v>225</v>
+        <v>174</v>
       </c>
       <c r="G34">
-        <v>17429</v>
+        <v>20218</v>
       </c>
       <c r="H34">
-        <v>18157</v>
+        <v>15887</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
       <c r="J34">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="K34">
         <v>0</v>
       </c>
       <c r="L34">
-        <v>6856</v>
+        <v>7362</v>
       </c>
       <c r="M34">
         <v>0</v>
@@ -2611,7 +2291,7 @@
         <v>0</v>
       </c>
       <c r="O34">
-        <v>15225</v>
+        <v>17683</v>
       </c>
       <c r="P34">
         <v>74626</v>
@@ -2626,12 +2306,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35">
       <c r="A35">
         <v>32</v>
       </c>
-      <c r="B35" t="s">
-        <v>54</v>
+      <c r="B35" t="str">
+        <v>70 - Khatima</v>
       </c>
       <c r="C35">
         <v>33564</v>
@@ -2640,40 +2320,40 @@
         <v>0</v>
       </c>
       <c r="E35">
-        <v>33192</v>
+        <v>33304</v>
       </c>
       <c r="F35">
-        <v>372</v>
+        <v>260</v>
       </c>
       <c r="G35">
-        <v>20077</v>
+        <v>21377</v>
       </c>
       <c r="H35">
-        <v>11116</v>
+        <v>10590</v>
       </c>
       <c r="I35">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="J35">
-        <v>65</v>
+        <v>293</v>
       </c>
       <c r="K35">
         <v>0</v>
       </c>
       <c r="L35">
-        <v>1982</v>
+        <v>2138</v>
       </c>
       <c r="M35">
         <v>0</v>
       </c>
       <c r="N35">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="O35">
-        <v>17699</v>
+        <v>18566</v>
       </c>
       <c r="P35">
-        <v>62346</v>
+        <v>68809</v>
       </c>
       <c r="Q35">
         <v>8879</v>
@@ -2685,12 +2365,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36">
       <c r="A36">
         <v>33</v>
       </c>
-      <c r="B36" t="s">
-        <v>55</v>
+      <c r="B36" t="str">
+        <v>42 - Dharchula</v>
       </c>
       <c r="C36">
         <v>20905</v>
@@ -2744,12 +2424,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37">
       <c r="A37">
         <v>34</v>
       </c>
-      <c r="B37" t="s">
-        <v>56</v>
+      <c r="B37" t="str">
+        <v>43 - Didihat</v>
       </c>
       <c r="C37">
         <v>17692</v>
@@ -2773,22 +2453,22 @@
         <v>0</v>
       </c>
       <c r="J37">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K37">
         <v>0</v>
       </c>
       <c r="L37">
-        <v>2277</v>
+        <v>2302</v>
       </c>
       <c r="M37">
         <v>0</v>
       </c>
       <c r="N37">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="O37">
-        <v>17120</v>
+        <v>17144</v>
       </c>
       <c r="P37">
         <v>57832</v>
@@ -2803,12 +2483,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38">
       <c r="A38">
         <v>35</v>
       </c>
-      <c r="B38" t="s">
-        <v>57</v>
+      <c r="B38" t="str">
+        <v>44 - Pithoragarh</v>
       </c>
       <c r="C38">
         <v>29110</v>
@@ -2823,13 +2503,13 @@
         <v>0</v>
       </c>
       <c r="G38">
-        <v>28892</v>
+        <v>29110</v>
       </c>
       <c r="H38">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="I38">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J38">
         <v>28</v>
@@ -2838,19 +2518,19 @@
         <v>0</v>
       </c>
       <c r="L38">
-        <v>4845</v>
+        <v>4935</v>
       </c>
       <c r="M38">
         <v>2</v>
       </c>
       <c r="N38">
-        <v>474</v>
+        <v>493</v>
       </c>
       <c r="O38">
-        <v>24561</v>
+        <v>24565</v>
       </c>
       <c r="P38">
-        <v>61242</v>
+        <v>61880</v>
       </c>
       <c r="Q38">
         <v>5160</v>
@@ -2862,12 +2542,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39">
       <c r="A39">
         <v>36</v>
       </c>
-      <c r="B39" t="s">
-        <v>58</v>
+      <c r="B39" t="str">
+        <v>45 - Gangolihat</v>
       </c>
       <c r="C39">
         <v>21367</v>
@@ -2897,16 +2577,16 @@
         <v>0</v>
       </c>
       <c r="L39">
-        <v>4509</v>
+        <v>4518</v>
       </c>
       <c r="M39">
         <v>1</v>
       </c>
       <c r="N39">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="O39">
-        <v>19483</v>
+        <v>20111</v>
       </c>
       <c r="P39">
         <v>71133</v>
@@ -2921,12 +2601,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40">
       <c r="A40">
         <v>37</v>
       </c>
-      <c r="B40" t="s">
-        <v>59</v>
+      <c r="B40" t="str">
+        <v>46 - Kapkot</v>
       </c>
       <c r="C40">
         <v>18905</v>
@@ -2941,31 +2621,31 @@
         <v>0</v>
       </c>
       <c r="G40">
-        <v>14851</v>
+        <v>15546</v>
       </c>
       <c r="H40">
-        <v>355</v>
+        <v>254</v>
       </c>
       <c r="I40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J40">
-        <v>549</v>
+        <v>615</v>
       </c>
       <c r="K40">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="L40">
-        <v>666</v>
+        <v>786</v>
       </c>
       <c r="M40">
         <v>0</v>
       </c>
       <c r="N40">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O40">
-        <v>13696</v>
+        <v>14366</v>
       </c>
       <c r="P40">
         <v>73242</v>
@@ -2980,12 +2660,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41">
       <c r="A41">
         <v>38</v>
       </c>
-      <c r="B41" t="s">
-        <v>60</v>
+      <c r="B41" t="str">
+        <v>47 - Bageshwar</v>
       </c>
       <c r="C41">
         <v>23521</v>
@@ -3000,31 +2680,31 @@
         <v>0</v>
       </c>
       <c r="G41">
-        <v>20575</v>
+        <v>21111</v>
       </c>
       <c r="H41">
-        <v>534</v>
+        <v>709</v>
       </c>
       <c r="I41">
         <v>0</v>
       </c>
       <c r="J41">
-        <v>469</v>
+        <v>255</v>
       </c>
       <c r="K41">
         <v>0</v>
       </c>
       <c r="L41">
-        <v>557</v>
+        <v>652</v>
       </c>
       <c r="M41">
         <v>0</v>
       </c>
       <c r="N41">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="O41">
-        <v>19410</v>
+        <v>19940</v>
       </c>
       <c r="P41">
         <v>85249</v>
@@ -3039,12 +2719,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="42" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42">
       <c r="A42">
         <v>39</v>
       </c>
-      <c r="B42" t="s">
-        <v>61</v>
+      <c r="B42" t="str">
+        <v>54 - Lohaghat</v>
       </c>
       <c r="C42">
         <v>27565</v>
@@ -3068,13 +2748,13 @@
         <v>0</v>
       </c>
       <c r="J42">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K42">
         <v>0</v>
       </c>
       <c r="L42">
-        <v>6178</v>
+        <v>6188</v>
       </c>
       <c r="M42">
         <v>0</v>
@@ -3086,7 +2766,7 @@
         <v>25756</v>
       </c>
       <c r="P42">
-        <v>46029</v>
+        <v>58915</v>
       </c>
       <c r="Q42">
         <v>4713</v>
@@ -3098,12 +2778,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43">
       <c r="A43">
         <v>40</v>
       </c>
-      <c r="B43" t="s">
-        <v>62</v>
+      <c r="B43" t="str">
+        <v>55 - Champawat</v>
       </c>
       <c r="C43">
         <v>29700</v>
@@ -3118,22 +2798,22 @@
         <v>0</v>
       </c>
       <c r="G43">
-        <v>29699</v>
+        <v>29700</v>
       </c>
       <c r="H43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43">
         <v>0</v>
       </c>
       <c r="J43">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K43">
         <v>0</v>
       </c>
       <c r="L43">
-        <v>6713</v>
+        <v>6720</v>
       </c>
       <c r="M43">
         <v>1</v>
@@ -3142,10 +2822,10 @@
         <v>900</v>
       </c>
       <c r="O43">
-        <v>24092</v>
+        <v>24728</v>
       </c>
       <c r="P43">
-        <v>42801</v>
+        <v>45739</v>
       </c>
       <c r="Q43">
         <v>5271</v>
@@ -3157,12 +2837,12 @@
         <v>121</v>
       </c>
     </row>
-    <row r="44" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44">
       <c r="A44">
         <v>41</v>
       </c>
-      <c r="B44" t="s">
-        <v>63</v>
+      <c r="B44" t="str">
+        <v>4 - Badrinath</v>
       </c>
       <c r="C44">
         <v>21900</v>
@@ -3177,31 +2857,31 @@
         <v>0</v>
       </c>
       <c r="G44">
-        <v>20193</v>
+        <v>20510</v>
       </c>
       <c r="H44">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="I44">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J44">
-        <v>1035</v>
+        <v>398</v>
       </c>
       <c r="K44">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L44">
-        <v>4865</v>
+        <v>5585</v>
       </c>
       <c r="M44">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N44">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="O44">
-        <v>15730</v>
+        <v>16069</v>
       </c>
       <c r="P44">
         <v>68393</v>
@@ -3216,12 +2896,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45">
       <c r="A45">
         <v>42</v>
       </c>
-      <c r="B45" t="s">
-        <v>64</v>
+      <c r="B45" t="str">
+        <v>5 - Tharali</v>
       </c>
       <c r="C45">
         <v>19935</v>
@@ -3236,31 +2916,31 @@
         <v>0</v>
       </c>
       <c r="G45">
-        <v>15081</v>
+        <v>15702</v>
       </c>
       <c r="H45">
-        <v>2508</v>
+        <v>2390</v>
       </c>
       <c r="I45">
         <v>13</v>
       </c>
       <c r="J45">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="K45">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L45">
-        <v>1494</v>
+        <v>1561</v>
       </c>
       <c r="M45">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N45">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="O45">
-        <v>13500</v>
+        <v>14031</v>
       </c>
       <c r="P45">
         <v>76002</v>
@@ -3275,12 +2955,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="46" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46">
       <c r="A46">
         <v>43</v>
       </c>
-      <c r="B46" t="s">
-        <v>65</v>
+      <c r="B46" t="str">
+        <v>6 - Karanprayag</v>
       </c>
       <c r="C46">
         <v>21512</v>
@@ -3295,16 +2975,16 @@
         <v>0</v>
       </c>
       <c r="G46">
-        <v>20173</v>
+        <v>20502</v>
       </c>
       <c r="H46">
-        <v>1339</v>
+        <v>1010</v>
       </c>
       <c r="I46">
         <v>0</v>
       </c>
       <c r="J46">
-        <v>83</v>
+        <v>280</v>
       </c>
       <c r="K46">
         <v>0</v>
@@ -3316,10 +2996,10 @@
         <v>1</v>
       </c>
       <c r="N46">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="O46">
-        <v>15906</v>
+        <v>16147</v>
       </c>
       <c r="P46">
         <v>64160</v>
@@ -3334,12 +3014,12 @@
         <v>152</v>
       </c>
     </row>
-    <row r="47" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47">
       <c r="A47">
         <v>44</v>
       </c>
-      <c r="B47" t="s">
-        <v>66</v>
+      <c r="B47" t="str">
+        <v>1 - Purola</v>
       </c>
       <c r="C47">
         <v>22426</v>
@@ -3354,16 +3034,16 @@
         <v>0</v>
       </c>
       <c r="G47">
-        <v>19667</v>
+        <v>20115</v>
       </c>
       <c r="H47">
-        <v>1862</v>
+        <v>1459</v>
       </c>
       <c r="I47">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="J47">
-        <v>249</v>
+        <v>330</v>
       </c>
       <c r="K47">
         <v>0</v>
@@ -3375,10 +3055,10 @@
         <v>1</v>
       </c>
       <c r="N47">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="O47">
-        <v>18239</v>
+        <v>18797</v>
       </c>
       <c r="P47">
         <v>49875</v>
@@ -3393,12 +3073,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48">
       <c r="A48">
         <v>45</v>
       </c>
-      <c r="B48" t="s">
-        <v>67</v>
+      <c r="B48" t="str">
+        <v>2 - Yamunotri</v>
       </c>
       <c r="C48">
         <v>19641</v>
@@ -3413,31 +3093,31 @@
         <v>47</v>
       </c>
       <c r="G48">
-        <v>19515</v>
+        <v>19520</v>
       </c>
       <c r="H48">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="I48">
         <v>5</v>
       </c>
       <c r="J48">
-        <v>363</v>
+        <v>74</v>
       </c>
       <c r="K48">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L48">
-        <v>3396</v>
+        <v>3685</v>
       </c>
       <c r="M48">
         <v>4</v>
       </c>
       <c r="N48">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="O48">
-        <v>18717</v>
+        <v>19166</v>
       </c>
       <c r="P48">
         <v>54142</v>
@@ -3452,12 +3132,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49">
       <c r="A49">
         <v>46</v>
       </c>
-      <c r="B49" t="s">
-        <v>68</v>
+      <c r="B49" t="str">
+        <v>3 - Gangotri</v>
       </c>
       <c r="C49">
         <v>21651</v>
@@ -3466,37 +3146,37 @@
         <v>0</v>
       </c>
       <c r="E49">
-        <v>21628</v>
+        <v>21631</v>
       </c>
       <c r="F49">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G49">
-        <v>17943</v>
+        <v>18414</v>
       </c>
       <c r="H49">
-        <v>959</v>
+        <v>1531</v>
       </c>
       <c r="I49">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="J49">
-        <v>470</v>
+        <v>255</v>
       </c>
       <c r="K49">
         <v>0</v>
       </c>
       <c r="L49">
-        <v>2471</v>
+        <v>2823</v>
       </c>
       <c r="M49">
         <v>0</v>
       </c>
       <c r="N49">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="O49">
-        <v>16011</v>
+        <v>16730</v>
       </c>
       <c r="P49">
         <v>49949</v>
@@ -3511,12 +3191,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50">
       <c r="A50">
         <v>47</v>
       </c>
-      <c r="B50" t="s">
-        <v>69</v>
+      <c r="B50" t="str">
+        <v>7 - Kedarnath</v>
       </c>
       <c r="C50">
         <v>21936</v>
@@ -3531,22 +3211,22 @@
         <v>0</v>
       </c>
       <c r="G50">
-        <v>20306</v>
+        <v>20576</v>
       </c>
       <c r="H50">
-        <v>1225</v>
+        <v>1136</v>
       </c>
       <c r="I50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="K50">
         <v>0</v>
       </c>
       <c r="L50">
-        <v>3269</v>
+        <v>3371</v>
       </c>
       <c r="M50">
         <v>5</v>
@@ -3555,7 +3235,7 @@
         <v>11</v>
       </c>
       <c r="O50">
-        <v>18998</v>
+        <v>19876</v>
       </c>
       <c r="P50">
         <v>63298</v>
@@ -3570,12 +3250,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51">
       <c r="A51">
         <v>48</v>
       </c>
-      <c r="B51" t="s">
-        <v>70</v>
+      <c r="B51" t="str">
+        <v>8 - Rudraprayag</v>
       </c>
       <c r="C51">
         <v>23798</v>
@@ -3590,31 +3270,31 @@
         <v>0</v>
       </c>
       <c r="G51">
-        <v>21674</v>
+        <v>22217</v>
       </c>
       <c r="H51">
-        <v>826</v>
+        <v>875</v>
       </c>
       <c r="I51">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J51">
-        <v>12</v>
+        <v>133</v>
       </c>
       <c r="K51">
         <v>0</v>
       </c>
       <c r="L51">
-        <v>4118</v>
+        <v>4191</v>
       </c>
       <c r="M51">
         <v>11</v>
       </c>
       <c r="N51">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="O51">
-        <v>18706</v>
+        <v>19190</v>
       </c>
       <c r="P51">
         <v>71754</v>
@@ -3629,12 +3309,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="52" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52">
       <c r="A52">
         <v>49</v>
       </c>
-      <c r="B52" t="s">
-        <v>71</v>
+      <c r="B52" t="str">
+        <v>9 - Ghansali</v>
       </c>
       <c r="C52">
         <v>21094</v>
@@ -3649,31 +3329,31 @@
         <v>0</v>
       </c>
       <c r="G52">
-        <v>20659</v>
+        <v>20836</v>
       </c>
       <c r="H52">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I52">
         <v>0</v>
       </c>
       <c r="J52">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="K52">
         <v>1</v>
       </c>
       <c r="L52">
-        <v>2309</v>
+        <v>2350</v>
       </c>
       <c r="M52">
         <v>1</v>
       </c>
       <c r="N52">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="O52">
-        <v>20075</v>
+        <v>20270</v>
       </c>
       <c r="P52">
         <v>63986</v>
@@ -3688,12 +3368,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53">
       <c r="A53">
         <v>50</v>
       </c>
-      <c r="B53" t="s">
-        <v>72</v>
+      <c r="B53" t="str">
+        <v>10 - Devprayag</v>
       </c>
       <c r="C53">
         <v>19131</v>
@@ -3717,19 +3397,19 @@
         <v>0</v>
       </c>
       <c r="J53">
-        <v>660</v>
+        <v>511</v>
       </c>
       <c r="K53">
-        <v>148</v>
+        <v>175</v>
       </c>
       <c r="L53">
-        <v>2733</v>
+        <v>2864</v>
       </c>
       <c r="M53">
         <v>1</v>
       </c>
       <c r="N53">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O53">
         <v>18140</v>
@@ -3747,12 +3427,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54">
       <c r="A54">
         <v>51</v>
       </c>
-      <c r="B54" t="s">
-        <v>73</v>
+      <c r="B54" t="str">
+        <v>11 - Narendranagar</v>
       </c>
       <c r="C54">
         <v>20758</v>
@@ -3767,31 +3447,31 @@
         <v>0</v>
       </c>
       <c r="G54">
-        <v>20192</v>
+        <v>20328</v>
       </c>
       <c r="H54">
-        <v>416</v>
+        <v>349</v>
       </c>
       <c r="I54">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="J54">
-        <v>668</v>
+        <v>708</v>
       </c>
       <c r="K54">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="L54">
-        <v>1533</v>
+        <v>1624</v>
       </c>
       <c r="M54">
         <v>3</v>
       </c>
       <c r="N54">
-        <v>221</v>
+        <v>250</v>
       </c>
       <c r="O54">
-        <v>17635</v>
+        <v>17670</v>
       </c>
       <c r="P54">
         <v>58440</v>
@@ -3806,12 +3486,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55">
       <c r="A55">
         <v>52</v>
       </c>
-      <c r="B55" t="s">
-        <v>74</v>
+      <c r="B55" t="str">
+        <v>12 - Pratapnagar</v>
       </c>
       <c r="C55">
         <v>16022</v>
@@ -3826,31 +3506,31 @@
         <v>0</v>
       </c>
       <c r="G55">
-        <v>15930</v>
+        <v>15963</v>
       </c>
       <c r="H55">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I55">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J55">
-        <v>580</v>
+        <v>524</v>
       </c>
       <c r="K55">
-        <v>2</v>
+        <v>108</v>
       </c>
       <c r="L55">
-        <v>1413</v>
+        <v>1482</v>
       </c>
       <c r="M55">
         <v>0</v>
       </c>
       <c r="N55">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O55">
-        <v>15156</v>
+        <v>15232</v>
       </c>
       <c r="P55">
         <v>58215</v>
@@ -3865,12 +3545,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56">
       <c r="A56">
         <v>53</v>
       </c>
-      <c r="B56" t="s">
-        <v>75</v>
+      <c r="B56" t="str">
+        <v>13 - Tehri</v>
       </c>
       <c r="C56">
         <v>19256</v>
@@ -3885,31 +3565,31 @@
         <v>0</v>
       </c>
       <c r="G56">
-        <v>18505</v>
+        <v>18684</v>
       </c>
       <c r="H56">
-        <v>237</v>
+        <v>320</v>
       </c>
       <c r="I56">
         <v>0</v>
       </c>
       <c r="J56">
-        <v>1368</v>
+        <v>1237</v>
       </c>
       <c r="K56">
-        <v>411</v>
+        <v>538</v>
       </c>
       <c r="L56">
-        <v>2268</v>
+        <v>2442</v>
       </c>
       <c r="M56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N56">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="O56">
-        <v>14206</v>
+        <v>14322</v>
       </c>
       <c r="P56">
         <v>46365</v>
@@ -3924,12 +3604,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="57" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57">
       <c r="A57">
         <v>54</v>
       </c>
-      <c r="B57" t="s">
-        <v>76</v>
+      <c r="B57" t="str">
+        <v>14 - Dhanolti</v>
       </c>
       <c r="C57">
         <v>21240</v>
@@ -3944,31 +3624,31 @@
         <v>0</v>
       </c>
       <c r="G57">
-        <v>21105</v>
+        <v>21107</v>
       </c>
       <c r="H57">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I57">
         <v>0</v>
       </c>
       <c r="J57">
-        <v>216</v>
+        <v>24</v>
       </c>
       <c r="K57">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L57">
-        <v>1666</v>
+        <v>1746</v>
       </c>
       <c r="M57">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N57">
         <v>35</v>
       </c>
       <c r="O57">
-        <v>20842</v>
+        <v>20852</v>
       </c>
       <c r="P57">
         <v>61556</v>
@@ -3983,12 +3663,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58">
       <c r="A58">
         <v>55</v>
       </c>
-      <c r="B58" t="s">
-        <v>77</v>
+      <c r="B58" t="str">
+        <v>36 - Yamkeshwar</v>
       </c>
       <c r="C58">
         <v>22819</v>
@@ -4003,31 +3683,31 @@
         <v>0</v>
       </c>
       <c r="G58">
-        <v>21092</v>
+        <v>21348</v>
       </c>
       <c r="H58">
-        <v>1504</v>
+        <v>1126</v>
       </c>
       <c r="I58">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J58">
-        <v>1973</v>
+        <v>1555</v>
       </c>
       <c r="K58">
-        <v>483</v>
+        <v>378</v>
       </c>
       <c r="L58">
-        <v>4829</v>
+        <v>5418</v>
       </c>
       <c r="M58">
         <v>3</v>
       </c>
       <c r="N58">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O58">
-        <v>15152</v>
+        <v>15235</v>
       </c>
       <c r="P58">
         <v>57577</v>
@@ -4042,12 +3722,12 @@
         <v>64</v>
       </c>
     </row>
-    <row r="59" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59">
       <c r="A59">
         <v>56</v>
       </c>
-      <c r="B59" t="s">
-        <v>78</v>
+      <c r="B59" t="str">
+        <v>37 - Pauri</v>
       </c>
       <c r="C59">
         <v>18776</v>
@@ -4062,13 +3742,13 @@
         <v>0</v>
       </c>
       <c r="G59">
-        <v>18771</v>
+        <v>18775</v>
       </c>
       <c r="H59">
         <v>0</v>
       </c>
       <c r="I59">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J59">
         <v>0</v>
@@ -4077,13 +3757,13 @@
         <v>0</v>
       </c>
       <c r="L59">
-        <v>2488</v>
+        <v>2489</v>
       </c>
       <c r="M59">
         <v>2</v>
       </c>
       <c r="N59">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="O59">
         <v>15993</v>
@@ -4101,12 +3781,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="60" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60">
       <c r="A60">
         <v>57</v>
       </c>
-      <c r="B60" t="s">
-        <v>79</v>
+      <c r="B60" t="str">
+        <v>38 - Srinagar</v>
       </c>
       <c r="C60">
         <v>23749</v>
@@ -4121,31 +3801,31 @@
         <v>0</v>
       </c>
       <c r="G60">
-        <v>22579</v>
+        <v>22954</v>
       </c>
       <c r="H60">
-        <v>631</v>
+        <v>384</v>
       </c>
       <c r="I60">
         <v>0</v>
       </c>
       <c r="J60">
-        <v>914</v>
+        <v>543</v>
       </c>
       <c r="K60">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="L60">
-        <v>4531</v>
+        <v>4903</v>
       </c>
       <c r="M60">
         <v>0</v>
       </c>
       <c r="N60">
-        <v>199</v>
+        <v>223</v>
       </c>
       <c r="O60">
-        <v>20865</v>
+        <v>21183</v>
       </c>
       <c r="P60">
         <v>70140</v>
@@ -4160,12 +3840,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="61" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61">
       <c r="A61">
         <v>58</v>
       </c>
-      <c r="B61" t="s">
-        <v>80</v>
+      <c r="B61" t="str">
+        <v>39 - Chaubattakhal</v>
       </c>
       <c r="C61">
         <v>22069</v>
@@ -4189,10 +3869,10 @@
         <v>0</v>
       </c>
       <c r="J61">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="K61">
-        <v>171</v>
+        <v>265</v>
       </c>
       <c r="L61">
         <v>9558</v>
@@ -4219,12 +3899,12 @@
         <v>268</v>
       </c>
     </row>
-    <row r="62" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62">
       <c r="A62">
         <v>59</v>
       </c>
-      <c r="B62" t="s">
-        <v>81</v>
+      <c r="B62" t="str">
+        <v>40 - Lansdowne</v>
       </c>
       <c r="C62">
         <v>15800</v>
@@ -4239,31 +3919,31 @@
         <v>0</v>
       </c>
       <c r="G62">
-        <v>15191</v>
+        <v>15328</v>
       </c>
       <c r="H62">
-        <v>451</v>
+        <v>350</v>
       </c>
       <c r="I62">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="J62">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="K62">
-        <v>40</v>
+        <v>251</v>
       </c>
       <c r="L62">
-        <v>3449</v>
+        <v>3468</v>
       </c>
       <c r="M62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N62">
-        <v>302</v>
+        <v>351</v>
       </c>
       <c r="O62">
-        <v>14217</v>
+        <v>14315</v>
       </c>
       <c r="P62">
         <v>51334</v>
@@ -4278,12 +3958,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63">
       <c r="A63">
         <v>60</v>
       </c>
-      <c r="B63" t="s">
-        <v>82</v>
+      <c r="B63" t="str">
+        <v>41 - Kotdwar</v>
       </c>
       <c r="C63">
         <v>36754</v>
@@ -4298,37 +3978,37 @@
         <v>0</v>
       </c>
       <c r="G63">
-        <v>36533</v>
+        <v>36585</v>
       </c>
       <c r="H63">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="I63">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="J63">
-        <v>183</v>
+        <v>0</v>
       </c>
       <c r="K63">
         <v>0</v>
       </c>
       <c r="L63">
-        <v>10368</v>
+        <v>10610</v>
       </c>
       <c r="M63">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N63">
-        <v>809</v>
+        <v>835</v>
       </c>
       <c r="O63">
-        <v>31546</v>
+        <v>31722</v>
       </c>
       <c r="P63">
         <v>68691</v>
       </c>
       <c r="Q63">
-        <v>9810</v>
+        <v>9804</v>
       </c>
       <c r="R63">
         <v>0</v>
@@ -4337,12 +4017,12 @@
         <v>153</v>
       </c>
     </row>
-    <row r="64" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64">
       <c r="A64">
         <v>61</v>
       </c>
-      <c r="B64" t="s">
-        <v>83</v>
+      <c r="B64" t="str">
+        <v>15 - Chakrata</v>
       </c>
       <c r="C64">
         <v>42048</v>
@@ -4357,31 +4037,31 @@
         <v>0</v>
       </c>
       <c r="G64">
-        <v>38964</v>
+        <v>39581</v>
       </c>
       <c r="H64">
-        <v>2310</v>
+        <v>1984</v>
       </c>
       <c r="I64">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J64">
-        <v>117</v>
+        <v>92</v>
       </c>
       <c r="K64">
         <v>0</v>
       </c>
       <c r="L64">
-        <v>8857</v>
+        <v>9076</v>
       </c>
       <c r="M64">
         <v>8</v>
       </c>
       <c r="N64">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="O64">
-        <v>35634</v>
+        <v>36066</v>
       </c>
       <c r="P64">
         <v>60527</v>
@@ -4396,12 +4076,12 @@
         <v>101</v>
       </c>
     </row>
-    <row r="65" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65">
       <c r="A65">
         <v>62</v>
       </c>
-      <c r="B65" t="s">
-        <v>84</v>
+      <c r="B65" t="str">
+        <v>16 - Vikasnagar</v>
       </c>
       <c r="C65">
         <v>41389</v>
@@ -4416,31 +4096,31 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>33911</v>
+        <v>34567</v>
       </c>
       <c r="H65">
-        <v>5822</v>
+        <v>5163</v>
       </c>
       <c r="I65">
-        <v>428</v>
+        <v>1060</v>
       </c>
       <c r="J65">
-        <v>359</v>
+        <v>134</v>
       </c>
       <c r="K65">
         <v>0</v>
       </c>
       <c r="L65">
-        <v>9843</v>
+        <v>10211</v>
       </c>
       <c r="M65">
         <v>2</v>
       </c>
       <c r="N65">
-        <v>487</v>
+        <v>525</v>
       </c>
       <c r="O65">
-        <v>24359</v>
+        <v>24791</v>
       </c>
       <c r="P65">
         <v>34607</v>
@@ -4455,12 +4135,12 @@
         <v>138</v>
       </c>
     </row>
-    <row r="66" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66">
       <c r="A66">
         <v>63</v>
       </c>
-      <c r="B66" t="s">
-        <v>85</v>
+      <c r="B66" t="str">
+        <v>17 - Sahaspur</v>
       </c>
       <c r="C66">
         <v>67362</v>
@@ -4475,31 +4155,31 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>48573</v>
+        <v>51344</v>
       </c>
       <c r="H66">
-        <v>11039</v>
+        <v>10736</v>
       </c>
       <c r="I66">
-        <v>150</v>
+        <v>292</v>
       </c>
       <c r="J66">
-        <v>633</v>
+        <v>132</v>
       </c>
       <c r="K66">
         <v>0</v>
       </c>
       <c r="L66">
-        <v>9053</v>
+        <v>10081</v>
       </c>
       <c r="M66">
         <v>2</v>
       </c>
       <c r="N66">
-        <v>546</v>
+        <v>957</v>
       </c>
       <c r="O66">
-        <v>41225</v>
+        <v>43151</v>
       </c>
       <c r="P66">
         <v>93810</v>
@@ -4514,12 +4194,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="67" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67">
       <c r="A67">
         <v>64</v>
       </c>
-      <c r="B67" t="s">
-        <v>86</v>
+      <c r="B67" t="str">
+        <v>18 - Dharmpur</v>
       </c>
       <c r="C67">
         <v>68828</v>
@@ -4534,31 +4214,31 @@
         <v>0</v>
       </c>
       <c r="G67">
-        <v>60533</v>
+        <v>62084</v>
       </c>
       <c r="H67">
-        <v>2339</v>
+        <v>1153</v>
       </c>
       <c r="I67">
-        <v>2040</v>
+        <v>2696</v>
       </c>
       <c r="J67">
-        <v>629</v>
+        <v>167</v>
       </c>
       <c r="K67">
         <v>0</v>
       </c>
       <c r="L67">
-        <v>16701</v>
+        <v>17555</v>
       </c>
       <c r="M67">
         <v>10</v>
       </c>
       <c r="N67">
-        <v>769</v>
+        <v>1085</v>
       </c>
       <c r="O67">
-        <v>46872</v>
+        <v>48822</v>
       </c>
       <c r="P67">
         <v>78022</v>
@@ -4573,12 +4253,12 @@
         <v>116</v>
       </c>
     </row>
-    <row r="68" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68">
       <c r="A68">
         <v>65</v>
       </c>
-      <c r="B68" t="s">
-        <v>87</v>
+      <c r="B68" t="str">
+        <v>19 - Raipur</v>
       </c>
       <c r="C68">
         <v>65397</v>
@@ -4587,37 +4267,37 @@
         <v>0</v>
       </c>
       <c r="E68">
-        <v>65362</v>
+        <v>65397</v>
       </c>
       <c r="F68">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G68">
-        <v>58665</v>
+        <v>59397</v>
       </c>
       <c r="H68">
-        <v>5649</v>
+        <v>4894</v>
       </c>
       <c r="I68">
-        <v>765</v>
+        <v>869</v>
       </c>
       <c r="J68">
-        <v>463</v>
+        <v>202</v>
       </c>
       <c r="K68">
         <v>0</v>
       </c>
       <c r="L68">
-        <v>14166</v>
+        <v>14846</v>
       </c>
       <c r="M68">
         <v>2</v>
       </c>
       <c r="N68">
-        <v>304</v>
+        <v>335</v>
       </c>
       <c r="O68">
-        <v>49254</v>
+        <v>49616</v>
       </c>
       <c r="P68">
         <v>61338</v>
@@ -4632,12 +4312,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="69" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69">
       <c r="A69">
         <v>66</v>
       </c>
-      <c r="B69" t="s">
-        <v>88</v>
+      <c r="B69" t="str">
+        <v>20 - Rajpur Road</v>
       </c>
       <c r="C69">
         <v>43938</v>
@@ -4652,34 +4332,34 @@
         <v>0</v>
       </c>
       <c r="G69">
-        <v>35843</v>
+        <v>36833</v>
       </c>
       <c r="H69">
-        <v>5472</v>
+        <v>6038</v>
       </c>
       <c r="I69">
-        <v>184</v>
+        <v>376</v>
       </c>
       <c r="J69">
-        <v>225</v>
+        <v>339</v>
       </c>
       <c r="K69">
         <v>0</v>
       </c>
       <c r="L69">
-        <v>13264</v>
+        <v>13833</v>
       </c>
       <c r="M69">
         <v>2</v>
       </c>
       <c r="N69">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="O69">
-        <v>26602</v>
+        <v>27549</v>
       </c>
       <c r="P69">
-        <v>33969</v>
+        <v>34089</v>
       </c>
       <c r="Q69">
         <v>6528</v>
@@ -4691,12 +4371,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="70" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70">
       <c r="A70">
         <v>67</v>
       </c>
-      <c r="B70" t="s">
-        <v>89</v>
+      <c r="B70" t="str">
+        <v>21 - Dehradun Cantonment</v>
       </c>
       <c r="C70">
         <v>47711</v>
@@ -4711,31 +4391,31 @@
         <v>0</v>
       </c>
       <c r="G70">
-        <v>42918</v>
+        <v>43233</v>
       </c>
       <c r="H70">
-        <v>1688</v>
+        <v>1388</v>
       </c>
       <c r="I70">
-        <v>2208</v>
+        <v>2339</v>
       </c>
       <c r="J70">
-        <v>193</v>
+        <v>33</v>
       </c>
       <c r="K70">
         <v>0</v>
       </c>
       <c r="L70">
-        <v>16834</v>
+        <v>17076</v>
       </c>
       <c r="M70">
         <v>2</v>
       </c>
       <c r="N70">
-        <v>450</v>
+        <v>556</v>
       </c>
       <c r="O70">
-        <v>34998</v>
+        <v>35345</v>
       </c>
       <c r="P70">
         <v>42040</v>
@@ -4750,12 +4430,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="71" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71">
       <c r="A71">
         <v>68</v>
       </c>
-      <c r="B71" t="s">
-        <v>90</v>
+      <c r="B71" t="str">
+        <v>22 - Mussoorie</v>
       </c>
       <c r="C71">
         <v>50963</v>
@@ -4770,31 +4450,31 @@
         <v>0</v>
       </c>
       <c r="G71">
-        <v>44856</v>
+        <v>45446</v>
       </c>
       <c r="H71">
-        <v>4381</v>
+        <v>3980</v>
       </c>
       <c r="I71">
-        <v>1431</v>
+        <v>1421</v>
       </c>
       <c r="J71">
-        <v>50</v>
+        <v>114</v>
       </c>
       <c r="K71">
         <v>0</v>
       </c>
       <c r="L71">
-        <v>20037</v>
+        <v>20361</v>
       </c>
       <c r="M71">
         <v>1</v>
       </c>
       <c r="N71">
-        <v>2495</v>
+        <v>2684</v>
       </c>
       <c r="O71">
-        <v>31257</v>
+        <v>31293</v>
       </c>
       <c r="P71">
         <v>48896</v>
@@ -4809,12 +4489,12 @@
         <v>235</v>
       </c>
     </row>
-    <row r="72" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72">
       <c r="A72">
         <v>69</v>
       </c>
-      <c r="B72" t="s">
-        <v>91</v>
+      <c r="B72" t="str">
+        <v>23 - Doiwala</v>
       </c>
       <c r="C72">
         <v>61543</v>
@@ -4829,31 +4509,31 @@
         <v>1</v>
       </c>
       <c r="G72">
-        <v>51375</v>
+        <v>52673</v>
       </c>
       <c r="H72">
-        <v>8101</v>
+        <v>6930</v>
       </c>
       <c r="I72">
-        <v>1659</v>
+        <v>1704</v>
       </c>
       <c r="J72">
-        <v>325</v>
+        <v>246</v>
       </c>
       <c r="K72">
         <v>0</v>
       </c>
       <c r="L72">
-        <v>14612</v>
+        <v>15093</v>
       </c>
       <c r="M72">
         <v>9</v>
       </c>
       <c r="N72">
-        <v>346</v>
+        <v>394</v>
       </c>
       <c r="O72">
-        <v>39880</v>
+        <v>41398</v>
       </c>
       <c r="P72">
         <v>85505</v>
@@ -4868,12 +4548,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="73" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73">
       <c r="A73">
         <v>70</v>
       </c>
-      <c r="B73" t="s">
-        <v>92</v>
+      <c r="B73" t="str">
+        <v>24 - Rishikesh</v>
       </c>
       <c r="C73">
         <v>58915</v>
@@ -4888,31 +4568,31 @@
         <v>0</v>
       </c>
       <c r="G73">
-        <v>44837</v>
+        <v>46625</v>
       </c>
       <c r="H73">
-        <v>13083</v>
+        <v>11684</v>
       </c>
       <c r="I73">
-        <v>267</v>
+        <v>210</v>
       </c>
       <c r="J73">
-        <v>389</v>
+        <v>472</v>
       </c>
       <c r="K73">
         <v>0</v>
       </c>
       <c r="L73">
-        <v>8596</v>
+        <v>9294</v>
       </c>
       <c r="M73">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N73">
-        <v>400</v>
+        <v>507</v>
       </c>
       <c r="O73">
-        <v>38947</v>
+        <v>40900</v>
       </c>
       <c r="P73">
         <v>67550</v>
@@ -4927,11 +4607,10 @@
         <v>74</v>
       </c>
     </row>
-    <row r="74" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B74" s="1"/>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>Total</v>
+      </c>
       <c r="C74">
         <v>2430382</v>
       </c>
@@ -4939,43 +4618,43 @@
         <v>0</v>
       </c>
       <c r="E74">
-        <v>2428641</v>
+        <v>2429160</v>
       </c>
       <c r="F74">
-        <v>1741</v>
+        <v>1222</v>
       </c>
       <c r="G74">
-        <v>1911957</v>
+        <v>1983893</v>
       </c>
       <c r="H74">
-        <v>400625</v>
+        <v>359454</v>
       </c>
       <c r="I74">
-        <v>14727</v>
+        <v>17684</v>
       </c>
       <c r="J74">
-        <v>77303</v>
+        <v>76391</v>
       </c>
       <c r="K74">
-        <v>35826</v>
+        <v>38833</v>
       </c>
       <c r="L74">
-        <v>402785</v>
+        <v>421009</v>
       </c>
       <c r="M74">
-        <v>366</v>
+        <v>391</v>
       </c>
       <c r="N74">
-        <v>24703</v>
+        <v>28064</v>
       </c>
       <c r="O74">
-        <v>1613361</v>
+        <v>1682675</v>
       </c>
       <c r="P74">
-        <v>4246005</v>
+        <v>4302032</v>
       </c>
       <c r="Q74">
-        <v>629685</v>
+        <v>629579</v>
       </c>
       <c r="R74">
         <v>1</v>
@@ -4986,7 +4665,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A74:B74"/>
     <mergeCell ref="A1:T1"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
@@ -4998,10 +4676,10 @@
     <mergeCell ref="J2:M2"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="A74:B74"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A2:S74 B1:S1" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S74"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -1,41 +1,316 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MANNA\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210"/>
+  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
+  <si>
+    <t>S. No.</t>
+  </si>
+  <si>
+    <t>AC No. - AC Name</t>
+  </si>
+  <si>
+    <t>Notice Generated</t>
+  </si>
+  <si>
+    <t>Pending for Notice Generation</t>
+  </si>
+  <si>
+    <t>Notice Delivered</t>
+  </si>
+  <si>
+    <t>Notices pending delivery</t>
+  </si>
+  <si>
+    <t>Hearing</t>
+  </si>
+  <si>
+    <t>DEO Status</t>
+  </si>
+  <si>
+    <t>ERO/AERO Status</t>
+  </si>
+  <si>
+    <t>DSE with UP</t>
+  </si>
+  <si>
+    <t>Hearing Held</t>
+  </si>
+  <si>
+    <t>Hearing Date Lapsed</t>
+  </si>
+  <si>
+    <t>Reschedule Date Lapsed</t>
+  </si>
+  <si>
+    <t>Total Pending</t>
+  </si>
+  <si>
+    <t>Pending &gt; 5 days</t>
+  </si>
+  <si>
+    <t>Verified</t>
+  </si>
+  <si>
+    <t>Not Verified</t>
+  </si>
+  <si>
+    <t>Found Ineligible for Final</t>
+  </si>
+  <si>
+    <t>Parked for Final Publication w.r.t. Notices Generated</t>
+  </si>
+  <si>
+    <t>Parked For Final Publication w.r.t. Others</t>
+  </si>
+  <si>
+    <t>Electors having DSE with UP</t>
+  </si>
+  <si>
+    <t>Form 7 Generated</t>
+  </si>
+  <si>
+    <t>No Action Required</t>
+  </si>
+  <si>
+    <t>25 - Haridwar</t>
+  </si>
+  <si>
+    <t>26 - BHEL Ranipur</t>
+  </si>
+  <si>
+    <t>27 - Jwalapur</t>
+  </si>
+  <si>
+    <t>28 - Bhagwanpur</t>
+  </si>
+  <si>
+    <t>29 - Jhabrera</t>
+  </si>
+  <si>
+    <t>30 - Piran Kaliyar</t>
+  </si>
+  <si>
+    <t>31 - Roorkee</t>
+  </si>
+  <si>
+    <t>32 - Khanpur</t>
+  </si>
+  <si>
+    <t>33 - Manglore</t>
+  </si>
+  <si>
+    <t>34 - Laksar</t>
+  </si>
+  <si>
+    <t>35 - Haridwar Rural</t>
+  </si>
+  <si>
+    <t>56 - Lalkuan</t>
+  </si>
+  <si>
+    <t>57 - Bhimtal</t>
+  </si>
+  <si>
+    <t>58 - Nainital</t>
+  </si>
+  <si>
+    <t>59 - Haldwani</t>
+  </si>
+  <si>
+    <t>60 - Kaladhungi</t>
+  </si>
+  <si>
+    <t>61 - Ramnagar</t>
+  </si>
+  <si>
+    <t>48 - Dwarahat</t>
+  </si>
+  <si>
+    <t>49 - Salt</t>
+  </si>
+  <si>
+    <t>50 - Ranikhet</t>
+  </si>
+  <si>
+    <t>51 - Someshwar</t>
+  </si>
+  <si>
+    <t>52 - Almora</t>
+  </si>
+  <si>
+    <t>53 - Jageshwar</t>
+  </si>
+  <si>
+    <t>62 - Jaspur</t>
+  </si>
+  <si>
+    <t>63 - Kashipur</t>
+  </si>
+  <si>
+    <t>64 - Bajpur</t>
+  </si>
+  <si>
+    <t>65 - Gadarpur</t>
+  </si>
+  <si>
+    <t>66 - Rudrapur</t>
+  </si>
+  <si>
+    <t>67 - Kichha</t>
+  </si>
+  <si>
+    <t>68 - Sitarganj</t>
+  </si>
+  <si>
+    <t>69 - Nanakmatta</t>
+  </si>
+  <si>
+    <t>70 - Khatima</t>
+  </si>
+  <si>
+    <t>42 - Dharchula</t>
+  </si>
+  <si>
+    <t>43 - Didihat</t>
+  </si>
+  <si>
+    <t>44 - Pithoragarh</t>
+  </si>
+  <si>
+    <t>45 - Gangolihat</t>
+  </si>
+  <si>
+    <t>46 - Kapkot</t>
+  </si>
+  <si>
+    <t>47 - Bageshwar</t>
+  </si>
+  <si>
+    <t>54 - Lohaghat</t>
+  </si>
+  <si>
+    <t>55 - Champawat</t>
+  </si>
+  <si>
+    <t>4 - Badrinath</t>
+  </si>
+  <si>
+    <t>5 - Tharali</t>
+  </si>
+  <si>
+    <t>6 - Karanprayag</t>
+  </si>
+  <si>
+    <t>1 - Purola</t>
+  </si>
+  <si>
+    <t>2 - Yamunotri</t>
+  </si>
+  <si>
+    <t>3 - Gangotri</t>
+  </si>
+  <si>
+    <t>7 - Kedarnath</t>
+  </si>
+  <si>
+    <t>8 - Rudraprayag</t>
+  </si>
+  <si>
+    <t>9 - Ghansali</t>
+  </si>
+  <si>
+    <t>10 - Devprayag</t>
+  </si>
+  <si>
+    <t>11 - Narendranagar</t>
+  </si>
+  <si>
+    <t>12 - Pratapnagar</t>
+  </si>
+  <si>
+    <t>13 - Tehri</t>
+  </si>
+  <si>
+    <t>14 - Dhanolti</t>
+  </si>
+  <si>
+    <t>36 - Yamkeshwar</t>
+  </si>
+  <si>
+    <t>37 - Pauri</t>
+  </si>
+  <si>
+    <t>38 - Srinagar</t>
+  </si>
+  <si>
+    <t>39 - Chaubattakhal</t>
+  </si>
+  <si>
+    <t>40 - Lansdowne</t>
+  </si>
+  <si>
+    <t>41 - Kotdwar</t>
+  </si>
+  <si>
+    <t>15 - Chakrata</t>
+  </si>
+  <si>
+    <t>16 - Vikasnagar</t>
+  </si>
+  <si>
+    <t>17 - Sahaspur</t>
+  </si>
+  <si>
+    <t>18 - Dharmpur</t>
+  </si>
+  <si>
+    <t>19 - Raipur</t>
+  </si>
+  <si>
+    <t>20 - Rajpur Road</t>
+  </si>
+  <si>
+    <t>21 - Dehradun Cantonment</t>
+  </si>
+  <si>
+    <t>22 - Mussoorie</t>
+  </si>
+  <si>
+    <t>23 - Doiwala</t>
+  </si>
+  <si>
+    <t>24 - Rishikesh</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Notice &amp; Hearing Report Last Updated On : 26-08-2026 07:57:22</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -64,7 +339,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -72,6 +348,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,93 +680,128 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S74"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:T74"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Notice &amp; Hearing Report</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>S. No.</v>
-      </c>
-      <c r="B2" t="str">
-        <v>AC No. - AC Name</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Notice Generated</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Pending for Notice Generation</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Notice Delivered</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Notices pending delivery</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Hearing</v>
-      </c>
-      <c r="J2" t="str">
-        <v>DEO Status</v>
-      </c>
-      <c r="N2" t="str">
-        <v>ERO/AERO Status</v>
-      </c>
-      <c r="Q2" t="str">
-        <v>DSE with UP</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="G3" t="str">
-        <v>Hearing Held</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Hearing Date Lapsed</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Reschedule Date Lapsed</v>
-      </c>
-      <c r="J3" t="str">
-        <v>Total Pending</v>
-      </c>
-      <c r="K3" t="str">
-        <v>Pending &gt; 5 days</v>
-      </c>
-      <c r="L3" t="str">
-        <v>Verified</v>
-      </c>
-      <c r="M3" t="str">
-        <v>Not Verified</v>
-      </c>
-      <c r="N3" t="str">
-        <v>Found Ineligible for Final</v>
-      </c>
-      <c r="O3" t="str">
-        <v>Parked for Final Publication w.r.t. Notices Generated</v>
-      </c>
-      <c r="P3" t="str">
-        <v>Parked For Final Publication w.r.t. Others</v>
-      </c>
-      <c r="Q3" t="str">
-        <v>Electors having DSE with UP</v>
-      </c>
-      <c r="R3" t="str">
-        <v>Form 7 Generated</v>
-      </c>
-      <c r="S3" t="str">
-        <v>No Action Required</v>
-      </c>
-    </row>
-    <row r="4">
+    <row r="1" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+    </row>
+    <row r="2" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+    </row>
+    <row r="3" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N3" t="s">
+        <v>17</v>
+      </c>
+      <c r="O3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R3" t="s">
+        <v>21</v>
+      </c>
+      <c r="S3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" t="str">
-        <v>25 - Haridwar</v>
+      <c r="B4" t="s">
+        <v>23</v>
       </c>
       <c r="C4">
         <v>51528</v>
@@ -536,12 +855,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
-      <c r="B5" t="str">
-        <v>26 - BHEL Ranipur</v>
+      <c r="B5" t="s">
+        <v>24</v>
       </c>
       <c r="C5">
         <v>53911</v>
@@ -595,12 +914,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
-      <c r="B6" t="str">
-        <v>27 - Jwalapur</v>
+      <c r="B6" t="s">
+        <v>25</v>
       </c>
       <c r="C6">
         <v>39773</v>
@@ -654,12 +973,12 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4</v>
       </c>
-      <c r="B7" t="str">
-        <v>28 - Bhagwanpur</v>
+      <c r="B7" t="s">
+        <v>26</v>
       </c>
       <c r="C7">
         <v>39463</v>
@@ -713,12 +1032,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
-      <c r="B8" t="str">
-        <v>29 - Jhabrera</v>
+      <c r="B8" t="s">
+        <v>27</v>
       </c>
       <c r="C8">
         <v>40552</v>
@@ -772,12 +1091,12 @@
         <v>110</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6</v>
       </c>
-      <c r="B9" t="str">
-        <v>30 - Piran Kaliyar</v>
+      <c r="B9" t="s">
+        <v>28</v>
       </c>
       <c r="C9">
         <v>43273</v>
@@ -831,12 +1150,12 @@
         <v>110</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>7</v>
       </c>
-      <c r="B10" t="str">
-        <v>31 - Roorkee</v>
+      <c r="B10" t="s">
+        <v>29</v>
       </c>
       <c r="C10">
         <v>36576</v>
@@ -890,12 +1209,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>8</v>
       </c>
-      <c r="B11" t="str">
-        <v>32 - Khanpur</v>
+      <c r="B11" t="s">
+        <v>30</v>
       </c>
       <c r="C11">
         <v>50998</v>
@@ -949,12 +1268,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
-      <c r="B12" t="str">
-        <v>33 - Manglore</v>
+      <c r="B12" t="s">
+        <v>31</v>
       </c>
       <c r="C12">
         <v>40739</v>
@@ -1008,12 +1327,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
-      <c r="B13" t="str">
-        <v>34 - Laksar</v>
+      <c r="B13" t="s">
+        <v>32</v>
       </c>
       <c r="C13">
         <v>37031</v>
@@ -1067,12 +1386,12 @@
         <v>109</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>11</v>
       </c>
-      <c r="B14" t="str">
-        <v>35 - Haridwar Rural</v>
+      <c r="B14" t="s">
+        <v>33</v>
       </c>
       <c r="C14">
         <v>48966</v>
@@ -1126,12 +1445,12 @@
         <v>174</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12</v>
       </c>
-      <c r="B15" t="str">
-        <v>56 - Lalkuan</v>
+      <c r="B15" t="s">
+        <v>34</v>
       </c>
       <c r="C15">
         <v>42703</v>
@@ -1185,12 +1504,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13</v>
       </c>
-      <c r="B16" t="str">
-        <v>57 - Bhimtal</v>
+      <c r="B16" t="s">
+        <v>35</v>
       </c>
       <c r="C16">
         <v>25549</v>
@@ -1244,12 +1563,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>14</v>
       </c>
-      <c r="B17" t="str">
-        <v>58 - Nainital</v>
+      <c r="B17" t="s">
+        <v>36</v>
       </c>
       <c r="C17">
         <v>27707</v>
@@ -1303,12 +1622,12 @@
         <v>105</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>15</v>
       </c>
-      <c r="B18" t="str">
-        <v>59 - Haldwani</v>
+      <c r="B18" t="s">
+        <v>37</v>
       </c>
       <c r="C18">
         <v>47836</v>
@@ -1362,12 +1681,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>16</v>
       </c>
-      <c r="B19" t="str">
-        <v>60 - Kaladhungi</v>
+      <c r="B19" t="s">
+        <v>38</v>
       </c>
       <c r="C19">
         <v>56490</v>
@@ -1421,12 +1740,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>17</v>
       </c>
-      <c r="B20" t="str">
-        <v>61 - Ramnagar</v>
+      <c r="B20" t="s">
+        <v>39</v>
       </c>
       <c r="C20">
         <v>35017</v>
@@ -1480,12 +1799,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>18</v>
       </c>
-      <c r="B21" t="str">
-        <v>48 - Dwarahat</v>
+      <c r="B21" t="s">
+        <v>40</v>
       </c>
       <c r="C21">
         <v>16962</v>
@@ -1539,12 +1858,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>19</v>
       </c>
-      <c r="B22" t="str">
-        <v>49 - Salt</v>
+      <c r="B22" t="s">
+        <v>41</v>
       </c>
       <c r="C22">
         <v>18668</v>
@@ -1598,12 +1917,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>20</v>
       </c>
-      <c r="B23" t="str">
-        <v>50 - Ranikhet</v>
+      <c r="B23" t="s">
+        <v>42</v>
       </c>
       <c r="C23">
         <v>12020</v>
@@ -1657,12 +1976,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>21</v>
       </c>
-      <c r="B24" t="str">
-        <v>51 - Someshwar</v>
+      <c r="B24" t="s">
+        <v>43</v>
       </c>
       <c r="C24">
         <v>14056</v>
@@ -1716,12 +2035,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>22</v>
       </c>
-      <c r="B25" t="str">
-        <v>52 - Almora</v>
+      <c r="B25" t="s">
+        <v>44</v>
       </c>
       <c r="C25">
         <v>19266</v>
@@ -1775,12 +2094,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23</v>
       </c>
-      <c r="B26" t="str">
-        <v>53 - Jageshwar</v>
+      <c r="B26" t="s">
+        <v>45</v>
       </c>
       <c r="C26">
         <v>17557</v>
@@ -1834,12 +2153,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>24</v>
       </c>
-      <c r="B27" t="str">
-        <v>62 - Jaspur</v>
+      <c r="B27" t="s">
+        <v>46</v>
       </c>
       <c r="C27">
         <v>44276</v>
@@ -1893,12 +2212,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25</v>
       </c>
-      <c r="B28" t="str">
-        <v>63 - Kashipur</v>
+      <c r="B28" t="s">
+        <v>47</v>
       </c>
       <c r="C28">
         <v>54349</v>
@@ -1952,12 +2271,12 @@
         <v>134</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26</v>
       </c>
-      <c r="B29" t="str">
-        <v>64 - Bajpur</v>
+      <c r="B29" t="s">
+        <v>48</v>
       </c>
       <c r="C29">
         <v>47111</v>
@@ -2011,12 +2330,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>27</v>
       </c>
-      <c r="B30" t="str">
-        <v>65 - Gadarpur</v>
+      <c r="B30" t="s">
+        <v>49</v>
       </c>
       <c r="C30">
         <v>52653</v>
@@ -2070,12 +2389,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>28</v>
       </c>
-      <c r="B31" t="str">
-        <v>66 - Rudrapur</v>
+      <c r="B31" t="s">
+        <v>50</v>
       </c>
       <c r="C31">
         <v>91162</v>
@@ -2129,12 +2448,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>29</v>
       </c>
-      <c r="B32" t="str">
-        <v>67 - Kichha</v>
+      <c r="B32" t="s">
+        <v>51</v>
       </c>
       <c r="C32">
         <v>46728</v>
@@ -2188,12 +2507,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>30</v>
       </c>
-      <c r="B33" t="str">
-        <v>68 - Sitarganj</v>
+      <c r="B33" t="s">
+        <v>52</v>
       </c>
       <c r="C33">
         <v>40230</v>
@@ -2247,12 +2566,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>31</v>
       </c>
-      <c r="B34" t="str">
-        <v>69 - Nanakmatta</v>
+      <c r="B34" t="s">
+        <v>53</v>
       </c>
       <c r="C34">
         <v>36542</v>
@@ -2306,12 +2625,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32</v>
       </c>
-      <c r="B35" t="str">
-        <v>70 - Khatima</v>
+      <c r="B35" t="s">
+        <v>54</v>
       </c>
       <c r="C35">
         <v>33564</v>
@@ -2365,12 +2684,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>33</v>
       </c>
-      <c r="B36" t="str">
-        <v>42 - Dharchula</v>
+      <c r="B36" t="s">
+        <v>55</v>
       </c>
       <c r="C36">
         <v>20905</v>
@@ -2424,12 +2743,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>34</v>
       </c>
-      <c r="B37" t="str">
-        <v>43 - Didihat</v>
+      <c r="B37" t="s">
+        <v>56</v>
       </c>
       <c r="C37">
         <v>17692</v>
@@ -2483,12 +2802,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>35</v>
       </c>
-      <c r="B38" t="str">
-        <v>44 - Pithoragarh</v>
+      <c r="B38" t="s">
+        <v>57</v>
       </c>
       <c r="C38">
         <v>29110</v>
@@ -2542,12 +2861,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>36</v>
       </c>
-      <c r="B39" t="str">
-        <v>45 - Gangolihat</v>
+      <c r="B39" t="s">
+        <v>58</v>
       </c>
       <c r="C39">
         <v>21367</v>
@@ -2601,12 +2920,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>37</v>
       </c>
-      <c r="B40" t="str">
-        <v>46 - Kapkot</v>
+      <c r="B40" t="s">
+        <v>59</v>
       </c>
       <c r="C40">
         <v>18905</v>
@@ -2660,12 +2979,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>38</v>
       </c>
-      <c r="B41" t="str">
-        <v>47 - Bageshwar</v>
+      <c r="B41" t="s">
+        <v>60</v>
       </c>
       <c r="C41">
         <v>23521</v>
@@ -2719,12 +3038,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>39</v>
       </c>
-      <c r="B42" t="str">
-        <v>54 - Lohaghat</v>
+      <c r="B42" t="s">
+        <v>61</v>
       </c>
       <c r="C42">
         <v>27565</v>
@@ -2778,12 +3097,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>40</v>
       </c>
-      <c r="B43" t="str">
-        <v>55 - Champawat</v>
+      <c r="B43" t="s">
+        <v>62</v>
       </c>
       <c r="C43">
         <v>29700</v>
@@ -2837,12 +3156,12 @@
         <v>121</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>41</v>
       </c>
-      <c r="B44" t="str">
-        <v>4 - Badrinath</v>
+      <c r="B44" t="s">
+        <v>63</v>
       </c>
       <c r="C44">
         <v>21900</v>
@@ -2896,12 +3215,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>42</v>
       </c>
-      <c r="B45" t="str">
-        <v>5 - Tharali</v>
+      <c r="B45" t="s">
+        <v>64</v>
       </c>
       <c r="C45">
         <v>19935</v>
@@ -2955,12 +3274,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>43</v>
       </c>
-      <c r="B46" t="str">
-        <v>6 - Karanprayag</v>
+      <c r="B46" t="s">
+        <v>65</v>
       </c>
       <c r="C46">
         <v>21512</v>
@@ -3014,12 +3333,12 @@
         <v>152</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>44</v>
       </c>
-      <c r="B47" t="str">
-        <v>1 - Purola</v>
+      <c r="B47" t="s">
+        <v>66</v>
       </c>
       <c r="C47">
         <v>22426</v>
@@ -3073,12 +3392,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>45</v>
       </c>
-      <c r="B48" t="str">
-        <v>2 - Yamunotri</v>
+      <c r="B48" t="s">
+        <v>67</v>
       </c>
       <c r="C48">
         <v>19641</v>
@@ -3132,12 +3451,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>46</v>
       </c>
-      <c r="B49" t="str">
-        <v>3 - Gangotri</v>
+      <c r="B49" t="s">
+        <v>68</v>
       </c>
       <c r="C49">
         <v>21651</v>
@@ -3191,12 +3510,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>47</v>
       </c>
-      <c r="B50" t="str">
-        <v>7 - Kedarnath</v>
+      <c r="B50" t="s">
+        <v>69</v>
       </c>
       <c r="C50">
         <v>21936</v>
@@ -3250,12 +3569,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>48</v>
       </c>
-      <c r="B51" t="str">
-        <v>8 - Rudraprayag</v>
+      <c r="B51" t="s">
+        <v>70</v>
       </c>
       <c r="C51">
         <v>23798</v>
@@ -3309,12 +3628,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>49</v>
       </c>
-      <c r="B52" t="str">
-        <v>9 - Ghansali</v>
+      <c r="B52" t="s">
+        <v>71</v>
       </c>
       <c r="C52">
         <v>21094</v>
@@ -3368,12 +3687,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>50</v>
       </c>
-      <c r="B53" t="str">
-        <v>10 - Devprayag</v>
+      <c r="B53" t="s">
+        <v>72</v>
       </c>
       <c r="C53">
         <v>19131</v>
@@ -3427,12 +3746,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>51</v>
       </c>
-      <c r="B54" t="str">
-        <v>11 - Narendranagar</v>
+      <c r="B54" t="s">
+        <v>73</v>
       </c>
       <c r="C54">
         <v>20758</v>
@@ -3486,12 +3805,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>52</v>
       </c>
-      <c r="B55" t="str">
-        <v>12 - Pratapnagar</v>
+      <c r="B55" t="s">
+        <v>74</v>
       </c>
       <c r="C55">
         <v>16022</v>
@@ -3545,12 +3864,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>53</v>
       </c>
-      <c r="B56" t="str">
-        <v>13 - Tehri</v>
+      <c r="B56" t="s">
+        <v>75</v>
       </c>
       <c r="C56">
         <v>19256</v>
@@ -3604,12 +3923,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>54</v>
       </c>
-      <c r="B57" t="str">
-        <v>14 - Dhanolti</v>
+      <c r="B57" t="s">
+        <v>76</v>
       </c>
       <c r="C57">
         <v>21240</v>
@@ -3663,12 +3982,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>55</v>
       </c>
-      <c r="B58" t="str">
-        <v>36 - Yamkeshwar</v>
+      <c r="B58" t="s">
+        <v>77</v>
       </c>
       <c r="C58">
         <v>22819</v>
@@ -3722,12 +4041,12 @@
         <v>64</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>56</v>
       </c>
-      <c r="B59" t="str">
-        <v>37 - Pauri</v>
+      <c r="B59" t="s">
+        <v>78</v>
       </c>
       <c r="C59">
         <v>18776</v>
@@ -3781,12 +4100,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>57</v>
       </c>
-      <c r="B60" t="str">
-        <v>38 - Srinagar</v>
+      <c r="B60" t="s">
+        <v>79</v>
       </c>
       <c r="C60">
         <v>23749</v>
@@ -3840,12 +4159,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>58</v>
       </c>
-      <c r="B61" t="str">
-        <v>39 - Chaubattakhal</v>
+      <c r="B61" t="s">
+        <v>80</v>
       </c>
       <c r="C61">
         <v>22069</v>
@@ -3899,12 +4218,12 @@
         <v>268</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>59</v>
       </c>
-      <c r="B62" t="str">
-        <v>40 - Lansdowne</v>
+      <c r="B62" t="s">
+        <v>81</v>
       </c>
       <c r="C62">
         <v>15800</v>
@@ -3958,12 +4277,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>60</v>
       </c>
-      <c r="B63" t="str">
-        <v>41 - Kotdwar</v>
+      <c r="B63" t="s">
+        <v>82</v>
       </c>
       <c r="C63">
         <v>36754</v>
@@ -4017,12 +4336,12 @@
         <v>153</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>61</v>
       </c>
-      <c r="B64" t="str">
-        <v>15 - Chakrata</v>
+      <c r="B64" t="s">
+        <v>83</v>
       </c>
       <c r="C64">
         <v>42048</v>
@@ -4076,12 +4395,12 @@
         <v>101</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>62</v>
       </c>
-      <c r="B65" t="str">
-        <v>16 - Vikasnagar</v>
+      <c r="B65" t="s">
+        <v>84</v>
       </c>
       <c r="C65">
         <v>41389</v>
@@ -4135,12 +4454,12 @@
         <v>138</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>63</v>
       </c>
-      <c r="B66" t="str">
-        <v>17 - Sahaspur</v>
+      <c r="B66" t="s">
+        <v>85</v>
       </c>
       <c r="C66">
         <v>67362</v>
@@ -4194,12 +4513,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>64</v>
       </c>
-      <c r="B67" t="str">
-        <v>18 - Dharmpur</v>
+      <c r="B67" t="s">
+        <v>86</v>
       </c>
       <c r="C67">
         <v>68828</v>
@@ -4253,12 +4572,12 @@
         <v>116</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>65</v>
       </c>
-      <c r="B68" t="str">
-        <v>19 - Raipur</v>
+      <c r="B68" t="s">
+        <v>87</v>
       </c>
       <c r="C68">
         <v>65397</v>
@@ -4312,12 +4631,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>66</v>
       </c>
-      <c r="B69" t="str">
-        <v>20 - Rajpur Road</v>
+      <c r="B69" t="s">
+        <v>88</v>
       </c>
       <c r="C69">
         <v>43938</v>
@@ -4371,12 +4690,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>67</v>
       </c>
-      <c r="B70" t="str">
-        <v>21 - Dehradun Cantonment</v>
+      <c r="B70" t="s">
+        <v>89</v>
       </c>
       <c r="C70">
         <v>47711</v>
@@ -4430,12 +4749,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>68</v>
       </c>
-      <c r="B71" t="str">
-        <v>22 - Mussoorie</v>
+      <c r="B71" t="s">
+        <v>90</v>
       </c>
       <c r="C71">
         <v>50963</v>
@@ -4489,12 +4808,12 @@
         <v>235</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>69</v>
       </c>
-      <c r="B72" t="str">
-        <v>23 - Doiwala</v>
+      <c r="B72" t="s">
+        <v>91</v>
       </c>
       <c r="C72">
         <v>61543</v>
@@ -4548,12 +4867,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>70</v>
       </c>
-      <c r="B73" t="str">
-        <v>24 - Rishikesh</v>
+      <c r="B73" t="s">
+        <v>92</v>
       </c>
       <c r="C73">
         <v>58915</v>
@@ -4607,10 +4926,11 @@
         <v>74</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="str">
-        <v>Total</v>
-      </c>
+    <row r="74" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B74" s="1"/>
       <c r="C74">
         <v>2430382</v>
       </c>
@@ -4665,6 +4985,7 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A74:B74"/>
     <mergeCell ref="A1:T1"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
@@ -4676,10 +4997,10 @@
     <mergeCell ref="J2:M2"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="A74:B74"/>
   </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S74"/>
+    <ignoredError sqref="A2:S74 B1:S1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MANNA\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\FormProcess\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF7B09EA-A705-4FEB-89BB-1C13ACE3B583}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -303,13 +304,13 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Notice &amp; Hearing Report Last Updated On : 26-08-2026 07:57:22</t>
+    <t>Notice &amp; Hearing Report Last Updated On : 27-08-2026 07:57:21</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -340,8 +341,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -680,7 +681,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T74"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -816,31 +817,31 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>29665</v>
+        <v>36073</v>
       </c>
       <c r="H4">
-        <v>17738</v>
+        <v>13086</v>
       </c>
       <c r="I4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J4">
-        <v>5691</v>
+        <v>5876</v>
       </c>
       <c r="K4">
-        <v>2902</v>
+        <v>2949</v>
       </c>
       <c r="L4">
-        <v>2870</v>
+        <v>3432</v>
       </c>
       <c r="M4">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="N4">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="O4">
-        <v>22187</v>
+        <v>27819</v>
       </c>
       <c r="P4">
         <v>53812</v>
@@ -875,31 +876,31 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>40511</v>
+        <v>45813</v>
       </c>
       <c r="H5">
-        <v>10295</v>
+        <v>6003</v>
       </c>
       <c r="I5">
         <v>7</v>
       </c>
       <c r="J5">
-        <v>3912</v>
+        <v>3701</v>
       </c>
       <c r="K5">
-        <v>1962</v>
+        <v>2102</v>
       </c>
       <c r="L5">
-        <v>2911</v>
+        <v>3332</v>
       </c>
       <c r="M5">
         <v>40</v>
       </c>
       <c r="N5">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O5">
-        <v>35695</v>
+        <v>41473</v>
       </c>
       <c r="P5">
         <v>55484</v>
@@ -934,34 +935,34 @@
         <v>2</v>
       </c>
       <c r="G6">
-        <v>21051</v>
+        <v>24637</v>
       </c>
       <c r="H6">
-        <v>13460</v>
+        <v>9897</v>
       </c>
       <c r="I6">
-        <v>194</v>
+        <v>133</v>
       </c>
       <c r="J6">
-        <v>1450</v>
+        <v>1884</v>
       </c>
       <c r="K6">
-        <v>1077</v>
+        <v>1096</v>
       </c>
       <c r="L6">
-        <v>1613</v>
+        <v>1712</v>
       </c>
       <c r="M6">
         <v>27</v>
       </c>
       <c r="N6">
-        <v>652</v>
+        <v>677</v>
       </c>
       <c r="O6">
-        <v>17848</v>
+        <v>20924</v>
       </c>
       <c r="P6">
-        <v>44466</v>
+        <v>50445</v>
       </c>
       <c r="Q6">
         <v>17918</v>
@@ -993,31 +994,31 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>28254</v>
+        <v>33275</v>
       </c>
       <c r="H7">
-        <v>10925</v>
+        <v>5939</v>
       </c>
       <c r="I7">
-        <v>284</v>
+        <v>249</v>
       </c>
       <c r="J7">
-        <v>4245</v>
+        <v>4282</v>
       </c>
       <c r="K7">
-        <v>3226</v>
+        <v>3423</v>
       </c>
       <c r="L7">
-        <v>1146</v>
+        <v>1287</v>
       </c>
       <c r="M7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N7">
-        <v>702</v>
+        <v>1030</v>
       </c>
       <c r="O7">
-        <v>22862</v>
+        <v>27635</v>
       </c>
       <c r="P7">
         <v>77581</v>
@@ -1052,34 +1053,34 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>23537</v>
+        <v>25410</v>
       </c>
       <c r="H8">
-        <v>17014</v>
+        <v>15141</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8">
-        <v>8983</v>
+        <v>9317</v>
       </c>
       <c r="K8">
-        <v>3915</v>
+        <v>5374</v>
       </c>
       <c r="L8">
-        <v>3327</v>
+        <v>3598</v>
       </c>
       <c r="M8">
         <v>16</v>
       </c>
       <c r="N8">
-        <v>183</v>
+        <v>215</v>
       </c>
       <c r="O8">
-        <v>10812</v>
+        <v>12780</v>
       </c>
       <c r="P8">
-        <v>21334</v>
+        <v>25650</v>
       </c>
       <c r="Q8">
         <v>20902</v>
@@ -1111,31 +1112,31 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>31661</v>
+        <v>32615</v>
       </c>
       <c r="H9">
-        <v>11197</v>
+        <v>10247</v>
       </c>
       <c r="I9">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="J9">
-        <v>5135</v>
+        <v>4486</v>
       </c>
       <c r="K9">
-        <v>3792</v>
+        <v>3274</v>
       </c>
       <c r="L9">
-        <v>561</v>
+        <v>1255</v>
       </c>
       <c r="M9">
         <v>7</v>
       </c>
       <c r="N9">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="O9">
-        <v>25676</v>
+        <v>26561</v>
       </c>
       <c r="P9">
         <v>50354</v>
@@ -1170,34 +1171,34 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>28175</v>
+        <v>29985</v>
       </c>
       <c r="H10">
-        <v>8331</v>
+        <v>6529</v>
       </c>
       <c r="I10">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="J10">
-        <v>7377</v>
+        <v>3656</v>
       </c>
       <c r="K10">
-        <v>5239</v>
+        <v>2375</v>
       </c>
       <c r="L10">
-        <v>1729</v>
+        <v>5843</v>
       </c>
       <c r="M10">
         <v>13</v>
       </c>
       <c r="N10">
-        <v>268</v>
+        <v>349</v>
       </c>
       <c r="O10">
-        <v>18979</v>
+        <v>20298</v>
       </c>
       <c r="P10">
-        <v>19376</v>
+        <v>37192</v>
       </c>
       <c r="Q10">
         <v>9516</v>
@@ -1229,34 +1230,34 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>36214</v>
+        <v>38500</v>
       </c>
       <c r="H11">
-        <v>12960</v>
+        <v>10755</v>
       </c>
       <c r="I11">
-        <v>756</v>
+        <v>738</v>
       </c>
       <c r="J11">
-        <v>5099</v>
+        <v>5020</v>
       </c>
       <c r="K11">
-        <v>2173</v>
+        <v>2268</v>
       </c>
       <c r="L11">
-        <v>532</v>
+        <v>967</v>
       </c>
       <c r="M11">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="N11">
-        <v>236</v>
+        <v>258</v>
       </c>
       <c r="O11">
-        <v>30298</v>
+        <v>32180</v>
       </c>
       <c r="P11">
-        <v>77667</v>
+        <v>84443</v>
       </c>
       <c r="Q11">
         <v>23805</v>
@@ -1288,19 +1289,19 @@
         <v>36</v>
       </c>
       <c r="G12">
-        <v>23582</v>
+        <v>27665</v>
       </c>
       <c r="H12">
-        <v>16681</v>
+        <v>12602</v>
       </c>
       <c r="I12">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="J12">
-        <v>8233</v>
+        <v>8473</v>
       </c>
       <c r="K12">
-        <v>5709</v>
+        <v>6100</v>
       </c>
       <c r="L12">
         <v>316</v>
@@ -1309,13 +1310,13 @@
         <v>2</v>
       </c>
       <c r="N12">
-        <v>341</v>
+        <v>369</v>
       </c>
       <c r="O12">
-        <v>14842</v>
+        <v>18657</v>
       </c>
       <c r="P12">
-        <v>49539</v>
+        <v>61097</v>
       </c>
       <c r="Q12">
         <v>17907</v>
@@ -1341,40 +1342,40 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>36896</v>
+        <v>36908</v>
       </c>
       <c r="F13">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="G13">
-        <v>24217</v>
+        <v>26005</v>
       </c>
       <c r="H13">
-        <v>11105</v>
+        <v>9566</v>
       </c>
       <c r="I13">
         <v>12</v>
       </c>
       <c r="J13">
-        <v>3541</v>
+        <v>3402</v>
       </c>
       <c r="K13">
-        <v>1854</v>
+        <v>1965</v>
       </c>
       <c r="L13">
-        <v>275</v>
+        <v>709</v>
       </c>
       <c r="M13">
         <v>0</v>
       </c>
       <c r="N13">
-        <v>1839</v>
+        <v>1944</v>
       </c>
       <c r="O13">
-        <v>18544</v>
+        <v>20027</v>
       </c>
       <c r="P13">
-        <v>54599</v>
+        <v>56590</v>
       </c>
       <c r="Q13">
         <v>16822</v>
@@ -1400,40 +1401,40 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>48964</v>
+        <v>48966</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>28778</v>
+        <v>30619</v>
       </c>
       <c r="H14">
-        <v>13680</v>
+        <v>12265</v>
       </c>
       <c r="I14">
-        <v>698</v>
+        <v>673</v>
       </c>
       <c r="J14">
-        <v>7971</v>
+        <v>8506</v>
       </c>
       <c r="K14">
-        <v>5016</v>
+        <v>5539</v>
       </c>
       <c r="L14">
-        <v>1519</v>
+        <v>1674</v>
       </c>
       <c r="M14">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="N14">
-        <v>400</v>
+        <v>484</v>
       </c>
       <c r="O14">
-        <v>19291</v>
+        <v>20328</v>
       </c>
       <c r="P14">
-        <v>44013</v>
+        <v>53792</v>
       </c>
       <c r="Q14">
         <v>20044</v>
@@ -1465,13 +1466,13 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>39104</v>
+        <v>40214</v>
       </c>
       <c r="H15">
-        <v>3540</v>
+        <v>2489</v>
       </c>
       <c r="I15">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="J15">
         <v>3</v>
@@ -1480,22 +1481,22 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>8446</v>
+        <v>8625</v>
       </c>
       <c r="M15">
         <v>0</v>
       </c>
       <c r="N15">
-        <v>1518</v>
+        <v>2018</v>
       </c>
       <c r="O15">
-        <v>36825</v>
+        <v>38070</v>
       </c>
       <c r="P15">
         <v>67178</v>
       </c>
       <c r="Q15">
-        <v>4952</v>
+        <v>4949</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -1518,37 +1519,37 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>25477</v>
+        <v>25533</v>
       </c>
       <c r="F16">
-        <v>72</v>
+        <v>16</v>
       </c>
       <c r="G16">
-        <v>19585</v>
+        <v>21709</v>
       </c>
       <c r="H16">
-        <v>4901</v>
+        <v>2773</v>
       </c>
       <c r="I16">
-        <v>245</v>
+        <v>138</v>
       </c>
       <c r="J16">
-        <v>20</v>
+        <v>320</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
       <c r="L16">
-        <v>11060</v>
+        <v>11674</v>
       </c>
       <c r="M16">
         <v>1</v>
       </c>
       <c r="N16">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="O16">
-        <v>12966</v>
+        <v>15309</v>
       </c>
       <c r="P16">
         <v>67240</v>
@@ -1583,31 +1584,31 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>26577</v>
+        <v>27452</v>
       </c>
       <c r="H17">
-        <v>972</v>
+        <v>103</v>
       </c>
       <c r="I17">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="J17">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K17">
         <v>0</v>
       </c>
       <c r="L17">
-        <v>8775</v>
+        <v>9112</v>
       </c>
       <c r="M17">
         <v>2</v>
       </c>
       <c r="N17">
-        <v>326</v>
+        <v>394</v>
       </c>
       <c r="O17">
-        <v>24312</v>
+        <v>25289</v>
       </c>
       <c r="P17">
         <v>65457</v>
@@ -1636,40 +1637,40 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>47783</v>
+        <v>47804</v>
       </c>
       <c r="F18">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="G18">
-        <v>45652</v>
+        <v>46427</v>
       </c>
       <c r="H18">
-        <v>1750</v>
+        <v>1047</v>
       </c>
       <c r="I18">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K18">
         <v>0</v>
       </c>
       <c r="L18">
-        <v>7267</v>
+        <v>7562</v>
       </c>
       <c r="M18">
         <v>3</v>
       </c>
       <c r="N18">
-        <v>1579</v>
+        <v>1645</v>
       </c>
       <c r="O18">
-        <v>41097</v>
+        <v>41926</v>
       </c>
       <c r="P18">
-        <v>69692</v>
+        <v>70738</v>
       </c>
       <c r="Q18">
         <v>6867</v>
@@ -1695,43 +1696,43 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>56364</v>
+        <v>56378</v>
       </c>
       <c r="F19">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="G19">
-        <v>50998</v>
+        <v>52768</v>
       </c>
       <c r="H19">
-        <v>5059</v>
+        <v>3373</v>
       </c>
       <c r="I19">
-        <v>430</v>
+        <v>349</v>
       </c>
       <c r="J19">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="K19">
         <v>0</v>
       </c>
       <c r="L19">
-        <v>13591</v>
+        <v>13983</v>
       </c>
       <c r="M19">
         <v>1</v>
       </c>
       <c r="N19">
-        <v>476</v>
+        <v>551</v>
       </c>
       <c r="O19">
-        <v>44245</v>
+        <v>46491</v>
       </c>
       <c r="P19">
         <v>105570</v>
       </c>
       <c r="Q19">
-        <v>6165</v>
+        <v>6158</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -1754,37 +1755,37 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>34994</v>
+        <v>35007</v>
       </c>
       <c r="F20">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="G20">
-        <v>33496</v>
+        <v>33930</v>
       </c>
       <c r="H20">
-        <v>1509</v>
+        <v>1075</v>
       </c>
       <c r="I20">
         <v>12</v>
       </c>
       <c r="J20">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K20">
         <v>0</v>
       </c>
       <c r="L20">
-        <v>5605</v>
+        <v>5737</v>
       </c>
       <c r="M20">
         <v>5</v>
       </c>
       <c r="N20">
-        <v>230</v>
+        <v>257</v>
       </c>
       <c r="O20">
-        <v>32520</v>
+        <v>32895</v>
       </c>
       <c r="P20">
         <v>75694</v>
@@ -1828,13 +1829,13 @@
         <v>0</v>
       </c>
       <c r="J21">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K21">
         <v>0</v>
       </c>
       <c r="L21">
-        <v>4018</v>
+        <v>4030</v>
       </c>
       <c r="M21">
         <v>3</v>
@@ -1878,16 +1879,16 @@
         <v>0</v>
       </c>
       <c r="G22">
-        <v>18186</v>
+        <v>18328</v>
       </c>
       <c r="H22">
-        <v>300</v>
+        <v>158</v>
       </c>
       <c r="I22">
         <v>0</v>
       </c>
       <c r="J22">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -1899,10 +1900,10 @@
         <v>0</v>
       </c>
       <c r="N22">
-        <v>180</v>
+        <v>214</v>
       </c>
       <c r="O22">
-        <v>17272</v>
+        <v>17367</v>
       </c>
       <c r="P22">
         <v>64099</v>
@@ -1937,22 +1938,22 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>12018</v>
+        <v>12020</v>
       </c>
       <c r="H23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I23">
         <v>0</v>
       </c>
       <c r="J23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K23">
         <v>0</v>
       </c>
       <c r="L23">
-        <v>2103</v>
+        <v>2105</v>
       </c>
       <c r="M23">
         <v>0</v>
@@ -1961,10 +1962,10 @@
         <v>108</v>
       </c>
       <c r="O23">
-        <v>11902</v>
+        <v>11904</v>
       </c>
       <c r="P23">
-        <v>57093</v>
+        <v>57094</v>
       </c>
       <c r="Q23">
         <v>3541</v>
@@ -1996,31 +1997,31 @@
         <v>0</v>
       </c>
       <c r="G24">
-        <v>13820</v>
+        <v>14056</v>
       </c>
       <c r="H24">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I24">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J24">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K24">
         <v>0</v>
       </c>
       <c r="L24">
-        <v>3425</v>
+        <v>3480</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N24">
-        <v>202</v>
+        <v>230</v>
       </c>
       <c r="O24">
-        <v>13534</v>
+        <v>13699</v>
       </c>
       <c r="P24">
         <v>65629</v>
@@ -2055,16 +2056,16 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>18928</v>
+        <v>19052</v>
       </c>
       <c r="H25">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="I25">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J25">
-        <v>34</v>
+        <v>161</v>
       </c>
       <c r="K25">
         <v>0</v>
@@ -2076,10 +2077,10 @@
         <v>0</v>
       </c>
       <c r="N25">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O25">
-        <v>18243</v>
+        <v>18251</v>
       </c>
       <c r="P25">
         <v>57533</v>
@@ -2114,31 +2115,31 @@
         <v>0</v>
       </c>
       <c r="G26">
-        <v>16873</v>
+        <v>17340</v>
       </c>
       <c r="H26">
-        <v>633</v>
+        <v>217</v>
       </c>
       <c r="I26">
         <v>0</v>
       </c>
       <c r="J26">
-        <v>40</v>
+        <v>210</v>
       </c>
       <c r="K26">
         <v>0</v>
       </c>
       <c r="L26">
-        <v>3310</v>
+        <v>3415</v>
       </c>
       <c r="M26">
         <v>3</v>
       </c>
       <c r="N26">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="O26">
-        <v>15821</v>
+        <v>16520</v>
       </c>
       <c r="P26">
         <v>66594</v>
@@ -2173,22 +2174,22 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>27129</v>
+        <v>31010</v>
       </c>
       <c r="H27">
-        <v>14854</v>
+        <v>11018</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27">
-        <v>192</v>
+        <v>578</v>
       </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="L27">
-        <v>5221</v>
+        <v>6079</v>
       </c>
       <c r="M27">
         <v>0</v>
@@ -2197,10 +2198,10 @@
         <v>56</v>
       </c>
       <c r="O27">
-        <v>25587</v>
+        <v>29659</v>
       </c>
       <c r="P27">
-        <v>40558</v>
+        <v>43496</v>
       </c>
       <c r="Q27">
         <v>12669</v>
@@ -2226,37 +2227,37 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>54240</v>
+        <v>54267</v>
       </c>
       <c r="F28">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="G28">
-        <v>25443</v>
+        <v>27648</v>
       </c>
       <c r="H28">
-        <v>24526</v>
+        <v>22333</v>
       </c>
       <c r="I28">
         <v>37</v>
       </c>
       <c r="J28">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="K28">
         <v>0</v>
       </c>
       <c r="L28">
-        <v>3549</v>
+        <v>3840</v>
       </c>
       <c r="M28">
         <v>11</v>
       </c>
       <c r="N28">
-        <v>349</v>
+        <v>474</v>
       </c>
       <c r="O28">
-        <v>21999</v>
+        <v>23853</v>
       </c>
       <c r="P28">
         <v>80639</v>
@@ -2291,31 +2292,31 @@
         <v>0</v>
       </c>
       <c r="G29">
-        <v>35478</v>
+        <v>38337</v>
       </c>
       <c r="H29">
-        <v>10820</v>
+        <v>7932</v>
       </c>
       <c r="I29">
-        <v>353</v>
+        <v>315</v>
       </c>
       <c r="J29">
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="K29">
         <v>0</v>
       </c>
       <c r="L29">
-        <v>5361</v>
+        <v>5797</v>
       </c>
       <c r="M29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N29">
-        <v>441</v>
+        <v>503</v>
       </c>
       <c r="O29">
-        <v>31262</v>
+        <v>33483</v>
       </c>
       <c r="P29">
         <v>83837</v>
@@ -2344,37 +2345,37 @@
         <v>0</v>
       </c>
       <c r="E30">
-        <v>52595</v>
+        <v>52630</v>
       </c>
       <c r="F30">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="G30">
-        <v>28012</v>
+        <v>31741</v>
       </c>
       <c r="H30">
-        <v>20183</v>
+        <v>15671</v>
       </c>
       <c r="I30">
-        <v>1239</v>
+        <v>2332</v>
       </c>
       <c r="J30">
-        <v>508</v>
+        <v>745</v>
       </c>
       <c r="K30">
         <v>0</v>
       </c>
       <c r="L30">
-        <v>2869</v>
+        <v>3475</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N30">
-        <v>140</v>
+        <v>227</v>
       </c>
       <c r="O30">
-        <v>25710</v>
+        <v>28760</v>
       </c>
       <c r="P30">
         <v>86935</v>
@@ -2409,22 +2410,22 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>86571</v>
+        <v>87005</v>
       </c>
       <c r="H31">
-        <v>1324</v>
+        <v>1199</v>
       </c>
       <c r="I31">
         <v>77</v>
       </c>
       <c r="J31">
-        <v>441</v>
+        <v>161</v>
       </c>
       <c r="K31">
         <v>0</v>
       </c>
       <c r="L31">
-        <v>40384</v>
+        <v>40824</v>
       </c>
       <c r="M31">
         <v>24</v>
@@ -2433,7 +2434,7 @@
         <v>1609</v>
       </c>
       <c r="O31">
-        <v>80828</v>
+        <v>81208</v>
       </c>
       <c r="P31">
         <v>81642</v>
@@ -2462,37 +2463,37 @@
         <v>0</v>
       </c>
       <c r="E32">
-        <v>46705</v>
+        <v>46707</v>
       </c>
       <c r="F32">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G32">
-        <v>24494</v>
+        <v>27430</v>
       </c>
       <c r="H32">
-        <v>17769</v>
+        <v>14928</v>
       </c>
       <c r="I32">
-        <v>680</v>
+        <v>581</v>
       </c>
       <c r="J32">
-        <v>551</v>
+        <v>437</v>
       </c>
       <c r="K32">
         <v>0</v>
       </c>
       <c r="L32">
-        <v>5185</v>
+        <v>5847</v>
       </c>
       <c r="M32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N32">
-        <v>216</v>
+        <v>338</v>
       </c>
       <c r="O32">
-        <v>20642</v>
+        <v>22883</v>
       </c>
       <c r="P32">
         <v>16303</v>
@@ -2521,40 +2522,40 @@
         <v>0</v>
       </c>
       <c r="E33">
-        <v>40149</v>
+        <v>40186</v>
       </c>
       <c r="F33">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="G33">
-        <v>21884</v>
+        <v>26699</v>
       </c>
       <c r="H33">
-        <v>14359</v>
+        <v>10271</v>
       </c>
       <c r="I33">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="J33">
-        <v>323</v>
+        <v>119</v>
       </c>
       <c r="K33">
         <v>0</v>
       </c>
       <c r="L33">
-        <v>2748</v>
+        <v>3164</v>
       </c>
       <c r="M33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N33">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O33">
-        <v>20551</v>
+        <v>25274</v>
       </c>
       <c r="P33">
-        <v>69510</v>
+        <v>73201</v>
       </c>
       <c r="Q33">
         <v>6678</v>
@@ -2580,28 +2581,28 @@
         <v>0</v>
       </c>
       <c r="E34">
-        <v>36368</v>
+        <v>36461</v>
       </c>
       <c r="F34">
-        <v>174</v>
+        <v>81</v>
       </c>
       <c r="G34">
-        <v>20218</v>
+        <v>24732</v>
       </c>
       <c r="H34">
-        <v>15887</v>
+        <v>11753</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
       <c r="J34">
-        <v>416</v>
+        <v>882</v>
       </c>
       <c r="K34">
         <v>0</v>
       </c>
       <c r="L34">
-        <v>7362</v>
+        <v>8003</v>
       </c>
       <c r="M34">
         <v>0</v>
@@ -2610,7 +2611,7 @@
         <v>0</v>
       </c>
       <c r="O34">
-        <v>17683</v>
+        <v>21282</v>
       </c>
       <c r="P34">
         <v>74626</v>
@@ -2639,40 +2640,40 @@
         <v>0</v>
       </c>
       <c r="E35">
-        <v>33304</v>
+        <v>33512</v>
       </c>
       <c r="F35">
-        <v>260</v>
+        <v>52</v>
       </c>
       <c r="G35">
-        <v>21377</v>
+        <v>24807</v>
       </c>
       <c r="H35">
-        <v>10590</v>
+        <v>7293</v>
       </c>
       <c r="I35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J35">
-        <v>293</v>
+        <v>428</v>
       </c>
       <c r="K35">
         <v>0</v>
       </c>
       <c r="L35">
-        <v>2138</v>
+        <v>3333</v>
       </c>
       <c r="M35">
         <v>0</v>
       </c>
       <c r="N35">
-        <v>36</v>
+        <v>145</v>
       </c>
       <c r="O35">
-        <v>18566</v>
+        <v>23045</v>
       </c>
       <c r="P35">
-        <v>68809</v>
+        <v>71712</v>
       </c>
       <c r="Q35">
         <v>8879</v>
@@ -2719,13 +2720,13 @@
         <v>0</v>
       </c>
       <c r="L36">
-        <v>7288</v>
+        <v>7294</v>
       </c>
       <c r="M36">
         <v>0</v>
       </c>
       <c r="N36">
-        <v>940</v>
+        <v>945</v>
       </c>
       <c r="O36">
         <v>12868</v>
@@ -2778,16 +2779,16 @@
         <v>0</v>
       </c>
       <c r="L37">
-        <v>2302</v>
+        <v>2307</v>
       </c>
       <c r="M37">
         <v>0</v>
       </c>
       <c r="N37">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="O37">
-        <v>17144</v>
+        <v>17150</v>
       </c>
       <c r="P37">
         <v>57832</v>
@@ -2831,13 +2832,13 @@
         <v>0</v>
       </c>
       <c r="J38">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K38">
         <v>0</v>
       </c>
       <c r="L38">
-        <v>4935</v>
+        <v>4949</v>
       </c>
       <c r="M38">
         <v>2</v>
@@ -2846,10 +2847,10 @@
         <v>493</v>
       </c>
       <c r="O38">
-        <v>24565</v>
+        <v>24573</v>
       </c>
       <c r="P38">
-        <v>61880</v>
+        <v>63038</v>
       </c>
       <c r="Q38">
         <v>5160</v>
@@ -2896,16 +2897,16 @@
         <v>0</v>
       </c>
       <c r="L39">
-        <v>4518</v>
+        <v>4526</v>
       </c>
       <c r="M39">
         <v>1</v>
       </c>
       <c r="N39">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O39">
-        <v>20111</v>
+        <v>20698</v>
       </c>
       <c r="P39">
         <v>71133</v>
@@ -2940,22 +2941,22 @@
         <v>0</v>
       </c>
       <c r="G40">
-        <v>15546</v>
+        <v>16506</v>
       </c>
       <c r="H40">
-        <v>254</v>
+        <v>225</v>
       </c>
       <c r="I40">
         <v>0</v>
       </c>
       <c r="J40">
-        <v>615</v>
+        <v>368</v>
       </c>
       <c r="K40">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="L40">
-        <v>786</v>
+        <v>1005</v>
       </c>
       <c r="M40">
         <v>0</v>
@@ -2964,7 +2965,7 @@
         <v>24</v>
       </c>
       <c r="O40">
-        <v>14366</v>
+        <v>15330</v>
       </c>
       <c r="P40">
         <v>73242</v>
@@ -2999,31 +3000,31 @@
         <v>0</v>
       </c>
       <c r="G41">
-        <v>21111</v>
+        <v>21807</v>
       </c>
       <c r="H41">
-        <v>709</v>
+        <v>294</v>
       </c>
       <c r="I41">
         <v>0</v>
       </c>
       <c r="J41">
-        <v>255</v>
+        <v>222</v>
       </c>
       <c r="K41">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L41">
-        <v>652</v>
+        <v>670</v>
       </c>
       <c r="M41">
         <v>0</v>
       </c>
       <c r="N41">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="O41">
-        <v>19940</v>
+        <v>20551</v>
       </c>
       <c r="P41">
         <v>85249</v>
@@ -3067,13 +3068,13 @@
         <v>0</v>
       </c>
       <c r="J42">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K42">
         <v>0</v>
       </c>
       <c r="L42">
-        <v>6188</v>
+        <v>6195</v>
       </c>
       <c r="M42">
         <v>0</v>
@@ -3082,10 +3083,10 @@
         <v>417</v>
       </c>
       <c r="O42">
-        <v>25756</v>
+        <v>26522</v>
       </c>
       <c r="P42">
-        <v>58915</v>
+        <v>64464</v>
       </c>
       <c r="Q42">
         <v>4713</v>
@@ -3132,7 +3133,7 @@
         <v>0</v>
       </c>
       <c r="L43">
-        <v>6720</v>
+        <v>6721</v>
       </c>
       <c r="M43">
         <v>1</v>
@@ -3141,10 +3142,10 @@
         <v>900</v>
       </c>
       <c r="O43">
-        <v>24728</v>
+        <v>25153</v>
       </c>
       <c r="P43">
-        <v>45739</v>
+        <v>59619</v>
       </c>
       <c r="Q43">
         <v>5271</v>
@@ -3176,31 +3177,31 @@
         <v>0</v>
       </c>
       <c r="G44">
-        <v>20510</v>
+        <v>20605</v>
       </c>
       <c r="H44">
-        <v>803</v>
+        <v>901</v>
       </c>
       <c r="I44">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J44">
-        <v>398</v>
+        <v>17</v>
       </c>
       <c r="K44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44">
-        <v>5585</v>
+        <v>6121</v>
       </c>
       <c r="M44">
         <v>8</v>
       </c>
       <c r="N44">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="O44">
-        <v>16069</v>
+        <v>16330</v>
       </c>
       <c r="P44">
         <v>68393</v>
@@ -3235,31 +3236,31 @@
         <v>0</v>
       </c>
       <c r="G45">
-        <v>15702</v>
+        <v>16475</v>
       </c>
       <c r="H45">
-        <v>2390</v>
+        <v>1747</v>
       </c>
       <c r="I45">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J45">
-        <v>260</v>
+        <v>388</v>
       </c>
       <c r="K45">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="L45">
-        <v>1561</v>
+        <v>1576</v>
       </c>
       <c r="M45">
         <v>10</v>
       </c>
       <c r="N45">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="O45">
-        <v>14031</v>
+        <v>14656</v>
       </c>
       <c r="P45">
         <v>76002</v>
@@ -3294,31 +3295,31 @@
         <v>0</v>
       </c>
       <c r="G46">
-        <v>20502</v>
+        <v>20772</v>
       </c>
       <c r="H46">
-        <v>1010</v>
+        <v>740</v>
       </c>
       <c r="I46">
         <v>0</v>
       </c>
       <c r="J46">
-        <v>280</v>
+        <v>412</v>
       </c>
       <c r="K46">
         <v>0</v>
       </c>
       <c r="L46">
-        <v>7310</v>
+        <v>7363</v>
       </c>
       <c r="M46">
         <v>1</v>
       </c>
       <c r="N46">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="O46">
-        <v>16147</v>
+        <v>17044</v>
       </c>
       <c r="P46">
         <v>64160</v>
@@ -3353,22 +3354,22 @@
         <v>0</v>
       </c>
       <c r="G47">
-        <v>20115</v>
+        <v>20891</v>
       </c>
       <c r="H47">
-        <v>1459</v>
+        <v>1143</v>
       </c>
       <c r="I47">
         <v>35</v>
       </c>
       <c r="J47">
-        <v>330</v>
+        <v>16</v>
       </c>
       <c r="K47">
         <v>0</v>
       </c>
       <c r="L47">
-        <v>1587</v>
+        <v>1913</v>
       </c>
       <c r="M47">
         <v>1</v>
@@ -3377,7 +3378,7 @@
         <v>86</v>
       </c>
       <c r="O47">
-        <v>18797</v>
+        <v>19585</v>
       </c>
       <c r="P47">
         <v>49875</v>
@@ -3412,31 +3413,31 @@
         <v>47</v>
       </c>
       <c r="G48">
-        <v>19520</v>
+        <v>19540</v>
       </c>
       <c r="H48">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="I48">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J48">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="K48">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L48">
-        <v>3685</v>
+        <v>3757</v>
       </c>
       <c r="M48">
         <v>4</v>
       </c>
       <c r="N48">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="O48">
-        <v>19166</v>
+        <v>19173</v>
       </c>
       <c r="P48">
         <v>54142</v>
@@ -3465,40 +3466,40 @@
         <v>0</v>
       </c>
       <c r="E49">
-        <v>21631</v>
+        <v>21632</v>
       </c>
       <c r="F49">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G49">
-        <v>18414</v>
+        <v>19051</v>
       </c>
       <c r="H49">
-        <v>1531</v>
+        <v>1028</v>
       </c>
       <c r="I49">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="J49">
-        <v>255</v>
+        <v>59</v>
       </c>
       <c r="K49">
         <v>0</v>
       </c>
       <c r="L49">
-        <v>2823</v>
+        <v>3069</v>
       </c>
       <c r="M49">
         <v>0</v>
       </c>
       <c r="N49">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="O49">
-        <v>16730</v>
+        <v>17313</v>
       </c>
       <c r="P49">
-        <v>49949</v>
+        <v>50563</v>
       </c>
       <c r="Q49">
         <v>5057</v>
@@ -3530,22 +3531,22 @@
         <v>0</v>
       </c>
       <c r="G50">
-        <v>20576</v>
+        <v>21055</v>
       </c>
       <c r="H50">
-        <v>1136</v>
+        <v>657</v>
       </c>
       <c r="I50">
         <v>0</v>
       </c>
       <c r="J50">
-        <v>30</v>
+        <v>213</v>
       </c>
       <c r="K50">
         <v>0</v>
       </c>
       <c r="L50">
-        <v>3371</v>
+        <v>3462</v>
       </c>
       <c r="M50">
         <v>5</v>
@@ -3554,7 +3555,7 @@
         <v>11</v>
       </c>
       <c r="O50">
-        <v>19876</v>
+        <v>20081</v>
       </c>
       <c r="P50">
         <v>63298</v>
@@ -3589,31 +3590,31 @@
         <v>0</v>
       </c>
       <c r="G51">
-        <v>22217</v>
+        <v>22367</v>
       </c>
       <c r="H51">
-        <v>875</v>
+        <v>768</v>
       </c>
       <c r="I51">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J51">
-        <v>133</v>
+        <v>60</v>
       </c>
       <c r="K51">
         <v>0</v>
       </c>
       <c r="L51">
-        <v>4191</v>
+        <v>4324</v>
       </c>
       <c r="M51">
         <v>11</v>
       </c>
       <c r="N51">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="O51">
-        <v>19190</v>
+        <v>19288</v>
       </c>
       <c r="P51">
         <v>71754</v>
@@ -3648,22 +3649,22 @@
         <v>0</v>
       </c>
       <c r="G52">
-        <v>20836</v>
+        <v>20860</v>
       </c>
       <c r="H52">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="I52">
         <v>0</v>
       </c>
       <c r="J52">
-        <v>346</v>
+        <v>314</v>
       </c>
       <c r="K52">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="L52">
-        <v>2350</v>
+        <v>2392</v>
       </c>
       <c r="M52">
         <v>1</v>
@@ -3672,7 +3673,7 @@
         <v>30</v>
       </c>
       <c r="O52">
-        <v>20270</v>
+        <v>20305</v>
       </c>
       <c r="P52">
         <v>63986</v>
@@ -3716,19 +3717,19 @@
         <v>0</v>
       </c>
       <c r="J53">
-        <v>511</v>
+        <v>335</v>
       </c>
       <c r="K53">
-        <v>175</v>
+        <v>103</v>
       </c>
       <c r="L53">
-        <v>2864</v>
+        <v>3030</v>
       </c>
       <c r="M53">
         <v>1</v>
       </c>
       <c r="N53">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O53">
         <v>18140</v>
@@ -3766,31 +3767,31 @@
         <v>0</v>
       </c>
       <c r="G54">
-        <v>20328</v>
+        <v>20349</v>
       </c>
       <c r="H54">
-        <v>349</v>
+        <v>328</v>
       </c>
       <c r="I54">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="J54">
-        <v>708</v>
+        <v>626</v>
       </c>
       <c r="K54">
-        <v>149</v>
+        <v>92</v>
       </c>
       <c r="L54">
-        <v>1624</v>
+        <v>1708</v>
       </c>
       <c r="M54">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N54">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="O54">
-        <v>17670</v>
+        <v>17772</v>
       </c>
       <c r="P54">
         <v>58440</v>
@@ -3825,19 +3826,19 @@
         <v>0</v>
       </c>
       <c r="G55">
-        <v>15963</v>
+        <v>15975</v>
       </c>
       <c r="H55">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="I55">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J55">
-        <v>524</v>
+        <v>576</v>
       </c>
       <c r="K55">
-        <v>108</v>
+        <v>268</v>
       </c>
       <c r="L55">
         <v>1482</v>
@@ -3846,7 +3847,7 @@
         <v>0</v>
       </c>
       <c r="N55">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="O55">
         <v>15232</v>
@@ -3884,31 +3885,31 @@
         <v>0</v>
       </c>
       <c r="G56">
-        <v>18684</v>
+        <v>18858</v>
       </c>
       <c r="H56">
-        <v>320</v>
+        <v>163</v>
       </c>
       <c r="I56">
         <v>0</v>
       </c>
       <c r="J56">
-        <v>1237</v>
+        <v>895</v>
       </c>
       <c r="K56">
-        <v>538</v>
+        <v>472</v>
       </c>
       <c r="L56">
-        <v>2442</v>
+        <v>2788</v>
       </c>
       <c r="M56">
         <v>2</v>
       </c>
       <c r="N56">
-        <v>354</v>
+        <v>371</v>
       </c>
       <c r="O56">
-        <v>14322</v>
+        <v>14464</v>
       </c>
       <c r="P56">
         <v>46365</v>
@@ -3943,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="G57">
-        <v>21107</v>
+        <v>21108</v>
       </c>
       <c r="H57">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -3955,7 +3956,7 @@
         <v>24</v>
       </c>
       <c r="K57">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="L57">
         <v>1746</v>
@@ -3967,7 +3968,7 @@
         <v>35</v>
       </c>
       <c r="O57">
-        <v>20852</v>
+        <v>20857</v>
       </c>
       <c r="P57">
         <v>61556</v>
@@ -4002,31 +4003,31 @@
         <v>0</v>
       </c>
       <c r="G58">
-        <v>21348</v>
+        <v>21690</v>
       </c>
       <c r="H58">
-        <v>1126</v>
+        <v>498</v>
       </c>
       <c r="I58">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="J58">
-        <v>1555</v>
+        <v>1659</v>
       </c>
       <c r="K58">
-        <v>378</v>
+        <v>417</v>
       </c>
       <c r="L58">
-        <v>5418</v>
+        <v>5571</v>
       </c>
       <c r="M58">
         <v>3</v>
       </c>
       <c r="N58">
-        <v>273</v>
+        <v>299</v>
       </c>
       <c r="O58">
-        <v>15235</v>
+        <v>15367</v>
       </c>
       <c r="P58">
         <v>57577</v>
@@ -4061,13 +4062,13 @@
         <v>0</v>
       </c>
       <c r="G59">
-        <v>18775</v>
+        <v>18776</v>
       </c>
       <c r="H59">
         <v>0</v>
       </c>
       <c r="I59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J59">
         <v>0</v>
@@ -4082,7 +4083,7 @@
         <v>2</v>
       </c>
       <c r="N59">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O59">
         <v>15993</v>
@@ -4120,31 +4121,31 @@
         <v>0</v>
       </c>
       <c r="G60">
-        <v>22954</v>
+        <v>23283</v>
       </c>
       <c r="H60">
-        <v>384</v>
+        <v>224</v>
       </c>
       <c r="I60">
         <v>0</v>
       </c>
       <c r="J60">
-        <v>543</v>
+        <v>371</v>
       </c>
       <c r="K60">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="L60">
-        <v>4903</v>
+        <v>5180</v>
       </c>
       <c r="M60">
         <v>0</v>
       </c>
       <c r="N60">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="O60">
-        <v>21183</v>
+        <v>21383</v>
       </c>
       <c r="P60">
         <v>70140</v>
@@ -4188,22 +4189,22 @@
         <v>0</v>
       </c>
       <c r="J61">
-        <v>439</v>
+        <v>117</v>
       </c>
       <c r="K61">
-        <v>265</v>
+        <v>73</v>
       </c>
       <c r="L61">
-        <v>9558</v>
+        <v>9858</v>
       </c>
       <c r="M61">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="N61">
         <v>1</v>
       </c>
       <c r="O61">
-        <v>13948</v>
+        <v>13959</v>
       </c>
       <c r="P61">
         <v>55240</v>
@@ -4238,31 +4239,31 @@
         <v>0</v>
       </c>
       <c r="G62">
-        <v>15328</v>
+        <v>15669</v>
       </c>
       <c r="H62">
-        <v>350</v>
+        <v>105</v>
       </c>
       <c r="I62">
-        <v>122</v>
+        <v>26</v>
       </c>
       <c r="J62">
-        <v>614</v>
+        <v>655</v>
       </c>
       <c r="K62">
-        <v>251</v>
+        <v>274</v>
       </c>
       <c r="L62">
-        <v>3468</v>
+        <v>3513</v>
       </c>
       <c r="M62">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="N62">
-        <v>351</v>
+        <v>399</v>
       </c>
       <c r="O62">
-        <v>14315</v>
+        <v>14563</v>
       </c>
       <c r="P62">
         <v>51334</v>
@@ -4297,16 +4298,16 @@
         <v>0</v>
       </c>
       <c r="G63">
-        <v>36585</v>
+        <v>36633</v>
       </c>
       <c r="H63">
         <v>26</v>
       </c>
       <c r="I63">
-        <v>143</v>
+        <v>95</v>
       </c>
       <c r="J63">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="K63">
         <v>0</v>
@@ -4318,10 +4319,10 @@
         <v>35</v>
       </c>
       <c r="N63">
-        <v>835</v>
+        <v>865</v>
       </c>
       <c r="O63">
-        <v>31722</v>
+        <v>31744</v>
       </c>
       <c r="P63">
         <v>68691</v>
@@ -4356,31 +4357,31 @@
         <v>0</v>
       </c>
       <c r="G64">
-        <v>39581</v>
+        <v>40286</v>
       </c>
       <c r="H64">
-        <v>1984</v>
+        <v>1493</v>
       </c>
       <c r="I64">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J64">
-        <v>92</v>
+        <v>155</v>
       </c>
       <c r="K64">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L64">
-        <v>9076</v>
+        <v>9179</v>
       </c>
       <c r="M64">
         <v>8</v>
       </c>
       <c r="N64">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="O64">
-        <v>36066</v>
+        <v>37144</v>
       </c>
       <c r="P64">
         <v>60527</v>
@@ -4415,31 +4416,31 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>34567</v>
+        <v>36131</v>
       </c>
       <c r="H65">
-        <v>5163</v>
+        <v>3686</v>
       </c>
       <c r="I65">
-        <v>1060</v>
+        <v>1123</v>
       </c>
       <c r="J65">
-        <v>134</v>
+        <v>55</v>
       </c>
       <c r="K65">
         <v>0</v>
       </c>
       <c r="L65">
-        <v>10211</v>
+        <v>11038</v>
       </c>
       <c r="M65">
         <v>2</v>
       </c>
       <c r="N65">
-        <v>525</v>
+        <v>567</v>
       </c>
       <c r="O65">
-        <v>24791</v>
+        <v>25933</v>
       </c>
       <c r="P65">
         <v>34607</v>
@@ -4474,37 +4475,37 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>51344</v>
+        <v>54650</v>
       </c>
       <c r="H66">
-        <v>10736</v>
+        <v>7404</v>
       </c>
       <c r="I66">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="J66">
-        <v>132</v>
+        <v>169</v>
       </c>
       <c r="K66">
         <v>0</v>
       </c>
       <c r="L66">
-        <v>10081</v>
+        <v>10603</v>
       </c>
       <c r="M66">
         <v>2</v>
       </c>
       <c r="N66">
-        <v>957</v>
+        <v>1378</v>
       </c>
       <c r="O66">
-        <v>43151</v>
+        <v>48604</v>
       </c>
       <c r="P66">
         <v>93810</v>
       </c>
       <c r="Q66">
-        <v>17744</v>
+        <v>17742</v>
       </c>
       <c r="R66">
         <v>0</v>
@@ -4533,31 +4534,31 @@
         <v>0</v>
       </c>
       <c r="G67">
-        <v>62084</v>
+        <v>62962</v>
       </c>
       <c r="H67">
-        <v>1153</v>
+        <v>14</v>
       </c>
       <c r="I67">
-        <v>2696</v>
+        <v>2739</v>
       </c>
       <c r="J67">
-        <v>167</v>
+        <v>131</v>
       </c>
       <c r="K67">
         <v>0</v>
       </c>
       <c r="L67">
-        <v>17555</v>
+        <v>17770</v>
       </c>
       <c r="M67">
         <v>10</v>
       </c>
       <c r="N67">
-        <v>1085</v>
+        <v>1237</v>
       </c>
       <c r="O67">
-        <v>48822</v>
+        <v>50786</v>
       </c>
       <c r="P67">
         <v>78022</v>
@@ -4592,16 +4593,16 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>59397</v>
+        <v>60251</v>
       </c>
       <c r="H68">
-        <v>4894</v>
+        <v>4055</v>
       </c>
       <c r="I68">
-        <v>869</v>
+        <v>854</v>
       </c>
       <c r="J68">
-        <v>202</v>
+        <v>676</v>
       </c>
       <c r="K68">
         <v>0</v>
@@ -4613,13 +4614,13 @@
         <v>2</v>
       </c>
       <c r="N68">
-        <v>335</v>
+        <v>385</v>
       </c>
       <c r="O68">
-        <v>49616</v>
+        <v>49980</v>
       </c>
       <c r="P68">
-        <v>61338</v>
+        <v>61342</v>
       </c>
       <c r="Q68">
         <v>7850</v>
@@ -4651,34 +4652,34 @@
         <v>0</v>
       </c>
       <c r="G69">
-        <v>36833</v>
+        <v>37481</v>
       </c>
       <c r="H69">
-        <v>6038</v>
+        <v>5726</v>
       </c>
       <c r="I69">
-        <v>376</v>
+        <v>471</v>
       </c>
       <c r="J69">
-        <v>339</v>
+        <v>781</v>
       </c>
       <c r="K69">
         <v>0</v>
       </c>
       <c r="L69">
-        <v>13833</v>
+        <v>13850</v>
       </c>
       <c r="M69">
         <v>2</v>
       </c>
       <c r="N69">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="O69">
-        <v>27549</v>
+        <v>33105</v>
       </c>
       <c r="P69">
-        <v>34089</v>
+        <v>34092</v>
       </c>
       <c r="Q69">
         <v>6528</v>
@@ -4710,16 +4711,16 @@
         <v>0</v>
       </c>
       <c r="G70">
-        <v>43233</v>
+        <v>43853</v>
       </c>
       <c r="H70">
-        <v>1388</v>
+        <v>1199</v>
       </c>
       <c r="I70">
-        <v>2339</v>
+        <v>2332</v>
       </c>
       <c r="J70">
-        <v>33</v>
+        <v>347</v>
       </c>
       <c r="K70">
         <v>0</v>
@@ -4731,10 +4732,10 @@
         <v>2</v>
       </c>
       <c r="N70">
-        <v>556</v>
+        <v>728</v>
       </c>
       <c r="O70">
-        <v>35345</v>
+        <v>38912</v>
       </c>
       <c r="P70">
         <v>42040</v>
@@ -4769,16 +4770,16 @@
         <v>0</v>
       </c>
       <c r="G71">
-        <v>45446</v>
+        <v>46068</v>
       </c>
       <c r="H71">
-        <v>3980</v>
+        <v>3465</v>
       </c>
       <c r="I71">
-        <v>1421</v>
+        <v>1314</v>
       </c>
       <c r="J71">
-        <v>114</v>
+        <v>551</v>
       </c>
       <c r="K71">
         <v>0</v>
@@ -4790,10 +4791,10 @@
         <v>1</v>
       </c>
       <c r="N71">
-        <v>2684</v>
+        <v>2828</v>
       </c>
       <c r="O71">
-        <v>31293</v>
+        <v>34035</v>
       </c>
       <c r="P71">
         <v>48896</v>
@@ -4822,22 +4823,22 @@
         <v>0</v>
       </c>
       <c r="E72">
-        <v>61542</v>
+        <v>61543</v>
       </c>
       <c r="F72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G72">
-        <v>52673</v>
+        <v>53966</v>
       </c>
       <c r="H72">
-        <v>6930</v>
+        <v>5900</v>
       </c>
       <c r="I72">
-        <v>1704</v>
+        <v>1514</v>
       </c>
       <c r="J72">
-        <v>246</v>
+        <v>519</v>
       </c>
       <c r="K72">
         <v>0</v>
@@ -4849,10 +4850,10 @@
         <v>9</v>
       </c>
       <c r="N72">
-        <v>394</v>
+        <v>546</v>
       </c>
       <c r="O72">
-        <v>41398</v>
+        <v>43218</v>
       </c>
       <c r="P72">
         <v>85505</v>
@@ -4887,16 +4888,16 @@
         <v>0</v>
       </c>
       <c r="G73">
-        <v>46625</v>
+        <v>48261</v>
       </c>
       <c r="H73">
-        <v>11684</v>
+        <v>10271</v>
       </c>
       <c r="I73">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="J73">
-        <v>472</v>
+        <v>1058</v>
       </c>
       <c r="K73">
         <v>0</v>
@@ -4908,10 +4909,10 @@
         <v>5</v>
       </c>
       <c r="N73">
-        <v>507</v>
+        <v>591</v>
       </c>
       <c r="O73">
-        <v>40900</v>
+        <v>42673</v>
       </c>
       <c r="P73">
         <v>67550</v>
@@ -4938,43 +4939,43 @@
         <v>0</v>
       </c>
       <c r="E74">
-        <v>2429160</v>
+        <v>2429682</v>
       </c>
       <c r="F74">
-        <v>1222</v>
+        <v>700</v>
       </c>
       <c r="G74">
-        <v>1983893</v>
+        <v>2073982</v>
       </c>
       <c r="H74">
-        <v>359454</v>
+        <v>278061</v>
       </c>
       <c r="I74">
-        <v>17684</v>
+        <v>17926</v>
       </c>
       <c r="J74">
-        <v>76391</v>
+        <v>75429</v>
       </c>
       <c r="K74">
-        <v>38833</v>
+        <v>38294</v>
       </c>
       <c r="L74">
-        <v>421009</v>
+        <v>440850</v>
       </c>
       <c r="M74">
-        <v>391</v>
+        <v>486</v>
       </c>
       <c r="N74">
-        <v>28064</v>
+        <v>31653</v>
       </c>
       <c r="O74">
-        <v>1682675</v>
+        <v>1783113</v>
       </c>
       <c r="P74">
-        <v>4302032</v>
+        <v>4392034</v>
       </c>
       <c r="Q74">
-        <v>629579</v>
+        <v>629567</v>
       </c>
       <c r="R74">
         <v>1</v>

--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\FormProcess\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF7B09EA-A705-4FEB-89BB-1C13ACE3B583}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0F88578-0968-413B-A313-EBB5325058A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -304,7 +304,7 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Notice &amp; Hearing Report Last Updated On : 27-08-2026 07:57:21</t>
+    <t>Notice &amp; Hearing Report Last Updated On : 27-08-2026 12:00:13</t>
   </si>
 </sst>
 </file>
@@ -817,31 +817,31 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>36073</v>
+        <v>36716</v>
       </c>
       <c r="H4">
-        <v>13086</v>
+        <v>12620</v>
       </c>
       <c r="I4">
         <v>9</v>
       </c>
       <c r="J4">
-        <v>5876</v>
+        <v>5975</v>
       </c>
       <c r="K4">
         <v>2949</v>
       </c>
       <c r="L4">
-        <v>3432</v>
+        <v>3485</v>
       </c>
       <c r="M4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N4">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="O4">
-        <v>27819</v>
+        <v>28334</v>
       </c>
       <c r="P4">
         <v>53812</v>
@@ -876,22 +876,22 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>45813</v>
+        <v>46037</v>
       </c>
       <c r="H5">
-        <v>6003</v>
+        <v>5909</v>
       </c>
       <c r="I5">
         <v>7</v>
       </c>
       <c r="J5">
-        <v>3701</v>
+        <v>3667</v>
       </c>
       <c r="K5">
-        <v>2102</v>
+        <v>2074</v>
       </c>
       <c r="L5">
-        <v>3332</v>
+        <v>3384</v>
       </c>
       <c r="M5">
         <v>40</v>
@@ -900,7 +900,7 @@
         <v>332</v>
       </c>
       <c r="O5">
-        <v>41473</v>
+        <v>41682</v>
       </c>
       <c r="P5">
         <v>55484</v>
@@ -935,22 +935,22 @@
         <v>2</v>
       </c>
       <c r="G6">
-        <v>24637</v>
+        <v>24834</v>
       </c>
       <c r="H6">
-        <v>9897</v>
+        <v>9775</v>
       </c>
       <c r="I6">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="J6">
-        <v>1884</v>
+        <v>1753</v>
       </c>
       <c r="K6">
         <v>1096</v>
       </c>
       <c r="L6">
-        <v>1712</v>
+        <v>1832</v>
       </c>
       <c r="M6">
         <v>27</v>
@@ -959,10 +959,10 @@
         <v>677</v>
       </c>
       <c r="O6">
-        <v>20924</v>
+        <v>21120</v>
       </c>
       <c r="P6">
-        <v>50445</v>
+        <v>52459</v>
       </c>
       <c r="Q6">
         <v>17918</v>
@@ -994,31 +994,31 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>33275</v>
+        <v>33990</v>
       </c>
       <c r="H7">
-        <v>5939</v>
+        <v>5225</v>
       </c>
       <c r="I7">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J7">
-        <v>4282</v>
+        <v>4249</v>
       </c>
       <c r="K7">
-        <v>3423</v>
+        <v>3365</v>
       </c>
       <c r="L7">
-        <v>1287</v>
+        <v>1329</v>
       </c>
       <c r="M7">
         <v>29</v>
       </c>
       <c r="N7">
-        <v>1030</v>
+        <v>1061</v>
       </c>
       <c r="O7">
-        <v>27635</v>
+        <v>28296</v>
       </c>
       <c r="P7">
         <v>77581</v>
@@ -1053,34 +1053,34 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>25410</v>
+        <v>25898</v>
       </c>
       <c r="H8">
-        <v>15141</v>
+        <v>14653</v>
       </c>
       <c r="I8">
         <v>1</v>
       </c>
       <c r="J8">
-        <v>9317</v>
+        <v>9280</v>
       </c>
       <c r="K8">
-        <v>5374</v>
+        <v>5373</v>
       </c>
       <c r="L8">
-        <v>3598</v>
+        <v>3752</v>
       </c>
       <c r="M8">
         <v>16</v>
       </c>
       <c r="N8">
-        <v>215</v>
+        <v>252</v>
       </c>
       <c r="O8">
-        <v>12780</v>
+        <v>13439</v>
       </c>
       <c r="P8">
-        <v>25650</v>
+        <v>26226</v>
       </c>
       <c r="Q8">
         <v>20902</v>
@@ -1112,34 +1112,34 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>32615</v>
+        <v>32889</v>
       </c>
       <c r="H9">
-        <v>10247</v>
+        <v>9976</v>
       </c>
       <c r="I9">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="J9">
-        <v>4486</v>
+        <v>4257</v>
       </c>
       <c r="K9">
-        <v>3274</v>
+        <v>3055</v>
       </c>
       <c r="L9">
-        <v>1255</v>
+        <v>1495</v>
       </c>
       <c r="M9">
         <v>7</v>
       </c>
       <c r="N9">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="O9">
-        <v>26561</v>
+        <v>27085</v>
       </c>
       <c r="P9">
-        <v>50354</v>
+        <v>53534</v>
       </c>
       <c r="Q9">
         <v>18214</v>
@@ -1171,22 +1171,22 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>29985</v>
+        <v>30450</v>
       </c>
       <c r="H10">
-        <v>6529</v>
+        <v>6065</v>
       </c>
       <c r="I10">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J10">
-        <v>3656</v>
+        <v>3731</v>
       </c>
       <c r="K10">
         <v>2375</v>
       </c>
       <c r="L10">
-        <v>5843</v>
+        <v>5870</v>
       </c>
       <c r="M10">
         <v>13</v>
@@ -1195,10 +1195,10 @@
         <v>349</v>
       </c>
       <c r="O10">
-        <v>20298</v>
+        <v>21006</v>
       </c>
       <c r="P10">
-        <v>37192</v>
+        <v>37227</v>
       </c>
       <c r="Q10">
         <v>9516</v>
@@ -1230,31 +1230,31 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>38500</v>
+        <v>39123</v>
       </c>
       <c r="H11">
-        <v>10755</v>
+        <v>10111</v>
       </c>
       <c r="I11">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="J11">
-        <v>5020</v>
+        <v>5036</v>
       </c>
       <c r="K11">
-        <v>2268</v>
+        <v>2243</v>
       </c>
       <c r="L11">
-        <v>967</v>
+        <v>1152</v>
       </c>
       <c r="M11">
         <v>20</v>
       </c>
       <c r="N11">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O11">
-        <v>32180</v>
+        <v>32600</v>
       </c>
       <c r="P11">
         <v>84443</v>
@@ -1283,28 +1283,28 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>40703</v>
+        <v>40716</v>
       </c>
       <c r="F12">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="G12">
-        <v>27665</v>
+        <v>28498</v>
       </c>
       <c r="H12">
-        <v>12602</v>
+        <v>11771</v>
       </c>
       <c r="I12">
         <v>237</v>
       </c>
       <c r="J12">
-        <v>8473</v>
+        <v>8440</v>
       </c>
       <c r="K12">
-        <v>6100</v>
+        <v>6085</v>
       </c>
       <c r="L12">
-        <v>316</v>
+        <v>348</v>
       </c>
       <c r="M12">
         <v>2</v>
@@ -1313,10 +1313,10 @@
         <v>369</v>
       </c>
       <c r="O12">
-        <v>18657</v>
+        <v>19475</v>
       </c>
       <c r="P12">
-        <v>61097</v>
+        <v>61589</v>
       </c>
       <c r="Q12">
         <v>17907</v>
@@ -1348,31 +1348,31 @@
         <v>123</v>
       </c>
       <c r="G13">
-        <v>26005</v>
+        <v>26304</v>
       </c>
       <c r="H13">
-        <v>9566</v>
+        <v>9300</v>
       </c>
       <c r="I13">
         <v>12</v>
       </c>
       <c r="J13">
-        <v>3402</v>
+        <v>3433</v>
       </c>
       <c r="K13">
         <v>1965</v>
       </c>
       <c r="L13">
-        <v>709</v>
+        <v>717</v>
       </c>
       <c r="M13">
         <v>0</v>
       </c>
       <c r="N13">
-        <v>1944</v>
+        <v>1955</v>
       </c>
       <c r="O13">
-        <v>20027</v>
+        <v>20264</v>
       </c>
       <c r="P13">
         <v>56590</v>
@@ -1407,31 +1407,31 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>30619</v>
+        <v>31348</v>
       </c>
       <c r="H14">
-        <v>12265</v>
+        <v>11704</v>
       </c>
       <c r="I14">
-        <v>673</v>
+        <v>621</v>
       </c>
       <c r="J14">
-        <v>8506</v>
+        <v>8551</v>
       </c>
       <c r="K14">
-        <v>5539</v>
+        <v>5447</v>
       </c>
       <c r="L14">
-        <v>1674</v>
+        <v>1772</v>
       </c>
       <c r="M14">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N14">
-        <v>484</v>
+        <v>599</v>
       </c>
       <c r="O14">
-        <v>20328</v>
+        <v>20797</v>
       </c>
       <c r="P14">
         <v>53792</v>
@@ -1466,31 +1466,31 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>40214</v>
+        <v>40673</v>
       </c>
       <c r="H15">
-        <v>2489</v>
+        <v>2030</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>3</v>
+        <v>94</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15">
-        <v>8625</v>
+        <v>8633</v>
       </c>
       <c r="M15">
         <v>0</v>
       </c>
       <c r="N15">
-        <v>2018</v>
+        <v>2192</v>
       </c>
       <c r="O15">
-        <v>38070</v>
+        <v>38269</v>
       </c>
       <c r="P15">
         <v>67178</v>
@@ -1519,40 +1519,40 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>25533</v>
+        <v>25536</v>
       </c>
       <c r="F16">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G16">
-        <v>21709</v>
+        <v>21947</v>
       </c>
       <c r="H16">
-        <v>2773</v>
+        <v>2607</v>
       </c>
       <c r="I16">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J16">
-        <v>320</v>
+        <v>101</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
       <c r="L16">
-        <v>11674</v>
+        <v>12005</v>
       </c>
       <c r="M16">
         <v>1</v>
       </c>
       <c r="N16">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="O16">
-        <v>15309</v>
+        <v>17017</v>
       </c>
       <c r="P16">
-        <v>67240</v>
+        <v>67761</v>
       </c>
       <c r="Q16">
         <v>5208</v>
@@ -1584,34 +1584,34 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>27452</v>
+        <v>27548</v>
       </c>
       <c r="H17">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="I17">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="J17">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="K17">
         <v>0</v>
       </c>
       <c r="L17">
-        <v>9112</v>
+        <v>9140</v>
       </c>
       <c r="M17">
         <v>2</v>
       </c>
       <c r="N17">
-        <v>394</v>
+        <v>415</v>
       </c>
       <c r="O17">
-        <v>25289</v>
+        <v>26362</v>
       </c>
       <c r="P17">
-        <v>65457</v>
+        <v>65458</v>
       </c>
       <c r="Q17">
         <v>5441</v>
@@ -1637,37 +1637,37 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>47804</v>
+        <v>47807</v>
       </c>
       <c r="F18">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G18">
-        <v>46427</v>
+        <v>46600</v>
       </c>
       <c r="H18">
-        <v>1047</v>
+        <v>971</v>
       </c>
       <c r="I18">
-        <v>310</v>
+        <v>224</v>
       </c>
       <c r="J18">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="K18">
         <v>0</v>
       </c>
       <c r="L18">
-        <v>7562</v>
+        <v>7582</v>
       </c>
       <c r="M18">
         <v>3</v>
       </c>
       <c r="N18">
-        <v>1645</v>
+        <v>1703</v>
       </c>
       <c r="O18">
-        <v>41926</v>
+        <v>42413</v>
       </c>
       <c r="P18">
         <v>70738</v>
@@ -1696,40 +1696,40 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>56378</v>
+        <v>56383</v>
       </c>
       <c r="F19">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="G19">
-        <v>52768</v>
+        <v>53251</v>
       </c>
       <c r="H19">
-        <v>3373</v>
+        <v>2956</v>
       </c>
       <c r="I19">
-        <v>349</v>
+        <v>283</v>
       </c>
       <c r="J19">
-        <v>120</v>
+        <v>61</v>
       </c>
       <c r="K19">
         <v>0</v>
       </c>
       <c r="L19">
-        <v>13983</v>
+        <v>14142</v>
       </c>
       <c r="M19">
         <v>1</v>
       </c>
       <c r="N19">
-        <v>551</v>
+        <v>566</v>
       </c>
       <c r="O19">
-        <v>46491</v>
+        <v>47252</v>
       </c>
       <c r="P19">
-        <v>105570</v>
+        <v>106226</v>
       </c>
       <c r="Q19">
         <v>6158</v>
@@ -1755,40 +1755,40 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>35007</v>
+        <v>35010</v>
       </c>
       <c r="F20">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G20">
-        <v>33930</v>
+        <v>34066</v>
       </c>
       <c r="H20">
-        <v>1075</v>
+        <v>939</v>
       </c>
       <c r="I20">
         <v>12</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K20">
         <v>0</v>
       </c>
       <c r="L20">
-        <v>5737</v>
+        <v>5765</v>
       </c>
       <c r="M20">
         <v>5</v>
       </c>
       <c r="N20">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="O20">
-        <v>32895</v>
+        <v>32987</v>
       </c>
       <c r="P20">
-        <v>75694</v>
+        <v>75719</v>
       </c>
       <c r="Q20">
         <v>9014</v>
@@ -1844,7 +1844,7 @@
         <v>171</v>
       </c>
       <c r="O21">
-        <v>16779</v>
+        <v>16791</v>
       </c>
       <c r="P21">
         <v>62460</v>
@@ -1879,31 +1879,31 @@
         <v>0</v>
       </c>
       <c r="G22">
-        <v>18328</v>
+        <v>18628</v>
       </c>
       <c r="H22">
-        <v>158</v>
+        <v>40</v>
       </c>
       <c r="I22">
         <v>0</v>
       </c>
       <c r="J22">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="K22">
         <v>0</v>
       </c>
       <c r="L22">
-        <v>7342</v>
+        <v>7465</v>
       </c>
       <c r="M22">
         <v>0</v>
       </c>
       <c r="N22">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="O22">
-        <v>17367</v>
+        <v>17553</v>
       </c>
       <c r="P22">
         <v>64099</v>
@@ -1947,13 +1947,13 @@
         <v>0</v>
       </c>
       <c r="J23">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K23">
         <v>0</v>
       </c>
       <c r="L23">
-        <v>2105</v>
+        <v>2113</v>
       </c>
       <c r="M23">
         <v>0</v>
@@ -1962,7 +1962,7 @@
         <v>108</v>
       </c>
       <c r="O23">
-        <v>11904</v>
+        <v>11912</v>
       </c>
       <c r="P23">
         <v>57094</v>
@@ -2018,10 +2018,10 @@
         <v>5</v>
       </c>
       <c r="N24">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O24">
-        <v>13699</v>
+        <v>13818</v>
       </c>
       <c r="P24">
         <v>65629</v>
@@ -2056,31 +2056,31 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>19052</v>
+        <v>19194</v>
       </c>
       <c r="H25">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="I25">
         <v>1</v>
       </c>
       <c r="J25">
-        <v>161</v>
+        <v>222</v>
       </c>
       <c r="K25">
         <v>0</v>
       </c>
       <c r="L25">
-        <v>4569</v>
+        <v>4579</v>
       </c>
       <c r="M25">
         <v>0</v>
       </c>
       <c r="N25">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="O25">
-        <v>18251</v>
+        <v>18306</v>
       </c>
       <c r="P25">
         <v>57533</v>
@@ -2115,31 +2115,31 @@
         <v>0</v>
       </c>
       <c r="G26">
-        <v>17340</v>
+        <v>17360</v>
       </c>
       <c r="H26">
-        <v>217</v>
+        <v>197</v>
       </c>
       <c r="I26">
         <v>0</v>
       </c>
       <c r="J26">
-        <v>210</v>
+        <v>138</v>
       </c>
       <c r="K26">
         <v>0</v>
       </c>
       <c r="L26">
-        <v>3415</v>
+        <v>3525</v>
       </c>
       <c r="M26">
         <v>3</v>
       </c>
       <c r="N26">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O26">
-        <v>16520</v>
+        <v>16547</v>
       </c>
       <c r="P26">
         <v>66594</v>
@@ -2174,22 +2174,22 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>31010</v>
+        <v>31564</v>
       </c>
       <c r="H27">
-        <v>11018</v>
+        <v>10464</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27">
-        <v>578</v>
+        <v>399</v>
       </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="L27">
-        <v>6079</v>
+        <v>6402</v>
       </c>
       <c r="M27">
         <v>0</v>
@@ -2198,10 +2198,10 @@
         <v>56</v>
       </c>
       <c r="O27">
-        <v>29659</v>
+        <v>30366</v>
       </c>
       <c r="P27">
-        <v>43496</v>
+        <v>44406</v>
       </c>
       <c r="Q27">
         <v>12669</v>
@@ -2227,37 +2227,37 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>54267</v>
+        <v>54270</v>
       </c>
       <c r="F28">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G28">
-        <v>27648</v>
+        <v>27963</v>
       </c>
       <c r="H28">
-        <v>22333</v>
+        <v>22029</v>
       </c>
       <c r="I28">
         <v>37</v>
       </c>
       <c r="J28">
-        <v>275</v>
+        <v>192</v>
       </c>
       <c r="K28">
         <v>0</v>
       </c>
       <c r="L28">
-        <v>3840</v>
+        <v>3917</v>
       </c>
       <c r="M28">
         <v>11</v>
       </c>
       <c r="N28">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="O28">
-        <v>23853</v>
+        <v>24133</v>
       </c>
       <c r="P28">
         <v>80639</v>
@@ -2292,31 +2292,31 @@
         <v>0</v>
       </c>
       <c r="G29">
-        <v>38337</v>
+        <v>39142</v>
       </c>
       <c r="H29">
-        <v>7932</v>
+        <v>7182</v>
       </c>
       <c r="I29">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="J29">
-        <v>506</v>
+        <v>623</v>
       </c>
       <c r="K29">
         <v>0</v>
       </c>
       <c r="L29">
-        <v>5797</v>
+        <v>5924</v>
       </c>
       <c r="M29">
         <v>3</v>
       </c>
       <c r="N29">
-        <v>503</v>
+        <v>517</v>
       </c>
       <c r="O29">
-        <v>33483</v>
+        <v>34133</v>
       </c>
       <c r="P29">
         <v>83837</v>
@@ -2345,37 +2345,37 @@
         <v>0</v>
       </c>
       <c r="E30">
-        <v>52630</v>
+        <v>52633</v>
       </c>
       <c r="F30">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G30">
-        <v>31741</v>
+        <v>31950</v>
       </c>
       <c r="H30">
-        <v>15671</v>
+        <v>15462</v>
       </c>
       <c r="I30">
-        <v>2332</v>
+        <v>2326</v>
       </c>
       <c r="J30">
-        <v>745</v>
+        <v>246</v>
       </c>
       <c r="K30">
         <v>0</v>
       </c>
       <c r="L30">
-        <v>3475</v>
+        <v>3887</v>
       </c>
       <c r="M30">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N30">
-        <v>227</v>
+        <v>253</v>
       </c>
       <c r="O30">
-        <v>28760</v>
+        <v>28970</v>
       </c>
       <c r="P30">
         <v>86935</v>
@@ -2410,31 +2410,31 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>87005</v>
+        <v>87370</v>
       </c>
       <c r="H31">
-        <v>1199</v>
+        <v>1003</v>
       </c>
       <c r="I31">
         <v>77</v>
       </c>
       <c r="J31">
-        <v>161</v>
+        <v>316</v>
       </c>
       <c r="K31">
         <v>0</v>
       </c>
       <c r="L31">
-        <v>40824</v>
+        <v>40909</v>
       </c>
       <c r="M31">
         <v>24</v>
       </c>
       <c r="N31">
-        <v>1609</v>
+        <v>1698</v>
       </c>
       <c r="O31">
-        <v>81208</v>
+        <v>82030</v>
       </c>
       <c r="P31">
         <v>81642</v>
@@ -2469,34 +2469,34 @@
         <v>21</v>
       </c>
       <c r="G32">
-        <v>27430</v>
+        <v>28381</v>
       </c>
       <c r="H32">
-        <v>14928</v>
+        <v>14043</v>
       </c>
       <c r="I32">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="J32">
-        <v>437</v>
+        <v>451</v>
       </c>
       <c r="K32">
         <v>0</v>
       </c>
       <c r="L32">
-        <v>5847</v>
+        <v>6125</v>
       </c>
       <c r="M32">
         <v>7</v>
       </c>
       <c r="N32">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="O32">
-        <v>22883</v>
+        <v>23505</v>
       </c>
       <c r="P32">
-        <v>16303</v>
+        <v>16690</v>
       </c>
       <c r="Q32">
         <v>11379</v>
@@ -2522,28 +2522,28 @@
         <v>0</v>
       </c>
       <c r="E33">
-        <v>40186</v>
+        <v>40200</v>
       </c>
       <c r="F33">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="G33">
-        <v>26699</v>
+        <v>27804</v>
       </c>
       <c r="H33">
-        <v>10271</v>
+        <v>9308</v>
       </c>
       <c r="I33">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J33">
-        <v>119</v>
+        <v>203</v>
       </c>
       <c r="K33">
         <v>0</v>
       </c>
       <c r="L33">
-        <v>3164</v>
+        <v>3211</v>
       </c>
       <c r="M33">
         <v>6</v>
@@ -2552,10 +2552,10 @@
         <v>12</v>
       </c>
       <c r="O33">
-        <v>25274</v>
+        <v>26272</v>
       </c>
       <c r="P33">
-        <v>73201</v>
+        <v>73301</v>
       </c>
       <c r="Q33">
         <v>6678</v>
@@ -2581,37 +2581,37 @@
         <v>0</v>
       </c>
       <c r="E34">
-        <v>36461</v>
+        <v>36478</v>
       </c>
       <c r="F34">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="G34">
-        <v>24732</v>
+        <v>25617</v>
       </c>
       <c r="H34">
-        <v>11753</v>
+        <v>10868</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
       <c r="J34">
-        <v>882</v>
+        <v>387</v>
       </c>
       <c r="K34">
         <v>0</v>
       </c>
       <c r="L34">
-        <v>8003</v>
+        <v>8517</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N34">
         <v>0</v>
       </c>
       <c r="O34">
-        <v>21282</v>
+        <v>22125</v>
       </c>
       <c r="P34">
         <v>74626</v>
@@ -2640,40 +2640,40 @@
         <v>0</v>
       </c>
       <c r="E35">
-        <v>33512</v>
+        <v>33522</v>
       </c>
       <c r="F35">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="G35">
-        <v>24807</v>
+        <v>25350</v>
       </c>
       <c r="H35">
-        <v>7293</v>
+        <v>6881</v>
       </c>
       <c r="I35">
         <v>1</v>
       </c>
       <c r="J35">
-        <v>428</v>
+        <v>285</v>
       </c>
       <c r="K35">
         <v>0</v>
       </c>
       <c r="L35">
-        <v>3333</v>
+        <v>3599</v>
       </c>
       <c r="M35">
         <v>0</v>
       </c>
       <c r="N35">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="O35">
-        <v>23045</v>
+        <v>23634</v>
       </c>
       <c r="P35">
-        <v>71712</v>
+        <v>72020</v>
       </c>
       <c r="Q35">
         <v>8879</v>
@@ -2729,7 +2729,7 @@
         <v>945</v>
       </c>
       <c r="O36">
-        <v>12868</v>
+        <v>13067</v>
       </c>
       <c r="P36">
         <v>60419</v>
@@ -2773,13 +2773,13 @@
         <v>0</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37">
         <v>0</v>
       </c>
       <c r="L37">
-        <v>2307</v>
+        <v>2309</v>
       </c>
       <c r="M37">
         <v>0</v>
@@ -2788,7 +2788,7 @@
         <v>538</v>
       </c>
       <c r="O37">
-        <v>17150</v>
+        <v>17151</v>
       </c>
       <c r="P37">
         <v>57832</v>
@@ -2847,7 +2847,7 @@
         <v>493</v>
       </c>
       <c r="O38">
-        <v>24573</v>
+        <v>24757</v>
       </c>
       <c r="P38">
         <v>63038</v>
@@ -2891,7 +2891,7 @@
         <v>0</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K39">
         <v>0</v>
@@ -2906,7 +2906,7 @@
         <v>234</v>
       </c>
       <c r="O39">
-        <v>20698</v>
+        <v>20802</v>
       </c>
       <c r="P39">
         <v>71133</v>
@@ -2941,31 +2941,31 @@
         <v>0</v>
       </c>
       <c r="G40">
-        <v>16506</v>
+        <v>16586</v>
       </c>
       <c r="H40">
-        <v>225</v>
+        <v>177</v>
       </c>
       <c r="I40">
         <v>0</v>
       </c>
       <c r="J40">
-        <v>368</v>
+        <v>297</v>
       </c>
       <c r="K40">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L40">
-        <v>1005</v>
+        <v>1106</v>
       </c>
       <c r="M40">
         <v>0</v>
       </c>
       <c r="N40">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O40">
-        <v>15330</v>
+        <v>15384</v>
       </c>
       <c r="P40">
         <v>73242</v>
@@ -3000,31 +3000,31 @@
         <v>0</v>
       </c>
       <c r="G41">
-        <v>21807</v>
+        <v>22091</v>
       </c>
       <c r="H41">
-        <v>294</v>
+        <v>258</v>
       </c>
       <c r="I41">
         <v>0</v>
       </c>
       <c r="J41">
-        <v>222</v>
+        <v>276</v>
       </c>
       <c r="K41">
         <v>5</v>
       </c>
       <c r="L41">
-        <v>670</v>
+        <v>680</v>
       </c>
       <c r="M41">
         <v>0</v>
       </c>
       <c r="N41">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="O41">
-        <v>20551</v>
+        <v>20793</v>
       </c>
       <c r="P41">
         <v>85249</v>
@@ -3068,13 +3068,13 @@
         <v>0</v>
       </c>
       <c r="J42">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K42">
         <v>0</v>
       </c>
       <c r="L42">
-        <v>6195</v>
+        <v>6196</v>
       </c>
       <c r="M42">
         <v>0</v>
@@ -3083,10 +3083,10 @@
         <v>417</v>
       </c>
       <c r="O42">
-        <v>26522</v>
+        <v>26532</v>
       </c>
       <c r="P42">
-        <v>64464</v>
+        <v>66010</v>
       </c>
       <c r="Q42">
         <v>4713</v>
@@ -3127,7 +3127,7 @@
         <v>0</v>
       </c>
       <c r="J43">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K43">
         <v>0</v>
@@ -3145,7 +3145,7 @@
         <v>25153</v>
       </c>
       <c r="P43">
-        <v>59619</v>
+        <v>61445</v>
       </c>
       <c r="Q43">
         <v>5271</v>
@@ -3177,31 +3177,31 @@
         <v>0</v>
       </c>
       <c r="G44">
-        <v>20605</v>
+        <v>20779</v>
       </c>
       <c r="H44">
-        <v>901</v>
+        <v>727</v>
       </c>
       <c r="I44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J44">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="K44">
         <v>0</v>
       </c>
       <c r="L44">
-        <v>6121</v>
+        <v>6132</v>
       </c>
       <c r="M44">
         <v>8</v>
       </c>
       <c r="N44">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="O44">
-        <v>16330</v>
+        <v>16479</v>
       </c>
       <c r="P44">
         <v>68393</v>
@@ -3236,16 +3236,16 @@
         <v>0</v>
       </c>
       <c r="G45">
-        <v>16475</v>
+        <v>16644</v>
       </c>
       <c r="H45">
-        <v>1747</v>
+        <v>1661</v>
       </c>
       <c r="I45">
         <v>12</v>
       </c>
       <c r="J45">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="K45">
         <v>31</v>
@@ -3257,10 +3257,10 @@
         <v>10</v>
       </c>
       <c r="N45">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="O45">
-        <v>14656</v>
+        <v>14820</v>
       </c>
       <c r="P45">
         <v>76002</v>
@@ -3295,16 +3295,16 @@
         <v>0</v>
       </c>
       <c r="G46">
-        <v>20772</v>
+        <v>20891</v>
       </c>
       <c r="H46">
-        <v>740</v>
+        <v>621</v>
       </c>
       <c r="I46">
         <v>0</v>
       </c>
       <c r="J46">
-        <v>412</v>
+        <v>475</v>
       </c>
       <c r="K46">
         <v>0</v>
@@ -3316,10 +3316,10 @@
         <v>1</v>
       </c>
       <c r="N46">
-        <v>194</v>
+        <v>220</v>
       </c>
       <c r="O46">
-        <v>17044</v>
+        <v>17090</v>
       </c>
       <c r="P46">
         <v>64160</v>
@@ -3354,16 +3354,16 @@
         <v>0</v>
       </c>
       <c r="G47">
-        <v>20891</v>
+        <v>21098</v>
       </c>
       <c r="H47">
-        <v>1143</v>
+        <v>1035</v>
       </c>
       <c r="I47">
         <v>35</v>
       </c>
       <c r="J47">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K47">
         <v>0</v>
@@ -3375,10 +3375,10 @@
         <v>1</v>
       </c>
       <c r="N47">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O47">
-        <v>19585</v>
+        <v>19810</v>
       </c>
       <c r="P47">
         <v>49875</v>
@@ -3413,16 +3413,16 @@
         <v>47</v>
       </c>
       <c r="G48">
-        <v>19540</v>
+        <v>19548</v>
       </c>
       <c r="H48">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="I48">
         <v>3</v>
       </c>
       <c r="J48">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K48">
         <v>0</v>
@@ -3434,10 +3434,10 @@
         <v>4</v>
       </c>
       <c r="N48">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="O48">
-        <v>19173</v>
+        <v>19198</v>
       </c>
       <c r="P48">
         <v>54142</v>
@@ -3472,31 +3472,31 @@
         <v>19</v>
       </c>
       <c r="G49">
-        <v>19051</v>
+        <v>19088</v>
       </c>
       <c r="H49">
-        <v>1028</v>
+        <v>1024</v>
       </c>
       <c r="I49">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J49">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="K49">
         <v>0</v>
       </c>
       <c r="L49">
-        <v>3069</v>
+        <v>3116</v>
       </c>
       <c r="M49">
         <v>0</v>
       </c>
       <c r="N49">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="O49">
-        <v>17313</v>
+        <v>17338</v>
       </c>
       <c r="P49">
         <v>50563</v>
@@ -3531,22 +3531,22 @@
         <v>0</v>
       </c>
       <c r="G50">
-        <v>21055</v>
+        <v>21220</v>
       </c>
       <c r="H50">
-        <v>657</v>
+        <v>583</v>
       </c>
       <c r="I50">
         <v>0</v>
       </c>
       <c r="J50">
-        <v>213</v>
+        <v>105</v>
       </c>
       <c r="K50">
         <v>0</v>
       </c>
       <c r="L50">
-        <v>3462</v>
+        <v>3634</v>
       </c>
       <c r="M50">
         <v>5</v>
@@ -3555,7 +3555,7 @@
         <v>11</v>
       </c>
       <c r="O50">
-        <v>20081</v>
+        <v>20245</v>
       </c>
       <c r="P50">
         <v>63298</v>
@@ -3590,16 +3590,16 @@
         <v>0</v>
       </c>
       <c r="G51">
-        <v>22367</v>
+        <v>22587</v>
       </c>
       <c r="H51">
-        <v>768</v>
+        <v>548</v>
       </c>
       <c r="I51">
         <v>3</v>
       </c>
       <c r="J51">
-        <v>60</v>
+        <v>193</v>
       </c>
       <c r="K51">
         <v>0</v>
@@ -3614,7 +3614,7 @@
         <v>61</v>
       </c>
       <c r="O51">
-        <v>19288</v>
+        <v>19385</v>
       </c>
       <c r="P51">
         <v>71754</v>
@@ -3649,31 +3649,31 @@
         <v>0</v>
       </c>
       <c r="G52">
-        <v>20860</v>
+        <v>20902</v>
       </c>
       <c r="H52">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="I52">
         <v>0</v>
       </c>
       <c r="J52">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="K52">
         <v>29</v>
       </c>
       <c r="L52">
-        <v>2392</v>
+        <v>2403</v>
       </c>
       <c r="M52">
         <v>1</v>
       </c>
       <c r="N52">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="O52">
-        <v>20305</v>
+        <v>20309</v>
       </c>
       <c r="P52">
         <v>63986</v>
@@ -3717,13 +3717,13 @@
         <v>0</v>
       </c>
       <c r="J53">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="K53">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="L53">
-        <v>3030</v>
+        <v>3032</v>
       </c>
       <c r="M53">
         <v>1</v>
@@ -3732,7 +3732,7 @@
         <v>7</v>
       </c>
       <c r="O53">
-        <v>18140</v>
+        <v>18565</v>
       </c>
       <c r="P53">
         <v>56304</v>
@@ -3767,31 +3767,31 @@
         <v>0</v>
       </c>
       <c r="G54">
-        <v>20349</v>
+        <v>20367</v>
       </c>
       <c r="H54">
-        <v>328</v>
+        <v>312</v>
       </c>
       <c r="I54">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J54">
-        <v>626</v>
+        <v>592</v>
       </c>
       <c r="K54">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="L54">
-        <v>1708</v>
+        <v>1737</v>
       </c>
       <c r="M54">
         <v>5</v>
       </c>
       <c r="N54">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O54">
-        <v>17772</v>
+        <v>17787</v>
       </c>
       <c r="P54">
         <v>58440</v>
@@ -3826,31 +3826,31 @@
         <v>0</v>
       </c>
       <c r="G55">
-        <v>15975</v>
+        <v>15992</v>
       </c>
       <c r="H55">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="I55">
         <v>0</v>
       </c>
       <c r="J55">
-        <v>576</v>
+        <v>529</v>
       </c>
       <c r="K55">
-        <v>268</v>
+        <v>232</v>
       </c>
       <c r="L55">
-        <v>1482</v>
+        <v>1525</v>
       </c>
       <c r="M55">
         <v>0</v>
       </c>
       <c r="N55">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="O55">
-        <v>15232</v>
+        <v>15274</v>
       </c>
       <c r="P55">
         <v>58215</v>
@@ -3885,16 +3885,16 @@
         <v>0</v>
       </c>
       <c r="G56">
-        <v>18858</v>
+        <v>18883</v>
       </c>
       <c r="H56">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="I56">
         <v>0</v>
       </c>
       <c r="J56">
-        <v>895</v>
+        <v>926</v>
       </c>
       <c r="K56">
         <v>472</v>
@@ -3906,10 +3906,10 @@
         <v>2</v>
       </c>
       <c r="N56">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="O56">
-        <v>14464</v>
+        <v>14479</v>
       </c>
       <c r="P56">
         <v>46365</v>
@@ -3944,31 +3944,31 @@
         <v>0</v>
       </c>
       <c r="G57">
-        <v>21108</v>
+        <v>21201</v>
       </c>
       <c r="H57">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="I57">
         <v>0</v>
       </c>
       <c r="J57">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K57">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="L57">
-        <v>1746</v>
+        <v>1754</v>
       </c>
       <c r="M57">
         <v>5</v>
       </c>
       <c r="N57">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O57">
-        <v>20857</v>
+        <v>21022</v>
       </c>
       <c r="P57">
         <v>61556</v>
@@ -4003,31 +4003,31 @@
         <v>0</v>
       </c>
       <c r="G58">
-        <v>21690</v>
+        <v>21790</v>
       </c>
       <c r="H58">
-        <v>498</v>
+        <v>426</v>
       </c>
       <c r="I58">
         <v>24</v>
       </c>
       <c r="J58">
-        <v>1659</v>
+        <v>1657</v>
       </c>
       <c r="K58">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="L58">
-        <v>5571</v>
+        <v>5726</v>
       </c>
       <c r="M58">
         <v>3</v>
       </c>
       <c r="N58">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O58">
-        <v>15367</v>
+        <v>15381</v>
       </c>
       <c r="P58">
         <v>57577</v>
@@ -4121,22 +4121,22 @@
         <v>0</v>
       </c>
       <c r="G60">
-        <v>23283</v>
+        <v>23330</v>
       </c>
       <c r="H60">
-        <v>224</v>
+        <v>177</v>
       </c>
       <c r="I60">
         <v>0</v>
       </c>
       <c r="J60">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="K60">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="L60">
-        <v>5180</v>
+        <v>5232</v>
       </c>
       <c r="M60">
         <v>0</v>
@@ -4145,7 +4145,7 @@
         <v>246</v>
       </c>
       <c r="O60">
-        <v>21383</v>
+        <v>21451</v>
       </c>
       <c r="P60">
         <v>70140</v>
@@ -4189,16 +4189,16 @@
         <v>0</v>
       </c>
       <c r="J61">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="K61">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="L61">
-        <v>9858</v>
+        <v>9875</v>
       </c>
       <c r="M61">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="N61">
         <v>1</v>
@@ -4239,16 +4239,16 @@
         <v>0</v>
       </c>
       <c r="G62">
-        <v>15669</v>
+        <v>15692</v>
       </c>
       <c r="H62">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="I62">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J62">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="K62">
         <v>274</v>
@@ -4260,10 +4260,10 @@
         <v>11</v>
       </c>
       <c r="N62">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="O62">
-        <v>14563</v>
+        <v>14580</v>
       </c>
       <c r="P62">
         <v>51334</v>
@@ -4298,16 +4298,16 @@
         <v>0</v>
       </c>
       <c r="G63">
-        <v>36633</v>
+        <v>36672</v>
       </c>
       <c r="H63">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="I63">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="J63">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="K63">
         <v>0</v>
@@ -4319,10 +4319,10 @@
         <v>35</v>
       </c>
       <c r="N63">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="O63">
-        <v>31744</v>
+        <v>31787</v>
       </c>
       <c r="P63">
         <v>68691</v>
@@ -4357,16 +4357,16 @@
         <v>0</v>
       </c>
       <c r="G64">
-        <v>40286</v>
+        <v>40556</v>
       </c>
       <c r="H64">
-        <v>1493</v>
+        <v>1227</v>
       </c>
       <c r="I64">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J64">
-        <v>155</v>
+        <v>307</v>
       </c>
       <c r="K64">
         <v>2</v>
@@ -4381,7 +4381,7 @@
         <v>250</v>
       </c>
       <c r="O64">
-        <v>37144</v>
+        <v>38054</v>
       </c>
       <c r="P64">
         <v>60527</v>
@@ -4416,34 +4416,34 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>36131</v>
+        <v>36388</v>
       </c>
       <c r="H65">
-        <v>3686</v>
+        <v>3434</v>
       </c>
       <c r="I65">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="J65">
-        <v>55</v>
+        <v>199</v>
       </c>
       <c r="K65">
         <v>0</v>
       </c>
       <c r="L65">
-        <v>11038</v>
+        <v>11081</v>
       </c>
       <c r="M65">
         <v>2</v>
       </c>
       <c r="N65">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O65">
-        <v>25933</v>
+        <v>26066</v>
       </c>
       <c r="P65">
-        <v>34607</v>
+        <v>34611</v>
       </c>
       <c r="Q65">
         <v>13284</v>
@@ -4475,31 +4475,31 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>54650</v>
+        <v>55600</v>
       </c>
       <c r="H66">
-        <v>7404</v>
+        <v>6629</v>
       </c>
       <c r="I66">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="J66">
-        <v>169</v>
+        <v>217</v>
       </c>
       <c r="K66">
         <v>0</v>
       </c>
       <c r="L66">
-        <v>10603</v>
+        <v>10764</v>
       </c>
       <c r="M66">
         <v>2</v>
       </c>
       <c r="N66">
-        <v>1378</v>
+        <v>1466</v>
       </c>
       <c r="O66">
-        <v>48604</v>
+        <v>49664</v>
       </c>
       <c r="P66">
         <v>93810</v>
@@ -4534,31 +4534,31 @@
         <v>0</v>
       </c>
       <c r="G67">
-        <v>62962</v>
+        <v>63395</v>
       </c>
       <c r="H67">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I67">
-        <v>2739</v>
+        <v>2646</v>
       </c>
       <c r="J67">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="K67">
         <v>0</v>
       </c>
       <c r="L67">
-        <v>17770</v>
+        <v>17926</v>
       </c>
       <c r="M67">
         <v>10</v>
       </c>
       <c r="N67">
-        <v>1237</v>
+        <v>1241</v>
       </c>
       <c r="O67">
-        <v>50786</v>
+        <v>51810</v>
       </c>
       <c r="P67">
         <v>78022</v>
@@ -4593,34 +4593,34 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>60251</v>
+        <v>60512</v>
       </c>
       <c r="H68">
-        <v>4055</v>
+        <v>3818</v>
       </c>
       <c r="I68">
-        <v>854</v>
+        <v>834</v>
       </c>
       <c r="J68">
-        <v>676</v>
+        <v>479</v>
       </c>
       <c r="K68">
         <v>0</v>
       </c>
       <c r="L68">
-        <v>14846</v>
+        <v>15146</v>
       </c>
       <c r="M68">
         <v>2</v>
       </c>
       <c r="N68">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="O68">
-        <v>49980</v>
+        <v>50416</v>
       </c>
       <c r="P68">
-        <v>61342</v>
+        <v>61388</v>
       </c>
       <c r="Q68">
         <v>7850</v>
@@ -4652,34 +4652,34 @@
         <v>0</v>
       </c>
       <c r="G69">
-        <v>37481</v>
+        <v>37690</v>
       </c>
       <c r="H69">
-        <v>5726</v>
+        <v>5580</v>
       </c>
       <c r="I69">
-        <v>471</v>
+        <v>456</v>
       </c>
       <c r="J69">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="K69">
         <v>0</v>
       </c>
       <c r="L69">
-        <v>13850</v>
+        <v>14001</v>
       </c>
       <c r="M69">
         <v>2</v>
       </c>
       <c r="N69">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="O69">
-        <v>33105</v>
+        <v>33139</v>
       </c>
       <c r="P69">
-        <v>34092</v>
+        <v>34467</v>
       </c>
       <c r="Q69">
         <v>6528</v>
@@ -4711,31 +4711,31 @@
         <v>0</v>
       </c>
       <c r="G70">
-        <v>43853</v>
+        <v>44024</v>
       </c>
       <c r="H70">
-        <v>1199</v>
+        <v>1104</v>
       </c>
       <c r="I70">
-        <v>2332</v>
+        <v>2262</v>
       </c>
       <c r="J70">
-        <v>347</v>
+        <v>124</v>
       </c>
       <c r="K70">
         <v>0</v>
       </c>
       <c r="L70">
-        <v>17076</v>
+        <v>17343</v>
       </c>
       <c r="M70">
         <v>2</v>
       </c>
       <c r="N70">
-        <v>728</v>
+        <v>771</v>
       </c>
       <c r="O70">
-        <v>38912</v>
+        <v>39707</v>
       </c>
       <c r="P70">
         <v>42040</v>
@@ -4770,31 +4770,31 @@
         <v>0</v>
       </c>
       <c r="G71">
-        <v>46068</v>
+        <v>46226</v>
       </c>
       <c r="H71">
-        <v>3465</v>
+        <v>3314</v>
       </c>
       <c r="I71">
-        <v>1314</v>
+        <v>1307</v>
       </c>
       <c r="J71">
-        <v>551</v>
+        <v>69</v>
       </c>
       <c r="K71">
         <v>0</v>
       </c>
       <c r="L71">
-        <v>20361</v>
+        <v>20901</v>
       </c>
       <c r="M71">
         <v>1</v>
       </c>
       <c r="N71">
-        <v>2828</v>
+        <v>2836</v>
       </c>
       <c r="O71">
-        <v>34035</v>
+        <v>34434</v>
       </c>
       <c r="P71">
         <v>48896</v>
@@ -4829,31 +4829,31 @@
         <v>0</v>
       </c>
       <c r="G72">
-        <v>53966</v>
+        <v>54461</v>
       </c>
       <c r="H72">
-        <v>5900</v>
+        <v>5501</v>
       </c>
       <c r="I72">
-        <v>1514</v>
+        <v>1418</v>
       </c>
       <c r="J72">
-        <v>519</v>
+        <v>28</v>
       </c>
       <c r="K72">
         <v>0</v>
       </c>
       <c r="L72">
-        <v>15093</v>
+        <v>15731</v>
       </c>
       <c r="M72">
         <v>9</v>
       </c>
       <c r="N72">
-        <v>546</v>
+        <v>697</v>
       </c>
       <c r="O72">
-        <v>43218</v>
+        <v>43450</v>
       </c>
       <c r="P72">
         <v>85505</v>
@@ -4888,31 +4888,31 @@
         <v>0</v>
       </c>
       <c r="G73">
-        <v>48261</v>
+        <v>48519</v>
       </c>
       <c r="H73">
-        <v>10271</v>
+        <v>10032</v>
       </c>
       <c r="I73">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="J73">
-        <v>1058</v>
+        <v>719</v>
       </c>
       <c r="K73">
         <v>0</v>
       </c>
       <c r="L73">
-        <v>9294</v>
+        <v>9724</v>
       </c>
       <c r="M73">
         <v>5</v>
       </c>
       <c r="N73">
-        <v>591</v>
+        <v>617</v>
       </c>
       <c r="O73">
-        <v>42673</v>
+        <v>42964</v>
       </c>
       <c r="P73">
         <v>67550</v>
@@ -4939,40 +4939,40 @@
         <v>0</v>
       </c>
       <c r="E74">
-        <v>2429682</v>
+        <v>2429756</v>
       </c>
       <c r="F74">
-        <v>700</v>
+        <v>626</v>
       </c>
       <c r="G74">
-        <v>2073982</v>
+        <v>2092580</v>
       </c>
       <c r="H74">
-        <v>278061</v>
+        <v>262847</v>
       </c>
       <c r="I74">
-        <v>17926</v>
+        <v>17336</v>
       </c>
       <c r="J74">
-        <v>75429</v>
+        <v>72726</v>
       </c>
       <c r="K74">
-        <v>38294</v>
+        <v>37711</v>
       </c>
       <c r="L74">
-        <v>440850</v>
+        <v>448162</v>
       </c>
       <c r="M74">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="N74">
-        <v>31653</v>
+        <v>32749</v>
       </c>
       <c r="O74">
-        <v>1783113</v>
+        <v>1806788</v>
       </c>
       <c r="P74">
-        <v>4392034</v>
+        <v>4405036</v>
       </c>
       <c r="Q74">
         <v>629567</v>

--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MANNA\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0F88578-0968-413B-A313-EBB5325058A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25125" windowHeight="12210"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -304,13 +303,13 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Notice &amp; Hearing Report Last Updated On : 27-08-2026 12:00:13</t>
+    <t>Notice &amp; Hearing Report Last Updated On : 27-08-2026 19:57:07</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -341,8 +340,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -681,7 +680,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T74"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -817,31 +816,31 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>36716</v>
+        <v>39772</v>
       </c>
       <c r="H4">
-        <v>12620</v>
+        <v>10252</v>
       </c>
       <c r="I4">
         <v>9</v>
       </c>
       <c r="J4">
-        <v>5975</v>
+        <v>6435</v>
       </c>
       <c r="K4">
-        <v>2949</v>
+        <v>2780</v>
       </c>
       <c r="L4">
-        <v>3485</v>
+        <v>3773</v>
       </c>
       <c r="M4">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="N4">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="O4">
-        <v>28334</v>
+        <v>31110</v>
       </c>
       <c r="P4">
         <v>53812</v>
@@ -876,34 +875,34 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>46037</v>
+        <v>48035</v>
       </c>
       <c r="H5">
-        <v>5909</v>
+        <v>4529</v>
       </c>
       <c r="I5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>3667</v>
+        <v>3708</v>
       </c>
       <c r="K5">
-        <v>2074</v>
+        <v>1906</v>
       </c>
       <c r="L5">
-        <v>3384</v>
+        <v>3694</v>
       </c>
       <c r="M5">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="N5">
-        <v>332</v>
+        <v>371</v>
       </c>
       <c r="O5">
-        <v>41682</v>
+        <v>43574</v>
       </c>
       <c r="P5">
-        <v>55484</v>
+        <v>55483</v>
       </c>
       <c r="Q5">
         <v>16108</v>
@@ -935,34 +934,34 @@
         <v>2</v>
       </c>
       <c r="G6">
-        <v>24834</v>
+        <v>27048</v>
       </c>
       <c r="H6">
-        <v>9775</v>
+        <v>8609</v>
       </c>
       <c r="I6">
-        <v>129</v>
+        <v>49</v>
       </c>
       <c r="J6">
-        <v>1753</v>
+        <v>2076</v>
       </c>
       <c r="K6">
         <v>1096</v>
       </c>
       <c r="L6">
-        <v>1832</v>
+        <v>1836</v>
       </c>
       <c r="M6">
         <v>27</v>
       </c>
       <c r="N6">
-        <v>677</v>
+        <v>745</v>
       </c>
       <c r="O6">
-        <v>21120</v>
+        <v>22946</v>
       </c>
       <c r="P6">
-        <v>52459</v>
+        <v>53017</v>
       </c>
       <c r="Q6">
         <v>17918</v>
@@ -994,31 +993,31 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>33990</v>
+        <v>35902</v>
       </c>
       <c r="H7">
-        <v>5225</v>
+        <v>3325</v>
       </c>
       <c r="I7">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="J7">
-        <v>4249</v>
+        <v>4162</v>
       </c>
       <c r="K7">
-        <v>3365</v>
+        <v>3233</v>
       </c>
       <c r="L7">
-        <v>1329</v>
+        <v>1443</v>
       </c>
       <c r="M7">
         <v>29</v>
       </c>
       <c r="N7">
-        <v>1061</v>
+        <v>1249</v>
       </c>
       <c r="O7">
-        <v>28296</v>
+        <v>29955</v>
       </c>
       <c r="P7">
         <v>77581</v>
@@ -1053,34 +1052,34 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>25898</v>
+        <v>26777</v>
       </c>
       <c r="H8">
-        <v>14653</v>
+        <v>13775</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>9280</v>
+        <v>8696</v>
       </c>
       <c r="K8">
-        <v>5373</v>
+        <v>5372</v>
       </c>
       <c r="L8">
-        <v>3752</v>
+        <v>4300</v>
       </c>
       <c r="M8">
         <v>16</v>
       </c>
       <c r="N8">
-        <v>252</v>
+        <v>289</v>
       </c>
       <c r="O8">
-        <v>13439</v>
+        <v>14296</v>
       </c>
       <c r="P8">
-        <v>26226</v>
+        <v>32770</v>
       </c>
       <c r="Q8">
         <v>20902</v>
@@ -1112,34 +1111,34 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>32889</v>
+        <v>35150</v>
       </c>
       <c r="H9">
-        <v>9976</v>
+        <v>7761</v>
       </c>
       <c r="I9">
-        <v>408</v>
+        <v>362</v>
       </c>
       <c r="J9">
-        <v>4257</v>
+        <v>3306</v>
       </c>
       <c r="K9">
-        <v>3055</v>
+        <v>2688</v>
       </c>
       <c r="L9">
-        <v>1495</v>
+        <v>2601</v>
       </c>
       <c r="M9">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N9">
-        <v>203</v>
+        <v>289</v>
       </c>
       <c r="O9">
-        <v>27085</v>
+        <v>29979</v>
       </c>
       <c r="P9">
-        <v>53534</v>
+        <v>66749</v>
       </c>
       <c r="Q9">
         <v>18214</v>
@@ -1171,34 +1170,34 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>30450</v>
+        <v>31865</v>
       </c>
       <c r="H10">
-        <v>6065</v>
+        <v>4662</v>
       </c>
       <c r="I10">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="J10">
-        <v>3731</v>
+        <v>2417</v>
       </c>
       <c r="K10">
-        <v>2375</v>
+        <v>1175</v>
       </c>
       <c r="L10">
-        <v>5870</v>
+        <v>7371</v>
       </c>
       <c r="M10">
         <v>13</v>
       </c>
       <c r="N10">
-        <v>349</v>
+        <v>370</v>
       </c>
       <c r="O10">
-        <v>21006</v>
+        <v>23629</v>
       </c>
       <c r="P10">
-        <v>37227</v>
+        <v>48109</v>
       </c>
       <c r="Q10">
         <v>9516</v>
@@ -1230,31 +1229,31 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>39123</v>
+        <v>41323</v>
       </c>
       <c r="H11">
-        <v>10111</v>
+        <v>8318</v>
       </c>
       <c r="I11">
-        <v>737</v>
+        <v>462</v>
       </c>
       <c r="J11">
-        <v>5036</v>
+        <v>5267</v>
       </c>
       <c r="K11">
-        <v>2243</v>
+        <v>2090</v>
       </c>
       <c r="L11">
-        <v>1152</v>
+        <v>1369</v>
       </c>
       <c r="M11">
         <v>20</v>
       </c>
       <c r="N11">
-        <v>260</v>
+        <v>334</v>
       </c>
       <c r="O11">
-        <v>32600</v>
+        <v>34265</v>
       </c>
       <c r="P11">
         <v>84443</v>
@@ -1283,40 +1282,40 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>40716</v>
+        <v>40739</v>
       </c>
       <c r="F12">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>28498</v>
+        <v>31186</v>
       </c>
       <c r="H12">
-        <v>11771</v>
+        <v>9260</v>
       </c>
       <c r="I12">
-        <v>237</v>
+        <v>156</v>
       </c>
       <c r="J12">
-        <v>8440</v>
+        <v>8468</v>
       </c>
       <c r="K12">
-        <v>6085</v>
+        <v>5996</v>
       </c>
       <c r="L12">
-        <v>348</v>
+        <v>489</v>
       </c>
       <c r="M12">
         <v>2</v>
       </c>
       <c r="N12">
-        <v>369</v>
+        <v>537</v>
       </c>
       <c r="O12">
-        <v>19475</v>
+        <v>21880</v>
       </c>
       <c r="P12">
-        <v>61589</v>
+        <v>62789</v>
       </c>
       <c r="Q12">
         <v>17907</v>
@@ -1342,22 +1341,22 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>36908</v>
+        <v>37025</v>
       </c>
       <c r="F13">
-        <v>123</v>
+        <v>6</v>
       </c>
       <c r="G13">
-        <v>26304</v>
+        <v>28653</v>
       </c>
       <c r="H13">
-        <v>9300</v>
+        <v>7317</v>
       </c>
       <c r="I13">
         <v>12</v>
       </c>
       <c r="J13">
-        <v>3433</v>
+        <v>4324</v>
       </c>
       <c r="K13">
         <v>1965</v>
@@ -1369,10 +1368,10 @@
         <v>0</v>
       </c>
       <c r="N13">
-        <v>1955</v>
+        <v>2045</v>
       </c>
       <c r="O13">
-        <v>20264</v>
+        <v>21631</v>
       </c>
       <c r="P13">
         <v>56590</v>
@@ -1407,34 +1406,34 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>31348</v>
+        <v>32807</v>
       </c>
       <c r="H14">
-        <v>11704</v>
+        <v>10566</v>
       </c>
       <c r="I14">
-        <v>621</v>
+        <v>595</v>
       </c>
       <c r="J14">
-        <v>8551</v>
+        <v>8929</v>
       </c>
       <c r="K14">
-        <v>5447</v>
+        <v>5438</v>
       </c>
       <c r="L14">
-        <v>1772</v>
+        <v>1781</v>
       </c>
       <c r="M14">
         <v>57</v>
       </c>
       <c r="N14">
-        <v>599</v>
+        <v>783</v>
       </c>
       <c r="O14">
-        <v>20797</v>
+        <v>21694</v>
       </c>
       <c r="P14">
-        <v>53792</v>
+        <v>54138</v>
       </c>
       <c r="Q14">
         <v>20044</v>
@@ -1466,31 +1465,31 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>40673</v>
+        <v>41510</v>
       </c>
       <c r="H15">
-        <v>2030</v>
+        <v>1193</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>94</v>
+        <v>13</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15">
-        <v>8633</v>
+        <v>8921</v>
       </c>
       <c r="M15">
         <v>0</v>
       </c>
       <c r="N15">
-        <v>2192</v>
+        <v>2529</v>
       </c>
       <c r="O15">
-        <v>38269</v>
+        <v>38843</v>
       </c>
       <c r="P15">
         <v>67178</v>
@@ -1519,40 +1518,40 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>25536</v>
+        <v>25548</v>
       </c>
       <c r="F16">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G16">
-        <v>21947</v>
+        <v>22758</v>
       </c>
       <c r="H16">
-        <v>2607</v>
+        <v>1903</v>
       </c>
       <c r="I16">
-        <v>137</v>
+        <v>96</v>
       </c>
       <c r="J16">
-        <v>101</v>
+        <v>16</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
       <c r="L16">
-        <v>12005</v>
+        <v>12504</v>
       </c>
       <c r="M16">
         <v>1</v>
       </c>
       <c r="N16">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="O16">
-        <v>17017</v>
+        <v>19653</v>
       </c>
       <c r="P16">
-        <v>67761</v>
+        <v>67815</v>
       </c>
       <c r="Q16">
         <v>5208</v>
@@ -1584,31 +1583,31 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>27548</v>
+        <v>27707</v>
       </c>
       <c r="H17">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J17">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="K17">
         <v>0</v>
       </c>
       <c r="L17">
-        <v>9140</v>
+        <v>9249</v>
       </c>
       <c r="M17">
         <v>2</v>
       </c>
       <c r="N17">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="O17">
-        <v>26362</v>
+        <v>27219</v>
       </c>
       <c r="P17">
         <v>65458</v>
@@ -1637,37 +1636,37 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>47807</v>
+        <v>47810</v>
       </c>
       <c r="F18">
+        <v>26</v>
+      </c>
+      <c r="G18">
+        <v>47513</v>
+      </c>
+      <c r="H18">
+        <v>306</v>
+      </c>
+      <c r="I18">
+        <v>16</v>
+      </c>
+      <c r="J18">
         <v>29</v>
       </c>
-      <c r="G18">
-        <v>46600</v>
-      </c>
-      <c r="H18">
-        <v>971</v>
-      </c>
-      <c r="I18">
-        <v>224</v>
-      </c>
-      <c r="J18">
-        <v>26</v>
-      </c>
       <c r="K18">
         <v>0</v>
       </c>
       <c r="L18">
-        <v>7582</v>
+        <v>7736</v>
       </c>
       <c r="M18">
         <v>3</v>
       </c>
       <c r="N18">
-        <v>1703</v>
+        <v>1867</v>
       </c>
       <c r="O18">
-        <v>42413</v>
+        <v>43600</v>
       </c>
       <c r="P18">
         <v>70738</v>
@@ -1696,37 +1695,37 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>56383</v>
+        <v>56392</v>
       </c>
       <c r="F19">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="G19">
-        <v>53251</v>
+        <v>54360</v>
       </c>
       <c r="H19">
-        <v>2956</v>
+        <v>1932</v>
       </c>
       <c r="I19">
-        <v>283</v>
+        <v>194</v>
       </c>
       <c r="J19">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="K19">
         <v>0</v>
       </c>
       <c r="L19">
-        <v>14142</v>
+        <v>14440</v>
       </c>
       <c r="M19">
         <v>1</v>
       </c>
       <c r="N19">
-        <v>566</v>
+        <v>670</v>
       </c>
       <c r="O19">
-        <v>47252</v>
+        <v>48800</v>
       </c>
       <c r="P19">
         <v>106226</v>
@@ -1755,40 +1754,40 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>35010</v>
+        <v>35016</v>
       </c>
       <c r="F20">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G20">
-        <v>34066</v>
+        <v>34441</v>
       </c>
       <c r="H20">
-        <v>939</v>
+        <v>573</v>
       </c>
       <c r="I20">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J20">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c r="K20">
         <v>0</v>
       </c>
       <c r="L20">
-        <v>5765</v>
+        <v>5831</v>
       </c>
       <c r="M20">
         <v>5</v>
       </c>
       <c r="N20">
-        <v>261</v>
+        <v>371</v>
       </c>
       <c r="O20">
-        <v>32987</v>
+        <v>33245</v>
       </c>
       <c r="P20">
-        <v>75719</v>
+        <v>75794</v>
       </c>
       <c r="Q20">
         <v>9014</v>
@@ -1879,31 +1878,31 @@
         <v>0</v>
       </c>
       <c r="G22">
-        <v>18628</v>
+        <v>18657</v>
       </c>
       <c r="H22">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="I22">
         <v>0</v>
       </c>
       <c r="J22">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="K22">
         <v>0</v>
       </c>
       <c r="L22">
-        <v>7465</v>
+        <v>7504</v>
       </c>
       <c r="M22">
         <v>0</v>
       </c>
       <c r="N22">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="O22">
-        <v>17553</v>
+        <v>17612</v>
       </c>
       <c r="P22">
         <v>64099</v>
@@ -2012,7 +2011,7 @@
         <v>0</v>
       </c>
       <c r="L24">
-        <v>3480</v>
+        <v>3482</v>
       </c>
       <c r="M24">
         <v>5</v>
@@ -2021,7 +2020,7 @@
         <v>231</v>
       </c>
       <c r="O24">
-        <v>13818</v>
+        <v>13825</v>
       </c>
       <c r="P24">
         <v>65629</v>
@@ -2056,31 +2055,31 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>19194</v>
+        <v>19247</v>
       </c>
       <c r="H25">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="I25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25">
-        <v>222</v>
+        <v>6</v>
       </c>
       <c r="K25">
         <v>0</v>
       </c>
       <c r="L25">
-        <v>4579</v>
+        <v>4826</v>
       </c>
       <c r="M25">
         <v>0</v>
       </c>
       <c r="N25">
-        <v>261</v>
+        <v>287</v>
       </c>
       <c r="O25">
-        <v>18306</v>
+        <v>18665</v>
       </c>
       <c r="P25">
         <v>57533</v>
@@ -2115,31 +2114,31 @@
         <v>0</v>
       </c>
       <c r="G26">
-        <v>17360</v>
+        <v>17413</v>
       </c>
       <c r="H26">
-        <v>197</v>
+        <v>144</v>
       </c>
       <c r="I26">
         <v>0</v>
       </c>
       <c r="J26">
-        <v>138</v>
+        <v>2</v>
       </c>
       <c r="K26">
         <v>0</v>
       </c>
       <c r="L26">
-        <v>3525</v>
+        <v>3655</v>
       </c>
       <c r="M26">
         <v>3</v>
       </c>
       <c r="N26">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="O26">
-        <v>16547</v>
+        <v>16962</v>
       </c>
       <c r="P26">
         <v>66594</v>
@@ -2174,22 +2173,22 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>31564</v>
+        <v>34440</v>
       </c>
       <c r="H27">
-        <v>10464</v>
+        <v>7720</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27">
-        <v>399</v>
+        <v>181</v>
       </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="L27">
-        <v>6402</v>
+        <v>7136</v>
       </c>
       <c r="M27">
         <v>0</v>
@@ -2198,10 +2197,10 @@
         <v>56</v>
       </c>
       <c r="O27">
-        <v>30366</v>
+        <v>33155</v>
       </c>
       <c r="P27">
-        <v>44406</v>
+        <v>48916</v>
       </c>
       <c r="Q27">
         <v>12669</v>
@@ -2233,31 +2232,31 @@
         <v>79</v>
       </c>
       <c r="G28">
-        <v>27963</v>
+        <v>29232</v>
       </c>
       <c r="H28">
-        <v>22029</v>
+        <v>20906</v>
       </c>
       <c r="I28">
         <v>37</v>
       </c>
       <c r="J28">
-        <v>192</v>
+        <v>157</v>
       </c>
       <c r="K28">
         <v>0</v>
       </c>
       <c r="L28">
-        <v>3917</v>
+        <v>4127</v>
       </c>
       <c r="M28">
         <v>11</v>
       </c>
       <c r="N28">
-        <v>481</v>
+        <v>520</v>
       </c>
       <c r="O28">
-        <v>24133</v>
+        <v>25507</v>
       </c>
       <c r="P28">
         <v>80639</v>
@@ -2292,31 +2291,31 @@
         <v>0</v>
       </c>
       <c r="G29">
-        <v>39142</v>
+        <v>40605</v>
       </c>
       <c r="H29">
-        <v>7182</v>
+        <v>6003</v>
       </c>
       <c r="I29">
-        <v>305</v>
+        <v>251</v>
       </c>
       <c r="J29">
-        <v>623</v>
+        <v>98</v>
       </c>
       <c r="K29">
         <v>0</v>
       </c>
       <c r="L29">
-        <v>5924</v>
+        <v>6698</v>
       </c>
       <c r="M29">
         <v>3</v>
       </c>
       <c r="N29">
-        <v>517</v>
+        <v>602</v>
       </c>
       <c r="O29">
-        <v>34133</v>
+        <v>35409</v>
       </c>
       <c r="P29">
         <v>83837</v>
@@ -2345,37 +2344,37 @@
         <v>0</v>
       </c>
       <c r="E30">
-        <v>52633</v>
+        <v>52634</v>
       </c>
       <c r="F30">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G30">
-        <v>31950</v>
+        <v>34260</v>
       </c>
       <c r="H30">
-        <v>15462</v>
+        <v>11716</v>
       </c>
       <c r="I30">
-        <v>2326</v>
+        <v>2198</v>
       </c>
       <c r="J30">
-        <v>246</v>
+        <v>338</v>
       </c>
       <c r="K30">
         <v>0</v>
       </c>
       <c r="L30">
-        <v>3887</v>
+        <v>4265</v>
       </c>
       <c r="M30">
         <v>4</v>
       </c>
       <c r="N30">
-        <v>253</v>
+        <v>346</v>
       </c>
       <c r="O30">
-        <v>28970</v>
+        <v>30972</v>
       </c>
       <c r="P30">
         <v>86935</v>
@@ -2410,31 +2409,31 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>87370</v>
+        <v>88469</v>
       </c>
       <c r="H31">
-        <v>1003</v>
+        <v>632</v>
       </c>
       <c r="I31">
         <v>77</v>
       </c>
       <c r="J31">
-        <v>316</v>
+        <v>6</v>
       </c>
       <c r="K31">
         <v>0</v>
       </c>
       <c r="L31">
-        <v>40909</v>
+        <v>41667</v>
       </c>
       <c r="M31">
         <v>24</v>
       </c>
       <c r="N31">
-        <v>1698</v>
+        <v>1753</v>
       </c>
       <c r="O31">
-        <v>82030</v>
+        <v>83101</v>
       </c>
       <c r="P31">
         <v>81642</v>
@@ -2463,40 +2462,40 @@
         <v>0</v>
       </c>
       <c r="E32">
-        <v>46707</v>
+        <v>46709</v>
       </c>
       <c r="F32">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G32">
-        <v>28381</v>
+        <v>30337</v>
       </c>
       <c r="H32">
-        <v>14043</v>
+        <v>12284</v>
       </c>
       <c r="I32">
-        <v>579</v>
+        <v>507</v>
       </c>
       <c r="J32">
-        <v>451</v>
+        <v>99</v>
       </c>
       <c r="K32">
         <v>0</v>
       </c>
       <c r="L32">
-        <v>6125</v>
+        <v>6760</v>
       </c>
       <c r="M32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N32">
-        <v>347</v>
+        <v>523</v>
       </c>
       <c r="O32">
-        <v>23505</v>
+        <v>26804</v>
       </c>
       <c r="P32">
-        <v>16690</v>
+        <v>23456</v>
       </c>
       <c r="Q32">
         <v>11379</v>
@@ -2522,40 +2521,40 @@
         <v>0</v>
       </c>
       <c r="E33">
-        <v>40200</v>
+        <v>40220</v>
       </c>
       <c r="F33">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G33">
-        <v>27804</v>
+        <v>30501</v>
       </c>
       <c r="H33">
-        <v>9308</v>
+        <v>7125</v>
       </c>
       <c r="I33">
         <v>34</v>
       </c>
       <c r="J33">
-        <v>203</v>
+        <v>26</v>
       </c>
       <c r="K33">
         <v>0</v>
       </c>
       <c r="L33">
-        <v>3211</v>
+        <v>3584</v>
       </c>
       <c r="M33">
         <v>6</v>
       </c>
       <c r="N33">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O33">
-        <v>26272</v>
+        <v>28919</v>
       </c>
       <c r="P33">
-        <v>73301</v>
+        <v>73606</v>
       </c>
       <c r="Q33">
         <v>6678</v>
@@ -2581,37 +2580,37 @@
         <v>0</v>
       </c>
       <c r="E34">
-        <v>36478</v>
+        <v>36536</v>
       </c>
       <c r="F34">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="G34">
-        <v>25617</v>
+        <v>27640</v>
       </c>
       <c r="H34">
-        <v>10868</v>
+        <v>8845</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
       <c r="J34">
-        <v>387</v>
+        <v>138</v>
       </c>
       <c r="K34">
         <v>0</v>
       </c>
       <c r="L34">
-        <v>8517</v>
+        <v>9450</v>
       </c>
       <c r="M34">
         <v>1</v>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O34">
-        <v>22125</v>
+        <v>25737</v>
       </c>
       <c r="P34">
         <v>74626</v>
@@ -2640,37 +2639,37 @@
         <v>0</v>
       </c>
       <c r="E35">
-        <v>33522</v>
+        <v>33537</v>
       </c>
       <c r="F35">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="G35">
-        <v>25350</v>
+        <v>26742</v>
       </c>
       <c r="H35">
-        <v>6881</v>
+        <v>5810</v>
       </c>
       <c r="I35">
         <v>1</v>
       </c>
       <c r="J35">
-        <v>285</v>
+        <v>184</v>
       </c>
       <c r="K35">
         <v>0</v>
       </c>
       <c r="L35">
-        <v>3599</v>
+        <v>4024</v>
       </c>
       <c r="M35">
         <v>0</v>
       </c>
       <c r="N35">
-        <v>149</v>
+        <v>197</v>
       </c>
       <c r="O35">
-        <v>23634</v>
+        <v>25436</v>
       </c>
       <c r="P35">
         <v>72020</v>
@@ -2714,22 +2713,22 @@
         <v>0</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36">
         <v>0</v>
       </c>
       <c r="L36">
-        <v>7294</v>
+        <v>7309</v>
       </c>
       <c r="M36">
         <v>0</v>
       </c>
       <c r="N36">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="O36">
-        <v>13067</v>
+        <v>16950</v>
       </c>
       <c r="P36">
         <v>60419</v>
@@ -2773,19 +2772,19 @@
         <v>0</v>
       </c>
       <c r="J37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37">
         <v>0</v>
       </c>
       <c r="L37">
-        <v>2309</v>
+        <v>2311</v>
       </c>
       <c r="M37">
         <v>0</v>
       </c>
       <c r="N37">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="O37">
         <v>17151</v>
@@ -2838,16 +2837,16 @@
         <v>0</v>
       </c>
       <c r="L38">
-        <v>4949</v>
+        <v>4950</v>
       </c>
       <c r="M38">
         <v>2</v>
       </c>
       <c r="N38">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="O38">
-        <v>24757</v>
+        <v>28039</v>
       </c>
       <c r="P38">
         <v>63038</v>
@@ -2891,13 +2890,13 @@
         <v>0</v>
       </c>
       <c r="J39">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K39">
         <v>0</v>
       </c>
       <c r="L39">
-        <v>4526</v>
+        <v>4528</v>
       </c>
       <c r="M39">
         <v>1</v>
@@ -2906,7 +2905,7 @@
         <v>234</v>
       </c>
       <c r="O39">
-        <v>20802</v>
+        <v>21132</v>
       </c>
       <c r="P39">
         <v>71133</v>
@@ -2941,22 +2940,22 @@
         <v>0</v>
       </c>
       <c r="G40">
-        <v>16586</v>
+        <v>16905</v>
       </c>
       <c r="H40">
-        <v>177</v>
+        <v>99</v>
       </c>
       <c r="I40">
         <v>0</v>
       </c>
       <c r="J40">
-        <v>297</v>
+        <v>72</v>
       </c>
       <c r="K40">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L40">
-        <v>1106</v>
+        <v>1417</v>
       </c>
       <c r="M40">
         <v>0</v>
@@ -2965,7 +2964,7 @@
         <v>25</v>
       </c>
       <c r="O40">
-        <v>15384</v>
+        <v>15781</v>
       </c>
       <c r="P40">
         <v>73242</v>
@@ -3000,31 +2999,31 @@
         <v>0</v>
       </c>
       <c r="G41">
-        <v>22091</v>
+        <v>22494</v>
       </c>
       <c r="H41">
-        <v>258</v>
+        <v>142</v>
       </c>
       <c r="I41">
         <v>0</v>
       </c>
       <c r="J41">
-        <v>276</v>
+        <v>27</v>
       </c>
       <c r="K41">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L41">
-        <v>680</v>
+        <v>1022</v>
       </c>
       <c r="M41">
         <v>0</v>
       </c>
       <c r="N41">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="O41">
-        <v>20793</v>
+        <v>21122</v>
       </c>
       <c r="P41">
         <v>85249</v>
@@ -3068,25 +3067,25 @@
         <v>0</v>
       </c>
       <c r="J42">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="K42">
         <v>0</v>
       </c>
       <c r="L42">
-        <v>6196</v>
+        <v>6198</v>
       </c>
       <c r="M42">
         <v>0</v>
       </c>
       <c r="N42">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O42">
-        <v>26532</v>
+        <v>26798</v>
       </c>
       <c r="P42">
-        <v>66010</v>
+        <v>68615</v>
       </c>
       <c r="Q42">
         <v>4713</v>
@@ -3127,13 +3126,13 @@
         <v>0</v>
       </c>
       <c r="J43">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="K43">
         <v>0</v>
       </c>
       <c r="L43">
-        <v>6721</v>
+        <v>6732</v>
       </c>
       <c r="M43">
         <v>1</v>
@@ -3142,10 +3141,10 @@
         <v>900</v>
       </c>
       <c r="O43">
-        <v>25153</v>
+        <v>26809</v>
       </c>
       <c r="P43">
-        <v>61445</v>
+        <v>63036</v>
       </c>
       <c r="Q43">
         <v>5271</v>
@@ -3177,31 +3176,31 @@
         <v>0</v>
       </c>
       <c r="G44">
-        <v>20779</v>
+        <v>21272</v>
       </c>
       <c r="H44">
-        <v>727</v>
+        <v>428</v>
       </c>
       <c r="I44">
         <v>0</v>
       </c>
       <c r="J44">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="K44">
         <v>0</v>
       </c>
       <c r="L44">
-        <v>6132</v>
+        <v>6301</v>
       </c>
       <c r="M44">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="N44">
-        <v>114</v>
+        <v>169</v>
       </c>
       <c r="O44">
-        <v>16479</v>
+        <v>18985</v>
       </c>
       <c r="P44">
         <v>68393</v>
@@ -3236,31 +3235,31 @@
         <v>0</v>
       </c>
       <c r="G45">
-        <v>16644</v>
+        <v>17057</v>
       </c>
       <c r="H45">
-        <v>1661</v>
+        <v>1429</v>
       </c>
       <c r="I45">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J45">
-        <v>394</v>
+        <v>21</v>
       </c>
       <c r="K45">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="L45">
-        <v>1576</v>
+        <v>1983</v>
       </c>
       <c r="M45">
         <v>10</v>
       </c>
       <c r="N45">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="O45">
-        <v>14820</v>
+        <v>15190</v>
       </c>
       <c r="P45">
         <v>76002</v>
@@ -3295,31 +3294,31 @@
         <v>0</v>
       </c>
       <c r="G46">
-        <v>20891</v>
+        <v>21030</v>
       </c>
       <c r="H46">
-        <v>621</v>
+        <v>482</v>
       </c>
       <c r="I46">
         <v>0</v>
       </c>
       <c r="J46">
-        <v>475</v>
+        <v>61</v>
       </c>
       <c r="K46">
         <v>0</v>
       </c>
       <c r="L46">
-        <v>7363</v>
+        <v>7876</v>
       </c>
       <c r="M46">
         <v>1</v>
       </c>
       <c r="N46">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="O46">
-        <v>17090</v>
+        <v>18295</v>
       </c>
       <c r="P46">
         <v>64160</v>
@@ -3354,16 +3353,16 @@
         <v>0</v>
       </c>
       <c r="G47">
-        <v>21098</v>
+        <v>21501</v>
       </c>
       <c r="H47">
-        <v>1035</v>
+        <v>864</v>
       </c>
       <c r="I47">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="J47">
-        <v>18</v>
+        <v>146</v>
       </c>
       <c r="K47">
         <v>0</v>
@@ -3375,10 +3374,10 @@
         <v>1</v>
       </c>
       <c r="N47">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="O47">
-        <v>19810</v>
+        <v>20166</v>
       </c>
       <c r="P47">
         <v>49875</v>
@@ -3413,16 +3412,16 @@
         <v>47</v>
       </c>
       <c r="G48">
-        <v>19548</v>
+        <v>19561</v>
       </c>
       <c r="H48">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="I48">
         <v>3</v>
       </c>
       <c r="J48">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K48">
         <v>0</v>
@@ -3434,10 +3433,10 @@
         <v>4</v>
       </c>
       <c r="N48">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="O48">
-        <v>19198</v>
+        <v>19248</v>
       </c>
       <c r="P48">
         <v>54142</v>
@@ -3472,16 +3471,16 @@
         <v>19</v>
       </c>
       <c r="G49">
-        <v>19088</v>
+        <v>19548</v>
       </c>
       <c r="H49">
-        <v>1024</v>
+        <v>996</v>
       </c>
       <c r="I49">
         <v>114</v>
       </c>
       <c r="J49">
-        <v>20</v>
+        <v>272</v>
       </c>
       <c r="K49">
         <v>0</v>
@@ -3496,10 +3495,10 @@
         <v>313</v>
       </c>
       <c r="O49">
-        <v>17338</v>
+        <v>17546</v>
       </c>
       <c r="P49">
-        <v>50563</v>
+        <v>51231</v>
       </c>
       <c r="Q49">
         <v>5057</v>
@@ -3531,22 +3530,22 @@
         <v>0</v>
       </c>
       <c r="G50">
-        <v>21220</v>
+        <v>21469</v>
       </c>
       <c r="H50">
-        <v>583</v>
+        <v>445</v>
       </c>
       <c r="I50">
         <v>0</v>
       </c>
       <c r="J50">
-        <v>105</v>
+        <v>46</v>
       </c>
       <c r="K50">
         <v>0</v>
       </c>
       <c r="L50">
-        <v>3634</v>
+        <v>3800</v>
       </c>
       <c r="M50">
         <v>5</v>
@@ -3555,7 +3554,7 @@
         <v>11</v>
       </c>
       <c r="O50">
-        <v>20245</v>
+        <v>20393</v>
       </c>
       <c r="P50">
         <v>63298</v>
@@ -3590,31 +3589,31 @@
         <v>0</v>
       </c>
       <c r="G51">
-        <v>22587</v>
+        <v>22598</v>
       </c>
       <c r="H51">
-        <v>548</v>
+        <v>538</v>
       </c>
       <c r="I51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J51">
-        <v>193</v>
+        <v>1</v>
       </c>
       <c r="K51">
         <v>0</v>
       </c>
       <c r="L51">
-        <v>4324</v>
+        <v>4518</v>
       </c>
       <c r="M51">
         <v>11</v>
       </c>
       <c r="N51">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="O51">
-        <v>19385</v>
+        <v>19778</v>
       </c>
       <c r="P51">
         <v>71754</v>
@@ -3649,31 +3648,31 @@
         <v>0</v>
       </c>
       <c r="G52">
-        <v>20902</v>
+        <v>21002</v>
       </c>
       <c r="H52">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="I52">
         <v>0</v>
       </c>
       <c r="J52">
-        <v>318</v>
+        <v>14</v>
       </c>
       <c r="K52">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="L52">
-        <v>2403</v>
+        <v>2729</v>
       </c>
       <c r="M52">
         <v>1</v>
       </c>
       <c r="N52">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O52">
-        <v>20309</v>
+        <v>20341</v>
       </c>
       <c r="P52">
         <v>63986</v>
@@ -3717,19 +3716,19 @@
         <v>0</v>
       </c>
       <c r="J53">
-        <v>340</v>
+        <v>293</v>
       </c>
       <c r="K53">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="L53">
-        <v>3032</v>
+        <v>3129</v>
       </c>
       <c r="M53">
         <v>1</v>
       </c>
       <c r="N53">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="O53">
         <v>18565</v>
@@ -3767,31 +3766,31 @@
         <v>0</v>
       </c>
       <c r="G54">
-        <v>20367</v>
+        <v>20523</v>
       </c>
       <c r="H54">
-        <v>312</v>
+        <v>181</v>
       </c>
       <c r="I54">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="J54">
-        <v>592</v>
+        <v>578</v>
       </c>
       <c r="K54">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="L54">
-        <v>1737</v>
+        <v>1834</v>
       </c>
       <c r="M54">
         <v>5</v>
       </c>
       <c r="N54">
-        <v>254</v>
+        <v>282</v>
       </c>
       <c r="O54">
-        <v>17787</v>
+        <v>17872</v>
       </c>
       <c r="P54">
         <v>58440</v>
@@ -3826,31 +3825,31 @@
         <v>0</v>
       </c>
       <c r="G55">
-        <v>15992</v>
+        <v>15996</v>
       </c>
       <c r="H55">
+        <v>26</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>304</v>
+      </c>
+      <c r="K55">
         <v>30</v>
       </c>
-      <c r="I55">
-        <v>0</v>
-      </c>
-      <c r="J55">
-        <v>529</v>
-      </c>
-      <c r="K55">
-        <v>232</v>
-      </c>
       <c r="L55">
-        <v>1525</v>
+        <v>1704</v>
       </c>
       <c r="M55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N55">
         <v>88</v>
       </c>
       <c r="O55">
-        <v>15274</v>
+        <v>15472</v>
       </c>
       <c r="P55">
         <v>58215</v>
@@ -3885,16 +3884,16 @@
         <v>0</v>
       </c>
       <c r="G56">
-        <v>18883</v>
+        <v>19081</v>
       </c>
       <c r="H56">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="I56">
         <v>0</v>
       </c>
       <c r="J56">
-        <v>926</v>
+        <v>1018</v>
       </c>
       <c r="K56">
         <v>472</v>
@@ -3906,10 +3905,10 @@
         <v>2</v>
       </c>
       <c r="N56">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="O56">
-        <v>14479</v>
+        <v>14602</v>
       </c>
       <c r="P56">
         <v>46365</v>
@@ -3944,31 +3943,31 @@
         <v>0</v>
       </c>
       <c r="G57">
-        <v>21201</v>
+        <v>21207</v>
       </c>
       <c r="H57">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="I57">
         <v>0</v>
       </c>
       <c r="J57">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K57">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L57">
-        <v>1754</v>
+        <v>1774</v>
       </c>
       <c r="M57">
         <v>5</v>
       </c>
       <c r="N57">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O57">
-        <v>21022</v>
+        <v>21026</v>
       </c>
       <c r="P57">
         <v>61556</v>
@@ -4003,31 +4002,31 @@
         <v>0</v>
       </c>
       <c r="G58">
-        <v>21790</v>
+        <v>22004</v>
       </c>
       <c r="H58">
-        <v>426</v>
+        <v>272</v>
       </c>
       <c r="I58">
         <v>24</v>
       </c>
       <c r="J58">
-        <v>1657</v>
+        <v>1356</v>
       </c>
       <c r="K58">
-        <v>412</v>
+        <v>125</v>
       </c>
       <c r="L58">
-        <v>5726</v>
+        <v>6162</v>
       </c>
       <c r="M58">
         <v>3</v>
       </c>
       <c r="N58">
-        <v>300</v>
+        <v>357</v>
       </c>
       <c r="O58">
-        <v>15381</v>
+        <v>15508</v>
       </c>
       <c r="P58">
         <v>57577</v>
@@ -4121,31 +4120,31 @@
         <v>0</v>
       </c>
       <c r="G60">
-        <v>23330</v>
+        <v>23489</v>
       </c>
       <c r="H60">
-        <v>177</v>
+        <v>115</v>
       </c>
       <c r="I60">
         <v>0</v>
       </c>
       <c r="J60">
-        <v>360</v>
+        <v>11</v>
       </c>
       <c r="K60">
         <v>0</v>
       </c>
       <c r="L60">
-        <v>5232</v>
+        <v>5533</v>
       </c>
       <c r="M60">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N60">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="O60">
-        <v>21451</v>
+        <v>21564</v>
       </c>
       <c r="P60">
         <v>70140</v>
@@ -4189,16 +4188,16 @@
         <v>0</v>
       </c>
       <c r="J61">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="K61">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="L61">
-        <v>9875</v>
+        <v>9944</v>
       </c>
       <c r="M61">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="N61">
         <v>1</v>
@@ -4239,16 +4238,16 @@
         <v>0</v>
       </c>
       <c r="G62">
-        <v>15692</v>
+        <v>15760</v>
       </c>
       <c r="H62">
-        <v>88</v>
+        <v>23</v>
       </c>
       <c r="I62">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J62">
-        <v>658</v>
+        <v>669</v>
       </c>
       <c r="K62">
         <v>274</v>
@@ -4260,10 +4259,10 @@
         <v>11</v>
       </c>
       <c r="N62">
-        <v>402</v>
+        <v>454</v>
       </c>
       <c r="O62">
-        <v>14580</v>
+        <v>14588</v>
       </c>
       <c r="P62">
         <v>51334</v>
@@ -4298,16 +4297,16 @@
         <v>0</v>
       </c>
       <c r="G63">
-        <v>36672</v>
+        <v>36727</v>
       </c>
       <c r="H63">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I63">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="J63">
-        <v>75</v>
+        <v>239</v>
       </c>
       <c r="K63">
         <v>0</v>
@@ -4319,10 +4318,10 @@
         <v>35</v>
       </c>
       <c r="N63">
-        <v>868</v>
+        <v>897</v>
       </c>
       <c r="O63">
-        <v>31787</v>
+        <v>32100</v>
       </c>
       <c r="P63">
         <v>68691</v>
@@ -4357,31 +4356,31 @@
         <v>0</v>
       </c>
       <c r="G64">
-        <v>40556</v>
+        <v>41187</v>
       </c>
       <c r="H64">
-        <v>1227</v>
+        <v>709</v>
       </c>
       <c r="I64">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J64">
-        <v>307</v>
+        <v>107</v>
       </c>
       <c r="K64">
         <v>2</v>
       </c>
       <c r="L64">
-        <v>9179</v>
+        <v>9428</v>
       </c>
       <c r="M64">
         <v>8</v>
       </c>
       <c r="N64">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="O64">
-        <v>38054</v>
+        <v>39235</v>
       </c>
       <c r="P64">
         <v>60527</v>
@@ -4416,34 +4415,34 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>36388</v>
+        <v>37605</v>
       </c>
       <c r="H65">
-        <v>3434</v>
+        <v>2354</v>
       </c>
       <c r="I65">
-        <v>1121</v>
+        <v>1067</v>
       </c>
       <c r="J65">
-        <v>199</v>
+        <v>415</v>
       </c>
       <c r="K65">
         <v>0</v>
       </c>
       <c r="L65">
-        <v>11081</v>
+        <v>11643</v>
       </c>
       <c r="M65">
         <v>2</v>
       </c>
       <c r="N65">
-        <v>568</v>
+        <v>707</v>
       </c>
       <c r="O65">
-        <v>26066</v>
+        <v>26534</v>
       </c>
       <c r="P65">
-        <v>34611</v>
+        <v>37122</v>
       </c>
       <c r="Q65">
         <v>13284</v>
@@ -4475,31 +4474,31 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>55600</v>
+        <v>58140</v>
       </c>
       <c r="H66">
-        <v>6629</v>
+        <v>5052</v>
       </c>
       <c r="I66">
-        <v>272</v>
+        <v>209</v>
       </c>
       <c r="J66">
-        <v>217</v>
+        <v>96</v>
       </c>
       <c r="K66">
         <v>0</v>
       </c>
       <c r="L66">
-        <v>10764</v>
+        <v>11750</v>
       </c>
       <c r="M66">
         <v>2</v>
       </c>
       <c r="N66">
-        <v>1466</v>
+        <v>1717</v>
       </c>
       <c r="O66">
-        <v>49664</v>
+        <v>52742</v>
       </c>
       <c r="P66">
         <v>93810</v>
@@ -4534,31 +4533,31 @@
         <v>0</v>
       </c>
       <c r="G67">
-        <v>63395</v>
+        <v>64125</v>
       </c>
       <c r="H67">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I67">
-        <v>2646</v>
+        <v>2411</v>
       </c>
       <c r="J67">
-        <v>112</v>
+        <v>48</v>
       </c>
       <c r="K67">
         <v>0</v>
       </c>
       <c r="L67">
-        <v>17926</v>
+        <v>18320</v>
       </c>
       <c r="M67">
         <v>10</v>
       </c>
       <c r="N67">
-        <v>1241</v>
+        <v>1326</v>
       </c>
       <c r="O67">
-        <v>51810</v>
+        <v>56171</v>
       </c>
       <c r="P67">
         <v>78022</v>
@@ -4593,34 +4592,34 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>60512</v>
+        <v>60993</v>
       </c>
       <c r="H68">
-        <v>3818</v>
+        <v>3351</v>
       </c>
       <c r="I68">
-        <v>834</v>
+        <v>800</v>
       </c>
       <c r="J68">
-        <v>479</v>
+        <v>49</v>
       </c>
       <c r="K68">
         <v>0</v>
       </c>
       <c r="L68">
-        <v>15146</v>
+        <v>15820</v>
       </c>
       <c r="M68">
         <v>2</v>
       </c>
       <c r="N68">
-        <v>398</v>
+        <v>437</v>
       </c>
       <c r="O68">
-        <v>50416</v>
+        <v>50722</v>
       </c>
       <c r="P68">
-        <v>61388</v>
+        <v>61394</v>
       </c>
       <c r="Q68">
         <v>7850</v>
@@ -4652,31 +4651,31 @@
         <v>0</v>
       </c>
       <c r="G69">
-        <v>37690</v>
+        <v>38334</v>
       </c>
       <c r="H69">
-        <v>5580</v>
+        <v>5121</v>
       </c>
       <c r="I69">
-        <v>456</v>
+        <v>371</v>
       </c>
       <c r="J69">
-        <v>783</v>
+        <v>247</v>
       </c>
       <c r="K69">
         <v>0</v>
       </c>
       <c r="L69">
-        <v>14001</v>
+        <v>14976</v>
       </c>
       <c r="M69">
         <v>2</v>
       </c>
       <c r="N69">
-        <v>201</v>
+        <v>288</v>
       </c>
       <c r="O69">
-        <v>33139</v>
+        <v>34572</v>
       </c>
       <c r="P69">
         <v>34467</v>
@@ -4711,31 +4710,31 @@
         <v>0</v>
       </c>
       <c r="G70">
-        <v>44024</v>
+        <v>44560</v>
       </c>
       <c r="H70">
-        <v>1104</v>
+        <v>938</v>
       </c>
       <c r="I70">
-        <v>2262</v>
+        <v>1939</v>
       </c>
       <c r="J70">
-        <v>124</v>
+        <v>25</v>
       </c>
       <c r="K70">
         <v>0</v>
       </c>
       <c r="L70">
-        <v>17343</v>
+        <v>17677</v>
       </c>
       <c r="M70">
         <v>2</v>
       </c>
       <c r="N70">
-        <v>771</v>
+        <v>935</v>
       </c>
       <c r="O70">
-        <v>39707</v>
+        <v>40709</v>
       </c>
       <c r="P70">
         <v>42040</v>
@@ -4770,31 +4769,31 @@
         <v>0</v>
       </c>
       <c r="G71">
-        <v>46226</v>
+        <v>47309</v>
       </c>
       <c r="H71">
-        <v>3314</v>
+        <v>2324</v>
       </c>
       <c r="I71">
-        <v>1307</v>
+        <v>1232</v>
       </c>
       <c r="J71">
-        <v>69</v>
+        <v>144</v>
       </c>
       <c r="K71">
         <v>0</v>
       </c>
       <c r="L71">
-        <v>20901</v>
+        <v>21084</v>
       </c>
       <c r="M71">
         <v>1</v>
       </c>
       <c r="N71">
-        <v>2836</v>
+        <v>2871</v>
       </c>
       <c r="O71">
-        <v>34434</v>
+        <v>36837</v>
       </c>
       <c r="P71">
         <v>48896</v>
@@ -4829,31 +4828,31 @@
         <v>0</v>
       </c>
       <c r="G72">
-        <v>54461</v>
+        <v>55963</v>
       </c>
       <c r="H72">
-        <v>5501</v>
+        <v>4268</v>
       </c>
       <c r="I72">
-        <v>1418</v>
+        <v>1162</v>
       </c>
       <c r="J72">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="K72">
         <v>0</v>
       </c>
       <c r="L72">
-        <v>15731</v>
+        <v>15999</v>
       </c>
       <c r="M72">
         <v>9</v>
       </c>
       <c r="N72">
-        <v>697</v>
+        <v>1242</v>
       </c>
       <c r="O72">
-        <v>43450</v>
+        <v>44562</v>
       </c>
       <c r="P72">
         <v>85505</v>
@@ -4888,31 +4887,31 @@
         <v>0</v>
       </c>
       <c r="G73">
-        <v>48519</v>
+        <v>50699</v>
       </c>
       <c r="H73">
-        <v>10032</v>
+        <v>7888</v>
       </c>
       <c r="I73">
         <v>188</v>
       </c>
       <c r="J73">
-        <v>719</v>
+        <v>381</v>
       </c>
       <c r="K73">
         <v>0</v>
       </c>
       <c r="L73">
-        <v>9724</v>
+        <v>11067</v>
       </c>
       <c r="M73">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N73">
-        <v>617</v>
+        <v>760</v>
       </c>
       <c r="O73">
-        <v>42964</v>
+        <v>44973</v>
       </c>
       <c r="P73">
         <v>67550</v>
@@ -4939,40 +4938,40 @@
         <v>0</v>
       </c>
       <c r="E74">
-        <v>2429756</v>
+        <v>2430022</v>
       </c>
       <c r="F74">
-        <v>626</v>
+        <v>360</v>
       </c>
       <c r="G74">
-        <v>2092580</v>
+        <v>2151842</v>
       </c>
       <c r="H74">
-        <v>262847</v>
+        <v>213799</v>
       </c>
       <c r="I74">
-        <v>17336</v>
+        <v>14960</v>
       </c>
       <c r="J74">
-        <v>72726</v>
+        <v>66173</v>
       </c>
       <c r="K74">
-        <v>37711</v>
+        <v>34646</v>
       </c>
       <c r="L74">
-        <v>448162</v>
+        <v>469080</v>
       </c>
       <c r="M74">
-        <v>498</v>
+        <v>551</v>
       </c>
       <c r="N74">
-        <v>32749</v>
+        <v>36825</v>
       </c>
       <c r="O74">
-        <v>1806788</v>
+        <v>1889156</v>
       </c>
       <c r="P74">
-        <v>4405036</v>
+        <v>4456871</v>
       </c>
       <c r="Q74">
         <v>629567</v>

--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25125" windowHeight="12210"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -303,7 +303,7 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Notice &amp; Hearing Report Last Updated On : 27-08-2026 19:57:07</t>
+    <t>Notice &amp; Hearing Report Last Updated On : 29-08-2026 07:57:04</t>
   </si>
 </sst>
 </file>
@@ -816,19 +816,19 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>39772</v>
+        <v>41140</v>
       </c>
       <c r="H4">
-        <v>10252</v>
+        <v>9359</v>
       </c>
       <c r="I4">
         <v>9</v>
       </c>
       <c r="J4">
-        <v>6435</v>
+        <v>7010</v>
       </c>
       <c r="K4">
-        <v>2780</v>
+        <v>3677</v>
       </c>
       <c r="L4">
         <v>3773</v>
@@ -840,7 +840,7 @@
         <v>180</v>
       </c>
       <c r="O4">
-        <v>31110</v>
+        <v>32106</v>
       </c>
       <c r="P4">
         <v>53812</v>
@@ -875,31 +875,31 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>48035</v>
+        <v>48372</v>
       </c>
       <c r="H5">
-        <v>4529</v>
+        <v>4451</v>
       </c>
       <c r="I5">
         <v>2</v>
       </c>
       <c r="J5">
-        <v>3708</v>
+        <v>2830</v>
       </c>
       <c r="K5">
-        <v>1906</v>
+        <v>1693</v>
       </c>
       <c r="L5">
-        <v>3694</v>
+        <v>4585</v>
       </c>
       <c r="M5">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="N5">
         <v>371</v>
       </c>
       <c r="O5">
-        <v>43574</v>
+        <v>44616</v>
       </c>
       <c r="P5">
         <v>55483</v>
@@ -928,25 +928,25 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>39771</v>
+        <v>39773</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>27048</v>
+        <v>30129</v>
       </c>
       <c r="H6">
-        <v>8609</v>
+        <v>6552</v>
       </c>
       <c r="I6">
-        <v>49</v>
+        <v>217</v>
       </c>
       <c r="J6">
-        <v>2076</v>
+        <v>2377</v>
       </c>
       <c r="K6">
-        <v>1096</v>
+        <v>1219</v>
       </c>
       <c r="L6">
         <v>1836</v>
@@ -955,13 +955,13 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="O6">
-        <v>22946</v>
+        <v>25764</v>
       </c>
       <c r="P6">
-        <v>53017</v>
+        <v>54584</v>
       </c>
       <c r="Q6">
         <v>17918</v>
@@ -993,19 +993,19 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>35902</v>
+        <v>36922</v>
       </c>
       <c r="H7">
-        <v>3325</v>
+        <v>2305</v>
       </c>
       <c r="I7">
         <v>236</v>
       </c>
       <c r="J7">
-        <v>4162</v>
+        <v>4176</v>
       </c>
       <c r="K7">
-        <v>3233</v>
+        <v>3504</v>
       </c>
       <c r="L7">
         <v>1443</v>
@@ -1014,10 +1014,10 @@
         <v>29</v>
       </c>
       <c r="N7">
-        <v>1249</v>
+        <v>1297</v>
       </c>
       <c r="O7">
-        <v>29955</v>
+        <v>30913</v>
       </c>
       <c r="P7">
         <v>77581</v>
@@ -1052,19 +1052,19 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>26777</v>
+        <v>29644</v>
       </c>
       <c r="H8">
-        <v>13775</v>
+        <v>10908</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>8696</v>
+        <v>8903</v>
       </c>
       <c r="K8">
-        <v>5372</v>
+        <v>6358</v>
       </c>
       <c r="L8">
         <v>4300</v>
@@ -1073,13 +1073,13 @@
         <v>16</v>
       </c>
       <c r="N8">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="O8">
-        <v>14296</v>
+        <v>20108</v>
       </c>
       <c r="P8">
-        <v>32770</v>
+        <v>37523</v>
       </c>
       <c r="Q8">
         <v>20902</v>
@@ -1111,19 +1111,19 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>35150</v>
+        <v>35831</v>
       </c>
       <c r="H9">
-        <v>7761</v>
+        <v>7081</v>
       </c>
       <c r="I9">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="J9">
-        <v>3306</v>
+        <v>3411</v>
       </c>
       <c r="K9">
-        <v>2688</v>
+        <v>2808</v>
       </c>
       <c r="L9">
         <v>2601</v>
@@ -1135,10 +1135,10 @@
         <v>289</v>
       </c>
       <c r="O9">
-        <v>29979</v>
+        <v>30555</v>
       </c>
       <c r="P9">
-        <v>66749</v>
+        <v>66897</v>
       </c>
       <c r="Q9">
         <v>18214</v>
@@ -1170,37 +1170,37 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>31865</v>
+        <v>33537</v>
       </c>
       <c r="H10">
-        <v>4662</v>
+        <v>2999</v>
       </c>
       <c r="I10">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J10">
-        <v>2417</v>
+        <v>2072</v>
       </c>
       <c r="K10">
-        <v>1175</v>
+        <v>1260</v>
       </c>
       <c r="L10">
-        <v>7371</v>
+        <v>8033</v>
       </c>
       <c r="M10">
         <v>13</v>
       </c>
       <c r="N10">
-        <v>370</v>
+        <v>406</v>
       </c>
       <c r="O10">
-        <v>23629</v>
+        <v>24960</v>
       </c>
       <c r="P10">
         <v>48109</v>
       </c>
       <c r="Q10">
-        <v>9516</v>
+        <v>9511</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -1229,19 +1229,19 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>41323</v>
+        <v>42237</v>
       </c>
       <c r="H11">
-        <v>8318</v>
+        <v>7925</v>
       </c>
       <c r="I11">
-        <v>462</v>
+        <v>532</v>
       </c>
       <c r="J11">
-        <v>5267</v>
+        <v>5614</v>
       </c>
       <c r="K11">
-        <v>2090</v>
+        <v>2640</v>
       </c>
       <c r="L11">
         <v>1369</v>
@@ -1250,10 +1250,10 @@
         <v>20</v>
       </c>
       <c r="N11">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O11">
-        <v>34265</v>
+        <v>34831</v>
       </c>
       <c r="P11">
         <v>84443</v>
@@ -1288,19 +1288,19 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>31186</v>
+        <v>34194</v>
       </c>
       <c r="H12">
-        <v>9260</v>
+        <v>6271</v>
       </c>
       <c r="I12">
-        <v>156</v>
+        <v>189</v>
       </c>
       <c r="J12">
-        <v>8468</v>
+        <v>8918</v>
       </c>
       <c r="K12">
-        <v>5996</v>
+        <v>7074</v>
       </c>
       <c r="L12">
         <v>489</v>
@@ -1309,13 +1309,13 @@
         <v>2</v>
       </c>
       <c r="N12">
-        <v>537</v>
+        <v>583</v>
       </c>
       <c r="O12">
-        <v>21880</v>
+        <v>24416</v>
       </c>
       <c r="P12">
-        <v>62789</v>
+        <v>66685</v>
       </c>
       <c r="Q12">
         <v>17907</v>
@@ -1341,25 +1341,25 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>37025</v>
+        <v>37026</v>
       </c>
       <c r="F13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G13">
-        <v>28653</v>
+        <v>31344</v>
       </c>
       <c r="H13">
-        <v>7317</v>
+        <v>5436</v>
       </c>
       <c r="I13">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J13">
-        <v>4324</v>
+        <v>4984</v>
       </c>
       <c r="K13">
-        <v>1965</v>
+        <v>2274</v>
       </c>
       <c r="L13">
         <v>717</v>
@@ -1368,13 +1368,13 @@
         <v>0</v>
       </c>
       <c r="N13">
-        <v>2045</v>
+        <v>2686</v>
       </c>
       <c r="O13">
-        <v>21631</v>
+        <v>23063</v>
       </c>
       <c r="P13">
-        <v>56590</v>
+        <v>56565</v>
       </c>
       <c r="Q13">
         <v>16822</v>
@@ -1406,19 +1406,19 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>32807</v>
+        <v>34677</v>
       </c>
       <c r="H14">
-        <v>10566</v>
+        <v>10285</v>
       </c>
       <c r="I14">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="J14">
-        <v>8929</v>
+        <v>9213</v>
       </c>
       <c r="K14">
-        <v>5438</v>
+        <v>6275</v>
       </c>
       <c r="L14">
         <v>1781</v>
@@ -1427,13 +1427,13 @@
         <v>57</v>
       </c>
       <c r="N14">
-        <v>783</v>
+        <v>1247</v>
       </c>
       <c r="O14">
-        <v>21694</v>
+        <v>22817</v>
       </c>
       <c r="P14">
-        <v>54138</v>
+        <v>55446</v>
       </c>
       <c r="Q14">
         <v>20044</v>
@@ -1465,37 +1465,37 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>41510</v>
+        <v>41808</v>
       </c>
       <c r="H15">
-        <v>1193</v>
+        <v>895</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15">
-        <v>8921</v>
+        <v>8968</v>
       </c>
       <c r="M15">
         <v>0</v>
       </c>
       <c r="N15">
-        <v>2529</v>
+        <v>2691</v>
       </c>
       <c r="O15">
-        <v>38843</v>
+        <v>38955</v>
       </c>
       <c r="P15">
         <v>67178</v>
       </c>
       <c r="Q15">
-        <v>4949</v>
+        <v>4892</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -1518,40 +1518,40 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>25548</v>
+        <v>25549</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16">
-        <v>22758</v>
+        <v>23267</v>
       </c>
       <c r="H16">
-        <v>1903</v>
+        <v>1660</v>
       </c>
       <c r="I16">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="J16">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
       <c r="L16">
-        <v>12504</v>
+        <v>12946</v>
       </c>
       <c r="M16">
         <v>1</v>
       </c>
       <c r="N16">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="O16">
-        <v>19653</v>
+        <v>19749</v>
       </c>
       <c r="P16">
-        <v>67815</v>
+        <v>68193</v>
       </c>
       <c r="Q16">
         <v>5208</v>
@@ -1592,28 +1592,28 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K17">
         <v>0</v>
       </c>
       <c r="L17">
-        <v>9249</v>
+        <v>9287</v>
       </c>
       <c r="M17">
         <v>2</v>
       </c>
       <c r="N17">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="O17">
-        <v>27219</v>
+        <v>27276</v>
       </c>
       <c r="P17">
         <v>65458</v>
       </c>
       <c r="Q17">
-        <v>5441</v>
+        <v>5418</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -1642,37 +1642,37 @@
         <v>26</v>
       </c>
       <c r="G18">
-        <v>47513</v>
+        <v>47631</v>
       </c>
       <c r="H18">
-        <v>306</v>
+        <v>188</v>
       </c>
       <c r="I18">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J18">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K18">
         <v>0</v>
       </c>
       <c r="L18">
-        <v>7736</v>
+        <v>7788</v>
       </c>
       <c r="M18">
         <v>3</v>
       </c>
       <c r="N18">
-        <v>1867</v>
+        <v>1873</v>
       </c>
       <c r="O18">
-        <v>43600</v>
+        <v>43869</v>
       </c>
       <c r="P18">
         <v>70738</v>
       </c>
       <c r="Q18">
-        <v>6867</v>
+        <v>6857</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -1695,43 +1695,43 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>56392</v>
+        <v>56399</v>
       </c>
       <c r="F19">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="G19">
-        <v>54360</v>
+        <v>55094</v>
       </c>
       <c r="H19">
-        <v>1932</v>
+        <v>1249</v>
       </c>
       <c r="I19">
-        <v>194</v>
+        <v>147</v>
       </c>
       <c r="J19">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="K19">
         <v>0</v>
       </c>
       <c r="L19">
-        <v>14440</v>
+        <v>14722</v>
       </c>
       <c r="M19">
         <v>1</v>
       </c>
       <c r="N19">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="O19">
-        <v>48800</v>
+        <v>50038</v>
       </c>
       <c r="P19">
         <v>106226</v>
       </c>
       <c r="Q19">
-        <v>6158</v>
+        <v>6151</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -1760,37 +1760,37 @@
         <v>1</v>
       </c>
       <c r="G20">
-        <v>34441</v>
+        <v>34518</v>
       </c>
       <c r="H20">
-        <v>573</v>
+        <v>496</v>
       </c>
       <c r="I20">
         <v>3</v>
       </c>
       <c r="J20">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="K20">
         <v>0</v>
       </c>
       <c r="L20">
-        <v>5831</v>
+        <v>5930</v>
       </c>
       <c r="M20">
         <v>5</v>
       </c>
       <c r="N20">
-        <v>371</v>
+        <v>388</v>
       </c>
       <c r="O20">
-        <v>33245</v>
+        <v>33390</v>
       </c>
       <c r="P20">
         <v>75794</v>
       </c>
       <c r="Q20">
-        <v>9014</v>
+        <v>9010</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -1878,16 +1878,16 @@
         <v>0</v>
       </c>
       <c r="G22">
-        <v>18657</v>
+        <v>18667</v>
       </c>
       <c r="H22">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I22">
         <v>0</v>
       </c>
       <c r="J22">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -1899,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="N22">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="O22">
         <v>17612</v>
@@ -2026,7 +2026,7 @@
         <v>65629</v>
       </c>
       <c r="Q24">
-        <v>3497</v>
+        <v>3496</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -2085,7 +2085,7 @@
         <v>57533</v>
       </c>
       <c r="Q25">
-        <v>3236</v>
+        <v>3232</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -2114,16 +2114,16 @@
         <v>0</v>
       </c>
       <c r="G26">
-        <v>17413</v>
+        <v>17483</v>
       </c>
       <c r="H26">
-        <v>144</v>
+        <v>74</v>
       </c>
       <c r="I26">
         <v>0</v>
       </c>
       <c r="J26">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K26">
         <v>0</v>
@@ -2135,10 +2135,10 @@
         <v>3</v>
       </c>
       <c r="N26">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="O26">
-        <v>16962</v>
+        <v>17187</v>
       </c>
       <c r="P26">
         <v>66594</v>
@@ -2173,16 +2173,16 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>34440</v>
+        <v>34590</v>
       </c>
       <c r="H27">
-        <v>7720</v>
+        <v>8662</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="K27">
         <v>0</v>
@@ -2197,7 +2197,7 @@
         <v>56</v>
       </c>
       <c r="O27">
-        <v>33155</v>
+        <v>33293</v>
       </c>
       <c r="P27">
         <v>48916</v>
@@ -2232,16 +2232,16 @@
         <v>79</v>
       </c>
       <c r="G28">
-        <v>29232</v>
+        <v>31505</v>
       </c>
       <c r="H28">
-        <v>20906</v>
+        <v>20949</v>
       </c>
       <c r="I28">
         <v>37</v>
       </c>
       <c r="J28">
-        <v>157</v>
+        <v>511</v>
       </c>
       <c r="K28">
         <v>0</v>
@@ -2253,16 +2253,16 @@
         <v>11</v>
       </c>
       <c r="N28">
-        <v>520</v>
+        <v>531</v>
       </c>
       <c r="O28">
-        <v>25507</v>
+        <v>27466</v>
       </c>
       <c r="P28">
         <v>80639</v>
       </c>
       <c r="Q28">
-        <v>14117</v>
+        <v>14114</v>
       </c>
       <c r="R28">
         <v>0</v>
@@ -2291,16 +2291,16 @@
         <v>0</v>
       </c>
       <c r="G29">
-        <v>40605</v>
+        <v>41317</v>
       </c>
       <c r="H29">
-        <v>6003</v>
+        <v>5338</v>
       </c>
       <c r="I29">
-        <v>251</v>
+        <v>380</v>
       </c>
       <c r="J29">
-        <v>98</v>
+        <v>288</v>
       </c>
       <c r="K29">
         <v>0</v>
@@ -2312,10 +2312,10 @@
         <v>3</v>
       </c>
       <c r="N29">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="O29">
-        <v>35409</v>
+        <v>36127</v>
       </c>
       <c r="P29">
         <v>83837</v>
@@ -2350,16 +2350,16 @@
         <v>19</v>
       </c>
       <c r="G30">
-        <v>34260</v>
+        <v>35253</v>
       </c>
       <c r="H30">
-        <v>11716</v>
+        <v>9932</v>
       </c>
       <c r="I30">
-        <v>2198</v>
+        <v>3775</v>
       </c>
       <c r="J30">
-        <v>338</v>
+        <v>943</v>
       </c>
       <c r="K30">
         <v>0</v>
@@ -2371,10 +2371,10 @@
         <v>4</v>
       </c>
       <c r="N30">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O30">
-        <v>30972</v>
+        <v>32122</v>
       </c>
       <c r="P30">
         <v>86935</v>
@@ -2409,16 +2409,16 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>88469</v>
+        <v>89024</v>
       </c>
       <c r="H31">
-        <v>632</v>
+        <v>976</v>
       </c>
       <c r="I31">
         <v>77</v>
       </c>
       <c r="J31">
-        <v>6</v>
+        <v>396</v>
       </c>
       <c r="K31">
         <v>0</v>
@@ -2433,7 +2433,7 @@
         <v>1753</v>
       </c>
       <c r="O31">
-        <v>83101</v>
+        <v>83389</v>
       </c>
       <c r="P31">
         <v>81642</v>
@@ -2468,16 +2468,16 @@
         <v>19</v>
       </c>
       <c r="G32">
-        <v>30337</v>
+        <v>31750</v>
       </c>
       <c r="H32">
-        <v>12284</v>
+        <v>14576</v>
       </c>
       <c r="I32">
-        <v>507</v>
+        <v>386</v>
       </c>
       <c r="J32">
-        <v>99</v>
+        <v>366</v>
       </c>
       <c r="K32">
         <v>0</v>
@@ -2489,13 +2489,13 @@
         <v>8</v>
       </c>
       <c r="N32">
-        <v>523</v>
+        <v>688</v>
       </c>
       <c r="O32">
-        <v>26804</v>
+        <v>28817</v>
       </c>
       <c r="P32">
-        <v>23456</v>
+        <v>38759</v>
       </c>
       <c r="Q32">
         <v>11379</v>
@@ -2521,22 +2521,22 @@
         <v>0</v>
       </c>
       <c r="E33">
-        <v>40220</v>
+        <v>40223</v>
       </c>
       <c r="F33">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G33">
-        <v>30501</v>
+        <v>32586</v>
       </c>
       <c r="H33">
-        <v>7125</v>
+        <v>6599</v>
       </c>
       <c r="I33">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="J33">
-        <v>26</v>
+        <v>271</v>
       </c>
       <c r="K33">
         <v>0</v>
@@ -2548,10 +2548,10 @@
         <v>6</v>
       </c>
       <c r="N33">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="O33">
-        <v>28919</v>
+        <v>31026</v>
       </c>
       <c r="P33">
         <v>73606</v>
@@ -2580,22 +2580,22 @@
         <v>0</v>
       </c>
       <c r="E34">
-        <v>36536</v>
+        <v>36542</v>
       </c>
       <c r="F34">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G34">
-        <v>27640</v>
+        <v>28092</v>
       </c>
       <c r="H34">
-        <v>8845</v>
+        <v>8450</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
       <c r="J34">
-        <v>138</v>
+        <v>239</v>
       </c>
       <c r="K34">
         <v>0</v>
@@ -2610,7 +2610,7 @@
         <v>1</v>
       </c>
       <c r="O34">
-        <v>25737</v>
+        <v>26115</v>
       </c>
       <c r="P34">
         <v>74626</v>
@@ -2645,16 +2645,16 @@
         <v>27</v>
       </c>
       <c r="G35">
-        <v>26742</v>
+        <v>27779</v>
       </c>
       <c r="H35">
-        <v>5810</v>
+        <v>5047</v>
       </c>
       <c r="I35">
         <v>1</v>
       </c>
       <c r="J35">
-        <v>184</v>
+        <v>1187</v>
       </c>
       <c r="K35">
         <v>0</v>
@@ -2666,10 +2666,10 @@
         <v>0</v>
       </c>
       <c r="N35">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="O35">
-        <v>25436</v>
+        <v>25651</v>
       </c>
       <c r="P35">
         <v>72020</v>
@@ -2713,13 +2713,13 @@
         <v>0</v>
       </c>
       <c r="J36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K36">
         <v>0</v>
       </c>
       <c r="L36">
-        <v>7309</v>
+        <v>7310</v>
       </c>
       <c r="M36">
         <v>0</v>
@@ -2728,7 +2728,7 @@
         <v>949</v>
       </c>
       <c r="O36">
-        <v>16950</v>
+        <v>19914</v>
       </c>
       <c r="P36">
         <v>60419</v>
@@ -2940,16 +2940,16 @@
         <v>0</v>
       </c>
       <c r="G40">
-        <v>16905</v>
+        <v>17452</v>
       </c>
       <c r="H40">
-        <v>99</v>
+        <v>168</v>
       </c>
       <c r="I40">
         <v>0</v>
       </c>
       <c r="J40">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="K40">
         <v>0</v>
@@ -2961,10 +2961,10 @@
         <v>0</v>
       </c>
       <c r="N40">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="O40">
-        <v>15781</v>
+        <v>16308</v>
       </c>
       <c r="P40">
         <v>73242</v>
@@ -2999,16 +2999,16 @@
         <v>0</v>
       </c>
       <c r="G41">
-        <v>22494</v>
+        <v>22715</v>
       </c>
       <c r="H41">
-        <v>142</v>
+        <v>33</v>
       </c>
       <c r="I41">
         <v>0</v>
       </c>
       <c r="J41">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="K41">
         <v>0</v>
@@ -3020,10 +3020,10 @@
         <v>0</v>
       </c>
       <c r="N41">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="O41">
-        <v>21122</v>
+        <v>21339</v>
       </c>
       <c r="P41">
         <v>85249</v>
@@ -3067,13 +3067,13 @@
         <v>0</v>
       </c>
       <c r="J42">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="K42">
         <v>0</v>
       </c>
       <c r="L42">
-        <v>6198</v>
+        <v>6258</v>
       </c>
       <c r="M42">
         <v>0</v>
@@ -3082,7 +3082,7 @@
         <v>418</v>
       </c>
       <c r="O42">
-        <v>26798</v>
+        <v>26842</v>
       </c>
       <c r="P42">
         <v>68615</v>
@@ -3126,28 +3126,28 @@
         <v>0</v>
       </c>
       <c r="J43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43">
         <v>0</v>
       </c>
       <c r="L43">
-        <v>6732</v>
+        <v>6733</v>
       </c>
       <c r="M43">
         <v>1</v>
       </c>
       <c r="N43">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="O43">
-        <v>26809</v>
+        <v>27959</v>
       </c>
       <c r="P43">
         <v>63036</v>
       </c>
       <c r="Q43">
-        <v>5271</v>
+        <v>5260</v>
       </c>
       <c r="R43">
         <v>0</v>
@@ -3176,31 +3176,31 @@
         <v>0</v>
       </c>
       <c r="G44">
-        <v>21272</v>
+        <v>21380</v>
       </c>
       <c r="H44">
-        <v>428</v>
+        <v>519</v>
       </c>
       <c r="I44">
         <v>0</v>
       </c>
       <c r="J44">
-        <v>98</v>
+        <v>46</v>
       </c>
       <c r="K44">
         <v>0</v>
       </c>
       <c r="L44">
-        <v>6301</v>
+        <v>6409</v>
       </c>
       <c r="M44">
         <v>12</v>
       </c>
       <c r="N44">
-        <v>169</v>
+        <v>197</v>
       </c>
       <c r="O44">
-        <v>18985</v>
+        <v>19142</v>
       </c>
       <c r="P44">
         <v>68393</v>
@@ -3235,16 +3235,16 @@
         <v>0</v>
       </c>
       <c r="G45">
-        <v>17057</v>
+        <v>17486</v>
       </c>
       <c r="H45">
-        <v>1429</v>
+        <v>1526</v>
       </c>
       <c r="I45">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J45">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="K45">
         <v>0</v>
@@ -3256,10 +3256,10 @@
         <v>10</v>
       </c>
       <c r="N45">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="O45">
-        <v>15190</v>
+        <v>15685</v>
       </c>
       <c r="P45">
         <v>76002</v>
@@ -3353,19 +3353,19 @@
         <v>0</v>
       </c>
       <c r="G47">
-        <v>21501</v>
+        <v>21689</v>
       </c>
       <c r="H47">
-        <v>864</v>
+        <v>699</v>
       </c>
       <c r="I47">
         <v>27</v>
       </c>
       <c r="J47">
-        <v>146</v>
+        <v>334</v>
       </c>
       <c r="K47">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L47">
         <v>1913</v>
@@ -3377,7 +3377,7 @@
         <v>109</v>
       </c>
       <c r="O47">
-        <v>20166</v>
+        <v>20192</v>
       </c>
       <c r="P47">
         <v>49875</v>
@@ -3424,7 +3424,7 @@
         <v>11</v>
       </c>
       <c r="K48">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L48">
         <v>3757</v>
@@ -3471,16 +3471,16 @@
         <v>19</v>
       </c>
       <c r="G49">
-        <v>19548</v>
+        <v>19865</v>
       </c>
       <c r="H49">
-        <v>996</v>
+        <v>888</v>
       </c>
       <c r="I49">
-        <v>114</v>
+        <v>241</v>
       </c>
       <c r="J49">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="K49">
         <v>0</v>
@@ -3495,10 +3495,10 @@
         <v>313</v>
       </c>
       <c r="O49">
-        <v>17546</v>
+        <v>17851</v>
       </c>
       <c r="P49">
-        <v>51231</v>
+        <v>51751</v>
       </c>
       <c r="Q49">
         <v>5057</v>
@@ -3530,22 +3530,22 @@
         <v>0</v>
       </c>
       <c r="G50">
-        <v>21469</v>
+        <v>21512</v>
       </c>
       <c r="H50">
-        <v>445</v>
+        <v>424</v>
       </c>
       <c r="I50">
         <v>0</v>
       </c>
       <c r="J50">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="K50">
         <v>0</v>
       </c>
       <c r="L50">
-        <v>3800</v>
+        <v>3858</v>
       </c>
       <c r="M50">
         <v>5</v>
@@ -3554,7 +3554,7 @@
         <v>11</v>
       </c>
       <c r="O50">
-        <v>20393</v>
+        <v>20480</v>
       </c>
       <c r="P50">
         <v>63298</v>
@@ -3589,22 +3589,22 @@
         <v>0</v>
       </c>
       <c r="G51">
-        <v>22598</v>
+        <v>22758</v>
       </c>
       <c r="H51">
-        <v>538</v>
+        <v>637</v>
       </c>
       <c r="I51">
         <v>2</v>
       </c>
       <c r="J51">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="K51">
         <v>0</v>
       </c>
       <c r="L51">
-        <v>4518</v>
+        <v>4527</v>
       </c>
       <c r="M51">
         <v>11</v>
@@ -3613,7 +3613,7 @@
         <v>65</v>
       </c>
       <c r="O51">
-        <v>19778</v>
+        <v>20336</v>
       </c>
       <c r="P51">
         <v>71754</v>
@@ -3648,16 +3648,16 @@
         <v>0</v>
       </c>
       <c r="G52">
-        <v>21002</v>
+        <v>21018</v>
       </c>
       <c r="H52">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="I52">
         <v>0</v>
       </c>
       <c r="J52">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="K52">
         <v>1</v>
@@ -3672,7 +3672,7 @@
         <v>42</v>
       </c>
       <c r="O52">
-        <v>20341</v>
+        <v>20372</v>
       </c>
       <c r="P52">
         <v>63986</v>
@@ -3719,7 +3719,7 @@
         <v>293</v>
       </c>
       <c r="K53">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="L53">
         <v>3129</v>
@@ -3766,31 +3766,31 @@
         <v>0</v>
       </c>
       <c r="G54">
-        <v>20523</v>
+        <v>20528</v>
       </c>
       <c r="H54">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I54">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J54">
-        <v>578</v>
+        <v>443</v>
       </c>
       <c r="K54">
-        <v>1</v>
+        <v>109</v>
       </c>
       <c r="L54">
-        <v>1834</v>
+        <v>1947</v>
       </c>
       <c r="M54">
         <v>5</v>
       </c>
       <c r="N54">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="O54">
-        <v>17872</v>
+        <v>17874</v>
       </c>
       <c r="P54">
         <v>58440</v>
@@ -3825,19 +3825,19 @@
         <v>0</v>
       </c>
       <c r="G55">
-        <v>15996</v>
+        <v>15997</v>
       </c>
       <c r="H55">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I55">
         <v>0</v>
       </c>
       <c r="J55">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="K55">
-        <v>30</v>
+        <v>128</v>
       </c>
       <c r="L55">
         <v>1704</v>
@@ -3846,7 +3846,7 @@
         <v>1</v>
       </c>
       <c r="N55">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O55">
         <v>15472</v>
@@ -3884,7 +3884,7 @@
         <v>0</v>
       </c>
       <c r="G56">
-        <v>19081</v>
+        <v>19084</v>
       </c>
       <c r="H56">
         <v>82</v>
@@ -3893,13 +3893,13 @@
         <v>0</v>
       </c>
       <c r="J56">
-        <v>1018</v>
+        <v>908</v>
       </c>
       <c r="K56">
-        <v>472</v>
+        <v>549</v>
       </c>
       <c r="L56">
-        <v>2788</v>
+        <v>2904</v>
       </c>
       <c r="M56">
         <v>2</v>
@@ -3908,7 +3908,7 @@
         <v>385</v>
       </c>
       <c r="O56">
-        <v>14602</v>
+        <v>14604</v>
       </c>
       <c r="P56">
         <v>46365</v>
@@ -3943,16 +3943,16 @@
         <v>0</v>
       </c>
       <c r="G57">
-        <v>21207</v>
+        <v>21212</v>
       </c>
       <c r="H57">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="I57">
         <v>0</v>
       </c>
       <c r="J57">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="K57">
         <v>0</v>
@@ -3967,7 +3967,7 @@
         <v>37</v>
       </c>
       <c r="O57">
-        <v>21026</v>
+        <v>21030</v>
       </c>
       <c r="P57">
         <v>61556</v>
@@ -4008,13 +4008,13 @@
         <v>272</v>
       </c>
       <c r="I58">
-        <v>24</v>
+        <v>143</v>
       </c>
       <c r="J58">
         <v>1356</v>
       </c>
       <c r="K58">
-        <v>125</v>
+        <v>276</v>
       </c>
       <c r="L58">
         <v>6162</v>
@@ -4026,7 +4026,7 @@
         <v>357</v>
       </c>
       <c r="O58">
-        <v>15508</v>
+        <v>16858</v>
       </c>
       <c r="P58">
         <v>57577</v>
@@ -4120,16 +4120,16 @@
         <v>0</v>
       </c>
       <c r="G60">
-        <v>23489</v>
+        <v>23592</v>
       </c>
       <c r="H60">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="I60">
         <v>0</v>
       </c>
       <c r="J60">
-        <v>11</v>
+        <v>120</v>
       </c>
       <c r="K60">
         <v>0</v>
@@ -4141,10 +4141,10 @@
         <v>7</v>
       </c>
       <c r="N60">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="O60">
-        <v>21564</v>
+        <v>21653</v>
       </c>
       <c r="P60">
         <v>70140</v>
@@ -4238,28 +4238,28 @@
         <v>0</v>
       </c>
       <c r="G62">
-        <v>15760</v>
+        <v>15783</v>
       </c>
       <c r="H62">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I62">
         <v>17</v>
       </c>
       <c r="J62">
-        <v>669</v>
+        <v>352</v>
       </c>
       <c r="K62">
-        <v>274</v>
+        <v>234</v>
       </c>
       <c r="L62">
-        <v>3513</v>
+        <v>3690</v>
       </c>
       <c r="M62">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="N62">
-        <v>454</v>
+        <v>477</v>
       </c>
       <c r="O62">
         <v>14588</v>
@@ -4306,7 +4306,7 @@
         <v>19</v>
       </c>
       <c r="J63">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="K63">
         <v>0</v>
@@ -4356,19 +4356,19 @@
         <v>0</v>
       </c>
       <c r="G64">
-        <v>41187</v>
+        <v>41501</v>
       </c>
       <c r="H64">
-        <v>709</v>
+        <v>529</v>
       </c>
       <c r="I64">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J64">
-        <v>107</v>
+        <v>177</v>
       </c>
       <c r="K64">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L64">
         <v>9428</v>
@@ -4380,7 +4380,7 @@
         <v>257</v>
       </c>
       <c r="O64">
-        <v>39235</v>
+        <v>40629</v>
       </c>
       <c r="P64">
         <v>60527</v>
@@ -4415,34 +4415,34 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>37605</v>
+        <v>38246</v>
       </c>
       <c r="H65">
-        <v>2354</v>
+        <v>1832</v>
       </c>
       <c r="I65">
-        <v>1067</v>
+        <v>1252</v>
       </c>
       <c r="J65">
-        <v>415</v>
+        <v>159</v>
       </c>
       <c r="K65">
         <v>0</v>
       </c>
       <c r="L65">
-        <v>11643</v>
+        <v>12207</v>
       </c>
       <c r="M65">
         <v>2</v>
       </c>
       <c r="N65">
-        <v>707</v>
+        <v>717</v>
       </c>
       <c r="O65">
-        <v>26534</v>
+        <v>27217</v>
       </c>
       <c r="P65">
-        <v>37122</v>
+        <v>37163</v>
       </c>
       <c r="Q65">
         <v>13284</v>
@@ -4474,31 +4474,31 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>58140</v>
+        <v>59194</v>
       </c>
       <c r="H66">
-        <v>5052</v>
+        <v>6154</v>
       </c>
       <c r="I66">
-        <v>209</v>
+        <v>723</v>
       </c>
       <c r="J66">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="K66">
         <v>0</v>
       </c>
       <c r="L66">
-        <v>11750</v>
+        <v>12105</v>
       </c>
       <c r="M66">
         <v>2</v>
       </c>
       <c r="N66">
-        <v>1717</v>
+        <v>1891</v>
       </c>
       <c r="O66">
-        <v>52742</v>
+        <v>53676</v>
       </c>
       <c r="P66">
         <v>93810</v>
@@ -4533,31 +4533,31 @@
         <v>0</v>
       </c>
       <c r="G67">
-        <v>64125</v>
+        <v>64260</v>
       </c>
       <c r="H67">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="I67">
-        <v>2411</v>
+        <v>2702</v>
       </c>
       <c r="J67">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="K67">
         <v>0</v>
       </c>
       <c r="L67">
-        <v>18320</v>
+        <v>18366</v>
       </c>
       <c r="M67">
         <v>10</v>
       </c>
       <c r="N67">
-        <v>1326</v>
+        <v>1394</v>
       </c>
       <c r="O67">
-        <v>56171</v>
+        <v>57057</v>
       </c>
       <c r="P67">
         <v>78022</v>
@@ -4592,16 +4592,16 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>60993</v>
+        <v>61100</v>
       </c>
       <c r="H68">
-        <v>3351</v>
+        <v>3133</v>
       </c>
       <c r="I68">
-        <v>800</v>
+        <v>877</v>
       </c>
       <c r="J68">
-        <v>49</v>
+        <v>148</v>
       </c>
       <c r="K68">
         <v>0</v>
@@ -4613,13 +4613,13 @@
         <v>2</v>
       </c>
       <c r="N68">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="O68">
-        <v>50722</v>
+        <v>51035</v>
       </c>
       <c r="P68">
-        <v>61394</v>
+        <v>61396</v>
       </c>
       <c r="Q68">
         <v>7850</v>
@@ -4651,16 +4651,16 @@
         <v>0</v>
       </c>
       <c r="G69">
-        <v>38334</v>
+        <v>38557</v>
       </c>
       <c r="H69">
-        <v>5121</v>
+        <v>5010</v>
       </c>
       <c r="I69">
         <v>371</v>
       </c>
       <c r="J69">
-        <v>247</v>
+        <v>436</v>
       </c>
       <c r="K69">
         <v>0</v>
@@ -4672,13 +4672,13 @@
         <v>2</v>
       </c>
       <c r="N69">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="O69">
-        <v>34572</v>
+        <v>34730</v>
       </c>
       <c r="P69">
-        <v>34467</v>
+        <v>35481</v>
       </c>
       <c r="Q69">
         <v>6528</v>
@@ -4710,16 +4710,16 @@
         <v>0</v>
       </c>
       <c r="G70">
-        <v>44560</v>
+        <v>44569</v>
       </c>
       <c r="H70">
-        <v>938</v>
+        <v>931</v>
       </c>
       <c r="I70">
-        <v>1939</v>
+        <v>2211</v>
       </c>
       <c r="J70">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="K70">
         <v>0</v>
@@ -4734,7 +4734,7 @@
         <v>935</v>
       </c>
       <c r="O70">
-        <v>40709</v>
+        <v>40981</v>
       </c>
       <c r="P70">
         <v>42040</v>
@@ -4769,16 +4769,16 @@
         <v>0</v>
       </c>
       <c r="G71">
-        <v>47309</v>
+        <v>48326</v>
       </c>
       <c r="H71">
-        <v>2324</v>
+        <v>1322</v>
       </c>
       <c r="I71">
-        <v>1232</v>
+        <v>1315</v>
       </c>
       <c r="J71">
-        <v>144</v>
+        <v>1053</v>
       </c>
       <c r="K71">
         <v>0</v>
@@ -4793,7 +4793,7 @@
         <v>2871</v>
       </c>
       <c r="O71">
-        <v>36837</v>
+        <v>37147</v>
       </c>
       <c r="P71">
         <v>48896</v>
@@ -4828,16 +4828,16 @@
         <v>0</v>
       </c>
       <c r="G72">
-        <v>55963</v>
+        <v>56798</v>
       </c>
       <c r="H72">
-        <v>4268</v>
+        <v>3653</v>
       </c>
       <c r="I72">
-        <v>1162</v>
+        <v>1033</v>
       </c>
       <c r="J72">
-        <v>61</v>
+        <v>160</v>
       </c>
       <c r="K72">
         <v>0</v>
@@ -4849,10 +4849,10 @@
         <v>9</v>
       </c>
       <c r="N72">
-        <v>1242</v>
+        <v>1556</v>
       </c>
       <c r="O72">
-        <v>44562</v>
+        <v>45353</v>
       </c>
       <c r="P72">
         <v>85505</v>
@@ -4887,16 +4887,16 @@
         <v>0</v>
       </c>
       <c r="G73">
-        <v>50699</v>
+        <v>51023</v>
       </c>
       <c r="H73">
-        <v>7888</v>
+        <v>7689</v>
       </c>
       <c r="I73">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="J73">
-        <v>381</v>
+        <v>561</v>
       </c>
       <c r="K73">
         <v>0</v>
@@ -4908,10 +4908,10 @@
         <v>6</v>
       </c>
       <c r="N73">
-        <v>760</v>
+        <v>808</v>
       </c>
       <c r="O73">
-        <v>44973</v>
+        <v>45303</v>
       </c>
       <c r="P73">
         <v>67550</v>
@@ -4938,43 +4938,43 @@
         <v>0</v>
       </c>
       <c r="E74">
-        <v>2430022</v>
+        <v>2430042</v>
       </c>
       <c r="F74">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="G74">
-        <v>2151842</v>
+        <v>2189665</v>
       </c>
       <c r="H74">
-        <v>213799</v>
+        <v>195209</v>
       </c>
       <c r="I74">
-        <v>14960</v>
+        <v>18322</v>
       </c>
       <c r="J74">
-        <v>66173</v>
+        <v>71817</v>
       </c>
       <c r="K74">
-        <v>34646</v>
+        <v>40242</v>
       </c>
       <c r="L74">
-        <v>469080</v>
+        <v>473201</v>
       </c>
       <c r="M74">
-        <v>551</v>
+        <v>566</v>
       </c>
       <c r="N74">
-        <v>36825</v>
+        <v>39250</v>
       </c>
       <c r="O74">
-        <v>1889156</v>
+        <v>1933533</v>
       </c>
       <c r="P74">
-        <v>4456871</v>
+        <v>4485776</v>
       </c>
       <c r="Q74">
-        <v>629567</v>
+        <v>629442</v>
       </c>
       <c r="R74">
         <v>1</v>

--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25125" windowHeight="12210"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -303,7 +303,7 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Notice &amp; Hearing Report Last Updated On : 29-08-2026 07:57:04</t>
+    <t>Notice &amp; Hearing Report Last Updated On : 29-08-2026 11:57:04</t>
   </si>
 </sst>
 </file>
@@ -816,22 +816,22 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>41140</v>
+        <v>41469</v>
       </c>
       <c r="H4">
-        <v>9359</v>
+        <v>9104</v>
       </c>
       <c r="I4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J4">
-        <v>7010</v>
+        <v>7042</v>
       </c>
       <c r="K4">
-        <v>3677</v>
+        <v>3661</v>
       </c>
       <c r="L4">
-        <v>3773</v>
+        <v>3818</v>
       </c>
       <c r="M4">
         <v>34</v>
@@ -840,7 +840,7 @@
         <v>180</v>
       </c>
       <c r="O4">
-        <v>32106</v>
+        <v>32706</v>
       </c>
       <c r="P4">
         <v>53812</v>
@@ -875,22 +875,22 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>48372</v>
+        <v>48411</v>
       </c>
       <c r="H5">
-        <v>4451</v>
+        <v>4424</v>
       </c>
       <c r="I5">
         <v>2</v>
       </c>
       <c r="J5">
-        <v>2830</v>
+        <v>2630</v>
       </c>
       <c r="K5">
-        <v>1693</v>
+        <v>1632</v>
       </c>
       <c r="L5">
-        <v>4585</v>
+        <v>4779</v>
       </c>
       <c r="M5">
         <v>74</v>
@@ -899,10 +899,10 @@
         <v>371</v>
       </c>
       <c r="O5">
-        <v>44616</v>
+        <v>44653</v>
       </c>
       <c r="P5">
-        <v>55483</v>
+        <v>56098</v>
       </c>
       <c r="Q5">
         <v>16108</v>
@@ -934,34 +934,34 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>30129</v>
+        <v>30400</v>
       </c>
       <c r="H6">
-        <v>6552</v>
+        <v>6472</v>
       </c>
       <c r="I6">
         <v>217</v>
       </c>
       <c r="J6">
-        <v>2377</v>
+        <v>2324</v>
       </c>
       <c r="K6">
         <v>1219</v>
       </c>
       <c r="L6">
-        <v>1836</v>
+        <v>1906</v>
       </c>
       <c r="M6">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="N6">
         <v>757</v>
       </c>
       <c r="O6">
-        <v>25764</v>
+        <v>26014</v>
       </c>
       <c r="P6">
-        <v>54584</v>
+        <v>54999</v>
       </c>
       <c r="Q6">
         <v>17918</v>
@@ -993,31 +993,31 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>36922</v>
+        <v>37236</v>
       </c>
       <c r="H7">
-        <v>2305</v>
+        <v>1991</v>
       </c>
       <c r="I7">
         <v>236</v>
       </c>
       <c r="J7">
-        <v>4176</v>
+        <v>4147</v>
       </c>
       <c r="K7">
-        <v>3504</v>
+        <v>3501</v>
       </c>
       <c r="L7">
-        <v>1443</v>
+        <v>1451</v>
       </c>
       <c r="M7">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="N7">
-        <v>1297</v>
+        <v>1332</v>
       </c>
       <c r="O7">
-        <v>30913</v>
+        <v>31189</v>
       </c>
       <c r="P7">
         <v>77581</v>
@@ -1052,34 +1052,34 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>29644</v>
+        <v>30151</v>
       </c>
       <c r="H8">
-        <v>10908</v>
+        <v>10401</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>8903</v>
+        <v>8809</v>
       </c>
       <c r="K8">
-        <v>6358</v>
+        <v>6318</v>
       </c>
       <c r="L8">
-        <v>4300</v>
+        <v>4414</v>
       </c>
       <c r="M8">
         <v>16</v>
       </c>
       <c r="N8">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="O8">
-        <v>20108</v>
+        <v>20560</v>
       </c>
       <c r="P8">
-        <v>37523</v>
+        <v>49016</v>
       </c>
       <c r="Q8">
         <v>20902</v>
@@ -1111,31 +1111,31 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>35831</v>
+        <v>35839</v>
       </c>
       <c r="H9">
-        <v>7081</v>
+        <v>7080</v>
       </c>
       <c r="I9">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="J9">
-        <v>3411</v>
+        <v>3290</v>
       </c>
       <c r="K9">
-        <v>2808</v>
+        <v>2686</v>
       </c>
       <c r="L9">
-        <v>2601</v>
+        <v>2726</v>
       </c>
       <c r="M9">
         <v>9</v>
       </c>
       <c r="N9">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="O9">
-        <v>30555</v>
+        <v>30705</v>
       </c>
       <c r="P9">
         <v>66897</v>
@@ -1170,34 +1170,34 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>33537</v>
+        <v>33840</v>
       </c>
       <c r="H10">
-        <v>2999</v>
+        <v>2698</v>
       </c>
       <c r="I10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J10">
-        <v>2072</v>
+        <v>2112</v>
       </c>
       <c r="K10">
-        <v>1260</v>
+        <v>1253</v>
       </c>
       <c r="L10">
-        <v>8033</v>
+        <v>8034</v>
       </c>
       <c r="M10">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="N10">
-        <v>406</v>
+        <v>421</v>
       </c>
       <c r="O10">
-        <v>24960</v>
+        <v>25796</v>
       </c>
       <c r="P10">
-        <v>48109</v>
+        <v>49571</v>
       </c>
       <c r="Q10">
         <v>9511</v>
@@ -1229,31 +1229,31 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>42237</v>
+        <v>42731</v>
       </c>
       <c r="H11">
-        <v>7925</v>
+        <v>7474</v>
       </c>
       <c r="I11">
-        <v>532</v>
+        <v>508</v>
       </c>
       <c r="J11">
-        <v>5614</v>
+        <v>5709</v>
       </c>
       <c r="K11">
         <v>2640</v>
       </c>
       <c r="L11">
-        <v>1369</v>
+        <v>1463</v>
       </c>
       <c r="M11">
         <v>20</v>
       </c>
       <c r="N11">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="O11">
-        <v>34831</v>
+        <v>35124</v>
       </c>
       <c r="P11">
         <v>84443</v>
@@ -1288,31 +1288,31 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>34194</v>
+        <v>34506</v>
       </c>
       <c r="H12">
-        <v>6271</v>
+        <v>5959</v>
       </c>
       <c r="I12">
         <v>189</v>
       </c>
       <c r="J12">
-        <v>8918</v>
+        <v>8810</v>
       </c>
       <c r="K12">
-        <v>7074</v>
+        <v>7034</v>
       </c>
       <c r="L12">
-        <v>489</v>
+        <v>598</v>
       </c>
       <c r="M12">
         <v>2</v>
       </c>
       <c r="N12">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="O12">
-        <v>24416</v>
+        <v>24709</v>
       </c>
       <c r="P12">
         <v>66685</v>
@@ -1347,31 +1347,31 @@
         <v>5</v>
       </c>
       <c r="G13">
-        <v>31344</v>
+        <v>31955</v>
       </c>
       <c r="H13">
-        <v>5436</v>
+        <v>4825</v>
       </c>
       <c r="I13">
         <v>1</v>
       </c>
       <c r="J13">
-        <v>4984</v>
+        <v>5172</v>
       </c>
       <c r="K13">
-        <v>2274</v>
+        <v>2226</v>
       </c>
       <c r="L13">
-        <v>717</v>
+        <v>824</v>
       </c>
       <c r="M13">
         <v>0</v>
       </c>
       <c r="N13">
-        <v>2686</v>
+        <v>2764</v>
       </c>
       <c r="O13">
-        <v>23063</v>
+        <v>23301</v>
       </c>
       <c r="P13">
         <v>56565</v>
@@ -1406,31 +1406,31 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>34677</v>
+        <v>34820</v>
       </c>
       <c r="H14">
-        <v>10285</v>
+        <v>10191</v>
       </c>
       <c r="I14">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="J14">
-        <v>9213</v>
+        <v>9181</v>
       </c>
       <c r="K14">
-        <v>6275</v>
+        <v>6224</v>
       </c>
       <c r="L14">
-        <v>1781</v>
+        <v>1835</v>
       </c>
       <c r="M14">
         <v>57</v>
       </c>
       <c r="N14">
-        <v>1247</v>
+        <v>1299</v>
       </c>
       <c r="O14">
-        <v>22817</v>
+        <v>22886</v>
       </c>
       <c r="P14">
         <v>55446</v>
@@ -1465,31 +1465,31 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>41808</v>
+        <v>41918</v>
       </c>
       <c r="H15">
-        <v>895</v>
+        <v>785</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15">
-        <v>8968</v>
+        <v>8985</v>
       </c>
       <c r="M15">
         <v>0</v>
       </c>
       <c r="N15">
-        <v>2691</v>
+        <v>2705</v>
       </c>
       <c r="O15">
-        <v>38955</v>
+        <v>39156</v>
       </c>
       <c r="P15">
         <v>67178</v>
@@ -1524,31 +1524,31 @@
         <v>0</v>
       </c>
       <c r="G16">
-        <v>23267</v>
+        <v>23602</v>
       </c>
       <c r="H16">
-        <v>1660</v>
+        <v>1427</v>
       </c>
       <c r="I16">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
       <c r="L16">
-        <v>12946</v>
+        <v>13216</v>
       </c>
       <c r="M16">
         <v>1</v>
       </c>
       <c r="N16">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="O16">
-        <v>19749</v>
+        <v>20104</v>
       </c>
       <c r="P16">
         <v>68193</v>
@@ -1604,10 +1604,10 @@
         <v>2</v>
       </c>
       <c r="N17">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O17">
-        <v>27276</v>
+        <v>27285</v>
       </c>
       <c r="P17">
         <v>65458</v>
@@ -1636,40 +1636,40 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>47810</v>
+        <v>47811</v>
       </c>
       <c r="F18">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G18">
-        <v>47631</v>
+        <v>47706</v>
       </c>
       <c r="H18">
-        <v>188</v>
+        <v>123</v>
       </c>
       <c r="I18">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18">
         <v>0</v>
       </c>
       <c r="L18">
-        <v>7788</v>
+        <v>7806</v>
       </c>
       <c r="M18">
         <v>3</v>
       </c>
       <c r="N18">
-        <v>1873</v>
+        <v>1917</v>
       </c>
       <c r="O18">
-        <v>43869</v>
+        <v>43961</v>
       </c>
       <c r="P18">
-        <v>70738</v>
+        <v>70988</v>
       </c>
       <c r="Q18">
         <v>6857</v>
@@ -1695,37 +1695,37 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>56399</v>
+        <v>56407</v>
       </c>
       <c r="F19">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="G19">
-        <v>55094</v>
+        <v>55243</v>
       </c>
       <c r="H19">
-        <v>1249</v>
+        <v>1147</v>
       </c>
       <c r="I19">
-        <v>147</v>
+        <v>100</v>
       </c>
       <c r="J19">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="K19">
         <v>0</v>
       </c>
       <c r="L19">
-        <v>14722</v>
+        <v>14740</v>
       </c>
       <c r="M19">
         <v>1</v>
       </c>
       <c r="N19">
-        <v>733</v>
+        <v>750</v>
       </c>
       <c r="O19">
-        <v>50038</v>
+        <v>50846</v>
       </c>
       <c r="P19">
         <v>106226</v>
@@ -1754,22 +1754,22 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>35016</v>
+        <v>35017</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>34518</v>
+        <v>34559</v>
       </c>
       <c r="H20">
-        <v>496</v>
+        <v>455</v>
       </c>
       <c r="I20">
         <v>3</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20">
         <v>0</v>
@@ -1781,13 +1781,13 @@
         <v>5</v>
       </c>
       <c r="N20">
-        <v>388</v>
+        <v>412</v>
       </c>
       <c r="O20">
-        <v>33390</v>
+        <v>33885</v>
       </c>
       <c r="P20">
-        <v>75794</v>
+        <v>75795</v>
       </c>
       <c r="Q20">
         <v>9010</v>
@@ -1878,22 +1878,22 @@
         <v>0</v>
       </c>
       <c r="G22">
-        <v>18667</v>
+        <v>18668</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22">
         <v>0</v>
       </c>
       <c r="J22">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="K22">
         <v>0</v>
       </c>
       <c r="L22">
-        <v>7504</v>
+        <v>7552</v>
       </c>
       <c r="M22">
         <v>0</v>
@@ -1902,7 +1902,7 @@
         <v>234</v>
       </c>
       <c r="O22">
-        <v>17612</v>
+        <v>17615</v>
       </c>
       <c r="P22">
         <v>64099</v>
@@ -2055,31 +2055,31 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>19247</v>
+        <v>19264</v>
       </c>
       <c r="H25">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="I25">
         <v>0</v>
       </c>
       <c r="J25">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K25">
         <v>0</v>
       </c>
       <c r="L25">
-        <v>4826</v>
+        <v>4842</v>
       </c>
       <c r="M25">
         <v>0</v>
       </c>
       <c r="N25">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="O25">
-        <v>18665</v>
+        <v>18854</v>
       </c>
       <c r="P25">
         <v>57533</v>
@@ -2114,31 +2114,31 @@
         <v>0</v>
       </c>
       <c r="G26">
-        <v>17483</v>
+        <v>17487</v>
       </c>
       <c r="H26">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I26">
         <v>0</v>
       </c>
       <c r="J26">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K26">
         <v>0</v>
       </c>
       <c r="L26">
-        <v>3655</v>
+        <v>3662</v>
       </c>
       <c r="M26">
         <v>3</v>
       </c>
       <c r="N26">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="O26">
-        <v>17187</v>
+        <v>17196</v>
       </c>
       <c r="P26">
         <v>66594</v>
@@ -2173,22 +2173,22 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>34590</v>
+        <v>35120</v>
       </c>
       <c r="H27">
-        <v>8662</v>
+        <v>8132</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="L27">
-        <v>7136</v>
+        <v>7307</v>
       </c>
       <c r="M27">
         <v>0</v>
@@ -2197,10 +2197,10 @@
         <v>56</v>
       </c>
       <c r="O27">
-        <v>33293</v>
+        <v>33766</v>
       </c>
       <c r="P27">
-        <v>48916</v>
+        <v>49114</v>
       </c>
       <c r="Q27">
         <v>12669</v>
@@ -2226,37 +2226,37 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>54270</v>
+        <v>54271</v>
       </c>
       <c r="F28">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G28">
-        <v>31505</v>
+        <v>31954</v>
       </c>
       <c r="H28">
-        <v>20949</v>
+        <v>20570</v>
       </c>
       <c r="I28">
         <v>37</v>
       </c>
       <c r="J28">
-        <v>511</v>
+        <v>280</v>
       </c>
       <c r="K28">
         <v>0</v>
       </c>
       <c r="L28">
-        <v>4127</v>
+        <v>4366</v>
       </c>
       <c r="M28">
         <v>11</v>
       </c>
       <c r="N28">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="O28">
-        <v>27466</v>
+        <v>27833</v>
       </c>
       <c r="P28">
         <v>80639</v>
@@ -2291,31 +2291,31 @@
         <v>0</v>
       </c>
       <c r="G29">
-        <v>41317</v>
+        <v>41486</v>
       </c>
       <c r="H29">
-        <v>5338</v>
+        <v>5283</v>
       </c>
       <c r="I29">
-        <v>380</v>
+        <v>275</v>
       </c>
       <c r="J29">
-        <v>288</v>
+        <v>94</v>
       </c>
       <c r="K29">
         <v>0</v>
       </c>
       <c r="L29">
-        <v>6698</v>
+        <v>6895</v>
       </c>
       <c r="M29">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N29">
-        <v>604</v>
+        <v>701</v>
       </c>
       <c r="O29">
-        <v>36127</v>
+        <v>36670</v>
       </c>
       <c r="P29">
         <v>83837</v>
@@ -2350,31 +2350,31 @@
         <v>19</v>
       </c>
       <c r="G30">
-        <v>35253</v>
+        <v>35599</v>
       </c>
       <c r="H30">
-        <v>9932</v>
+        <v>9588</v>
       </c>
       <c r="I30">
-        <v>3775</v>
+        <v>3725</v>
       </c>
       <c r="J30">
-        <v>943</v>
+        <v>262</v>
       </c>
       <c r="K30">
         <v>0</v>
       </c>
       <c r="L30">
-        <v>4265</v>
+        <v>4951</v>
       </c>
       <c r="M30">
         <v>4</v>
       </c>
       <c r="N30">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O30">
-        <v>32122</v>
+        <v>32642</v>
       </c>
       <c r="P30">
         <v>86935</v>
@@ -2409,31 +2409,31 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>89024</v>
+        <v>89475</v>
       </c>
       <c r="H31">
-        <v>976</v>
+        <v>717</v>
       </c>
       <c r="I31">
         <v>77</v>
       </c>
       <c r="J31">
-        <v>396</v>
+        <v>298</v>
       </c>
       <c r="K31">
         <v>0</v>
       </c>
       <c r="L31">
-        <v>41667</v>
+        <v>42054</v>
       </c>
       <c r="M31">
         <v>24</v>
       </c>
       <c r="N31">
-        <v>1753</v>
+        <v>1755</v>
       </c>
       <c r="O31">
-        <v>83389</v>
+        <v>83616</v>
       </c>
       <c r="P31">
         <v>81642</v>
@@ -2468,34 +2468,34 @@
         <v>19</v>
       </c>
       <c r="G32">
-        <v>31750</v>
+        <v>32018</v>
       </c>
       <c r="H32">
-        <v>14576</v>
+        <v>14309</v>
       </c>
       <c r="I32">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="J32">
-        <v>366</v>
+        <v>263</v>
       </c>
       <c r="K32">
         <v>0</v>
       </c>
       <c r="L32">
-        <v>6760</v>
+        <v>6924</v>
       </c>
       <c r="M32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N32">
-        <v>688</v>
+        <v>702</v>
       </c>
       <c r="O32">
-        <v>28817</v>
+        <v>28979</v>
       </c>
       <c r="P32">
-        <v>38759</v>
+        <v>41455</v>
       </c>
       <c r="Q32">
         <v>11379</v>
@@ -2521,28 +2521,28 @@
         <v>0</v>
       </c>
       <c r="E33">
-        <v>40223</v>
+        <v>40225</v>
       </c>
       <c r="F33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G33">
-        <v>32586</v>
+        <v>32925</v>
       </c>
       <c r="H33">
-        <v>6599</v>
+        <v>6307</v>
       </c>
       <c r="I33">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J33">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="K33">
         <v>0</v>
       </c>
       <c r="L33">
-        <v>3584</v>
+        <v>3635</v>
       </c>
       <c r="M33">
         <v>6</v>
@@ -2551,7 +2551,7 @@
         <v>18</v>
       </c>
       <c r="O33">
-        <v>31026</v>
+        <v>31326</v>
       </c>
       <c r="P33">
         <v>73606</v>
@@ -2586,22 +2586,22 @@
         <v>0</v>
       </c>
       <c r="G34">
-        <v>28092</v>
+        <v>28588</v>
       </c>
       <c r="H34">
-        <v>8450</v>
+        <v>7954</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
       <c r="J34">
-        <v>239</v>
+        <v>258</v>
       </c>
       <c r="K34">
         <v>0</v>
       </c>
       <c r="L34">
-        <v>9450</v>
+        <v>9584</v>
       </c>
       <c r="M34">
         <v>1</v>
@@ -2610,7 +2610,7 @@
         <v>1</v>
       </c>
       <c r="O34">
-        <v>26115</v>
+        <v>26479</v>
       </c>
       <c r="P34">
         <v>74626</v>
@@ -2639,37 +2639,37 @@
         <v>0</v>
       </c>
       <c r="E35">
-        <v>33537</v>
+        <v>33552</v>
       </c>
       <c r="F35">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="G35">
-        <v>27779</v>
+        <v>28174</v>
       </c>
       <c r="H35">
-        <v>5047</v>
+        <v>4865</v>
       </c>
       <c r="I35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J35">
-        <v>1187</v>
+        <v>798</v>
       </c>
       <c r="K35">
         <v>0</v>
       </c>
       <c r="L35">
-        <v>4024</v>
+        <v>4471</v>
       </c>
       <c r="M35">
         <v>0</v>
       </c>
       <c r="N35">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="O35">
-        <v>25651</v>
+        <v>26083</v>
       </c>
       <c r="P35">
         <v>72020</v>
@@ -2831,19 +2831,19 @@
         <v>0</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K38">
         <v>0</v>
       </c>
       <c r="L38">
-        <v>4950</v>
+        <v>4954</v>
       </c>
       <c r="M38">
         <v>2</v>
       </c>
       <c r="N38">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="O38">
         <v>28039</v>
@@ -2940,22 +2940,22 @@
         <v>0</v>
       </c>
       <c r="G40">
-        <v>17452</v>
+        <v>17610</v>
       </c>
       <c r="H40">
-        <v>168</v>
+        <v>89</v>
       </c>
       <c r="I40">
         <v>0</v>
       </c>
       <c r="J40">
-        <v>118</v>
+        <v>10</v>
       </c>
       <c r="K40">
         <v>0</v>
       </c>
       <c r="L40">
-        <v>1417</v>
+        <v>1527</v>
       </c>
       <c r="M40">
         <v>0</v>
@@ -2964,7 +2964,7 @@
         <v>28</v>
       </c>
       <c r="O40">
-        <v>16308</v>
+        <v>16505</v>
       </c>
       <c r="P40">
         <v>73242</v>
@@ -2999,31 +2999,31 @@
         <v>0</v>
       </c>
       <c r="G41">
-        <v>22715</v>
+        <v>22826</v>
       </c>
       <c r="H41">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I41">
         <v>0</v>
       </c>
       <c r="J41">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="K41">
         <v>0</v>
       </c>
       <c r="L41">
-        <v>1022</v>
+        <v>1085</v>
       </c>
       <c r="M41">
         <v>0</v>
       </c>
       <c r="N41">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O41">
-        <v>21339</v>
+        <v>21471</v>
       </c>
       <c r="P41">
         <v>85249</v>
@@ -3067,13 +3067,13 @@
         <v>0</v>
       </c>
       <c r="J42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K42">
         <v>0</v>
       </c>
       <c r="L42">
-        <v>6258</v>
+        <v>6260</v>
       </c>
       <c r="M42">
         <v>0</v>
@@ -3082,7 +3082,7 @@
         <v>418</v>
       </c>
       <c r="O42">
-        <v>26842</v>
+        <v>27144</v>
       </c>
       <c r="P42">
         <v>68615</v>
@@ -3126,7 +3126,7 @@
         <v>0</v>
       </c>
       <c r="J43">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K43">
         <v>0</v>
@@ -3141,7 +3141,7 @@
         <v>902</v>
       </c>
       <c r="O43">
-        <v>27959</v>
+        <v>27960</v>
       </c>
       <c r="P43">
         <v>63036</v>
@@ -3176,31 +3176,31 @@
         <v>0</v>
       </c>
       <c r="G44">
-        <v>21380</v>
+        <v>21624</v>
       </c>
       <c r="H44">
-        <v>519</v>
+        <v>275</v>
       </c>
       <c r="I44">
         <v>0</v>
       </c>
       <c r="J44">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="K44">
         <v>0</v>
       </c>
       <c r="L44">
-        <v>6409</v>
+        <v>6540</v>
       </c>
       <c r="M44">
         <v>12</v>
       </c>
       <c r="N44">
-        <v>197</v>
+        <v>239</v>
       </c>
       <c r="O44">
-        <v>19142</v>
+        <v>19569</v>
       </c>
       <c r="P44">
         <v>68393</v>
@@ -3235,16 +3235,16 @@
         <v>0</v>
       </c>
       <c r="G45">
-        <v>17486</v>
+        <v>17764</v>
       </c>
       <c r="H45">
-        <v>1526</v>
+        <v>1374</v>
       </c>
       <c r="I45">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J45">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="K45">
         <v>0</v>
@@ -3256,10 +3256,10 @@
         <v>10</v>
       </c>
       <c r="N45">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="O45">
-        <v>15685</v>
+        <v>15947</v>
       </c>
       <c r="P45">
         <v>76002</v>
@@ -3294,16 +3294,16 @@
         <v>0</v>
       </c>
       <c r="G46">
-        <v>21030</v>
+        <v>21082</v>
       </c>
       <c r="H46">
-        <v>482</v>
+        <v>430</v>
       </c>
       <c r="I46">
         <v>0</v>
       </c>
       <c r="J46">
-        <v>61</v>
+        <v>110</v>
       </c>
       <c r="K46">
         <v>0</v>
@@ -3315,10 +3315,10 @@
         <v>1</v>
       </c>
       <c r="N46">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O46">
-        <v>18295</v>
+        <v>18318</v>
       </c>
       <c r="P46">
         <v>64160</v>
@@ -3353,16 +3353,16 @@
         <v>0</v>
       </c>
       <c r="G47">
-        <v>21689</v>
+        <v>21773</v>
       </c>
       <c r="H47">
-        <v>699</v>
+        <v>615</v>
       </c>
       <c r="I47">
         <v>27</v>
       </c>
       <c r="J47">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="K47">
         <v>11</v>
@@ -3377,7 +3377,7 @@
         <v>109</v>
       </c>
       <c r="O47">
-        <v>20192</v>
+        <v>20577</v>
       </c>
       <c r="P47">
         <v>49875</v>
@@ -3406,10 +3406,10 @@
         <v>0</v>
       </c>
       <c r="E48">
-        <v>19594</v>
+        <v>19597</v>
       </c>
       <c r="F48">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G48">
         <v>19561</v>
@@ -3433,10 +3433,10 @@
         <v>4</v>
       </c>
       <c r="N48">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="O48">
-        <v>19248</v>
+        <v>19245</v>
       </c>
       <c r="P48">
         <v>54142</v>
@@ -3471,16 +3471,16 @@
         <v>19</v>
       </c>
       <c r="G49">
-        <v>19865</v>
+        <v>19874</v>
       </c>
       <c r="H49">
-        <v>888</v>
+        <v>885</v>
       </c>
       <c r="I49">
         <v>241</v>
       </c>
       <c r="J49">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="K49">
         <v>0</v>
@@ -3492,13 +3492,13 @@
         <v>0</v>
       </c>
       <c r="N49">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O49">
-        <v>17851</v>
+        <v>17855</v>
       </c>
       <c r="P49">
-        <v>51751</v>
+        <v>52099</v>
       </c>
       <c r="Q49">
         <v>5057</v>
@@ -3530,31 +3530,31 @@
         <v>0</v>
       </c>
       <c r="G50">
-        <v>21512</v>
+        <v>21608</v>
       </c>
       <c r="H50">
-        <v>424</v>
+        <v>328</v>
       </c>
       <c r="I50">
         <v>0</v>
       </c>
       <c r="J50">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="K50">
         <v>0</v>
       </c>
       <c r="L50">
-        <v>3858</v>
+        <v>3881</v>
       </c>
       <c r="M50">
         <v>5</v>
       </c>
       <c r="N50">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O50">
-        <v>20480</v>
+        <v>20568</v>
       </c>
       <c r="P50">
         <v>63298</v>
@@ -3589,22 +3589,22 @@
         <v>0</v>
       </c>
       <c r="G51">
-        <v>22758</v>
+        <v>22768</v>
       </c>
       <c r="H51">
-        <v>637</v>
+        <v>630</v>
       </c>
       <c r="I51">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J51">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K51">
         <v>0</v>
       </c>
       <c r="L51">
-        <v>4527</v>
+        <v>4544</v>
       </c>
       <c r="M51">
         <v>11</v>
@@ -3613,7 +3613,7 @@
         <v>65</v>
       </c>
       <c r="O51">
-        <v>20336</v>
+        <v>20345</v>
       </c>
       <c r="P51">
         <v>71754</v>
@@ -3648,16 +3648,16 @@
         <v>0</v>
       </c>
       <c r="G52">
-        <v>21018</v>
+        <v>21035</v>
       </c>
       <c r="H52">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I52">
         <v>0</v>
       </c>
       <c r="J52">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="K52">
         <v>1</v>
@@ -3672,7 +3672,7 @@
         <v>42</v>
       </c>
       <c r="O52">
-        <v>20372</v>
+        <v>20397</v>
       </c>
       <c r="P52">
         <v>63986</v>
@@ -3716,7 +3716,7 @@
         <v>0</v>
       </c>
       <c r="J53">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="K53">
         <v>141</v>
@@ -3766,31 +3766,31 @@
         <v>0</v>
       </c>
       <c r="G54">
-        <v>20528</v>
+        <v>20540</v>
       </c>
       <c r="H54">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="I54">
         <v>23</v>
       </c>
       <c r="J54">
-        <v>443</v>
+        <v>428</v>
       </c>
       <c r="K54">
         <v>109</v>
       </c>
       <c r="L54">
-        <v>1947</v>
+        <v>1961</v>
       </c>
       <c r="M54">
         <v>5</v>
       </c>
       <c r="N54">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="O54">
-        <v>17874</v>
+        <v>17953</v>
       </c>
       <c r="P54">
         <v>58440</v>
@@ -3834,13 +3834,13 @@
         <v>0</v>
       </c>
       <c r="J55">
-        <v>314</v>
+        <v>213</v>
       </c>
       <c r="K55">
-        <v>128</v>
+        <v>67</v>
       </c>
       <c r="L55">
-        <v>1704</v>
+        <v>1788</v>
       </c>
       <c r="M55">
         <v>1</v>
@@ -3849,7 +3849,7 @@
         <v>90</v>
       </c>
       <c r="O55">
-        <v>15472</v>
+        <v>15523</v>
       </c>
       <c r="P55">
         <v>58215</v>
@@ -3884,22 +3884,22 @@
         <v>0</v>
       </c>
       <c r="G56">
-        <v>19084</v>
+        <v>19085</v>
       </c>
       <c r="H56">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I56">
         <v>0</v>
       </c>
       <c r="J56">
-        <v>908</v>
+        <v>760</v>
       </c>
       <c r="K56">
-        <v>549</v>
+        <v>401</v>
       </c>
       <c r="L56">
-        <v>2904</v>
+        <v>3053</v>
       </c>
       <c r="M56">
         <v>2</v>
@@ -3908,7 +3908,7 @@
         <v>385</v>
       </c>
       <c r="O56">
-        <v>14604</v>
+        <v>14605</v>
       </c>
       <c r="P56">
         <v>46365</v>
@@ -3943,22 +3943,22 @@
         <v>0</v>
       </c>
       <c r="G57">
-        <v>21212</v>
+        <v>21232</v>
       </c>
       <c r="H57">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="I57">
         <v>0</v>
       </c>
       <c r="J57">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K57">
         <v>0</v>
       </c>
       <c r="L57">
-        <v>1774</v>
+        <v>1817</v>
       </c>
       <c r="M57">
         <v>5</v>
@@ -3967,7 +3967,7 @@
         <v>37</v>
       </c>
       <c r="O57">
-        <v>21030</v>
+        <v>21068</v>
       </c>
       <c r="P57">
         <v>61556</v>
@@ -4002,16 +4002,16 @@
         <v>0</v>
       </c>
       <c r="G58">
-        <v>22004</v>
+        <v>22043</v>
       </c>
       <c r="H58">
-        <v>272</v>
+        <v>241</v>
       </c>
       <c r="I58">
         <v>143</v>
       </c>
       <c r="J58">
-        <v>1356</v>
+        <v>1392</v>
       </c>
       <c r="K58">
         <v>276</v>
@@ -4026,7 +4026,7 @@
         <v>357</v>
       </c>
       <c r="O58">
-        <v>16858</v>
+        <v>17761</v>
       </c>
       <c r="P58">
         <v>57577</v>
@@ -4120,28 +4120,28 @@
         <v>0</v>
       </c>
       <c r="G60">
-        <v>23592</v>
+        <v>23595</v>
       </c>
       <c r="H60">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I60">
         <v>0</v>
       </c>
       <c r="J60">
-        <v>120</v>
+        <v>14</v>
       </c>
       <c r="K60">
         <v>0</v>
       </c>
       <c r="L60">
-        <v>5533</v>
+        <v>5560</v>
       </c>
       <c r="M60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N60">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="O60">
         <v>21653</v>
@@ -4203,7 +4203,7 @@
         <v>1</v>
       </c>
       <c r="O61">
-        <v>13959</v>
+        <v>13964</v>
       </c>
       <c r="P61">
         <v>55240</v>
@@ -4238,16 +4238,16 @@
         <v>0</v>
       </c>
       <c r="G62">
-        <v>15783</v>
+        <v>15795</v>
       </c>
       <c r="H62">
         <v>0</v>
       </c>
       <c r="I62">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="J62">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="K62">
         <v>234</v>
@@ -4259,10 +4259,10 @@
         <v>15</v>
       </c>
       <c r="N62">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="O62">
-        <v>14588</v>
+        <v>14776</v>
       </c>
       <c r="P62">
         <v>51334</v>
@@ -4297,22 +4297,22 @@
         <v>0</v>
       </c>
       <c r="G63">
-        <v>36727</v>
+        <v>36730</v>
       </c>
       <c r="H63">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I63">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J63">
-        <v>246</v>
+        <v>210</v>
       </c>
       <c r="K63">
         <v>0</v>
       </c>
       <c r="L63">
-        <v>10610</v>
+        <v>10662</v>
       </c>
       <c r="M63">
         <v>35</v>
@@ -4321,7 +4321,7 @@
         <v>897</v>
       </c>
       <c r="O63">
-        <v>32100</v>
+        <v>32109</v>
       </c>
       <c r="P63">
         <v>68691</v>
@@ -4356,31 +4356,31 @@
         <v>0</v>
       </c>
       <c r="G64">
-        <v>41501</v>
+        <v>41633</v>
       </c>
       <c r="H64">
-        <v>529</v>
+        <v>398</v>
       </c>
       <c r="I64">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J64">
-        <v>177</v>
+        <v>216</v>
       </c>
       <c r="K64">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L64">
-        <v>9428</v>
+        <v>9448</v>
       </c>
       <c r="M64">
         <v>8</v>
       </c>
       <c r="N64">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O64">
-        <v>40629</v>
+        <v>40728</v>
       </c>
       <c r="P64">
         <v>60527</v>
@@ -4415,16 +4415,16 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>38246</v>
+        <v>38353</v>
       </c>
       <c r="H65">
-        <v>1832</v>
+        <v>1786</v>
       </c>
       <c r="I65">
-        <v>1252</v>
+        <v>1191</v>
       </c>
       <c r="J65">
-        <v>159</v>
+        <v>216</v>
       </c>
       <c r="K65">
         <v>0</v>
@@ -4436,10 +4436,10 @@
         <v>2</v>
       </c>
       <c r="N65">
-        <v>717</v>
+        <v>756</v>
       </c>
       <c r="O65">
-        <v>27217</v>
+        <v>27262</v>
       </c>
       <c r="P65">
         <v>37163</v>
@@ -4474,31 +4474,31 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>59194</v>
+        <v>59913</v>
       </c>
       <c r="H66">
-        <v>6154</v>
+        <v>5613</v>
       </c>
       <c r="I66">
-        <v>723</v>
+        <v>703</v>
       </c>
       <c r="J66">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="K66">
         <v>0</v>
       </c>
       <c r="L66">
-        <v>12105</v>
+        <v>12155</v>
       </c>
       <c r="M66">
         <v>2</v>
       </c>
       <c r="N66">
-        <v>1891</v>
+        <v>1913</v>
       </c>
       <c r="O66">
-        <v>53676</v>
+        <v>54293</v>
       </c>
       <c r="P66">
         <v>93810</v>
@@ -4533,31 +4533,31 @@
         <v>0</v>
       </c>
       <c r="G67">
-        <v>64260</v>
+        <v>64552</v>
       </c>
       <c r="H67">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I67">
-        <v>2702</v>
+        <v>2587</v>
       </c>
       <c r="J67">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="K67">
         <v>0</v>
       </c>
       <c r="L67">
-        <v>18366</v>
+        <v>18441</v>
       </c>
       <c r="M67">
         <v>10</v>
       </c>
       <c r="N67">
-        <v>1394</v>
+        <v>1434</v>
       </c>
       <c r="O67">
-        <v>57057</v>
+        <v>57488</v>
       </c>
       <c r="P67">
         <v>78022</v>
@@ -4592,34 +4592,34 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>61100</v>
+        <v>61186</v>
       </c>
       <c r="H68">
-        <v>3133</v>
+        <v>3080</v>
       </c>
       <c r="I68">
-        <v>877</v>
+        <v>860</v>
       </c>
       <c r="J68">
-        <v>148</v>
+        <v>40</v>
       </c>
       <c r="K68">
         <v>0</v>
       </c>
       <c r="L68">
-        <v>15820</v>
+        <v>15973</v>
       </c>
       <c r="M68">
         <v>2</v>
       </c>
       <c r="N68">
-        <v>441</v>
+        <v>455</v>
       </c>
       <c r="O68">
-        <v>51035</v>
+        <v>51088</v>
       </c>
       <c r="P68">
-        <v>61396</v>
+        <v>61644</v>
       </c>
       <c r="Q68">
         <v>7850</v>
@@ -4651,31 +4651,31 @@
         <v>0</v>
       </c>
       <c r="G69">
-        <v>38557</v>
+        <v>38663</v>
       </c>
       <c r="H69">
-        <v>5010</v>
+        <v>4938</v>
       </c>
       <c r="I69">
-        <v>371</v>
+        <v>329</v>
       </c>
       <c r="J69">
-        <v>436</v>
+        <v>173</v>
       </c>
       <c r="K69">
         <v>0</v>
       </c>
       <c r="L69">
-        <v>14976</v>
+        <v>15310</v>
       </c>
       <c r="M69">
         <v>2</v>
       </c>
       <c r="N69">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="O69">
-        <v>34730</v>
+        <v>35123</v>
       </c>
       <c r="P69">
         <v>35481</v>
@@ -4710,16 +4710,16 @@
         <v>0</v>
       </c>
       <c r="G70">
-        <v>44569</v>
+        <v>44689</v>
       </c>
       <c r="H70">
-        <v>931</v>
+        <v>882</v>
       </c>
       <c r="I70">
-        <v>2211</v>
+        <v>2140</v>
       </c>
       <c r="J70">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="K70">
         <v>0</v>
@@ -4731,10 +4731,10 @@
         <v>2</v>
       </c>
       <c r="N70">
-        <v>935</v>
+        <v>1020</v>
       </c>
       <c r="O70">
-        <v>40981</v>
+        <v>41072</v>
       </c>
       <c r="P70">
         <v>42040</v>
@@ -4769,31 +4769,31 @@
         <v>0</v>
       </c>
       <c r="G71">
-        <v>48326</v>
+        <v>48466</v>
       </c>
       <c r="H71">
-        <v>1322</v>
+        <v>1272</v>
       </c>
       <c r="I71">
-        <v>1315</v>
+        <v>1225</v>
       </c>
       <c r="J71">
-        <v>1053</v>
+        <v>15</v>
       </c>
       <c r="K71">
         <v>0</v>
       </c>
       <c r="L71">
-        <v>21084</v>
+        <v>22144</v>
       </c>
       <c r="M71">
         <v>1</v>
       </c>
       <c r="N71">
-        <v>2871</v>
+        <v>2979</v>
       </c>
       <c r="O71">
-        <v>37147</v>
+        <v>37636</v>
       </c>
       <c r="P71">
         <v>48896</v>
@@ -4828,31 +4828,31 @@
         <v>0</v>
       </c>
       <c r="G72">
-        <v>56798</v>
+        <v>57041</v>
       </c>
       <c r="H72">
-        <v>3653</v>
+        <v>3424</v>
       </c>
       <c r="I72">
-        <v>1033</v>
+        <v>1019</v>
       </c>
       <c r="J72">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="K72">
         <v>0</v>
       </c>
       <c r="L72">
-        <v>15999</v>
+        <v>16084</v>
       </c>
       <c r="M72">
         <v>9</v>
       </c>
       <c r="N72">
-        <v>1556</v>
+        <v>1626</v>
       </c>
       <c r="O72">
-        <v>45353</v>
+        <v>45648</v>
       </c>
       <c r="P72">
         <v>85505</v>
@@ -4887,31 +4887,31 @@
         <v>0</v>
       </c>
       <c r="G73">
-        <v>51023</v>
+        <v>51332</v>
       </c>
       <c r="H73">
-        <v>7689</v>
+        <v>7391</v>
       </c>
       <c r="I73">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="J73">
-        <v>561</v>
+        <v>367</v>
       </c>
       <c r="K73">
         <v>0</v>
       </c>
       <c r="L73">
-        <v>11067</v>
+        <v>11367</v>
       </c>
       <c r="M73">
         <v>6</v>
       </c>
       <c r="N73">
-        <v>808</v>
+        <v>882</v>
       </c>
       <c r="O73">
-        <v>45303</v>
+        <v>45860</v>
       </c>
       <c r="P73">
         <v>67550</v>
@@ -4938,40 +4938,40 @@
         <v>0</v>
       </c>
       <c r="E74">
-        <v>2430042</v>
+        <v>2430073</v>
       </c>
       <c r="F74">
-        <v>340</v>
+        <v>309</v>
       </c>
       <c r="G74">
-        <v>2189665</v>
+        <v>2200574</v>
       </c>
       <c r="H74">
-        <v>195209</v>
+        <v>186614</v>
       </c>
       <c r="I74">
-        <v>18322</v>
+        <v>17570</v>
       </c>
       <c r="J74">
-        <v>71817</v>
+        <v>68055</v>
       </c>
       <c r="K74">
-        <v>40242</v>
+        <v>39640</v>
       </c>
       <c r="L74">
-        <v>473201</v>
+        <v>479788</v>
       </c>
       <c r="M74">
-        <v>566</v>
+        <v>601</v>
       </c>
       <c r="N74">
-        <v>39250</v>
+        <v>40265</v>
       </c>
       <c r="O74">
-        <v>1933533</v>
+        <v>1948772</v>
       </c>
       <c r="P74">
-        <v>4485776</v>
+        <v>4503502</v>
       </c>
       <c r="Q74">
         <v>629442</v>

--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25125" windowHeight="12210"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -303,7 +303,7 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Notice &amp; Hearing Report Last Updated On : 29-08-2026 11:57:04</t>
+    <t>Notice &amp; Hearing Report Last Updated On : 29-08-2026 13:57:04</t>
   </si>
 </sst>
 </file>
@@ -816,31 +816,31 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>41469</v>
+        <v>42150</v>
       </c>
       <c r="H4">
-        <v>9104</v>
+        <v>8517</v>
       </c>
       <c r="I4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>7042</v>
+        <v>6256</v>
       </c>
       <c r="K4">
-        <v>3661</v>
+        <v>3511</v>
       </c>
       <c r="L4">
-        <v>3818</v>
+        <v>4828</v>
       </c>
       <c r="M4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N4">
         <v>180</v>
       </c>
       <c r="O4">
-        <v>32706</v>
+        <v>34203</v>
       </c>
       <c r="P4">
         <v>53812</v>
@@ -875,34 +875,34 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>48411</v>
+        <v>48450</v>
       </c>
       <c r="H5">
-        <v>4424</v>
+        <v>4385</v>
       </c>
       <c r="I5">
         <v>2</v>
       </c>
       <c r="J5">
-        <v>2630</v>
+        <v>2535</v>
       </c>
       <c r="K5">
-        <v>1632</v>
+        <v>1586</v>
       </c>
       <c r="L5">
-        <v>4779</v>
+        <v>4890</v>
       </c>
       <c r="M5">
         <v>74</v>
       </c>
       <c r="N5">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O5">
-        <v>44653</v>
+        <v>44915</v>
       </c>
       <c r="P5">
-        <v>56098</v>
+        <v>56969</v>
       </c>
       <c r="Q5">
         <v>16108</v>
@@ -934,31 +934,31 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>30400</v>
+        <v>31043</v>
       </c>
       <c r="H6">
-        <v>6472</v>
+        <v>6257</v>
       </c>
       <c r="I6">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="J6">
-        <v>2324</v>
+        <v>2396</v>
       </c>
       <c r="K6">
         <v>1219</v>
       </c>
       <c r="L6">
-        <v>1906</v>
+        <v>1929</v>
       </c>
       <c r="M6">
         <v>29</v>
       </c>
       <c r="N6">
-        <v>757</v>
+        <v>801</v>
       </c>
       <c r="O6">
-        <v>26014</v>
+        <v>26523</v>
       </c>
       <c r="P6">
         <v>54999</v>
@@ -993,31 +993,31 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>37236</v>
+        <v>37382</v>
       </c>
       <c r="H7">
-        <v>1991</v>
+        <v>1889</v>
       </c>
       <c r="I7">
-        <v>236</v>
+        <v>192</v>
       </c>
       <c r="J7">
-        <v>4147</v>
+        <v>3841</v>
       </c>
       <c r="K7">
-        <v>3501</v>
+        <v>3356</v>
       </c>
       <c r="L7">
-        <v>1451</v>
+        <v>1759</v>
       </c>
       <c r="M7">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="N7">
-        <v>1332</v>
+        <v>1399</v>
       </c>
       <c r="O7">
-        <v>31189</v>
+        <v>31417</v>
       </c>
       <c r="P7">
         <v>77581</v>
@@ -1052,34 +1052,34 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>30151</v>
+        <v>30438</v>
       </c>
       <c r="H8">
-        <v>10401</v>
+        <v>10114</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>8809</v>
+        <v>8575</v>
       </c>
       <c r="K8">
-        <v>6318</v>
+        <v>6165</v>
       </c>
       <c r="L8">
-        <v>4414</v>
+        <v>4718</v>
       </c>
       <c r="M8">
         <v>16</v>
       </c>
       <c r="N8">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="O8">
-        <v>20560</v>
+        <v>20772</v>
       </c>
       <c r="P8">
-        <v>49016</v>
+        <v>70234</v>
       </c>
       <c r="Q8">
         <v>20902</v>
@@ -1111,31 +1111,31 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>35839</v>
+        <v>35964</v>
       </c>
       <c r="H9">
-        <v>7080</v>
+        <v>7001</v>
       </c>
       <c r="I9">
-        <v>354</v>
+        <v>308</v>
       </c>
       <c r="J9">
-        <v>3290</v>
+        <v>3250</v>
       </c>
       <c r="K9">
-        <v>2686</v>
+        <v>2636</v>
       </c>
       <c r="L9">
-        <v>2726</v>
+        <v>2781</v>
       </c>
       <c r="M9">
         <v>9</v>
       </c>
       <c r="N9">
-        <v>297</v>
+        <v>366</v>
       </c>
       <c r="O9">
-        <v>30705</v>
+        <v>30818</v>
       </c>
       <c r="P9">
         <v>66897</v>
@@ -1170,34 +1170,34 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>33840</v>
+        <v>34281</v>
       </c>
       <c r="H10">
-        <v>2698</v>
+        <v>2258</v>
       </c>
       <c r="I10">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J10">
-        <v>2112</v>
+        <v>2152</v>
       </c>
       <c r="K10">
-        <v>1253</v>
+        <v>1245</v>
       </c>
       <c r="L10">
-        <v>8034</v>
+        <v>8078</v>
       </c>
       <c r="M10">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="N10">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="O10">
-        <v>25796</v>
+        <v>26908</v>
       </c>
       <c r="P10">
-        <v>49571</v>
+        <v>52756</v>
       </c>
       <c r="Q10">
         <v>9511</v>
@@ -1229,31 +1229,31 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>42731</v>
+        <v>43433</v>
       </c>
       <c r="H11">
-        <v>7474</v>
+        <v>6898</v>
       </c>
       <c r="I11">
-        <v>508</v>
+        <v>425</v>
       </c>
       <c r="J11">
-        <v>5709</v>
+        <v>5929</v>
       </c>
       <c r="K11">
-        <v>2640</v>
+        <v>2639</v>
       </c>
       <c r="L11">
-        <v>1463</v>
+        <v>1571</v>
       </c>
       <c r="M11">
         <v>20</v>
       </c>
       <c r="N11">
-        <v>346</v>
+        <v>371</v>
       </c>
       <c r="O11">
-        <v>35124</v>
+        <v>35478</v>
       </c>
       <c r="P11">
         <v>84443</v>
@@ -1288,31 +1288,31 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>34506</v>
+        <v>35075</v>
       </c>
       <c r="H12">
-        <v>5959</v>
+        <v>5394</v>
       </c>
       <c r="I12">
         <v>189</v>
       </c>
       <c r="J12">
-        <v>8810</v>
+        <v>8595</v>
       </c>
       <c r="K12">
-        <v>7034</v>
+        <v>6794</v>
       </c>
       <c r="L12">
-        <v>598</v>
+        <v>836</v>
       </c>
       <c r="M12">
         <v>2</v>
       </c>
       <c r="N12">
-        <v>588</v>
+        <v>608</v>
       </c>
       <c r="O12">
-        <v>24709</v>
+        <v>25231</v>
       </c>
       <c r="P12">
         <v>66685</v>
@@ -1347,31 +1347,31 @@
         <v>5</v>
       </c>
       <c r="G13">
-        <v>31955</v>
+        <v>32456</v>
       </c>
       <c r="H13">
-        <v>4825</v>
+        <v>4344</v>
       </c>
       <c r="I13">
         <v>1</v>
       </c>
       <c r="J13">
-        <v>5172</v>
+        <v>4993</v>
       </c>
       <c r="K13">
-        <v>2226</v>
+        <v>2062</v>
       </c>
       <c r="L13">
-        <v>824</v>
+        <v>1231</v>
       </c>
       <c r="M13">
         <v>0</v>
       </c>
       <c r="N13">
-        <v>2764</v>
+        <v>2821</v>
       </c>
       <c r="O13">
-        <v>23301</v>
+        <v>23517</v>
       </c>
       <c r="P13">
         <v>56565</v>
@@ -1406,31 +1406,31 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>34820</v>
+        <v>35460</v>
       </c>
       <c r="H14">
-        <v>10191</v>
+        <v>9685</v>
       </c>
       <c r="I14">
-        <v>579</v>
+        <v>569</v>
       </c>
       <c r="J14">
-        <v>9181</v>
+        <v>9232</v>
       </c>
       <c r="K14">
-        <v>6224</v>
+        <v>6144</v>
       </c>
       <c r="L14">
-        <v>1835</v>
+        <v>1946</v>
       </c>
       <c r="M14">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="N14">
-        <v>1299</v>
+        <v>1359</v>
       </c>
       <c r="O14">
-        <v>22886</v>
+        <v>23292</v>
       </c>
       <c r="P14">
         <v>55446</v>
@@ -1465,10 +1465,10 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>41918</v>
+        <v>42130</v>
       </c>
       <c r="H15">
-        <v>785</v>
+        <v>573</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -1480,16 +1480,16 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>8985</v>
+        <v>9016</v>
       </c>
       <c r="M15">
         <v>0</v>
       </c>
       <c r="N15">
-        <v>2705</v>
+        <v>2732</v>
       </c>
       <c r="O15">
-        <v>39156</v>
+        <v>39317</v>
       </c>
       <c r="P15">
         <v>67178</v>
@@ -1524,31 +1524,31 @@
         <v>0</v>
       </c>
       <c r="G16">
-        <v>23602</v>
+        <v>23763</v>
       </c>
       <c r="H16">
-        <v>1427</v>
+        <v>1370</v>
       </c>
       <c r="I16">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="J16">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
       <c r="L16">
-        <v>13216</v>
+        <v>13361</v>
       </c>
       <c r="M16">
         <v>1</v>
       </c>
       <c r="N16">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="O16">
-        <v>20104</v>
+        <v>21340</v>
       </c>
       <c r="P16">
         <v>68193</v>
@@ -1642,22 +1642,22 @@
         <v>25</v>
       </c>
       <c r="G18">
-        <v>47706</v>
+        <v>47746</v>
       </c>
       <c r="H18">
-        <v>123</v>
+        <v>87</v>
       </c>
       <c r="I18">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K18">
         <v>0</v>
       </c>
       <c r="L18">
-        <v>7806</v>
+        <v>7841</v>
       </c>
       <c r="M18">
         <v>3</v>
@@ -1666,7 +1666,7 @@
         <v>1917</v>
       </c>
       <c r="O18">
-        <v>43961</v>
+        <v>43962</v>
       </c>
       <c r="P18">
         <v>70988</v>
@@ -1695,22 +1695,22 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>56407</v>
+        <v>56416</v>
       </c>
       <c r="F19">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G19">
-        <v>55243</v>
+        <v>55542</v>
       </c>
       <c r="H19">
-        <v>1147</v>
+        <v>882</v>
       </c>
       <c r="I19">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="J19">
-        <v>51</v>
+        <v>112</v>
       </c>
       <c r="K19">
         <v>0</v>
@@ -1722,10 +1722,10 @@
         <v>1</v>
       </c>
       <c r="N19">
-        <v>750</v>
+        <v>782</v>
       </c>
       <c r="O19">
-        <v>50846</v>
+        <v>51735</v>
       </c>
       <c r="P19">
         <v>106226</v>
@@ -1760,16 +1760,16 @@
         <v>0</v>
       </c>
       <c r="G20">
-        <v>34559</v>
+        <v>34630</v>
       </c>
       <c r="H20">
-        <v>455</v>
+        <v>375</v>
       </c>
       <c r="I20">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="K20">
         <v>0</v>
@@ -1781,10 +1781,10 @@
         <v>5</v>
       </c>
       <c r="N20">
-        <v>412</v>
+        <v>429</v>
       </c>
       <c r="O20">
-        <v>33885</v>
+        <v>34141</v>
       </c>
       <c r="P20">
         <v>75795</v>
@@ -1893,7 +1893,7 @@
         <v>0</v>
       </c>
       <c r="L22">
-        <v>7552</v>
+        <v>7555</v>
       </c>
       <c r="M22">
         <v>0</v>
@@ -2055,31 +2055,31 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>19264</v>
+        <v>19266</v>
       </c>
       <c r="H25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I25">
         <v>0</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25">
         <v>0</v>
       </c>
       <c r="L25">
-        <v>4842</v>
+        <v>4849</v>
       </c>
       <c r="M25">
         <v>0</v>
       </c>
       <c r="N25">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="O25">
-        <v>18854</v>
+        <v>18945</v>
       </c>
       <c r="P25">
         <v>57533</v>
@@ -2114,16 +2114,16 @@
         <v>0</v>
       </c>
       <c r="G26">
-        <v>17487</v>
+        <v>17513</v>
       </c>
       <c r="H26">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="I26">
         <v>0</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K26">
         <v>0</v>
@@ -2135,10 +2135,10 @@
         <v>3</v>
       </c>
       <c r="N26">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="O26">
-        <v>17196</v>
+        <v>17219</v>
       </c>
       <c r="P26">
         <v>66594</v>
@@ -2173,22 +2173,22 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>35120</v>
+        <v>35919</v>
       </c>
       <c r="H27">
-        <v>8132</v>
+        <v>7333</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27">
-        <v>213</v>
+        <v>587</v>
       </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="L27">
-        <v>7307</v>
+        <v>7332</v>
       </c>
       <c r="M27">
         <v>0</v>
@@ -2197,10 +2197,10 @@
         <v>56</v>
       </c>
       <c r="O27">
-        <v>33766</v>
+        <v>34297</v>
       </c>
       <c r="P27">
-        <v>49114</v>
+        <v>49325</v>
       </c>
       <c r="Q27">
         <v>12669</v>
@@ -2226,37 +2226,37 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>54271</v>
+        <v>54273</v>
       </c>
       <c r="F28">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G28">
-        <v>31954</v>
+        <v>32910</v>
       </c>
       <c r="H28">
-        <v>20570</v>
+        <v>19801</v>
       </c>
       <c r="I28">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J28">
-        <v>280</v>
+        <v>333</v>
       </c>
       <c r="K28">
         <v>0</v>
       </c>
       <c r="L28">
-        <v>4366</v>
+        <v>4416</v>
       </c>
       <c r="M28">
         <v>11</v>
       </c>
       <c r="N28">
-        <v>533</v>
+        <v>554</v>
       </c>
       <c r="O28">
-        <v>27833</v>
+        <v>28660</v>
       </c>
       <c r="P28">
         <v>80639</v>
@@ -2291,31 +2291,31 @@
         <v>0</v>
       </c>
       <c r="G29">
-        <v>41486</v>
+        <v>41852</v>
       </c>
       <c r="H29">
-        <v>5283</v>
+        <v>5017</v>
       </c>
       <c r="I29">
-        <v>275</v>
+        <v>197</v>
       </c>
       <c r="J29">
-        <v>94</v>
+        <v>139</v>
       </c>
       <c r="K29">
         <v>0</v>
       </c>
       <c r="L29">
-        <v>6895</v>
+        <v>6967</v>
       </c>
       <c r="M29">
         <v>5</v>
       </c>
       <c r="N29">
-        <v>701</v>
+        <v>779</v>
       </c>
       <c r="O29">
-        <v>36670</v>
+        <v>36931</v>
       </c>
       <c r="P29">
         <v>83837</v>
@@ -2350,31 +2350,31 @@
         <v>19</v>
       </c>
       <c r="G30">
-        <v>35599</v>
+        <v>36083</v>
       </c>
       <c r="H30">
-        <v>9588</v>
+        <v>9050</v>
       </c>
       <c r="I30">
-        <v>3725</v>
+        <v>3618</v>
       </c>
       <c r="J30">
-        <v>262</v>
+        <v>153</v>
       </c>
       <c r="K30">
         <v>0</v>
       </c>
       <c r="L30">
-        <v>4951</v>
+        <v>5096</v>
       </c>
       <c r="M30">
         <v>4</v>
       </c>
       <c r="N30">
-        <v>349</v>
+        <v>554</v>
       </c>
       <c r="O30">
-        <v>32642</v>
+        <v>33046</v>
       </c>
       <c r="P30">
         <v>86935</v>
@@ -2409,31 +2409,31 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>89475</v>
+        <v>89730</v>
       </c>
       <c r="H31">
-        <v>717</v>
+        <v>540</v>
       </c>
       <c r="I31">
         <v>77</v>
       </c>
       <c r="J31">
-        <v>298</v>
+        <v>575</v>
       </c>
       <c r="K31">
         <v>0</v>
       </c>
       <c r="L31">
-        <v>42054</v>
+        <v>42150</v>
       </c>
       <c r="M31">
         <v>24</v>
       </c>
       <c r="N31">
-        <v>1755</v>
+        <v>1762</v>
       </c>
       <c r="O31">
-        <v>83616</v>
+        <v>84445</v>
       </c>
       <c r="P31">
         <v>81642</v>
@@ -2468,34 +2468,34 @@
         <v>19</v>
       </c>
       <c r="G32">
-        <v>32018</v>
+        <v>32588</v>
       </c>
       <c r="H32">
-        <v>14309</v>
+        <v>13747</v>
       </c>
       <c r="I32">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="J32">
-        <v>263</v>
+        <v>181</v>
       </c>
       <c r="K32">
         <v>0</v>
       </c>
       <c r="L32">
-        <v>6924</v>
+        <v>7026</v>
       </c>
       <c r="M32">
         <v>9</v>
       </c>
       <c r="N32">
-        <v>702</v>
+        <v>739</v>
       </c>
       <c r="O32">
-        <v>28979</v>
+        <v>29485</v>
       </c>
       <c r="P32">
-        <v>41455</v>
+        <v>46145</v>
       </c>
       <c r="Q32">
         <v>11379</v>
@@ -2521,40 +2521,40 @@
         <v>0</v>
       </c>
       <c r="E33">
-        <v>40225</v>
+        <v>40229</v>
       </c>
       <c r="F33">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G33">
-        <v>32925</v>
+        <v>33225</v>
       </c>
       <c r="H33">
-        <v>6307</v>
+        <v>6002</v>
       </c>
       <c r="I33">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J33">
-        <v>259</v>
+        <v>187</v>
       </c>
       <c r="K33">
         <v>0</v>
       </c>
       <c r="L33">
-        <v>3635</v>
+        <v>3785</v>
       </c>
       <c r="M33">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="N33">
         <v>18</v>
       </c>
       <c r="O33">
-        <v>31326</v>
+        <v>31586</v>
       </c>
       <c r="P33">
-        <v>73606</v>
+        <v>74014</v>
       </c>
       <c r="Q33">
         <v>6678</v>
@@ -2586,31 +2586,31 @@
         <v>0</v>
       </c>
       <c r="G34">
-        <v>28588</v>
+        <v>28871</v>
       </c>
       <c r="H34">
-        <v>7954</v>
+        <v>7671</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
       <c r="J34">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="K34">
         <v>0</v>
       </c>
       <c r="L34">
-        <v>9584</v>
+        <v>9660</v>
       </c>
       <c r="M34">
         <v>1</v>
       </c>
       <c r="N34">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O34">
-        <v>26479</v>
+        <v>26722</v>
       </c>
       <c r="P34">
         <v>74626</v>
@@ -2639,37 +2639,37 @@
         <v>0</v>
       </c>
       <c r="E35">
-        <v>33552</v>
+        <v>33555</v>
       </c>
       <c r="F35">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G35">
-        <v>28174</v>
+        <v>28363</v>
       </c>
       <c r="H35">
-        <v>4865</v>
+        <v>4693</v>
       </c>
       <c r="I35">
         <v>0</v>
       </c>
       <c r="J35">
-        <v>798</v>
+        <v>585</v>
       </c>
       <c r="K35">
         <v>0</v>
       </c>
       <c r="L35">
-        <v>4471</v>
+        <v>4817</v>
       </c>
       <c r="M35">
         <v>0</v>
       </c>
       <c r="N35">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="O35">
-        <v>26083</v>
+        <v>26132</v>
       </c>
       <c r="P35">
         <v>72020</v>
@@ -2831,22 +2831,22 @@
         <v>0</v>
       </c>
       <c r="J38">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="K38">
         <v>0</v>
       </c>
       <c r="L38">
-        <v>4954</v>
+        <v>4958</v>
       </c>
       <c r="M38">
         <v>2</v>
       </c>
       <c r="N38">
-        <v>499</v>
+        <v>524</v>
       </c>
       <c r="O38">
-        <v>28039</v>
+        <v>28040</v>
       </c>
       <c r="P38">
         <v>63038</v>
@@ -2940,31 +2940,31 @@
         <v>0</v>
       </c>
       <c r="G40">
-        <v>17610</v>
+        <v>17895</v>
       </c>
       <c r="H40">
-        <v>89</v>
+        <v>36</v>
       </c>
       <c r="I40">
         <v>0</v>
       </c>
       <c r="J40">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="K40">
         <v>0</v>
       </c>
       <c r="L40">
-        <v>1527</v>
+        <v>1535</v>
       </c>
       <c r="M40">
         <v>0</v>
       </c>
       <c r="N40">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="O40">
-        <v>16505</v>
+        <v>16771</v>
       </c>
       <c r="P40">
         <v>73242</v>
@@ -2999,22 +2999,22 @@
         <v>0</v>
       </c>
       <c r="G41">
-        <v>22826</v>
+        <v>22979</v>
       </c>
       <c r="H41">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I41">
         <v>0</v>
       </c>
       <c r="J41">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K41">
         <v>0</v>
       </c>
       <c r="L41">
-        <v>1085</v>
+        <v>1094</v>
       </c>
       <c r="M41">
         <v>0</v>
@@ -3023,7 +3023,7 @@
         <v>65</v>
       </c>
       <c r="O41">
-        <v>21471</v>
+        <v>21624</v>
       </c>
       <c r="P41">
         <v>85249</v>
@@ -3067,7 +3067,7 @@
         <v>0</v>
       </c>
       <c r="J42">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K42">
         <v>0</v>
@@ -3126,7 +3126,7 @@
         <v>0</v>
       </c>
       <c r="J43">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="K43">
         <v>0</v>
@@ -3138,10 +3138,10 @@
         <v>1</v>
       </c>
       <c r="N43">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="O43">
-        <v>27960</v>
+        <v>27966</v>
       </c>
       <c r="P43">
         <v>63036</v>
@@ -3176,31 +3176,31 @@
         <v>0</v>
       </c>
       <c r="G44">
-        <v>21624</v>
+        <v>21643</v>
       </c>
       <c r="H44">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="I44">
         <v>0</v>
       </c>
       <c r="J44">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="K44">
         <v>0</v>
       </c>
       <c r="L44">
-        <v>6540</v>
+        <v>6572</v>
       </c>
       <c r="M44">
         <v>12</v>
       </c>
       <c r="N44">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="O44">
-        <v>19569</v>
+        <v>19727</v>
       </c>
       <c r="P44">
         <v>68393</v>
@@ -3235,31 +3235,31 @@
         <v>0</v>
       </c>
       <c r="G45">
-        <v>17764</v>
+        <v>17960</v>
       </c>
       <c r="H45">
-        <v>1374</v>
+        <v>1297</v>
       </c>
       <c r="I45">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J45">
-        <v>61</v>
+        <v>13</v>
       </c>
       <c r="K45">
         <v>0</v>
       </c>
       <c r="L45">
-        <v>1983</v>
+        <v>2050</v>
       </c>
       <c r="M45">
         <v>10</v>
       </c>
       <c r="N45">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O45">
-        <v>15947</v>
+        <v>16123</v>
       </c>
       <c r="P45">
         <v>76002</v>
@@ -3294,16 +3294,16 @@
         <v>0</v>
       </c>
       <c r="G46">
-        <v>21082</v>
+        <v>21247</v>
       </c>
       <c r="H46">
-        <v>430</v>
+        <v>265</v>
       </c>
       <c r="I46">
         <v>0</v>
       </c>
       <c r="J46">
-        <v>110</v>
+        <v>271</v>
       </c>
       <c r="K46">
         <v>0</v>
@@ -3315,10 +3315,10 @@
         <v>1</v>
       </c>
       <c r="N46">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="O46">
-        <v>18318</v>
+        <v>18909</v>
       </c>
       <c r="P46">
         <v>64160</v>
@@ -3353,16 +3353,16 @@
         <v>0</v>
       </c>
       <c r="G47">
-        <v>21773</v>
+        <v>21945</v>
       </c>
       <c r="H47">
-        <v>615</v>
+        <v>443</v>
       </c>
       <c r="I47">
         <v>27</v>
       </c>
       <c r="J47">
-        <v>341</v>
+        <v>384</v>
       </c>
       <c r="K47">
         <v>11</v>
@@ -3374,10 +3374,10 @@
         <v>1</v>
       </c>
       <c r="N47">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="O47">
-        <v>20577</v>
+        <v>20704</v>
       </c>
       <c r="P47">
         <v>49875</v>
@@ -3433,10 +3433,10 @@
         <v>4</v>
       </c>
       <c r="N48">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="O48">
-        <v>19245</v>
+        <v>19295</v>
       </c>
       <c r="P48">
         <v>54142</v>
@@ -3471,16 +3471,16 @@
         <v>19</v>
       </c>
       <c r="G49">
-        <v>19874</v>
+        <v>19914</v>
       </c>
       <c r="H49">
-        <v>885</v>
+        <v>879</v>
       </c>
       <c r="I49">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J49">
-        <v>288</v>
+        <v>312</v>
       </c>
       <c r="K49">
         <v>0</v>
@@ -3492,13 +3492,13 @@
         <v>0</v>
       </c>
       <c r="N49">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="O49">
-        <v>17855</v>
+        <v>17868</v>
       </c>
       <c r="P49">
-        <v>52099</v>
+        <v>52446</v>
       </c>
       <c r="Q49">
         <v>5057</v>
@@ -3530,22 +3530,22 @@
         <v>0</v>
       </c>
       <c r="G50">
-        <v>21608</v>
+        <v>21640</v>
       </c>
       <c r="H50">
-        <v>328</v>
+        <v>296</v>
       </c>
       <c r="I50">
         <v>0</v>
       </c>
       <c r="J50">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="K50">
         <v>0</v>
       </c>
       <c r="L50">
-        <v>3881</v>
+        <v>3894</v>
       </c>
       <c r="M50">
         <v>5</v>
@@ -3554,7 +3554,7 @@
         <v>12</v>
       </c>
       <c r="O50">
-        <v>20568</v>
+        <v>20585</v>
       </c>
       <c r="P50">
         <v>63298</v>
@@ -3589,16 +3589,16 @@
         <v>0</v>
       </c>
       <c r="G51">
-        <v>22768</v>
+        <v>22866</v>
       </c>
       <c r="H51">
-        <v>630</v>
+        <v>618</v>
       </c>
       <c r="I51">
         <v>0</v>
       </c>
       <c r="J51">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K51">
         <v>0</v>
@@ -3613,7 +3613,7 @@
         <v>65</v>
       </c>
       <c r="O51">
-        <v>20345</v>
+        <v>20429</v>
       </c>
       <c r="P51">
         <v>71754</v>
@@ -3648,7 +3648,7 @@
         <v>0</v>
       </c>
       <c r="G52">
-        <v>21035</v>
+        <v>21037</v>
       </c>
       <c r="H52">
         <v>33</v>
@@ -3657,7 +3657,7 @@
         <v>0</v>
       </c>
       <c r="J52">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="K52">
         <v>1</v>
@@ -3716,13 +3716,13 @@
         <v>0</v>
       </c>
       <c r="J53">
-        <v>305</v>
+        <v>272</v>
       </c>
       <c r="K53">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="L53">
-        <v>3129</v>
+        <v>3165</v>
       </c>
       <c r="M53">
         <v>1</v>
@@ -3731,7 +3731,7 @@
         <v>31</v>
       </c>
       <c r="O53">
-        <v>18565</v>
+        <v>18585</v>
       </c>
       <c r="P53">
         <v>56304</v>
@@ -3766,31 +3766,31 @@
         <v>0</v>
       </c>
       <c r="G54">
-        <v>20540</v>
+        <v>20575</v>
       </c>
       <c r="H54">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="I54">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J54">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K54">
         <v>109</v>
       </c>
       <c r="L54">
-        <v>1961</v>
+        <v>1993</v>
       </c>
       <c r="M54">
         <v>5</v>
       </c>
       <c r="N54">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="O54">
-        <v>17953</v>
+        <v>18148</v>
       </c>
       <c r="P54">
         <v>58440</v>
@@ -3825,22 +3825,22 @@
         <v>0</v>
       </c>
       <c r="G55">
-        <v>15997</v>
+        <v>16004</v>
       </c>
       <c r="H55">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I55">
         <v>0</v>
       </c>
       <c r="J55">
-        <v>213</v>
+        <v>98</v>
       </c>
       <c r="K55">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="L55">
-        <v>1788</v>
+        <v>1883</v>
       </c>
       <c r="M55">
         <v>1</v>
@@ -3849,7 +3849,7 @@
         <v>90</v>
       </c>
       <c r="O55">
-        <v>15523</v>
+        <v>15657</v>
       </c>
       <c r="P55">
         <v>58215</v>
@@ -3893,13 +3893,13 @@
         <v>0</v>
       </c>
       <c r="J56">
-        <v>760</v>
+        <v>557</v>
       </c>
       <c r="K56">
-        <v>401</v>
+        <v>281</v>
       </c>
       <c r="L56">
-        <v>3053</v>
+        <v>3253</v>
       </c>
       <c r="M56">
         <v>2</v>
@@ -3943,10 +3943,10 @@
         <v>0</v>
       </c>
       <c r="G57">
-        <v>21232</v>
+        <v>21235</v>
       </c>
       <c r="H57">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -3964,10 +3964,10 @@
         <v>5</v>
       </c>
       <c r="N57">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O57">
-        <v>21068</v>
+        <v>21108</v>
       </c>
       <c r="P57">
         <v>61556</v>
@@ -4002,31 +4002,31 @@
         <v>0</v>
       </c>
       <c r="G58">
-        <v>22043</v>
+        <v>22129</v>
       </c>
       <c r="H58">
-        <v>241</v>
+        <v>180</v>
       </c>
       <c r="I58">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J58">
-        <v>1392</v>
+        <v>1413</v>
       </c>
       <c r="K58">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="L58">
-        <v>6162</v>
+        <v>6188</v>
       </c>
       <c r="M58">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N58">
-        <v>357</v>
+        <v>390</v>
       </c>
       <c r="O58">
-        <v>17761</v>
+        <v>18228</v>
       </c>
       <c r="P58">
         <v>57577</v>
@@ -4120,22 +4120,22 @@
         <v>0</v>
       </c>
       <c r="G60">
-        <v>23595</v>
+        <v>23611</v>
       </c>
       <c r="H60">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="I60">
         <v>0</v>
       </c>
       <c r="J60">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K60">
         <v>0</v>
       </c>
       <c r="L60">
-        <v>5560</v>
+        <v>5563</v>
       </c>
       <c r="M60">
         <v>8</v>
@@ -4144,7 +4144,7 @@
         <v>266</v>
       </c>
       <c r="O60">
-        <v>21653</v>
+        <v>21665</v>
       </c>
       <c r="P60">
         <v>70140</v>
@@ -4188,7 +4188,7 @@
         <v>0</v>
       </c>
       <c r="J61">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K61">
         <v>2</v>
@@ -4238,16 +4238,16 @@
         <v>0</v>
       </c>
       <c r="G62">
-        <v>15795</v>
+        <v>15798</v>
       </c>
       <c r="H62">
         <v>0</v>
       </c>
       <c r="I62">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J62">
-        <v>361</v>
+        <v>384</v>
       </c>
       <c r="K62">
         <v>234</v>
@@ -4259,10 +4259,10 @@
         <v>15</v>
       </c>
       <c r="N62">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="O62">
-        <v>14776</v>
+        <v>14777</v>
       </c>
       <c r="P62">
         <v>51334</v>
@@ -4297,28 +4297,28 @@
         <v>0</v>
       </c>
       <c r="G63">
-        <v>36730</v>
+        <v>36740</v>
       </c>
       <c r="H63">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I63">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J63">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="K63">
         <v>0</v>
       </c>
       <c r="L63">
-        <v>10662</v>
+        <v>10692</v>
       </c>
       <c r="M63">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N63">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="O63">
         <v>32109</v>
@@ -4356,31 +4356,31 @@
         <v>0</v>
       </c>
       <c r="G64">
-        <v>41633</v>
+        <v>41697</v>
       </c>
       <c r="H64">
-        <v>398</v>
+        <v>338</v>
       </c>
       <c r="I64">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J64">
-        <v>216</v>
+        <v>184</v>
       </c>
       <c r="K64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L64">
-        <v>9448</v>
+        <v>9490</v>
       </c>
       <c r="M64">
         <v>8</v>
       </c>
       <c r="N64">
-        <v>258</v>
+        <v>295</v>
       </c>
       <c r="O64">
-        <v>40728</v>
+        <v>40743</v>
       </c>
       <c r="P64">
         <v>60527</v>
@@ -4415,16 +4415,16 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>38353</v>
+        <v>38470</v>
       </c>
       <c r="H65">
-        <v>1786</v>
+        <v>1742</v>
       </c>
       <c r="I65">
-        <v>1191</v>
+        <v>1119</v>
       </c>
       <c r="J65">
-        <v>216</v>
+        <v>264</v>
       </c>
       <c r="K65">
         <v>0</v>
@@ -4436,13 +4436,13 @@
         <v>2</v>
       </c>
       <c r="N65">
-        <v>756</v>
+        <v>828</v>
       </c>
       <c r="O65">
-        <v>27262</v>
+        <v>27373</v>
       </c>
       <c r="P65">
-        <v>37163</v>
+        <v>41452</v>
       </c>
       <c r="Q65">
         <v>13284</v>
@@ -4474,31 +4474,31 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>59913</v>
+        <v>60670</v>
       </c>
       <c r="H66">
-        <v>5613</v>
+        <v>5086</v>
       </c>
       <c r="I66">
-        <v>703</v>
+        <v>646</v>
       </c>
       <c r="J66">
-        <v>61</v>
+        <v>139</v>
       </c>
       <c r="K66">
         <v>0</v>
       </c>
       <c r="L66">
-        <v>12155</v>
+        <v>12238</v>
       </c>
       <c r="M66">
         <v>2</v>
       </c>
       <c r="N66">
-        <v>1913</v>
+        <v>1996</v>
       </c>
       <c r="O66">
-        <v>54293</v>
+        <v>55372</v>
       </c>
       <c r="P66">
         <v>93810</v>
@@ -4533,31 +4533,31 @@
         <v>0</v>
       </c>
       <c r="G67">
-        <v>64552</v>
+        <v>65096</v>
       </c>
       <c r="H67">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="I67">
-        <v>2587</v>
+        <v>2354</v>
       </c>
       <c r="J67">
-        <v>86</v>
+        <v>153</v>
       </c>
       <c r="K67">
         <v>0</v>
       </c>
       <c r="L67">
-        <v>18441</v>
+        <v>18505</v>
       </c>
       <c r="M67">
         <v>10</v>
       </c>
       <c r="N67">
-        <v>1434</v>
+        <v>1465</v>
       </c>
       <c r="O67">
-        <v>57488</v>
+        <v>58212</v>
       </c>
       <c r="P67">
         <v>78022</v>
@@ -4592,31 +4592,31 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>61186</v>
+        <v>61296</v>
       </c>
       <c r="H68">
-        <v>3080</v>
+        <v>2985</v>
       </c>
       <c r="I68">
-        <v>860</v>
+        <v>813</v>
       </c>
       <c r="J68">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="K68">
         <v>0</v>
       </c>
       <c r="L68">
-        <v>15973</v>
+        <v>16035</v>
       </c>
       <c r="M68">
         <v>2</v>
       </c>
       <c r="N68">
-        <v>455</v>
+        <v>472</v>
       </c>
       <c r="O68">
-        <v>51088</v>
+        <v>51152</v>
       </c>
       <c r="P68">
         <v>61644</v>
@@ -4651,31 +4651,31 @@
         <v>0</v>
       </c>
       <c r="G69">
-        <v>38663</v>
+        <v>38830</v>
       </c>
       <c r="H69">
-        <v>4938</v>
+        <v>4715</v>
       </c>
       <c r="I69">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="J69">
-        <v>173</v>
+        <v>78</v>
       </c>
       <c r="K69">
         <v>0</v>
       </c>
       <c r="L69">
-        <v>15310</v>
+        <v>15525</v>
       </c>
       <c r="M69">
         <v>2</v>
       </c>
       <c r="N69">
-        <v>323</v>
+        <v>357</v>
       </c>
       <c r="O69">
-        <v>35123</v>
+        <v>35378</v>
       </c>
       <c r="P69">
         <v>35481</v>
@@ -4710,31 +4710,31 @@
         <v>0</v>
       </c>
       <c r="G70">
-        <v>44689</v>
+        <v>45015</v>
       </c>
       <c r="H70">
-        <v>882</v>
+        <v>797</v>
       </c>
       <c r="I70">
-        <v>2140</v>
+        <v>1894</v>
       </c>
       <c r="J70">
-        <v>63</v>
+        <v>107</v>
       </c>
       <c r="K70">
         <v>0</v>
       </c>
       <c r="L70">
-        <v>17677</v>
+        <v>17738</v>
       </c>
       <c r="M70">
         <v>2</v>
       </c>
       <c r="N70">
-        <v>1020</v>
+        <v>1192</v>
       </c>
       <c r="O70">
-        <v>41072</v>
+        <v>41489</v>
       </c>
       <c r="P70">
         <v>42040</v>
@@ -4769,16 +4769,16 @@
         <v>0</v>
       </c>
       <c r="G71">
-        <v>48466</v>
+        <v>48807</v>
       </c>
       <c r="H71">
-        <v>1272</v>
+        <v>1044</v>
       </c>
       <c r="I71">
-        <v>1225</v>
+        <v>1112</v>
       </c>
       <c r="J71">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="K71">
         <v>0</v>
@@ -4790,10 +4790,10 @@
         <v>1</v>
       </c>
       <c r="N71">
-        <v>2979</v>
+        <v>3155</v>
       </c>
       <c r="O71">
-        <v>37636</v>
+        <v>37779</v>
       </c>
       <c r="P71">
         <v>48896</v>
@@ -4828,31 +4828,31 @@
         <v>0</v>
       </c>
       <c r="G72">
-        <v>57041</v>
+        <v>57521</v>
       </c>
       <c r="H72">
-        <v>3424</v>
+        <v>2992</v>
       </c>
       <c r="I72">
-        <v>1019</v>
+        <v>993</v>
       </c>
       <c r="J72">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="K72">
         <v>0</v>
       </c>
       <c r="L72">
-        <v>16084</v>
+        <v>16269</v>
       </c>
       <c r="M72">
         <v>9</v>
       </c>
       <c r="N72">
-        <v>1626</v>
+        <v>1799</v>
       </c>
       <c r="O72">
-        <v>45648</v>
+        <v>45877</v>
       </c>
       <c r="P72">
         <v>85505</v>
@@ -4887,31 +4887,31 @@
         <v>0</v>
       </c>
       <c r="G73">
-        <v>51332</v>
+        <v>51725</v>
       </c>
       <c r="H73">
-        <v>7391</v>
+        <v>7009</v>
       </c>
       <c r="I73">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="J73">
-        <v>367</v>
+        <v>129</v>
       </c>
       <c r="K73">
         <v>0</v>
       </c>
       <c r="L73">
-        <v>11367</v>
+        <v>11783</v>
       </c>
       <c r="M73">
         <v>6</v>
       </c>
       <c r="N73">
-        <v>882</v>
+        <v>960</v>
       </c>
       <c r="O73">
-        <v>45860</v>
+        <v>46301</v>
       </c>
       <c r="P73">
         <v>67550</v>
@@ -4938,40 +4938,40 @@
         <v>0</v>
       </c>
       <c r="E74">
-        <v>2430073</v>
+        <v>2430091</v>
       </c>
       <c r="F74">
-        <v>309</v>
+        <v>291</v>
       </c>
       <c r="G74">
-        <v>2200574</v>
+        <v>2214982</v>
       </c>
       <c r="H74">
-        <v>186614</v>
+        <v>175371</v>
       </c>
       <c r="I74">
-        <v>17570</v>
+        <v>16291</v>
       </c>
       <c r="J74">
-        <v>68055</v>
+        <v>66816</v>
       </c>
       <c r="K74">
-        <v>39640</v>
+        <v>38373</v>
       </c>
       <c r="L74">
-        <v>479788</v>
+        <v>485473</v>
       </c>
       <c r="M74">
-        <v>601</v>
+        <v>639</v>
       </c>
       <c r="N74">
-        <v>40265</v>
+        <v>42079</v>
       </c>
       <c r="O74">
-        <v>1948772</v>
+        <v>1966759</v>
       </c>
       <c r="P74">
-        <v>4503502</v>
+        <v>4538721</v>
       </c>
       <c r="Q74">
         <v>629442</v>

--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -303,7 +303,7 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Notice &amp; Hearing Report Last Updated On : 29-08-2026 13:57:04</t>
+    <t>Notice &amp; Hearing Report Last Updated On : 30-08-2026 10:00:03</t>
   </si>
 </sst>
 </file>
@@ -816,31 +816,31 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>42150</v>
+        <v>43225</v>
       </c>
       <c r="H4">
-        <v>8517</v>
+        <v>8108</v>
       </c>
       <c r="I4">
         <v>7</v>
       </c>
       <c r="J4">
-        <v>6256</v>
+        <v>2654</v>
       </c>
       <c r="K4">
-        <v>3511</v>
+        <v>1269</v>
       </c>
       <c r="L4">
-        <v>4828</v>
+        <v>8932</v>
       </c>
       <c r="M4">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="N4">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O4">
-        <v>34203</v>
+        <v>36681</v>
       </c>
       <c r="P4">
         <v>53812</v>
@@ -875,34 +875,34 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>48450</v>
+        <v>48936</v>
       </c>
       <c r="H5">
-        <v>4385</v>
+        <v>4219</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>2535</v>
+        <v>2709</v>
       </c>
       <c r="K5">
-        <v>1586</v>
+        <v>1925</v>
       </c>
       <c r="L5">
-        <v>4890</v>
+        <v>4934</v>
       </c>
       <c r="M5">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N5">
-        <v>372</v>
+        <v>419</v>
       </c>
       <c r="O5">
-        <v>44915</v>
+        <v>45354</v>
       </c>
       <c r="P5">
-        <v>56969</v>
+        <v>57974</v>
       </c>
       <c r="Q5">
         <v>16108</v>
@@ -934,34 +934,34 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>31043</v>
+        <v>32120</v>
       </c>
       <c r="H6">
-        <v>6257</v>
+        <v>6517</v>
       </c>
       <c r="I6">
-        <v>204</v>
+        <v>320</v>
       </c>
       <c r="J6">
-        <v>2396</v>
+        <v>2113</v>
       </c>
       <c r="K6">
-        <v>1219</v>
+        <v>884</v>
       </c>
       <c r="L6">
-        <v>1929</v>
+        <v>2364</v>
       </c>
       <c r="M6">
         <v>29</v>
       </c>
       <c r="N6">
-        <v>801</v>
+        <v>835</v>
       </c>
       <c r="O6">
-        <v>26523</v>
+        <v>27494</v>
       </c>
       <c r="P6">
-        <v>54999</v>
+        <v>55961</v>
       </c>
       <c r="Q6">
         <v>17918</v>
@@ -993,31 +993,31 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>37382</v>
+        <v>37794</v>
       </c>
       <c r="H7">
-        <v>1889</v>
+        <v>1668</v>
       </c>
       <c r="I7">
-        <v>192</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <v>3841</v>
+        <v>3366</v>
       </c>
       <c r="K7">
-        <v>3356</v>
+        <v>3087</v>
       </c>
       <c r="L7">
-        <v>1759</v>
+        <v>2257</v>
       </c>
       <c r="M7">
         <v>56</v>
       </c>
       <c r="N7">
-        <v>1399</v>
+        <v>1603</v>
       </c>
       <c r="O7">
-        <v>31417</v>
+        <v>31730</v>
       </c>
       <c r="P7">
         <v>77581</v>
@@ -1052,34 +1052,34 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>30438</v>
+        <v>31465</v>
       </c>
       <c r="H8">
-        <v>10114</v>
+        <v>9087</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>8575</v>
+        <v>7591</v>
       </c>
       <c r="K8">
-        <v>6165</v>
+        <v>5946</v>
       </c>
       <c r="L8">
-        <v>4718</v>
+        <v>5690</v>
       </c>
       <c r="M8">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="N8">
-        <v>335</v>
+        <v>417</v>
       </c>
       <c r="O8">
-        <v>20772</v>
+        <v>21625</v>
       </c>
       <c r="P8">
-        <v>70234</v>
+        <v>73458</v>
       </c>
       <c r="Q8">
         <v>20902</v>
@@ -1111,34 +1111,34 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>35964</v>
+        <v>37254</v>
       </c>
       <c r="H9">
-        <v>7001</v>
+        <v>5748</v>
       </c>
       <c r="I9">
-        <v>308</v>
+        <v>271</v>
       </c>
       <c r="J9">
-        <v>3250</v>
+        <v>3402</v>
       </c>
       <c r="K9">
-        <v>2636</v>
+        <v>2320</v>
       </c>
       <c r="L9">
-        <v>2781</v>
+        <v>3306</v>
       </c>
       <c r="M9">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="N9">
-        <v>366</v>
+        <v>461</v>
       </c>
       <c r="O9">
-        <v>30818</v>
+        <v>31914</v>
       </c>
       <c r="P9">
-        <v>66897</v>
+        <v>72647</v>
       </c>
       <c r="Q9">
         <v>18214</v>
@@ -1170,37 +1170,37 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>34281</v>
+        <v>35514</v>
       </c>
       <c r="H10">
-        <v>2258</v>
+        <v>1032</v>
       </c>
       <c r="I10">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J10">
-        <v>2152</v>
+        <v>2433</v>
       </c>
       <c r="K10">
-        <v>1245</v>
+        <v>1430</v>
       </c>
       <c r="L10">
-        <v>8078</v>
+        <v>8156</v>
       </c>
       <c r="M10">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="N10">
-        <v>427</v>
+        <v>456</v>
       </c>
       <c r="O10">
-        <v>26908</v>
+        <v>28533</v>
       </c>
       <c r="P10">
-        <v>52756</v>
+        <v>52921</v>
       </c>
       <c r="Q10">
-        <v>9511</v>
+        <v>9507</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -1229,31 +1229,31 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>43433</v>
+        <v>46522</v>
       </c>
       <c r="H11">
-        <v>6898</v>
+        <v>4050</v>
       </c>
       <c r="I11">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="J11">
-        <v>5929</v>
+        <v>6947</v>
       </c>
       <c r="K11">
-        <v>2639</v>
+        <v>2628</v>
       </c>
       <c r="L11">
-        <v>1571</v>
+        <v>2066</v>
       </c>
       <c r="M11">
         <v>20</v>
       </c>
       <c r="N11">
-        <v>371</v>
+        <v>505</v>
       </c>
       <c r="O11">
-        <v>35478</v>
+        <v>36920</v>
       </c>
       <c r="P11">
         <v>84443</v>
@@ -1288,31 +1288,31 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>35075</v>
+        <v>36810</v>
       </c>
       <c r="H12">
-        <v>5394</v>
+        <v>3669</v>
       </c>
       <c r="I12">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="J12">
-        <v>8595</v>
+        <v>8151</v>
       </c>
       <c r="K12">
-        <v>6794</v>
+        <v>6709</v>
       </c>
       <c r="L12">
-        <v>836</v>
+        <v>1366</v>
       </c>
       <c r="M12">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N12">
-        <v>608</v>
+        <v>674</v>
       </c>
       <c r="O12">
-        <v>25231</v>
+        <v>26810</v>
       </c>
       <c r="P12">
         <v>66685</v>
@@ -1341,37 +1341,37 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>37026</v>
+        <v>37031</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>32456</v>
+        <v>33718</v>
       </c>
       <c r="H13">
-        <v>4344</v>
+        <v>3301</v>
       </c>
       <c r="I13">
         <v>1</v>
       </c>
       <c r="J13">
-        <v>4993</v>
+        <v>5313</v>
       </c>
       <c r="K13">
-        <v>2062</v>
+        <v>2266</v>
       </c>
       <c r="L13">
-        <v>1231</v>
+        <v>1526</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N13">
-        <v>2821</v>
+        <v>3174</v>
       </c>
       <c r="O13">
-        <v>23517</v>
+        <v>23799</v>
       </c>
       <c r="P13">
         <v>56565</v>
@@ -1406,31 +1406,31 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>35460</v>
+        <v>37523</v>
       </c>
       <c r="H14">
-        <v>9685</v>
+        <v>9664</v>
       </c>
       <c r="I14">
         <v>569</v>
       </c>
       <c r="J14">
-        <v>9232</v>
+        <v>8373</v>
       </c>
       <c r="K14">
-        <v>6144</v>
+        <v>5767</v>
       </c>
       <c r="L14">
-        <v>1946</v>
+        <v>3518</v>
       </c>
       <c r="M14">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N14">
-        <v>1359</v>
+        <v>1744</v>
       </c>
       <c r="O14">
-        <v>23292</v>
+        <v>24259</v>
       </c>
       <c r="P14">
         <v>55446</v>
@@ -1465,37 +1465,37 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>42130</v>
+        <v>42703</v>
       </c>
       <c r="H15">
-        <v>573</v>
+        <v>0</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15">
-        <v>9016</v>
+        <v>9192</v>
       </c>
       <c r="M15">
         <v>0</v>
       </c>
       <c r="N15">
-        <v>2732</v>
+        <v>2821</v>
       </c>
       <c r="O15">
-        <v>39317</v>
+        <v>39882</v>
       </c>
       <c r="P15">
         <v>67178</v>
       </c>
       <c r="Q15">
-        <v>4892</v>
+        <v>4881</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -1524,34 +1524,34 @@
         <v>0</v>
       </c>
       <c r="G16">
-        <v>23763</v>
+        <v>24648</v>
       </c>
       <c r="H16">
-        <v>1370</v>
+        <v>701</v>
       </c>
       <c r="I16">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="J16">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
       <c r="L16">
-        <v>13361</v>
+        <v>14063</v>
       </c>
       <c r="M16">
         <v>1</v>
       </c>
       <c r="N16">
-        <v>121</v>
+        <v>180</v>
       </c>
       <c r="O16">
-        <v>21340</v>
+        <v>22457</v>
       </c>
       <c r="P16">
-        <v>68193</v>
+        <v>68729</v>
       </c>
       <c r="Q16">
         <v>5208</v>
@@ -1642,37 +1642,37 @@
         <v>25</v>
       </c>
       <c r="G18">
-        <v>47746</v>
+        <v>47799</v>
       </c>
       <c r="H18">
-        <v>87</v>
+        <v>35</v>
       </c>
       <c r="I18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J18">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K18">
         <v>0</v>
       </c>
       <c r="L18">
-        <v>7841</v>
+        <v>7868</v>
       </c>
       <c r="M18">
         <v>3</v>
       </c>
       <c r="N18">
-        <v>1917</v>
+        <v>1934</v>
       </c>
       <c r="O18">
-        <v>43962</v>
+        <v>44074</v>
       </c>
       <c r="P18">
         <v>70988</v>
       </c>
       <c r="Q18">
-        <v>6857</v>
+        <v>6856</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -1695,43 +1695,43 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>56416</v>
+        <v>56422</v>
       </c>
       <c r="F19">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G19">
-        <v>55542</v>
+        <v>55933</v>
       </c>
       <c r="H19">
-        <v>882</v>
+        <v>520</v>
       </c>
       <c r="I19">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="J19">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="K19">
         <v>0</v>
       </c>
       <c r="L19">
-        <v>14740</v>
+        <v>14984</v>
       </c>
       <c r="M19">
         <v>1</v>
       </c>
       <c r="N19">
-        <v>782</v>
+        <v>853</v>
       </c>
       <c r="O19">
-        <v>51735</v>
+        <v>53362</v>
       </c>
       <c r="P19">
         <v>106226</v>
       </c>
       <c r="Q19">
-        <v>6151</v>
+        <v>6140</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -1760,31 +1760,31 @@
         <v>0</v>
       </c>
       <c r="G20">
-        <v>34630</v>
+        <v>34711</v>
       </c>
       <c r="H20">
-        <v>375</v>
+        <v>306</v>
       </c>
       <c r="I20">
         <v>0</v>
       </c>
       <c r="J20">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K20">
         <v>0</v>
       </c>
       <c r="L20">
-        <v>5930</v>
+        <v>5996</v>
       </c>
       <c r="M20">
         <v>5</v>
       </c>
       <c r="N20">
-        <v>429</v>
+        <v>453</v>
       </c>
       <c r="O20">
-        <v>34141</v>
+        <v>34200</v>
       </c>
       <c r="P20">
         <v>75795</v>
@@ -1887,13 +1887,13 @@
         <v>0</v>
       </c>
       <c r="J22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K22">
         <v>0</v>
       </c>
       <c r="L22">
-        <v>7555</v>
+        <v>7557</v>
       </c>
       <c r="M22">
         <v>0</v>
@@ -2064,28 +2064,28 @@
         <v>0</v>
       </c>
       <c r="J25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25">
         <v>0</v>
       </c>
       <c r="L25">
-        <v>4849</v>
+        <v>4858</v>
       </c>
       <c r="M25">
         <v>0</v>
       </c>
       <c r="N25">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O25">
-        <v>18945</v>
+        <v>18964</v>
       </c>
       <c r="P25">
         <v>57533</v>
       </c>
       <c r="Q25">
-        <v>3232</v>
+        <v>3231</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -2114,31 +2114,31 @@
         <v>0</v>
       </c>
       <c r="G26">
-        <v>17513</v>
+        <v>17545</v>
       </c>
       <c r="H26">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="I26">
         <v>0</v>
       </c>
       <c r="J26">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K26">
         <v>0</v>
       </c>
       <c r="L26">
-        <v>3662</v>
+        <v>3675</v>
       </c>
       <c r="M26">
         <v>3</v>
       </c>
       <c r="N26">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="O26">
-        <v>17219</v>
+        <v>17291</v>
       </c>
       <c r="P26">
         <v>66594</v>
@@ -2173,34 +2173,34 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>35919</v>
+        <v>37415</v>
       </c>
       <c r="H27">
-        <v>7333</v>
+        <v>6861</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27">
-        <v>587</v>
+        <v>285</v>
       </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="L27">
-        <v>7332</v>
+        <v>8015</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N27">
         <v>56</v>
       </c>
       <c r="O27">
-        <v>34297</v>
+        <v>35819</v>
       </c>
       <c r="P27">
-        <v>49325</v>
+        <v>50631</v>
       </c>
       <c r="Q27">
         <v>12669</v>
@@ -2232,31 +2232,31 @@
         <v>76</v>
       </c>
       <c r="G28">
-        <v>32910</v>
+        <v>38333</v>
       </c>
       <c r="H28">
-        <v>19801</v>
+        <v>15953</v>
       </c>
       <c r="I28">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="J28">
-        <v>333</v>
+        <v>1026</v>
       </c>
       <c r="K28">
         <v>0</v>
       </c>
       <c r="L28">
-        <v>4416</v>
+        <v>4810</v>
       </c>
       <c r="M28">
         <v>11</v>
       </c>
       <c r="N28">
-        <v>554</v>
+        <v>608</v>
       </c>
       <c r="O28">
-        <v>28660</v>
+        <v>32998</v>
       </c>
       <c r="P28">
         <v>80639</v>
@@ -2291,31 +2291,31 @@
         <v>0</v>
       </c>
       <c r="G29">
-        <v>41852</v>
+        <v>42409</v>
       </c>
       <c r="H29">
-        <v>5017</v>
+        <v>4503</v>
       </c>
       <c r="I29">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="J29">
-        <v>139</v>
+        <v>204</v>
       </c>
       <c r="K29">
         <v>0</v>
       </c>
       <c r="L29">
-        <v>6967</v>
+        <v>7116</v>
       </c>
       <c r="M29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N29">
-        <v>779</v>
+        <v>833</v>
       </c>
       <c r="O29">
-        <v>36931</v>
+        <v>37437</v>
       </c>
       <c r="P29">
         <v>83837</v>
@@ -2350,31 +2350,31 @@
         <v>19</v>
       </c>
       <c r="G30">
-        <v>36083</v>
+        <v>39311</v>
       </c>
       <c r="H30">
-        <v>9050</v>
+        <v>4965</v>
       </c>
       <c r="I30">
-        <v>3618</v>
+        <v>5489</v>
       </c>
       <c r="J30">
-        <v>153</v>
+        <v>1050</v>
       </c>
       <c r="K30">
         <v>0</v>
       </c>
       <c r="L30">
-        <v>5096</v>
+        <v>5396</v>
       </c>
       <c r="M30">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N30">
-        <v>554</v>
+        <v>1157</v>
       </c>
       <c r="O30">
-        <v>33046</v>
+        <v>34774</v>
       </c>
       <c r="P30">
         <v>86935</v>
@@ -2409,31 +2409,31 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>89730</v>
+        <v>90062</v>
       </c>
       <c r="H31">
-        <v>540</v>
+        <v>917</v>
       </c>
       <c r="I31">
         <v>77</v>
       </c>
       <c r="J31">
-        <v>575</v>
+        <v>554</v>
       </c>
       <c r="K31">
         <v>0</v>
       </c>
       <c r="L31">
-        <v>42150</v>
+        <v>43114</v>
       </c>
       <c r="M31">
         <v>24</v>
       </c>
       <c r="N31">
-        <v>1762</v>
+        <v>1817</v>
       </c>
       <c r="O31">
-        <v>84445</v>
+        <v>85432</v>
       </c>
       <c r="P31">
         <v>81642</v>
@@ -2468,34 +2468,34 @@
         <v>19</v>
       </c>
       <c r="G32">
-        <v>32588</v>
+        <v>34751</v>
       </c>
       <c r="H32">
-        <v>13747</v>
+        <v>11598</v>
       </c>
       <c r="I32">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="J32">
-        <v>181</v>
+        <v>227</v>
       </c>
       <c r="K32">
         <v>0</v>
       </c>
       <c r="L32">
-        <v>7026</v>
+        <v>7262</v>
       </c>
       <c r="M32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N32">
-        <v>739</v>
+        <v>953</v>
       </c>
       <c r="O32">
-        <v>29485</v>
+        <v>31269</v>
       </c>
       <c r="P32">
-        <v>46145</v>
+        <v>60668</v>
       </c>
       <c r="Q32">
         <v>11379</v>
@@ -2521,28 +2521,28 @@
         <v>0</v>
       </c>
       <c r="E33">
-        <v>40229</v>
+        <v>40230</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33">
-        <v>33225</v>
+        <v>33814</v>
       </c>
       <c r="H33">
-        <v>6002</v>
+        <v>5762</v>
       </c>
       <c r="I33">
-        <v>49</v>
+        <v>536</v>
       </c>
       <c r="J33">
-        <v>187</v>
+        <v>58</v>
       </c>
       <c r="K33">
         <v>0</v>
       </c>
       <c r="L33">
-        <v>3785</v>
+        <v>4008</v>
       </c>
       <c r="M33">
         <v>24</v>
@@ -2551,10 +2551,10 @@
         <v>18</v>
       </c>
       <c r="O33">
-        <v>31586</v>
+        <v>32179</v>
       </c>
       <c r="P33">
-        <v>74014</v>
+        <v>74616</v>
       </c>
       <c r="Q33">
         <v>6678</v>
@@ -2586,31 +2586,31 @@
         <v>0</v>
       </c>
       <c r="G34">
-        <v>28871</v>
+        <v>29612</v>
       </c>
       <c r="H34">
-        <v>7671</v>
+        <v>6930</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
       <c r="J34">
-        <v>255</v>
+        <v>96</v>
       </c>
       <c r="K34">
         <v>0</v>
       </c>
       <c r="L34">
-        <v>9660</v>
+        <v>9944</v>
       </c>
       <c r="M34">
         <v>1</v>
       </c>
       <c r="N34">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O34">
-        <v>26722</v>
+        <v>27533</v>
       </c>
       <c r="P34">
         <v>74626</v>
@@ -2645,31 +2645,31 @@
         <v>9</v>
       </c>
       <c r="G35">
-        <v>28363</v>
+        <v>29095</v>
       </c>
       <c r="H35">
-        <v>4693</v>
+        <v>4379</v>
       </c>
       <c r="I35">
         <v>0</v>
       </c>
       <c r="J35">
-        <v>585</v>
+        <v>99</v>
       </c>
       <c r="K35">
         <v>0</v>
       </c>
       <c r="L35">
-        <v>4817</v>
+        <v>5473</v>
       </c>
       <c r="M35">
         <v>0</v>
       </c>
       <c r="N35">
-        <v>241</v>
+        <v>316</v>
       </c>
       <c r="O35">
-        <v>26132</v>
+        <v>27015</v>
       </c>
       <c r="P35">
         <v>72020</v>
@@ -2719,7 +2719,7 @@
         <v>0</v>
       </c>
       <c r="L36">
-        <v>7310</v>
+        <v>7314</v>
       </c>
       <c r="M36">
         <v>0</v>
@@ -2728,7 +2728,7 @@
         <v>949</v>
       </c>
       <c r="O36">
-        <v>19914</v>
+        <v>19918</v>
       </c>
       <c r="P36">
         <v>60419</v>
@@ -2831,28 +2831,28 @@
         <v>0</v>
       </c>
       <c r="J38">
-        <v>70</v>
+        <v>182</v>
       </c>
       <c r="K38">
         <v>0</v>
       </c>
       <c r="L38">
-        <v>4958</v>
+        <v>5043</v>
       </c>
       <c r="M38">
         <v>2</v>
       </c>
       <c r="N38">
-        <v>524</v>
+        <v>571</v>
       </c>
       <c r="O38">
-        <v>28040</v>
+        <v>28063</v>
       </c>
       <c r="P38">
         <v>63038</v>
       </c>
       <c r="Q38">
-        <v>5160</v>
+        <v>5143</v>
       </c>
       <c r="R38">
         <v>0</v>
@@ -2940,31 +2940,31 @@
         <v>0</v>
       </c>
       <c r="G40">
-        <v>17895</v>
+        <v>18265</v>
       </c>
       <c r="H40">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="I40">
         <v>0</v>
       </c>
       <c r="J40">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K40">
         <v>0</v>
       </c>
       <c r="L40">
-        <v>1535</v>
+        <v>1626</v>
       </c>
       <c r="M40">
         <v>0</v>
       </c>
       <c r="N40">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="O40">
-        <v>16771</v>
+        <v>17123</v>
       </c>
       <c r="P40">
         <v>73242</v>
@@ -2999,31 +2999,31 @@
         <v>0</v>
       </c>
       <c r="G41">
-        <v>22979</v>
+        <v>23475</v>
       </c>
       <c r="H41">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="I41">
         <v>0</v>
       </c>
       <c r="J41">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="K41">
         <v>0</v>
       </c>
       <c r="L41">
-        <v>1094</v>
+        <v>1219</v>
       </c>
       <c r="M41">
         <v>0</v>
       </c>
       <c r="N41">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="O41">
-        <v>21624</v>
+        <v>22071</v>
       </c>
       <c r="P41">
         <v>85249</v>
@@ -3067,13 +3067,13 @@
         <v>0</v>
       </c>
       <c r="J42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K42">
         <v>0</v>
       </c>
       <c r="L42">
-        <v>6260</v>
+        <v>6263</v>
       </c>
       <c r="M42">
         <v>0</v>
@@ -3082,7 +3082,7 @@
         <v>418</v>
       </c>
       <c r="O42">
-        <v>27144</v>
+        <v>27147</v>
       </c>
       <c r="P42">
         <v>68615</v>
@@ -3126,25 +3126,25 @@
         <v>0</v>
       </c>
       <c r="J43">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="K43">
         <v>0</v>
       </c>
       <c r="L43">
-        <v>6733</v>
+        <v>6785</v>
       </c>
       <c r="M43">
         <v>1</v>
       </c>
       <c r="N43">
-        <v>903</v>
+        <v>910</v>
       </c>
       <c r="O43">
-        <v>27966</v>
+        <v>28770</v>
       </c>
       <c r="P43">
-        <v>63036</v>
+        <v>63043</v>
       </c>
       <c r="Q43">
         <v>5260</v>
@@ -3176,31 +3176,31 @@
         <v>0</v>
       </c>
       <c r="G44">
-        <v>21643</v>
+        <v>21711</v>
       </c>
       <c r="H44">
-        <v>256</v>
+        <v>188</v>
       </c>
       <c r="I44">
         <v>0</v>
       </c>
       <c r="J44">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="K44">
         <v>0</v>
       </c>
       <c r="L44">
-        <v>6572</v>
+        <v>6582</v>
       </c>
       <c r="M44">
         <v>12</v>
       </c>
       <c r="N44">
-        <v>255</v>
+        <v>286</v>
       </c>
       <c r="O44">
-        <v>19727</v>
+        <v>20503</v>
       </c>
       <c r="P44">
         <v>68393</v>
@@ -3235,31 +3235,31 @@
         <v>0</v>
       </c>
       <c r="G45">
-        <v>17960</v>
+        <v>18285</v>
       </c>
       <c r="H45">
-        <v>1297</v>
+        <v>1290</v>
       </c>
       <c r="I45">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J45">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="K45">
         <v>0</v>
       </c>
       <c r="L45">
-        <v>2050</v>
+        <v>2095</v>
       </c>
       <c r="M45">
         <v>10</v>
       </c>
       <c r="N45">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="O45">
-        <v>16123</v>
+        <v>16360</v>
       </c>
       <c r="P45">
         <v>76002</v>
@@ -3294,31 +3294,31 @@
         <v>0</v>
       </c>
       <c r="G46">
-        <v>21247</v>
+        <v>21420</v>
       </c>
       <c r="H46">
-        <v>265</v>
+        <v>92</v>
       </c>
       <c r="I46">
         <v>0</v>
       </c>
       <c r="J46">
-        <v>271</v>
+        <v>54</v>
       </c>
       <c r="K46">
         <v>0</v>
       </c>
       <c r="L46">
-        <v>7876</v>
+        <v>8195</v>
       </c>
       <c r="M46">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="N46">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="O46">
-        <v>18909</v>
+        <v>19297</v>
       </c>
       <c r="P46">
         <v>64160</v>
@@ -3353,31 +3353,31 @@
         <v>0</v>
       </c>
       <c r="G47">
-        <v>21945</v>
+        <v>22078</v>
       </c>
       <c r="H47">
-        <v>443</v>
+        <v>310</v>
       </c>
       <c r="I47">
         <v>27</v>
       </c>
       <c r="J47">
-        <v>384</v>
+        <v>124</v>
       </c>
       <c r="K47">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L47">
-        <v>1913</v>
+        <v>2269</v>
       </c>
       <c r="M47">
         <v>1</v>
       </c>
       <c r="N47">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O47">
-        <v>20704</v>
+        <v>21016</v>
       </c>
       <c r="P47">
         <v>49875</v>
@@ -3421,13 +3421,13 @@
         <v>3</v>
       </c>
       <c r="J48">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K48">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L48">
-        <v>3757</v>
+        <v>3768</v>
       </c>
       <c r="M48">
         <v>4</v>
@@ -3436,7 +3436,7 @@
         <v>245</v>
       </c>
       <c r="O48">
-        <v>19295</v>
+        <v>19304</v>
       </c>
       <c r="P48">
         <v>54142</v>
@@ -3471,16 +3471,16 @@
         <v>19</v>
       </c>
       <c r="G49">
-        <v>19914</v>
+        <v>20100</v>
       </c>
       <c r="H49">
-        <v>879</v>
+        <v>838</v>
       </c>
       <c r="I49">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="J49">
-        <v>312</v>
+        <v>350</v>
       </c>
       <c r="K49">
         <v>0</v>
@@ -3492,13 +3492,13 @@
         <v>0</v>
       </c>
       <c r="N49">
-        <v>317</v>
+        <v>336</v>
       </c>
       <c r="O49">
-        <v>17868</v>
+        <v>18029</v>
       </c>
       <c r="P49">
-        <v>52446</v>
+        <v>52676</v>
       </c>
       <c r="Q49">
         <v>5057</v>
@@ -3530,31 +3530,31 @@
         <v>0</v>
       </c>
       <c r="G50">
-        <v>21640</v>
+        <v>21841</v>
       </c>
       <c r="H50">
-        <v>296</v>
+        <v>95</v>
       </c>
       <c r="I50">
         <v>0</v>
       </c>
       <c r="J50">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K50">
         <v>0</v>
       </c>
       <c r="L50">
-        <v>3894</v>
+        <v>4041</v>
       </c>
       <c r="M50">
         <v>5</v>
       </c>
       <c r="N50">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="O50">
-        <v>20585</v>
+        <v>21132</v>
       </c>
       <c r="P50">
         <v>63298</v>
@@ -3589,31 +3589,31 @@
         <v>0</v>
       </c>
       <c r="G51">
-        <v>22866</v>
+        <v>23323</v>
       </c>
       <c r="H51">
-        <v>618</v>
+        <v>475</v>
       </c>
       <c r="I51">
         <v>0</v>
       </c>
       <c r="J51">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K51">
         <v>0</v>
       </c>
       <c r="L51">
-        <v>4544</v>
+        <v>4647</v>
       </c>
       <c r="M51">
         <v>11</v>
       </c>
       <c r="N51">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="O51">
-        <v>20429</v>
+        <v>21775</v>
       </c>
       <c r="P51">
         <v>71754</v>
@@ -3648,16 +3648,16 @@
         <v>0</v>
       </c>
       <c r="G52">
-        <v>21037</v>
+        <v>21046</v>
       </c>
       <c r="H52">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I52">
         <v>0</v>
       </c>
       <c r="J52">
-        <v>47</v>
+        <v>105</v>
       </c>
       <c r="K52">
         <v>1</v>
@@ -3669,10 +3669,10 @@
         <v>1</v>
       </c>
       <c r="N52">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O52">
-        <v>20397</v>
+        <v>20520</v>
       </c>
       <c r="P52">
         <v>63986</v>
@@ -3716,13 +3716,13 @@
         <v>0</v>
       </c>
       <c r="J53">
-        <v>272</v>
+        <v>10</v>
       </c>
       <c r="K53">
-        <v>107</v>
+        <v>1</v>
       </c>
       <c r="L53">
-        <v>3165</v>
+        <v>3442</v>
       </c>
       <c r="M53">
         <v>1</v>
@@ -3731,7 +3731,7 @@
         <v>31</v>
       </c>
       <c r="O53">
-        <v>18585</v>
+        <v>18983</v>
       </c>
       <c r="P53">
         <v>56304</v>
@@ -3766,31 +3766,31 @@
         <v>0</v>
       </c>
       <c r="G54">
-        <v>20575</v>
+        <v>20668</v>
       </c>
       <c r="H54">
-        <v>139</v>
+        <v>61</v>
       </c>
       <c r="I54">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J54">
-        <v>431</v>
+        <v>197</v>
       </c>
       <c r="K54">
-        <v>109</v>
+        <v>12</v>
       </c>
       <c r="L54">
-        <v>1993</v>
+        <v>2284</v>
       </c>
       <c r="M54">
         <v>5</v>
       </c>
       <c r="N54">
-        <v>301</v>
+        <v>332</v>
       </c>
       <c r="O54">
-        <v>18148</v>
+        <v>18712</v>
       </c>
       <c r="P54">
         <v>58440</v>
@@ -3825,31 +3825,31 @@
         <v>0</v>
       </c>
       <c r="G55">
-        <v>16004</v>
+        <v>16012</v>
       </c>
       <c r="H55">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I55">
         <v>0</v>
       </c>
       <c r="J55">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="K55">
         <v>4</v>
       </c>
       <c r="L55">
-        <v>1883</v>
+        <v>1960</v>
       </c>
       <c r="M55">
         <v>1</v>
       </c>
       <c r="N55">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="O55">
-        <v>15657</v>
+        <v>15739</v>
       </c>
       <c r="P55">
         <v>58215</v>
@@ -3884,31 +3884,31 @@
         <v>0</v>
       </c>
       <c r="G56">
-        <v>19085</v>
+        <v>19150</v>
       </c>
       <c r="H56">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="I56">
         <v>0</v>
       </c>
       <c r="J56">
-        <v>557</v>
+        <v>2</v>
       </c>
       <c r="K56">
-        <v>281</v>
+        <v>0</v>
       </c>
       <c r="L56">
-        <v>3253</v>
+        <v>3692</v>
       </c>
       <c r="M56">
         <v>2</v>
       </c>
       <c r="N56">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="O56">
-        <v>14605</v>
+        <v>16285</v>
       </c>
       <c r="P56">
         <v>46365</v>
@@ -3943,10 +3943,10 @@
         <v>0</v>
       </c>
       <c r="G57">
-        <v>21235</v>
+        <v>21236</v>
       </c>
       <c r="H57">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -3967,7 +3967,7 @@
         <v>39</v>
       </c>
       <c r="O57">
-        <v>21108</v>
+        <v>21109</v>
       </c>
       <c r="P57">
         <v>61556</v>
@@ -4002,31 +4002,31 @@
         <v>0</v>
       </c>
       <c r="G58">
-        <v>22129</v>
+        <v>22271</v>
       </c>
       <c r="H58">
-        <v>180</v>
+        <v>142</v>
       </c>
       <c r="I58">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="J58">
-        <v>1413</v>
+        <v>802</v>
       </c>
       <c r="K58">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="L58">
-        <v>6188</v>
+        <v>6799</v>
       </c>
       <c r="M58">
         <v>4</v>
       </c>
       <c r="N58">
-        <v>390</v>
+        <v>462</v>
       </c>
       <c r="O58">
-        <v>18228</v>
+        <v>18916</v>
       </c>
       <c r="P58">
         <v>57577</v>
@@ -4120,16 +4120,16 @@
         <v>0</v>
       </c>
       <c r="G60">
-        <v>23611</v>
+        <v>23699</v>
       </c>
       <c r="H60">
-        <v>83</v>
+        <v>11</v>
       </c>
       <c r="I60">
         <v>0</v>
       </c>
       <c r="J60">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="K60">
         <v>0</v>
@@ -4141,10 +4141,10 @@
         <v>8</v>
       </c>
       <c r="N60">
-        <v>266</v>
+        <v>289</v>
       </c>
       <c r="O60">
-        <v>21665</v>
+        <v>21760</v>
       </c>
       <c r="P60">
         <v>70140</v>
@@ -4188,13 +4188,13 @@
         <v>0</v>
       </c>
       <c r="J61">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K61">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L61">
-        <v>9944</v>
+        <v>9976</v>
       </c>
       <c r="M61">
         <v>36</v>
@@ -4247,10 +4247,10 @@
         <v>2</v>
       </c>
       <c r="J62">
-        <v>384</v>
+        <v>435</v>
       </c>
       <c r="K62">
-        <v>234</v>
+        <v>285</v>
       </c>
       <c r="L62">
         <v>3690</v>
@@ -4297,31 +4297,31 @@
         <v>0</v>
       </c>
       <c r="G63">
-        <v>36740</v>
+        <v>36754</v>
       </c>
       <c r="H63">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I63">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J63">
-        <v>186</v>
+        <v>5</v>
       </c>
       <c r="K63">
         <v>0</v>
       </c>
       <c r="L63">
-        <v>10692</v>
+        <v>10868</v>
       </c>
       <c r="M63">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="N63">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="O63">
-        <v>32109</v>
+        <v>32187</v>
       </c>
       <c r="P63">
         <v>68691</v>
@@ -4356,31 +4356,31 @@
         <v>0</v>
       </c>
       <c r="G64">
-        <v>41697</v>
+        <v>41775</v>
       </c>
       <c r="H64">
-        <v>338</v>
+        <v>260</v>
       </c>
       <c r="I64">
         <v>13</v>
       </c>
       <c r="J64">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="K64">
         <v>0</v>
       </c>
       <c r="L64">
-        <v>9490</v>
+        <v>9530</v>
       </c>
       <c r="M64">
         <v>8</v>
       </c>
       <c r="N64">
-        <v>295</v>
+        <v>324</v>
       </c>
       <c r="O64">
-        <v>40743</v>
+        <v>40979</v>
       </c>
       <c r="P64">
         <v>60527</v>
@@ -4415,34 +4415,34 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>38470</v>
+        <v>38855</v>
       </c>
       <c r="H65">
-        <v>1742</v>
+        <v>1542</v>
       </c>
       <c r="I65">
-        <v>1119</v>
+        <v>956</v>
       </c>
       <c r="J65">
-        <v>264</v>
+        <v>122</v>
       </c>
       <c r="K65">
         <v>0</v>
       </c>
       <c r="L65">
-        <v>12207</v>
+        <v>12396</v>
       </c>
       <c r="M65">
         <v>2</v>
       </c>
       <c r="N65">
-        <v>828</v>
+        <v>1077</v>
       </c>
       <c r="O65">
-        <v>27373</v>
+        <v>27866</v>
       </c>
       <c r="P65">
-        <v>41452</v>
+        <v>54867</v>
       </c>
       <c r="Q65">
         <v>13284</v>
@@ -4474,31 +4474,31 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>60670</v>
+        <v>62218</v>
       </c>
       <c r="H66">
-        <v>5086</v>
+        <v>4594</v>
       </c>
       <c r="I66">
-        <v>646</v>
+        <v>550</v>
       </c>
       <c r="J66">
-        <v>139</v>
+        <v>11</v>
       </c>
       <c r="K66">
         <v>0</v>
       </c>
       <c r="L66">
-        <v>12238</v>
+        <v>12683</v>
       </c>
       <c r="M66">
         <v>2</v>
       </c>
       <c r="N66">
-        <v>1996</v>
+        <v>2200</v>
       </c>
       <c r="O66">
-        <v>55372</v>
+        <v>56803</v>
       </c>
       <c r="P66">
         <v>93810</v>
@@ -4533,37 +4533,37 @@
         <v>0</v>
       </c>
       <c r="G67">
-        <v>65096</v>
+        <v>65548</v>
       </c>
       <c r="H67">
         <v>0</v>
       </c>
       <c r="I67">
-        <v>2354</v>
+        <v>3275</v>
       </c>
       <c r="J67">
-        <v>153</v>
+        <v>18</v>
       </c>
       <c r="K67">
         <v>0</v>
       </c>
       <c r="L67">
-        <v>18505</v>
+        <v>18745</v>
       </c>
       <c r="M67">
         <v>10</v>
       </c>
       <c r="N67">
-        <v>1465</v>
+        <v>1530</v>
       </c>
       <c r="O67">
-        <v>58212</v>
+        <v>59709</v>
       </c>
       <c r="P67">
         <v>78022</v>
       </c>
       <c r="Q67">
-        <v>9810</v>
+        <v>9807</v>
       </c>
       <c r="R67">
         <v>0</v>
@@ -4592,34 +4592,34 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>61296</v>
+        <v>61670</v>
       </c>
       <c r="H68">
-        <v>2985</v>
+        <v>2692</v>
       </c>
       <c r="I68">
-        <v>813</v>
+        <v>914</v>
       </c>
       <c r="J68">
-        <v>36</v>
+        <v>138</v>
       </c>
       <c r="K68">
         <v>0</v>
       </c>
       <c r="L68">
-        <v>16035</v>
+        <v>16123</v>
       </c>
       <c r="M68">
         <v>2</v>
       </c>
       <c r="N68">
-        <v>472</v>
+        <v>563</v>
       </c>
       <c r="O68">
-        <v>51152</v>
+        <v>51297</v>
       </c>
       <c r="P68">
-        <v>61644</v>
+        <v>61648</v>
       </c>
       <c r="Q68">
         <v>7850</v>
@@ -4651,34 +4651,34 @@
         <v>0</v>
       </c>
       <c r="G69">
-        <v>38830</v>
+        <v>39184</v>
       </c>
       <c r="H69">
-        <v>4715</v>
+        <v>4412</v>
       </c>
       <c r="I69">
-        <v>321</v>
+        <v>270</v>
       </c>
       <c r="J69">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="K69">
         <v>0</v>
       </c>
       <c r="L69">
-        <v>15525</v>
+        <v>15784</v>
       </c>
       <c r="M69">
         <v>2</v>
       </c>
       <c r="N69">
-        <v>357</v>
+        <v>393</v>
       </c>
       <c r="O69">
-        <v>35378</v>
+        <v>35704</v>
       </c>
       <c r="P69">
-        <v>35481</v>
+        <v>35482</v>
       </c>
       <c r="Q69">
         <v>6528</v>
@@ -4710,31 +4710,31 @@
         <v>0</v>
       </c>
       <c r="G70">
-        <v>45015</v>
+        <v>45770</v>
       </c>
       <c r="H70">
-        <v>797</v>
+        <v>631</v>
       </c>
       <c r="I70">
-        <v>1894</v>
+        <v>1308</v>
       </c>
       <c r="J70">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="K70">
         <v>0</v>
       </c>
       <c r="L70">
-        <v>17738</v>
+        <v>17912</v>
       </c>
       <c r="M70">
         <v>2</v>
       </c>
       <c r="N70">
-        <v>1192</v>
+        <v>1710</v>
       </c>
       <c r="O70">
-        <v>41489</v>
+        <v>42585</v>
       </c>
       <c r="P70">
         <v>42040</v>
@@ -4769,31 +4769,31 @@
         <v>0</v>
       </c>
       <c r="G71">
-        <v>48807</v>
+        <v>49908</v>
       </c>
       <c r="H71">
-        <v>1044</v>
+        <v>366</v>
       </c>
       <c r="I71">
-        <v>1112</v>
+        <v>689</v>
       </c>
       <c r="J71">
-        <v>66</v>
+        <v>224</v>
       </c>
       <c r="K71">
         <v>0</v>
       </c>
       <c r="L71">
-        <v>22144</v>
+        <v>22257</v>
       </c>
       <c r="M71">
         <v>1</v>
       </c>
       <c r="N71">
-        <v>3155</v>
+        <v>3657</v>
       </c>
       <c r="O71">
-        <v>37779</v>
+        <v>39351</v>
       </c>
       <c r="P71">
         <v>48896</v>
@@ -4828,31 +4828,31 @@
         <v>0</v>
       </c>
       <c r="G72">
-        <v>57521</v>
+        <v>58603</v>
       </c>
       <c r="H72">
-        <v>2992</v>
+        <v>2086</v>
       </c>
       <c r="I72">
-        <v>993</v>
+        <v>854</v>
       </c>
       <c r="J72">
-        <v>119</v>
+        <v>70</v>
       </c>
       <c r="K72">
         <v>0</v>
       </c>
       <c r="L72">
-        <v>16269</v>
+        <v>16490</v>
       </c>
       <c r="M72">
         <v>9</v>
       </c>
       <c r="N72">
-        <v>1799</v>
+        <v>2327</v>
       </c>
       <c r="O72">
-        <v>45877</v>
+        <v>47761</v>
       </c>
       <c r="P72">
         <v>85505</v>
@@ -4887,31 +4887,31 @@
         <v>0</v>
       </c>
       <c r="G73">
-        <v>51725</v>
+        <v>52903</v>
       </c>
       <c r="H73">
-        <v>7009</v>
+        <v>5841</v>
       </c>
       <c r="I73">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="J73">
-        <v>129</v>
+        <v>447</v>
       </c>
       <c r="K73">
         <v>0</v>
       </c>
       <c r="L73">
-        <v>11783</v>
+        <v>12188</v>
       </c>
       <c r="M73">
         <v>6</v>
       </c>
       <c r="N73">
-        <v>960</v>
+        <v>1108</v>
       </c>
       <c r="O73">
-        <v>46301</v>
+        <v>47206</v>
       </c>
       <c r="P73">
         <v>67550</v>
@@ -4938,43 +4938,43 @@
         <v>0</v>
       </c>
       <c r="E74">
-        <v>2430091</v>
+        <v>2430103</v>
       </c>
       <c r="F74">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="G74">
-        <v>2214982</v>
+        <v>2257143</v>
       </c>
       <c r="H74">
-        <v>175371</v>
+        <v>146706</v>
       </c>
       <c r="I74">
-        <v>16291</v>
+        <v>18029</v>
       </c>
       <c r="J74">
-        <v>66816</v>
+        <v>60534</v>
       </c>
       <c r="K74">
-        <v>38373</v>
+        <v>34811</v>
       </c>
       <c r="L74">
-        <v>485473</v>
+        <v>505577</v>
       </c>
       <c r="M74">
-        <v>639</v>
+        <v>761</v>
       </c>
       <c r="N74">
-        <v>42079</v>
+        <v>47518</v>
       </c>
       <c r="O74">
-        <v>1966759</v>
+        <v>2014230</v>
       </c>
       <c r="P74">
-        <v>4538721</v>
+        <v>4580451</v>
       </c>
       <c r="Q74">
-        <v>629442</v>
+        <v>629394</v>
       </c>
       <c r="R74">
         <v>1</v>

--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MANNA\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DD368D4-02C9-4FAA-9037-02905543435E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -303,13 +304,13 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Notice &amp; Hearing Report Last Updated On : 30-08-2026 10:00:03</t>
+    <t>Notice &amp; Hearing Report Last Updated On : 31-08-2026 08:00:00</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -340,8 +341,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -680,7 +681,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T74"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -816,31 +817,31 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>43225</v>
+        <v>44795</v>
       </c>
       <c r="H4">
-        <v>8108</v>
+        <v>6556</v>
       </c>
       <c r="I4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J4">
-        <v>2654</v>
+        <v>1900</v>
       </c>
       <c r="K4">
-        <v>1269</v>
+        <v>532</v>
       </c>
       <c r="L4">
-        <v>8932</v>
+        <v>10556</v>
       </c>
       <c r="M4">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N4">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="O4">
-        <v>36681</v>
+        <v>40953</v>
       </c>
       <c r="P4">
         <v>53812</v>
@@ -875,34 +876,34 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>48936</v>
+        <v>49573</v>
       </c>
       <c r="H5">
-        <v>4219</v>
+        <v>3587</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>2709</v>
+        <v>1760</v>
       </c>
       <c r="K5">
-        <v>1925</v>
+        <v>1033</v>
       </c>
       <c r="L5">
-        <v>4934</v>
+        <v>6281</v>
       </c>
       <c r="M5">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="N5">
-        <v>419</v>
+        <v>457</v>
       </c>
       <c r="O5">
-        <v>45354</v>
+        <v>46227</v>
       </c>
       <c r="P5">
-        <v>57974</v>
+        <v>61262</v>
       </c>
       <c r="Q5">
         <v>16108</v>
@@ -934,34 +935,34 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>32120</v>
+        <v>33978</v>
       </c>
       <c r="H6">
-        <v>6517</v>
+        <v>4789</v>
       </c>
       <c r="I6">
-        <v>320</v>
+        <v>336</v>
       </c>
       <c r="J6">
-        <v>2113</v>
+        <v>2444</v>
       </c>
       <c r="K6">
-        <v>884</v>
+        <v>955</v>
       </c>
       <c r="L6">
-        <v>2364</v>
+        <v>2465</v>
       </c>
       <c r="M6">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N6">
-        <v>835</v>
+        <v>987</v>
       </c>
       <c r="O6">
-        <v>27494</v>
+        <v>28783</v>
       </c>
       <c r="P6">
-        <v>55961</v>
+        <v>56698</v>
       </c>
       <c r="Q6">
         <v>17918</v>
@@ -993,31 +994,31 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>37794</v>
+        <v>38339</v>
       </c>
       <c r="H7">
-        <v>1668</v>
+        <v>1123</v>
       </c>
       <c r="I7">
         <v>1</v>
       </c>
       <c r="J7">
-        <v>3366</v>
+        <v>3120</v>
       </c>
       <c r="K7">
-        <v>3087</v>
+        <v>2930</v>
       </c>
       <c r="L7">
-        <v>2257</v>
+        <v>2525</v>
       </c>
       <c r="M7">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="N7">
-        <v>1603</v>
+        <v>1697</v>
       </c>
       <c r="O7">
-        <v>31730</v>
+        <v>32435</v>
       </c>
       <c r="P7">
         <v>77581</v>
@@ -1052,31 +1053,31 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>31465</v>
+        <v>33722</v>
       </c>
       <c r="H8">
-        <v>9087</v>
+        <v>6830</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>7591</v>
+        <v>7018</v>
       </c>
       <c r="K8">
-        <v>5946</v>
+        <v>5781</v>
       </c>
       <c r="L8">
-        <v>5690</v>
+        <v>6392</v>
       </c>
       <c r="M8">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N8">
-        <v>417</v>
+        <v>482</v>
       </c>
       <c r="O8">
-        <v>21625</v>
+        <v>23984</v>
       </c>
       <c r="P8">
         <v>73458</v>
@@ -1111,37 +1112,37 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>37254</v>
+        <v>39807</v>
       </c>
       <c r="H9">
-        <v>5748</v>
+        <v>3414</v>
       </c>
       <c r="I9">
-        <v>271</v>
+        <v>52</v>
       </c>
       <c r="J9">
-        <v>3402</v>
+        <v>3524</v>
       </c>
       <c r="K9">
-        <v>2320</v>
+        <v>2176</v>
       </c>
       <c r="L9">
-        <v>3306</v>
+        <v>3496</v>
       </c>
       <c r="M9">
         <v>16</v>
       </c>
       <c r="N9">
-        <v>461</v>
+        <v>914</v>
       </c>
       <c r="O9">
-        <v>31914</v>
+        <v>34992</v>
       </c>
       <c r="P9">
-        <v>72647</v>
+        <v>72763</v>
       </c>
       <c r="Q9">
-        <v>18214</v>
+        <v>18178</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -1170,37 +1171,37 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>35514</v>
+        <v>36183</v>
       </c>
       <c r="H10">
-        <v>1032</v>
+        <v>393</v>
       </c>
       <c r="I10">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>2433</v>
+        <v>2545</v>
       </c>
       <c r="K10">
-        <v>1430</v>
+        <v>1384</v>
       </c>
       <c r="L10">
-        <v>8156</v>
+        <v>8282</v>
       </c>
       <c r="M10">
         <v>54</v>
       </c>
       <c r="N10">
-        <v>456</v>
+        <v>625</v>
       </c>
       <c r="O10">
-        <v>28533</v>
+        <v>32027</v>
       </c>
       <c r="P10">
-        <v>52921</v>
+        <v>53124</v>
       </c>
       <c r="Q10">
-        <v>9507</v>
+        <v>9502</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -1229,34 +1230,34 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>46522</v>
+        <v>47950</v>
       </c>
       <c r="H11">
-        <v>4050</v>
+        <v>2633</v>
       </c>
       <c r="I11">
         <v>414</v>
       </c>
       <c r="J11">
-        <v>6947</v>
+        <v>4959</v>
       </c>
       <c r="K11">
-        <v>2628</v>
+        <v>2940</v>
       </c>
       <c r="L11">
-        <v>2066</v>
+        <v>4007</v>
       </c>
       <c r="M11">
-        <v>20</v>
+        <v>153</v>
       </c>
       <c r="N11">
-        <v>505</v>
+        <v>659</v>
       </c>
       <c r="O11">
-        <v>36920</v>
+        <v>37956</v>
       </c>
       <c r="P11">
-        <v>84443</v>
+        <v>84442</v>
       </c>
       <c r="Q11">
         <v>23805</v>
@@ -1288,31 +1289,31 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>36810</v>
+        <v>38264</v>
       </c>
       <c r="H12">
-        <v>3669</v>
+        <v>2236</v>
       </c>
       <c r="I12">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="J12">
-        <v>8151</v>
+        <v>7415</v>
       </c>
       <c r="K12">
-        <v>6709</v>
+        <v>6358</v>
       </c>
       <c r="L12">
-        <v>1366</v>
+        <v>2178</v>
       </c>
       <c r="M12">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="N12">
-        <v>674</v>
+        <v>701</v>
       </c>
       <c r="O12">
-        <v>26810</v>
+        <v>28101</v>
       </c>
       <c r="P12">
         <v>66685</v>
@@ -1347,31 +1348,31 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>33718</v>
+        <v>35156</v>
       </c>
       <c r="H13">
-        <v>3301</v>
+        <v>1863</v>
       </c>
       <c r="I13">
         <v>1</v>
       </c>
       <c r="J13">
-        <v>5313</v>
+        <v>5306</v>
       </c>
       <c r="K13">
-        <v>2266</v>
+        <v>2504</v>
       </c>
       <c r="L13">
-        <v>1526</v>
+        <v>2171</v>
       </c>
       <c r="M13">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="N13">
-        <v>3174</v>
+        <v>3458</v>
       </c>
       <c r="O13">
-        <v>23799</v>
+        <v>24302</v>
       </c>
       <c r="P13">
         <v>56565</v>
@@ -1406,31 +1407,31 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>37523</v>
+        <v>40340</v>
       </c>
       <c r="H14">
-        <v>9664</v>
+        <v>7387</v>
       </c>
       <c r="I14">
-        <v>569</v>
+        <v>98</v>
       </c>
       <c r="J14">
-        <v>8373</v>
+        <v>7567</v>
       </c>
       <c r="K14">
-        <v>5767</v>
+        <v>4830</v>
       </c>
       <c r="L14">
-        <v>3518</v>
+        <v>5774</v>
       </c>
       <c r="M14">
-        <v>66</v>
+        <v>111</v>
       </c>
       <c r="N14">
-        <v>1744</v>
+        <v>2112</v>
       </c>
       <c r="O14">
-        <v>24259</v>
+        <v>25253</v>
       </c>
       <c r="P14">
         <v>55446</v>
@@ -1495,7 +1496,7 @@
         <v>67178</v>
       </c>
       <c r="Q15">
-        <v>4881</v>
+        <v>4869</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -1524,34 +1525,34 @@
         <v>0</v>
       </c>
       <c r="G16">
-        <v>24648</v>
+        <v>25135</v>
       </c>
       <c r="H16">
-        <v>701</v>
+        <v>335</v>
       </c>
       <c r="I16">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="J16">
-        <v>18</v>
+        <v>244</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
       <c r="L16">
-        <v>14063</v>
+        <v>14270</v>
       </c>
       <c r="M16">
         <v>1</v>
       </c>
       <c r="N16">
-        <v>180</v>
+        <v>223</v>
       </c>
       <c r="O16">
-        <v>22457</v>
+        <v>23038</v>
       </c>
       <c r="P16">
-        <v>68729</v>
+        <v>71052</v>
       </c>
       <c r="Q16">
         <v>5208</v>
@@ -1636,16 +1637,16 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>47811</v>
+        <v>47836</v>
       </c>
       <c r="F18">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G18">
-        <v>47799</v>
+        <v>47808</v>
       </c>
       <c r="H18">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="I18">
         <v>2</v>
@@ -1663,13 +1664,13 @@
         <v>3</v>
       </c>
       <c r="N18">
-        <v>1934</v>
+        <v>1942</v>
       </c>
       <c r="O18">
-        <v>44074</v>
+        <v>44464</v>
       </c>
       <c r="P18">
-        <v>70988</v>
+        <v>71475</v>
       </c>
       <c r="Q18">
         <v>6856</v>
@@ -1695,19 +1696,19 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>56422</v>
+        <v>56466</v>
       </c>
       <c r="F19">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="G19">
-        <v>55933</v>
+        <v>56253</v>
       </c>
       <c r="H19">
-        <v>520</v>
+        <v>207</v>
       </c>
       <c r="I19">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -1716,22 +1717,22 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>14984</v>
+        <v>15157</v>
       </c>
       <c r="M19">
         <v>1</v>
       </c>
       <c r="N19">
-        <v>853</v>
+        <v>872</v>
       </c>
       <c r="O19">
-        <v>53362</v>
+        <v>54135</v>
       </c>
       <c r="P19">
         <v>106226</v>
       </c>
       <c r="Q19">
-        <v>6140</v>
+        <v>6139</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -1760,22 +1761,22 @@
         <v>0</v>
       </c>
       <c r="G20">
-        <v>34711</v>
+        <v>34750</v>
       </c>
       <c r="H20">
-        <v>306</v>
+        <v>266</v>
       </c>
       <c r="I20">
         <v>0</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20">
         <v>0</v>
       </c>
       <c r="L20">
-        <v>5996</v>
+        <v>6023</v>
       </c>
       <c r="M20">
         <v>5</v>
@@ -1784,19 +1785,19 @@
         <v>453</v>
       </c>
       <c r="O20">
-        <v>34200</v>
+        <v>34257</v>
       </c>
       <c r="P20">
-        <v>75795</v>
+        <v>75799</v>
       </c>
       <c r="Q20">
-        <v>9010</v>
+        <v>8998</v>
       </c>
       <c r="R20">
         <v>0</v>
       </c>
       <c r="S20">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
@@ -2114,22 +2115,22 @@
         <v>0</v>
       </c>
       <c r="G26">
-        <v>17545</v>
+        <v>17557</v>
       </c>
       <c r="H26">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I26">
         <v>0</v>
       </c>
       <c r="J26">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K26">
         <v>0</v>
       </c>
       <c r="L26">
-        <v>3675</v>
+        <v>3711</v>
       </c>
       <c r="M26">
         <v>3</v>
@@ -2138,7 +2139,7 @@
         <v>192</v>
       </c>
       <c r="O26">
-        <v>17291</v>
+        <v>17332</v>
       </c>
       <c r="P26">
         <v>66594</v>
@@ -2173,34 +2174,34 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>37415</v>
+        <v>38967</v>
       </c>
       <c r="H27">
-        <v>6861</v>
+        <v>5309</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27">
-        <v>285</v>
+        <v>490</v>
       </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="L27">
-        <v>8015</v>
+        <v>8220</v>
       </c>
       <c r="M27">
         <v>2</v>
       </c>
       <c r="N27">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O27">
-        <v>35819</v>
+        <v>37396</v>
       </c>
       <c r="P27">
-        <v>50631</v>
+        <v>54979</v>
       </c>
       <c r="Q27">
         <v>12669</v>
@@ -2226,22 +2227,22 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>54273</v>
+        <v>54346</v>
       </c>
       <c r="F28">
-        <v>76</v>
+        <v>3</v>
       </c>
       <c r="G28">
-        <v>38333</v>
+        <v>41765</v>
       </c>
       <c r="H28">
-        <v>15953</v>
+        <v>12521</v>
       </c>
       <c r="I28">
         <v>57</v>
       </c>
       <c r="J28">
-        <v>1026</v>
+        <v>1754</v>
       </c>
       <c r="K28">
         <v>0</v>
@@ -2253,16 +2254,16 @@
         <v>11</v>
       </c>
       <c r="N28">
-        <v>608</v>
+        <v>727</v>
       </c>
       <c r="O28">
-        <v>32998</v>
+        <v>36652</v>
       </c>
       <c r="P28">
-        <v>80639</v>
+        <v>80638</v>
       </c>
       <c r="Q28">
-        <v>14114</v>
+        <v>14113</v>
       </c>
       <c r="R28">
         <v>0</v>
@@ -2291,31 +2292,31 @@
         <v>0</v>
       </c>
       <c r="G29">
-        <v>42409</v>
+        <v>45692</v>
       </c>
       <c r="H29">
-        <v>4503</v>
+        <v>1343</v>
       </c>
       <c r="I29">
-        <v>182</v>
+        <v>76</v>
       </c>
       <c r="J29">
-        <v>204</v>
+        <v>327</v>
       </c>
       <c r="K29">
         <v>0</v>
       </c>
       <c r="L29">
-        <v>7116</v>
+        <v>7295</v>
       </c>
       <c r="M29">
         <v>6</v>
       </c>
       <c r="N29">
-        <v>833</v>
+        <v>3108</v>
       </c>
       <c r="O29">
-        <v>37437</v>
+        <v>39059</v>
       </c>
       <c r="P29">
         <v>83837</v>
@@ -2344,37 +2345,37 @@
         <v>0</v>
       </c>
       <c r="E30">
-        <v>52634</v>
+        <v>52640</v>
       </c>
       <c r="F30">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G30">
-        <v>39311</v>
+        <v>43161</v>
       </c>
       <c r="H30">
-        <v>4965</v>
+        <v>2471</v>
       </c>
       <c r="I30">
-        <v>5489</v>
+        <v>6377</v>
       </c>
       <c r="J30">
-        <v>1050</v>
+        <v>1217</v>
       </c>
       <c r="K30">
         <v>0</v>
       </c>
       <c r="L30">
-        <v>5396</v>
+        <v>5722</v>
       </c>
       <c r="M30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N30">
-        <v>1157</v>
+        <v>2650</v>
       </c>
       <c r="O30">
-        <v>34774</v>
+        <v>37209</v>
       </c>
       <c r="P30">
         <v>86935</v>
@@ -2409,31 +2410,31 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>90062</v>
+        <v>90207</v>
       </c>
       <c r="H31">
-        <v>917</v>
+        <v>761</v>
       </c>
       <c r="I31">
         <v>77</v>
       </c>
       <c r="J31">
-        <v>554</v>
+        <v>455</v>
       </c>
       <c r="K31">
         <v>0</v>
       </c>
       <c r="L31">
-        <v>43114</v>
+        <v>44100</v>
       </c>
       <c r="M31">
         <v>24</v>
       </c>
       <c r="N31">
-        <v>1817</v>
+        <v>1845</v>
       </c>
       <c r="O31">
-        <v>85432</v>
+        <v>85942</v>
       </c>
       <c r="P31">
         <v>81642</v>
@@ -2462,40 +2463,40 @@
         <v>0</v>
       </c>
       <c r="E32">
-        <v>46709</v>
+        <v>46718</v>
       </c>
       <c r="F32">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G32">
-        <v>34751</v>
+        <v>37093</v>
       </c>
       <c r="H32">
-        <v>11598</v>
+        <v>9263</v>
       </c>
       <c r="I32">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="J32">
-        <v>227</v>
+        <v>873</v>
       </c>
       <c r="K32">
         <v>0</v>
       </c>
       <c r="L32">
-        <v>7262</v>
+        <v>7367</v>
       </c>
       <c r="M32">
         <v>10</v>
       </c>
       <c r="N32">
-        <v>953</v>
+        <v>1121</v>
       </c>
       <c r="O32">
-        <v>31269</v>
+        <v>32779</v>
       </c>
       <c r="P32">
-        <v>60668</v>
+        <v>74817</v>
       </c>
       <c r="Q32">
         <v>11379</v>
@@ -2527,16 +2528,16 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <v>33814</v>
+        <v>34617</v>
       </c>
       <c r="H33">
-        <v>5762</v>
+        <v>4993</v>
       </c>
       <c r="I33">
-        <v>536</v>
+        <v>465</v>
       </c>
       <c r="J33">
-        <v>58</v>
+        <v>136</v>
       </c>
       <c r="K33">
         <v>0</v>
@@ -2548,10 +2549,10 @@
         <v>24</v>
       </c>
       <c r="N33">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="O33">
-        <v>32179</v>
+        <v>32917</v>
       </c>
       <c r="P33">
         <v>74616</v>
@@ -2586,31 +2587,31 @@
         <v>0</v>
       </c>
       <c r="G34">
-        <v>29612</v>
+        <v>30845</v>
       </c>
       <c r="H34">
-        <v>6930</v>
+        <v>5697</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
       <c r="J34">
-        <v>96</v>
+        <v>484</v>
       </c>
       <c r="K34">
         <v>0</v>
       </c>
       <c r="L34">
-        <v>9944</v>
+        <v>10008</v>
       </c>
       <c r="M34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N34">
-        <v>10</v>
+        <v>108</v>
       </c>
       <c r="O34">
-        <v>27533</v>
+        <v>28277</v>
       </c>
       <c r="P34">
         <v>74626</v>
@@ -2639,40 +2640,40 @@
         <v>0</v>
       </c>
       <c r="E35">
-        <v>33555</v>
+        <v>33564</v>
       </c>
       <c r="F35">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G35">
-        <v>29095</v>
+        <v>29693</v>
       </c>
       <c r="H35">
-        <v>4379</v>
+        <v>3781</v>
       </c>
       <c r="I35">
         <v>0</v>
       </c>
       <c r="J35">
-        <v>99</v>
+        <v>713</v>
       </c>
       <c r="K35">
         <v>0</v>
       </c>
       <c r="L35">
-        <v>5473</v>
+        <v>5476</v>
       </c>
       <c r="M35">
         <v>0</v>
       </c>
       <c r="N35">
-        <v>316</v>
+        <v>389</v>
       </c>
       <c r="O35">
-        <v>27015</v>
+        <v>27179</v>
       </c>
       <c r="P35">
-        <v>72020</v>
+        <v>75609</v>
       </c>
       <c r="Q35">
         <v>8879</v>
@@ -2831,7 +2832,7 @@
         <v>0</v>
       </c>
       <c r="J38">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="K38">
         <v>0</v>
@@ -2843,7 +2844,7 @@
         <v>2</v>
       </c>
       <c r="N38">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="O38">
         <v>28063</v>
@@ -2852,7 +2853,7 @@
         <v>63038</v>
       </c>
       <c r="Q38">
-        <v>5143</v>
+        <v>5139</v>
       </c>
       <c r="R38">
         <v>0</v>
@@ -2940,31 +2941,31 @@
         <v>0</v>
       </c>
       <c r="G40">
-        <v>18265</v>
+        <v>18804</v>
       </c>
       <c r="H40">
-        <v>94</v>
+        <v>5</v>
       </c>
       <c r="I40">
         <v>0</v>
       </c>
       <c r="J40">
-        <v>15</v>
+        <v>103</v>
       </c>
       <c r="K40">
         <v>0</v>
       </c>
       <c r="L40">
-        <v>1626</v>
+        <v>1641</v>
       </c>
       <c r="M40">
         <v>0</v>
       </c>
       <c r="N40">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="O40">
-        <v>17123</v>
+        <v>17680</v>
       </c>
       <c r="P40">
         <v>73242</v>
@@ -2999,31 +3000,31 @@
         <v>0</v>
       </c>
       <c r="G41">
-        <v>23475</v>
+        <v>23505</v>
       </c>
       <c r="H41">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I41">
         <v>0</v>
       </c>
       <c r="J41">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="K41">
         <v>0</v>
       </c>
       <c r="L41">
-        <v>1219</v>
+        <v>1261</v>
       </c>
       <c r="M41">
         <v>0</v>
       </c>
       <c r="N41">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="O41">
-        <v>22071</v>
+        <v>22136</v>
       </c>
       <c r="P41">
         <v>85249</v>
@@ -3067,13 +3068,13 @@
         <v>0</v>
       </c>
       <c r="J42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42">
         <v>0</v>
       </c>
       <c r="L42">
-        <v>6263</v>
+        <v>6264</v>
       </c>
       <c r="M42">
         <v>0</v>
@@ -3082,7 +3083,7 @@
         <v>418</v>
       </c>
       <c r="O42">
-        <v>27147</v>
+        <v>27148</v>
       </c>
       <c r="P42">
         <v>68615</v>
@@ -3126,13 +3127,13 @@
         <v>0</v>
       </c>
       <c r="J43">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K43">
         <v>0</v>
       </c>
       <c r="L43">
-        <v>6785</v>
+        <v>6792</v>
       </c>
       <c r="M43">
         <v>1</v>
@@ -3141,7 +3142,7 @@
         <v>910</v>
       </c>
       <c r="O43">
-        <v>28770</v>
+        <v>28771</v>
       </c>
       <c r="P43">
         <v>63043</v>
@@ -3176,31 +3177,31 @@
         <v>0</v>
       </c>
       <c r="G44">
-        <v>21711</v>
+        <v>21756</v>
       </c>
       <c r="H44">
-        <v>188</v>
+        <v>143</v>
       </c>
       <c r="I44">
         <v>0</v>
       </c>
       <c r="J44">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="K44">
         <v>0</v>
       </c>
       <c r="L44">
-        <v>6582</v>
+        <v>6586</v>
       </c>
       <c r="M44">
         <v>12</v>
       </c>
       <c r="N44">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="O44">
-        <v>20503</v>
+        <v>21074</v>
       </c>
       <c r="P44">
         <v>68393</v>
@@ -3235,16 +3236,16 @@
         <v>0</v>
       </c>
       <c r="G45">
-        <v>18285</v>
+        <v>18531</v>
       </c>
       <c r="H45">
-        <v>1290</v>
+        <v>1047</v>
       </c>
       <c r="I45">
         <v>1</v>
       </c>
       <c r="J45">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="K45">
         <v>0</v>
@@ -3256,10 +3257,10 @@
         <v>10</v>
       </c>
       <c r="N45">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="O45">
-        <v>16360</v>
+        <v>16594</v>
       </c>
       <c r="P45">
         <v>76002</v>
@@ -3294,16 +3295,16 @@
         <v>0</v>
       </c>
       <c r="G46">
-        <v>21420</v>
+        <v>21501</v>
       </c>
       <c r="H46">
-        <v>92</v>
+        <v>11</v>
       </c>
       <c r="I46">
         <v>0</v>
       </c>
       <c r="J46">
-        <v>54</v>
+        <v>101</v>
       </c>
       <c r="K46">
         <v>0</v>
@@ -3315,10 +3316,10 @@
         <v>19</v>
       </c>
       <c r="N46">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O46">
-        <v>19297</v>
+        <v>19334</v>
       </c>
       <c r="P46">
         <v>64160</v>
@@ -3353,31 +3354,31 @@
         <v>0</v>
       </c>
       <c r="G47">
-        <v>22078</v>
+        <v>22265</v>
       </c>
       <c r="H47">
-        <v>310</v>
+        <v>133</v>
       </c>
       <c r="I47">
         <v>27</v>
       </c>
       <c r="J47">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="K47">
         <v>0</v>
       </c>
       <c r="L47">
-        <v>2269</v>
+        <v>2385</v>
       </c>
       <c r="M47">
         <v>1</v>
       </c>
       <c r="N47">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="O47">
-        <v>21016</v>
+        <v>21119</v>
       </c>
       <c r="P47">
         <v>49875</v>
@@ -3471,34 +3472,34 @@
         <v>19</v>
       </c>
       <c r="G49">
-        <v>20100</v>
+        <v>20257</v>
       </c>
       <c r="H49">
-        <v>838</v>
+        <v>960</v>
       </c>
       <c r="I49">
-        <v>236</v>
+        <v>268</v>
       </c>
       <c r="J49">
-        <v>350</v>
+        <v>52</v>
       </c>
       <c r="K49">
         <v>0</v>
       </c>
       <c r="L49">
-        <v>3116</v>
+        <v>3476</v>
       </c>
       <c r="M49">
         <v>0</v>
       </c>
       <c r="N49">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="O49">
-        <v>18029</v>
+        <v>18539</v>
       </c>
       <c r="P49">
-        <v>52676</v>
+        <v>54938</v>
       </c>
       <c r="Q49">
         <v>5057</v>
@@ -3530,22 +3531,22 @@
         <v>0</v>
       </c>
       <c r="G50">
-        <v>21841</v>
+        <v>21936</v>
       </c>
       <c r="H50">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="I50">
         <v>0</v>
       </c>
       <c r="J50">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K50">
         <v>0</v>
       </c>
       <c r="L50">
-        <v>4041</v>
+        <v>4136</v>
       </c>
       <c r="M50">
         <v>5</v>
@@ -3554,7 +3555,7 @@
         <v>24</v>
       </c>
       <c r="O50">
-        <v>21132</v>
+        <v>21800</v>
       </c>
       <c r="P50">
         <v>63298</v>
@@ -3589,31 +3590,31 @@
         <v>0</v>
       </c>
       <c r="G51">
-        <v>23323</v>
+        <v>23550</v>
       </c>
       <c r="H51">
-        <v>475</v>
+        <v>248</v>
       </c>
       <c r="I51">
         <v>0</v>
       </c>
       <c r="J51">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K51">
         <v>0</v>
       </c>
       <c r="L51">
-        <v>4647</v>
+        <v>4725</v>
       </c>
       <c r="M51">
         <v>11</v>
       </c>
       <c r="N51">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="O51">
-        <v>21775</v>
+        <v>23364</v>
       </c>
       <c r="P51">
         <v>71754</v>
@@ -3648,7 +3649,7 @@
         <v>0</v>
       </c>
       <c r="G52">
-        <v>21046</v>
+        <v>21061</v>
       </c>
       <c r="H52">
         <v>32</v>
@@ -3657,7 +3658,7 @@
         <v>0</v>
       </c>
       <c r="J52">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="K52">
         <v>1</v>
@@ -3672,7 +3673,7 @@
         <v>43</v>
       </c>
       <c r="O52">
-        <v>20520</v>
+        <v>20728</v>
       </c>
       <c r="P52">
         <v>63986</v>
@@ -3716,22 +3717,22 @@
         <v>0</v>
       </c>
       <c r="J53">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K53">
         <v>1</v>
       </c>
       <c r="L53">
-        <v>3442</v>
+        <v>3458</v>
       </c>
       <c r="M53">
         <v>1</v>
       </c>
       <c r="N53">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="O53">
-        <v>18983</v>
+        <v>18997</v>
       </c>
       <c r="P53">
         <v>56304</v>
@@ -3766,31 +3767,31 @@
         <v>0</v>
       </c>
       <c r="G54">
-        <v>20668</v>
+        <v>20689</v>
       </c>
       <c r="H54">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="I54">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J54">
-        <v>197</v>
+        <v>3</v>
       </c>
       <c r="K54">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L54">
-        <v>2284</v>
+        <v>2411</v>
       </c>
       <c r="M54">
         <v>5</v>
       </c>
       <c r="N54">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="O54">
-        <v>18712</v>
+        <v>19420</v>
       </c>
       <c r="P54">
         <v>58440</v>
@@ -3825,31 +3826,31 @@
         <v>0</v>
       </c>
       <c r="G55">
-        <v>16012</v>
+        <v>16013</v>
       </c>
       <c r="H55">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I55">
         <v>0</v>
       </c>
       <c r="J55">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="K55">
         <v>4</v>
       </c>
       <c r="L55">
-        <v>1960</v>
+        <v>2008</v>
       </c>
       <c r="M55">
         <v>1</v>
       </c>
       <c r="N55">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="O55">
-        <v>15739</v>
+        <v>15787</v>
       </c>
       <c r="P55">
         <v>58215</v>
@@ -3884,16 +3885,16 @@
         <v>0</v>
       </c>
       <c r="G56">
-        <v>19150</v>
+        <v>19152</v>
       </c>
       <c r="H56">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I56">
         <v>0</v>
       </c>
       <c r="J56">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K56">
         <v>0</v>
@@ -3905,10 +3906,10 @@
         <v>2</v>
       </c>
       <c r="N56">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="O56">
-        <v>16285</v>
+        <v>16749</v>
       </c>
       <c r="P56">
         <v>46365</v>
@@ -3943,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="G57">
-        <v>21236</v>
+        <v>21240</v>
       </c>
       <c r="H57">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -3967,7 +3968,7 @@
         <v>39</v>
       </c>
       <c r="O57">
-        <v>21109</v>
+        <v>21113</v>
       </c>
       <c r="P57">
         <v>61556</v>
@@ -4002,31 +4003,31 @@
         <v>0</v>
       </c>
       <c r="G58">
-        <v>22271</v>
+        <v>22815</v>
       </c>
       <c r="H58">
-        <v>142</v>
+        <v>2</v>
       </c>
       <c r="I58">
-        <v>162</v>
+        <v>2</v>
       </c>
       <c r="J58">
-        <v>802</v>
+        <v>899</v>
       </c>
       <c r="K58">
-        <v>277</v>
+        <v>418</v>
       </c>
       <c r="L58">
-        <v>6799</v>
+        <v>7135</v>
       </c>
       <c r="M58">
         <v>4</v>
       </c>
       <c r="N58">
-        <v>462</v>
+        <v>546</v>
       </c>
       <c r="O58">
-        <v>18916</v>
+        <v>19643</v>
       </c>
       <c r="P58">
         <v>57577</v>
@@ -4126,7 +4127,7 @@
         <v>11</v>
       </c>
       <c r="I60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60">
         <v>59</v>
@@ -4238,19 +4239,19 @@
         <v>0</v>
       </c>
       <c r="G62">
-        <v>15798</v>
+        <v>15800</v>
       </c>
       <c r="H62">
         <v>0</v>
       </c>
       <c r="I62">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J62">
-        <v>435</v>
+        <v>490</v>
       </c>
       <c r="K62">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="L62">
         <v>3690</v>
@@ -4262,7 +4263,7 @@
         <v>483</v>
       </c>
       <c r="O62">
-        <v>14777</v>
+        <v>14778</v>
       </c>
       <c r="P62">
         <v>51334</v>
@@ -4306,7 +4307,7 @@
         <v>0</v>
       </c>
       <c r="J63">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K63">
         <v>0</v>
@@ -4327,7 +4328,7 @@
         <v>68691</v>
       </c>
       <c r="Q63">
-        <v>9804</v>
+        <v>9776</v>
       </c>
       <c r="R63">
         <v>0</v>
@@ -4356,31 +4357,31 @@
         <v>0</v>
       </c>
       <c r="G64">
-        <v>41775</v>
+        <v>41898</v>
       </c>
       <c r="H64">
-        <v>260</v>
+        <v>141</v>
       </c>
       <c r="I64">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J64">
-        <v>160</v>
+        <v>17</v>
       </c>
       <c r="K64">
         <v>0</v>
       </c>
       <c r="L64">
-        <v>9530</v>
+        <v>9657</v>
       </c>
       <c r="M64">
         <v>8</v>
       </c>
       <c r="N64">
-        <v>324</v>
+        <v>386</v>
       </c>
       <c r="O64">
-        <v>40979</v>
+        <v>41120</v>
       </c>
       <c r="P64">
         <v>60527</v>
@@ -4415,34 +4416,34 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>38855</v>
+        <v>39069</v>
       </c>
       <c r="H65">
-        <v>1542</v>
+        <v>1492</v>
       </c>
       <c r="I65">
-        <v>956</v>
+        <v>827</v>
       </c>
       <c r="J65">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="K65">
         <v>0</v>
       </c>
       <c r="L65">
-        <v>12396</v>
+        <v>12467</v>
       </c>
       <c r="M65">
         <v>2</v>
       </c>
       <c r="N65">
-        <v>1077</v>
+        <v>1198</v>
       </c>
       <c r="O65">
-        <v>27866</v>
+        <v>29306</v>
       </c>
       <c r="P65">
-        <v>54867</v>
+        <v>58103</v>
       </c>
       <c r="Q65">
         <v>13284</v>
@@ -4474,31 +4475,31 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>62218</v>
+        <v>63143</v>
       </c>
       <c r="H66">
-        <v>4594</v>
+        <v>3938</v>
       </c>
       <c r="I66">
-        <v>550</v>
+        <v>281</v>
       </c>
       <c r="J66">
-        <v>11</v>
+        <v>120</v>
       </c>
       <c r="K66">
         <v>0</v>
       </c>
       <c r="L66">
-        <v>12683</v>
+        <v>12834</v>
       </c>
       <c r="M66">
         <v>2</v>
       </c>
       <c r="N66">
-        <v>2200</v>
+        <v>2487</v>
       </c>
       <c r="O66">
-        <v>56803</v>
+        <v>57391</v>
       </c>
       <c r="P66">
         <v>93810</v>
@@ -4533,31 +4534,31 @@
         <v>0</v>
       </c>
       <c r="G67">
-        <v>65548</v>
+        <v>65914</v>
       </c>
       <c r="H67">
         <v>0</v>
       </c>
       <c r="I67">
-        <v>3275</v>
+        <v>2911</v>
       </c>
       <c r="J67">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="K67">
         <v>0</v>
       </c>
       <c r="L67">
-        <v>18745</v>
+        <v>18836</v>
       </c>
       <c r="M67">
         <v>10</v>
       </c>
       <c r="N67">
-        <v>1530</v>
+        <v>1681</v>
       </c>
       <c r="O67">
-        <v>59709</v>
+        <v>60661</v>
       </c>
       <c r="P67">
         <v>78022</v>
@@ -4592,16 +4593,16 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>61670</v>
+        <v>61897</v>
       </c>
       <c r="H68">
-        <v>2692</v>
+        <v>2489</v>
       </c>
       <c r="I68">
-        <v>914</v>
+        <v>940</v>
       </c>
       <c r="J68">
-        <v>138</v>
+        <v>311</v>
       </c>
       <c r="K68">
         <v>0</v>
@@ -4613,13 +4614,13 @@
         <v>2</v>
       </c>
       <c r="N68">
-        <v>563</v>
+        <v>600</v>
       </c>
       <c r="O68">
-        <v>51297</v>
+        <v>52106</v>
       </c>
       <c r="P68">
-        <v>61648</v>
+        <v>61650</v>
       </c>
       <c r="Q68">
         <v>7850</v>
@@ -4651,34 +4652,34 @@
         <v>0</v>
       </c>
       <c r="G69">
-        <v>39184</v>
+        <v>39584</v>
       </c>
       <c r="H69">
-        <v>4412</v>
+        <v>4049</v>
       </c>
       <c r="I69">
-        <v>270</v>
+        <v>202</v>
       </c>
       <c r="J69">
-        <v>99</v>
+        <v>389</v>
       </c>
       <c r="K69">
         <v>0</v>
       </c>
       <c r="L69">
-        <v>15784</v>
+        <v>15801</v>
       </c>
       <c r="M69">
         <v>2</v>
       </c>
       <c r="N69">
-        <v>393</v>
+        <v>472</v>
       </c>
       <c r="O69">
-        <v>35704</v>
+        <v>35729</v>
       </c>
       <c r="P69">
-        <v>35482</v>
+        <v>36120</v>
       </c>
       <c r="Q69">
         <v>6528</v>
@@ -4710,16 +4711,16 @@
         <v>0</v>
       </c>
       <c r="G70">
-        <v>45770</v>
+        <v>46281</v>
       </c>
       <c r="H70">
-        <v>631</v>
+        <v>480</v>
       </c>
       <c r="I70">
-        <v>1308</v>
+        <v>949</v>
       </c>
       <c r="J70">
-        <v>76</v>
+        <v>202</v>
       </c>
       <c r="K70">
         <v>0</v>
@@ -4731,10 +4732,10 @@
         <v>2</v>
       </c>
       <c r="N70">
-        <v>1710</v>
+        <v>2059</v>
       </c>
       <c r="O70">
-        <v>42585</v>
+        <v>42944</v>
       </c>
       <c r="P70">
         <v>42040</v>
@@ -4769,16 +4770,16 @@
         <v>0</v>
       </c>
       <c r="G71">
-        <v>49908</v>
+        <v>50247</v>
       </c>
       <c r="H71">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="I71">
-        <v>689</v>
+        <v>358</v>
       </c>
       <c r="J71">
-        <v>224</v>
+        <v>266</v>
       </c>
       <c r="K71">
         <v>0</v>
@@ -4790,10 +4791,10 @@
         <v>1</v>
       </c>
       <c r="N71">
-        <v>3657</v>
+        <v>3982</v>
       </c>
       <c r="O71">
-        <v>39351</v>
+        <v>45853</v>
       </c>
       <c r="P71">
         <v>48896</v>
@@ -4828,16 +4829,16 @@
         <v>0</v>
       </c>
       <c r="G72">
-        <v>58603</v>
+        <v>59801</v>
       </c>
       <c r="H72">
-        <v>2086</v>
+        <v>1142</v>
       </c>
       <c r="I72">
-        <v>854</v>
+        <v>600</v>
       </c>
       <c r="J72">
-        <v>70</v>
+        <v>348</v>
       </c>
       <c r="K72">
         <v>0</v>
@@ -4849,10 +4850,10 @@
         <v>9</v>
       </c>
       <c r="N72">
-        <v>2327</v>
+        <v>2791</v>
       </c>
       <c r="O72">
-        <v>47761</v>
+        <v>49852</v>
       </c>
       <c r="P72">
         <v>85505</v>
@@ -4887,16 +4888,16 @@
         <v>0</v>
       </c>
       <c r="G73">
-        <v>52903</v>
+        <v>53894</v>
       </c>
       <c r="H73">
-        <v>5841</v>
+        <v>4867</v>
       </c>
       <c r="I73">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="J73">
-        <v>447</v>
+        <v>1227</v>
       </c>
       <c r="K73">
         <v>0</v>
@@ -4908,10 +4909,10 @@
         <v>6</v>
       </c>
       <c r="N73">
-        <v>1108</v>
+        <v>1181</v>
       </c>
       <c r="O73">
-        <v>47206</v>
+        <v>47466</v>
       </c>
       <c r="P73">
         <v>67550</v>
@@ -4938,49 +4939,49 @@
         <v>0</v>
       </c>
       <c r="E74">
-        <v>2430103</v>
+        <v>2430269</v>
       </c>
       <c r="F74">
-        <v>279</v>
+        <v>113</v>
       </c>
       <c r="G74">
-        <v>2257143</v>
+        <v>2299964</v>
       </c>
       <c r="H74">
-        <v>146706</v>
+        <v>109504</v>
       </c>
       <c r="I74">
-        <v>18029</v>
+        <v>16100</v>
       </c>
       <c r="J74">
-        <v>60534</v>
+        <v>59548</v>
       </c>
       <c r="K74">
-        <v>34811</v>
+        <v>32136</v>
       </c>
       <c r="L74">
-        <v>505577</v>
+        <v>519602</v>
       </c>
       <c r="M74">
-        <v>761</v>
+        <v>971</v>
       </c>
       <c r="N74">
-        <v>47518</v>
+        <v>55798</v>
       </c>
       <c r="O74">
-        <v>2014230</v>
+        <v>2068597</v>
       </c>
       <c r="P74">
-        <v>4580451</v>
+        <v>4615831</v>
       </c>
       <c r="Q74">
-        <v>629394</v>
+        <v>629295</v>
       </c>
       <c r="R74">
         <v>1</v>
       </c>
       <c r="S74">
-        <v>3457</v>
+        <v>3456</v>
       </c>
     </row>
   </sheetData>

--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DD368D4-02C9-4FAA-9037-02905543435E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF3A3779-3F99-4597-95BB-CFC6ABF3B07C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -304,7 +304,7 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Notice &amp; Hearing Report Last Updated On : 31-08-2026 08:00:00</t>
+    <t>Notice &amp; Hearing Report Last Updated On : 01-09-2026 08:00:06</t>
   </si>
 </sst>
 </file>
@@ -817,31 +817,31 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>44795</v>
+        <v>46706</v>
       </c>
       <c r="H4">
-        <v>6556</v>
+        <v>4815</v>
       </c>
       <c r="I4">
         <v>6</v>
       </c>
       <c r="J4">
-        <v>1900</v>
+        <v>3169</v>
       </c>
       <c r="K4">
-        <v>532</v>
+        <v>410</v>
       </c>
       <c r="L4">
-        <v>10556</v>
+        <v>10979</v>
       </c>
       <c r="M4">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N4">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O4">
-        <v>40953</v>
+        <v>41571</v>
       </c>
       <c r="P4">
         <v>53812</v>
@@ -876,34 +876,34 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>49573</v>
+        <v>51266</v>
       </c>
       <c r="H5">
-        <v>3587</v>
+        <v>2282</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="J5">
-        <v>1760</v>
+        <v>2830</v>
       </c>
       <c r="K5">
-        <v>1033</v>
+        <v>1123</v>
       </c>
       <c r="L5">
-        <v>6281</v>
+        <v>6690</v>
       </c>
       <c r="M5">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="N5">
-        <v>457</v>
+        <v>572</v>
       </c>
       <c r="O5">
-        <v>46227</v>
+        <v>46829</v>
       </c>
       <c r="P5">
-        <v>61262</v>
+        <v>65728</v>
       </c>
       <c r="Q5">
         <v>16108</v>
@@ -935,37 +935,37 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>33978</v>
+        <v>35812</v>
       </c>
       <c r="H6">
-        <v>4789</v>
+        <v>3638</v>
       </c>
       <c r="I6">
-        <v>336</v>
+        <v>197</v>
       </c>
       <c r="J6">
-        <v>2444</v>
+        <v>2056</v>
       </c>
       <c r="K6">
-        <v>955</v>
+        <v>986</v>
       </c>
       <c r="L6">
-        <v>2465</v>
+        <v>3113</v>
       </c>
       <c r="M6">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="N6">
-        <v>987</v>
+        <v>1076</v>
       </c>
       <c r="O6">
-        <v>28783</v>
+        <v>30204</v>
       </c>
       <c r="P6">
-        <v>56698</v>
+        <v>60714</v>
       </c>
       <c r="Q6">
-        <v>17918</v>
+        <v>17849</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -994,37 +994,37 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>38339</v>
+        <v>38966</v>
       </c>
       <c r="H7">
-        <v>1123</v>
+        <v>497</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>3120</v>
+        <v>2716</v>
       </c>
       <c r="K7">
-        <v>2930</v>
+        <v>2513</v>
       </c>
       <c r="L7">
-        <v>2525</v>
+        <v>3030</v>
       </c>
       <c r="M7">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="N7">
-        <v>1697</v>
+        <v>1794</v>
       </c>
       <c r="O7">
-        <v>32435</v>
+        <v>33277</v>
       </c>
       <c r="P7">
         <v>77581</v>
       </c>
       <c r="Q7">
-        <v>20905</v>
+        <v>20511</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -1053,37 +1053,37 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>33722</v>
+        <v>36120</v>
       </c>
       <c r="H8">
-        <v>6830</v>
+        <v>4432</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>7018</v>
+        <v>5176</v>
       </c>
       <c r="K8">
-        <v>5781</v>
+        <v>4618</v>
       </c>
       <c r="L8">
-        <v>6392</v>
+        <v>8257</v>
       </c>
       <c r="M8">
-        <v>33</v>
+        <v>120</v>
       </c>
       <c r="N8">
-        <v>482</v>
+        <v>648</v>
       </c>
       <c r="O8">
-        <v>23984</v>
+        <v>26388</v>
       </c>
       <c r="P8">
         <v>73458</v>
       </c>
       <c r="Q8">
-        <v>20902</v>
+        <v>20788</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -1112,37 +1112,37 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>39807</v>
+        <v>41494</v>
       </c>
       <c r="H9">
-        <v>3414</v>
+        <v>1755</v>
       </c>
       <c r="I9">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="J9">
-        <v>3524</v>
+        <v>2044</v>
       </c>
       <c r="K9">
-        <v>2176</v>
+        <v>1626</v>
       </c>
       <c r="L9">
-        <v>3496</v>
+        <v>5546</v>
       </c>
       <c r="M9">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="N9">
-        <v>914</v>
+        <v>1114</v>
       </c>
       <c r="O9">
-        <v>34992</v>
+        <v>36904</v>
       </c>
       <c r="P9">
-        <v>72763</v>
+        <v>72762</v>
       </c>
       <c r="Q9">
-        <v>18178</v>
+        <v>18148</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -1171,31 +1171,31 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>36183</v>
+        <v>36409</v>
       </c>
       <c r="H10">
-        <v>393</v>
+        <v>167</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10">
-        <v>2545</v>
+        <v>1791</v>
       </c>
       <c r="K10">
-        <v>1384</v>
+        <v>1448</v>
       </c>
       <c r="L10">
-        <v>8282</v>
+        <v>9135</v>
       </c>
       <c r="M10">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="N10">
-        <v>625</v>
+        <v>691</v>
       </c>
       <c r="O10">
-        <v>32027</v>
+        <v>32832</v>
       </c>
       <c r="P10">
         <v>53124</v>
@@ -1230,37 +1230,37 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>47950</v>
+        <v>49657</v>
       </c>
       <c r="H11">
-        <v>2633</v>
+        <v>1090</v>
       </c>
       <c r="I11">
-        <v>414</v>
+        <v>244</v>
       </c>
       <c r="J11">
-        <v>4959</v>
+        <v>3754</v>
       </c>
       <c r="K11">
-        <v>2940</v>
+        <v>2322</v>
       </c>
       <c r="L11">
-        <v>4007</v>
+        <v>5844</v>
       </c>
       <c r="M11">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="N11">
-        <v>659</v>
+        <v>887</v>
       </c>
       <c r="O11">
-        <v>37956</v>
+        <v>39185</v>
       </c>
       <c r="P11">
-        <v>84442</v>
+        <v>84439</v>
       </c>
       <c r="Q11">
-        <v>23805</v>
+        <v>23626</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -1289,37 +1289,37 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>38264</v>
+        <v>39560</v>
       </c>
       <c r="H12">
-        <v>2236</v>
+        <v>1049</v>
       </c>
       <c r="I12">
-        <v>177</v>
+        <v>130</v>
       </c>
       <c r="J12">
-        <v>7415</v>
+        <v>6804</v>
       </c>
       <c r="K12">
-        <v>6358</v>
+        <v>5825</v>
       </c>
       <c r="L12">
-        <v>2178</v>
+        <v>2882</v>
       </c>
       <c r="M12">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="N12">
-        <v>701</v>
+        <v>942</v>
       </c>
       <c r="O12">
-        <v>28101</v>
+        <v>29673</v>
       </c>
       <c r="P12">
         <v>66685</v>
       </c>
       <c r="Q12">
-        <v>17907</v>
+        <v>17847</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -1348,43 +1348,43 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>35156</v>
+        <v>37031</v>
       </c>
       <c r="H13">
-        <v>1863</v>
+        <v>0</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>5306</v>
+        <v>5516</v>
       </c>
       <c r="K13">
-        <v>2504</v>
+        <v>2630</v>
       </c>
       <c r="L13">
-        <v>2171</v>
+        <v>2514</v>
       </c>
       <c r="M13">
         <v>14</v>
       </c>
       <c r="N13">
-        <v>3458</v>
+        <v>3818</v>
       </c>
       <c r="O13">
-        <v>24302</v>
+        <v>27497</v>
       </c>
       <c r="P13">
         <v>56565</v>
       </c>
       <c r="Q13">
-        <v>16822</v>
+        <v>16281</v>
       </c>
       <c r="R13">
         <v>0</v>
       </c>
       <c r="S13">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
@@ -1407,37 +1407,37 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>40340</v>
+        <v>43000</v>
       </c>
       <c r="H14">
-        <v>7387</v>
+        <v>5921</v>
       </c>
       <c r="I14">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="J14">
-        <v>7567</v>
+        <v>8111</v>
       </c>
       <c r="K14">
-        <v>4830</v>
+        <v>4763</v>
       </c>
       <c r="L14">
-        <v>5774</v>
+        <v>6459</v>
       </c>
       <c r="M14">
-        <v>111</v>
+        <v>205</v>
       </c>
       <c r="N14">
-        <v>2112</v>
+        <v>2675</v>
       </c>
       <c r="O14">
-        <v>25253</v>
+        <v>26468</v>
       </c>
       <c r="P14">
-        <v>55446</v>
+        <v>62926</v>
       </c>
       <c r="Q14">
-        <v>20044</v>
+        <v>19716</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -1496,7 +1496,7 @@
         <v>67178</v>
       </c>
       <c r="Q15">
-        <v>4869</v>
+        <v>4868</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -1525,37 +1525,37 @@
         <v>0</v>
       </c>
       <c r="G16">
-        <v>25135</v>
+        <v>25545</v>
       </c>
       <c r="H16">
-        <v>335</v>
+        <v>1</v>
       </c>
       <c r="I16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J16">
-        <v>244</v>
+        <v>0</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
       <c r="L16">
-        <v>14270</v>
+        <v>14861</v>
       </c>
       <c r="M16">
         <v>1</v>
       </c>
       <c r="N16">
-        <v>223</v>
+        <v>259</v>
       </c>
       <c r="O16">
-        <v>23038</v>
+        <v>23466</v>
       </c>
       <c r="P16">
-        <v>71052</v>
+        <v>71423</v>
       </c>
       <c r="Q16">
-        <v>5208</v>
+        <v>5198</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="G18">
-        <v>47808</v>
+        <v>47828</v>
       </c>
       <c r="H18">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="I18">
         <v>2</v>
@@ -1658,22 +1658,22 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>7868</v>
+        <v>7870</v>
       </c>
       <c r="M18">
         <v>3</v>
       </c>
       <c r="N18">
-        <v>1942</v>
+        <v>1964</v>
       </c>
       <c r="O18">
-        <v>44464</v>
+        <v>44489</v>
       </c>
       <c r="P18">
         <v>71475</v>
       </c>
       <c r="Q18">
-        <v>6856</v>
+        <v>6836</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -1696,19 +1696,19 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>56466</v>
+        <v>56490</v>
       </c>
       <c r="F19">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G19">
-        <v>56253</v>
+        <v>56490</v>
       </c>
       <c r="H19">
-        <v>207</v>
+        <v>0</v>
       </c>
       <c r="I19">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -1717,28 +1717,28 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>15157</v>
+        <v>15283</v>
       </c>
       <c r="M19">
         <v>1</v>
       </c>
       <c r="N19">
-        <v>872</v>
+        <v>909</v>
       </c>
       <c r="O19">
-        <v>54135</v>
+        <v>54359</v>
       </c>
       <c r="P19">
         <v>106226</v>
       </c>
       <c r="Q19">
-        <v>6139</v>
+        <v>6135</v>
       </c>
       <c r="R19">
         <v>0</v>
       </c>
       <c r="S19">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
@@ -1749,7 +1749,7 @@
         <v>39</v>
       </c>
       <c r="C20">
-        <v>35017</v>
+        <v>35022</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1758,40 +1758,40 @@
         <v>35017</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G20">
-        <v>34750</v>
+        <v>34993</v>
       </c>
       <c r="H20">
-        <v>266</v>
+        <v>24</v>
       </c>
       <c r="I20">
         <v>0</v>
       </c>
       <c r="J20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20">
         <v>0</v>
       </c>
       <c r="L20">
-        <v>6023</v>
+        <v>6075</v>
       </c>
       <c r="M20">
         <v>5</v>
       </c>
       <c r="N20">
-        <v>453</v>
+        <v>546</v>
       </c>
       <c r="O20">
-        <v>34257</v>
+        <v>34419</v>
       </c>
       <c r="P20">
-        <v>75799</v>
+        <v>75812</v>
       </c>
       <c r="Q20">
-        <v>8998</v>
+        <v>8984</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -1888,22 +1888,22 @@
         <v>0</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K22">
         <v>0</v>
       </c>
       <c r="L22">
-        <v>7557</v>
+        <v>7614</v>
       </c>
       <c r="M22">
         <v>0</v>
       </c>
       <c r="N22">
-        <v>234</v>
+        <v>291</v>
       </c>
       <c r="O22">
-        <v>17615</v>
+        <v>18272</v>
       </c>
       <c r="P22">
         <v>64099</v>
@@ -2027,7 +2027,7 @@
         <v>65629</v>
       </c>
       <c r="Q24">
-        <v>3496</v>
+        <v>3492</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -2071,7 +2071,7 @@
         <v>0</v>
       </c>
       <c r="L25">
-        <v>4858</v>
+        <v>4862</v>
       </c>
       <c r="M25">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>298</v>
       </c>
       <c r="O25">
-        <v>18964</v>
+        <v>18968</v>
       </c>
       <c r="P25">
         <v>57533</v>
@@ -2130,7 +2130,7 @@
         <v>0</v>
       </c>
       <c r="L26">
-        <v>3711</v>
+        <v>3720</v>
       </c>
       <c r="M26">
         <v>3</v>
@@ -2139,13 +2139,13 @@
         <v>192</v>
       </c>
       <c r="O26">
-        <v>17332</v>
+        <v>17342</v>
       </c>
       <c r="P26">
         <v>66594</v>
       </c>
       <c r="Q26">
-        <v>3340</v>
+        <v>3333</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -2174,34 +2174,34 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>38967</v>
+        <v>40624</v>
       </c>
       <c r="H27">
-        <v>5309</v>
+        <v>3652</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27">
-        <v>490</v>
+        <v>17</v>
       </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="L27">
-        <v>8220</v>
+        <v>9060</v>
       </c>
       <c r="M27">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="N27">
-        <v>58</v>
+        <v>159</v>
       </c>
       <c r="O27">
-        <v>37396</v>
+        <v>38908</v>
       </c>
       <c r="P27">
-        <v>54979</v>
+        <v>60528</v>
       </c>
       <c r="Q27">
         <v>12669</v>
@@ -2227,40 +2227,40 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>54346</v>
+        <v>54347</v>
       </c>
       <c r="F28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G28">
-        <v>41765</v>
+        <v>46075</v>
       </c>
       <c r="H28">
-        <v>12521</v>
+        <v>8250</v>
       </c>
       <c r="I28">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="J28">
-        <v>1754</v>
+        <v>312</v>
       </c>
       <c r="K28">
         <v>0</v>
       </c>
       <c r="L28">
-        <v>4810</v>
+        <v>6739</v>
       </c>
       <c r="M28">
-        <v>11</v>
+        <v>193</v>
       </c>
       <c r="N28">
-        <v>727</v>
+        <v>975</v>
       </c>
       <c r="O28">
-        <v>36652</v>
+        <v>43372</v>
       </c>
       <c r="P28">
-        <v>80638</v>
+        <v>80623</v>
       </c>
       <c r="Q28">
         <v>14113</v>
@@ -2292,31 +2292,31 @@
         <v>0</v>
       </c>
       <c r="G29">
-        <v>45692</v>
+        <v>47111</v>
       </c>
       <c r="H29">
-        <v>1343</v>
+        <v>0</v>
       </c>
       <c r="I29">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="J29">
-        <v>327</v>
+        <v>15</v>
       </c>
       <c r="K29">
         <v>0</v>
       </c>
       <c r="L29">
-        <v>7295</v>
+        <v>8241</v>
       </c>
       <c r="M29">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="N29">
-        <v>3108</v>
+        <v>4191</v>
       </c>
       <c r="O29">
-        <v>39059</v>
+        <v>39791</v>
       </c>
       <c r="P29">
         <v>83837</v>
@@ -2345,37 +2345,37 @@
         <v>0</v>
       </c>
       <c r="E30">
-        <v>52640</v>
+        <v>52649</v>
       </c>
       <c r="F30">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G30">
-        <v>43161</v>
+        <v>48451</v>
       </c>
       <c r="H30">
-        <v>2471</v>
+        <v>678</v>
       </c>
       <c r="I30">
-        <v>6377</v>
+        <v>3524</v>
       </c>
       <c r="J30">
-        <v>1217</v>
+        <v>1138</v>
       </c>
       <c r="K30">
         <v>0</v>
       </c>
       <c r="L30">
-        <v>5722</v>
+        <v>7457</v>
       </c>
       <c r="M30">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="N30">
-        <v>2650</v>
+        <v>4350</v>
       </c>
       <c r="O30">
-        <v>37209</v>
+        <v>41292</v>
       </c>
       <c r="P30">
         <v>86935</v>
@@ -2410,31 +2410,31 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>90207</v>
+        <v>90875</v>
       </c>
       <c r="H31">
-        <v>761</v>
+        <v>275</v>
       </c>
       <c r="I31">
-        <v>77</v>
+        <v>12</v>
       </c>
       <c r="J31">
-        <v>455</v>
+        <v>178</v>
       </c>
       <c r="K31">
         <v>0</v>
       </c>
       <c r="L31">
-        <v>44100</v>
+        <v>45084</v>
       </c>
       <c r="M31">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N31">
-        <v>1845</v>
+        <v>1879</v>
       </c>
       <c r="O31">
-        <v>85942</v>
+        <v>87036</v>
       </c>
       <c r="P31">
         <v>81642</v>
@@ -2469,31 +2469,31 @@
         <v>10</v>
       </c>
       <c r="G32">
-        <v>37093</v>
+        <v>40126</v>
       </c>
       <c r="H32">
-        <v>9263</v>
+        <v>6320</v>
       </c>
       <c r="I32">
-        <v>372</v>
+        <v>282</v>
       </c>
       <c r="J32">
-        <v>873</v>
+        <v>637</v>
       </c>
       <c r="K32">
         <v>0</v>
       </c>
       <c r="L32">
-        <v>7367</v>
+        <v>8463</v>
       </c>
       <c r="M32">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="N32">
-        <v>1121</v>
+        <v>1545</v>
       </c>
       <c r="O32">
-        <v>32779</v>
+        <v>36773</v>
       </c>
       <c r="P32">
         <v>74817</v>
@@ -2528,34 +2528,34 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <v>34617</v>
+        <v>37139</v>
       </c>
       <c r="H33">
-        <v>4993</v>
+        <v>2779</v>
       </c>
       <c r="I33">
-        <v>465</v>
+        <v>311</v>
       </c>
       <c r="J33">
-        <v>136</v>
+        <v>92</v>
       </c>
       <c r="K33">
         <v>0</v>
       </c>
       <c r="L33">
-        <v>4008</v>
+        <v>4350</v>
       </c>
       <c r="M33">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="N33">
-        <v>49</v>
+        <v>152</v>
       </c>
       <c r="O33">
-        <v>32917</v>
+        <v>35211</v>
       </c>
       <c r="P33">
-        <v>74616</v>
+        <v>76315</v>
       </c>
       <c r="Q33">
         <v>6678</v>
@@ -2587,37 +2587,37 @@
         <v>0</v>
       </c>
       <c r="G34">
-        <v>30845</v>
+        <v>33588</v>
       </c>
       <c r="H34">
-        <v>5697</v>
+        <v>2954</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
       <c r="J34">
-        <v>484</v>
+        <v>443</v>
       </c>
       <c r="K34">
         <v>0</v>
       </c>
       <c r="L34">
-        <v>10008</v>
+        <v>10814</v>
       </c>
       <c r="M34">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="N34">
-        <v>108</v>
+        <v>391</v>
       </c>
       <c r="O34">
-        <v>28277</v>
+        <v>30399</v>
       </c>
       <c r="P34">
-        <v>74626</v>
+        <v>74625</v>
       </c>
       <c r="Q34">
-        <v>7152</v>
+        <v>7149</v>
       </c>
       <c r="R34">
         <v>0</v>
@@ -2646,34 +2646,34 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>29693</v>
+        <v>30872</v>
       </c>
       <c r="H35">
-        <v>3781</v>
+        <v>2692</v>
       </c>
       <c r="I35">
         <v>0</v>
       </c>
       <c r="J35">
-        <v>713</v>
+        <v>20</v>
       </c>
       <c r="K35">
         <v>0</v>
       </c>
       <c r="L35">
-        <v>5476</v>
+        <v>6426</v>
       </c>
       <c r="M35">
         <v>0</v>
       </c>
       <c r="N35">
-        <v>389</v>
+        <v>665</v>
       </c>
       <c r="O35">
-        <v>27179</v>
+        <v>28408</v>
       </c>
       <c r="P35">
-        <v>75609</v>
+        <v>76465</v>
       </c>
       <c r="Q35">
         <v>8879</v>
@@ -2714,7 +2714,7 @@
         <v>0</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="K36">
         <v>0</v>
@@ -2832,28 +2832,28 @@
         <v>0</v>
       </c>
       <c r="J38">
-        <v>203</v>
+        <v>18</v>
       </c>
       <c r="K38">
         <v>0</v>
       </c>
       <c r="L38">
-        <v>5043</v>
+        <v>5352</v>
       </c>
       <c r="M38">
         <v>2</v>
       </c>
       <c r="N38">
-        <v>574</v>
+        <v>620</v>
       </c>
       <c r="O38">
-        <v>28063</v>
+        <v>28420</v>
       </c>
       <c r="P38">
         <v>63038</v>
       </c>
       <c r="Q38">
-        <v>5139</v>
+        <v>5136</v>
       </c>
       <c r="R38">
         <v>0</v>
@@ -2897,7 +2897,7 @@
         <v>0</v>
       </c>
       <c r="L39">
-        <v>4528</v>
+        <v>4529</v>
       </c>
       <c r="M39">
         <v>1</v>
@@ -2906,7 +2906,7 @@
         <v>234</v>
       </c>
       <c r="O39">
-        <v>21132</v>
+        <v>21133</v>
       </c>
       <c r="P39">
         <v>71133</v>
@@ -2941,31 +2941,31 @@
         <v>0</v>
       </c>
       <c r="G40">
-        <v>18804</v>
+        <v>18905</v>
       </c>
       <c r="H40">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I40">
         <v>0</v>
       </c>
       <c r="J40">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="K40">
         <v>0</v>
       </c>
       <c r="L40">
-        <v>1641</v>
+        <v>1765</v>
       </c>
       <c r="M40">
         <v>0</v>
       </c>
       <c r="N40">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="O40">
-        <v>17680</v>
+        <v>18558</v>
       </c>
       <c r="P40">
         <v>73242</v>
@@ -3000,31 +3000,31 @@
         <v>0</v>
       </c>
       <c r="G41">
-        <v>23505</v>
+        <v>23521</v>
       </c>
       <c r="H41">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I41">
         <v>0</v>
       </c>
       <c r="J41">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K41">
         <v>0</v>
       </c>
       <c r="L41">
-        <v>1261</v>
+        <v>1490</v>
       </c>
       <c r="M41">
         <v>0</v>
       </c>
       <c r="N41">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="O41">
-        <v>22136</v>
+        <v>23381</v>
       </c>
       <c r="P41">
         <v>85249</v>
@@ -3133,22 +3133,22 @@
         <v>0</v>
       </c>
       <c r="L43">
-        <v>6792</v>
+        <v>6804</v>
       </c>
       <c r="M43">
         <v>1</v>
       </c>
       <c r="N43">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="O43">
-        <v>28771</v>
+        <v>28789</v>
       </c>
       <c r="P43">
         <v>63043</v>
       </c>
       <c r="Q43">
-        <v>5260</v>
+        <v>5249</v>
       </c>
       <c r="R43">
         <v>0</v>
@@ -3177,31 +3177,31 @@
         <v>0</v>
       </c>
       <c r="G44">
-        <v>21756</v>
+        <v>21900</v>
       </c>
       <c r="H44">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="I44">
         <v>0</v>
       </c>
       <c r="J44">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K44">
         <v>0</v>
       </c>
       <c r="L44">
-        <v>6586</v>
+        <v>6643</v>
       </c>
       <c r="M44">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="N44">
-        <v>294</v>
+        <v>347</v>
       </c>
       <c r="O44">
-        <v>21074</v>
+        <v>21552</v>
       </c>
       <c r="P44">
         <v>68393</v>
@@ -3236,31 +3236,31 @@
         <v>0</v>
       </c>
       <c r="G45">
-        <v>18531</v>
+        <v>19316</v>
       </c>
       <c r="H45">
-        <v>1047</v>
+        <v>614</v>
       </c>
       <c r="I45">
         <v>1</v>
       </c>
       <c r="J45">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="K45">
         <v>0</v>
       </c>
       <c r="L45">
-        <v>2095</v>
+        <v>2166</v>
       </c>
       <c r="M45">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="N45">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="O45">
-        <v>16594</v>
+        <v>18217</v>
       </c>
       <c r="P45">
         <v>76002</v>
@@ -3295,31 +3295,31 @@
         <v>0</v>
       </c>
       <c r="G46">
-        <v>21501</v>
+        <v>21508</v>
       </c>
       <c r="H46">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I46">
         <v>0</v>
       </c>
       <c r="J46">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="K46">
         <v>0</v>
       </c>
       <c r="L46">
-        <v>8195</v>
+        <v>8292</v>
       </c>
       <c r="M46">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="N46">
-        <v>238</v>
+        <v>276</v>
       </c>
       <c r="O46">
-        <v>19334</v>
+        <v>20407</v>
       </c>
       <c r="P46">
         <v>64160</v>
@@ -3354,31 +3354,31 @@
         <v>0</v>
       </c>
       <c r="G47">
-        <v>22265</v>
+        <v>22426</v>
       </c>
       <c r="H47">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="I47">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="J47">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="K47">
         <v>0</v>
       </c>
       <c r="L47">
-        <v>2385</v>
+        <v>2521</v>
       </c>
       <c r="M47">
         <v>1</v>
       </c>
       <c r="N47">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="O47">
-        <v>21119</v>
+        <v>21149</v>
       </c>
       <c r="P47">
         <v>49875</v>
@@ -3407,28 +3407,28 @@
         <v>0</v>
       </c>
       <c r="E48">
-        <v>19597</v>
+        <v>19604</v>
       </c>
       <c r="F48">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="G48">
-        <v>19561</v>
+        <v>19568</v>
       </c>
       <c r="H48">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I48">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48">
         <v>0</v>
       </c>
       <c r="L48">
-        <v>3768</v>
+        <v>3772</v>
       </c>
       <c r="M48">
         <v>4</v>
@@ -3437,7 +3437,7 @@
         <v>245</v>
       </c>
       <c r="O48">
-        <v>19304</v>
+        <v>19306</v>
       </c>
       <c r="P48">
         <v>54142</v>
@@ -3466,40 +3466,40 @@
         <v>0</v>
       </c>
       <c r="E49">
-        <v>21632</v>
+        <v>21642</v>
       </c>
       <c r="F49">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="G49">
-        <v>20257</v>
+        <v>20620</v>
       </c>
       <c r="H49">
-        <v>960</v>
+        <v>692</v>
       </c>
       <c r="I49">
-        <v>268</v>
+        <v>236</v>
       </c>
       <c r="J49">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="K49">
         <v>0</v>
       </c>
       <c r="L49">
-        <v>3476</v>
+        <v>3563</v>
       </c>
       <c r="M49">
         <v>0</v>
       </c>
       <c r="N49">
-        <v>340</v>
+        <v>362</v>
       </c>
       <c r="O49">
-        <v>18539</v>
+        <v>19383</v>
       </c>
       <c r="P49">
-        <v>54938</v>
+        <v>55376</v>
       </c>
       <c r="Q49">
         <v>5057</v>
@@ -3540,22 +3540,22 @@
         <v>0</v>
       </c>
       <c r="J50">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K50">
         <v>0</v>
       </c>
       <c r="L50">
-        <v>4136</v>
+        <v>4160</v>
       </c>
       <c r="M50">
         <v>5</v>
       </c>
       <c r="N50">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="O50">
-        <v>21800</v>
+        <v>21910</v>
       </c>
       <c r="P50">
         <v>63298</v>
@@ -3590,22 +3590,22 @@
         <v>0</v>
       </c>
       <c r="G51">
-        <v>23550</v>
+        <v>23763</v>
       </c>
       <c r="H51">
-        <v>248</v>
+        <v>35</v>
       </c>
       <c r="I51">
         <v>0</v>
       </c>
       <c r="J51">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="K51">
         <v>0</v>
       </c>
       <c r="L51">
-        <v>4725</v>
+        <v>4729</v>
       </c>
       <c r="M51">
         <v>11</v>
@@ -3614,13 +3614,13 @@
         <v>73</v>
       </c>
       <c r="O51">
-        <v>23364</v>
+        <v>23554</v>
       </c>
       <c r="P51">
         <v>71754</v>
       </c>
       <c r="Q51">
-        <v>7716</v>
+        <v>7715</v>
       </c>
       <c r="R51">
         <v>0</v>
@@ -3649,31 +3649,31 @@
         <v>0</v>
       </c>
       <c r="G52">
-        <v>21061</v>
+        <v>21091</v>
       </c>
       <c r="H52">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="I52">
         <v>0</v>
       </c>
       <c r="J52">
-        <v>117</v>
+        <v>11</v>
       </c>
       <c r="K52">
         <v>1</v>
       </c>
       <c r="L52">
-        <v>2729</v>
+        <v>2890</v>
       </c>
       <c r="M52">
         <v>1</v>
       </c>
       <c r="N52">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O52">
-        <v>20728</v>
+        <v>20968</v>
       </c>
       <c r="P52">
         <v>63986</v>
@@ -3717,22 +3717,22 @@
         <v>0</v>
       </c>
       <c r="J53">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K53">
         <v>1</v>
       </c>
       <c r="L53">
-        <v>3458</v>
+        <v>3490</v>
       </c>
       <c r="M53">
         <v>1</v>
       </c>
       <c r="N53">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="O53">
-        <v>18997</v>
+        <v>19032</v>
       </c>
       <c r="P53">
         <v>56304</v>
@@ -3767,16 +3767,16 @@
         <v>0</v>
       </c>
       <c r="G54">
-        <v>20689</v>
+        <v>20754</v>
       </c>
       <c r="H54">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="I54">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J54">
-        <v>3</v>
+        <v>123</v>
       </c>
       <c r="K54">
         <v>1</v>
@@ -3788,10 +3788,10 @@
         <v>5</v>
       </c>
       <c r="N54">
-        <v>346</v>
+        <v>380</v>
       </c>
       <c r="O54">
-        <v>19420</v>
+        <v>20153</v>
       </c>
       <c r="P54">
         <v>58440</v>
@@ -3826,31 +3826,31 @@
         <v>0</v>
       </c>
       <c r="G55">
-        <v>16013</v>
+        <v>16017</v>
       </c>
       <c r="H55">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I55">
         <v>0</v>
       </c>
       <c r="J55">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="K55">
         <v>4</v>
       </c>
       <c r="L55">
-        <v>2008</v>
+        <v>2017</v>
       </c>
       <c r="M55">
         <v>1</v>
       </c>
       <c r="N55">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="O55">
-        <v>15787</v>
+        <v>15799</v>
       </c>
       <c r="P55">
         <v>58215</v>
@@ -3885,16 +3885,16 @@
         <v>0</v>
       </c>
       <c r="G56">
-        <v>19152</v>
+        <v>19234</v>
       </c>
       <c r="H56">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="I56">
         <v>0</v>
       </c>
       <c r="J56">
-        <v>4</v>
+        <v>117</v>
       </c>
       <c r="K56">
         <v>0</v>
@@ -3906,10 +3906,10 @@
         <v>2</v>
       </c>
       <c r="N56">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="O56">
-        <v>16749</v>
+        <v>18257</v>
       </c>
       <c r="P56">
         <v>46365</v>
@@ -3959,7 +3959,7 @@
         <v>0</v>
       </c>
       <c r="L57">
-        <v>1817</v>
+        <v>1854</v>
       </c>
       <c r="M57">
         <v>5</v>
@@ -3968,7 +3968,7 @@
         <v>39</v>
       </c>
       <c r="O57">
-        <v>21113</v>
+        <v>21149</v>
       </c>
       <c r="P57">
         <v>61556</v>
@@ -4003,31 +4003,31 @@
         <v>0</v>
       </c>
       <c r="G58">
-        <v>22815</v>
+        <v>22819</v>
       </c>
       <c r="H58">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I58">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J58">
-        <v>899</v>
+        <v>91</v>
       </c>
       <c r="K58">
-        <v>418</v>
+        <v>56</v>
       </c>
       <c r="L58">
-        <v>7135</v>
+        <v>7987</v>
       </c>
       <c r="M58">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N58">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="O58">
-        <v>19643</v>
+        <v>19947</v>
       </c>
       <c r="P58">
         <v>57577</v>
@@ -4121,31 +4121,31 @@
         <v>0</v>
       </c>
       <c r="G60">
-        <v>23699</v>
+        <v>23749</v>
       </c>
       <c r="H60">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J60">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="K60">
         <v>0</v>
       </c>
       <c r="L60">
-        <v>5563</v>
+        <v>5615</v>
       </c>
       <c r="M60">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N60">
-        <v>289</v>
+        <v>323</v>
       </c>
       <c r="O60">
-        <v>21760</v>
+        <v>21761</v>
       </c>
       <c r="P60">
         <v>70140</v>
@@ -4189,7 +4189,7 @@
         <v>0</v>
       </c>
       <c r="J61">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K61">
         <v>0</v>
@@ -4204,7 +4204,7 @@
         <v>1</v>
       </c>
       <c r="O61">
-        <v>13964</v>
+        <v>15495</v>
       </c>
       <c r="P61">
         <v>55240</v>
@@ -4248,13 +4248,13 @@
         <v>0</v>
       </c>
       <c r="J62">
-        <v>490</v>
+        <v>316</v>
       </c>
       <c r="K62">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="L62">
-        <v>3690</v>
+        <v>3876</v>
       </c>
       <c r="M62">
         <v>15</v>
@@ -4263,7 +4263,7 @@
         <v>483</v>
       </c>
       <c r="O62">
-        <v>14778</v>
+        <v>14964</v>
       </c>
       <c r="P62">
         <v>51334</v>
@@ -4307,22 +4307,22 @@
         <v>0</v>
       </c>
       <c r="J63">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K63">
         <v>0</v>
       </c>
       <c r="L63">
-        <v>10868</v>
+        <v>10946</v>
       </c>
       <c r="M63">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="N63">
-        <v>903</v>
+        <v>914</v>
       </c>
       <c r="O63">
-        <v>32187</v>
+        <v>33136</v>
       </c>
       <c r="P63">
         <v>68691</v>
@@ -4357,19 +4357,19 @@
         <v>0</v>
       </c>
       <c r="G64">
-        <v>41898</v>
+        <v>41956</v>
       </c>
       <c r="H64">
-        <v>141</v>
+        <v>83</v>
       </c>
       <c r="I64">
         <v>9</v>
       </c>
       <c r="J64">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="K64">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L64">
         <v>9657</v>
@@ -4378,10 +4378,10 @@
         <v>8</v>
       </c>
       <c r="N64">
-        <v>386</v>
+        <v>418</v>
       </c>
       <c r="O64">
-        <v>41120</v>
+        <v>41194</v>
       </c>
       <c r="P64">
         <v>60527</v>
@@ -4416,31 +4416,31 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>39069</v>
+        <v>39878</v>
       </c>
       <c r="H65">
-        <v>1492</v>
+        <v>1127</v>
       </c>
       <c r="I65">
-        <v>827</v>
+        <v>384</v>
       </c>
       <c r="J65">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="K65">
         <v>0</v>
       </c>
       <c r="L65">
-        <v>12467</v>
+        <v>12688</v>
       </c>
       <c r="M65">
         <v>2</v>
       </c>
       <c r="N65">
-        <v>1198</v>
+        <v>1692</v>
       </c>
       <c r="O65">
-        <v>29306</v>
+        <v>30962</v>
       </c>
       <c r="P65">
         <v>58103</v>
@@ -4475,31 +4475,31 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>63143</v>
+        <v>64863</v>
       </c>
       <c r="H66">
-        <v>3938</v>
+        <v>2498</v>
       </c>
       <c r="I66">
-        <v>281</v>
+        <v>0</v>
       </c>
       <c r="J66">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="K66">
         <v>0</v>
       </c>
       <c r="L66">
-        <v>12834</v>
+        <v>13278</v>
       </c>
       <c r="M66">
         <v>2</v>
       </c>
       <c r="N66">
-        <v>2487</v>
+        <v>3037</v>
       </c>
       <c r="O66">
-        <v>57391</v>
+        <v>58804</v>
       </c>
       <c r="P66">
         <v>93810</v>
@@ -4534,31 +4534,31 @@
         <v>0</v>
       </c>
       <c r="G67">
-        <v>65914</v>
+        <v>68341</v>
       </c>
       <c r="H67">
         <v>0</v>
       </c>
       <c r="I67">
-        <v>2911</v>
+        <v>487</v>
       </c>
       <c r="J67">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="K67">
         <v>0</v>
       </c>
       <c r="L67">
-        <v>18836</v>
+        <v>19243</v>
       </c>
       <c r="M67">
         <v>10</v>
       </c>
       <c r="N67">
-        <v>1681</v>
+        <v>3171</v>
       </c>
       <c r="O67">
-        <v>60661</v>
+        <v>64834</v>
       </c>
       <c r="P67">
         <v>78022</v>
@@ -4593,34 +4593,34 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>61897</v>
+        <v>62429</v>
       </c>
       <c r="H68">
-        <v>2489</v>
+        <v>2157</v>
       </c>
       <c r="I68">
-        <v>940</v>
+        <v>804</v>
       </c>
       <c r="J68">
-        <v>311</v>
+        <v>25</v>
       </c>
       <c r="K68">
         <v>0</v>
       </c>
       <c r="L68">
-        <v>16123</v>
+        <v>16635</v>
       </c>
       <c r="M68">
         <v>2</v>
       </c>
       <c r="N68">
-        <v>600</v>
+        <v>766</v>
       </c>
       <c r="O68">
-        <v>52106</v>
+        <v>52449</v>
       </c>
       <c r="P68">
-        <v>61650</v>
+        <v>64211</v>
       </c>
       <c r="Q68">
         <v>7850</v>
@@ -4652,34 +4652,34 @@
         <v>0</v>
       </c>
       <c r="G69">
-        <v>39584</v>
+        <v>41414</v>
       </c>
       <c r="H69">
-        <v>4049</v>
+        <v>2429</v>
       </c>
       <c r="I69">
-        <v>202</v>
+        <v>95</v>
       </c>
       <c r="J69">
-        <v>389</v>
+        <v>370</v>
       </c>
       <c r="K69">
         <v>0</v>
       </c>
       <c r="L69">
-        <v>15801</v>
+        <v>16600</v>
       </c>
       <c r="M69">
         <v>2</v>
       </c>
       <c r="N69">
-        <v>472</v>
+        <v>1454</v>
       </c>
       <c r="O69">
-        <v>35729</v>
+        <v>36470</v>
       </c>
       <c r="P69">
-        <v>36120</v>
+        <v>36117</v>
       </c>
       <c r="Q69">
         <v>6528</v>
@@ -4711,31 +4711,31 @@
         <v>0</v>
       </c>
       <c r="G70">
-        <v>46281</v>
+        <v>47443</v>
       </c>
       <c r="H70">
-        <v>480</v>
+        <v>156</v>
       </c>
       <c r="I70">
-        <v>949</v>
+        <v>112</v>
       </c>
       <c r="J70">
-        <v>202</v>
+        <v>47</v>
       </c>
       <c r="K70">
         <v>0</v>
       </c>
       <c r="L70">
-        <v>17912</v>
+        <v>18189</v>
       </c>
       <c r="M70">
         <v>2</v>
       </c>
       <c r="N70">
-        <v>2059</v>
+        <v>3020</v>
       </c>
       <c r="O70">
-        <v>42944</v>
+        <v>44136</v>
       </c>
       <c r="P70">
         <v>42040</v>
@@ -4770,31 +4770,31 @@
         <v>0</v>
       </c>
       <c r="G71">
-        <v>50247</v>
+        <v>50645</v>
       </c>
       <c r="H71">
-        <v>358</v>
+        <v>136</v>
       </c>
       <c r="I71">
-        <v>358</v>
+        <v>182</v>
       </c>
       <c r="J71">
-        <v>266</v>
+        <v>74</v>
       </c>
       <c r="K71">
         <v>0</v>
       </c>
       <c r="L71">
-        <v>22257</v>
+        <v>22652</v>
       </c>
       <c r="M71">
         <v>1</v>
       </c>
       <c r="N71">
-        <v>3982</v>
+        <v>4154</v>
       </c>
       <c r="O71">
-        <v>45853</v>
+        <v>46054</v>
       </c>
       <c r="P71">
         <v>48896</v>
@@ -4829,31 +4829,31 @@
         <v>0</v>
       </c>
       <c r="G72">
-        <v>59801</v>
+        <v>61063</v>
       </c>
       <c r="H72">
-        <v>1142</v>
+        <v>338</v>
       </c>
       <c r="I72">
-        <v>600</v>
+        <v>142</v>
       </c>
       <c r="J72">
-        <v>348</v>
+        <v>50</v>
       </c>
       <c r="K72">
         <v>0</v>
       </c>
       <c r="L72">
-        <v>16490</v>
+        <v>16945</v>
       </c>
       <c r="M72">
         <v>9</v>
       </c>
       <c r="N72">
-        <v>2791</v>
+        <v>3432</v>
       </c>
       <c r="O72">
-        <v>49852</v>
+        <v>51144</v>
       </c>
       <c r="P72">
         <v>85505</v>
@@ -4888,37 +4888,37 @@
         <v>0</v>
       </c>
       <c r="G73">
-        <v>53894</v>
+        <v>55532</v>
       </c>
       <c r="H73">
-        <v>4867</v>
+        <v>3268</v>
       </c>
       <c r="I73">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="J73">
-        <v>1227</v>
+        <v>389</v>
       </c>
       <c r="K73">
         <v>0</v>
       </c>
       <c r="L73">
-        <v>12188</v>
+        <v>13436</v>
       </c>
       <c r="M73">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N73">
-        <v>1181</v>
+        <v>1795</v>
       </c>
       <c r="O73">
-        <v>47466</v>
+        <v>48465</v>
       </c>
       <c r="P73">
         <v>67550</v>
       </c>
       <c r="Q73">
-        <v>10016</v>
+        <v>10011</v>
       </c>
       <c r="R73">
         <v>0</v>
@@ -4933,55 +4933,55 @@
       </c>
       <c r="B74" s="1"/>
       <c r="C74">
-        <v>2430382</v>
+        <v>2430387</v>
       </c>
       <c r="D74">
         <v>0</v>
       </c>
       <c r="E74">
-        <v>2430269</v>
+        <v>2430320</v>
       </c>
       <c r="F74">
-        <v>113</v>
+        <v>67</v>
       </c>
       <c r="G74">
-        <v>2299964</v>
+        <v>2355477</v>
       </c>
       <c r="H74">
-        <v>109504</v>
+        <v>66920</v>
       </c>
       <c r="I74">
-        <v>16100</v>
+        <v>7425</v>
       </c>
       <c r="J74">
-        <v>59548</v>
+        <v>48940</v>
       </c>
       <c r="K74">
-        <v>32136</v>
+        <v>28630</v>
       </c>
       <c r="L74">
-        <v>519602</v>
+        <v>547713</v>
       </c>
       <c r="M74">
-        <v>971</v>
+        <v>1596</v>
       </c>
       <c r="N74">
-        <v>55798</v>
+        <v>68859</v>
       </c>
       <c r="O74">
-        <v>2068597</v>
+        <v>2134170</v>
       </c>
       <c r="P74">
-        <v>4615831</v>
+        <v>4643257</v>
       </c>
       <c r="Q74">
-        <v>629295</v>
+        <v>627497</v>
       </c>
       <c r="R74">
         <v>1</v>
       </c>
       <c r="S74">
-        <v>3456</v>
+        <v>3452</v>
       </c>
     </row>
   </sheetData>

--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF3A3779-3F99-4597-95BB-CFC6ABF3B07C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D46BBB2-8252-4D89-B33B-CDE4DA83B0C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -304,7 +304,7 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Notice &amp; Hearing Report Last Updated On : 01-09-2026 08:00:06</t>
+    <t>Notice &amp; Hearing Report Last Updated On : 01-09-2026 16:00:08</t>
   </si>
 </sst>
 </file>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>46706</v>
+        <v>47732</v>
       </c>
       <c r="H4">
-        <v>4815</v>
+        <v>3789</v>
       </c>
       <c r="I4">
         <v>6</v>
       </c>
       <c r="J4">
-        <v>3169</v>
+        <v>4228</v>
       </c>
       <c r="K4">
         <v>410</v>
@@ -838,10 +838,10 @@
         <v>48</v>
       </c>
       <c r="N4">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="O4">
-        <v>41571</v>
+        <v>41686</v>
       </c>
       <c r="P4">
         <v>53812</v>
@@ -876,34 +876,34 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>51266</v>
+        <v>52079</v>
       </c>
       <c r="H5">
-        <v>2282</v>
+        <v>1554</v>
       </c>
       <c r="I5">
         <v>64</v>
       </c>
       <c r="J5">
-        <v>2830</v>
+        <v>3652</v>
       </c>
       <c r="K5">
         <v>1123</v>
       </c>
       <c r="L5">
-        <v>6690</v>
+        <v>6699</v>
       </c>
       <c r="M5">
         <v>108</v>
       </c>
       <c r="N5">
-        <v>572</v>
+        <v>581</v>
       </c>
       <c r="O5">
-        <v>46829</v>
+        <v>46984</v>
       </c>
       <c r="P5">
-        <v>65728</v>
+        <v>69907</v>
       </c>
       <c r="Q5">
         <v>16108</v>
@@ -935,16 +935,16 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>35812</v>
+        <v>36807</v>
       </c>
       <c r="H6">
-        <v>3638</v>
+        <v>2751</v>
       </c>
       <c r="I6">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="J6">
-        <v>2056</v>
+        <v>2575</v>
       </c>
       <c r="K6">
         <v>986</v>
@@ -956,13 +956,13 @@
         <v>44</v>
       </c>
       <c r="N6">
-        <v>1076</v>
+        <v>1105</v>
       </c>
       <c r="O6">
-        <v>30204</v>
+        <v>30651</v>
       </c>
       <c r="P6">
-        <v>60714</v>
+        <v>65857</v>
       </c>
       <c r="Q6">
         <v>17849</v>
@@ -994,31 +994,31 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>38966</v>
+        <v>39166</v>
       </c>
       <c r="H7">
-        <v>497</v>
+        <v>297</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7">
-        <v>2716</v>
+        <v>2535</v>
       </c>
       <c r="K7">
-        <v>2513</v>
+        <v>2339</v>
       </c>
       <c r="L7">
-        <v>3030</v>
+        <v>3211</v>
       </c>
       <c r="M7">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="N7">
-        <v>1794</v>
+        <v>1804</v>
       </c>
       <c r="O7">
-        <v>33277</v>
+        <v>33510</v>
       </c>
       <c r="P7">
         <v>77581</v>
@@ -1053,31 +1053,31 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>36120</v>
+        <v>38281</v>
       </c>
       <c r="H8">
-        <v>4432</v>
+        <v>2271</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>5176</v>
+        <v>469</v>
       </c>
       <c r="K8">
-        <v>4618</v>
+        <v>405</v>
       </c>
       <c r="L8">
-        <v>8257</v>
+        <v>13466</v>
       </c>
       <c r="M8">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="N8">
-        <v>648</v>
+        <v>1192</v>
       </c>
       <c r="O8">
-        <v>26388</v>
+        <v>27628</v>
       </c>
       <c r="P8">
         <v>73458</v>
@@ -1112,31 +1112,31 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>41494</v>
+        <v>42297</v>
       </c>
       <c r="H9">
-        <v>1755</v>
+        <v>974</v>
       </c>
       <c r="I9">
+        <v>2</v>
+      </c>
+      <c r="J9">
+        <v>1641</v>
+      </c>
+      <c r="K9">
+        <v>1217</v>
+      </c>
+      <c r="L9">
+        <v>5660</v>
+      </c>
+      <c r="M9">
         <v>24</v>
       </c>
-      <c r="J9">
-        <v>2044</v>
-      </c>
-      <c r="K9">
-        <v>1626</v>
-      </c>
-      <c r="L9">
-        <v>5546</v>
-      </c>
-      <c r="M9">
-        <v>22</v>
-      </c>
       <c r="N9">
-        <v>1114</v>
+        <v>1225</v>
       </c>
       <c r="O9">
-        <v>36904</v>
+        <v>38273</v>
       </c>
       <c r="P9">
         <v>72762</v>
@@ -1171,31 +1171,31 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>36409</v>
+        <v>36463</v>
       </c>
       <c r="H10">
-        <v>167</v>
+        <v>113</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10">
-        <v>1791</v>
+        <v>1835</v>
       </c>
       <c r="K10">
-        <v>1448</v>
+        <v>1442</v>
       </c>
       <c r="L10">
-        <v>9135</v>
+        <v>9141</v>
       </c>
       <c r="M10">
         <v>63</v>
       </c>
       <c r="N10">
-        <v>691</v>
+        <v>709</v>
       </c>
       <c r="O10">
-        <v>32832</v>
+        <v>33835</v>
       </c>
       <c r="P10">
         <v>53124</v>
@@ -1230,34 +1230,34 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>49657</v>
+        <v>50610</v>
       </c>
       <c r="H11">
-        <v>1090</v>
+        <v>346</v>
       </c>
       <c r="I11">
-        <v>244</v>
+        <v>35</v>
       </c>
       <c r="J11">
-        <v>3754</v>
+        <v>1174</v>
       </c>
       <c r="K11">
-        <v>2322</v>
+        <v>629</v>
       </c>
       <c r="L11">
-        <v>5844</v>
+        <v>8514</v>
       </c>
       <c r="M11">
-        <v>158</v>
+        <v>212</v>
       </c>
       <c r="N11">
-        <v>887</v>
+        <v>1286</v>
       </c>
       <c r="O11">
-        <v>39185</v>
+        <v>42251</v>
       </c>
       <c r="P11">
-        <v>84439</v>
+        <v>84438</v>
       </c>
       <c r="Q11">
         <v>23626</v>
@@ -1289,31 +1289,31 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>39560</v>
+        <v>40082</v>
       </c>
       <c r="H12">
-        <v>1049</v>
+        <v>596</v>
       </c>
       <c r="I12">
-        <v>130</v>
+        <v>61</v>
       </c>
       <c r="J12">
-        <v>6804</v>
+        <v>5362</v>
       </c>
       <c r="K12">
-        <v>5825</v>
+        <v>4679</v>
       </c>
       <c r="L12">
-        <v>2882</v>
+        <v>4409</v>
       </c>
       <c r="M12">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="N12">
-        <v>942</v>
+        <v>1008</v>
       </c>
       <c r="O12">
-        <v>29673</v>
+        <v>31657</v>
       </c>
       <c r="P12">
         <v>66685</v>
@@ -1357,22 +1357,22 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>5516</v>
+        <v>4785</v>
       </c>
       <c r="K13">
-        <v>2630</v>
+        <v>2374</v>
       </c>
       <c r="L13">
-        <v>2514</v>
+        <v>3224</v>
       </c>
       <c r="M13">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="N13">
         <v>3818</v>
       </c>
       <c r="O13">
-        <v>27497</v>
+        <v>28352</v>
       </c>
       <c r="P13">
         <v>56565</v>
@@ -1407,16 +1407,16 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>43000</v>
+        <v>43668</v>
       </c>
       <c r="H14">
-        <v>5921</v>
+        <v>5262</v>
       </c>
       <c r="I14">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J14">
-        <v>8111</v>
+        <v>8392</v>
       </c>
       <c r="K14">
         <v>4763</v>
@@ -1428,13 +1428,13 @@
         <v>205</v>
       </c>
       <c r="N14">
-        <v>2675</v>
+        <v>3000</v>
       </c>
       <c r="O14">
-        <v>26468</v>
+        <v>26862</v>
       </c>
       <c r="P14">
-        <v>62926</v>
+        <v>67825</v>
       </c>
       <c r="Q14">
         <v>19716</v>
@@ -1525,13 +1525,13 @@
         <v>0</v>
       </c>
       <c r="G16">
-        <v>25545</v>
+        <v>25547</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -1546,13 +1546,13 @@
         <v>1</v>
       </c>
       <c r="N16">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O16">
-        <v>23466</v>
+        <v>24629</v>
       </c>
       <c r="P16">
-        <v>71423</v>
+        <v>71426</v>
       </c>
       <c r="Q16">
         <v>5198</v>
@@ -1643,31 +1643,31 @@
         <v>0</v>
       </c>
       <c r="G18">
-        <v>47828</v>
+        <v>47836</v>
       </c>
       <c r="H18">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18">
         <v>0</v>
       </c>
       <c r="L18">
-        <v>7870</v>
+        <v>7874</v>
       </c>
       <c r="M18">
         <v>3</v>
       </c>
       <c r="N18">
-        <v>1964</v>
+        <v>1969</v>
       </c>
       <c r="O18">
-        <v>44489</v>
+        <v>44491</v>
       </c>
       <c r="P18">
         <v>71475</v>
@@ -1726,10 +1726,10 @@
         <v>909</v>
       </c>
       <c r="O19">
-        <v>54359</v>
+        <v>54989</v>
       </c>
       <c r="P19">
-        <v>106226</v>
+        <v>106227</v>
       </c>
       <c r="Q19">
         <v>6135</v>
@@ -1761,10 +1761,10 @@
         <v>5</v>
       </c>
       <c r="G20">
-        <v>34993</v>
+        <v>35011</v>
       </c>
       <c r="H20">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -1776,7 +1776,7 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>6075</v>
+        <v>6088</v>
       </c>
       <c r="M20">
         <v>5</v>
@@ -1785,7 +1785,7 @@
         <v>546</v>
       </c>
       <c r="O20">
-        <v>34419</v>
+        <v>34424</v>
       </c>
       <c r="P20">
         <v>75812</v>
@@ -1888,22 +1888,22 @@
         <v>0</v>
       </c>
       <c r="J22">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K22">
         <v>0</v>
       </c>
       <c r="L22">
-        <v>7614</v>
+        <v>7630</v>
       </c>
       <c r="M22">
         <v>0</v>
       </c>
       <c r="N22">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O22">
-        <v>18272</v>
+        <v>18331</v>
       </c>
       <c r="P22">
         <v>64099</v>
@@ -2130,16 +2130,16 @@
         <v>0</v>
       </c>
       <c r="L26">
-        <v>3720</v>
+        <v>3741</v>
       </c>
       <c r="M26">
         <v>3</v>
       </c>
       <c r="N26">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="O26">
-        <v>17342</v>
+        <v>17363</v>
       </c>
       <c r="P26">
         <v>66594</v>
@@ -2174,34 +2174,34 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>40624</v>
+        <v>41177</v>
       </c>
       <c r="H27">
-        <v>3652</v>
+        <v>3099</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="L27">
-        <v>9060</v>
+        <v>9128</v>
       </c>
       <c r="M27">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N27">
-        <v>159</v>
+        <v>379</v>
       </c>
       <c r="O27">
-        <v>38908</v>
+        <v>39318</v>
       </c>
       <c r="P27">
-        <v>60528</v>
+        <v>60896</v>
       </c>
       <c r="Q27">
         <v>12669</v>
@@ -2227,37 +2227,37 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>54347</v>
+        <v>54349</v>
       </c>
       <c r="F28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G28">
-        <v>46075</v>
+        <v>49235</v>
       </c>
       <c r="H28">
-        <v>8250</v>
+        <v>5095</v>
       </c>
       <c r="I28">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J28">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="K28">
         <v>0</v>
       </c>
       <c r="L28">
-        <v>6739</v>
+        <v>7303</v>
       </c>
       <c r="M28">
-        <v>193</v>
+        <v>253</v>
       </c>
       <c r="N28">
-        <v>975</v>
+        <v>1251</v>
       </c>
       <c r="O28">
-        <v>43372</v>
+        <v>45907</v>
       </c>
       <c r="P28">
         <v>80623</v>
@@ -2301,22 +2301,22 @@
         <v>0</v>
       </c>
       <c r="J29">
-        <v>15</v>
+        <v>213</v>
       </c>
       <c r="K29">
         <v>0</v>
       </c>
       <c r="L29">
-        <v>8241</v>
+        <v>8386</v>
       </c>
       <c r="M29">
         <v>37</v>
       </c>
       <c r="N29">
-        <v>4191</v>
+        <v>4220</v>
       </c>
       <c r="O29">
-        <v>39791</v>
+        <v>42064</v>
       </c>
       <c r="P29">
         <v>83837</v>
@@ -2351,31 +2351,31 @@
         <v>4</v>
       </c>
       <c r="G30">
-        <v>48451</v>
+        <v>49099</v>
       </c>
       <c r="H30">
-        <v>678</v>
+        <v>561</v>
       </c>
       <c r="I30">
-        <v>3524</v>
+        <v>2993</v>
       </c>
       <c r="J30">
-        <v>1138</v>
+        <v>396</v>
       </c>
       <c r="K30">
         <v>0</v>
       </c>
       <c r="L30">
-        <v>7457</v>
+        <v>8327</v>
       </c>
       <c r="M30">
-        <v>37</v>
+        <v>243</v>
       </c>
       <c r="N30">
-        <v>4350</v>
+        <v>4557</v>
       </c>
       <c r="O30">
-        <v>41292</v>
+        <v>41836</v>
       </c>
       <c r="P30">
         <v>86935</v>
@@ -2410,31 +2410,31 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>90875</v>
+        <v>91147</v>
       </c>
       <c r="H31">
-        <v>275</v>
+        <v>15</v>
       </c>
       <c r="I31">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J31">
-        <v>178</v>
+        <v>404</v>
       </c>
       <c r="K31">
         <v>0</v>
       </c>
       <c r="L31">
-        <v>45084</v>
+        <v>45277</v>
       </c>
       <c r="M31">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N31">
-        <v>1879</v>
+        <v>1891</v>
       </c>
       <c r="O31">
-        <v>87036</v>
+        <v>87438</v>
       </c>
       <c r="P31">
         <v>81642</v>
@@ -2469,31 +2469,31 @@
         <v>10</v>
       </c>
       <c r="G32">
-        <v>40126</v>
+        <v>41517</v>
       </c>
       <c r="H32">
-        <v>6320</v>
+        <v>4957</v>
       </c>
       <c r="I32">
-        <v>282</v>
+        <v>254</v>
       </c>
       <c r="J32">
-        <v>637</v>
+        <v>588</v>
       </c>
       <c r="K32">
         <v>0</v>
       </c>
       <c r="L32">
-        <v>8463</v>
+        <v>9051</v>
       </c>
       <c r="M32">
-        <v>36</v>
+        <v>149</v>
       </c>
       <c r="N32">
-        <v>1545</v>
+        <v>1943</v>
       </c>
       <c r="O32">
-        <v>36773</v>
+        <v>37402</v>
       </c>
       <c r="P32">
         <v>74817</v>
@@ -2528,31 +2528,31 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <v>37139</v>
+        <v>38162</v>
       </c>
       <c r="H33">
-        <v>2779</v>
+        <v>2022</v>
       </c>
       <c r="I33">
-        <v>311</v>
+        <v>45</v>
       </c>
       <c r="J33">
-        <v>92</v>
+        <v>341</v>
       </c>
       <c r="K33">
         <v>0</v>
       </c>
       <c r="L33">
-        <v>4350</v>
+        <v>4463</v>
       </c>
       <c r="M33">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="N33">
-        <v>152</v>
+        <v>408</v>
       </c>
       <c r="O33">
-        <v>35211</v>
+        <v>35838</v>
       </c>
       <c r="P33">
         <v>76315</v>
@@ -2587,31 +2587,31 @@
         <v>0</v>
       </c>
       <c r="G34">
-        <v>33588</v>
+        <v>34420</v>
       </c>
       <c r="H34">
-        <v>2954</v>
+        <v>2122</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
       <c r="J34">
-        <v>443</v>
+        <v>265</v>
       </c>
       <c r="K34">
         <v>0</v>
       </c>
       <c r="L34">
-        <v>10814</v>
+        <v>11101</v>
       </c>
       <c r="M34">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="N34">
-        <v>391</v>
+        <v>581</v>
       </c>
       <c r="O34">
-        <v>30399</v>
+        <v>31794</v>
       </c>
       <c r="P34">
         <v>74625</v>
@@ -2646,31 +2646,31 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>30872</v>
+        <v>31609</v>
       </c>
       <c r="H35">
-        <v>2692</v>
+        <v>1955</v>
       </c>
       <c r="I35">
         <v>0</v>
       </c>
       <c r="J35">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K35">
         <v>0</v>
       </c>
       <c r="L35">
-        <v>6426</v>
+        <v>6461</v>
       </c>
       <c r="M35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35">
-        <v>665</v>
+        <v>922</v>
       </c>
       <c r="O35">
-        <v>28408</v>
+        <v>29564</v>
       </c>
       <c r="P35">
         <v>76465</v>
@@ -2714,22 +2714,22 @@
         <v>0</v>
       </c>
       <c r="J36">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="K36">
         <v>0</v>
       </c>
       <c r="L36">
-        <v>7314</v>
+        <v>7350</v>
       </c>
       <c r="M36">
         <v>0</v>
       </c>
       <c r="N36">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="O36">
-        <v>19918</v>
+        <v>19954</v>
       </c>
       <c r="P36">
         <v>60419</v>
@@ -2832,22 +2832,22 @@
         <v>0</v>
       </c>
       <c r="J38">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="K38">
         <v>0</v>
       </c>
       <c r="L38">
-        <v>5352</v>
+        <v>5370</v>
       </c>
       <c r="M38">
         <v>2</v>
       </c>
       <c r="N38">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="O38">
-        <v>28420</v>
+        <v>28441</v>
       </c>
       <c r="P38">
         <v>63038</v>
@@ -2950,22 +2950,22 @@
         <v>0</v>
       </c>
       <c r="J40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K40">
         <v>0</v>
       </c>
       <c r="L40">
-        <v>1765</v>
+        <v>1810</v>
       </c>
       <c r="M40">
         <v>0</v>
       </c>
       <c r="N40">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O40">
-        <v>18558</v>
+        <v>18850</v>
       </c>
       <c r="P40">
         <v>73242</v>
@@ -3015,7 +3015,7 @@
         <v>0</v>
       </c>
       <c r="L41">
-        <v>1490</v>
+        <v>1499</v>
       </c>
       <c r="M41">
         <v>0</v>
@@ -3024,10 +3024,10 @@
         <v>92</v>
       </c>
       <c r="O41">
-        <v>23381</v>
+        <v>23429</v>
       </c>
       <c r="P41">
-        <v>85249</v>
+        <v>85251</v>
       </c>
       <c r="Q41">
         <v>6018</v>
@@ -3201,7 +3201,7 @@
         <v>347</v>
       </c>
       <c r="O44">
-        <v>21552</v>
+        <v>21553</v>
       </c>
       <c r="P44">
         <v>68393</v>
@@ -3236,31 +3236,31 @@
         <v>0</v>
       </c>
       <c r="G45">
-        <v>19316</v>
+        <v>19622</v>
       </c>
       <c r="H45">
-        <v>614</v>
+        <v>309</v>
       </c>
       <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
         <v>1</v>
       </c>
-      <c r="J45">
-        <v>17</v>
-      </c>
       <c r="K45">
         <v>0</v>
       </c>
       <c r="L45">
-        <v>2166</v>
+        <v>2217</v>
       </c>
       <c r="M45">
         <v>13</v>
       </c>
       <c r="N45">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="O45">
-        <v>18217</v>
+        <v>18880</v>
       </c>
       <c r="P45">
         <v>76002</v>
@@ -3295,10 +3295,10 @@
         <v>0</v>
       </c>
       <c r="G46">
-        <v>21508</v>
+        <v>21512</v>
       </c>
       <c r="H46">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -3310,7 +3310,7 @@
         <v>0</v>
       </c>
       <c r="L46">
-        <v>8292</v>
+        <v>8297</v>
       </c>
       <c r="M46">
         <v>32</v>
@@ -3319,7 +3319,7 @@
         <v>276</v>
       </c>
       <c r="O46">
-        <v>20407</v>
+        <v>20906</v>
       </c>
       <c r="P46">
         <v>64160</v>
@@ -3363,13 +3363,13 @@
         <v>0</v>
       </c>
       <c r="J47">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="K47">
         <v>0</v>
       </c>
       <c r="L47">
-        <v>2521</v>
+        <v>2592</v>
       </c>
       <c r="M47">
         <v>1</v>
@@ -3378,7 +3378,7 @@
         <v>137</v>
       </c>
       <c r="O47">
-        <v>21149</v>
+        <v>21232</v>
       </c>
       <c r="P47">
         <v>49875</v>
@@ -3413,22 +3413,22 @@
         <v>37</v>
       </c>
       <c r="G48">
-        <v>19568</v>
+        <v>19589</v>
       </c>
       <c r="H48">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="I48">
         <v>1</v>
       </c>
       <c r="J48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K48">
         <v>0</v>
       </c>
       <c r="L48">
-        <v>3772</v>
+        <v>3773</v>
       </c>
       <c r="M48">
         <v>4</v>
@@ -3437,7 +3437,7 @@
         <v>245</v>
       </c>
       <c r="O48">
-        <v>19306</v>
+        <v>19330</v>
       </c>
       <c r="P48">
         <v>54142</v>
@@ -3466,28 +3466,28 @@
         <v>0</v>
       </c>
       <c r="E49">
-        <v>21642</v>
+        <v>21643</v>
       </c>
       <c r="F49">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G49">
-        <v>20620</v>
+        <v>20792</v>
       </c>
       <c r="H49">
-        <v>692</v>
+        <v>627</v>
       </c>
       <c r="I49">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="J49">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="K49">
         <v>0</v>
       </c>
       <c r="L49">
-        <v>3563</v>
+        <v>3591</v>
       </c>
       <c r="M49">
         <v>0</v>
@@ -3496,7 +3496,7 @@
         <v>362</v>
       </c>
       <c r="O49">
-        <v>19383</v>
+        <v>19543</v>
       </c>
       <c r="P49">
         <v>55376</v>
@@ -3590,22 +3590,22 @@
         <v>0</v>
       </c>
       <c r="G51">
-        <v>23763</v>
+        <v>23798</v>
       </c>
       <c r="H51">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="I51">
         <v>0</v>
       </c>
       <c r="J51">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="K51">
         <v>0</v>
       </c>
       <c r="L51">
-        <v>4729</v>
+        <v>4827</v>
       </c>
       <c r="M51">
         <v>11</v>
@@ -3614,7 +3614,7 @@
         <v>73</v>
       </c>
       <c r="O51">
-        <v>23554</v>
+        <v>23591</v>
       </c>
       <c r="P51">
         <v>71754</v>
@@ -3649,10 +3649,10 @@
         <v>0</v>
       </c>
       <c r="G52">
-        <v>21091</v>
+        <v>21094</v>
       </c>
       <c r="H52">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -3664,7 +3664,7 @@
         <v>1</v>
       </c>
       <c r="L52">
-        <v>2890</v>
+        <v>2912</v>
       </c>
       <c r="M52">
         <v>1</v>
@@ -3673,7 +3673,7 @@
         <v>44</v>
       </c>
       <c r="O52">
-        <v>20968</v>
+        <v>21003</v>
       </c>
       <c r="P52">
         <v>63986</v>
@@ -3717,19 +3717,19 @@
         <v>0</v>
       </c>
       <c r="J53">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="K53">
         <v>1</v>
       </c>
       <c r="L53">
-        <v>3490</v>
+        <v>3498</v>
       </c>
       <c r="M53">
         <v>1</v>
       </c>
       <c r="N53">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="O53">
         <v>19032</v>
@@ -3767,22 +3767,22 @@
         <v>0</v>
       </c>
       <c r="G54">
-        <v>20754</v>
+        <v>20755</v>
       </c>
       <c r="H54">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I54">
         <v>0</v>
       </c>
       <c r="J54">
-        <v>123</v>
+        <v>36</v>
       </c>
       <c r="K54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L54">
-        <v>2411</v>
+        <v>2477</v>
       </c>
       <c r="M54">
         <v>5</v>
@@ -3791,7 +3791,7 @@
         <v>380</v>
       </c>
       <c r="O54">
-        <v>20153</v>
+        <v>20163</v>
       </c>
       <c r="P54">
         <v>58440</v>
@@ -3835,22 +3835,22 @@
         <v>0</v>
       </c>
       <c r="J55">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="K55">
         <v>4</v>
       </c>
       <c r="L55">
-        <v>2017</v>
+        <v>2056</v>
       </c>
       <c r="M55">
         <v>1</v>
       </c>
       <c r="N55">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="O55">
-        <v>15799</v>
+        <v>15839</v>
       </c>
       <c r="P55">
         <v>58215</v>
@@ -3885,31 +3885,31 @@
         <v>0</v>
       </c>
       <c r="G56">
-        <v>19234</v>
+        <v>19246</v>
       </c>
       <c r="H56">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="I56">
         <v>0</v>
       </c>
       <c r="J56">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="K56">
         <v>0</v>
       </c>
       <c r="L56">
-        <v>3692</v>
+        <v>3700</v>
       </c>
       <c r="M56">
         <v>2</v>
       </c>
       <c r="N56">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O56">
-        <v>18257</v>
+        <v>18263</v>
       </c>
       <c r="P56">
         <v>46365</v>
@@ -3953,7 +3953,7 @@
         <v>0</v>
       </c>
       <c r="J57">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="K57">
         <v>0</v>
@@ -4012,7 +4012,7 @@
         <v>0</v>
       </c>
       <c r="J58">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="K58">
         <v>56</v>
@@ -4024,10 +4024,10 @@
         <v>8</v>
       </c>
       <c r="N58">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="O58">
-        <v>19947</v>
+        <v>20420</v>
       </c>
       <c r="P58">
         <v>57577</v>
@@ -4071,7 +4071,7 @@
         <v>0</v>
       </c>
       <c r="J59">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K59">
         <v>0</v>
@@ -4086,7 +4086,7 @@
         <v>283</v>
       </c>
       <c r="O59">
-        <v>15993</v>
+        <v>17087</v>
       </c>
       <c r="P59">
         <v>60495</v>
@@ -4130,22 +4130,22 @@
         <v>0</v>
       </c>
       <c r="J60">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K60">
         <v>0</v>
       </c>
       <c r="L60">
-        <v>5615</v>
+        <v>5649</v>
       </c>
       <c r="M60">
         <v>9</v>
       </c>
       <c r="N60">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O60">
-        <v>21761</v>
+        <v>21762</v>
       </c>
       <c r="P60">
         <v>70140</v>
@@ -4204,7 +4204,7 @@
         <v>1</v>
       </c>
       <c r="O61">
-        <v>15495</v>
+        <v>16668</v>
       </c>
       <c r="P61">
         <v>55240</v>
@@ -4248,22 +4248,22 @@
         <v>0</v>
       </c>
       <c r="J62">
-        <v>316</v>
+        <v>17</v>
       </c>
       <c r="K62">
-        <v>296</v>
+        <v>0</v>
       </c>
       <c r="L62">
-        <v>3876</v>
+        <v>4117</v>
       </c>
       <c r="M62">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="N62">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="O62">
-        <v>14964</v>
+        <v>15209</v>
       </c>
       <c r="P62">
         <v>51334</v>
@@ -4307,22 +4307,22 @@
         <v>0</v>
       </c>
       <c r="J63">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K63">
         <v>0</v>
       </c>
       <c r="L63">
-        <v>10946</v>
+        <v>10969</v>
       </c>
       <c r="M63">
         <v>68</v>
       </c>
       <c r="N63">
-        <v>914</v>
+        <v>921</v>
       </c>
       <c r="O63">
-        <v>33136</v>
+        <v>35808</v>
       </c>
       <c r="P63">
         <v>68691</v>
@@ -4357,31 +4357,31 @@
         <v>0</v>
       </c>
       <c r="G64">
-        <v>41956</v>
+        <v>42034</v>
       </c>
       <c r="H64">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="I64">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J64">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="K64">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L64">
-        <v>9657</v>
+        <v>9673</v>
       </c>
       <c r="M64">
         <v>8</v>
       </c>
       <c r="N64">
-        <v>418</v>
+        <v>465</v>
       </c>
       <c r="O64">
-        <v>41194</v>
+        <v>41242</v>
       </c>
       <c r="P64">
         <v>60527</v>
@@ -4416,31 +4416,31 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>39878</v>
+        <v>40118</v>
       </c>
       <c r="H65">
-        <v>1127</v>
+        <v>922</v>
       </c>
       <c r="I65">
-        <v>384</v>
+        <v>349</v>
       </c>
       <c r="J65">
-        <v>99</v>
+        <v>45</v>
       </c>
       <c r="K65">
         <v>0</v>
       </c>
       <c r="L65">
-        <v>12688</v>
+        <v>12781</v>
       </c>
       <c r="M65">
         <v>2</v>
       </c>
       <c r="N65">
-        <v>1692</v>
+        <v>1817</v>
       </c>
       <c r="O65">
-        <v>30962</v>
+        <v>31743</v>
       </c>
       <c r="P65">
         <v>58103</v>
@@ -4475,31 +4475,31 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>64863</v>
+        <v>65445</v>
       </c>
       <c r="H66">
-        <v>2498</v>
+        <v>1916</v>
       </c>
       <c r="I66">
         <v>0</v>
       </c>
       <c r="J66">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="K66">
         <v>0</v>
       </c>
       <c r="L66">
-        <v>13278</v>
+        <v>13375</v>
       </c>
       <c r="M66">
         <v>2</v>
       </c>
       <c r="N66">
-        <v>3037</v>
+        <v>3196</v>
       </c>
       <c r="O66">
-        <v>58804</v>
+        <v>59679</v>
       </c>
       <c r="P66">
         <v>93810</v>
@@ -4534,31 +4534,31 @@
         <v>0</v>
       </c>
       <c r="G67">
-        <v>68341</v>
+        <v>68597</v>
       </c>
       <c r="H67">
         <v>0</v>
       </c>
       <c r="I67">
-        <v>487</v>
+        <v>231</v>
       </c>
       <c r="J67">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="K67">
         <v>0</v>
       </c>
       <c r="L67">
-        <v>19243</v>
+        <v>19329</v>
       </c>
       <c r="M67">
         <v>10</v>
       </c>
       <c r="N67">
-        <v>3171</v>
+        <v>3427</v>
       </c>
       <c r="O67">
-        <v>64834</v>
+        <v>64857</v>
       </c>
       <c r="P67">
         <v>78022</v>
@@ -4593,34 +4593,34 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>62429</v>
+        <v>62718</v>
       </c>
       <c r="H68">
-        <v>2157</v>
+        <v>1878</v>
       </c>
       <c r="I68">
-        <v>804</v>
+        <v>733</v>
       </c>
       <c r="J68">
-        <v>25</v>
+        <v>145</v>
       </c>
       <c r="K68">
         <v>0</v>
       </c>
       <c r="L68">
-        <v>16635</v>
+        <v>16722</v>
       </c>
       <c r="M68">
         <v>2</v>
       </c>
       <c r="N68">
-        <v>766</v>
+        <v>786</v>
       </c>
       <c r="O68">
-        <v>52449</v>
+        <v>53183</v>
       </c>
       <c r="P68">
-        <v>64211</v>
+        <v>67572</v>
       </c>
       <c r="Q68">
         <v>7850</v>
@@ -4652,31 +4652,31 @@
         <v>0</v>
       </c>
       <c r="G69">
-        <v>41414</v>
+        <v>41837</v>
       </c>
       <c r="H69">
-        <v>2429</v>
+        <v>2071</v>
       </c>
       <c r="I69">
-        <v>95</v>
+        <v>30</v>
       </c>
       <c r="J69">
-        <v>370</v>
+        <v>53</v>
       </c>
       <c r="K69">
         <v>0</v>
       </c>
       <c r="L69">
-        <v>16600</v>
+        <v>17003</v>
       </c>
       <c r="M69">
         <v>2</v>
       </c>
       <c r="N69">
-        <v>1454</v>
+        <v>1693</v>
       </c>
       <c r="O69">
-        <v>36470</v>
+        <v>37141</v>
       </c>
       <c r="P69">
         <v>36117</v>
@@ -4711,31 +4711,31 @@
         <v>0</v>
       </c>
       <c r="G70">
-        <v>47443</v>
+        <v>47642</v>
       </c>
       <c r="H70">
-        <v>156</v>
+        <v>61</v>
       </c>
       <c r="I70">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="J70">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="K70">
         <v>0</v>
       </c>
       <c r="L70">
-        <v>18189</v>
+        <v>18241</v>
       </c>
       <c r="M70">
         <v>2</v>
       </c>
       <c r="N70">
-        <v>3020</v>
+        <v>3181</v>
       </c>
       <c r="O70">
-        <v>44136</v>
+        <v>44285</v>
       </c>
       <c r="P70">
         <v>42040</v>
@@ -4770,31 +4770,31 @@
         <v>0</v>
       </c>
       <c r="G71">
-        <v>50645</v>
+        <v>50669</v>
       </c>
       <c r="H71">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="I71">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="J71">
-        <v>74</v>
+        <v>2</v>
       </c>
       <c r="K71">
         <v>0</v>
       </c>
       <c r="L71">
-        <v>22652</v>
+        <v>22723</v>
       </c>
       <c r="M71">
         <v>1</v>
       </c>
       <c r="N71">
-        <v>4154</v>
+        <v>4171</v>
       </c>
       <c r="O71">
-        <v>46054</v>
+        <v>46143</v>
       </c>
       <c r="P71">
         <v>48896</v>
@@ -4829,31 +4829,31 @@
         <v>0</v>
       </c>
       <c r="G72">
-        <v>61063</v>
+        <v>61334</v>
       </c>
       <c r="H72">
-        <v>338</v>
+        <v>142</v>
       </c>
       <c r="I72">
-        <v>142</v>
+        <v>67</v>
       </c>
       <c r="J72">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="K72">
         <v>0</v>
       </c>
       <c r="L72">
-        <v>16945</v>
+        <v>17016</v>
       </c>
       <c r="M72">
         <v>9</v>
       </c>
       <c r="N72">
-        <v>3432</v>
+        <v>3561</v>
       </c>
       <c r="O72">
-        <v>51144</v>
+        <v>51336</v>
       </c>
       <c r="P72">
         <v>85505</v>
@@ -4888,31 +4888,31 @@
         <v>0</v>
       </c>
       <c r="G73">
-        <v>55532</v>
+        <v>56040</v>
       </c>
       <c r="H73">
-        <v>3268</v>
+        <v>2764</v>
       </c>
       <c r="I73">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="J73">
-        <v>389</v>
+        <v>7</v>
       </c>
       <c r="K73">
         <v>0</v>
       </c>
       <c r="L73">
-        <v>13436</v>
+        <v>13936</v>
       </c>
       <c r="M73">
         <v>7</v>
       </c>
       <c r="N73">
-        <v>1795</v>
+        <v>1875</v>
       </c>
       <c r="O73">
-        <v>48465</v>
+        <v>48936</v>
       </c>
       <c r="P73">
         <v>67550</v>
@@ -4939,40 +4939,40 @@
         <v>0</v>
       </c>
       <c r="E74">
-        <v>2430320</v>
+        <v>2430323</v>
       </c>
       <c r="F74">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G74">
-        <v>2355477</v>
+        <v>2375740</v>
       </c>
       <c r="H74">
-        <v>66920</v>
+        <v>48675</v>
       </c>
       <c r="I74">
-        <v>7425</v>
+        <v>5631</v>
       </c>
       <c r="J74">
-        <v>48940</v>
+        <v>40165</v>
       </c>
       <c r="K74">
-        <v>28630</v>
+        <v>20429</v>
       </c>
       <c r="L74">
-        <v>547713</v>
+        <v>563335</v>
       </c>
       <c r="M74">
-        <v>1596</v>
+        <v>2252</v>
       </c>
       <c r="N74">
-        <v>68859</v>
+        <v>73503</v>
       </c>
       <c r="O74">
-        <v>2134170</v>
+        <v>2168528</v>
       </c>
       <c r="P74">
-        <v>4643257</v>
+        <v>4661212</v>
       </c>
       <c r="Q74">
         <v>627497</v>

--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\New folder (13)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D46BBB2-8252-4D89-B33B-CDE4DA83B0C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49F51FAF-BDAF-435D-ACC3-D9DE92521456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -304,7 +304,7 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Notice &amp; Hearing Report Last Updated On : 01-09-2026 16:00:08</t>
+    <t>Notice &amp; Hearing Report Last Updated On : 02-09-2026 08:00:00</t>
   </si>
 </sst>
 </file>
@@ -817,19 +817,19 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>47732</v>
+        <v>48194</v>
       </c>
       <c r="H4">
-        <v>3789</v>
+        <v>3330</v>
       </c>
       <c r="I4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J4">
-        <v>4228</v>
+        <v>4709</v>
       </c>
       <c r="K4">
-        <v>410</v>
+        <v>517</v>
       </c>
       <c r="L4">
         <v>10979</v>
@@ -841,7 +841,7 @@
         <v>201</v>
       </c>
       <c r="O4">
-        <v>41686</v>
+        <v>41773</v>
       </c>
       <c r="P4">
         <v>53812</v>
@@ -876,34 +876,34 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>52079</v>
+        <v>52459</v>
       </c>
       <c r="H5">
-        <v>1554</v>
+        <v>1265</v>
       </c>
       <c r="I5">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="J5">
-        <v>3652</v>
+        <v>3041</v>
       </c>
       <c r="K5">
-        <v>1123</v>
+        <v>1116</v>
       </c>
       <c r="L5">
-        <v>6699</v>
+        <v>7684</v>
       </c>
       <c r="M5">
         <v>108</v>
       </c>
       <c r="N5">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="O5">
-        <v>46984</v>
+        <v>48210</v>
       </c>
       <c r="P5">
-        <v>69907</v>
+        <v>74320</v>
       </c>
       <c r="Q5">
         <v>16108</v>
@@ -935,19 +935,19 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>36807</v>
+        <v>37335</v>
       </c>
       <c r="H6">
-        <v>2751</v>
+        <v>2246</v>
       </c>
       <c r="I6">
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="J6">
-        <v>2575</v>
+        <v>2681</v>
       </c>
       <c r="K6">
-        <v>986</v>
+        <v>1223</v>
       </c>
       <c r="L6">
         <v>3113</v>
@@ -956,16 +956,16 @@
         <v>44</v>
       </c>
       <c r="N6">
-        <v>1105</v>
+        <v>1162</v>
       </c>
       <c r="O6">
-        <v>30651</v>
+        <v>31018</v>
       </c>
       <c r="P6">
-        <v>65857</v>
+        <v>70908</v>
       </c>
       <c r="Q6">
-        <v>17849</v>
+        <v>17830</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>39166</v>
+        <v>39199</v>
       </c>
       <c r="H7">
-        <v>297</v>
+        <v>264</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7">
-        <v>2535</v>
+        <v>2498</v>
       </c>
       <c r="K7">
-        <v>2339</v>
+        <v>2347</v>
       </c>
       <c r="L7">
-        <v>3211</v>
+        <v>3243</v>
       </c>
       <c r="M7">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="N7">
         <v>1804</v>
       </c>
       <c r="O7">
-        <v>33510</v>
+        <v>33630</v>
       </c>
       <c r="P7">
         <v>77581</v>
@@ -1053,31 +1053,31 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>38281</v>
+        <v>38632</v>
       </c>
       <c r="H8">
-        <v>2271</v>
+        <v>1920</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>469</v>
+        <v>85</v>
       </c>
       <c r="K8">
-        <v>405</v>
+        <v>0</v>
       </c>
       <c r="L8">
-        <v>13466</v>
+        <v>13904</v>
       </c>
       <c r="M8">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="N8">
         <v>1192</v>
       </c>
       <c r="O8">
-        <v>27628</v>
+        <v>28507</v>
       </c>
       <c r="P8">
         <v>73458</v>
@@ -1112,37 +1112,37 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>42297</v>
+        <v>42954</v>
       </c>
       <c r="H9">
-        <v>974</v>
+        <v>317</v>
       </c>
       <c r="I9">
         <v>2</v>
       </c>
       <c r="J9">
-        <v>1641</v>
+        <v>1521</v>
       </c>
       <c r="K9">
-        <v>1217</v>
+        <v>1118</v>
       </c>
       <c r="L9">
-        <v>5660</v>
+        <v>5764</v>
       </c>
       <c r="M9">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="N9">
-        <v>1225</v>
+        <v>1236</v>
       </c>
       <c r="O9">
-        <v>38273</v>
+        <v>38918</v>
       </c>
       <c r="P9">
         <v>72762</v>
       </c>
       <c r="Q9">
-        <v>18148</v>
+        <v>18141</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -1171,19 +1171,19 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>36463</v>
+        <v>36549</v>
       </c>
       <c r="H10">
-        <v>113</v>
+        <v>27</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10">
-        <v>1835</v>
+        <v>1892</v>
       </c>
       <c r="K10">
-        <v>1442</v>
+        <v>1450</v>
       </c>
       <c r="L10">
         <v>9141</v>
@@ -1192,16 +1192,16 @@
         <v>63</v>
       </c>
       <c r="N10">
-        <v>709</v>
+        <v>746</v>
       </c>
       <c r="O10">
-        <v>33835</v>
+        <v>33860</v>
       </c>
       <c r="P10">
         <v>53124</v>
       </c>
       <c r="Q10">
-        <v>9502</v>
+        <v>9498</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -1230,31 +1230,31 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>50610</v>
+        <v>50998</v>
       </c>
       <c r="H11">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="J11">
-        <v>1174</v>
+        <v>1222</v>
       </c>
       <c r="K11">
-        <v>629</v>
+        <v>597</v>
       </c>
       <c r="L11">
-        <v>8514</v>
+        <v>8691</v>
       </c>
       <c r="M11">
         <v>212</v>
       </c>
       <c r="N11">
-        <v>1286</v>
+        <v>1487</v>
       </c>
       <c r="O11">
-        <v>42251</v>
+        <v>45815</v>
       </c>
       <c r="P11">
         <v>84438</v>
@@ -1289,37 +1289,37 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>40082</v>
+        <v>40310</v>
       </c>
       <c r="H12">
-        <v>596</v>
+        <v>392</v>
       </c>
       <c r="I12">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="J12">
-        <v>5362</v>
+        <v>2943</v>
       </c>
       <c r="K12">
-        <v>4679</v>
+        <v>2627</v>
       </c>
       <c r="L12">
-        <v>4409</v>
+        <v>6842</v>
       </c>
       <c r="M12">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="N12">
-        <v>1008</v>
+        <v>1020</v>
       </c>
       <c r="O12">
-        <v>31657</v>
+        <v>32682</v>
       </c>
       <c r="P12">
         <v>66685</v>
       </c>
       <c r="Q12">
-        <v>17847</v>
+        <v>17787</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -1357,22 +1357,22 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>4785</v>
+        <v>2125</v>
       </c>
       <c r="K13">
-        <v>2374</v>
+        <v>1441</v>
       </c>
       <c r="L13">
-        <v>3224</v>
+        <v>5641</v>
       </c>
       <c r="M13">
-        <v>95</v>
+        <v>244</v>
       </c>
       <c r="N13">
         <v>3818</v>
       </c>
       <c r="O13">
-        <v>28352</v>
+        <v>30234</v>
       </c>
       <c r="P13">
         <v>56565</v>
@@ -1407,34 +1407,34 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>43668</v>
+        <v>45398</v>
       </c>
       <c r="H14">
-        <v>5262</v>
+        <v>3539</v>
       </c>
       <c r="I14">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="J14">
-        <v>8392</v>
+        <v>8464</v>
       </c>
       <c r="K14">
-        <v>4763</v>
+        <v>4812</v>
       </c>
       <c r="L14">
-        <v>6459</v>
+        <v>6665</v>
       </c>
       <c r="M14">
-        <v>205</v>
+        <v>314</v>
       </c>
       <c r="N14">
-        <v>3000</v>
+        <v>3467</v>
       </c>
       <c r="O14">
-        <v>26862</v>
+        <v>27909</v>
       </c>
       <c r="P14">
-        <v>67825</v>
+        <v>70636</v>
       </c>
       <c r="Q14">
         <v>19716</v>
@@ -1496,7 +1496,7 @@
         <v>67178</v>
       </c>
       <c r="Q15">
-        <v>4868</v>
+        <v>4867</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -1549,13 +1549,13 @@
         <v>261</v>
       </c>
       <c r="O16">
-        <v>24629</v>
+        <v>24857</v>
       </c>
       <c r="P16">
-        <v>71426</v>
+        <v>71642</v>
       </c>
       <c r="Q16">
-        <v>5198</v>
+        <v>5197</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -1652,13 +1652,13 @@
         <v>0</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18">
         <v>0</v>
       </c>
       <c r="L18">
-        <v>7874</v>
+        <v>7875</v>
       </c>
       <c r="M18">
         <v>3</v>
@@ -1667,13 +1667,13 @@
         <v>1969</v>
       </c>
       <c r="O18">
-        <v>44491</v>
+        <v>44492</v>
       </c>
       <c r="P18">
         <v>71475</v>
       </c>
       <c r="Q18">
-        <v>6836</v>
+        <v>6819</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -1723,10 +1723,10 @@
         <v>1</v>
       </c>
       <c r="N19">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="O19">
-        <v>54989</v>
+        <v>55194</v>
       </c>
       <c r="P19">
         <v>106227</v>
@@ -1761,10 +1761,10 @@
         <v>5</v>
       </c>
       <c r="G20">
-        <v>35011</v>
+        <v>35022</v>
       </c>
       <c r="H20">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -1776,7 +1776,7 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>6088</v>
+        <v>6093</v>
       </c>
       <c r="M20">
         <v>5</v>
@@ -1785,7 +1785,7 @@
         <v>546</v>
       </c>
       <c r="O20">
-        <v>34424</v>
+        <v>34464</v>
       </c>
       <c r="P20">
         <v>75812</v>
@@ -1888,7 +1888,7 @@
         <v>0</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>64099</v>
       </c>
       <c r="Q22">
-        <v>4866</v>
+        <v>4849</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -2174,34 +2174,34 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>41177</v>
+        <v>41478</v>
       </c>
       <c r="H27">
-        <v>3099</v>
+        <v>2798</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="L27">
-        <v>9128</v>
+        <v>9189</v>
       </c>
       <c r="M27">
         <v>26</v>
       </c>
       <c r="N27">
-        <v>379</v>
+        <v>583</v>
       </c>
       <c r="O27">
-        <v>39318</v>
+        <v>39395</v>
       </c>
       <c r="P27">
-        <v>60896</v>
+        <v>62365</v>
       </c>
       <c r="Q27">
         <v>12669</v>
@@ -2233,43 +2233,43 @@
         <v>0</v>
       </c>
       <c r="G28">
-        <v>49235</v>
+        <v>51523</v>
       </c>
       <c r="H28">
-        <v>5095</v>
+        <v>2826</v>
       </c>
       <c r="I28">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J28">
-        <v>310</v>
+        <v>633</v>
       </c>
       <c r="K28">
         <v>0</v>
       </c>
       <c r="L28">
-        <v>7303</v>
+        <v>7421</v>
       </c>
       <c r="M28">
         <v>253</v>
       </c>
       <c r="N28">
-        <v>1251</v>
+        <v>1736</v>
       </c>
       <c r="O28">
-        <v>45907</v>
+        <v>47489</v>
       </c>
       <c r="P28">
         <v>80623</v>
       </c>
       <c r="Q28">
-        <v>14113</v>
+        <v>13995</v>
       </c>
       <c r="R28">
         <v>0</v>
       </c>
       <c r="S28">
-        <v>134</v>
+        <v>127</v>
       </c>
     </row>
     <row r="29" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
@@ -2301,28 +2301,28 @@
         <v>0</v>
       </c>
       <c r="J29">
-        <v>213</v>
+        <v>427</v>
       </c>
       <c r="K29">
         <v>0</v>
       </c>
       <c r="L29">
-        <v>8386</v>
+        <v>8456</v>
       </c>
       <c r="M29">
         <v>37</v>
       </c>
       <c r="N29">
-        <v>4220</v>
+        <v>4227</v>
       </c>
       <c r="O29">
-        <v>42064</v>
+        <v>42138</v>
       </c>
       <c r="P29">
         <v>83837</v>
       </c>
       <c r="Q29">
-        <v>14644</v>
+        <v>14229</v>
       </c>
       <c r="R29">
         <v>0</v>
@@ -2345,40 +2345,40 @@
         <v>0</v>
       </c>
       <c r="E30">
-        <v>52649</v>
+        <v>52650</v>
       </c>
       <c r="F30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G30">
-        <v>49099</v>
+        <v>50324</v>
       </c>
       <c r="H30">
-        <v>561</v>
+        <v>392</v>
       </c>
       <c r="I30">
-        <v>2993</v>
+        <v>1937</v>
       </c>
       <c r="J30">
-        <v>396</v>
+        <v>1382</v>
       </c>
       <c r="K30">
         <v>0</v>
       </c>
       <c r="L30">
-        <v>8327</v>
+        <v>8487</v>
       </c>
       <c r="M30">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N30">
-        <v>4557</v>
+        <v>4962</v>
       </c>
       <c r="O30">
-        <v>41836</v>
+        <v>43432</v>
       </c>
       <c r="P30">
-        <v>86935</v>
+        <v>86933</v>
       </c>
       <c r="Q30">
         <v>12564</v>
@@ -2410,37 +2410,37 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>91147</v>
+        <v>91162</v>
       </c>
       <c r="H31">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I31">
         <v>0</v>
       </c>
       <c r="J31">
-        <v>404</v>
+        <v>1315</v>
       </c>
       <c r="K31">
         <v>0</v>
       </c>
       <c r="L31">
-        <v>45277</v>
+        <v>45364</v>
       </c>
       <c r="M31">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="N31">
         <v>1891</v>
       </c>
       <c r="O31">
-        <v>87438</v>
+        <v>87492</v>
       </c>
       <c r="P31">
         <v>81642</v>
       </c>
       <c r="Q31">
-        <v>14710</v>
+        <v>14581</v>
       </c>
       <c r="R31">
         <v>0</v>
@@ -2463,40 +2463,40 @@
         <v>0</v>
       </c>
       <c r="E32">
-        <v>46718</v>
+        <v>46724</v>
       </c>
       <c r="F32">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G32">
-        <v>41517</v>
+        <v>42600</v>
       </c>
       <c r="H32">
-        <v>4957</v>
+        <v>3886</v>
       </c>
       <c r="I32">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="J32">
-        <v>588</v>
+        <v>822</v>
       </c>
       <c r="K32">
         <v>0</v>
       </c>
       <c r="L32">
-        <v>9051</v>
+        <v>9153</v>
       </c>
       <c r="M32">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="N32">
-        <v>1943</v>
+        <v>2462</v>
       </c>
       <c r="O32">
-        <v>37402</v>
+        <v>38658</v>
       </c>
       <c r="P32">
-        <v>74817</v>
+        <v>74814</v>
       </c>
       <c r="Q32">
         <v>11379</v>
@@ -2528,31 +2528,31 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <v>38162</v>
+        <v>38371</v>
       </c>
       <c r="H33">
-        <v>2022</v>
+        <v>1824</v>
       </c>
       <c r="I33">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="J33">
-        <v>341</v>
+        <v>273</v>
       </c>
       <c r="K33">
         <v>0</v>
       </c>
       <c r="L33">
-        <v>4463</v>
+        <v>4549</v>
       </c>
       <c r="M33">
         <v>50</v>
       </c>
       <c r="N33">
-        <v>408</v>
+        <v>435</v>
       </c>
       <c r="O33">
-        <v>35838</v>
+        <v>36023</v>
       </c>
       <c r="P33">
         <v>76315</v>
@@ -2587,37 +2587,37 @@
         <v>0</v>
       </c>
       <c r="G34">
-        <v>34420</v>
+        <v>34730</v>
       </c>
       <c r="H34">
-        <v>2122</v>
+        <v>1812</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
       <c r="J34">
-        <v>265</v>
+        <v>197</v>
       </c>
       <c r="K34">
         <v>0</v>
       </c>
       <c r="L34">
-        <v>11101</v>
+        <v>11215</v>
       </c>
       <c r="M34">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="N34">
-        <v>581</v>
+        <v>690</v>
       </c>
       <c r="O34">
-        <v>31794</v>
+        <v>32158</v>
       </c>
       <c r="P34">
         <v>74625</v>
       </c>
       <c r="Q34">
-        <v>7149</v>
+        <v>7137</v>
       </c>
       <c r="R34">
         <v>0</v>
@@ -2646,31 +2646,31 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>31609</v>
+        <v>31667</v>
       </c>
       <c r="H35">
-        <v>1955</v>
+        <v>1897</v>
       </c>
       <c r="I35">
         <v>0</v>
       </c>
       <c r="J35">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K35">
         <v>0</v>
       </c>
       <c r="L35">
-        <v>6461</v>
+        <v>6479</v>
       </c>
       <c r="M35">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N35">
-        <v>922</v>
+        <v>968</v>
       </c>
       <c r="O35">
-        <v>29564</v>
+        <v>29599</v>
       </c>
       <c r="P35">
         <v>76465</v>
@@ -2714,7 +2714,7 @@
         <v>0</v>
       </c>
       <c r="J36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K36">
         <v>0</v>
@@ -2726,7 +2726,7 @@
         <v>0</v>
       </c>
       <c r="N36">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="O36">
         <v>19954</v>
@@ -2735,7 +2735,7 @@
         <v>60419</v>
       </c>
       <c r="Q36">
-        <v>3869</v>
+        <v>3855</v>
       </c>
       <c r="R36">
         <v>0</v>
@@ -2832,28 +2832,28 @@
         <v>0</v>
       </c>
       <c r="J38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K38">
         <v>0</v>
       </c>
       <c r="L38">
-        <v>5370</v>
+        <v>5374</v>
       </c>
       <c r="M38">
         <v>2</v>
       </c>
       <c r="N38">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="O38">
-        <v>28441</v>
+        <v>28463</v>
       </c>
       <c r="P38">
         <v>63038</v>
       </c>
       <c r="Q38">
-        <v>5136</v>
+        <v>5135</v>
       </c>
       <c r="R38">
         <v>0</v>
@@ -2950,22 +2950,22 @@
         <v>0</v>
       </c>
       <c r="J40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K40">
         <v>0</v>
       </c>
       <c r="L40">
-        <v>1810</v>
+        <v>1812</v>
       </c>
       <c r="M40">
         <v>0</v>
       </c>
       <c r="N40">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O40">
-        <v>18850</v>
+        <v>18853</v>
       </c>
       <c r="P40">
         <v>73242</v>
@@ -3089,7 +3089,7 @@
         <v>68615</v>
       </c>
       <c r="Q42">
-        <v>4713</v>
+        <v>4708</v>
       </c>
       <c r="R42">
         <v>0</v>
@@ -3148,7 +3148,7 @@
         <v>63043</v>
       </c>
       <c r="Q43">
-        <v>5249</v>
+        <v>5219</v>
       </c>
       <c r="R43">
         <v>0</v>
@@ -3236,16 +3236,16 @@
         <v>0</v>
       </c>
       <c r="G45">
-        <v>19622</v>
+        <v>19884</v>
       </c>
       <c r="H45">
-        <v>309</v>
+        <v>48</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J45">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K45">
         <v>0</v>
@@ -3257,10 +3257,10 @@
         <v>13</v>
       </c>
       <c r="N45">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="O45">
-        <v>18880</v>
+        <v>19164</v>
       </c>
       <c r="P45">
         <v>76002</v>
@@ -3319,7 +3319,7 @@
         <v>276</v>
       </c>
       <c r="O46">
-        <v>20906</v>
+        <v>20909</v>
       </c>
       <c r="P46">
         <v>64160</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="E48">
-        <v>19604</v>
+        <v>19605</v>
       </c>
       <c r="F48">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G48">
         <v>19589</v>
@@ -3472,16 +3472,16 @@
         <v>8</v>
       </c>
       <c r="G49">
-        <v>20792</v>
+        <v>20819</v>
       </c>
       <c r="H49">
-        <v>627</v>
+        <v>603</v>
       </c>
       <c r="I49">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="J49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K49">
         <v>0</v>
@@ -3496,7 +3496,7 @@
         <v>362</v>
       </c>
       <c r="O49">
-        <v>19543</v>
+        <v>19591</v>
       </c>
       <c r="P49">
         <v>55376</v>
@@ -3611,10 +3611,10 @@
         <v>11</v>
       </c>
       <c r="N51">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O51">
-        <v>23591</v>
+        <v>23695</v>
       </c>
       <c r="P51">
         <v>71754</v>
@@ -3658,13 +3658,13 @@
         <v>0</v>
       </c>
       <c r="J52">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="K52">
         <v>1</v>
       </c>
       <c r="L52">
-        <v>2912</v>
+        <v>2922</v>
       </c>
       <c r="M52">
         <v>1</v>
@@ -3717,22 +3717,22 @@
         <v>0</v>
       </c>
       <c r="J53">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="K53">
         <v>1</v>
       </c>
       <c r="L53">
-        <v>3498</v>
+        <v>3510</v>
       </c>
       <c r="M53">
         <v>1</v>
       </c>
       <c r="N53">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="O53">
-        <v>19032</v>
+        <v>19052</v>
       </c>
       <c r="P53">
         <v>56304</v>
@@ -3767,37 +3767,37 @@
         <v>0</v>
       </c>
       <c r="G54">
-        <v>20755</v>
+        <v>20756</v>
       </c>
       <c r="H54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I54">
         <v>0</v>
       </c>
       <c r="J54">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K54">
         <v>0</v>
       </c>
       <c r="L54">
-        <v>2477</v>
+        <v>2497</v>
       </c>
       <c r="M54">
         <v>5</v>
       </c>
       <c r="N54">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O54">
-        <v>20163</v>
+        <v>20260</v>
       </c>
       <c r="P54">
         <v>58440</v>
       </c>
       <c r="Q54">
-        <v>7378</v>
+        <v>7376</v>
       </c>
       <c r="R54">
         <v>0</v>
@@ -3826,16 +3826,16 @@
         <v>0</v>
       </c>
       <c r="G55">
-        <v>16017</v>
+        <v>16022</v>
       </c>
       <c r="H55">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I55">
         <v>0</v>
       </c>
       <c r="J55">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K55">
         <v>4</v>
@@ -3847,10 +3847,10 @@
         <v>1</v>
       </c>
       <c r="N55">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="O55">
-        <v>15839</v>
+        <v>15843</v>
       </c>
       <c r="P55">
         <v>58215</v>
@@ -3885,31 +3885,31 @@
         <v>0</v>
       </c>
       <c r="G56">
-        <v>19246</v>
+        <v>19255</v>
       </c>
       <c r="H56">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I56">
         <v>0</v>
       </c>
       <c r="J56">
-        <v>129</v>
+        <v>4</v>
       </c>
       <c r="K56">
         <v>0</v>
       </c>
       <c r="L56">
-        <v>3700</v>
+        <v>3844</v>
       </c>
       <c r="M56">
         <v>2</v>
       </c>
       <c r="N56">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="O56">
-        <v>18263</v>
+        <v>18265</v>
       </c>
       <c r="P56">
         <v>46365</v>
@@ -3953,13 +3953,13 @@
         <v>0</v>
       </c>
       <c r="J57">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K57">
         <v>0</v>
       </c>
       <c r="L57">
-        <v>1854</v>
+        <v>1891</v>
       </c>
       <c r="M57">
         <v>5</v>
@@ -3968,7 +3968,7 @@
         <v>39</v>
       </c>
       <c r="O57">
-        <v>21149</v>
+        <v>21186</v>
       </c>
       <c r="P57">
         <v>61556</v>
@@ -4015,7 +4015,7 @@
         <v>116</v>
       </c>
       <c r="K58">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="L58">
         <v>7987</v>
@@ -4033,7 +4033,7 @@
         <v>57577</v>
       </c>
       <c r="Q58">
-        <v>8916</v>
+        <v>8898</v>
       </c>
       <c r="R58">
         <v>0</v>
@@ -4086,13 +4086,13 @@
         <v>283</v>
       </c>
       <c r="O59">
-        <v>17087</v>
+        <v>17426</v>
       </c>
       <c r="P59">
         <v>60495</v>
       </c>
       <c r="Q59">
-        <v>8042</v>
+        <v>8028</v>
       </c>
       <c r="R59">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0</v>
       </c>
       <c r="J60">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="K60">
         <v>0</v>
       </c>
       <c r="L60">
-        <v>5649</v>
+        <v>5666</v>
       </c>
       <c r="M60">
         <v>9</v>
@@ -4145,13 +4145,13 @@
         <v>324</v>
       </c>
       <c r="O60">
-        <v>21762</v>
+        <v>21763</v>
       </c>
       <c r="P60">
         <v>70140</v>
       </c>
       <c r="Q60">
-        <v>7432</v>
+        <v>7415</v>
       </c>
       <c r="R60">
         <v>0</v>
@@ -4204,7 +4204,7 @@
         <v>1</v>
       </c>
       <c r="O61">
-        <v>16668</v>
+        <v>19565</v>
       </c>
       <c r="P61">
         <v>55240</v>
@@ -4248,13 +4248,13 @@
         <v>0</v>
       </c>
       <c r="J62">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="K62">
         <v>0</v>
       </c>
       <c r="L62">
-        <v>4117</v>
+        <v>4134</v>
       </c>
       <c r="M62">
         <v>19</v>
@@ -4269,7 +4269,7 @@
         <v>51334</v>
       </c>
       <c r="Q62">
-        <v>6956</v>
+        <v>6917</v>
       </c>
       <c r="R62">
         <v>0</v>
@@ -4313,22 +4313,22 @@
         <v>0</v>
       </c>
       <c r="L63">
-        <v>10969</v>
+        <v>10970</v>
       </c>
       <c r="M63">
         <v>68</v>
       </c>
       <c r="N63">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="O63">
-        <v>35808</v>
+        <v>35821</v>
       </c>
       <c r="P63">
         <v>68691</v>
       </c>
       <c r="Q63">
-        <v>9776</v>
+        <v>9775</v>
       </c>
       <c r="R63">
         <v>0</v>
@@ -4357,31 +4357,31 @@
         <v>0</v>
       </c>
       <c r="G64">
-        <v>42034</v>
+        <v>42036</v>
       </c>
       <c r="H64">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I64">
         <v>0</v>
       </c>
       <c r="J64">
-        <v>82</v>
+        <v>6</v>
       </c>
       <c r="K64">
         <v>0</v>
       </c>
       <c r="L64">
-        <v>9673</v>
+        <v>9738</v>
       </c>
       <c r="M64">
         <v>8</v>
       </c>
       <c r="N64">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="O64">
-        <v>41242</v>
+        <v>41248</v>
       </c>
       <c r="P64">
         <v>60527</v>
@@ -4416,37 +4416,37 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>40118</v>
+        <v>40209</v>
       </c>
       <c r="H65">
-        <v>922</v>
+        <v>832</v>
       </c>
       <c r="I65">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J65">
-        <v>45</v>
+        <v>253</v>
       </c>
       <c r="K65">
         <v>0</v>
       </c>
       <c r="L65">
-        <v>12781</v>
+        <v>12828</v>
       </c>
       <c r="M65">
         <v>2</v>
       </c>
       <c r="N65">
-        <v>1817</v>
+        <v>1908</v>
       </c>
       <c r="O65">
-        <v>31743</v>
+        <v>31767</v>
       </c>
       <c r="P65">
         <v>58103</v>
       </c>
       <c r="Q65">
-        <v>13284</v>
+        <v>13282</v>
       </c>
       <c r="R65">
         <v>0</v>
@@ -4475,31 +4475,31 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>65445</v>
+        <v>65980</v>
       </c>
       <c r="H66">
-        <v>1916</v>
+        <v>1382</v>
       </c>
       <c r="I66">
         <v>0</v>
       </c>
       <c r="J66">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="K66">
         <v>0</v>
       </c>
       <c r="L66">
-        <v>13375</v>
+        <v>13462</v>
       </c>
       <c r="M66">
         <v>2</v>
       </c>
       <c r="N66">
-        <v>3196</v>
+        <v>3243</v>
       </c>
       <c r="O66">
-        <v>59679</v>
+        <v>60956</v>
       </c>
       <c r="P66">
         <v>93810</v>
@@ -4534,31 +4534,31 @@
         <v>0</v>
       </c>
       <c r="G67">
-        <v>68597</v>
+        <v>68753</v>
       </c>
       <c r="H67">
         <v>0</v>
       </c>
       <c r="I67">
-        <v>231</v>
+        <v>75</v>
       </c>
       <c r="J67">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="K67">
         <v>0</v>
       </c>
       <c r="L67">
-        <v>19329</v>
+        <v>19385</v>
       </c>
       <c r="M67">
         <v>10</v>
       </c>
       <c r="N67">
-        <v>3427</v>
+        <v>3543</v>
       </c>
       <c r="O67">
-        <v>64857</v>
+        <v>64897</v>
       </c>
       <c r="P67">
         <v>78022</v>
@@ -4593,34 +4593,34 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>62718</v>
+        <v>62752</v>
       </c>
       <c r="H68">
-        <v>1878</v>
+        <v>1846</v>
       </c>
       <c r="I68">
         <v>733</v>
       </c>
       <c r="J68">
-        <v>145</v>
+        <v>53</v>
       </c>
       <c r="K68">
         <v>0</v>
       </c>
       <c r="L68">
-        <v>16722</v>
+        <v>16841</v>
       </c>
       <c r="M68">
         <v>2</v>
       </c>
       <c r="N68">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="O68">
-        <v>53183</v>
+        <v>53208</v>
       </c>
       <c r="P68">
-        <v>67572</v>
+        <v>69868</v>
       </c>
       <c r="Q68">
         <v>7850</v>
@@ -4652,31 +4652,31 @@
         <v>0</v>
       </c>
       <c r="G69">
-        <v>41837</v>
+        <v>42103</v>
       </c>
       <c r="H69">
-        <v>2071</v>
+        <v>1808</v>
       </c>
       <c r="I69">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J69">
-        <v>53</v>
+        <v>239</v>
       </c>
       <c r="K69">
         <v>0</v>
       </c>
       <c r="L69">
-        <v>17003</v>
+        <v>17047</v>
       </c>
       <c r="M69">
         <v>2</v>
       </c>
       <c r="N69">
-        <v>1693</v>
+        <v>1740</v>
       </c>
       <c r="O69">
-        <v>37141</v>
+        <v>37204</v>
       </c>
       <c r="P69">
         <v>36117</v>
@@ -4711,31 +4711,31 @@
         <v>0</v>
       </c>
       <c r="G70">
-        <v>47642</v>
+        <v>47649</v>
       </c>
       <c r="H70">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="I70">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J70">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K70">
         <v>0</v>
       </c>
       <c r="L70">
-        <v>18241</v>
+        <v>18253</v>
       </c>
       <c r="M70">
         <v>2</v>
       </c>
       <c r="N70">
-        <v>3181</v>
+        <v>3194</v>
       </c>
       <c r="O70">
-        <v>44285</v>
+        <v>44418</v>
       </c>
       <c r="P70">
         <v>42040</v>
@@ -4770,22 +4770,22 @@
         <v>0</v>
       </c>
       <c r="G71">
-        <v>50669</v>
+        <v>50694</v>
       </c>
       <c r="H71">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="I71">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J71">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="K71">
         <v>0</v>
       </c>
       <c r="L71">
-        <v>22723</v>
+        <v>22728</v>
       </c>
       <c r="M71">
         <v>1</v>
@@ -4794,7 +4794,7 @@
         <v>4171</v>
       </c>
       <c r="O71">
-        <v>46143</v>
+        <v>46154</v>
       </c>
       <c r="P71">
         <v>48896</v>
@@ -4829,16 +4829,16 @@
         <v>0</v>
       </c>
       <c r="G72">
-        <v>61334</v>
+        <v>61346</v>
       </c>
       <c r="H72">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="I72">
         <v>67</v>
       </c>
       <c r="J72">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="K72">
         <v>0</v>
@@ -4850,16 +4850,16 @@
         <v>9</v>
       </c>
       <c r="N72">
-        <v>3561</v>
+        <v>3571</v>
       </c>
       <c r="O72">
-        <v>51336</v>
+        <v>51795</v>
       </c>
       <c r="P72">
         <v>85505</v>
       </c>
       <c r="Q72">
-        <v>12373</v>
+        <v>12353</v>
       </c>
       <c r="R72">
         <v>0</v>
@@ -4888,37 +4888,37 @@
         <v>0</v>
       </c>
       <c r="G73">
-        <v>56040</v>
+        <v>56283</v>
       </c>
       <c r="H73">
-        <v>2764</v>
+        <v>2554</v>
       </c>
       <c r="I73">
-        <v>111</v>
+        <v>78</v>
       </c>
       <c r="J73">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="K73">
         <v>0</v>
       </c>
       <c r="L73">
-        <v>13936</v>
+        <v>13954</v>
       </c>
       <c r="M73">
         <v>7</v>
       </c>
       <c r="N73">
-        <v>1875</v>
+        <v>1989</v>
       </c>
       <c r="O73">
-        <v>48936</v>
+        <v>49076</v>
       </c>
       <c r="P73">
         <v>67550</v>
       </c>
       <c r="Q73">
-        <v>10011</v>
+        <v>10010</v>
       </c>
       <c r="R73">
         <v>0</v>
@@ -4939,49 +4939,49 @@
         <v>0</v>
       </c>
       <c r="E74">
-        <v>2430323</v>
+        <v>2430331</v>
       </c>
       <c r="F74">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="G74">
-        <v>2375740</v>
+        <v>2387758</v>
       </c>
       <c r="H74">
-        <v>48675</v>
+        <v>38154</v>
       </c>
       <c r="I74">
-        <v>5631</v>
+        <v>4237</v>
       </c>
       <c r="J74">
-        <v>40165</v>
+        <v>37516</v>
       </c>
       <c r="K74">
-        <v>20429</v>
+        <v>17317</v>
       </c>
       <c r="L74">
-        <v>563335</v>
+        <v>571666</v>
       </c>
       <c r="M74">
-        <v>2252</v>
+        <v>2608</v>
       </c>
       <c r="N74">
-        <v>73503</v>
+        <v>76565</v>
       </c>
       <c r="O74">
-        <v>2168528</v>
+        <v>2191144</v>
       </c>
       <c r="P74">
-        <v>4661212</v>
+        <v>4677463</v>
       </c>
       <c r="Q74">
-        <v>627497</v>
+        <v>626533</v>
       </c>
       <c r="R74">
         <v>1</v>
       </c>
       <c r="S74">
-        <v>3452</v>
+        <v>3445</v>
       </c>
     </row>
   </sheetData>

--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -1,317 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\New folder (13)\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49F51FAF-BDAF-435D-ACC3-D9DE92521456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
-  <si>
-    <t>S. No.</t>
-  </si>
-  <si>
-    <t>AC No. - AC Name</t>
-  </si>
-  <si>
-    <t>Notice Generated</t>
-  </si>
-  <si>
-    <t>Pending for Notice Generation</t>
-  </si>
-  <si>
-    <t>Notice Delivered</t>
-  </si>
-  <si>
-    <t>Notices pending delivery</t>
-  </si>
-  <si>
-    <t>Hearing</t>
-  </si>
-  <si>
-    <t>DEO Status</t>
-  </si>
-  <si>
-    <t>ERO/AERO Status</t>
-  </si>
-  <si>
-    <t>DSE with UP</t>
-  </si>
-  <si>
-    <t>Hearing Held</t>
-  </si>
-  <si>
-    <t>Hearing Date Lapsed</t>
-  </si>
-  <si>
-    <t>Reschedule Date Lapsed</t>
-  </si>
-  <si>
-    <t>Total Pending</t>
-  </si>
-  <si>
-    <t>Pending &gt; 5 days</t>
-  </si>
-  <si>
-    <t>Verified</t>
-  </si>
-  <si>
-    <t>Not Verified</t>
-  </si>
-  <si>
-    <t>Found Ineligible for Final</t>
-  </si>
-  <si>
-    <t>Parked for Final Publication w.r.t. Notices Generated</t>
-  </si>
-  <si>
-    <t>Parked For Final Publication w.r.t. Others</t>
-  </si>
-  <si>
-    <t>Electors having DSE with UP</t>
-  </si>
-  <si>
-    <t>Form 7 Generated</t>
-  </si>
-  <si>
-    <t>No Action Required</t>
-  </si>
-  <si>
-    <t>25 - Haridwar</t>
-  </si>
-  <si>
-    <t>26 - BHEL Ranipur</t>
-  </si>
-  <si>
-    <t>27 - Jwalapur</t>
-  </si>
-  <si>
-    <t>28 - Bhagwanpur</t>
-  </si>
-  <si>
-    <t>29 - Jhabrera</t>
-  </si>
-  <si>
-    <t>30 - Piran Kaliyar</t>
-  </si>
-  <si>
-    <t>31 - Roorkee</t>
-  </si>
-  <si>
-    <t>32 - Khanpur</t>
-  </si>
-  <si>
-    <t>33 - Manglore</t>
-  </si>
-  <si>
-    <t>34 - Laksar</t>
-  </si>
-  <si>
-    <t>35 - Haridwar Rural</t>
-  </si>
-  <si>
-    <t>56 - Lalkuan</t>
-  </si>
-  <si>
-    <t>57 - Bhimtal</t>
-  </si>
-  <si>
-    <t>58 - Nainital</t>
-  </si>
-  <si>
-    <t>59 - Haldwani</t>
-  </si>
-  <si>
-    <t>60 - Kaladhungi</t>
-  </si>
-  <si>
-    <t>61 - Ramnagar</t>
-  </si>
-  <si>
-    <t>48 - Dwarahat</t>
-  </si>
-  <si>
-    <t>49 - Salt</t>
-  </si>
-  <si>
-    <t>50 - Ranikhet</t>
-  </si>
-  <si>
-    <t>51 - Someshwar</t>
-  </si>
-  <si>
-    <t>52 - Almora</t>
-  </si>
-  <si>
-    <t>53 - Jageshwar</t>
-  </si>
-  <si>
-    <t>62 - Jaspur</t>
-  </si>
-  <si>
-    <t>63 - Kashipur</t>
-  </si>
-  <si>
-    <t>64 - Bajpur</t>
-  </si>
-  <si>
-    <t>65 - Gadarpur</t>
-  </si>
-  <si>
-    <t>66 - Rudrapur</t>
-  </si>
-  <si>
-    <t>67 - Kichha</t>
-  </si>
-  <si>
-    <t>68 - Sitarganj</t>
-  </si>
-  <si>
-    <t>69 - Nanakmatta</t>
-  </si>
-  <si>
-    <t>70 - Khatima</t>
-  </si>
-  <si>
-    <t>42 - Dharchula</t>
-  </si>
-  <si>
-    <t>43 - Didihat</t>
-  </si>
-  <si>
-    <t>44 - Pithoragarh</t>
-  </si>
-  <si>
-    <t>45 - Gangolihat</t>
-  </si>
-  <si>
-    <t>46 - Kapkot</t>
-  </si>
-  <si>
-    <t>47 - Bageshwar</t>
-  </si>
-  <si>
-    <t>54 - Lohaghat</t>
-  </si>
-  <si>
-    <t>55 - Champawat</t>
-  </si>
-  <si>
-    <t>4 - Badrinath</t>
-  </si>
-  <si>
-    <t>5 - Tharali</t>
-  </si>
-  <si>
-    <t>6 - Karanprayag</t>
-  </si>
-  <si>
-    <t>1 - Purola</t>
-  </si>
-  <si>
-    <t>2 - Yamunotri</t>
-  </si>
-  <si>
-    <t>3 - Gangotri</t>
-  </si>
-  <si>
-    <t>7 - Kedarnath</t>
-  </si>
-  <si>
-    <t>8 - Rudraprayag</t>
-  </si>
-  <si>
-    <t>9 - Ghansali</t>
-  </si>
-  <si>
-    <t>10 - Devprayag</t>
-  </si>
-  <si>
-    <t>11 - Narendranagar</t>
-  </si>
-  <si>
-    <t>12 - Pratapnagar</t>
-  </si>
-  <si>
-    <t>13 - Tehri</t>
-  </si>
-  <si>
-    <t>14 - Dhanolti</t>
-  </si>
-  <si>
-    <t>36 - Yamkeshwar</t>
-  </si>
-  <si>
-    <t>37 - Pauri</t>
-  </si>
-  <si>
-    <t>38 - Srinagar</t>
-  </si>
-  <si>
-    <t>39 - Chaubattakhal</t>
-  </si>
-  <si>
-    <t>40 - Lansdowne</t>
-  </si>
-  <si>
-    <t>41 - Kotdwar</t>
-  </si>
-  <si>
-    <t>15 - Chakrata</t>
-  </si>
-  <si>
-    <t>16 - Vikasnagar</t>
-  </si>
-  <si>
-    <t>17 - Sahaspur</t>
-  </si>
-  <si>
-    <t>18 - Dharmpur</t>
-  </si>
-  <si>
-    <t>19 - Raipur</t>
-  </si>
-  <si>
-    <t>20 - Rajpur Road</t>
-  </si>
-  <si>
-    <t>21 - Dehradun Cantonment</t>
-  </si>
-  <si>
-    <t>22 - Mussoorie</t>
-  </si>
-  <si>
-    <t>23 - Doiwala</t>
-  </si>
-  <si>
-    <t>24 - Rishikesh</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Notice &amp; Hearing Report Last Updated On : 02-09-2026 08:00:00</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -340,23 +64,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -681,128 +396,93 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T74"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S74"/>
   <sheetData>
-    <row r="1" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-    </row>
-    <row r="2" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-    </row>
-    <row r="3" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K3" t="s">
-        <v>14</v>
-      </c>
-      <c r="L3" t="s">
-        <v>15</v>
-      </c>
-      <c r="M3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N3" t="s">
-        <v>17</v>
-      </c>
-      <c r="O3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P3" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R3" t="s">
-        <v>21</v>
-      </c>
-      <c r="S3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Notice &amp; Hearing Report</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>S. No.</v>
+      </c>
+      <c r="B2" t="str">
+        <v>AC No. - AC Name</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Notice Generated</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Pending for Notice Generation</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Notice Delivered</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Notices pending delivery</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Hearing</v>
+      </c>
+      <c r="J2" t="str">
+        <v>DEO Status</v>
+      </c>
+      <c r="N2" t="str">
+        <v>ERO/AERO Status</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>DSE with UP</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="G3" t="str">
+        <v>Hearing Held</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Hearing Date Lapsed</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Reschedule Date Lapsed</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Total Pending</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Pending &gt; 5 days</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Verified</v>
+      </c>
+      <c r="M3" t="str">
+        <v>Not Verified</v>
+      </c>
+      <c r="N3" t="str">
+        <v>Found Ineligible for Final</v>
+      </c>
+      <c r="O3" t="str">
+        <v>Parked for Final Publication w.r.t. Notices Generated</v>
+      </c>
+      <c r="P3" t="str">
+        <v>Parked For Final Publication w.r.t. Others</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>Electors having DSE with UP</v>
+      </c>
+      <c r="R3" t="str">
+        <v>Form 7 Generated</v>
+      </c>
+      <c r="S3" t="str">
+        <v>No Action Required</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" t="s">
-        <v>23</v>
+      <c r="B4" t="str">
+        <v>25 - Haridwar</v>
       </c>
       <c r="C4">
         <v>51528</v>
@@ -817,31 +497,31 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>48194</v>
+        <v>48568</v>
       </c>
       <c r="H4">
-        <v>3330</v>
+        <v>2956</v>
       </c>
       <c r="I4">
         <v>4</v>
       </c>
       <c r="J4">
-        <v>4709</v>
+        <v>4744</v>
       </c>
       <c r="K4">
-        <v>517</v>
+        <v>472</v>
       </c>
       <c r="L4">
-        <v>10979</v>
+        <v>11099</v>
       </c>
       <c r="M4">
-        <v>48</v>
+        <v>255</v>
       </c>
       <c r="N4">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="O4">
-        <v>41773</v>
+        <v>42145</v>
       </c>
       <c r="P4">
         <v>53812</v>
@@ -856,12 +536,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5">
         <v>2</v>
       </c>
-      <c r="B5" t="s">
-        <v>24</v>
+      <c r="B5" t="str">
+        <v>26 - BHEL Ranipur</v>
       </c>
       <c r="C5">
         <v>53911</v>
@@ -876,34 +556,34 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>52459</v>
+        <v>52682</v>
       </c>
       <c r="H5">
-        <v>1265</v>
+        <v>1097</v>
       </c>
       <c r="I5">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>3041</v>
+        <v>3009</v>
       </c>
       <c r="K5">
-        <v>1116</v>
+        <v>1076</v>
       </c>
       <c r="L5">
-        <v>7684</v>
+        <v>7833</v>
       </c>
       <c r="M5">
-        <v>108</v>
+        <v>204</v>
       </c>
       <c r="N5">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="O5">
-        <v>48210</v>
+        <v>48302</v>
       </c>
       <c r="P5">
-        <v>74320</v>
+        <v>74848</v>
       </c>
       <c r="Q5">
         <v>16108</v>
@@ -915,12 +595,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6">
         <v>3</v>
       </c>
-      <c r="B6" t="s">
-        <v>25</v>
+      <c r="B6" t="str">
+        <v>27 - Jwalapur</v>
       </c>
       <c r="C6">
         <v>39773</v>
@@ -935,31 +615,31 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>37335</v>
+        <v>37664</v>
       </c>
       <c r="H6">
-        <v>2246</v>
+        <v>1946</v>
       </c>
       <c r="I6">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="J6">
-        <v>2681</v>
+        <v>2526</v>
       </c>
       <c r="K6">
         <v>1223</v>
       </c>
       <c r="L6">
-        <v>3113</v>
+        <v>3293</v>
       </c>
       <c r="M6">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N6">
-        <v>1162</v>
+        <v>1178</v>
       </c>
       <c r="O6">
-        <v>31018</v>
+        <v>31336</v>
       </c>
       <c r="P6">
         <v>70908</v>
@@ -974,12 +654,12 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7">
         <v>4</v>
       </c>
-      <c r="B7" t="s">
-        <v>26</v>
+      <c r="B7" t="str">
+        <v>28 - Bhagwanpur</v>
       </c>
       <c r="C7">
         <v>39463</v>
@@ -994,31 +674,31 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>39199</v>
+        <v>39263</v>
       </c>
       <c r="H7">
-        <v>264</v>
+        <v>200</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7">
-        <v>2498</v>
+        <v>2165</v>
       </c>
       <c r="K7">
-        <v>2347</v>
+        <v>2027</v>
       </c>
       <c r="L7">
-        <v>3243</v>
+        <v>3573</v>
       </c>
       <c r="M7">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="N7">
-        <v>1804</v>
+        <v>1834</v>
       </c>
       <c r="O7">
-        <v>33630</v>
+        <v>33747</v>
       </c>
       <c r="P7">
         <v>77581</v>
@@ -1033,12 +713,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8">
         <v>5</v>
       </c>
-      <c r="B8" t="s">
-        <v>27</v>
+      <c r="B8" t="str">
+        <v>29 - Jhabrera</v>
       </c>
       <c r="C8">
         <v>40552</v>
@@ -1053,16 +733,16 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>38632</v>
+        <v>39028</v>
       </c>
       <c r="H8">
-        <v>1920</v>
+        <v>1524</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>85</v>
+        <v>148</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -1074,10 +754,10 @@
         <v>158</v>
       </c>
       <c r="N8">
-        <v>1192</v>
+        <v>1255</v>
       </c>
       <c r="O8">
-        <v>28507</v>
+        <v>30186</v>
       </c>
       <c r="P8">
         <v>73458</v>
@@ -1092,12 +772,12 @@
         <v>110</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9">
         <v>6</v>
       </c>
-      <c r="B9" t="s">
-        <v>28</v>
+      <c r="B9" t="str">
+        <v>30 - Piran Kaliyar</v>
       </c>
       <c r="C9">
         <v>43273</v>
@@ -1112,31 +792,31 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>42954</v>
+        <v>43224</v>
       </c>
       <c r="H9">
-        <v>317</v>
+        <v>48</v>
       </c>
       <c r="I9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J9">
-        <v>1521</v>
+        <v>1333</v>
       </c>
       <c r="K9">
-        <v>1118</v>
+        <v>987</v>
       </c>
       <c r="L9">
-        <v>5764</v>
+        <v>5878</v>
       </c>
       <c r="M9">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="N9">
         <v>1236</v>
       </c>
       <c r="O9">
-        <v>38918</v>
+        <v>39208</v>
       </c>
       <c r="P9">
         <v>72762</v>
@@ -1151,12 +831,12 @@
         <v>110</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10">
         <v>7</v>
       </c>
-      <c r="B10" t="s">
-        <v>29</v>
+      <c r="B10" t="str">
+        <v>31 - Roorkee</v>
       </c>
       <c r="C10">
         <v>36576</v>
@@ -1171,31 +851,31 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>36549</v>
+        <v>36552</v>
       </c>
       <c r="H10">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10">
-        <v>1892</v>
+        <v>1760</v>
       </c>
       <c r="K10">
-        <v>1450</v>
+        <v>1422</v>
       </c>
       <c r="L10">
-        <v>9141</v>
+        <v>9273</v>
       </c>
       <c r="M10">
         <v>63</v>
       </c>
       <c r="N10">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="O10">
-        <v>33860</v>
+        <v>33861</v>
       </c>
       <c r="P10">
         <v>53124</v>
@@ -1210,12 +890,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11">
         <v>8</v>
       </c>
-      <c r="B11" t="s">
-        <v>30</v>
+      <c r="B11" t="str">
+        <v>32 - Khanpur</v>
       </c>
       <c r="C11">
         <v>50998</v>
@@ -1239,22 +919,22 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>1222</v>
+        <v>612</v>
       </c>
       <c r="K11">
-        <v>597</v>
+        <v>133</v>
       </c>
       <c r="L11">
-        <v>8691</v>
+        <v>9281</v>
       </c>
       <c r="M11">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="N11">
-        <v>1487</v>
+        <v>1514</v>
       </c>
       <c r="O11">
-        <v>45815</v>
+        <v>48528</v>
       </c>
       <c r="P11">
         <v>84438</v>
@@ -1269,12 +949,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12">
         <v>9</v>
       </c>
-      <c r="B12" t="s">
-        <v>31</v>
+      <c r="B12" t="str">
+        <v>33 - Manglore</v>
       </c>
       <c r="C12">
         <v>40739</v>
@@ -1289,31 +969,31 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>40310</v>
+        <v>40416</v>
       </c>
       <c r="H12">
-        <v>392</v>
+        <v>323</v>
       </c>
       <c r="I12">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>2943</v>
+        <v>2430</v>
       </c>
       <c r="K12">
-        <v>2627</v>
+        <v>2150</v>
       </c>
       <c r="L12">
-        <v>6842</v>
+        <v>7366</v>
       </c>
       <c r="M12">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="N12">
         <v>1020</v>
       </c>
       <c r="O12">
-        <v>32682</v>
+        <v>32806</v>
       </c>
       <c r="P12">
         <v>66685</v>
@@ -1328,12 +1008,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13">
         <v>10</v>
       </c>
-      <c r="B13" t="s">
-        <v>32</v>
+      <c r="B13" t="str">
+        <v>34 - Laksar</v>
       </c>
       <c r="C13">
         <v>37031</v>
@@ -1357,22 +1037,22 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>2125</v>
+        <v>832</v>
       </c>
       <c r="K13">
-        <v>1441</v>
+        <v>510</v>
       </c>
       <c r="L13">
-        <v>5641</v>
+        <v>7005</v>
       </c>
       <c r="M13">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="N13">
         <v>3818</v>
       </c>
       <c r="O13">
-        <v>30234</v>
+        <v>30741</v>
       </c>
       <c r="P13">
         <v>56565</v>
@@ -1387,12 +1067,12 @@
         <v>106</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14">
         <v>11</v>
       </c>
-      <c r="B14" t="s">
-        <v>33</v>
+      <c r="B14" t="str">
+        <v>35 - Haridwar Rural</v>
       </c>
       <c r="C14">
         <v>48966</v>
@@ -1407,34 +1087,34 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>45398</v>
+        <v>45733</v>
       </c>
       <c r="H14">
-        <v>3539</v>
+        <v>3187</v>
       </c>
       <c r="I14">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J14">
-        <v>8464</v>
+        <v>8490</v>
       </c>
       <c r="K14">
-        <v>4812</v>
+        <v>4793</v>
       </c>
       <c r="L14">
-        <v>6665</v>
+        <v>6703</v>
       </c>
       <c r="M14">
-        <v>314</v>
+        <v>496</v>
       </c>
       <c r="N14">
-        <v>3467</v>
+        <v>3594</v>
       </c>
       <c r="O14">
-        <v>27909</v>
+        <v>28309</v>
       </c>
       <c r="P14">
-        <v>70636</v>
+        <v>72777</v>
       </c>
       <c r="Q14">
         <v>19716</v>
@@ -1446,12 +1126,12 @@
         <v>174</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15">
         <v>12</v>
       </c>
-      <c r="B15" t="s">
-        <v>34</v>
+      <c r="B15" t="str">
+        <v>56 - Lalkuan</v>
       </c>
       <c r="C15">
         <v>42703</v>
@@ -1505,12 +1185,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16">
         <v>13</v>
       </c>
-      <c r="B16" t="s">
-        <v>35</v>
+      <c r="B16" t="str">
+        <v>57 - Bhimtal</v>
       </c>
       <c r="C16">
         <v>25549</v>
@@ -1549,10 +1229,10 @@
         <v>261</v>
       </c>
       <c r="O16">
-        <v>24857</v>
+        <v>25288</v>
       </c>
       <c r="P16">
-        <v>71642</v>
+        <v>71673</v>
       </c>
       <c r="Q16">
         <v>5197</v>
@@ -1564,12 +1244,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17">
         <v>14</v>
       </c>
-      <c r="B17" t="s">
-        <v>36</v>
+      <c r="B17" t="str">
+        <v>58 - Nainital</v>
       </c>
       <c r="C17">
         <v>27707</v>
@@ -1623,12 +1303,12 @@
         <v>105</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="A18">
         <v>15</v>
       </c>
-      <c r="B18" t="s">
-        <v>37</v>
+      <c r="B18" t="str">
+        <v>59 - Haldwani</v>
       </c>
       <c r="C18">
         <v>47836</v>
@@ -1682,12 +1362,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19">
       <c r="A19">
         <v>16</v>
       </c>
-      <c r="B19" t="s">
-        <v>38</v>
+      <c r="B19" t="str">
+        <v>60 - Kaladhungi</v>
       </c>
       <c r="C19">
         <v>56490</v>
@@ -1726,7 +1406,7 @@
         <v>910</v>
       </c>
       <c r="O19">
-        <v>55194</v>
+        <v>55229</v>
       </c>
       <c r="P19">
         <v>106227</v>
@@ -1741,12 +1421,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20">
       <c r="A20">
         <v>17</v>
       </c>
-      <c r="B20" t="s">
-        <v>39</v>
+      <c r="B20" t="str">
+        <v>61 - Ramnagar</v>
       </c>
       <c r="C20">
         <v>35022</v>
@@ -1755,10 +1435,10 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>35017</v>
+        <v>35022</v>
       </c>
       <c r="F20">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G20">
         <v>35022</v>
@@ -1800,12 +1480,12 @@
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21">
       <c r="A21">
         <v>18</v>
       </c>
-      <c r="B21" t="s">
-        <v>40</v>
+      <c r="B21" t="str">
+        <v>48 - Dwarahat</v>
       </c>
       <c r="C21">
         <v>16962</v>
@@ -1859,12 +1539,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22">
       <c r="A22">
         <v>19</v>
       </c>
-      <c r="B22" t="s">
-        <v>41</v>
+      <c r="B22" t="str">
+        <v>49 - Salt</v>
       </c>
       <c r="C22">
         <v>18668</v>
@@ -1888,22 +1568,22 @@
         <v>0</v>
       </c>
       <c r="J22">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K22">
         <v>0</v>
       </c>
       <c r="L22">
-        <v>7630</v>
+        <v>7661</v>
       </c>
       <c r="M22">
         <v>0</v>
       </c>
       <c r="N22">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="O22">
-        <v>18331</v>
+        <v>18360</v>
       </c>
       <c r="P22">
         <v>64099</v>
@@ -1918,12 +1598,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23">
       <c r="A23">
         <v>20</v>
       </c>
-      <c r="B23" t="s">
-        <v>42</v>
+      <c r="B23" t="str">
+        <v>50 - Ranikhet</v>
       </c>
       <c r="C23">
         <v>12020</v>
@@ -1977,12 +1657,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24">
       <c r="A24">
         <v>21</v>
       </c>
-      <c r="B24" t="s">
-        <v>43</v>
+      <c r="B24" t="str">
+        <v>51 - Someshwar</v>
       </c>
       <c r="C24">
         <v>14056</v>
@@ -2036,12 +1716,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25">
       <c r="A25">
         <v>22</v>
       </c>
-      <c r="B25" t="s">
-        <v>44</v>
+      <c r="B25" t="str">
+        <v>52 - Almora</v>
       </c>
       <c r="C25">
         <v>19266</v>
@@ -2095,12 +1775,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26">
       <c r="A26">
         <v>23</v>
       </c>
-      <c r="B26" t="s">
-        <v>45</v>
+      <c r="B26" t="str">
+        <v>53 - Jageshwar</v>
       </c>
       <c r="C26">
         <v>17557</v>
@@ -2154,12 +1834,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27">
       <c r="A27">
         <v>24</v>
       </c>
-      <c r="B27" t="s">
-        <v>46</v>
+      <c r="B27" t="str">
+        <v>62 - Jaspur</v>
       </c>
       <c r="C27">
         <v>44276</v>
@@ -2174,34 +1854,34 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>41478</v>
+        <v>41836</v>
       </c>
       <c r="H27">
-        <v>2798</v>
+        <v>2440</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="L27">
-        <v>9189</v>
+        <v>9263</v>
       </c>
       <c r="M27">
         <v>26</v>
       </c>
       <c r="N27">
-        <v>583</v>
+        <v>783</v>
       </c>
       <c r="O27">
-        <v>39395</v>
+        <v>39519</v>
       </c>
       <c r="P27">
-        <v>62365</v>
+        <v>63060</v>
       </c>
       <c r="Q27">
         <v>12669</v>
@@ -2213,12 +1893,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28">
       <c r="A28">
         <v>25</v>
       </c>
-      <c r="B28" t="s">
-        <v>47</v>
+      <c r="B28" t="str">
+        <v>63 - Kashipur</v>
       </c>
       <c r="C28">
         <v>54349</v>
@@ -2233,31 +1913,31 @@
         <v>0</v>
       </c>
       <c r="G28">
-        <v>51523</v>
+        <v>52088</v>
       </c>
       <c r="H28">
-        <v>2826</v>
+        <v>2261</v>
       </c>
       <c r="I28">
         <v>0</v>
       </c>
       <c r="J28">
-        <v>633</v>
+        <v>749</v>
       </c>
       <c r="K28">
         <v>0</v>
       </c>
       <c r="L28">
-        <v>7421</v>
+        <v>7567</v>
       </c>
       <c r="M28">
         <v>253</v>
       </c>
       <c r="N28">
-        <v>1736</v>
+        <v>1903</v>
       </c>
       <c r="O28">
-        <v>47489</v>
+        <v>48063</v>
       </c>
       <c r="P28">
         <v>80623</v>
@@ -2272,12 +1952,12 @@
         <v>127</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29">
       <c r="A29">
         <v>26</v>
       </c>
-      <c r="B29" t="s">
-        <v>48</v>
+      <c r="B29" t="str">
+        <v>64 - Bajpur</v>
       </c>
       <c r="C29">
         <v>47111</v>
@@ -2301,13 +1981,13 @@
         <v>0</v>
       </c>
       <c r="J29">
-        <v>427</v>
+        <v>398</v>
       </c>
       <c r="K29">
         <v>0</v>
       </c>
       <c r="L29">
-        <v>8456</v>
+        <v>8485</v>
       </c>
       <c r="M29">
         <v>37</v>
@@ -2331,12 +2011,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30">
       <c r="A30">
         <v>27</v>
       </c>
-      <c r="B30" t="s">
-        <v>49</v>
+      <c r="B30" t="str">
+        <v>65 - Gadarpur</v>
       </c>
       <c r="C30">
         <v>52653</v>
@@ -2345,37 +2025,37 @@
         <v>0</v>
       </c>
       <c r="E30">
-        <v>52650</v>
+        <v>52653</v>
       </c>
       <c r="F30">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G30">
-        <v>50324</v>
+        <v>50778</v>
       </c>
       <c r="H30">
-        <v>392</v>
+        <v>273</v>
       </c>
       <c r="I30">
-        <v>1937</v>
+        <v>1602</v>
       </c>
       <c r="J30">
-        <v>1382</v>
+        <v>632</v>
       </c>
       <c r="K30">
         <v>0</v>
       </c>
       <c r="L30">
-        <v>8487</v>
+        <v>9488</v>
       </c>
       <c r="M30">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="N30">
-        <v>4962</v>
+        <v>5017</v>
       </c>
       <c r="O30">
-        <v>43432</v>
+        <v>44651</v>
       </c>
       <c r="P30">
         <v>86933</v>
@@ -2390,12 +2070,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31">
       <c r="A31">
         <v>28</v>
       </c>
-      <c r="B31" t="s">
-        <v>50</v>
+      <c r="B31" t="str">
+        <v>66 - Rudrapur</v>
       </c>
       <c r="C31">
         <v>91162</v>
@@ -2419,22 +2099,22 @@
         <v>0</v>
       </c>
       <c r="J31">
-        <v>1315</v>
+        <v>79</v>
       </c>
       <c r="K31">
         <v>0</v>
       </c>
       <c r="L31">
-        <v>45364</v>
+        <v>46599</v>
       </c>
       <c r="M31">
         <v>42</v>
       </c>
       <c r="N31">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="O31">
-        <v>87492</v>
+        <v>87899</v>
       </c>
       <c r="P31">
         <v>81642</v>
@@ -2449,12 +2129,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32">
       <c r="A32">
         <v>29</v>
       </c>
-      <c r="B32" t="s">
-        <v>51</v>
+      <c r="B32" t="str">
+        <v>67 - Kichha</v>
       </c>
       <c r="C32">
         <v>46728</v>
@@ -2463,40 +2143,40 @@
         <v>0</v>
       </c>
       <c r="E32">
-        <v>46724</v>
+        <v>46728</v>
       </c>
       <c r="F32">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G32">
-        <v>42600</v>
+        <v>43505</v>
       </c>
       <c r="H32">
-        <v>3886</v>
+        <v>2983</v>
       </c>
       <c r="I32">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="J32">
-        <v>822</v>
+        <v>758</v>
       </c>
       <c r="K32">
         <v>0</v>
       </c>
       <c r="L32">
-        <v>9153</v>
+        <v>9572</v>
       </c>
       <c r="M32">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="N32">
-        <v>2462</v>
+        <v>2795</v>
       </c>
       <c r="O32">
-        <v>38658</v>
+        <v>38916</v>
       </c>
       <c r="P32">
-        <v>74814</v>
+        <v>74812</v>
       </c>
       <c r="Q32">
         <v>11379</v>
@@ -2508,12 +2188,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33">
       <c r="A33">
         <v>30</v>
       </c>
-      <c r="B33" t="s">
-        <v>52</v>
+      <c r="B33" t="str">
+        <v>68 - Sitarganj</v>
       </c>
       <c r="C33">
         <v>40230</v>
@@ -2528,34 +2208,34 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <v>38371</v>
+        <v>38643</v>
       </c>
       <c r="H33">
-        <v>1824</v>
+        <v>1571</v>
       </c>
       <c r="I33">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="J33">
-        <v>273</v>
+        <v>255</v>
       </c>
       <c r="K33">
         <v>0</v>
       </c>
       <c r="L33">
-        <v>4549</v>
+        <v>4629</v>
       </c>
       <c r="M33">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="N33">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="O33">
-        <v>36023</v>
+        <v>36245</v>
       </c>
       <c r="P33">
-        <v>76315</v>
+        <v>76489</v>
       </c>
       <c r="Q33">
         <v>6678</v>
@@ -2567,12 +2247,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="34" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34">
       <c r="A34">
         <v>31</v>
       </c>
-      <c r="B34" t="s">
-        <v>53</v>
+      <c r="B34" t="str">
+        <v>69 - Nanakmatta</v>
       </c>
       <c r="C34">
         <v>36542</v>
@@ -2587,34 +2267,34 @@
         <v>0</v>
       </c>
       <c r="G34">
-        <v>34730</v>
+        <v>34989</v>
       </c>
       <c r="H34">
-        <v>1812</v>
+        <v>1553</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
       <c r="J34">
-        <v>197</v>
+        <v>122</v>
       </c>
       <c r="K34">
         <v>0</v>
       </c>
       <c r="L34">
-        <v>11215</v>
+        <v>11329</v>
       </c>
       <c r="M34">
         <v>53</v>
       </c>
       <c r="N34">
-        <v>690</v>
+        <v>766</v>
       </c>
       <c r="O34">
-        <v>32158</v>
+        <v>32637</v>
       </c>
       <c r="P34">
-        <v>74625</v>
+        <v>74624</v>
       </c>
       <c r="Q34">
         <v>7137</v>
@@ -2626,12 +2306,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35">
       <c r="A35">
         <v>32</v>
       </c>
-      <c r="B35" t="s">
-        <v>54</v>
+      <c r="B35" t="str">
+        <v>70 - Khatima</v>
       </c>
       <c r="C35">
         <v>33564</v>
@@ -2646,31 +2326,31 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>31667</v>
+        <v>31813</v>
       </c>
       <c r="H35">
-        <v>1897</v>
+        <v>1751</v>
       </c>
       <c r="I35">
         <v>0</v>
       </c>
       <c r="J35">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="K35">
         <v>0</v>
       </c>
       <c r="L35">
-        <v>6479</v>
+        <v>6574</v>
       </c>
       <c r="M35">
         <v>8</v>
       </c>
       <c r="N35">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="O35">
-        <v>29599</v>
+        <v>29942</v>
       </c>
       <c r="P35">
         <v>76465</v>
@@ -2685,12 +2365,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36">
       <c r="A36">
         <v>33</v>
       </c>
-      <c r="B36" t="s">
-        <v>55</v>
+      <c r="B36" t="str">
+        <v>42 - Dharchula</v>
       </c>
       <c r="C36">
         <v>20905</v>
@@ -2744,12 +2424,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37">
       <c r="A37">
         <v>34</v>
       </c>
-      <c r="B37" t="s">
-        <v>56</v>
+      <c r="B37" t="str">
+        <v>43 - Didihat</v>
       </c>
       <c r="C37">
         <v>17692</v>
@@ -2803,12 +2483,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38">
       <c r="A38">
         <v>35</v>
       </c>
-      <c r="B38" t="s">
-        <v>57</v>
+      <c r="B38" t="str">
+        <v>44 - Pithoragarh</v>
       </c>
       <c r="C38">
         <v>29110</v>
@@ -2832,13 +2512,13 @@
         <v>0</v>
       </c>
       <c r="J38">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K38">
         <v>0</v>
       </c>
       <c r="L38">
-        <v>5374</v>
+        <v>5381</v>
       </c>
       <c r="M38">
         <v>2</v>
@@ -2862,12 +2542,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39">
       <c r="A39">
         <v>36</v>
       </c>
-      <c r="B39" t="s">
-        <v>58</v>
+      <c r="B39" t="str">
+        <v>45 - Gangolihat</v>
       </c>
       <c r="C39">
         <v>21367</v>
@@ -2921,12 +2601,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40">
       <c r="A40">
         <v>37</v>
       </c>
-      <c r="B40" t="s">
-        <v>59</v>
+      <c r="B40" t="str">
+        <v>46 - Kapkot</v>
       </c>
       <c r="C40">
         <v>18905</v>
@@ -2980,12 +2660,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41">
       <c r="A41">
         <v>38</v>
       </c>
-      <c r="B41" t="s">
-        <v>60</v>
+      <c r="B41" t="str">
+        <v>47 - Bageshwar</v>
       </c>
       <c r="C41">
         <v>23521</v>
@@ -3039,12 +2719,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="42" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42">
       <c r="A42">
         <v>39</v>
       </c>
-      <c r="B42" t="s">
-        <v>61</v>
+      <c r="B42" t="str">
+        <v>54 - Lohaghat</v>
       </c>
       <c r="C42">
         <v>27565</v>
@@ -3098,12 +2778,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43">
       <c r="A43">
         <v>40</v>
       </c>
-      <c r="B43" t="s">
-        <v>62</v>
+      <c r="B43" t="str">
+        <v>55 - Champawat</v>
       </c>
       <c r="C43">
         <v>29700</v>
@@ -3157,12 +2837,12 @@
         <v>121</v>
       </c>
     </row>
-    <row r="44" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44">
       <c r="A44">
         <v>41</v>
       </c>
-      <c r="B44" t="s">
-        <v>63</v>
+      <c r="B44" t="str">
+        <v>4 - Badrinath</v>
       </c>
       <c r="C44">
         <v>21900</v>
@@ -3216,12 +2896,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45">
       <c r="A45">
         <v>42</v>
       </c>
-      <c r="B45" t="s">
-        <v>64</v>
+      <c r="B45" t="str">
+        <v>5 - Tharali</v>
       </c>
       <c r="C45">
         <v>19935</v>
@@ -3236,31 +2916,31 @@
         <v>0</v>
       </c>
       <c r="G45">
-        <v>19884</v>
+        <v>19900</v>
       </c>
       <c r="H45">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I45">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J45">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="K45">
         <v>0</v>
       </c>
       <c r="L45">
-        <v>2217</v>
+        <v>2234</v>
       </c>
       <c r="M45">
         <v>13</v>
       </c>
       <c r="N45">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="O45">
-        <v>19164</v>
+        <v>19217</v>
       </c>
       <c r="P45">
         <v>76002</v>
@@ -3275,12 +2955,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="46" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46">
       <c r="A46">
         <v>43</v>
       </c>
-      <c r="B46" t="s">
-        <v>65</v>
+      <c r="B46" t="str">
+        <v>6 - Karanprayag</v>
       </c>
       <c r="C46">
         <v>21512</v>
@@ -3319,7 +2999,7 @@
         <v>276</v>
       </c>
       <c r="O46">
-        <v>20909</v>
+        <v>20934</v>
       </c>
       <c r="P46">
         <v>64160</v>
@@ -3334,12 +3014,12 @@
         <v>152</v>
       </c>
     </row>
-    <row r="47" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47">
       <c r="A47">
         <v>44</v>
       </c>
-      <c r="B47" t="s">
-        <v>66</v>
+      <c r="B47" t="str">
+        <v>1 - Purola</v>
       </c>
       <c r="C47">
         <v>22426</v>
@@ -3363,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="J47">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K47">
         <v>0</v>
       </c>
       <c r="L47">
-        <v>2592</v>
+        <v>2594</v>
       </c>
       <c r="M47">
         <v>1</v>
@@ -3393,12 +3073,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48">
       <c r="A48">
         <v>45</v>
       </c>
-      <c r="B48" t="s">
-        <v>67</v>
+      <c r="B48" t="str">
+        <v>2 - Yamunotri</v>
       </c>
       <c r="C48">
         <v>19641</v>
@@ -3407,22 +3087,22 @@
         <v>0</v>
       </c>
       <c r="E48">
-        <v>19605</v>
+        <v>19617</v>
       </c>
       <c r="F48">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="G48">
-        <v>19589</v>
+        <v>19594</v>
       </c>
       <c r="H48">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="I48">
         <v>1</v>
       </c>
       <c r="J48">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K48">
         <v>0</v>
@@ -3434,7 +3114,7 @@
         <v>4</v>
       </c>
       <c r="N48">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="O48">
         <v>19330</v>
@@ -3452,12 +3132,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49">
       <c r="A49">
         <v>46</v>
       </c>
-      <c r="B49" t="s">
-        <v>68</v>
+      <c r="B49" t="str">
+        <v>3 - Gangotri</v>
       </c>
       <c r="C49">
         <v>21651</v>
@@ -3466,28 +3146,28 @@
         <v>0</v>
       </c>
       <c r="E49">
-        <v>21643</v>
+        <v>21650</v>
       </c>
       <c r="F49">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G49">
-        <v>20819</v>
+        <v>21244</v>
       </c>
       <c r="H49">
-        <v>603</v>
+        <v>181</v>
       </c>
       <c r="I49">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="J49">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K49">
         <v>0</v>
       </c>
       <c r="L49">
-        <v>3591</v>
+        <v>3594</v>
       </c>
       <c r="M49">
         <v>0</v>
@@ -3496,7 +3176,7 @@
         <v>362</v>
       </c>
       <c r="O49">
-        <v>19591</v>
+        <v>20011</v>
       </c>
       <c r="P49">
         <v>55376</v>
@@ -3511,12 +3191,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50">
       <c r="A50">
         <v>47</v>
       </c>
-      <c r="B50" t="s">
-        <v>69</v>
+      <c r="B50" t="str">
+        <v>7 - Kedarnath</v>
       </c>
       <c r="C50">
         <v>21936</v>
@@ -3570,12 +3250,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51">
       <c r="A51">
         <v>48</v>
       </c>
-      <c r="B51" t="s">
-        <v>70</v>
+      <c r="B51" t="str">
+        <v>8 - Rudraprayag</v>
       </c>
       <c r="C51">
         <v>23798</v>
@@ -3599,7 +3279,7 @@
         <v>0</v>
       </c>
       <c r="J51">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K51">
         <v>0</v>
@@ -3611,10 +3291,10 @@
         <v>11</v>
       </c>
       <c r="N51">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O51">
-        <v>23695</v>
+        <v>23707</v>
       </c>
       <c r="P51">
         <v>71754</v>
@@ -3629,12 +3309,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="52" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52">
       <c r="A52">
         <v>49</v>
       </c>
-      <c r="B52" t="s">
-        <v>71</v>
+      <c r="B52" t="str">
+        <v>9 - Ghansali</v>
       </c>
       <c r="C52">
         <v>21094</v>
@@ -3673,7 +3353,7 @@
         <v>44</v>
       </c>
       <c r="O52">
-        <v>21003</v>
+        <v>21023</v>
       </c>
       <c r="P52">
         <v>63986</v>
@@ -3688,12 +3368,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53">
       <c r="A53">
         <v>50</v>
       </c>
-      <c r="B53" t="s">
-        <v>72</v>
+      <c r="B53" t="str">
+        <v>10 - Devprayag</v>
       </c>
       <c r="C53">
         <v>19131</v>
@@ -3747,12 +3427,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54">
       <c r="A54">
         <v>51</v>
       </c>
-      <c r="B54" t="s">
-        <v>73</v>
+      <c r="B54" t="str">
+        <v>11 - Narendranagar</v>
       </c>
       <c r="C54">
         <v>20758</v>
@@ -3767,31 +3447,31 @@
         <v>0</v>
       </c>
       <c r="G54">
-        <v>20756</v>
+        <v>20758</v>
       </c>
       <c r="H54">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I54">
         <v>0</v>
       </c>
       <c r="J54">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K54">
         <v>0</v>
       </c>
       <c r="L54">
-        <v>2497</v>
+        <v>2531</v>
       </c>
       <c r="M54">
         <v>5</v>
       </c>
       <c r="N54">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="O54">
-        <v>20260</v>
+        <v>20291</v>
       </c>
       <c r="P54">
         <v>58440</v>
@@ -3806,12 +3486,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55">
       <c r="A55">
         <v>52</v>
       </c>
-      <c r="B55" t="s">
-        <v>74</v>
+      <c r="B55" t="str">
+        <v>12 - Pratapnagar</v>
       </c>
       <c r="C55">
         <v>16022</v>
@@ -3835,7 +3515,7 @@
         <v>0</v>
       </c>
       <c r="J55">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K55">
         <v>4</v>
@@ -3865,12 +3545,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56">
       <c r="A56">
         <v>53</v>
       </c>
-      <c r="B56" t="s">
-        <v>75</v>
+      <c r="B56" t="str">
+        <v>13 - Tehri</v>
       </c>
       <c r="C56">
         <v>19256</v>
@@ -3894,22 +3574,22 @@
         <v>0</v>
       </c>
       <c r="J56">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K56">
         <v>0</v>
       </c>
       <c r="L56">
-        <v>3844</v>
+        <v>3846</v>
       </c>
       <c r="M56">
         <v>2</v>
       </c>
       <c r="N56">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="O56">
-        <v>18265</v>
+        <v>18563</v>
       </c>
       <c r="P56">
         <v>46365</v>
@@ -3924,12 +3604,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="57" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57">
       <c r="A57">
         <v>54</v>
       </c>
-      <c r="B57" t="s">
-        <v>76</v>
+      <c r="B57" t="str">
+        <v>14 - Dhanolti</v>
       </c>
       <c r="C57">
         <v>21240</v>
@@ -3968,7 +3648,7 @@
         <v>39</v>
       </c>
       <c r="O57">
-        <v>21186</v>
+        <v>21187</v>
       </c>
       <c r="P57">
         <v>61556</v>
@@ -3983,12 +3663,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58">
       <c r="A58">
         <v>55</v>
       </c>
-      <c r="B58" t="s">
-        <v>77</v>
+      <c r="B58" t="str">
+        <v>36 - Yamkeshwar</v>
       </c>
       <c r="C58">
         <v>22819</v>
@@ -4012,22 +3692,22 @@
         <v>0</v>
       </c>
       <c r="J58">
-        <v>116</v>
+        <v>4</v>
       </c>
       <c r="K58">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="L58">
-        <v>7987</v>
+        <v>8092</v>
       </c>
       <c r="M58">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N58">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O58">
-        <v>20420</v>
+        <v>20506</v>
       </c>
       <c r="P58">
         <v>57577</v>
@@ -4042,12 +3722,12 @@
         <v>64</v>
       </c>
     </row>
-    <row r="59" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59">
       <c r="A59">
         <v>56</v>
       </c>
-      <c r="B59" t="s">
-        <v>78</v>
+      <c r="B59" t="str">
+        <v>37 - Pauri</v>
       </c>
       <c r="C59">
         <v>18776</v>
@@ -4071,13 +3751,13 @@
         <v>0</v>
       </c>
       <c r="J59">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K59">
         <v>0</v>
       </c>
       <c r="L59">
-        <v>2489</v>
+        <v>2494</v>
       </c>
       <c r="M59">
         <v>2</v>
@@ -4086,7 +3766,7 @@
         <v>283</v>
       </c>
       <c r="O59">
-        <v>17426</v>
+        <v>18442</v>
       </c>
       <c r="P59">
         <v>60495</v>
@@ -4101,12 +3781,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="60" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60">
       <c r="A60">
         <v>57</v>
       </c>
-      <c r="B60" t="s">
-        <v>79</v>
+      <c r="B60" t="str">
+        <v>38 - Srinagar</v>
       </c>
       <c r="C60">
         <v>23749</v>
@@ -4130,13 +3810,13 @@
         <v>0</v>
       </c>
       <c r="J60">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="K60">
         <v>0</v>
       </c>
       <c r="L60">
-        <v>5666</v>
+        <v>5716</v>
       </c>
       <c r="M60">
         <v>9</v>
@@ -4160,12 +3840,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="61" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61">
       <c r="A61">
         <v>58</v>
       </c>
-      <c r="B61" t="s">
-        <v>80</v>
+      <c r="B61" t="str">
+        <v>39 - Chaubattakhal</v>
       </c>
       <c r="C61">
         <v>22069</v>
@@ -4189,7 +3869,7 @@
         <v>0</v>
       </c>
       <c r="J61">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K61">
         <v>0</v>
@@ -4198,13 +3878,13 @@
         <v>9976</v>
       </c>
       <c r="M61">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N61">
         <v>1</v>
       </c>
       <c r="O61">
-        <v>19565</v>
+        <v>22030</v>
       </c>
       <c r="P61">
         <v>55240</v>
@@ -4219,12 +3899,12 @@
         <v>268</v>
       </c>
     </row>
-    <row r="62" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62">
       <c r="A62">
         <v>59</v>
       </c>
-      <c r="B62" t="s">
-        <v>81</v>
+      <c r="B62" t="str">
+        <v>40 - Lansdowne</v>
       </c>
       <c r="C62">
         <v>15800</v>
@@ -4248,22 +3928,22 @@
         <v>0</v>
       </c>
       <c r="J62">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K62">
         <v>0</v>
       </c>
       <c r="L62">
-        <v>4134</v>
+        <v>4138</v>
       </c>
       <c r="M62">
         <v>19</v>
       </c>
       <c r="N62">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="O62">
-        <v>15209</v>
+        <v>15230</v>
       </c>
       <c r="P62">
         <v>51334</v>
@@ -4278,12 +3958,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63">
       <c r="A63">
         <v>60</v>
       </c>
-      <c r="B63" t="s">
-        <v>82</v>
+      <c r="B63" t="str">
+        <v>41 - Kotdwar</v>
       </c>
       <c r="C63">
         <v>36754</v>
@@ -4307,13 +3987,13 @@
         <v>0</v>
       </c>
       <c r="J63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K63">
         <v>0</v>
       </c>
       <c r="L63">
-        <v>10970</v>
+        <v>10971</v>
       </c>
       <c r="M63">
         <v>68</v>
@@ -4337,12 +4017,12 @@
         <v>153</v>
       </c>
     </row>
-    <row r="64" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64">
       <c r="A64">
         <v>61</v>
       </c>
-      <c r="B64" t="s">
-        <v>83</v>
+      <c r="B64" t="str">
+        <v>15 - Chakrata</v>
       </c>
       <c r="C64">
         <v>42048</v>
@@ -4366,13 +4046,13 @@
         <v>0</v>
       </c>
       <c r="J64">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K64">
         <v>0</v>
       </c>
       <c r="L64">
-        <v>9738</v>
+        <v>9742</v>
       </c>
       <c r="M64">
         <v>8</v>
@@ -4381,7 +4061,7 @@
         <v>467</v>
       </c>
       <c r="O64">
-        <v>41248</v>
+        <v>41279</v>
       </c>
       <c r="P64">
         <v>60527</v>
@@ -4396,12 +4076,12 @@
         <v>101</v>
       </c>
     </row>
-    <row r="65" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65">
       <c r="A65">
         <v>62</v>
       </c>
-      <c r="B65" t="s">
-        <v>84</v>
+      <c r="B65" t="str">
+        <v>16 - Vikasnagar</v>
       </c>
       <c r="C65">
         <v>41389</v>
@@ -4416,31 +4096,31 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>40209</v>
+        <v>40317</v>
       </c>
       <c r="H65">
-        <v>832</v>
+        <v>748</v>
       </c>
       <c r="I65">
-        <v>348</v>
+        <v>324</v>
       </c>
       <c r="J65">
-        <v>253</v>
+        <v>190</v>
       </c>
       <c r="K65">
         <v>0</v>
       </c>
       <c r="L65">
-        <v>12828</v>
+        <v>12930</v>
       </c>
       <c r="M65">
         <v>2</v>
       </c>
       <c r="N65">
-        <v>1908</v>
+        <v>1928</v>
       </c>
       <c r="O65">
-        <v>31767</v>
+        <v>32001</v>
       </c>
       <c r="P65">
         <v>58103</v>
@@ -4455,12 +4135,12 @@
         <v>138</v>
       </c>
     </row>
-    <row r="66" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66">
       <c r="A66">
         <v>63</v>
       </c>
-      <c r="B66" t="s">
-        <v>85</v>
+      <c r="B66" t="str">
+        <v>17 - Sahaspur</v>
       </c>
       <c r="C66">
         <v>67362</v>
@@ -4475,31 +4155,31 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>65980</v>
+        <v>66243</v>
       </c>
       <c r="H66">
-        <v>1382</v>
+        <v>1119</v>
       </c>
       <c r="I66">
         <v>0</v>
       </c>
       <c r="J66">
-        <v>74</v>
+        <v>19</v>
       </c>
       <c r="K66">
         <v>0</v>
       </c>
       <c r="L66">
-        <v>13462</v>
+        <v>13554</v>
       </c>
       <c r="M66">
         <v>2</v>
       </c>
       <c r="N66">
-        <v>3243</v>
+        <v>3353</v>
       </c>
       <c r="O66">
-        <v>60956</v>
+        <v>62553</v>
       </c>
       <c r="P66">
         <v>93810</v>
@@ -4514,12 +4194,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="67" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67">
       <c r="A67">
         <v>64</v>
       </c>
-      <c r="B67" t="s">
-        <v>86</v>
+      <c r="B67" t="str">
+        <v>18 - Dharmpur</v>
       </c>
       <c r="C67">
         <v>68828</v>
@@ -4534,31 +4214,31 @@
         <v>0</v>
       </c>
       <c r="G67">
-        <v>68753</v>
+        <v>68768</v>
       </c>
       <c r="H67">
         <v>0</v>
       </c>
       <c r="I67">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="J67">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="K67">
         <v>0</v>
       </c>
       <c r="L67">
-        <v>19385</v>
+        <v>19406</v>
       </c>
       <c r="M67">
         <v>10</v>
       </c>
       <c r="N67">
-        <v>3543</v>
+        <v>3566</v>
       </c>
       <c r="O67">
-        <v>64897</v>
+        <v>64930</v>
       </c>
       <c r="P67">
         <v>78022</v>
@@ -4573,12 +4253,12 @@
         <v>116</v>
       </c>
     </row>
-    <row r="68" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68">
       <c r="A68">
         <v>65</v>
       </c>
-      <c r="B68" t="s">
-        <v>87</v>
+      <c r="B68" t="str">
+        <v>19 - Raipur</v>
       </c>
       <c r="C68">
         <v>65397</v>
@@ -4593,34 +4273,34 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>62752</v>
+        <v>62886</v>
       </c>
       <c r="H68">
-        <v>1846</v>
+        <v>1684</v>
       </c>
       <c r="I68">
-        <v>733</v>
+        <v>711</v>
       </c>
       <c r="J68">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="K68">
         <v>0</v>
       </c>
       <c r="L68">
-        <v>16841</v>
+        <v>16923</v>
       </c>
       <c r="M68">
         <v>2</v>
       </c>
       <c r="N68">
-        <v>789</v>
+        <v>832</v>
       </c>
       <c r="O68">
-        <v>53208</v>
+        <v>54372</v>
       </c>
       <c r="P68">
-        <v>69868</v>
+        <v>70054</v>
       </c>
       <c r="Q68">
         <v>7850</v>
@@ -4632,12 +4312,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="69" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69">
       <c r="A69">
         <v>66</v>
       </c>
-      <c r="B69" t="s">
-        <v>88</v>
+      <c r="B69" t="str">
+        <v>20 - Rajpur Road</v>
       </c>
       <c r="C69">
         <v>43938</v>
@@ -4652,31 +4332,31 @@
         <v>0</v>
       </c>
       <c r="G69">
-        <v>42103</v>
+        <v>42232</v>
       </c>
       <c r="H69">
-        <v>1808</v>
+        <v>1679</v>
       </c>
       <c r="I69">
         <v>27</v>
       </c>
       <c r="J69">
-        <v>239</v>
+        <v>19</v>
       </c>
       <c r="K69">
         <v>0</v>
       </c>
       <c r="L69">
-        <v>17047</v>
+        <v>17314</v>
       </c>
       <c r="M69">
         <v>2</v>
       </c>
       <c r="N69">
-        <v>1740</v>
+        <v>1818</v>
       </c>
       <c r="O69">
-        <v>37204</v>
+        <v>37698</v>
       </c>
       <c r="P69">
         <v>36117</v>
@@ -4691,12 +4371,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="70" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70">
       <c r="A70">
         <v>67</v>
       </c>
-      <c r="B70" t="s">
-        <v>89</v>
+      <c r="B70" t="str">
+        <v>21 - Dehradun Cantonment</v>
       </c>
       <c r="C70">
         <v>47711</v>
@@ -4711,34 +4391,34 @@
         <v>0</v>
       </c>
       <c r="G70">
-        <v>47649</v>
+        <v>47650</v>
       </c>
       <c r="H70">
         <v>55</v>
       </c>
       <c r="I70">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J70">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K70">
         <v>0</v>
       </c>
       <c r="L70">
-        <v>18253</v>
+        <v>18259</v>
       </c>
       <c r="M70">
         <v>2</v>
       </c>
       <c r="N70">
-        <v>3194</v>
+        <v>3196</v>
       </c>
       <c r="O70">
-        <v>44418</v>
+        <v>44425</v>
       </c>
       <c r="P70">
-        <v>42040</v>
+        <v>42039</v>
       </c>
       <c r="Q70">
         <v>5798</v>
@@ -4750,12 +4430,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="71" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71">
       <c r="A71">
         <v>68</v>
       </c>
-      <c r="B71" t="s">
-        <v>90</v>
+      <c r="B71" t="str">
+        <v>22 - Mussoorie</v>
       </c>
       <c r="C71">
         <v>50963</v>
@@ -4770,31 +4450,31 @@
         <v>0</v>
       </c>
       <c r="G71">
-        <v>50694</v>
+        <v>50702</v>
       </c>
       <c r="H71">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="I71">
         <v>174</v>
       </c>
       <c r="J71">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K71">
         <v>0</v>
       </c>
       <c r="L71">
-        <v>22728</v>
+        <v>22750</v>
       </c>
       <c r="M71">
         <v>1</v>
       </c>
       <c r="N71">
-        <v>4171</v>
+        <v>4176</v>
       </c>
       <c r="O71">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="P71">
         <v>48896</v>
@@ -4809,12 +4489,12 @@
         <v>235</v>
       </c>
     </row>
-    <row r="72" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72">
       <c r="A72">
         <v>69</v>
       </c>
-      <c r="B72" t="s">
-        <v>91</v>
+      <c r="B72" t="str">
+        <v>23 - Doiwala</v>
       </c>
       <c r="C72">
         <v>61543</v>
@@ -4829,31 +4509,31 @@
         <v>0</v>
       </c>
       <c r="G72">
-        <v>61346</v>
+        <v>61362</v>
       </c>
       <c r="H72">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="I72">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="J72">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="K72">
         <v>0</v>
       </c>
       <c r="L72">
-        <v>17016</v>
+        <v>17067</v>
       </c>
       <c r="M72">
         <v>9</v>
       </c>
       <c r="N72">
-        <v>3571</v>
+        <v>3580</v>
       </c>
       <c r="O72">
-        <v>51795</v>
+        <v>53245</v>
       </c>
       <c r="P72">
         <v>85505</v>
@@ -4868,12 +4548,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="73" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73">
       <c r="A73">
         <v>70</v>
       </c>
-      <c r="B73" t="s">
-        <v>92</v>
+      <c r="B73" t="str">
+        <v>24 - Rishikesh</v>
       </c>
       <c r="C73">
         <v>58915</v>
@@ -4888,31 +4568,31 @@
         <v>0</v>
       </c>
       <c r="G73">
-        <v>56283</v>
+        <v>56542</v>
       </c>
       <c r="H73">
-        <v>2554</v>
+        <v>2299</v>
       </c>
       <c r="I73">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="J73">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="K73">
         <v>0</v>
       </c>
       <c r="L73">
-        <v>13954</v>
+        <v>14097</v>
       </c>
       <c r="M73">
         <v>7</v>
       </c>
       <c r="N73">
-        <v>1989</v>
+        <v>2091</v>
       </c>
       <c r="O73">
-        <v>49076</v>
+        <v>49711</v>
       </c>
       <c r="P73">
         <v>67550</v>
@@ -4927,11 +4607,10 @@
         <v>74</v>
       </c>
     </row>
-    <row r="74" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B74" s="1"/>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>Total</v>
+      </c>
       <c r="C74">
         <v>2430387</v>
       </c>
@@ -4939,40 +4618,40 @@
         <v>0</v>
       </c>
       <c r="E74">
-        <v>2430331</v>
+        <v>2430362</v>
       </c>
       <c r="F74">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="G74">
-        <v>2387758</v>
+        <v>2394198</v>
       </c>
       <c r="H74">
-        <v>38154</v>
+        <v>32203</v>
       </c>
       <c r="I74">
-        <v>4237</v>
+        <v>3706</v>
       </c>
       <c r="J74">
-        <v>37516</v>
+        <v>31611</v>
       </c>
       <c r="K74">
-        <v>17317</v>
+        <v>14799</v>
       </c>
       <c r="L74">
-        <v>571666</v>
+        <v>579451</v>
       </c>
       <c r="M74">
-        <v>2608</v>
+        <v>3131</v>
       </c>
       <c r="N74">
-        <v>76565</v>
+        <v>78156</v>
       </c>
       <c r="O74">
-        <v>2191144</v>
+        <v>2211972</v>
       </c>
       <c r="P74">
-        <v>4677463</v>
+        <v>4681214</v>
       </c>
       <c r="Q74">
         <v>626533</v>
@@ -4986,7 +4665,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A74:B74"/>
     <mergeCell ref="A1:T1"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
@@ -4998,10 +4676,10 @@
     <mergeCell ref="J2:M2"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="A74:B74"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A2:S74 B1:S1" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S74"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -1,41 +1,317 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\New folder (13)\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{094E2CA3-4A53-4547-BEA6-F01FBA742248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
+  <si>
+    <t>S. No.</t>
+  </si>
+  <si>
+    <t>AC No. - AC Name</t>
+  </si>
+  <si>
+    <t>Notice Generated</t>
+  </si>
+  <si>
+    <t>Pending for Notice Generation</t>
+  </si>
+  <si>
+    <t>Notice Delivered</t>
+  </si>
+  <si>
+    <t>Notices pending delivery</t>
+  </si>
+  <si>
+    <t>Hearing</t>
+  </si>
+  <si>
+    <t>DEO Status</t>
+  </si>
+  <si>
+    <t>ERO/AERO Status</t>
+  </si>
+  <si>
+    <t>DSE with UP</t>
+  </si>
+  <si>
+    <t>Hearing Held</t>
+  </si>
+  <si>
+    <t>Hearing Date Lapsed</t>
+  </si>
+  <si>
+    <t>Reschedule Date Lapsed</t>
+  </si>
+  <si>
+    <t>Total Pending</t>
+  </si>
+  <si>
+    <t>Pending &gt; 5 days</t>
+  </si>
+  <si>
+    <t>Verified</t>
+  </si>
+  <si>
+    <t>Not Verified</t>
+  </si>
+  <si>
+    <t>Found Ineligible for Final</t>
+  </si>
+  <si>
+    <t>Parked for Final Publication w.r.t. Notices Generated</t>
+  </si>
+  <si>
+    <t>Parked For Final Publication w.r.t. Others</t>
+  </si>
+  <si>
+    <t>Electors having DSE with UP</t>
+  </si>
+  <si>
+    <t>Form 7 Generated</t>
+  </si>
+  <si>
+    <t>No Action Required</t>
+  </si>
+  <si>
+    <t>25 - Haridwar</t>
+  </si>
+  <si>
+    <t>26 - BHEL Ranipur</t>
+  </si>
+  <si>
+    <t>27 - Jwalapur</t>
+  </si>
+  <si>
+    <t>28 - Bhagwanpur</t>
+  </si>
+  <si>
+    <t>29 - Jhabrera</t>
+  </si>
+  <si>
+    <t>30 - Piran Kaliyar</t>
+  </si>
+  <si>
+    <t>31 - Roorkee</t>
+  </si>
+  <si>
+    <t>32 - Khanpur</t>
+  </si>
+  <si>
+    <t>33 - Manglore</t>
+  </si>
+  <si>
+    <t>34 - Laksar</t>
+  </si>
+  <si>
+    <t>35 - Haridwar Rural</t>
+  </si>
+  <si>
+    <t>56 - Lalkuan</t>
+  </si>
+  <si>
+    <t>57 - Bhimtal</t>
+  </si>
+  <si>
+    <t>58 - Nainital</t>
+  </si>
+  <si>
+    <t>59 - Haldwani</t>
+  </si>
+  <si>
+    <t>60 - Kaladhungi</t>
+  </si>
+  <si>
+    <t>61 - Ramnagar</t>
+  </si>
+  <si>
+    <t>48 - Dwarahat</t>
+  </si>
+  <si>
+    <t>49 - Salt</t>
+  </si>
+  <si>
+    <t>50 - Ranikhet</t>
+  </si>
+  <si>
+    <t>51 - Someshwar</t>
+  </si>
+  <si>
+    <t>52 - Almora</t>
+  </si>
+  <si>
+    <t>53 - Jageshwar</t>
+  </si>
+  <si>
+    <t>62 - Jaspur</t>
+  </si>
+  <si>
+    <t>63 - Kashipur</t>
+  </si>
+  <si>
+    <t>64 - Bajpur</t>
+  </si>
+  <si>
+    <t>65 - Gadarpur</t>
+  </si>
+  <si>
+    <t>66 - Rudrapur</t>
+  </si>
+  <si>
+    <t>67 - Kichha</t>
+  </si>
+  <si>
+    <t>68 - Sitarganj</t>
+  </si>
+  <si>
+    <t>69 - Nanakmatta</t>
+  </si>
+  <si>
+    <t>70 - Khatima</t>
+  </si>
+  <si>
+    <t>42 - Dharchula</t>
+  </si>
+  <si>
+    <t>43 - Didihat</t>
+  </si>
+  <si>
+    <t>44 - Pithoragarh</t>
+  </si>
+  <si>
+    <t>45 - Gangolihat</t>
+  </si>
+  <si>
+    <t>46 - Kapkot</t>
+  </si>
+  <si>
+    <t>47 - Bageshwar</t>
+  </si>
+  <si>
+    <t>54 - Lohaghat</t>
+  </si>
+  <si>
+    <t>55 - Champawat</t>
+  </si>
+  <si>
+    <t>4 - Badrinath</t>
+  </si>
+  <si>
+    <t>5 - Tharali</t>
+  </si>
+  <si>
+    <t>6 - Karanprayag</t>
+  </si>
+  <si>
+    <t>1 - Purola</t>
+  </si>
+  <si>
+    <t>2 - Yamunotri</t>
+  </si>
+  <si>
+    <t>3 - Gangotri</t>
+  </si>
+  <si>
+    <t>7 - Kedarnath</t>
+  </si>
+  <si>
+    <t>8 - Rudraprayag</t>
+  </si>
+  <si>
+    <t>9 - Ghansali</t>
+  </si>
+  <si>
+    <t>10 - Devprayag</t>
+  </si>
+  <si>
+    <t>11 - Narendranagar</t>
+  </si>
+  <si>
+    <t>12 - Pratapnagar</t>
+  </si>
+  <si>
+    <t>13 - Tehri</t>
+  </si>
+  <si>
+    <t>14 - Dhanolti</t>
+  </si>
+  <si>
+    <t>36 - Yamkeshwar</t>
+  </si>
+  <si>
+    <t>37 - Pauri</t>
+  </si>
+  <si>
+    <t>38 - Srinagar</t>
+  </si>
+  <si>
+    <t>39 - Chaubattakhal</t>
+  </si>
+  <si>
+    <t>40 - Lansdowne</t>
+  </si>
+  <si>
+    <t>41 - Kotdwar</t>
+  </si>
+  <si>
+    <t>15 - Chakrata</t>
+  </si>
+  <si>
+    <t>16 - Vikasnagar</t>
+  </si>
+  <si>
+    <t>17 - Sahaspur</t>
+  </si>
+  <si>
+    <t>18 - Dharmpur</t>
+  </si>
+  <si>
+    <t>19 - Raipur</t>
+  </si>
+  <si>
+    <t>20 - Rajpur Road</t>
+  </si>
+  <si>
+    <t>21 - Dehradun Cantonment</t>
+  </si>
+  <si>
+    <t>22 - Mussoorie</t>
+  </si>
+  <si>
+    <t>23 - Doiwala</t>
+  </si>
+  <si>
+    <t>24 - Rishikesh</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Notice &amp; Hearing Report Last Updated On : 02-09-2026 13:59:59</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -64,14 +340,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,93 +681,128 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S74"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:T74"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Notice &amp; Hearing Report</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>S. No.</v>
-      </c>
-      <c r="B2" t="str">
-        <v>AC No. - AC Name</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Notice Generated</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Pending for Notice Generation</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Notice Delivered</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Notices pending delivery</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Hearing</v>
-      </c>
-      <c r="J2" t="str">
-        <v>DEO Status</v>
-      </c>
-      <c r="N2" t="str">
-        <v>ERO/AERO Status</v>
-      </c>
-      <c r="Q2" t="str">
-        <v>DSE with UP</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="G3" t="str">
-        <v>Hearing Held</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Hearing Date Lapsed</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Reschedule Date Lapsed</v>
-      </c>
-      <c r="J3" t="str">
-        <v>Total Pending</v>
-      </c>
-      <c r="K3" t="str">
-        <v>Pending &gt; 5 days</v>
-      </c>
-      <c r="L3" t="str">
-        <v>Verified</v>
-      </c>
-      <c r="M3" t="str">
-        <v>Not Verified</v>
-      </c>
-      <c r="N3" t="str">
-        <v>Found Ineligible for Final</v>
-      </c>
-      <c r="O3" t="str">
-        <v>Parked for Final Publication w.r.t. Notices Generated</v>
-      </c>
-      <c r="P3" t="str">
-        <v>Parked For Final Publication w.r.t. Others</v>
-      </c>
-      <c r="Q3" t="str">
-        <v>Electors having DSE with UP</v>
-      </c>
-      <c r="R3" t="str">
-        <v>Form 7 Generated</v>
-      </c>
-      <c r="S3" t="str">
-        <v>No Action Required</v>
-      </c>
-    </row>
-    <row r="4">
+    <row r="1" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+    </row>
+    <row r="2" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+    </row>
+    <row r="3" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N3" t="s">
+        <v>17</v>
+      </c>
+      <c r="O3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R3" t="s">
+        <v>21</v>
+      </c>
+      <c r="S3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" t="str">
-        <v>25 - Haridwar</v>
+      <c r="B4" t="s">
+        <v>23</v>
       </c>
       <c r="C4">
         <v>51528</v>
@@ -536,12 +856,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
-      <c r="B5" t="str">
-        <v>26 - BHEL Ranipur</v>
+      <c r="B5" t="s">
+        <v>24</v>
       </c>
       <c r="C5">
         <v>53911</v>
@@ -595,12 +915,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
-      <c r="B6" t="str">
-        <v>27 - Jwalapur</v>
+      <c r="B6" t="s">
+        <v>25</v>
       </c>
       <c r="C6">
         <v>39773</v>
@@ -654,12 +974,12 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4</v>
       </c>
-      <c r="B7" t="str">
-        <v>28 - Bhagwanpur</v>
+      <c r="B7" t="s">
+        <v>26</v>
       </c>
       <c r="C7">
         <v>39463</v>
@@ -713,12 +1033,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
-      <c r="B8" t="str">
-        <v>29 - Jhabrera</v>
+      <c r="B8" t="s">
+        <v>27</v>
       </c>
       <c r="C8">
         <v>40552</v>
@@ -772,12 +1092,12 @@
         <v>110</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6</v>
       </c>
-      <c r="B9" t="str">
-        <v>30 - Piran Kaliyar</v>
+      <c r="B9" t="s">
+        <v>28</v>
       </c>
       <c r="C9">
         <v>43273</v>
@@ -831,12 +1151,12 @@
         <v>110</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>7</v>
       </c>
-      <c r="B10" t="str">
-        <v>31 - Roorkee</v>
+      <c r="B10" t="s">
+        <v>29</v>
       </c>
       <c r="C10">
         <v>36576</v>
@@ -890,12 +1210,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>8</v>
       </c>
-      <c r="B11" t="str">
-        <v>32 - Khanpur</v>
+      <c r="B11" t="s">
+        <v>30</v>
       </c>
       <c r="C11">
         <v>50998</v>
@@ -949,12 +1269,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
-      <c r="B12" t="str">
-        <v>33 - Manglore</v>
+      <c r="B12" t="s">
+        <v>31</v>
       </c>
       <c r="C12">
         <v>40739</v>
@@ -1008,12 +1328,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
-      <c r="B13" t="str">
-        <v>34 - Laksar</v>
+      <c r="B13" t="s">
+        <v>32</v>
       </c>
       <c r="C13">
         <v>37031</v>
@@ -1067,12 +1387,12 @@
         <v>106</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>11</v>
       </c>
-      <c r="B14" t="str">
-        <v>35 - Haridwar Rural</v>
+      <c r="B14" t="s">
+        <v>33</v>
       </c>
       <c r="C14">
         <v>48966</v>
@@ -1126,12 +1446,12 @@
         <v>174</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12</v>
       </c>
-      <c r="B15" t="str">
-        <v>56 - Lalkuan</v>
+      <c r="B15" t="s">
+        <v>34</v>
       </c>
       <c r="C15">
         <v>42703</v>
@@ -1185,12 +1505,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13</v>
       </c>
-      <c r="B16" t="str">
-        <v>57 - Bhimtal</v>
+      <c r="B16" t="s">
+        <v>35</v>
       </c>
       <c r="C16">
         <v>25549</v>
@@ -1244,12 +1564,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>14</v>
       </c>
-      <c r="B17" t="str">
-        <v>58 - Nainital</v>
+      <c r="B17" t="s">
+        <v>36</v>
       </c>
       <c r="C17">
         <v>27707</v>
@@ -1303,12 +1623,12 @@
         <v>105</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>15</v>
       </c>
-      <c r="B18" t="str">
-        <v>59 - Haldwani</v>
+      <c r="B18" t="s">
+        <v>37</v>
       </c>
       <c r="C18">
         <v>47836</v>
@@ -1362,12 +1682,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>16</v>
       </c>
-      <c r="B19" t="str">
-        <v>60 - Kaladhungi</v>
+      <c r="B19" t="s">
+        <v>38</v>
       </c>
       <c r="C19">
         <v>56490</v>
@@ -1421,12 +1741,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>17</v>
       </c>
-      <c r="B20" t="str">
-        <v>61 - Ramnagar</v>
+      <c r="B20" t="s">
+        <v>39</v>
       </c>
       <c r="C20">
         <v>35022</v>
@@ -1480,12 +1800,12 @@
         <v>71</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>18</v>
       </c>
-      <c r="B21" t="str">
-        <v>48 - Dwarahat</v>
+      <c r="B21" t="s">
+        <v>40</v>
       </c>
       <c r="C21">
         <v>16962</v>
@@ -1539,12 +1859,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>19</v>
       </c>
-      <c r="B22" t="str">
-        <v>49 - Salt</v>
+      <c r="B22" t="s">
+        <v>41</v>
       </c>
       <c r="C22">
         <v>18668</v>
@@ -1598,12 +1918,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>20</v>
       </c>
-      <c r="B23" t="str">
-        <v>50 - Ranikhet</v>
+      <c r="B23" t="s">
+        <v>42</v>
       </c>
       <c r="C23">
         <v>12020</v>
@@ -1657,12 +1977,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>21</v>
       </c>
-      <c r="B24" t="str">
-        <v>51 - Someshwar</v>
+      <c r="B24" t="s">
+        <v>43</v>
       </c>
       <c r="C24">
         <v>14056</v>
@@ -1716,12 +2036,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>22</v>
       </c>
-      <c r="B25" t="str">
-        <v>52 - Almora</v>
+      <c r="B25" t="s">
+        <v>44</v>
       </c>
       <c r="C25">
         <v>19266</v>
@@ -1775,12 +2095,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23</v>
       </c>
-      <c r="B26" t="str">
-        <v>53 - Jageshwar</v>
+      <c r="B26" t="s">
+        <v>45</v>
       </c>
       <c r="C26">
         <v>17557</v>
@@ -1834,12 +2154,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>24</v>
       </c>
-      <c r="B27" t="str">
-        <v>62 - Jaspur</v>
+      <c r="B27" t="s">
+        <v>46</v>
       </c>
       <c r="C27">
         <v>44276</v>
@@ -1893,12 +2213,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25</v>
       </c>
-      <c r="B28" t="str">
-        <v>63 - Kashipur</v>
+      <c r="B28" t="s">
+        <v>47</v>
       </c>
       <c r="C28">
         <v>54349</v>
@@ -1952,12 +2272,12 @@
         <v>127</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26</v>
       </c>
-      <c r="B29" t="str">
-        <v>64 - Bajpur</v>
+      <c r="B29" t="s">
+        <v>48</v>
       </c>
       <c r="C29">
         <v>47111</v>
@@ -2011,12 +2331,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>27</v>
       </c>
-      <c r="B30" t="str">
-        <v>65 - Gadarpur</v>
+      <c r="B30" t="s">
+        <v>49</v>
       </c>
       <c r="C30">
         <v>52653</v>
@@ -2070,12 +2390,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>28</v>
       </c>
-      <c r="B31" t="str">
-        <v>66 - Rudrapur</v>
+      <c r="B31" t="s">
+        <v>50</v>
       </c>
       <c r="C31">
         <v>91162</v>
@@ -2129,12 +2449,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>29</v>
       </c>
-      <c r="B32" t="str">
-        <v>67 - Kichha</v>
+      <c r="B32" t="s">
+        <v>51</v>
       </c>
       <c r="C32">
         <v>46728</v>
@@ -2188,12 +2508,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>30</v>
       </c>
-      <c r="B33" t="str">
-        <v>68 - Sitarganj</v>
+      <c r="B33" t="s">
+        <v>52</v>
       </c>
       <c r="C33">
         <v>40230</v>
@@ -2247,12 +2567,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>31</v>
       </c>
-      <c r="B34" t="str">
-        <v>69 - Nanakmatta</v>
+      <c r="B34" t="s">
+        <v>53</v>
       </c>
       <c r="C34">
         <v>36542</v>
@@ -2306,12 +2626,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32</v>
       </c>
-      <c r="B35" t="str">
-        <v>70 - Khatima</v>
+      <c r="B35" t="s">
+        <v>54</v>
       </c>
       <c r="C35">
         <v>33564</v>
@@ -2365,12 +2685,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>33</v>
       </c>
-      <c r="B36" t="str">
-        <v>42 - Dharchula</v>
+      <c r="B36" t="s">
+        <v>55</v>
       </c>
       <c r="C36">
         <v>20905</v>
@@ -2424,12 +2744,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>34</v>
       </c>
-      <c r="B37" t="str">
-        <v>43 - Didihat</v>
+      <c r="B37" t="s">
+        <v>56</v>
       </c>
       <c r="C37">
         <v>17692</v>
@@ -2483,12 +2803,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>35</v>
       </c>
-      <c r="B38" t="str">
-        <v>44 - Pithoragarh</v>
+      <c r="B38" t="s">
+        <v>57</v>
       </c>
       <c r="C38">
         <v>29110</v>
@@ -2542,12 +2862,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>36</v>
       </c>
-      <c r="B39" t="str">
-        <v>45 - Gangolihat</v>
+      <c r="B39" t="s">
+        <v>58</v>
       </c>
       <c r="C39">
         <v>21367</v>
@@ -2601,12 +2921,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>37</v>
       </c>
-      <c r="B40" t="str">
-        <v>46 - Kapkot</v>
+      <c r="B40" t="s">
+        <v>59</v>
       </c>
       <c r="C40">
         <v>18905</v>
@@ -2660,12 +2980,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>38</v>
       </c>
-      <c r="B41" t="str">
-        <v>47 - Bageshwar</v>
+      <c r="B41" t="s">
+        <v>60</v>
       </c>
       <c r="C41">
         <v>23521</v>
@@ -2719,12 +3039,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>39</v>
       </c>
-      <c r="B42" t="str">
-        <v>54 - Lohaghat</v>
+      <c r="B42" t="s">
+        <v>61</v>
       </c>
       <c r="C42">
         <v>27565</v>
@@ -2778,12 +3098,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>40</v>
       </c>
-      <c r="B43" t="str">
-        <v>55 - Champawat</v>
+      <c r="B43" t="s">
+        <v>62</v>
       </c>
       <c r="C43">
         <v>29700</v>
@@ -2837,12 +3157,12 @@
         <v>121</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>41</v>
       </c>
-      <c r="B44" t="str">
-        <v>4 - Badrinath</v>
+      <c r="B44" t="s">
+        <v>63</v>
       </c>
       <c r="C44">
         <v>21900</v>
@@ -2896,12 +3216,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>42</v>
       </c>
-      <c r="B45" t="str">
-        <v>5 - Tharali</v>
+      <c r="B45" t="s">
+        <v>64</v>
       </c>
       <c r="C45">
         <v>19935</v>
@@ -2955,12 +3275,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>43</v>
       </c>
-      <c r="B46" t="str">
-        <v>6 - Karanprayag</v>
+      <c r="B46" t="s">
+        <v>65</v>
       </c>
       <c r="C46">
         <v>21512</v>
@@ -3014,12 +3334,12 @@
         <v>152</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>44</v>
       </c>
-      <c r="B47" t="str">
-        <v>1 - Purola</v>
+      <c r="B47" t="s">
+        <v>66</v>
       </c>
       <c r="C47">
         <v>22426</v>
@@ -3073,12 +3393,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>45</v>
       </c>
-      <c r="B48" t="str">
-        <v>2 - Yamunotri</v>
+      <c r="B48" t="s">
+        <v>67</v>
       </c>
       <c r="C48">
         <v>19641</v>
@@ -3132,12 +3452,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>46</v>
       </c>
-      <c r="B49" t="str">
-        <v>3 - Gangotri</v>
+      <c r="B49" t="s">
+        <v>68</v>
       </c>
       <c r="C49">
         <v>21651</v>
@@ -3191,12 +3511,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>47</v>
       </c>
-      <c r="B50" t="str">
-        <v>7 - Kedarnath</v>
+      <c r="B50" t="s">
+        <v>69</v>
       </c>
       <c r="C50">
         <v>21936</v>
@@ -3250,12 +3570,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>48</v>
       </c>
-      <c r="B51" t="str">
-        <v>8 - Rudraprayag</v>
+      <c r="B51" t="s">
+        <v>70</v>
       </c>
       <c r="C51">
         <v>23798</v>
@@ -3309,12 +3629,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>49</v>
       </c>
-      <c r="B52" t="str">
-        <v>9 - Ghansali</v>
+      <c r="B52" t="s">
+        <v>71</v>
       </c>
       <c r="C52">
         <v>21094</v>
@@ -3368,12 +3688,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>50</v>
       </c>
-      <c r="B53" t="str">
-        <v>10 - Devprayag</v>
+      <c r="B53" t="s">
+        <v>72</v>
       </c>
       <c r="C53">
         <v>19131</v>
@@ -3427,12 +3747,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>51</v>
       </c>
-      <c r="B54" t="str">
-        <v>11 - Narendranagar</v>
+      <c r="B54" t="s">
+        <v>73</v>
       </c>
       <c r="C54">
         <v>20758</v>
@@ -3486,12 +3806,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>52</v>
       </c>
-      <c r="B55" t="str">
-        <v>12 - Pratapnagar</v>
+      <c r="B55" t="s">
+        <v>74</v>
       </c>
       <c r="C55">
         <v>16022</v>
@@ -3545,12 +3865,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>53</v>
       </c>
-      <c r="B56" t="str">
-        <v>13 - Tehri</v>
+      <c r="B56" t="s">
+        <v>75</v>
       </c>
       <c r="C56">
         <v>19256</v>
@@ -3604,12 +3924,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>54</v>
       </c>
-      <c r="B57" t="str">
-        <v>14 - Dhanolti</v>
+      <c r="B57" t="s">
+        <v>76</v>
       </c>
       <c r="C57">
         <v>21240</v>
@@ -3663,12 +3983,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>55</v>
       </c>
-      <c r="B58" t="str">
-        <v>36 - Yamkeshwar</v>
+      <c r="B58" t="s">
+        <v>77</v>
       </c>
       <c r="C58">
         <v>22819</v>
@@ -3722,12 +4042,12 @@
         <v>64</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>56</v>
       </c>
-      <c r="B59" t="str">
-        <v>37 - Pauri</v>
+      <c r="B59" t="s">
+        <v>78</v>
       </c>
       <c r="C59">
         <v>18776</v>
@@ -3781,12 +4101,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>57</v>
       </c>
-      <c r="B60" t="str">
-        <v>38 - Srinagar</v>
+      <c r="B60" t="s">
+        <v>79</v>
       </c>
       <c r="C60">
         <v>23749</v>
@@ -3840,12 +4160,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>58</v>
       </c>
-      <c r="B61" t="str">
-        <v>39 - Chaubattakhal</v>
+      <c r="B61" t="s">
+        <v>80</v>
       </c>
       <c r="C61">
         <v>22069</v>
@@ -3899,12 +4219,12 @@
         <v>268</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>59</v>
       </c>
-      <c r="B62" t="str">
-        <v>40 - Lansdowne</v>
+      <c r="B62" t="s">
+        <v>81</v>
       </c>
       <c r="C62">
         <v>15800</v>
@@ -3958,12 +4278,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>60</v>
       </c>
-      <c r="B63" t="str">
-        <v>41 - Kotdwar</v>
+      <c r="B63" t="s">
+        <v>82</v>
       </c>
       <c r="C63">
         <v>36754</v>
@@ -4017,12 +4337,12 @@
         <v>153</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>61</v>
       </c>
-      <c r="B64" t="str">
-        <v>15 - Chakrata</v>
+      <c r="B64" t="s">
+        <v>83</v>
       </c>
       <c r="C64">
         <v>42048</v>
@@ -4076,12 +4396,12 @@
         <v>101</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>62</v>
       </c>
-      <c r="B65" t="str">
-        <v>16 - Vikasnagar</v>
+      <c r="B65" t="s">
+        <v>84</v>
       </c>
       <c r="C65">
         <v>41389</v>
@@ -4135,12 +4455,12 @@
         <v>138</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>63</v>
       </c>
-      <c r="B66" t="str">
-        <v>17 - Sahaspur</v>
+      <c r="B66" t="s">
+        <v>85</v>
       </c>
       <c r="C66">
         <v>67362</v>
@@ -4194,12 +4514,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>64</v>
       </c>
-      <c r="B67" t="str">
-        <v>18 - Dharmpur</v>
+      <c r="B67" t="s">
+        <v>86</v>
       </c>
       <c r="C67">
         <v>68828</v>
@@ -4253,12 +4573,12 @@
         <v>116</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>65</v>
       </c>
-      <c r="B68" t="str">
-        <v>19 - Raipur</v>
+      <c r="B68" t="s">
+        <v>87</v>
       </c>
       <c r="C68">
         <v>65397</v>
@@ -4312,12 +4632,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>66</v>
       </c>
-      <c r="B69" t="str">
-        <v>20 - Rajpur Road</v>
+      <c r="B69" t="s">
+        <v>88</v>
       </c>
       <c r="C69">
         <v>43938</v>
@@ -4371,12 +4691,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>67</v>
       </c>
-      <c r="B70" t="str">
-        <v>21 - Dehradun Cantonment</v>
+      <c r="B70" t="s">
+        <v>89</v>
       </c>
       <c r="C70">
         <v>47711</v>
@@ -4430,12 +4750,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>68</v>
       </c>
-      <c r="B71" t="str">
-        <v>22 - Mussoorie</v>
+      <c r="B71" t="s">
+        <v>90</v>
       </c>
       <c r="C71">
         <v>50963</v>
@@ -4489,12 +4809,12 @@
         <v>235</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>69</v>
       </c>
-      <c r="B72" t="str">
-        <v>23 - Doiwala</v>
+      <c r="B72" t="s">
+        <v>91</v>
       </c>
       <c r="C72">
         <v>61543</v>
@@ -4548,12 +4868,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>70</v>
       </c>
-      <c r="B73" t="str">
-        <v>24 - Rishikesh</v>
+      <c r="B73" t="s">
+        <v>92</v>
       </c>
       <c r="C73">
         <v>58915</v>
@@ -4607,10 +4927,11 @@
         <v>74</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="str">
-        <v>Total</v>
-      </c>
+    <row r="74" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B74" s="1"/>
       <c r="C74">
         <v>2430387</v>
       </c>
@@ -4665,6 +4986,7 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A74:B74"/>
     <mergeCell ref="A1:T1"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
@@ -4676,10 +4998,10 @@
     <mergeCell ref="J2:M2"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="A74:B74"/>
   </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S74"/>
+    <ignoredError sqref="A2:S74 B1:S1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\New folder (13)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{094E2CA3-4A53-4547-BEA6-F01FBA742248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAE1EF5A-9D21-42DB-808B-9C3A78051400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -304,7 +304,7 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Notice &amp; Hearing Report Last Updated On : 02-09-2026 13:59:59</t>
+    <t>Notice &amp; Hearing Report Last Updated On : 02-09-2026 16:00:02</t>
   </si>
 </sst>
 </file>
@@ -817,31 +817,31 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>48568</v>
+        <v>49144</v>
       </c>
       <c r="H4">
-        <v>2956</v>
+        <v>2380</v>
       </c>
       <c r="I4">
         <v>4</v>
       </c>
       <c r="J4">
-        <v>4744</v>
+        <v>5096</v>
       </c>
       <c r="K4">
-        <v>472</v>
+        <v>447</v>
       </c>
       <c r="L4">
-        <v>11099</v>
+        <v>11186</v>
       </c>
       <c r="M4">
-        <v>255</v>
+        <v>391</v>
       </c>
       <c r="N4">
-        <v>220</v>
+        <v>291</v>
       </c>
       <c r="O4">
-        <v>42145</v>
+        <v>42356</v>
       </c>
       <c r="P4">
         <v>53812</v>
@@ -876,31 +876,31 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>52682</v>
+        <v>52954</v>
       </c>
       <c r="H5">
-        <v>1097</v>
+        <v>894</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>3009</v>
+        <v>3098</v>
       </c>
       <c r="K5">
-        <v>1076</v>
+        <v>1008</v>
       </c>
       <c r="L5">
-        <v>7833</v>
+        <v>7954</v>
       </c>
       <c r="M5">
-        <v>204</v>
+        <v>262</v>
       </c>
       <c r="N5">
         <v>590</v>
       </c>
       <c r="O5">
-        <v>48302</v>
+        <v>48649</v>
       </c>
       <c r="P5">
         <v>74848</v>
@@ -935,34 +935,34 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>37664</v>
+        <v>37732</v>
       </c>
       <c r="H6">
-        <v>1946</v>
+        <v>1879</v>
       </c>
       <c r="I6">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J6">
-        <v>2526</v>
+        <v>2444</v>
       </c>
       <c r="K6">
         <v>1223</v>
       </c>
       <c r="L6">
-        <v>3293</v>
+        <v>3391</v>
       </c>
       <c r="M6">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N6">
-        <v>1178</v>
+        <v>1181</v>
       </c>
       <c r="O6">
-        <v>31336</v>
+        <v>31391</v>
       </c>
       <c r="P6">
-        <v>70908</v>
+        <v>71361</v>
       </c>
       <c r="Q6">
         <v>17830</v>
@@ -994,31 +994,31 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>39263</v>
+        <v>39352</v>
       </c>
       <c r="H7">
-        <v>200</v>
+        <v>111</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7">
-        <v>2165</v>
+        <v>1812</v>
       </c>
       <c r="K7">
-        <v>2027</v>
+        <v>1688</v>
       </c>
       <c r="L7">
-        <v>3573</v>
+        <v>3899</v>
       </c>
       <c r="M7">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="N7">
-        <v>1834</v>
+        <v>1909</v>
       </c>
       <c r="O7">
-        <v>33747</v>
+        <v>33854</v>
       </c>
       <c r="P7">
         <v>77581</v>
@@ -1053,16 +1053,16 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>39028</v>
+        <v>39179</v>
       </c>
       <c r="H8">
-        <v>1524</v>
+        <v>1373</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>148</v>
+        <v>174</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -1074,10 +1074,10 @@
         <v>158</v>
       </c>
       <c r="N8">
-        <v>1255</v>
+        <v>1357</v>
       </c>
       <c r="O8">
-        <v>30186</v>
+        <v>30465</v>
       </c>
       <c r="P8">
         <v>73458</v>
@@ -1112,22 +1112,22 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>43224</v>
+        <v>43234</v>
       </c>
       <c r="H9">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="I9">
         <v>1</v>
       </c>
       <c r="J9">
-        <v>1333</v>
+        <v>1266</v>
       </c>
       <c r="K9">
-        <v>987</v>
+        <v>893</v>
       </c>
       <c r="L9">
-        <v>5878</v>
+        <v>5967</v>
       </c>
       <c r="M9">
         <v>35</v>
@@ -1136,7 +1136,7 @@
         <v>1236</v>
       </c>
       <c r="O9">
-        <v>39208</v>
+        <v>39380</v>
       </c>
       <c r="P9">
         <v>72762</v>
@@ -1171,31 +1171,31 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>36552</v>
+        <v>36569</v>
       </c>
       <c r="H10">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10">
-        <v>1760</v>
+        <v>1675</v>
       </c>
       <c r="K10">
-        <v>1422</v>
+        <v>1338</v>
       </c>
       <c r="L10">
-        <v>9273</v>
+        <v>9348</v>
       </c>
       <c r="M10">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="N10">
-        <v>749</v>
+        <v>764</v>
       </c>
       <c r="O10">
-        <v>33861</v>
+        <v>33862</v>
       </c>
       <c r="P10">
         <v>53124</v>
@@ -1239,22 +1239,22 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>612</v>
+        <v>426</v>
       </c>
       <c r="K11">
-        <v>133</v>
+        <v>71</v>
       </c>
       <c r="L11">
-        <v>9281</v>
+        <v>9462</v>
       </c>
       <c r="M11">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="N11">
-        <v>1514</v>
+        <v>1549</v>
       </c>
       <c r="O11">
-        <v>48528</v>
+        <v>48536</v>
       </c>
       <c r="P11">
         <v>84438</v>
@@ -1289,31 +1289,31 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>40416</v>
+        <v>40466</v>
       </c>
       <c r="H12">
-        <v>323</v>
+        <v>273</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12">
-        <v>2430</v>
+        <v>2151</v>
       </c>
       <c r="K12">
-        <v>2150</v>
+        <v>1986</v>
       </c>
       <c r="L12">
-        <v>7366</v>
+        <v>7663</v>
       </c>
       <c r="M12">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="N12">
         <v>1020</v>
       </c>
       <c r="O12">
-        <v>32806</v>
+        <v>32829</v>
       </c>
       <c r="P12">
         <v>66685</v>
@@ -1357,22 +1357,22 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>832</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>510</v>
+        <v>0</v>
       </c>
       <c r="L13">
-        <v>7005</v>
+        <v>7785</v>
       </c>
       <c r="M13">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="N13">
         <v>3818</v>
       </c>
       <c r="O13">
-        <v>30741</v>
+        <v>31436</v>
       </c>
       <c r="P13">
         <v>56565</v>
@@ -1407,34 +1407,34 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>45733</v>
+        <v>45844</v>
       </c>
       <c r="H14">
-        <v>3187</v>
+        <v>3076</v>
       </c>
       <c r="I14">
         <v>27</v>
       </c>
       <c r="J14">
-        <v>8490</v>
+        <v>8377</v>
       </c>
       <c r="K14">
-        <v>4793</v>
+        <v>4792</v>
       </c>
       <c r="L14">
-        <v>6703</v>
+        <v>6759</v>
       </c>
       <c r="M14">
-        <v>496</v>
+        <v>602</v>
       </c>
       <c r="N14">
-        <v>3594</v>
+        <v>3642</v>
       </c>
       <c r="O14">
-        <v>28309</v>
+        <v>28319</v>
       </c>
       <c r="P14">
-        <v>72777</v>
+        <v>73412</v>
       </c>
       <c r="Q14">
         <v>19716</v>
@@ -1726,7 +1726,7 @@
         <v>910</v>
       </c>
       <c r="O19">
-        <v>55229</v>
+        <v>55234</v>
       </c>
       <c r="P19">
         <v>106227</v>
@@ -2174,31 +2174,31 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>41836</v>
+        <v>42115</v>
       </c>
       <c r="H27">
-        <v>2440</v>
+        <v>2161</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27">
-        <v>95</v>
+        <v>185</v>
       </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="L27">
-        <v>9263</v>
+        <v>9278</v>
       </c>
       <c r="M27">
         <v>26</v>
       </c>
       <c r="N27">
-        <v>783</v>
+        <v>914</v>
       </c>
       <c r="O27">
-        <v>39519</v>
+        <v>39568</v>
       </c>
       <c r="P27">
         <v>63060</v>
@@ -2233,31 +2233,31 @@
         <v>0</v>
       </c>
       <c r="G28">
-        <v>52088</v>
+        <v>52463</v>
       </c>
       <c r="H28">
-        <v>2261</v>
+        <v>1886</v>
       </c>
       <c r="I28">
         <v>0</v>
       </c>
       <c r="J28">
-        <v>749</v>
+        <v>568</v>
       </c>
       <c r="K28">
         <v>0</v>
       </c>
       <c r="L28">
-        <v>7567</v>
+        <v>7841</v>
       </c>
       <c r="M28">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="N28">
-        <v>1903</v>
+        <v>1974</v>
       </c>
       <c r="O28">
-        <v>48063</v>
+        <v>48517</v>
       </c>
       <c r="P28">
         <v>80623</v>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="J29">
-        <v>398</v>
+        <v>314</v>
       </c>
       <c r="K29">
         <v>0</v>
       </c>
       <c r="L29">
-        <v>8485</v>
+        <v>8584</v>
       </c>
       <c r="M29">
         <v>37</v>
@@ -2351,31 +2351,31 @@
         <v>0</v>
       </c>
       <c r="G30">
-        <v>50778</v>
+        <v>51190</v>
       </c>
       <c r="H30">
-        <v>273</v>
+        <v>108</v>
       </c>
       <c r="I30">
-        <v>1602</v>
+        <v>1355</v>
       </c>
       <c r="J30">
-        <v>632</v>
+        <v>523</v>
       </c>
       <c r="K30">
         <v>0</v>
       </c>
       <c r="L30">
-        <v>9488</v>
+        <v>9978</v>
       </c>
       <c r="M30">
         <v>246</v>
       </c>
       <c r="N30">
-        <v>5017</v>
+        <v>5075</v>
       </c>
       <c r="O30">
-        <v>44651</v>
+        <v>45075</v>
       </c>
       <c r="P30">
         <v>86933</v>
@@ -2419,13 +2419,13 @@
         <v>0</v>
       </c>
       <c r="J31">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K31">
         <v>0</v>
       </c>
       <c r="L31">
-        <v>46599</v>
+        <v>46603</v>
       </c>
       <c r="M31">
         <v>42</v>
@@ -2434,7 +2434,7 @@
         <v>1892</v>
       </c>
       <c r="O31">
-        <v>87899</v>
+        <v>89154</v>
       </c>
       <c r="P31">
         <v>81642</v>
@@ -2469,31 +2469,31 @@
         <v>0</v>
       </c>
       <c r="G32">
-        <v>43505</v>
+        <v>43783</v>
       </c>
       <c r="H32">
-        <v>2983</v>
+        <v>2708</v>
       </c>
       <c r="I32">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="J32">
-        <v>758</v>
+        <v>505</v>
       </c>
       <c r="K32">
         <v>0</v>
       </c>
       <c r="L32">
-        <v>9572</v>
+        <v>9868</v>
       </c>
       <c r="M32">
         <v>157</v>
       </c>
       <c r="N32">
-        <v>2795</v>
+        <v>2987</v>
       </c>
       <c r="O32">
-        <v>38916</v>
+        <v>39214</v>
       </c>
       <c r="P32">
         <v>74812</v>
@@ -2528,34 +2528,34 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <v>38643</v>
+        <v>38889</v>
       </c>
       <c r="H33">
-        <v>1571</v>
+        <v>1327</v>
       </c>
       <c r="I33">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J33">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="K33">
         <v>0</v>
       </c>
       <c r="L33">
-        <v>4629</v>
+        <v>4705</v>
       </c>
       <c r="M33">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="N33">
-        <v>468</v>
+        <v>499</v>
       </c>
       <c r="O33">
-        <v>36245</v>
+        <v>36392</v>
       </c>
       <c r="P33">
-        <v>76489</v>
+        <v>76918</v>
       </c>
       <c r="Q33">
         <v>6678</v>
@@ -2587,31 +2587,31 @@
         <v>0</v>
       </c>
       <c r="G34">
-        <v>34989</v>
+        <v>35143</v>
       </c>
       <c r="H34">
-        <v>1553</v>
+        <v>1399</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
       <c r="J34">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="K34">
         <v>0</v>
       </c>
       <c r="L34">
-        <v>11329</v>
+        <v>11373</v>
       </c>
       <c r="M34">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N34">
-        <v>766</v>
+        <v>856</v>
       </c>
       <c r="O34">
-        <v>32637</v>
+        <v>32704</v>
       </c>
       <c r="P34">
         <v>74624</v>
@@ -2646,31 +2646,31 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>31813</v>
+        <v>31819</v>
       </c>
       <c r="H35">
-        <v>1751</v>
+        <v>1745</v>
       </c>
       <c r="I35">
         <v>0</v>
       </c>
       <c r="J35">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="K35">
         <v>0</v>
       </c>
       <c r="L35">
-        <v>6574</v>
+        <v>6601</v>
       </c>
       <c r="M35">
         <v>8</v>
       </c>
       <c r="N35">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="O35">
-        <v>29942</v>
+        <v>30067</v>
       </c>
       <c r="P35">
         <v>76465</v>
@@ -2832,7 +2832,7 @@
         <v>0</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38">
         <v>0</v>
@@ -2844,7 +2844,7 @@
         <v>2</v>
       </c>
       <c r="N38">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="O38">
         <v>28463</v>
@@ -3236,31 +3236,31 @@
         <v>0</v>
       </c>
       <c r="G45">
-        <v>19900</v>
+        <v>19906</v>
       </c>
       <c r="H45">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I45">
         <v>0</v>
       </c>
       <c r="J45">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K45">
         <v>0</v>
       </c>
       <c r="L45">
-        <v>2234</v>
+        <v>2235</v>
       </c>
       <c r="M45">
         <v>13</v>
       </c>
       <c r="N45">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="O45">
-        <v>19217</v>
+        <v>19325</v>
       </c>
       <c r="P45">
         <v>76002</v>
@@ -3319,7 +3319,7 @@
         <v>276</v>
       </c>
       <c r="O46">
-        <v>20934</v>
+        <v>20981</v>
       </c>
       <c r="P46">
         <v>64160</v>
@@ -3363,13 +3363,13 @@
         <v>0</v>
       </c>
       <c r="J47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47">
         <v>0</v>
       </c>
       <c r="L47">
-        <v>2594</v>
+        <v>2595</v>
       </c>
       <c r="M47">
         <v>1</v>
@@ -3413,10 +3413,10 @@
         <v>24</v>
       </c>
       <c r="G48">
-        <v>19594</v>
+        <v>19600</v>
       </c>
       <c r="H48">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="I48">
         <v>1</v>
@@ -3428,7 +3428,7 @@
         <v>0</v>
       </c>
       <c r="L48">
-        <v>3773</v>
+        <v>3776</v>
       </c>
       <c r="M48">
         <v>4</v>
@@ -3437,7 +3437,7 @@
         <v>247</v>
       </c>
       <c r="O48">
-        <v>19330</v>
+        <v>19333</v>
       </c>
       <c r="P48">
         <v>54142</v>
@@ -3466,28 +3466,28 @@
         <v>0</v>
       </c>
       <c r="E49">
-        <v>21650</v>
+        <v>21651</v>
       </c>
       <c r="F49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G49">
-        <v>21244</v>
+        <v>21340</v>
       </c>
       <c r="H49">
-        <v>181</v>
+        <v>85</v>
       </c>
       <c r="I49">
         <v>226</v>
       </c>
       <c r="J49">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K49">
         <v>0</v>
       </c>
       <c r="L49">
-        <v>3594</v>
+        <v>3599</v>
       </c>
       <c r="M49">
         <v>0</v>
@@ -3496,7 +3496,7 @@
         <v>362</v>
       </c>
       <c r="O49">
-        <v>20011</v>
+        <v>20106</v>
       </c>
       <c r="P49">
         <v>55376</v>
@@ -3599,13 +3599,13 @@
         <v>0</v>
       </c>
       <c r="J51">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K51">
         <v>0</v>
       </c>
       <c r="L51">
-        <v>4827</v>
+        <v>4833</v>
       </c>
       <c r="M51">
         <v>11</v>
@@ -3614,7 +3614,7 @@
         <v>75</v>
       </c>
       <c r="O51">
-        <v>23707</v>
+        <v>23713</v>
       </c>
       <c r="P51">
         <v>71754</v>
@@ -3776,13 +3776,13 @@
         <v>0</v>
       </c>
       <c r="J54">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="K54">
         <v>0</v>
       </c>
       <c r="L54">
-        <v>2531</v>
+        <v>2552</v>
       </c>
       <c r="M54">
         <v>5</v>
@@ -3791,7 +3791,7 @@
         <v>390</v>
       </c>
       <c r="O54">
-        <v>20291</v>
+        <v>20311</v>
       </c>
       <c r="P54">
         <v>58440</v>
@@ -3894,7 +3894,7 @@
         <v>0</v>
       </c>
       <c r="J56">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="K56">
         <v>0</v>
@@ -3906,10 +3906,10 @@
         <v>2</v>
       </c>
       <c r="N56">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="O56">
-        <v>18563</v>
+        <v>18561</v>
       </c>
       <c r="P56">
         <v>46365</v>
@@ -4027,7 +4027,7 @@
         <v>552</v>
       </c>
       <c r="O58">
-        <v>20506</v>
+        <v>21219</v>
       </c>
       <c r="P58">
         <v>57577</v>
@@ -4071,7 +4071,7 @@
         <v>0</v>
       </c>
       <c r="J59">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K59">
         <v>0</v>
@@ -4086,7 +4086,7 @@
         <v>283</v>
       </c>
       <c r="O59">
-        <v>18442</v>
+        <v>18463</v>
       </c>
       <c r="P59">
         <v>60495</v>
@@ -4189,7 +4189,7 @@
         <v>0</v>
       </c>
       <c r="J61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K61">
         <v>0</v>
@@ -4319,10 +4319,10 @@
         <v>68</v>
       </c>
       <c r="N63">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="O63">
-        <v>35821</v>
+        <v>35819</v>
       </c>
       <c r="P63">
         <v>68691</v>
@@ -4366,7 +4366,7 @@
         <v>0</v>
       </c>
       <c r="J64">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="K64">
         <v>0</v>
@@ -4378,7 +4378,7 @@
         <v>8</v>
       </c>
       <c r="N64">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="O64">
         <v>41279</v>
@@ -4416,16 +4416,16 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>40317</v>
+        <v>40356</v>
       </c>
       <c r="H65">
-        <v>748</v>
+        <v>712</v>
       </c>
       <c r="I65">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="J65">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="K65">
         <v>0</v>
@@ -4437,10 +4437,10 @@
         <v>2</v>
       </c>
       <c r="N65">
-        <v>1928</v>
+        <v>1947</v>
       </c>
       <c r="O65">
-        <v>32001</v>
+        <v>32019</v>
       </c>
       <c r="P65">
         <v>58103</v>
@@ -4475,31 +4475,31 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>66243</v>
+        <v>66425</v>
       </c>
       <c r="H66">
-        <v>1119</v>
+        <v>937</v>
       </c>
       <c r="I66">
         <v>0</v>
       </c>
       <c r="J66">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="K66">
         <v>0</v>
       </c>
       <c r="L66">
-        <v>13554</v>
+        <v>13578</v>
       </c>
       <c r="M66">
         <v>2</v>
       </c>
       <c r="N66">
-        <v>3353</v>
+        <v>3419</v>
       </c>
       <c r="O66">
-        <v>62553</v>
+        <v>62698</v>
       </c>
       <c r="P66">
         <v>93810</v>
@@ -4534,31 +4534,31 @@
         <v>0</v>
       </c>
       <c r="G67">
-        <v>68768</v>
+        <v>68777</v>
       </c>
       <c r="H67">
         <v>0</v>
       </c>
       <c r="I67">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J67">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K67">
         <v>0</v>
       </c>
       <c r="L67">
-        <v>19406</v>
+        <v>19408</v>
       </c>
       <c r="M67">
         <v>10</v>
       </c>
       <c r="N67">
-        <v>3566</v>
+        <v>3597</v>
       </c>
       <c r="O67">
-        <v>64930</v>
+        <v>65007</v>
       </c>
       <c r="P67">
         <v>78022</v>
@@ -4593,34 +4593,34 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>62886</v>
+        <v>63036</v>
       </c>
       <c r="H68">
-        <v>1684</v>
+        <v>1576</v>
       </c>
       <c r="I68">
-        <v>711</v>
+        <v>672</v>
       </c>
       <c r="J68">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="K68">
         <v>0</v>
       </c>
       <c r="L68">
-        <v>16923</v>
+        <v>17059</v>
       </c>
       <c r="M68">
         <v>2</v>
       </c>
       <c r="N68">
-        <v>832</v>
+        <v>858</v>
       </c>
       <c r="O68">
-        <v>54372</v>
+        <v>54716</v>
       </c>
       <c r="P68">
-        <v>70054</v>
+        <v>70187</v>
       </c>
       <c r="Q68">
         <v>7850</v>
@@ -4652,31 +4652,31 @@
         <v>0</v>
       </c>
       <c r="G69">
-        <v>42232</v>
+        <v>42333</v>
       </c>
       <c r="H69">
-        <v>1679</v>
+        <v>1585</v>
       </c>
       <c r="I69">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J69">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K69">
         <v>0</v>
       </c>
       <c r="L69">
-        <v>17314</v>
+        <v>17405</v>
       </c>
       <c r="M69">
         <v>2</v>
       </c>
       <c r="N69">
-        <v>1818</v>
+        <v>1844</v>
       </c>
       <c r="O69">
-        <v>37698</v>
+        <v>38174</v>
       </c>
       <c r="P69">
         <v>36117</v>
@@ -4711,13 +4711,13 @@
         <v>0</v>
       </c>
       <c r="G70">
-        <v>47650</v>
+        <v>47652</v>
       </c>
       <c r="H70">
         <v>55</v>
       </c>
       <c r="I70">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J70">
         <v>0</v>
@@ -4732,10 +4732,10 @@
         <v>2</v>
       </c>
       <c r="N70">
-        <v>3196</v>
+        <v>3198</v>
       </c>
       <c r="O70">
-        <v>44425</v>
+        <v>44427</v>
       </c>
       <c r="P70">
         <v>42039</v>
@@ -4829,31 +4829,31 @@
         <v>0</v>
       </c>
       <c r="G72">
-        <v>61362</v>
+        <v>61384</v>
       </c>
       <c r="H72">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="I72">
         <v>61</v>
       </c>
       <c r="J72">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K72">
         <v>0</v>
       </c>
       <c r="L72">
-        <v>17067</v>
+        <v>17082</v>
       </c>
       <c r="M72">
         <v>9</v>
       </c>
       <c r="N72">
-        <v>3580</v>
+        <v>3594</v>
       </c>
       <c r="O72">
-        <v>53245</v>
+        <v>54052</v>
       </c>
       <c r="P72">
         <v>85505</v>
@@ -4888,31 +4888,31 @@
         <v>0</v>
       </c>
       <c r="G73">
-        <v>56542</v>
+        <v>56658</v>
       </c>
       <c r="H73">
-        <v>2299</v>
+        <v>2184</v>
       </c>
       <c r="I73">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J73">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="K73">
         <v>0</v>
       </c>
       <c r="L73">
-        <v>14097</v>
+        <v>14176</v>
       </c>
       <c r="M73">
         <v>7</v>
       </c>
       <c r="N73">
-        <v>2091</v>
+        <v>2143</v>
       </c>
       <c r="O73">
-        <v>49711</v>
+        <v>49758</v>
       </c>
       <c r="P73">
         <v>67550</v>
@@ -4939,40 +4939,40 @@
         <v>0</v>
       </c>
       <c r="E74">
-        <v>2430362</v>
+        <v>2430363</v>
       </c>
       <c r="F74">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G74">
-        <v>2394198</v>
+        <v>2398021</v>
       </c>
       <c r="H74">
-        <v>32203</v>
+        <v>28766</v>
       </c>
       <c r="I74">
-        <v>3706</v>
+        <v>3392</v>
       </c>
       <c r="J74">
-        <v>31611</v>
+        <v>29495</v>
       </c>
       <c r="K74">
-        <v>14799</v>
+        <v>13452</v>
       </c>
       <c r="L74">
-        <v>579451</v>
+        <v>583270</v>
       </c>
       <c r="M74">
-        <v>3131</v>
+        <v>3484</v>
       </c>
       <c r="N74">
-        <v>78156</v>
+        <v>79332</v>
       </c>
       <c r="O74">
-        <v>2211972</v>
+        <v>2219629</v>
       </c>
       <c r="P74">
-        <v>4681214</v>
+        <v>4682864</v>
       </c>
       <c r="Q74">
         <v>626533</v>

--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\New folder (13)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAE1EF5A-9D21-42DB-808B-9C3A78051400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB433B1A-BE83-4204-8CD9-401AEA14EBEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21585" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -304,7 +304,7 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Notice &amp; Hearing Report Last Updated On : 02-09-2026 16:00:02</t>
+    <t>Notice &amp; Hearing Report Last Updated On : 03-09-2026 07:59:59</t>
   </si>
 </sst>
 </file>
@@ -817,31 +817,31 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>49144</v>
+        <v>49624</v>
       </c>
       <c r="H4">
-        <v>2380</v>
+        <v>1900</v>
       </c>
       <c r="I4">
         <v>4</v>
       </c>
       <c r="J4">
-        <v>5096</v>
+        <v>3154</v>
       </c>
       <c r="K4">
-        <v>447</v>
+        <v>409</v>
       </c>
       <c r="L4">
-        <v>11186</v>
+        <v>13404</v>
       </c>
       <c r="M4">
-        <v>391</v>
+        <v>470</v>
       </c>
       <c r="N4">
-        <v>291</v>
+        <v>369</v>
       </c>
       <c r="O4">
-        <v>42356</v>
+        <v>43003</v>
       </c>
       <c r="P4">
         <v>53812</v>
@@ -876,31 +876,31 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>52954</v>
+        <v>53483</v>
       </c>
       <c r="H5">
-        <v>894</v>
+        <v>422</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>3098</v>
+        <v>2217</v>
       </c>
       <c r="K5">
-        <v>1008</v>
+        <v>794</v>
       </c>
       <c r="L5">
-        <v>7954</v>
+        <v>8987</v>
       </c>
       <c r="M5">
-        <v>262</v>
+        <v>634</v>
       </c>
       <c r="N5">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="O5">
-        <v>48649</v>
+        <v>49712</v>
       </c>
       <c r="P5">
         <v>74848</v>
@@ -935,34 +935,34 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>37732</v>
+        <v>37909</v>
       </c>
       <c r="H6">
-        <v>1879</v>
+        <v>1750</v>
       </c>
       <c r="I6">
-        <v>152</v>
+        <v>104</v>
       </c>
       <c r="J6">
-        <v>2444</v>
+        <v>2182</v>
       </c>
       <c r="K6">
-        <v>1223</v>
+        <v>1159</v>
       </c>
       <c r="L6">
-        <v>3391</v>
+        <v>3667</v>
       </c>
       <c r="M6">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="N6">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="O6">
-        <v>31391</v>
+        <v>31527</v>
       </c>
       <c r="P6">
-        <v>71361</v>
+        <v>71989</v>
       </c>
       <c r="Q6">
         <v>17830</v>
@@ -994,31 +994,31 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>39352</v>
+        <v>39422</v>
       </c>
       <c r="H7">
-        <v>111</v>
+        <v>41</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7">
-        <v>1812</v>
+        <v>988</v>
       </c>
       <c r="K7">
-        <v>1688</v>
+        <v>901</v>
       </c>
       <c r="L7">
-        <v>3899</v>
+        <v>4624</v>
       </c>
       <c r="M7">
-        <v>102</v>
+        <v>166</v>
       </c>
       <c r="N7">
-        <v>1909</v>
+        <v>1958</v>
       </c>
       <c r="O7">
-        <v>33854</v>
+        <v>33862</v>
       </c>
       <c r="P7">
         <v>77581</v>
@@ -1053,31 +1053,31 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>39179</v>
+        <v>39671</v>
       </c>
       <c r="H8">
-        <v>1373</v>
+        <v>881</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>174</v>
+        <v>52</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>13904</v>
+        <v>14027</v>
       </c>
       <c r="M8">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="N8">
-        <v>1357</v>
+        <v>1564</v>
       </c>
       <c r="O8">
-        <v>30465</v>
+        <v>32025</v>
       </c>
       <c r="P8">
         <v>73458</v>
@@ -1112,31 +1112,31 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>43234</v>
+        <v>43253</v>
       </c>
       <c r="H9">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>1266</v>
+        <v>1244</v>
       </c>
       <c r="K9">
         <v>893</v>
       </c>
       <c r="L9">
-        <v>5967</v>
+        <v>5980</v>
       </c>
       <c r="M9">
         <v>35</v>
       </c>
       <c r="N9">
-        <v>1236</v>
+        <v>1242</v>
       </c>
       <c r="O9">
-        <v>39380</v>
+        <v>39515</v>
       </c>
       <c r="P9">
         <v>72762</v>
@@ -1171,31 +1171,31 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>36569</v>
+        <v>36576</v>
       </c>
       <c r="H10">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10">
-        <v>1675</v>
+        <v>1489</v>
       </c>
       <c r="K10">
-        <v>1338</v>
+        <v>1214</v>
       </c>
       <c r="L10">
-        <v>9348</v>
+        <v>9503</v>
       </c>
       <c r="M10">
-        <v>74</v>
+        <v>111</v>
       </c>
       <c r="N10">
-        <v>764</v>
+        <v>770</v>
       </c>
       <c r="O10">
-        <v>33862</v>
+        <v>33886</v>
       </c>
       <c r="P10">
         <v>53124</v>
@@ -1239,28 +1239,28 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>426</v>
+        <v>264</v>
       </c>
       <c r="K11">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="L11">
-        <v>9462</v>
+        <v>9623</v>
       </c>
       <c r="M11">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="N11">
-        <v>1549</v>
+        <v>1567</v>
       </c>
       <c r="O11">
-        <v>48536</v>
+        <v>48962</v>
       </c>
       <c r="P11">
         <v>84438</v>
       </c>
       <c r="Q11">
-        <v>23626</v>
+        <v>23477</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -1289,37 +1289,37 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>40466</v>
+        <v>40633</v>
       </c>
       <c r="H12">
-        <v>273</v>
+        <v>106</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12">
-        <v>2151</v>
+        <v>1868</v>
       </c>
       <c r="K12">
-        <v>1986</v>
+        <v>1614</v>
       </c>
       <c r="L12">
-        <v>7663</v>
+        <v>8064</v>
       </c>
       <c r="M12">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="N12">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="O12">
-        <v>32829</v>
+        <v>33999</v>
       </c>
       <c r="P12">
         <v>66685</v>
       </c>
       <c r="Q12">
-        <v>17787</v>
+        <v>17786</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -1369,16 +1369,16 @@
         <v>258</v>
       </c>
       <c r="N13">
-        <v>3818</v>
+        <v>3821</v>
       </c>
       <c r="O13">
-        <v>31436</v>
+        <v>32954</v>
       </c>
       <c r="P13">
         <v>56565</v>
       </c>
       <c r="Q13">
-        <v>16281</v>
+        <v>16237</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -1407,34 +1407,34 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>45844</v>
+        <v>46231</v>
       </c>
       <c r="H14">
-        <v>3076</v>
+        <v>2662</v>
       </c>
       <c r="I14">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J14">
-        <v>8377</v>
+        <v>8294</v>
       </c>
       <c r="K14">
-        <v>4792</v>
+        <v>4819</v>
       </c>
       <c r="L14">
-        <v>6759</v>
+        <v>6908</v>
       </c>
       <c r="M14">
-        <v>602</v>
+        <v>693</v>
       </c>
       <c r="N14">
-        <v>3642</v>
+        <v>3795</v>
       </c>
       <c r="O14">
-        <v>28319</v>
+        <v>28338</v>
       </c>
       <c r="P14">
-        <v>73412</v>
+        <v>73452</v>
       </c>
       <c r="Q14">
         <v>19716</v>
@@ -1496,7 +1496,7 @@
         <v>67178</v>
       </c>
       <c r="Q15">
-        <v>4867</v>
+        <v>4859</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -1614,7 +1614,7 @@
         <v>65458</v>
       </c>
       <c r="Q17">
-        <v>5418</v>
+        <v>5417</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -1894,7 +1894,7 @@
         <v>0</v>
       </c>
       <c r="L22">
-        <v>7661</v>
+        <v>7665</v>
       </c>
       <c r="M22">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>64099</v>
       </c>
       <c r="Q22">
-        <v>4849</v>
+        <v>4848</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -2174,34 +2174,34 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>42115</v>
+        <v>42404</v>
       </c>
       <c r="H27">
-        <v>2161</v>
+        <v>1872</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="L27">
-        <v>9278</v>
+        <v>9323</v>
       </c>
       <c r="M27">
         <v>26</v>
       </c>
       <c r="N27">
-        <v>914</v>
+        <v>1005</v>
       </c>
       <c r="O27">
-        <v>39568</v>
+        <v>39717</v>
       </c>
       <c r="P27">
-        <v>63060</v>
+        <v>63059</v>
       </c>
       <c r="Q27">
         <v>12669</v>
@@ -2233,34 +2233,34 @@
         <v>0</v>
       </c>
       <c r="G28">
-        <v>52463</v>
+        <v>52987</v>
       </c>
       <c r="H28">
-        <v>1886</v>
+        <v>1362</v>
       </c>
       <c r="I28">
         <v>0</v>
       </c>
       <c r="J28">
-        <v>568</v>
+        <v>649</v>
       </c>
       <c r="K28">
         <v>0</v>
       </c>
       <c r="L28">
-        <v>7841</v>
+        <v>8016</v>
       </c>
       <c r="M28">
         <v>261</v>
       </c>
       <c r="N28">
-        <v>1974</v>
+        <v>2496</v>
       </c>
       <c r="O28">
-        <v>48517</v>
+        <v>48989</v>
       </c>
       <c r="P28">
-        <v>80623</v>
+        <v>80620</v>
       </c>
       <c r="Q28">
         <v>13995</v>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="J29">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="K29">
         <v>0</v>
       </c>
       <c r="L29">
-        <v>8584</v>
+        <v>8587</v>
       </c>
       <c r="M29">
         <v>37</v>
@@ -2351,31 +2351,31 @@
         <v>0</v>
       </c>
       <c r="G30">
-        <v>51190</v>
+        <v>51929</v>
       </c>
       <c r="H30">
-        <v>108</v>
+        <v>59</v>
       </c>
       <c r="I30">
-        <v>1355</v>
+        <v>665</v>
       </c>
       <c r="J30">
-        <v>523</v>
+        <v>847</v>
       </c>
       <c r="K30">
         <v>0</v>
       </c>
       <c r="L30">
-        <v>9978</v>
+        <v>10240</v>
       </c>
       <c r="M30">
         <v>246</v>
       </c>
       <c r="N30">
-        <v>5075</v>
+        <v>5255</v>
       </c>
       <c r="O30">
-        <v>45075</v>
+        <v>45677</v>
       </c>
       <c r="P30">
         <v>86933</v>
@@ -2419,13 +2419,13 @@
         <v>0</v>
       </c>
       <c r="J31">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="K31">
         <v>0</v>
       </c>
       <c r="L31">
-        <v>46603</v>
+        <v>46672</v>
       </c>
       <c r="M31">
         <v>42</v>
@@ -2434,10 +2434,10 @@
         <v>1892</v>
       </c>
       <c r="O31">
-        <v>89154</v>
+        <v>89222</v>
       </c>
       <c r="P31">
-        <v>81642</v>
+        <v>81643</v>
       </c>
       <c r="Q31">
         <v>14581</v>
@@ -2469,31 +2469,31 @@
         <v>0</v>
       </c>
       <c r="G32">
-        <v>43783</v>
+        <v>44287</v>
       </c>
       <c r="H32">
-        <v>2708</v>
+        <v>2243</v>
       </c>
       <c r="I32">
-        <v>237</v>
+        <v>198</v>
       </c>
       <c r="J32">
-        <v>505</v>
+        <v>310</v>
       </c>
       <c r="K32">
         <v>0</v>
       </c>
       <c r="L32">
-        <v>9868</v>
+        <v>10116</v>
       </c>
       <c r="M32">
         <v>157</v>
       </c>
       <c r="N32">
-        <v>2987</v>
+        <v>3366</v>
       </c>
       <c r="O32">
-        <v>39214</v>
+        <v>39655</v>
       </c>
       <c r="P32">
         <v>74812</v>
@@ -2528,34 +2528,34 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <v>38889</v>
+        <v>39230</v>
       </c>
       <c r="H33">
-        <v>1327</v>
+        <v>990</v>
       </c>
       <c r="I33">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J33">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="K33">
         <v>0</v>
       </c>
       <c r="L33">
-        <v>4705</v>
+        <v>4805</v>
       </c>
       <c r="M33">
         <v>55</v>
       </c>
       <c r="N33">
-        <v>499</v>
+        <v>671</v>
       </c>
       <c r="O33">
-        <v>36392</v>
+        <v>36575</v>
       </c>
       <c r="P33">
-        <v>76918</v>
+        <v>76969</v>
       </c>
       <c r="Q33">
         <v>6678</v>
@@ -2587,31 +2587,31 @@
         <v>0</v>
       </c>
       <c r="G34">
-        <v>35143</v>
+        <v>35328</v>
       </c>
       <c r="H34">
-        <v>1399</v>
+        <v>1214</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
       <c r="J34">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="K34">
         <v>0</v>
       </c>
       <c r="L34">
-        <v>11373</v>
+        <v>11418</v>
       </c>
       <c r="M34">
         <v>54</v>
       </c>
       <c r="N34">
-        <v>856</v>
+        <v>907</v>
       </c>
       <c r="O34">
-        <v>32704</v>
+        <v>32838</v>
       </c>
       <c r="P34">
         <v>74624</v>
@@ -2655,22 +2655,22 @@
         <v>0</v>
       </c>
       <c r="J35">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="K35">
         <v>0</v>
       </c>
       <c r="L35">
-        <v>6601</v>
+        <v>6626</v>
       </c>
       <c r="M35">
         <v>8</v>
       </c>
       <c r="N35">
-        <v>971</v>
+        <v>983</v>
       </c>
       <c r="O35">
-        <v>30067</v>
+        <v>30252</v>
       </c>
       <c r="P35">
         <v>76465</v>
@@ -2794,7 +2794,7 @@
         <v>57832</v>
       </c>
       <c r="Q37">
-        <v>4044</v>
+        <v>4036</v>
       </c>
       <c r="R37">
         <v>0</v>
@@ -2832,7 +2832,7 @@
         <v>0</v>
       </c>
       <c r="J38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38">
         <v>0</v>
@@ -3030,7 +3030,7 @@
         <v>85251</v>
       </c>
       <c r="Q41">
-        <v>6018</v>
+        <v>6015</v>
       </c>
       <c r="R41">
         <v>0</v>
@@ -3245,22 +3245,22 @@
         <v>0</v>
       </c>
       <c r="J45">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K45">
         <v>0</v>
       </c>
       <c r="L45">
-        <v>2235</v>
+        <v>2242</v>
       </c>
       <c r="M45">
         <v>13</v>
       </c>
       <c r="N45">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O45">
-        <v>19325</v>
+        <v>19361</v>
       </c>
       <c r="P45">
         <v>76002</v>
@@ -3319,7 +3319,7 @@
         <v>276</v>
       </c>
       <c r="O46">
-        <v>20981</v>
+        <v>21033</v>
       </c>
       <c r="P46">
         <v>64160</v>
@@ -3407,22 +3407,22 @@
         <v>0</v>
       </c>
       <c r="E48">
-        <v>19617</v>
+        <v>19630</v>
       </c>
       <c r="F48">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="G48">
-        <v>19600</v>
+        <v>19607</v>
       </c>
       <c r="H48">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="I48">
         <v>1</v>
       </c>
       <c r="J48">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K48">
         <v>0</v>
@@ -3472,16 +3472,16 @@
         <v>0</v>
       </c>
       <c r="G49">
-        <v>21340</v>
+        <v>21370</v>
       </c>
       <c r="H49">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="I49">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="J49">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K49">
         <v>0</v>
@@ -3493,10 +3493,10 @@
         <v>0</v>
       </c>
       <c r="N49">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O49">
-        <v>20106</v>
+        <v>20138</v>
       </c>
       <c r="P49">
         <v>55376</v>
@@ -3605,7 +3605,7 @@
         <v>0</v>
       </c>
       <c r="L51">
-        <v>4833</v>
+        <v>4843</v>
       </c>
       <c r="M51">
         <v>11</v>
@@ -3614,7 +3614,7 @@
         <v>75</v>
       </c>
       <c r="O51">
-        <v>23713</v>
+        <v>23723</v>
       </c>
       <c r="P51">
         <v>71754</v>
@@ -3664,7 +3664,7 @@
         <v>1</v>
       </c>
       <c r="L52">
-        <v>2922</v>
+        <v>2923</v>
       </c>
       <c r="M52">
         <v>1</v>
@@ -3673,7 +3673,7 @@
         <v>44</v>
       </c>
       <c r="O52">
-        <v>21023</v>
+        <v>21030</v>
       </c>
       <c r="P52">
         <v>63986</v>
@@ -3729,7 +3729,7 @@
         <v>1</v>
       </c>
       <c r="N53">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="O53">
         <v>19052</v>
@@ -3776,7 +3776,7 @@
         <v>0</v>
       </c>
       <c r="J54">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="K54">
         <v>0</v>
@@ -3797,7 +3797,7 @@
         <v>58440</v>
       </c>
       <c r="Q54">
-        <v>7376</v>
+        <v>7347</v>
       </c>
       <c r="R54">
         <v>0</v>
@@ -3894,7 +3894,7 @@
         <v>0</v>
       </c>
       <c r="J56">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="K56">
         <v>0</v>
@@ -3959,7 +3959,7 @@
         <v>0</v>
       </c>
       <c r="L57">
-        <v>1891</v>
+        <v>1905</v>
       </c>
       <c r="M57">
         <v>5</v>
@@ -3968,7 +3968,7 @@
         <v>39</v>
       </c>
       <c r="O57">
-        <v>21187</v>
+        <v>21201</v>
       </c>
       <c r="P57">
         <v>61556</v>
@@ -4027,13 +4027,13 @@
         <v>552</v>
       </c>
       <c r="O58">
-        <v>21219</v>
+        <v>21714</v>
       </c>
       <c r="P58">
         <v>57577</v>
       </c>
       <c r="Q58">
-        <v>8898</v>
+        <v>8884</v>
       </c>
       <c r="R58">
         <v>0</v>
@@ -4071,13 +4071,13 @@
         <v>0</v>
       </c>
       <c r="J59">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K59">
         <v>0</v>
       </c>
       <c r="L59">
-        <v>2494</v>
+        <v>2501</v>
       </c>
       <c r="M59">
         <v>2</v>
@@ -4086,7 +4086,7 @@
         <v>283</v>
       </c>
       <c r="O59">
-        <v>18463</v>
+        <v>18470</v>
       </c>
       <c r="P59">
         <v>60495</v>
@@ -4248,7 +4248,7 @@
         <v>0</v>
       </c>
       <c r="J62">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K62">
         <v>0</v>
@@ -4319,16 +4319,16 @@
         <v>68</v>
       </c>
       <c r="N63">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="O63">
-        <v>35819</v>
+        <v>35818</v>
       </c>
       <c r="P63">
         <v>68691</v>
       </c>
       <c r="Q63">
-        <v>9775</v>
+        <v>9766</v>
       </c>
       <c r="R63">
         <v>0</v>
@@ -4366,13 +4366,13 @@
         <v>0</v>
       </c>
       <c r="J64">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K64">
         <v>0</v>
       </c>
       <c r="L64">
-        <v>9742</v>
+        <v>9747</v>
       </c>
       <c r="M64">
         <v>8</v>
@@ -4387,7 +4387,7 @@
         <v>60527</v>
       </c>
       <c r="Q64">
-        <v>6002</v>
+        <v>5985</v>
       </c>
       <c r="R64">
         <v>0</v>
@@ -4416,31 +4416,31 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>40356</v>
+        <v>40419</v>
       </c>
       <c r="H65">
-        <v>712</v>
+        <v>649</v>
       </c>
       <c r="I65">
         <v>321</v>
       </c>
       <c r="J65">
-        <v>201</v>
+        <v>173</v>
       </c>
       <c r="K65">
         <v>0</v>
       </c>
       <c r="L65">
-        <v>12930</v>
+        <v>12961</v>
       </c>
       <c r="M65">
         <v>2</v>
       </c>
       <c r="N65">
-        <v>1947</v>
+        <v>2004</v>
       </c>
       <c r="O65">
-        <v>32019</v>
+        <v>32834</v>
       </c>
       <c r="P65">
         <v>58103</v>
@@ -4475,34 +4475,34 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>66425</v>
+        <v>66607</v>
       </c>
       <c r="H66">
-        <v>937</v>
+        <v>755</v>
       </c>
       <c r="I66">
         <v>0</v>
       </c>
       <c r="J66">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="K66">
         <v>0</v>
       </c>
       <c r="L66">
-        <v>13578</v>
+        <v>13602</v>
       </c>
       <c r="M66">
         <v>2</v>
       </c>
       <c r="N66">
-        <v>3419</v>
+        <v>3526</v>
       </c>
       <c r="O66">
-        <v>62698</v>
+        <v>62800</v>
       </c>
       <c r="P66">
-        <v>93810</v>
+        <v>93809</v>
       </c>
       <c r="Q66">
         <v>17742</v>
@@ -4534,22 +4534,22 @@
         <v>0</v>
       </c>
       <c r="G67">
-        <v>68777</v>
+        <v>68787</v>
       </c>
       <c r="H67">
         <v>0</v>
       </c>
       <c r="I67">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="J67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K67">
         <v>0</v>
       </c>
       <c r="L67">
-        <v>19408</v>
+        <v>19409</v>
       </c>
       <c r="M67">
         <v>10</v>
@@ -4558,7 +4558,7 @@
         <v>3597</v>
       </c>
       <c r="O67">
-        <v>65007</v>
+        <v>65115</v>
       </c>
       <c r="P67">
         <v>78022</v>
@@ -4593,34 +4593,34 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>63036</v>
+        <v>63304</v>
       </c>
       <c r="H68">
-        <v>1576</v>
+        <v>1352</v>
       </c>
       <c r="I68">
-        <v>672</v>
+        <v>628</v>
       </c>
       <c r="J68">
-        <v>32</v>
+        <v>174</v>
       </c>
       <c r="K68">
         <v>0</v>
       </c>
       <c r="L68">
-        <v>17059</v>
+        <v>17119</v>
       </c>
       <c r="M68">
         <v>2</v>
       </c>
       <c r="N68">
-        <v>858</v>
+        <v>895</v>
       </c>
       <c r="O68">
-        <v>54716</v>
+        <v>55027</v>
       </c>
       <c r="P68">
-        <v>70187</v>
+        <v>71020</v>
       </c>
       <c r="Q68">
         <v>7850</v>
@@ -4652,31 +4652,31 @@
         <v>0</v>
       </c>
       <c r="G69">
-        <v>42333</v>
+        <v>42483</v>
       </c>
       <c r="H69">
-        <v>1585</v>
+        <v>1436</v>
       </c>
       <c r="I69">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J69">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="K69">
         <v>0</v>
       </c>
       <c r="L69">
-        <v>17405</v>
+        <v>17466</v>
       </c>
       <c r="M69">
         <v>2</v>
       </c>
       <c r="N69">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="O69">
-        <v>38174</v>
+        <v>38673</v>
       </c>
       <c r="P69">
         <v>36117</v>
@@ -4711,16 +4711,16 @@
         <v>0</v>
       </c>
       <c r="G70">
-        <v>47652</v>
+        <v>47665</v>
       </c>
       <c r="H70">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="I70">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J70">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K70">
         <v>0</v>
@@ -4732,10 +4732,10 @@
         <v>2</v>
       </c>
       <c r="N70">
-        <v>3198</v>
+        <v>3201</v>
       </c>
       <c r="O70">
-        <v>44427</v>
+        <v>44439</v>
       </c>
       <c r="P70">
         <v>42039</v>
@@ -4770,16 +4770,16 @@
         <v>0</v>
       </c>
       <c r="G71">
-        <v>50702</v>
+        <v>50894</v>
       </c>
       <c r="H71">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="I71">
-        <v>174</v>
+        <v>4</v>
       </c>
       <c r="J71">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K71">
         <v>0</v>
@@ -4791,7 +4791,7 @@
         <v>1</v>
       </c>
       <c r="N71">
-        <v>4176</v>
+        <v>4353</v>
       </c>
       <c r="O71">
         <v>46155</v>
@@ -4829,10 +4829,10 @@
         <v>0</v>
       </c>
       <c r="G72">
-        <v>61384</v>
+        <v>61397</v>
       </c>
       <c r="H72">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="I72">
         <v>61</v>
@@ -4844,22 +4844,22 @@
         <v>0</v>
       </c>
       <c r="L72">
-        <v>17082</v>
+        <v>17085</v>
       </c>
       <c r="M72">
         <v>9</v>
       </c>
       <c r="N72">
-        <v>3594</v>
+        <v>3602</v>
       </c>
       <c r="O72">
-        <v>54052</v>
+        <v>55873</v>
       </c>
       <c r="P72">
         <v>85505</v>
       </c>
       <c r="Q72">
-        <v>12353</v>
+        <v>12340</v>
       </c>
       <c r="R72">
         <v>0</v>
@@ -4888,31 +4888,31 @@
         <v>0</v>
       </c>
       <c r="G73">
-        <v>56658</v>
+        <v>57165</v>
       </c>
       <c r="H73">
-        <v>2184</v>
+        <v>1682</v>
       </c>
       <c r="I73">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="J73">
-        <v>15</v>
+        <v>179</v>
       </c>
       <c r="K73">
         <v>0</v>
       </c>
       <c r="L73">
-        <v>14176</v>
+        <v>14197</v>
       </c>
       <c r="M73">
         <v>7</v>
       </c>
       <c r="N73">
-        <v>2143</v>
+        <v>2405</v>
       </c>
       <c r="O73">
-        <v>49758</v>
+        <v>49970</v>
       </c>
       <c r="P73">
         <v>67550</v>
@@ -4939,43 +4939,43 @@
         <v>0</v>
       </c>
       <c r="E74">
-        <v>2430363</v>
+        <v>2430376</v>
       </c>
       <c r="F74">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="G74">
-        <v>2398021</v>
+        <v>2404366</v>
       </c>
       <c r="H74">
-        <v>28766</v>
+        <v>23469</v>
       </c>
       <c r="I74">
-        <v>3392</v>
+        <v>2373</v>
       </c>
       <c r="J74">
-        <v>29495</v>
+        <v>25348</v>
       </c>
       <c r="K74">
-        <v>13452</v>
+        <v>11886</v>
       </c>
       <c r="L74">
-        <v>583270</v>
+        <v>589745</v>
       </c>
       <c r="M74">
-        <v>3484</v>
+        <v>4156</v>
       </c>
       <c r="N74">
-        <v>79332</v>
+        <v>81932</v>
       </c>
       <c r="O74">
-        <v>2219629</v>
+        <v>2233101</v>
       </c>
       <c r="P74">
-        <v>4682864</v>
+        <v>4684412</v>
       </c>
       <c r="Q74">
-        <v>626533</v>
+        <v>626236</v>
       </c>
       <c r="R74">
         <v>1</v>

--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB433B1A-BE83-4204-8CD9-401AEA14EBEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B283BD09-EACB-4C7C-B90D-1F525DF32E2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21585" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -304,7 +304,7 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Notice &amp; Hearing Report Last Updated On : 03-09-2026 07:59:59</t>
+    <t>Notice &amp; Hearing Report Last Updated On : 03-09-2026 17:56:59</t>
   </si>
 </sst>
 </file>
@@ -817,31 +817,31 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>49624</v>
+        <v>50420</v>
       </c>
       <c r="H4">
-        <v>1900</v>
+        <v>1104</v>
       </c>
       <c r="I4">
         <v>4</v>
       </c>
       <c r="J4">
-        <v>3154</v>
+        <v>2847</v>
       </c>
       <c r="K4">
-        <v>409</v>
+        <v>320</v>
       </c>
       <c r="L4">
-        <v>13404</v>
+        <v>14391</v>
       </c>
       <c r="M4">
-        <v>470</v>
+        <v>544</v>
       </c>
       <c r="N4">
-        <v>369</v>
+        <v>533</v>
       </c>
       <c r="O4">
-        <v>43003</v>
+        <v>43687</v>
       </c>
       <c r="P4">
         <v>53812</v>
@@ -876,31 +876,31 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>53483</v>
+        <v>53663</v>
       </c>
       <c r="H5">
-        <v>422</v>
+        <v>248</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>2217</v>
+        <v>17</v>
       </c>
       <c r="K5">
-        <v>794</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>8987</v>
+        <v>11307</v>
       </c>
       <c r="M5">
-        <v>634</v>
+        <v>674</v>
       </c>
       <c r="N5">
-        <v>598</v>
+        <v>705</v>
       </c>
       <c r="O5">
-        <v>49712</v>
+        <v>51040</v>
       </c>
       <c r="P5">
         <v>74848</v>
@@ -935,31 +935,31 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>37909</v>
+        <v>38055</v>
       </c>
       <c r="H6">
-        <v>1750</v>
+        <v>1623</v>
       </c>
       <c r="I6">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="J6">
-        <v>2182</v>
+        <v>1454</v>
       </c>
       <c r="K6">
-        <v>1159</v>
+        <v>538</v>
       </c>
       <c r="L6">
-        <v>3667</v>
+        <v>4452</v>
       </c>
       <c r="M6">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="N6">
-        <v>1183</v>
+        <v>1204</v>
       </c>
       <c r="O6">
-        <v>31527</v>
+        <v>31703</v>
       </c>
       <c r="P6">
         <v>71989</v>
@@ -994,31 +994,31 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>39422</v>
+        <v>39463</v>
       </c>
       <c r="H7">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7">
-        <v>988</v>
+        <v>639</v>
       </c>
       <c r="K7">
-        <v>901</v>
+        <v>519</v>
       </c>
       <c r="L7">
-        <v>4624</v>
+        <v>4997</v>
       </c>
       <c r="M7">
-        <v>166</v>
+        <v>208</v>
       </c>
       <c r="N7">
-        <v>1958</v>
+        <v>1983</v>
       </c>
       <c r="O7">
-        <v>33862</v>
+        <v>34233</v>
       </c>
       <c r="P7">
         <v>77581</v>
@@ -1053,16 +1053,16 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>39671</v>
+        <v>40082</v>
       </c>
       <c r="H8">
-        <v>881</v>
+        <v>470</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>52</v>
+        <v>102</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -1074,10 +1074,10 @@
         <v>163</v>
       </c>
       <c r="N8">
-        <v>1564</v>
+        <v>1737</v>
       </c>
       <c r="O8">
-        <v>32025</v>
+        <v>32331</v>
       </c>
       <c r="P8">
         <v>73458</v>
@@ -1112,31 +1112,31 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>43253</v>
+        <v>43268</v>
       </c>
       <c r="H9">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>1244</v>
+        <v>1546</v>
       </c>
       <c r="K9">
         <v>893</v>
       </c>
       <c r="L9">
-        <v>5980</v>
+        <v>6050</v>
       </c>
       <c r="M9">
         <v>35</v>
       </c>
       <c r="N9">
-        <v>1242</v>
+        <v>1277</v>
       </c>
       <c r="O9">
-        <v>39515</v>
+        <v>39519</v>
       </c>
       <c r="P9">
         <v>72762</v>
@@ -1180,13 +1180,13 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>1489</v>
+        <v>1492</v>
       </c>
       <c r="K10">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="L10">
-        <v>9503</v>
+        <v>9504</v>
       </c>
       <c r="M10">
         <v>111</v>
@@ -1195,7 +1195,7 @@
         <v>770</v>
       </c>
       <c r="O10">
-        <v>33886</v>
+        <v>34209</v>
       </c>
       <c r="P10">
         <v>53124</v>
@@ -1239,7 +1239,7 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>264</v>
+        <v>310</v>
       </c>
       <c r="K11">
         <v>77</v>
@@ -1251,10 +1251,10 @@
         <v>241</v>
       </c>
       <c r="N11">
-        <v>1567</v>
+        <v>1611</v>
       </c>
       <c r="O11">
-        <v>48962</v>
+        <v>48965</v>
       </c>
       <c r="P11">
         <v>84438</v>
@@ -1289,31 +1289,31 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>40633</v>
+        <v>40714</v>
       </c>
       <c r="H12">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12">
-        <v>1868</v>
+        <v>1002</v>
       </c>
       <c r="K12">
-        <v>1614</v>
+        <v>928</v>
       </c>
       <c r="L12">
-        <v>8064</v>
+        <v>8928</v>
       </c>
       <c r="M12">
-        <v>128</v>
+        <v>165</v>
       </c>
       <c r="N12">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="O12">
-        <v>33999</v>
+        <v>34067</v>
       </c>
       <c r="P12">
         <v>66685</v>
@@ -1357,13 +1357,13 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>77</v>
+        <v>7</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
       <c r="L13">
-        <v>7785</v>
+        <v>7857</v>
       </c>
       <c r="M13">
         <v>258</v>
@@ -1372,7 +1372,7 @@
         <v>3821</v>
       </c>
       <c r="O13">
-        <v>32954</v>
+        <v>33160</v>
       </c>
       <c r="P13">
         <v>56565</v>
@@ -1407,34 +1407,34 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>46231</v>
+        <v>46891</v>
       </c>
       <c r="H14">
-        <v>2662</v>
+        <v>2002</v>
       </c>
       <c r="I14">
         <v>25</v>
       </c>
       <c r="J14">
-        <v>8294</v>
+        <v>7841</v>
       </c>
       <c r="K14">
-        <v>4819</v>
+        <v>4544</v>
       </c>
       <c r="L14">
-        <v>6908</v>
+        <v>7474</v>
       </c>
       <c r="M14">
-        <v>693</v>
+        <v>945</v>
       </c>
       <c r="N14">
-        <v>3795</v>
+        <v>3971</v>
       </c>
       <c r="O14">
-        <v>28338</v>
+        <v>28606</v>
       </c>
       <c r="P14">
-        <v>73452</v>
+        <v>77955</v>
       </c>
       <c r="Q14">
         <v>19716</v>
@@ -1726,7 +1726,7 @@
         <v>910</v>
       </c>
       <c r="O19">
-        <v>55234</v>
+        <v>55575</v>
       </c>
       <c r="P19">
         <v>106227</v>
@@ -1903,7 +1903,7 @@
         <v>302</v>
       </c>
       <c r="O22">
-        <v>18360</v>
+        <v>18366</v>
       </c>
       <c r="P22">
         <v>64099</v>
@@ -2174,31 +2174,31 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>42404</v>
+        <v>43020</v>
       </c>
       <c r="H27">
-        <v>1872</v>
+        <v>1256</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27">
-        <v>195</v>
+        <v>267</v>
       </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="L27">
-        <v>9323</v>
+        <v>9404</v>
       </c>
       <c r="M27">
         <v>26</v>
       </c>
       <c r="N27">
-        <v>1005</v>
+        <v>1406</v>
       </c>
       <c r="O27">
-        <v>39717</v>
+        <v>39942</v>
       </c>
       <c r="P27">
         <v>63059</v>
@@ -2233,31 +2233,31 @@
         <v>0</v>
       </c>
       <c r="G28">
-        <v>52987</v>
+        <v>53450</v>
       </c>
       <c r="H28">
-        <v>1362</v>
+        <v>899</v>
       </c>
       <c r="I28">
         <v>0</v>
       </c>
       <c r="J28">
-        <v>649</v>
+        <v>480</v>
       </c>
       <c r="K28">
         <v>0</v>
       </c>
       <c r="L28">
-        <v>8016</v>
+        <v>8311</v>
       </c>
       <c r="M28">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="N28">
-        <v>2496</v>
+        <v>2677</v>
       </c>
       <c r="O28">
-        <v>48989</v>
+        <v>49276</v>
       </c>
       <c r="P28">
         <v>80620</v>
@@ -2301,25 +2301,25 @@
         <v>0</v>
       </c>
       <c r="J29">
-        <v>320</v>
+        <v>369</v>
       </c>
       <c r="K29">
         <v>0</v>
       </c>
       <c r="L29">
-        <v>8587</v>
+        <v>8651</v>
       </c>
       <c r="M29">
         <v>37</v>
       </c>
       <c r="N29">
-        <v>4227</v>
+        <v>4228</v>
       </c>
       <c r="O29">
-        <v>42138</v>
+        <v>42161</v>
       </c>
       <c r="P29">
-        <v>83837</v>
+        <v>83836</v>
       </c>
       <c r="Q29">
         <v>14229</v>
@@ -2351,31 +2351,31 @@
         <v>0</v>
       </c>
       <c r="G30">
-        <v>51929</v>
+        <v>52282</v>
       </c>
       <c r="H30">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="I30">
-        <v>665</v>
+        <v>367</v>
       </c>
       <c r="J30">
-        <v>847</v>
+        <v>232</v>
       </c>
       <c r="K30">
         <v>0</v>
       </c>
       <c r="L30">
-        <v>10240</v>
+        <v>11270</v>
       </c>
       <c r="M30">
         <v>246</v>
       </c>
       <c r="N30">
-        <v>5255</v>
+        <v>5276</v>
       </c>
       <c r="O30">
-        <v>45677</v>
+        <v>46208</v>
       </c>
       <c r="P30">
         <v>86933</v>
@@ -2419,22 +2419,22 @@
         <v>0</v>
       </c>
       <c r="J31">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="K31">
         <v>0</v>
       </c>
       <c r="L31">
-        <v>46672</v>
+        <v>46718</v>
       </c>
       <c r="M31">
         <v>42</v>
       </c>
       <c r="N31">
-        <v>1892</v>
+        <v>1894</v>
       </c>
       <c r="O31">
-        <v>89222</v>
+        <v>89268</v>
       </c>
       <c r="P31">
         <v>81643</v>
@@ -2469,34 +2469,34 @@
         <v>0</v>
       </c>
       <c r="G32">
-        <v>44287</v>
+        <v>44868</v>
       </c>
       <c r="H32">
-        <v>2243</v>
+        <v>1704</v>
       </c>
       <c r="I32">
-        <v>198</v>
+        <v>156</v>
       </c>
       <c r="J32">
-        <v>310</v>
+        <v>170</v>
       </c>
       <c r="K32">
         <v>0</v>
       </c>
       <c r="L32">
-        <v>10116</v>
+        <v>10301</v>
       </c>
       <c r="M32">
         <v>157</v>
       </c>
       <c r="N32">
-        <v>3366</v>
+        <v>3845</v>
       </c>
       <c r="O32">
-        <v>39655</v>
+        <v>39882</v>
       </c>
       <c r="P32">
-        <v>74812</v>
+        <v>74811</v>
       </c>
       <c r="Q32">
         <v>11379</v>
@@ -2528,31 +2528,31 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <v>39230</v>
+        <v>39620</v>
       </c>
       <c r="H33">
-        <v>990</v>
+        <v>602</v>
       </c>
       <c r="I33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J33">
-        <v>239</v>
+        <v>205</v>
       </c>
       <c r="K33">
         <v>0</v>
       </c>
       <c r="L33">
-        <v>4805</v>
+        <v>4921</v>
       </c>
       <c r="M33">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N33">
-        <v>671</v>
+        <v>830</v>
       </c>
       <c r="O33">
-        <v>36575</v>
+        <v>36770</v>
       </c>
       <c r="P33">
         <v>76969</v>
@@ -2587,31 +2587,31 @@
         <v>0</v>
       </c>
       <c r="G34">
-        <v>35328</v>
+        <v>36360</v>
       </c>
       <c r="H34">
-        <v>1214</v>
+        <v>182</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
       <c r="J34">
-        <v>78</v>
+        <v>324</v>
       </c>
       <c r="K34">
         <v>0</v>
       </c>
       <c r="L34">
-        <v>11418</v>
+        <v>11568</v>
       </c>
       <c r="M34">
         <v>54</v>
       </c>
       <c r="N34">
-        <v>907</v>
+        <v>1157</v>
       </c>
       <c r="O34">
-        <v>32838</v>
+        <v>33750</v>
       </c>
       <c r="P34">
         <v>74624</v>
@@ -2646,31 +2646,31 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>31819</v>
+        <v>32209</v>
       </c>
       <c r="H35">
-        <v>1745</v>
+        <v>1355</v>
       </c>
       <c r="I35">
         <v>0</v>
       </c>
       <c r="J35">
-        <v>49</v>
+        <v>204</v>
       </c>
       <c r="K35">
         <v>0</v>
       </c>
       <c r="L35">
-        <v>6626</v>
+        <v>6720</v>
       </c>
       <c r="M35">
         <v>8</v>
       </c>
       <c r="N35">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="O35">
-        <v>30252</v>
+        <v>30713</v>
       </c>
       <c r="P35">
         <v>76465</v>
@@ -2838,16 +2838,16 @@
         <v>0</v>
       </c>
       <c r="L38">
-        <v>5381</v>
+        <v>5385</v>
       </c>
       <c r="M38">
         <v>2</v>
       </c>
       <c r="N38">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="O38">
-        <v>28463</v>
+        <v>28472</v>
       </c>
       <c r="P38">
         <v>63038</v>
@@ -3080,10 +3080,10 @@
         <v>0</v>
       </c>
       <c r="N42">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O42">
-        <v>27148</v>
+        <v>27147</v>
       </c>
       <c r="P42">
         <v>68615</v>
@@ -3236,10 +3236,10 @@
         <v>0</v>
       </c>
       <c r="G45">
-        <v>19906</v>
+        <v>19908</v>
       </c>
       <c r="H45">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -3251,16 +3251,16 @@
         <v>0</v>
       </c>
       <c r="L45">
-        <v>2242</v>
+        <v>2243</v>
       </c>
       <c r="M45">
         <v>13</v>
       </c>
       <c r="N45">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O45">
-        <v>19361</v>
+        <v>19423</v>
       </c>
       <c r="P45">
         <v>76002</v>
@@ -3310,7 +3310,7 @@
         <v>0</v>
       </c>
       <c r="L46">
-        <v>8297</v>
+        <v>8299</v>
       </c>
       <c r="M46">
         <v>32</v>
@@ -3319,7 +3319,7 @@
         <v>276</v>
       </c>
       <c r="O46">
-        <v>21033</v>
+        <v>21232</v>
       </c>
       <c r="P46">
         <v>64160</v>
@@ -3407,37 +3407,37 @@
         <v>0</v>
       </c>
       <c r="E48">
-        <v>19630</v>
+        <v>19639</v>
       </c>
       <c r="F48">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G48">
-        <v>19607</v>
+        <v>19619</v>
       </c>
       <c r="H48">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="I48">
         <v>1</v>
       </c>
       <c r="J48">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K48">
         <v>0</v>
       </c>
       <c r="L48">
-        <v>3776</v>
+        <v>3786</v>
       </c>
       <c r="M48">
         <v>4</v>
       </c>
       <c r="N48">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="O48">
-        <v>19333</v>
+        <v>19342</v>
       </c>
       <c r="P48">
         <v>54142</v>
@@ -3472,31 +3472,31 @@
         <v>0</v>
       </c>
       <c r="G49">
-        <v>21370</v>
+        <v>21517</v>
       </c>
       <c r="H49">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="I49">
-        <v>224</v>
+        <v>109</v>
       </c>
       <c r="J49">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K49">
         <v>0</v>
       </c>
       <c r="L49">
-        <v>3599</v>
+        <v>3604</v>
       </c>
       <c r="M49">
         <v>0</v>
       </c>
       <c r="N49">
-        <v>364</v>
+        <v>506</v>
       </c>
       <c r="O49">
-        <v>20138</v>
+        <v>20144</v>
       </c>
       <c r="P49">
         <v>55376</v>
@@ -3664,19 +3664,19 @@
         <v>1</v>
       </c>
       <c r="L52">
-        <v>2923</v>
+        <v>2941</v>
       </c>
       <c r="M52">
         <v>1</v>
       </c>
       <c r="N52">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O52">
-        <v>21030</v>
+        <v>21048</v>
       </c>
       <c r="P52">
-        <v>63986</v>
+        <v>63987</v>
       </c>
       <c r="Q52">
         <v>5655</v>
@@ -3723,19 +3723,19 @@
         <v>1</v>
       </c>
       <c r="L53">
-        <v>3510</v>
+        <v>3512</v>
       </c>
       <c r="M53">
         <v>1</v>
       </c>
       <c r="N53">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="O53">
-        <v>19052</v>
+        <v>19054</v>
       </c>
       <c r="P53">
-        <v>56304</v>
+        <v>56306</v>
       </c>
       <c r="Q53">
         <v>6551</v>
@@ -3776,22 +3776,22 @@
         <v>0</v>
       </c>
       <c r="J54">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="K54">
         <v>0</v>
       </c>
       <c r="L54">
-        <v>2552</v>
+        <v>2587</v>
       </c>
       <c r="M54">
         <v>5</v>
       </c>
       <c r="N54">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O54">
-        <v>20311</v>
+        <v>20346</v>
       </c>
       <c r="P54">
         <v>58440</v>
@@ -3835,13 +3835,13 @@
         <v>0</v>
       </c>
       <c r="J55">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K55">
         <v>4</v>
       </c>
       <c r="L55">
-        <v>2056</v>
+        <v>2064</v>
       </c>
       <c r="M55">
         <v>1</v>
@@ -3850,7 +3850,7 @@
         <v>124</v>
       </c>
       <c r="O55">
-        <v>15843</v>
+        <v>15851</v>
       </c>
       <c r="P55">
         <v>58215</v>
@@ -3894,19 +3894,19 @@
         <v>0</v>
       </c>
       <c r="J56">
-        <v>51</v>
+        <v>95</v>
       </c>
       <c r="K56">
         <v>0</v>
       </c>
       <c r="L56">
-        <v>3846</v>
+        <v>3895</v>
       </c>
       <c r="M56">
         <v>2</v>
       </c>
       <c r="N56">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="O56">
         <v>18561</v>
@@ -4012,13 +4012,13 @@
         <v>0</v>
       </c>
       <c r="J58">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K58">
         <v>0</v>
       </c>
       <c r="L58">
-        <v>8092</v>
+        <v>8098</v>
       </c>
       <c r="M58">
         <v>10</v>
@@ -4027,7 +4027,7 @@
         <v>552</v>
       </c>
       <c r="O58">
-        <v>21714</v>
+        <v>21732</v>
       </c>
       <c r="P58">
         <v>57577</v>
@@ -4071,22 +4071,22 @@
         <v>0</v>
       </c>
       <c r="J59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K59">
         <v>0</v>
       </c>
       <c r="L59">
-        <v>2501</v>
+        <v>2504</v>
       </c>
       <c r="M59">
         <v>2</v>
       </c>
       <c r="N59">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="O59">
-        <v>18470</v>
+        <v>18487</v>
       </c>
       <c r="P59">
         <v>60495</v>
@@ -4136,7 +4136,7 @@
         <v>0</v>
       </c>
       <c r="L60">
-        <v>5716</v>
+        <v>5764</v>
       </c>
       <c r="M60">
         <v>9</v>
@@ -4145,7 +4145,7 @@
         <v>324</v>
       </c>
       <c r="O60">
-        <v>21763</v>
+        <v>23374</v>
       </c>
       <c r="P60">
         <v>70140</v>
@@ -4201,10 +4201,10 @@
         <v>37</v>
       </c>
       <c r="N61">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="O61">
-        <v>22030</v>
+        <v>22032</v>
       </c>
       <c r="P61">
         <v>55240</v>
@@ -4248,22 +4248,22 @@
         <v>0</v>
       </c>
       <c r="J62">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K62">
         <v>0</v>
       </c>
       <c r="L62">
-        <v>4138</v>
+        <v>4197</v>
       </c>
       <c r="M62">
         <v>19</v>
       </c>
       <c r="N62">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="O62">
-        <v>15230</v>
+        <v>15289</v>
       </c>
       <c r="P62">
         <v>51334</v>
@@ -4307,7 +4307,7 @@
         <v>0</v>
       </c>
       <c r="J63">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K63">
         <v>0</v>
@@ -4319,10 +4319,10 @@
         <v>68</v>
       </c>
       <c r="N63">
-        <v>925</v>
+        <v>930</v>
       </c>
       <c r="O63">
-        <v>35818</v>
+        <v>35819</v>
       </c>
       <c r="P63">
         <v>68691</v>
@@ -4357,31 +4357,31 @@
         <v>0</v>
       </c>
       <c r="G64">
-        <v>42036</v>
+        <v>42042</v>
       </c>
       <c r="H64">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I64">
         <v>0</v>
       </c>
       <c r="J64">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="K64">
         <v>0</v>
       </c>
       <c r="L64">
-        <v>9747</v>
+        <v>9767</v>
       </c>
       <c r="M64">
         <v>8</v>
       </c>
       <c r="N64">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="O64">
-        <v>41279</v>
+        <v>41287</v>
       </c>
       <c r="P64">
         <v>60527</v>
@@ -4416,31 +4416,31 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>40419</v>
+        <v>40957</v>
       </c>
       <c r="H65">
-        <v>649</v>
+        <v>201</v>
       </c>
       <c r="I65">
-        <v>321</v>
+        <v>231</v>
       </c>
       <c r="J65">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="K65">
         <v>0</v>
       </c>
       <c r="L65">
-        <v>12961</v>
+        <v>13123</v>
       </c>
       <c r="M65">
         <v>2</v>
       </c>
       <c r="N65">
-        <v>2004</v>
+        <v>2234</v>
       </c>
       <c r="O65">
-        <v>32834</v>
+        <v>34204</v>
       </c>
       <c r="P65">
         <v>58103</v>
@@ -4475,31 +4475,31 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>66607</v>
+        <v>67215</v>
       </c>
       <c r="H66">
-        <v>755</v>
+        <v>147</v>
       </c>
       <c r="I66">
         <v>0</v>
       </c>
       <c r="J66">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K66">
         <v>0</v>
       </c>
       <c r="L66">
-        <v>13602</v>
+        <v>13684</v>
       </c>
       <c r="M66">
         <v>2</v>
       </c>
       <c r="N66">
-        <v>3526</v>
+        <v>3955</v>
       </c>
       <c r="O66">
-        <v>62800</v>
+        <v>62931</v>
       </c>
       <c r="P66">
         <v>93809</v>
@@ -4534,31 +4534,31 @@
         <v>0</v>
       </c>
       <c r="G67">
-        <v>68787</v>
+        <v>68807</v>
       </c>
       <c r="H67">
         <v>0</v>
       </c>
       <c r="I67">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="J67">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K67">
         <v>0</v>
       </c>
       <c r="L67">
-        <v>19409</v>
+        <v>19419</v>
       </c>
       <c r="M67">
         <v>10</v>
       </c>
       <c r="N67">
-        <v>3597</v>
+        <v>3616</v>
       </c>
       <c r="O67">
-        <v>65115</v>
+        <v>65113</v>
       </c>
       <c r="P67">
         <v>78022</v>
@@ -4593,34 +4593,34 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>63304</v>
+        <v>63831</v>
       </c>
       <c r="H68">
-        <v>1352</v>
+        <v>923</v>
       </c>
       <c r="I68">
-        <v>628</v>
+        <v>534</v>
       </c>
       <c r="J68">
-        <v>174</v>
+        <v>57</v>
       </c>
       <c r="K68">
         <v>0</v>
       </c>
       <c r="L68">
-        <v>17119</v>
+        <v>17589</v>
       </c>
       <c r="M68">
         <v>2</v>
       </c>
       <c r="N68">
-        <v>895</v>
+        <v>950</v>
       </c>
       <c r="O68">
-        <v>55027</v>
+        <v>56011</v>
       </c>
       <c r="P68">
-        <v>71020</v>
+        <v>71326</v>
       </c>
       <c r="Q68">
         <v>7850</v>
@@ -4652,31 +4652,31 @@
         <v>0</v>
       </c>
       <c r="G69">
-        <v>42483</v>
+        <v>42924</v>
       </c>
       <c r="H69">
-        <v>1436</v>
+        <v>1001</v>
       </c>
       <c r="I69">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J69">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="K69">
         <v>0</v>
       </c>
       <c r="L69">
-        <v>17466</v>
+        <v>17705</v>
       </c>
       <c r="M69">
         <v>2</v>
       </c>
       <c r="N69">
-        <v>1845</v>
+        <v>2050</v>
       </c>
       <c r="O69">
-        <v>38673</v>
+        <v>40671</v>
       </c>
       <c r="P69">
         <v>36117</v>
@@ -4711,31 +4711,31 @@
         <v>0</v>
       </c>
       <c r="G70">
-        <v>47665</v>
+        <v>47711</v>
       </c>
       <c r="H70">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="I70">
         <v>0</v>
       </c>
       <c r="J70">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K70">
         <v>0</v>
       </c>
       <c r="L70">
-        <v>18259</v>
+        <v>18266</v>
       </c>
       <c r="M70">
         <v>2</v>
       </c>
       <c r="N70">
-        <v>3201</v>
+        <v>3246</v>
       </c>
       <c r="O70">
-        <v>44439</v>
+        <v>44447</v>
       </c>
       <c r="P70">
         <v>42039</v>
@@ -4770,31 +4770,31 @@
         <v>0</v>
       </c>
       <c r="G71">
-        <v>50894</v>
+        <v>50962</v>
       </c>
       <c r="H71">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="I71">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J71">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K71">
         <v>0</v>
       </c>
       <c r="L71">
-        <v>22750</v>
+        <v>22777</v>
       </c>
       <c r="M71">
         <v>1</v>
       </c>
       <c r="N71">
-        <v>4353</v>
+        <v>4386</v>
       </c>
       <c r="O71">
-        <v>46155</v>
+        <v>46178</v>
       </c>
       <c r="P71">
         <v>48896</v>
@@ -4829,31 +4829,31 @@
         <v>0</v>
       </c>
       <c r="G72">
-        <v>61397</v>
+        <v>61436</v>
       </c>
       <c r="H72">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="I72">
         <v>61</v>
       </c>
       <c r="J72">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="K72">
         <v>0</v>
       </c>
       <c r="L72">
-        <v>17085</v>
+        <v>17105</v>
       </c>
       <c r="M72">
         <v>9</v>
       </c>
       <c r="N72">
-        <v>3602</v>
+        <v>3630</v>
       </c>
       <c r="O72">
-        <v>55873</v>
+        <v>56295</v>
       </c>
       <c r="P72">
         <v>85505</v>
@@ -4888,31 +4888,31 @@
         <v>0</v>
       </c>
       <c r="G73">
-        <v>57165</v>
+        <v>58328</v>
       </c>
       <c r="H73">
-        <v>1682</v>
+        <v>543</v>
       </c>
       <c r="I73">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="J73">
-        <v>179</v>
+        <v>53</v>
       </c>
       <c r="K73">
         <v>0</v>
       </c>
       <c r="L73">
-        <v>14197</v>
+        <v>14508</v>
       </c>
       <c r="M73">
         <v>7</v>
       </c>
       <c r="N73">
-        <v>2405</v>
+        <v>3224</v>
       </c>
       <c r="O73">
-        <v>49970</v>
+        <v>50298</v>
       </c>
       <c r="P73">
         <v>67550</v>
@@ -4939,40 +4939,40 @@
         <v>0</v>
       </c>
       <c r="E74">
-        <v>2430376</v>
+        <v>2430385</v>
       </c>
       <c r="F74">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G74">
-        <v>2404366</v>
+        <v>2414138</v>
       </c>
       <c r="H74">
-        <v>23469</v>
+        <v>14414</v>
       </c>
       <c r="I74">
-        <v>2373</v>
+        <v>1670</v>
       </c>
       <c r="J74">
-        <v>25348</v>
+        <v>19989</v>
       </c>
       <c r="K74">
-        <v>11886</v>
+        <v>9038</v>
       </c>
       <c r="L74">
-        <v>589745</v>
+        <v>599442</v>
       </c>
       <c r="M74">
-        <v>4156</v>
+        <v>4610</v>
       </c>
       <c r="N74">
-        <v>81932</v>
+        <v>86244</v>
       </c>
       <c r="O74">
-        <v>2233101</v>
+        <v>2247417</v>
       </c>
       <c r="P74">
-        <v>4684412</v>
+        <v>4689222</v>
       </c>
       <c r="Q74">
         <v>626236</v>

--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MANNA\Downloads\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B283BD09-EACB-4C7C-B90D-1F525DF32E2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
   <si>
     <t>S. No.</t>
   </si>
@@ -49,9 +48,6 @@
     <t>ERO/AERO Status</t>
   </si>
   <si>
-    <t>DSE with UP</t>
-  </si>
-  <si>
     <t>Hearing Held</t>
   </si>
   <si>
@@ -82,15 +78,6 @@
     <t>Parked For Final Publication w.r.t. Others</t>
   </si>
   <si>
-    <t>Electors having DSE with UP</t>
-  </si>
-  <si>
-    <t>Form 7 Generated</t>
-  </si>
-  <si>
-    <t>No Action Required</t>
-  </si>
-  <si>
     <t>25 - Haridwar</t>
   </si>
   <si>
@@ -304,13 +291,13 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Notice &amp; Hearing Report Last Updated On : 03-09-2026 17:56:59</t>
+    <t>Notice &amp; Hearing Report Last Updated On : 04-09-2026 09:56:59</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -341,8 +328,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -681,13 +668,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T74"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Q74"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -705,11 +692,8 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-    </row>
-    <row r="2" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -744,13 +728,8 @@
       </c>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
-      <c r="Q2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-    </row>
-    <row r="3" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -758,51 +737,42 @@
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" t="s">
         <v>10</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>11</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>12</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>13</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>14</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>15</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>16</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>17</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>18</v>
       </c>
-      <c r="P3" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R3" t="s">
-        <v>21</v>
-      </c>
-      <c r="S3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C4">
         <v>51528</v>
@@ -817,51 +787,42 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>50420</v>
+        <v>50740</v>
       </c>
       <c r="H4">
-        <v>1104</v>
+        <v>784</v>
       </c>
       <c r="I4">
         <v>4</v>
       </c>
       <c r="J4">
-        <v>2847</v>
+        <v>2707</v>
       </c>
       <c r="K4">
-        <v>320</v>
+        <v>281</v>
       </c>
       <c r="L4">
-        <v>14391</v>
+        <v>14753</v>
       </c>
       <c r="M4">
-        <v>544</v>
+        <v>641</v>
       </c>
       <c r="N4">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O4">
-        <v>43687</v>
+        <v>43712</v>
       </c>
       <c r="P4">
         <v>53812</v>
       </c>
-      <c r="Q4">
-        <v>12212</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C5">
         <v>53911</v>
@@ -876,51 +837,42 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>53663</v>
+        <v>53691</v>
       </c>
       <c r="H5">
-        <v>248</v>
+        <v>220</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>11307</v>
+        <v>11323</v>
       </c>
       <c r="M5">
         <v>674</v>
       </c>
       <c r="N5">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="O5">
-        <v>51040</v>
+        <v>51258</v>
       </c>
       <c r="P5">
         <v>74848</v>
       </c>
-      <c r="Q5">
-        <v>16108</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C6">
         <v>39773</v>
@@ -935,51 +887,42 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>38055</v>
+        <v>38188</v>
       </c>
       <c r="H6">
-        <v>1623</v>
+        <v>1448</v>
       </c>
       <c r="I6">
         <v>95</v>
       </c>
       <c r="J6">
-        <v>1454</v>
+        <v>513</v>
       </c>
       <c r="K6">
-        <v>538</v>
+        <v>286</v>
       </c>
       <c r="L6">
-        <v>4452</v>
+        <v>5383</v>
       </c>
       <c r="M6">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="N6">
-        <v>1204</v>
+        <v>1208</v>
       </c>
       <c r="O6">
-        <v>31703</v>
+        <v>31888</v>
       </c>
       <c r="P6">
         <v>71989</v>
       </c>
-      <c r="Q6">
-        <v>17830</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C7">
         <v>39463</v>
@@ -1003,42 +946,33 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>639</v>
+        <v>360</v>
       </c>
       <c r="K7">
-        <v>519</v>
+        <v>228</v>
       </c>
       <c r="L7">
-        <v>4997</v>
+        <v>5269</v>
       </c>
       <c r="M7">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="N7">
         <v>1983</v>
       </c>
       <c r="O7">
-        <v>34233</v>
+        <v>34810</v>
       </c>
       <c r="P7">
         <v>77581</v>
       </c>
-      <c r="Q7">
-        <v>20511</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C8">
         <v>40552</v>
@@ -1053,16 +987,16 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>40082</v>
+        <v>40131</v>
       </c>
       <c r="H8">
-        <v>470</v>
+        <v>421</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -1074,30 +1008,21 @@
         <v>163</v>
       </c>
       <c r="N8">
-        <v>1737</v>
+        <v>1778</v>
       </c>
       <c r="O8">
-        <v>32331</v>
+        <v>32521</v>
       </c>
       <c r="P8">
         <v>73458</v>
       </c>
-      <c r="Q8">
-        <v>20788</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C9">
         <v>43273</v>
@@ -1124,7 +1049,7 @@
         <v>1546</v>
       </c>
       <c r="K9">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="L9">
         <v>6050</v>
@@ -1133,30 +1058,21 @@
         <v>35</v>
       </c>
       <c r="N9">
-        <v>1277</v>
+        <v>1280</v>
       </c>
       <c r="O9">
-        <v>39519</v>
+        <v>39546</v>
       </c>
       <c r="P9">
         <v>72762</v>
       </c>
-      <c r="Q9">
-        <v>18141</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C10">
         <v>36576</v>
@@ -1183,7 +1099,7 @@
         <v>1492</v>
       </c>
       <c r="K10">
-        <v>1213</v>
+        <v>1240</v>
       </c>
       <c r="L10">
         <v>9504</v>
@@ -1195,27 +1111,18 @@
         <v>770</v>
       </c>
       <c r="O10">
-        <v>34209</v>
+        <v>34257</v>
       </c>
       <c r="P10">
         <v>53124</v>
       </c>
-      <c r="Q10">
-        <v>9498</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C11">
         <v>50998</v>
@@ -1242,7 +1149,7 @@
         <v>310</v>
       </c>
       <c r="K11">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="L11">
         <v>9623</v>
@@ -1259,22 +1166,13 @@
       <c r="P11">
         <v>84438</v>
       </c>
-      <c r="Q11">
-        <v>23477</v>
-      </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C12">
         <v>40739</v>
@@ -1289,51 +1187,42 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>40714</v>
+        <v>40739</v>
       </c>
       <c r="H12">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12">
-        <v>1002</v>
+        <v>929</v>
       </c>
       <c r="K12">
-        <v>928</v>
+        <v>845</v>
       </c>
       <c r="L12">
-        <v>8928</v>
+        <v>9012</v>
       </c>
       <c r="M12">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="N12">
-        <v>1023</v>
+        <v>1028</v>
       </c>
       <c r="O12">
-        <v>34067</v>
+        <v>34114</v>
       </c>
       <c r="P12">
         <v>66685</v>
       </c>
-      <c r="Q12">
-        <v>17786</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C13">
         <v>37031</v>
@@ -1357,13 +1246,13 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
       <c r="L13">
-        <v>7857</v>
+        <v>7864</v>
       </c>
       <c r="M13">
         <v>258</v>
@@ -1377,22 +1266,13 @@
       <c r="P13">
         <v>56565</v>
       </c>
-      <c r="Q13">
-        <v>16237</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C14">
         <v>48966</v>
@@ -1407,51 +1287,42 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>46891</v>
+        <v>47335</v>
       </c>
       <c r="H14">
-        <v>2002</v>
+        <v>1566</v>
       </c>
       <c r="I14">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="J14">
-        <v>7841</v>
+        <v>7843</v>
       </c>
       <c r="K14">
-        <v>4544</v>
+        <v>4911</v>
       </c>
       <c r="L14">
-        <v>7474</v>
+        <v>7518</v>
       </c>
       <c r="M14">
-        <v>945</v>
+        <v>950</v>
       </c>
       <c r="N14">
-        <v>3971</v>
+        <v>4093</v>
       </c>
       <c r="O14">
-        <v>28606</v>
+        <v>28880</v>
       </c>
       <c r="P14">
         <v>77955</v>
       </c>
-      <c r="Q14">
-        <v>19716</v>
-      </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C15">
         <v>42703</v>
@@ -1495,22 +1366,13 @@
       <c r="P15">
         <v>67178</v>
       </c>
-      <c r="Q15">
-        <v>4859</v>
-      </c>
-      <c r="R15">
-        <v>0</v>
-      </c>
-      <c r="S15">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C16">
         <v>25549</v>
@@ -1554,22 +1416,13 @@
       <c r="P16">
         <v>71673</v>
       </c>
-      <c r="Q16">
-        <v>5197</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C17">
         <v>27707</v>
@@ -1613,22 +1466,13 @@
       <c r="P17">
         <v>65458</v>
       </c>
-      <c r="Q17">
-        <v>5417</v>
-      </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C18">
         <v>47836</v>
@@ -1672,22 +1516,13 @@
       <c r="P18">
         <v>71475</v>
       </c>
-      <c r="Q18">
-        <v>6819</v>
-      </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
-      <c r="S18">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C19">
         <v>56490</v>
@@ -1731,22 +1566,13 @@
       <c r="P19">
         <v>106227</v>
       </c>
-      <c r="Q19">
-        <v>6135</v>
-      </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C20">
         <v>35022</v>
@@ -1790,22 +1616,13 @@
       <c r="P20">
         <v>75812</v>
       </c>
-      <c r="Q20">
-        <v>8984</v>
-      </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C21">
         <v>16962</v>
@@ -1849,22 +1666,13 @@
       <c r="P21">
         <v>62460</v>
       </c>
-      <c r="Q21">
-        <v>3868</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C22">
         <v>18668</v>
@@ -1908,22 +1716,13 @@
       <c r="P22">
         <v>64099</v>
       </c>
-      <c r="Q22">
-        <v>4848</v>
-      </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C23">
         <v>12020</v>
@@ -1967,22 +1766,13 @@
       <c r="P23">
         <v>57094</v>
       </c>
-      <c r="Q23">
-        <v>3541</v>
-      </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
-      <c r="S23">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C24">
         <v>14056</v>
@@ -2026,22 +1816,13 @@
       <c r="P24">
         <v>65629</v>
       </c>
-      <c r="Q24">
-        <v>3492</v>
-      </c>
-      <c r="R24">
-        <v>0</v>
-      </c>
-      <c r="S24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C25">
         <v>19266</v>
@@ -2085,22 +1866,13 @@
       <c r="P25">
         <v>57533</v>
       </c>
-      <c r="Q25">
-        <v>3231</v>
-      </c>
-      <c r="R25">
-        <v>0</v>
-      </c>
-      <c r="S25">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C26">
         <v>17557</v>
@@ -2144,22 +1916,13 @@
       <c r="P26">
         <v>66594</v>
       </c>
-      <c r="Q26">
-        <v>3333</v>
-      </c>
-      <c r="R26">
-        <v>0</v>
-      </c>
-      <c r="S26">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C27">
         <v>44276</v>
@@ -2174,16 +1937,16 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>43020</v>
+        <v>43069</v>
       </c>
       <c r="H27">
-        <v>1256</v>
+        <v>1207</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="K27">
         <v>0</v>
@@ -2195,30 +1958,21 @@
         <v>26</v>
       </c>
       <c r="N27">
-        <v>1406</v>
+        <v>1468</v>
       </c>
       <c r="O27">
-        <v>39942</v>
+        <v>40009</v>
       </c>
       <c r="P27">
         <v>63059</v>
       </c>
-      <c r="Q27">
-        <v>12669</v>
-      </c>
-      <c r="R27">
-        <v>0</v>
-      </c>
-      <c r="S27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C28">
         <v>54349</v>
@@ -2233,16 +1987,16 @@
         <v>0</v>
       </c>
       <c r="G28">
-        <v>53450</v>
+        <v>53475</v>
       </c>
       <c r="H28">
-        <v>899</v>
+        <v>874</v>
       </c>
       <c r="I28">
         <v>0</v>
       </c>
       <c r="J28">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="K28">
         <v>0</v>
@@ -2257,27 +2011,18 @@
         <v>2677</v>
       </c>
       <c r="O28">
-        <v>49276</v>
+        <v>49400</v>
       </c>
       <c r="P28">
         <v>80620</v>
       </c>
-      <c r="Q28">
-        <v>13995</v>
-      </c>
-      <c r="R28">
-        <v>0</v>
-      </c>
-      <c r="S28">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C29">
         <v>47111</v>
@@ -2321,22 +2066,13 @@
       <c r="P29">
         <v>83836</v>
       </c>
-      <c r="Q29">
-        <v>14229</v>
-      </c>
-      <c r="R29">
-        <v>0</v>
-      </c>
-      <c r="S29">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C30">
         <v>52653</v>
@@ -2351,16 +2087,16 @@
         <v>0</v>
       </c>
       <c r="G30">
-        <v>52282</v>
+        <v>52316</v>
       </c>
       <c r="H30">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I30">
-        <v>367</v>
+        <v>337</v>
       </c>
       <c r="J30">
-        <v>232</v>
+        <v>257</v>
       </c>
       <c r="K30">
         <v>0</v>
@@ -2375,27 +2111,18 @@
         <v>5276</v>
       </c>
       <c r="O30">
-        <v>46208</v>
+        <v>46217</v>
       </c>
       <c r="P30">
         <v>86933</v>
       </c>
-      <c r="Q30">
-        <v>12564</v>
-      </c>
-      <c r="R30">
-        <v>0</v>
-      </c>
-      <c r="S30">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C31">
         <v>91162</v>
@@ -2439,22 +2166,13 @@
       <c r="P31">
         <v>81643</v>
       </c>
-      <c r="Q31">
-        <v>14581</v>
-      </c>
-      <c r="R31">
-        <v>0</v>
-      </c>
-      <c r="S31">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C32">
         <v>46728</v>
@@ -2469,16 +2187,16 @@
         <v>0</v>
       </c>
       <c r="G32">
-        <v>44868</v>
+        <v>44991</v>
       </c>
       <c r="H32">
-        <v>1704</v>
+        <v>1581</v>
       </c>
       <c r="I32">
         <v>156</v>
       </c>
       <c r="J32">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K32">
         <v>0</v>
@@ -2490,30 +2208,21 @@
         <v>157</v>
       </c>
       <c r="N32">
-        <v>3845</v>
+        <v>3871</v>
       </c>
       <c r="O32">
-        <v>39882</v>
+        <v>40272</v>
       </c>
       <c r="P32">
-        <v>74811</v>
-      </c>
-      <c r="Q32">
-        <v>11379</v>
-      </c>
-      <c r="R32">
-        <v>0</v>
-      </c>
-      <c r="S32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>74810</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C33">
         <v>40230</v>
@@ -2528,19 +2237,19 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <v>39620</v>
+        <v>39744</v>
       </c>
       <c r="H33">
-        <v>602</v>
+        <v>482</v>
       </c>
       <c r="I33">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J33">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L33">
         <v>4921</v>
@@ -2549,30 +2258,21 @@
         <v>56</v>
       </c>
       <c r="N33">
-        <v>830</v>
+        <v>844</v>
       </c>
       <c r="O33">
-        <v>36770</v>
+        <v>36858</v>
       </c>
       <c r="P33">
         <v>76969</v>
       </c>
-      <c r="Q33">
-        <v>6678</v>
-      </c>
-      <c r="R33">
-        <v>0</v>
-      </c>
-      <c r="S33">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C34">
         <v>36542</v>
@@ -2587,16 +2287,16 @@
         <v>0</v>
       </c>
       <c r="G34">
-        <v>36360</v>
+        <v>36418</v>
       </c>
       <c r="H34">
-        <v>182</v>
+        <v>124</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
       <c r="J34">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="K34">
         <v>0</v>
@@ -2608,30 +2308,21 @@
         <v>54</v>
       </c>
       <c r="N34">
-        <v>1157</v>
+        <v>1210</v>
       </c>
       <c r="O34">
-        <v>33750</v>
+        <v>33770</v>
       </c>
       <c r="P34">
         <v>74624</v>
       </c>
-      <c r="Q34">
-        <v>7137</v>
-      </c>
-      <c r="R34">
-        <v>0</v>
-      </c>
-      <c r="S34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C35">
         <v>33564</v>
@@ -2646,16 +2337,16 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>32209</v>
+        <v>32211</v>
       </c>
       <c r="H35">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="I35">
         <v>0</v>
       </c>
       <c r="J35">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="K35">
         <v>0</v>
@@ -2667,7 +2358,7 @@
         <v>8</v>
       </c>
       <c r="N35">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="O35">
         <v>30713</v>
@@ -2675,22 +2366,13 @@
       <c r="P35">
         <v>76465</v>
       </c>
-      <c r="Q35">
-        <v>8879</v>
-      </c>
-      <c r="R35">
-        <v>0</v>
-      </c>
-      <c r="S35">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C36">
         <v>20905</v>
@@ -2734,22 +2416,13 @@
       <c r="P36">
         <v>60419</v>
       </c>
-      <c r="Q36">
-        <v>3855</v>
-      </c>
-      <c r="R36">
-        <v>0</v>
-      </c>
-      <c r="S36">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C37">
         <v>17692</v>
@@ -2793,22 +2466,13 @@
       <c r="P37">
         <v>57832</v>
       </c>
-      <c r="Q37">
-        <v>4036</v>
-      </c>
-      <c r="R37">
-        <v>0</v>
-      </c>
-      <c r="S37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C38">
         <v>29110</v>
@@ -2847,27 +2511,18 @@
         <v>635</v>
       </c>
       <c r="O38">
-        <v>28472</v>
+        <v>28474</v>
       </c>
       <c r="P38">
         <v>63038</v>
       </c>
-      <c r="Q38">
-        <v>5135</v>
-      </c>
-      <c r="R38">
-        <v>0</v>
-      </c>
-      <c r="S38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C39">
         <v>21367</v>
@@ -2911,22 +2566,13 @@
       <c r="P39">
         <v>71133</v>
       </c>
-      <c r="Q39">
-        <v>5903</v>
-      </c>
-      <c r="R39">
-        <v>0</v>
-      </c>
-      <c r="S39">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="40" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C40">
         <v>18905</v>
@@ -2970,22 +2616,13 @@
       <c r="P40">
         <v>73242</v>
       </c>
-      <c r="Q40">
-        <v>3824</v>
-      </c>
-      <c r="R40">
-        <v>0</v>
-      </c>
-      <c r="S40">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="41" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C41">
         <v>23521</v>
@@ -3029,22 +2666,13 @@
       <c r="P41">
         <v>85251</v>
       </c>
-      <c r="Q41">
-        <v>6015</v>
-      </c>
-      <c r="R41">
-        <v>0</v>
-      </c>
-      <c r="S41">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="42" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C42">
         <v>27565</v>
@@ -3088,22 +2716,13 @@
       <c r="P42">
         <v>68615</v>
       </c>
-      <c r="Q42">
-        <v>4708</v>
-      </c>
-      <c r="R42">
-        <v>0</v>
-      </c>
-      <c r="S42">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C43">
         <v>29700</v>
@@ -3147,22 +2766,13 @@
       <c r="P43">
         <v>63043</v>
       </c>
-      <c r="Q43">
-        <v>5219</v>
-      </c>
-      <c r="R43">
-        <v>0</v>
-      </c>
-      <c r="S43">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="44" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C44">
         <v>21900</v>
@@ -3206,22 +2816,13 @@
       <c r="P44">
         <v>68393</v>
       </c>
-      <c r="Q44">
-        <v>7659</v>
-      </c>
-      <c r="R44">
-        <v>0</v>
-      </c>
-      <c r="S44">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="45" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C45">
         <v>19935</v>
@@ -3236,16 +2837,16 @@
         <v>0</v>
       </c>
       <c r="G45">
-        <v>19908</v>
+        <v>19914</v>
       </c>
       <c r="H45">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I45">
         <v>0</v>
       </c>
       <c r="J45">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K45">
         <v>0</v>
@@ -3257,30 +2858,21 @@
         <v>13</v>
       </c>
       <c r="N45">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O45">
-        <v>19423</v>
+        <v>19464</v>
       </c>
       <c r="P45">
         <v>76002</v>
       </c>
-      <c r="Q45">
-        <v>6998</v>
-      </c>
-      <c r="R45">
-        <v>0</v>
-      </c>
-      <c r="S45">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="46" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C46">
         <v>21512</v>
@@ -3324,22 +2916,13 @@
       <c r="P46">
         <v>64160</v>
       </c>
-      <c r="Q46">
-        <v>7548</v>
-      </c>
-      <c r="R46">
-        <v>0</v>
-      </c>
-      <c r="S46">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="47" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C47">
         <v>22426</v>
@@ -3383,22 +2966,13 @@
       <c r="P47">
         <v>49875</v>
       </c>
-      <c r="Q47">
-        <v>5046</v>
-      </c>
-      <c r="R47">
-        <v>0</v>
-      </c>
-      <c r="S47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C48">
         <v>19641</v>
@@ -3442,22 +3016,13 @@
       <c r="P48">
         <v>54142</v>
       </c>
-      <c r="Q48">
-        <v>4623</v>
-      </c>
-      <c r="R48">
-        <v>0</v>
-      </c>
-      <c r="S48">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C49">
         <v>21651</v>
@@ -3501,22 +3066,13 @@
       <c r="P49">
         <v>55376</v>
       </c>
-      <c r="Q49">
-        <v>5057</v>
-      </c>
-      <c r="R49">
-        <v>0</v>
-      </c>
-      <c r="S49">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="50" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>47</v>
       </c>
       <c r="B50" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C50">
         <v>21936</v>
@@ -3560,22 +3116,13 @@
       <c r="P50">
         <v>63298</v>
       </c>
-      <c r="Q50">
-        <v>7292</v>
-      </c>
-      <c r="R50">
-        <v>0</v>
-      </c>
-      <c r="S50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>48</v>
       </c>
       <c r="B51" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C51">
         <v>23798</v>
@@ -3619,22 +3166,13 @@
       <c r="P51">
         <v>71754</v>
       </c>
-      <c r="Q51">
-        <v>7715</v>
-      </c>
-      <c r="R51">
-        <v>0</v>
-      </c>
-      <c r="S51">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="52" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>49</v>
       </c>
       <c r="B52" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C52">
         <v>21094</v>
@@ -3678,22 +3216,13 @@
       <c r="P52">
         <v>63987</v>
       </c>
-      <c r="Q52">
-        <v>5655</v>
-      </c>
-      <c r="R52">
-        <v>0</v>
-      </c>
-      <c r="S52">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>50</v>
       </c>
       <c r="B53" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C53">
         <v>19131</v>
@@ -3737,22 +3266,13 @@
       <c r="P53">
         <v>56306</v>
       </c>
-      <c r="Q53">
-        <v>6551</v>
-      </c>
-      <c r="R53">
-        <v>0</v>
-      </c>
-      <c r="S53">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>51</v>
       </c>
       <c r="B54" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C54">
         <v>20758</v>
@@ -3796,22 +3316,13 @@
       <c r="P54">
         <v>58440</v>
       </c>
-      <c r="Q54">
-        <v>7347</v>
-      </c>
-      <c r="R54">
-        <v>0</v>
-      </c>
-      <c r="S54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>52</v>
       </c>
       <c r="B55" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C55">
         <v>16022</v>
@@ -3855,22 +3366,13 @@
       <c r="P55">
         <v>58215</v>
       </c>
-      <c r="Q55">
-        <v>5098</v>
-      </c>
-      <c r="R55">
-        <v>0</v>
-      </c>
-      <c r="S55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>53</v>
       </c>
       <c r="B56" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C56">
         <v>19256</v>
@@ -3914,22 +3416,13 @@
       <c r="P56">
         <v>46365</v>
       </c>
-      <c r="Q56">
-        <v>4882</v>
-      </c>
-      <c r="R56">
-        <v>0</v>
-      </c>
-      <c r="S56">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="57" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>54</v>
       </c>
       <c r="B57" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C57">
         <v>21240</v>
@@ -3973,22 +3466,13 @@
       <c r="P57">
         <v>61556</v>
       </c>
-      <c r="Q57">
-        <v>6870</v>
-      </c>
-      <c r="R57">
-        <v>0</v>
-      </c>
-      <c r="S57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>55</v>
       </c>
       <c r="B58" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C58">
         <v>22819</v>
@@ -4027,27 +3511,18 @@
         <v>552</v>
       </c>
       <c r="O58">
-        <v>21732</v>
+        <v>22242</v>
       </c>
       <c r="P58">
         <v>57577</v>
       </c>
-      <c r="Q58">
-        <v>8884</v>
-      </c>
-      <c r="R58">
-        <v>0</v>
-      </c>
-      <c r="S58">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="59" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="59" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>56</v>
       </c>
       <c r="B59" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C59">
         <v>18776</v>
@@ -4091,22 +3566,13 @@
       <c r="P59">
         <v>60495</v>
       </c>
-      <c r="Q59">
-        <v>8028</v>
-      </c>
-      <c r="R59">
-        <v>0</v>
-      </c>
-      <c r="S59">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="60" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>57</v>
       </c>
       <c r="B60" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C60">
         <v>23749</v>
@@ -4150,22 +3616,13 @@
       <c r="P60">
         <v>70140</v>
       </c>
-      <c r="Q60">
-        <v>7415</v>
-      </c>
-      <c r="R60">
-        <v>0</v>
-      </c>
-      <c r="S60">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="61" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>58</v>
       </c>
       <c r="B61" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C61">
         <v>22069</v>
@@ -4209,22 +3666,13 @@
       <c r="P61">
         <v>55240</v>
       </c>
-      <c r="Q61">
-        <v>7927</v>
-      </c>
-      <c r="R61">
-        <v>1</v>
-      </c>
-      <c r="S61">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="62" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>59</v>
       </c>
       <c r="B62" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C62">
         <v>15800</v>
@@ -4248,7 +3696,7 @@
         <v>0</v>
       </c>
       <c r="J62">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K62">
         <v>0</v>
@@ -4268,22 +3716,13 @@
       <c r="P62">
         <v>51334</v>
       </c>
-      <c r="Q62">
-        <v>6917</v>
-      </c>
-      <c r="R62">
-        <v>0</v>
-      </c>
-      <c r="S62">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="63" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>60</v>
       </c>
       <c r="B63" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C63">
         <v>36754</v>
@@ -4307,13 +3746,13 @@
         <v>0</v>
       </c>
       <c r="J63">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K63">
         <v>0</v>
       </c>
       <c r="L63">
-        <v>10971</v>
+        <v>10975</v>
       </c>
       <c r="M63">
         <v>68</v>
@@ -4322,27 +3761,18 @@
         <v>930</v>
       </c>
       <c r="O63">
-        <v>35819</v>
+        <v>35820</v>
       </c>
       <c r="P63">
         <v>68691</v>
       </c>
-      <c r="Q63">
-        <v>9766</v>
-      </c>
-      <c r="R63">
-        <v>0</v>
-      </c>
-      <c r="S63">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="64" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>61</v>
       </c>
       <c r="B64" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C64">
         <v>42048</v>
@@ -4357,16 +3787,16 @@
         <v>0</v>
       </c>
       <c r="G64">
-        <v>42042</v>
+        <v>42048</v>
       </c>
       <c r="H64">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I64">
         <v>0</v>
       </c>
       <c r="J64">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="K64">
         <v>0</v>
@@ -4378,30 +3808,21 @@
         <v>8</v>
       </c>
       <c r="N64">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="O64">
-        <v>41287</v>
+        <v>41296</v>
       </c>
       <c r="P64">
         <v>60527</v>
       </c>
-      <c r="Q64">
-        <v>5985</v>
-      </c>
-      <c r="R64">
-        <v>0</v>
-      </c>
-      <c r="S64">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="65" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>62</v>
       </c>
       <c r="B65" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C65">
         <v>41389</v>
@@ -4416,51 +3837,42 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>40957</v>
+        <v>41057</v>
       </c>
       <c r="H65">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="I65">
-        <v>231</v>
+        <v>162</v>
       </c>
       <c r="J65">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="K65">
         <v>0</v>
       </c>
       <c r="L65">
-        <v>13123</v>
+        <v>13163</v>
       </c>
       <c r="M65">
         <v>2</v>
       </c>
       <c r="N65">
-        <v>2234</v>
+        <v>2285</v>
       </c>
       <c r="O65">
-        <v>34204</v>
+        <v>34206</v>
       </c>
       <c r="P65">
         <v>58103</v>
       </c>
-      <c r="Q65">
-        <v>13282</v>
-      </c>
-      <c r="R65">
-        <v>0</v>
-      </c>
-      <c r="S65">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="66" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="66" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>63</v>
       </c>
       <c r="B66" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C66">
         <v>67362</v>
@@ -4475,51 +3887,42 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>67215</v>
+        <v>67274</v>
       </c>
       <c r="H66">
-        <v>147</v>
+        <v>88</v>
       </c>
       <c r="I66">
         <v>0</v>
       </c>
       <c r="J66">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="K66">
         <v>0</v>
       </c>
       <c r="L66">
-        <v>13684</v>
+        <v>13690</v>
       </c>
       <c r="M66">
         <v>2</v>
       </c>
       <c r="N66">
-        <v>3955</v>
+        <v>4001</v>
       </c>
       <c r="O66">
-        <v>62931</v>
+        <v>63005</v>
       </c>
       <c r="P66">
         <v>93809</v>
       </c>
-      <c r="Q66">
-        <v>17742</v>
-      </c>
-      <c r="R66">
-        <v>0</v>
-      </c>
-      <c r="S66">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="67" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="67" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>64</v>
       </c>
       <c r="B67" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C67">
         <v>68828</v>
@@ -4534,16 +3937,16 @@
         <v>0</v>
       </c>
       <c r="G67">
-        <v>68807</v>
+        <v>68810</v>
       </c>
       <c r="H67">
         <v>0</v>
       </c>
       <c r="I67">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J67">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K67">
         <v>0</v>
@@ -4555,30 +3958,21 @@
         <v>10</v>
       </c>
       <c r="N67">
-        <v>3616</v>
+        <v>3628</v>
       </c>
       <c r="O67">
-        <v>65113</v>
+        <v>65109</v>
       </c>
       <c r="P67">
         <v>78022</v>
       </c>
-      <c r="Q67">
-        <v>9807</v>
-      </c>
-      <c r="R67">
-        <v>0</v>
-      </c>
-      <c r="S67">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="68" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="68" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>65</v>
       </c>
       <c r="B68" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C68">
         <v>65397</v>
@@ -4593,22 +3987,22 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>63831</v>
+        <v>63884</v>
       </c>
       <c r="H68">
-        <v>923</v>
+        <v>884</v>
       </c>
       <c r="I68">
-        <v>534</v>
+        <v>565</v>
       </c>
       <c r="J68">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="K68">
         <v>0</v>
       </c>
       <c r="L68">
-        <v>17589</v>
+        <v>17627</v>
       </c>
       <c r="M68">
         <v>2</v>
@@ -4617,27 +4011,18 @@
         <v>950</v>
       </c>
       <c r="O68">
-        <v>56011</v>
+        <v>56492</v>
       </c>
       <c r="P68">
         <v>71326</v>
       </c>
-      <c r="Q68">
-        <v>7850</v>
-      </c>
-      <c r="R68">
-        <v>0</v>
-      </c>
-      <c r="S68">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="69" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="69" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>66</v>
       </c>
       <c r="B69" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C69">
         <v>43938</v>
@@ -4652,16 +4037,16 @@
         <v>0</v>
       </c>
       <c r="G69">
-        <v>42924</v>
+        <v>43309</v>
       </c>
       <c r="H69">
-        <v>1001</v>
+        <v>625</v>
       </c>
       <c r="I69">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J69">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="K69">
         <v>0</v>
@@ -4673,30 +4058,21 @@
         <v>2</v>
       </c>
       <c r="N69">
-        <v>2050</v>
+        <v>2381</v>
       </c>
       <c r="O69">
-        <v>40671</v>
+        <v>40679</v>
       </c>
       <c r="P69">
         <v>36117</v>
       </c>
-      <c r="Q69">
-        <v>6528</v>
-      </c>
-      <c r="R69">
-        <v>0</v>
-      </c>
-      <c r="S69">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="70" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="70" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>67</v>
       </c>
       <c r="B70" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C70">
         <v>47711</v>
@@ -4735,27 +4111,18 @@
         <v>3246</v>
       </c>
       <c r="O70">
-        <v>44447</v>
+        <v>44449</v>
       </c>
       <c r="P70">
         <v>42039</v>
       </c>
-      <c r="Q70">
-        <v>5798</v>
-      </c>
-      <c r="R70">
-        <v>0</v>
-      </c>
-      <c r="S70">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="71" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>68</v>
       </c>
       <c r="B71" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C71">
         <v>50963</v>
@@ -4779,7 +4146,7 @@
         <v>1</v>
       </c>
       <c r="J71">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="K71">
         <v>0</v>
@@ -4791,30 +4158,21 @@
         <v>1</v>
       </c>
       <c r="N71">
-        <v>4386</v>
+        <v>4387</v>
       </c>
       <c r="O71">
-        <v>46178</v>
+        <v>46185</v>
       </c>
       <c r="P71">
         <v>48896</v>
       </c>
-      <c r="Q71">
-        <v>6782</v>
-      </c>
-      <c r="R71">
-        <v>0</v>
-      </c>
-      <c r="S71">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="72" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>69</v>
       </c>
       <c r="B72" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C72">
         <v>61543</v>
@@ -4829,16 +4187,16 @@
         <v>0</v>
       </c>
       <c r="G72">
-        <v>61436</v>
+        <v>61437</v>
       </c>
       <c r="H72">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I72">
         <v>61</v>
       </c>
       <c r="J72">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K72">
         <v>0</v>
@@ -4850,30 +4208,21 @@
         <v>9</v>
       </c>
       <c r="N72">
-        <v>3630</v>
+        <v>3631</v>
       </c>
       <c r="O72">
-        <v>56295</v>
+        <v>56402</v>
       </c>
       <c r="P72">
         <v>85505</v>
       </c>
-      <c r="Q72">
-        <v>12340</v>
-      </c>
-      <c r="R72">
-        <v>0</v>
-      </c>
-      <c r="S72">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="73" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>70</v>
       </c>
       <c r="B73" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C73">
         <v>58915</v>
@@ -4888,16 +4237,16 @@
         <v>0</v>
       </c>
       <c r="G73">
-        <v>58328</v>
+        <v>58442</v>
       </c>
       <c r="H73">
-        <v>543</v>
+        <v>473</v>
       </c>
       <c r="I73">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="J73">
-        <v>53</v>
+        <v>126</v>
       </c>
       <c r="K73">
         <v>0</v>
@@ -4909,27 +4258,18 @@
         <v>7</v>
       </c>
       <c r="N73">
-        <v>3224</v>
+        <v>3265</v>
       </c>
       <c r="O73">
-        <v>50298</v>
+        <v>50304</v>
       </c>
       <c r="P73">
         <v>67550</v>
       </c>
-      <c r="Q73">
-        <v>10010</v>
-      </c>
-      <c r="R73">
-        <v>0</v>
-      </c>
-      <c r="S73">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="74" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="74" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B74" s="1"/>
       <c r="C74">
@@ -4945,49 +4285,40 @@
         <v>2</v>
       </c>
       <c r="G74">
-        <v>2414138</v>
+        <v>2416279</v>
       </c>
       <c r="H74">
-        <v>14414</v>
+        <v>12412</v>
       </c>
       <c r="I74">
-        <v>1670</v>
+        <v>1582</v>
       </c>
       <c r="J74">
-        <v>19989</v>
+        <v>18853</v>
       </c>
       <c r="K74">
-        <v>9038</v>
+        <v>8781</v>
       </c>
       <c r="L74">
-        <v>599442</v>
+        <v>601246</v>
       </c>
       <c r="M74">
-        <v>4610</v>
+        <v>4750</v>
       </c>
       <c r="N74">
-        <v>86244</v>
+        <v>87066</v>
       </c>
       <c r="O74">
-        <v>2247417</v>
+        <v>2250952</v>
       </c>
       <c r="P74">
-        <v>4689222</v>
-      </c>
-      <c r="Q74">
-        <v>626236</v>
-      </c>
-      <c r="R74">
-        <v>1</v>
-      </c>
-      <c r="S74">
-        <v>3445</v>
+        <v>4689221</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="11">
     <mergeCell ref="A74:B74"/>
-    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
@@ -4997,11 +4328,10 @@
     <mergeCell ref="G2:I2"/>
     <mergeCell ref="J2:M2"/>
     <mergeCell ref="N2:P2"/>
-    <mergeCell ref="Q2:S2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A2:S74 B1:S1" numberStoredAsText="1"/>
+    <ignoredError sqref="A2:P74 B1:P1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
   <si>
     <t>S. No.</t>
   </si>
@@ -292,6 +292,18 @@
   </si>
   <si>
     <t>Notice &amp; Hearing Report Last Updated On : 04-09-2026 09:56:59</t>
+  </si>
+  <si>
+    <t>DSE with UP</t>
+  </si>
+  <si>
+    <t>Electors having DSE with UP</t>
+  </si>
+  <si>
+    <t>Form 7 Generated</t>
+  </si>
+  <si>
+    <t>No Action Required</t>
   </si>
 </sst>
 </file>
@@ -327,7 +339,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
@@ -669,73 +683,79 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q74"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:T74"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-    </row>
-    <row r="2" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1" t="s">
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-    </row>
-    <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="3"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
       <c r="G3" t="s">
         <v>9</v>
       </c>
@@ -766,8 +786,18 @@
       <c r="P3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q3" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="T3" s="3"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -816,8 +846,18 @@
       <c r="P4">
         <v>53812</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q4" s="3">
+        <v>12212</v>
+      </c>
+      <c r="R4" s="3">
+        <v>0</v>
+      </c>
+      <c r="S4" s="3">
+        <v>11</v>
+      </c>
+      <c r="T4" s="3"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
@@ -866,8 +906,18 @@
       <c r="P5">
         <v>74848</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q5" s="3">
+        <v>16108</v>
+      </c>
+      <c r="R5" s="3">
+        <v>0</v>
+      </c>
+      <c r="S5" s="3">
+        <v>30</v>
+      </c>
+      <c r="T5" s="3"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
@@ -916,8 +966,18 @@
       <c r="P6">
         <v>71989</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q6" s="3">
+        <v>17918</v>
+      </c>
+      <c r="R6" s="3">
+        <v>0</v>
+      </c>
+      <c r="S6" s="3">
+        <v>54</v>
+      </c>
+      <c r="T6" s="3"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4</v>
       </c>
@@ -966,8 +1026,18 @@
       <c r="P7">
         <v>77581</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q7" s="3">
+        <v>20905</v>
+      </c>
+      <c r="R7" s="3">
+        <v>0</v>
+      </c>
+      <c r="S7" s="3">
+        <v>8</v>
+      </c>
+      <c r="T7" s="3"/>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
@@ -1016,8 +1086,18 @@
       <c r="P8">
         <v>73458</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q8" s="3">
+        <v>20902</v>
+      </c>
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3">
+        <v>110</v>
+      </c>
+      <c r="T8" s="3"/>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6</v>
       </c>
@@ -1066,8 +1146,18 @@
       <c r="P9">
         <v>72762</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q9" s="3">
+        <v>18214</v>
+      </c>
+      <c r="R9" s="3">
+        <v>0</v>
+      </c>
+      <c r="S9" s="3">
+        <v>110</v>
+      </c>
+      <c r="T9" s="3"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>7</v>
       </c>
@@ -1116,8 +1206,18 @@
       <c r="P10">
         <v>53124</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q10" s="3">
+        <v>9511</v>
+      </c>
+      <c r="R10" s="3">
+        <v>0</v>
+      </c>
+      <c r="S10" s="3">
+        <v>2</v>
+      </c>
+      <c r="T10" s="3"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>8</v>
       </c>
@@ -1166,8 +1266,18 @@
       <c r="P11">
         <v>84438</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q11" s="3">
+        <v>23805</v>
+      </c>
+      <c r="R11" s="3">
+        <v>0</v>
+      </c>
+      <c r="S11" s="3">
+        <v>23</v>
+      </c>
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
@@ -1216,8 +1326,18 @@
       <c r="P12">
         <v>66685</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q12" s="3">
+        <v>17907</v>
+      </c>
+      <c r="R12" s="3">
+        <v>0</v>
+      </c>
+      <c r="S12" s="3">
+        <v>3</v>
+      </c>
+      <c r="T12" s="3"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
@@ -1266,8 +1386,18 @@
       <c r="P13">
         <v>56565</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q13" s="3">
+        <v>16822</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>109</v>
+      </c>
+      <c r="T13" s="3"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>11</v>
       </c>
@@ -1316,8 +1446,18 @@
       <c r="P14">
         <v>77955</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q14" s="3">
+        <v>20044</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
+        <v>174</v>
+      </c>
+      <c r="T14" s="3"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12</v>
       </c>
@@ -1366,8 +1506,18 @@
       <c r="P15">
         <v>67178</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q15" s="3">
+        <v>4892</v>
+      </c>
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3">
+        <v>50</v>
+      </c>
+      <c r="T15" s="3"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13</v>
       </c>
@@ -1416,8 +1566,18 @@
       <c r="P16">
         <v>71673</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q16" s="3">
+        <v>5208</v>
+      </c>
+      <c r="R16" s="3">
+        <v>0</v>
+      </c>
+      <c r="S16" s="3">
+        <v>47</v>
+      </c>
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>14</v>
       </c>
@@ -1466,8 +1626,18 @@
       <c r="P17">
         <v>65458</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q17" s="3">
+        <v>5418</v>
+      </c>
+      <c r="R17" s="3">
+        <v>0</v>
+      </c>
+      <c r="S17" s="3">
+        <v>105</v>
+      </c>
+      <c r="T17" s="1"/>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>15</v>
       </c>
@@ -1516,8 +1686,18 @@
       <c r="P18">
         <v>71475</v>
       </c>
-    </row>
-    <row r="19" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q18" s="3">
+        <v>6857</v>
+      </c>
+      <c r="R18" s="3">
+        <v>0</v>
+      </c>
+      <c r="S18" s="3">
+        <v>32</v>
+      </c>
+      <c r="T18" s="1"/>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>16</v>
       </c>
@@ -1566,8 +1746,18 @@
       <c r="P19">
         <v>106227</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q19" s="3">
+        <v>6151</v>
+      </c>
+      <c r="R19" s="3">
+        <v>0</v>
+      </c>
+      <c r="S19" s="3">
+        <v>37</v>
+      </c>
+      <c r="T19" s="1"/>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>17</v>
       </c>
@@ -1616,8 +1806,18 @@
       <c r="P20">
         <v>75812</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q20" s="3">
+        <v>9010</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
+        <v>72</v>
+      </c>
+      <c r="T20" s="1"/>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>18</v>
       </c>
@@ -1666,8 +1866,18 @@
       <c r="P21">
         <v>62460</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q21" s="3">
+        <v>3868</v>
+      </c>
+      <c r="R21" s="3">
+        <v>0</v>
+      </c>
+      <c r="S21" s="3">
+        <v>0</v>
+      </c>
+      <c r="T21" s="1"/>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>19</v>
       </c>
@@ -1716,8 +1926,18 @@
       <c r="P22">
         <v>64099</v>
       </c>
-    </row>
-    <row r="23" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q22" s="3">
+        <v>4866</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="1"/>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>20</v>
       </c>
@@ -1766,8 +1986,18 @@
       <c r="P23">
         <v>57094</v>
       </c>
-    </row>
-    <row r="24" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q23" s="3">
+        <v>3541</v>
+      </c>
+      <c r="R23" s="3">
+        <v>0</v>
+      </c>
+      <c r="S23" s="3">
+        <v>28</v>
+      </c>
+      <c r="T23" s="1"/>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>21</v>
       </c>
@@ -1816,8 +2046,18 @@
       <c r="P24">
         <v>65629</v>
       </c>
-    </row>
-    <row r="25" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q24" s="3">
+        <v>3496</v>
+      </c>
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="1"/>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>22</v>
       </c>
@@ -1866,8 +2106,18 @@
       <c r="P25">
         <v>57533</v>
       </c>
-    </row>
-    <row r="26" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q25" s="3">
+        <v>3232</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3">
+        <v>13</v>
+      </c>
+      <c r="T25" s="1"/>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23</v>
       </c>
@@ -1916,8 +2166,18 @@
       <c r="P26">
         <v>66594</v>
       </c>
-    </row>
-    <row r="27" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q26" s="3">
+        <v>3340</v>
+      </c>
+      <c r="R26" s="3">
+        <v>0</v>
+      </c>
+      <c r="S26" s="3">
+        <v>2</v>
+      </c>
+      <c r="T26" s="1"/>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>24</v>
       </c>
@@ -1966,8 +2226,18 @@
       <c r="P27">
         <v>63059</v>
       </c>
-    </row>
-    <row r="28" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q27" s="3">
+        <v>12669</v>
+      </c>
+      <c r="R27" s="3">
+        <v>0</v>
+      </c>
+      <c r="S27" s="3">
+        <v>0</v>
+      </c>
+      <c r="T27" s="1"/>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25</v>
       </c>
@@ -2016,8 +2286,18 @@
       <c r="P28">
         <v>80620</v>
       </c>
-    </row>
-    <row r="29" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q28" s="3">
+        <v>14114</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3">
+        <v>134</v>
+      </c>
+      <c r="T28" s="1"/>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26</v>
       </c>
@@ -2066,8 +2346,18 @@
       <c r="P29">
         <v>83836</v>
       </c>
-    </row>
-    <row r="30" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q29" s="3">
+        <v>14644</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
+        <v>22</v>
+      </c>
+      <c r="T29" s="1"/>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>27</v>
       </c>
@@ -2116,8 +2406,18 @@
       <c r="P30">
         <v>86933</v>
       </c>
-    </row>
-    <row r="31" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q30" s="3">
+        <v>12564</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>8</v>
+      </c>
+      <c r="T30" s="1"/>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>28</v>
       </c>
@@ -2166,8 +2466,18 @@
       <c r="P31">
         <v>81643</v>
       </c>
-    </row>
-    <row r="32" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q31" s="3">
+        <v>14710</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3">
+        <v>39</v>
+      </c>
+      <c r="T31" s="1"/>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>29</v>
       </c>
@@ -2216,8 +2526,18 @@
       <c r="P32">
         <v>74810</v>
       </c>
-    </row>
-    <row r="33" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q32" s="3">
+        <v>11379</v>
+      </c>
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="1"/>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>30</v>
       </c>
@@ -2266,8 +2586,18 @@
       <c r="P33">
         <v>76969</v>
       </c>
-    </row>
-    <row r="34" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q33" s="3">
+        <v>6678</v>
+      </c>
+      <c r="R33" s="3">
+        <v>0</v>
+      </c>
+      <c r="S33" s="3">
+        <v>19</v>
+      </c>
+      <c r="T33" s="1"/>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>31</v>
       </c>
@@ -2316,8 +2646,18 @@
       <c r="P34">
         <v>74624</v>
       </c>
-    </row>
-    <row r="35" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q34" s="3">
+        <v>7152</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+      <c r="T34" s="1"/>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32</v>
       </c>
@@ -2366,8 +2706,18 @@
       <c r="P35">
         <v>76465</v>
       </c>
-    </row>
-    <row r="36" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q35" s="3">
+        <v>8879</v>
+      </c>
+      <c r="R35" s="3">
+        <v>0</v>
+      </c>
+      <c r="S35" s="3">
+        <v>35</v>
+      </c>
+      <c r="T35" s="1"/>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>33</v>
       </c>
@@ -2416,8 +2766,18 @@
       <c r="P36">
         <v>60419</v>
       </c>
-    </row>
-    <row r="37" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q36" s="3">
+        <v>3869</v>
+      </c>
+      <c r="R36" s="3">
+        <v>0</v>
+      </c>
+      <c r="S36" s="3">
+        <v>2</v>
+      </c>
+      <c r="T36" s="1"/>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>34</v>
       </c>
@@ -2466,8 +2826,18 @@
       <c r="P37">
         <v>57832</v>
       </c>
-    </row>
-    <row r="38" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q37" s="3">
+        <v>4044</v>
+      </c>
+      <c r="R37" s="3">
+        <v>0</v>
+      </c>
+      <c r="S37" s="3">
+        <v>1</v>
+      </c>
+      <c r="T37" s="1"/>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>35</v>
       </c>
@@ -2516,8 +2886,18 @@
       <c r="P38">
         <v>63038</v>
       </c>
-    </row>
-    <row r="39" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q38" s="3">
+        <v>5160</v>
+      </c>
+      <c r="R38" s="3">
+        <v>0</v>
+      </c>
+      <c r="S38" s="3">
+        <v>0</v>
+      </c>
+      <c r="T38" s="1"/>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>36</v>
       </c>
@@ -2566,8 +2946,18 @@
       <c r="P39">
         <v>71133</v>
       </c>
-    </row>
-    <row r="40" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q39" s="3">
+        <v>5903</v>
+      </c>
+      <c r="R39" s="3">
+        <v>0</v>
+      </c>
+      <c r="S39" s="3">
+        <v>26</v>
+      </c>
+      <c r="T39" s="1"/>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>37</v>
       </c>
@@ -2616,8 +3006,18 @@
       <c r="P40">
         <v>73242</v>
       </c>
-    </row>
-    <row r="41" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q40" s="3">
+        <v>3824</v>
+      </c>
+      <c r="R40" s="3">
+        <v>0</v>
+      </c>
+      <c r="S40" s="3">
+        <v>61</v>
+      </c>
+      <c r="T40" s="1"/>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>38</v>
       </c>
@@ -2666,8 +3066,18 @@
       <c r="P41">
         <v>85251</v>
       </c>
-    </row>
-    <row r="42" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q41" s="3">
+        <v>6018</v>
+      </c>
+      <c r="R41" s="3">
+        <v>0</v>
+      </c>
+      <c r="S41" s="3">
+        <v>27</v>
+      </c>
+      <c r="T41" s="1"/>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>39</v>
       </c>
@@ -2716,8 +3126,18 @@
       <c r="P42">
         <v>68615</v>
       </c>
-    </row>
-    <row r="43" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q42" s="3">
+        <v>4713</v>
+      </c>
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3">
+        <v>8</v>
+      </c>
+      <c r="T42" s="1"/>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>40</v>
       </c>
@@ -2766,8 +3186,18 @@
       <c r="P43">
         <v>63043</v>
       </c>
-    </row>
-    <row r="44" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q43" s="3">
+        <v>5260</v>
+      </c>
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3">
+        <v>121</v>
+      </c>
+      <c r="T43" s="1"/>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>41</v>
       </c>
@@ -2816,8 +3246,18 @@
       <c r="P44">
         <v>68393</v>
       </c>
-    </row>
-    <row r="45" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q44" s="3">
+        <v>7659</v>
+      </c>
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3">
+        <v>20</v>
+      </c>
+      <c r="T44" s="1"/>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>42</v>
       </c>
@@ -2866,8 +3306,18 @@
       <c r="P45">
         <v>76002</v>
       </c>
-    </row>
-    <row r="46" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q45" s="3">
+        <v>6998</v>
+      </c>
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+      <c r="S45" s="3">
+        <v>129</v>
+      </c>
+      <c r="T45" s="1"/>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>43</v>
       </c>
@@ -2916,8 +3366,18 @@
       <c r="P46">
         <v>64160</v>
       </c>
-    </row>
-    <row r="47" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q46" s="3">
+        <v>7548</v>
+      </c>
+      <c r="R46" s="3">
+        <v>0</v>
+      </c>
+      <c r="S46" s="3">
+        <v>152</v>
+      </c>
+      <c r="T46" s="1"/>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>44</v>
       </c>
@@ -2966,8 +3426,18 @@
       <c r="P47">
         <v>49875</v>
       </c>
-    </row>
-    <row r="48" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q47" s="3">
+        <v>5046</v>
+      </c>
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+      <c r="T47" s="1"/>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>45</v>
       </c>
@@ -3016,8 +3486,18 @@
       <c r="P48">
         <v>54142</v>
       </c>
-    </row>
-    <row r="49" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q48" s="3">
+        <v>4623</v>
+      </c>
+      <c r="R48" s="3">
+        <v>0</v>
+      </c>
+      <c r="S48" s="3">
+        <v>9</v>
+      </c>
+      <c r="T48" s="1"/>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>46</v>
       </c>
@@ -3066,8 +3546,18 @@
       <c r="P49">
         <v>55376</v>
       </c>
-    </row>
-    <row r="50" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q49" s="3">
+        <v>5057</v>
+      </c>
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+      <c r="S49" s="3">
+        <v>4</v>
+      </c>
+      <c r="T49" s="1"/>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>47</v>
       </c>
@@ -3116,8 +3606,18 @@
       <c r="P50">
         <v>63298</v>
       </c>
-    </row>
-    <row r="51" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q50" s="3">
+        <v>7292</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3">
+        <v>1</v>
+      </c>
+      <c r="T50" s="1"/>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>48</v>
       </c>
@@ -3166,8 +3666,18 @@
       <c r="P51">
         <v>71754</v>
       </c>
-    </row>
-    <row r="52" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q51" s="3">
+        <v>7716</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3">
+        <v>40</v>
+      </c>
+      <c r="T51" s="1"/>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>49</v>
       </c>
@@ -3216,8 +3726,18 @@
       <c r="P52">
         <v>63987</v>
       </c>
-    </row>
-    <row r="53" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q52" s="3">
+        <v>5655</v>
+      </c>
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3">
+        <v>2</v>
+      </c>
+      <c r="T52" s="1"/>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>50</v>
       </c>
@@ -3266,8 +3786,18 @@
       <c r="P53">
         <v>56306</v>
       </c>
-    </row>
-    <row r="54" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q53" s="3">
+        <v>6551</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3">
+        <v>5</v>
+      </c>
+      <c r="T53" s="1"/>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>51</v>
       </c>
@@ -3316,8 +3846,18 @@
       <c r="P54">
         <v>58440</v>
       </c>
-    </row>
-    <row r="55" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q54" s="3">
+        <v>7378</v>
+      </c>
+      <c r="R54" s="3">
+        <v>0</v>
+      </c>
+      <c r="S54" s="3">
+        <v>1</v>
+      </c>
+      <c r="T54" s="1"/>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>52</v>
       </c>
@@ -3366,8 +3906,18 @@
       <c r="P55">
         <v>58215</v>
       </c>
-    </row>
-    <row r="56" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q55" s="3">
+        <v>5098</v>
+      </c>
+      <c r="R55" s="3">
+        <v>0</v>
+      </c>
+      <c r="S55" s="3">
+        <v>0</v>
+      </c>
+      <c r="T55" s="1"/>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>53</v>
       </c>
@@ -3416,8 +3966,18 @@
       <c r="P56">
         <v>46365</v>
       </c>
-    </row>
-    <row r="57" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q56" s="3">
+        <v>4882</v>
+      </c>
+      <c r="R56" s="3">
+        <v>0</v>
+      </c>
+      <c r="S56" s="3">
+        <v>30</v>
+      </c>
+      <c r="T56" s="1"/>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>54</v>
       </c>
@@ -3466,8 +4026,18 @@
       <c r="P57">
         <v>61556</v>
       </c>
-    </row>
-    <row r="58" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q57" s="3">
+        <v>6870</v>
+      </c>
+      <c r="R57" s="3">
+        <v>0</v>
+      </c>
+      <c r="S57" s="3">
+        <v>0</v>
+      </c>
+      <c r="T57" s="1"/>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>55</v>
       </c>
@@ -3516,8 +4086,18 @@
       <c r="P58">
         <v>57577</v>
       </c>
-    </row>
-    <row r="59" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q58" s="3">
+        <v>8916</v>
+      </c>
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
+        <v>64</v>
+      </c>
+      <c r="T58" s="1"/>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>56</v>
       </c>
@@ -3566,8 +4146,18 @@
       <c r="P59">
         <v>60495</v>
       </c>
-    </row>
-    <row r="60" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q59" s="3">
+        <v>8042</v>
+      </c>
+      <c r="R59" s="3">
+        <v>0</v>
+      </c>
+      <c r="S59" s="3">
+        <v>27</v>
+      </c>
+      <c r="T59" s="1"/>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>57</v>
       </c>
@@ -3616,8 +4206,18 @@
       <c r="P60">
         <v>70140</v>
       </c>
-    </row>
-    <row r="61" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q60" s="3">
+        <v>7432</v>
+      </c>
+      <c r="R60" s="3">
+        <v>0</v>
+      </c>
+      <c r="S60" s="3">
+        <v>32</v>
+      </c>
+      <c r="T60" s="1"/>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>58</v>
       </c>
@@ -3666,8 +4266,18 @@
       <c r="P61">
         <v>55240</v>
       </c>
-    </row>
-    <row r="62" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q61" s="3">
+        <v>7927</v>
+      </c>
+      <c r="R61" s="3">
+        <v>1</v>
+      </c>
+      <c r="S61" s="3">
+        <v>268</v>
+      </c>
+      <c r="T61" s="1"/>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>59</v>
       </c>
@@ -3716,8 +4326,18 @@
       <c r="P62">
         <v>51334</v>
       </c>
-    </row>
-    <row r="63" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q62" s="3">
+        <v>6956</v>
+      </c>
+      <c r="R62" s="3">
+        <v>0</v>
+      </c>
+      <c r="S62" s="3">
+        <v>100</v>
+      </c>
+      <c r="T62" s="1"/>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>60</v>
       </c>
@@ -3766,8 +4386,18 @@
       <c r="P63">
         <v>68691</v>
       </c>
-    </row>
-    <row r="64" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q63" s="3">
+        <v>9804</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>153</v>
+      </c>
+      <c r="T63" s="1"/>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>61</v>
       </c>
@@ -3816,8 +4446,18 @@
       <c r="P64">
         <v>60527</v>
       </c>
-    </row>
-    <row r="65" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q64" s="3">
+        <v>6002</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3">
+        <v>101</v>
+      </c>
+      <c r="T64" s="1"/>
+    </row>
+    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>62</v>
       </c>
@@ -3866,8 +4506,18 @@
       <c r="P65">
         <v>58103</v>
       </c>
-    </row>
-    <row r="66" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q65" s="3">
+        <v>13284</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3">
+        <v>138</v>
+      </c>
+      <c r="T65" s="1"/>
+    </row>
+    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>63</v>
       </c>
@@ -3916,8 +4566,18 @@
       <c r="P66">
         <v>93809</v>
       </c>
-    </row>
-    <row r="67" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q66" s="3">
+        <v>17742</v>
+      </c>
+      <c r="R66" s="3">
+        <v>0</v>
+      </c>
+      <c r="S66" s="3">
+        <v>52</v>
+      </c>
+      <c r="T66" s="1"/>
+    </row>
+    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>64</v>
       </c>
@@ -3966,8 +4626,18 @@
       <c r="P67">
         <v>78022</v>
       </c>
-    </row>
-    <row r="68" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q67" s="3">
+        <v>9810</v>
+      </c>
+      <c r="R67" s="3">
+        <v>0</v>
+      </c>
+      <c r="S67" s="3">
+        <v>116</v>
+      </c>
+      <c r="T67" s="1"/>
+    </row>
+    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>65</v>
       </c>
@@ -4016,8 +4686,18 @@
       <c r="P68">
         <v>71326</v>
       </c>
-    </row>
-    <row r="69" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q68" s="3">
+        <v>7850</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3">
+        <v>26</v>
+      </c>
+      <c r="T68" s="1"/>
+    </row>
+    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>66</v>
       </c>
@@ -4066,8 +4746,18 @@
       <c r="P69">
         <v>36117</v>
       </c>
-    </row>
-    <row r="70" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q69" s="3">
+        <v>6528</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3">
+        <v>47</v>
+      </c>
+      <c r="T69" s="1"/>
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>67</v>
       </c>
@@ -4116,8 +4806,18 @@
       <c r="P70">
         <v>42039</v>
       </c>
-    </row>
-    <row r="71" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q70" s="3">
+        <v>5798</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
+        <v>29</v>
+      </c>
+      <c r="T70" s="1"/>
+    </row>
+    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>68</v>
       </c>
@@ -4166,8 +4866,18 @@
       <c r="P71">
         <v>48896</v>
       </c>
-    </row>
-    <row r="72" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q71" s="3">
+        <v>6782</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3">
+        <v>235</v>
+      </c>
+      <c r="T71" s="1"/>
+    </row>
+    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>69</v>
       </c>
@@ -4216,8 +4926,18 @@
       <c r="P72">
         <v>85505</v>
       </c>
-    </row>
-    <row r="73" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q72" s="3">
+        <v>12373</v>
+      </c>
+      <c r="R72" s="3">
+        <v>0</v>
+      </c>
+      <c r="S72" s="3">
+        <v>79</v>
+      </c>
+      <c r="T72" s="1"/>
+    </row>
+    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>70</v>
       </c>
@@ -4266,12 +4986,22 @@
       <c r="P73">
         <v>67550</v>
       </c>
-    </row>
-    <row r="74" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
+      <c r="Q73" s="3">
+        <v>10016</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3">
+        <v>74</v>
+      </c>
+      <c r="T73" s="1"/>
+    </row>
+    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B74" s="1"/>
+      <c r="B74" s="2"/>
       <c r="C74">
         <v>2430387</v>
       </c>
@@ -4314,9 +5044,19 @@
       <c r="P74">
         <v>4689221</v>
       </c>
+      <c r="Q74" s="3">
+        <v>629442</v>
+      </c>
+      <c r="R74" s="3">
+        <v>1</v>
+      </c>
+      <c r="S74" s="3">
+        <v>3457</v>
+      </c>
+      <c r="T74" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="A74:B74"/>
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A2:A3"/>
@@ -4328,6 +5068,7 @@
     <mergeCell ref="G2:I2"/>
     <mergeCell ref="J2:M2"/>
     <mergeCell ref="N2:P2"/>
+    <mergeCell ref="Q2:S2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MANNA\Downloads\New folder\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B58BC206-27B9-46AD-B5FB-121DC723EE0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -291,7 +292,7 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Notice &amp; Hearing Report Last Updated On : 04-09-2026 09:56:59</t>
+    <t>Notice &amp; Hearing Report Last Updated On : 05-09-2026 09:56:58</t>
   </si>
   <si>
     <t>DSE with UP</t>
@@ -309,7 +310,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -339,11 +340,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -682,80 +681,79 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T74"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:S74"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2" t="s">
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2" t="s">
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2" t="s">
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="3"/>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+    </row>
+    <row r="3" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
       <c r="G3" t="s">
         <v>9</v>
       </c>
@@ -786,18 +784,17 @@
       <c r="P3" t="s">
         <v>18</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="Q3" t="s">
         <v>92</v>
       </c>
-      <c r="R3" s="3" t="s">
+      <c r="R3" t="s">
         <v>93</v>
       </c>
-      <c r="S3" s="3" t="s">
+      <c r="S3" t="s">
         <v>94</v>
       </c>
-      <c r="T3" s="3"/>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -817,47 +814,46 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>50740</v>
+        <v>51274</v>
       </c>
       <c r="H4">
-        <v>784</v>
+        <v>250</v>
       </c>
       <c r="I4">
         <v>4</v>
       </c>
       <c r="J4">
-        <v>2707</v>
+        <v>1828</v>
       </c>
       <c r="K4">
-        <v>281</v>
+        <v>365</v>
       </c>
       <c r="L4">
-        <v>14753</v>
+        <v>16111</v>
       </c>
       <c r="M4">
-        <v>641</v>
+        <v>671</v>
       </c>
       <c r="N4">
-        <v>534</v>
+        <v>632</v>
       </c>
       <c r="O4">
-        <v>43712</v>
+        <v>46109</v>
       </c>
       <c r="P4">
         <v>53812</v>
       </c>
-      <c r="Q4" s="3">
+      <c r="Q4">
         <v>12212</v>
       </c>
-      <c r="R4" s="3">
-        <v>0</v>
-      </c>
-      <c r="S4" s="3">
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
         <v>11</v>
       </c>
-      <c r="T4" s="3"/>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
@@ -877,47 +873,46 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>53691</v>
+        <v>53706</v>
       </c>
       <c r="H5">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>11323</v>
+        <v>11353</v>
       </c>
       <c r="M5">
-        <v>674</v>
+        <v>688</v>
       </c>
       <c r="N5">
-        <v>707</v>
+        <v>722</v>
       </c>
       <c r="O5">
-        <v>51258</v>
+        <v>51753</v>
       </c>
       <c r="P5">
         <v>74848</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="Q5">
         <v>16108</v>
       </c>
-      <c r="R5" s="3">
-        <v>0</v>
-      </c>
-      <c r="S5" s="3">
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
         <v>30</v>
       </c>
-      <c r="T5" s="3"/>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
@@ -937,47 +932,46 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>38188</v>
+        <v>38898</v>
       </c>
       <c r="H6">
-        <v>1448</v>
+        <v>738</v>
       </c>
       <c r="I6">
         <v>95</v>
       </c>
       <c r="J6">
-        <v>513</v>
+        <v>65</v>
       </c>
       <c r="K6">
-        <v>286</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>5383</v>
+        <v>5797</v>
       </c>
       <c r="M6">
-        <v>78</v>
+        <v>183</v>
       </c>
       <c r="N6">
-        <v>1208</v>
+        <v>1295</v>
       </c>
       <c r="O6">
-        <v>31888</v>
+        <v>32659</v>
       </c>
       <c r="P6">
         <v>71989</v>
       </c>
-      <c r="Q6" s="3">
-        <v>17918</v>
-      </c>
-      <c r="R6" s="3">
-        <v>0</v>
-      </c>
-      <c r="S6" s="3">
+      <c r="Q6">
+        <v>17830</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
         <v>54</v>
       </c>
-      <c r="T6" s="3"/>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4</v>
       </c>
@@ -1006,10 +1000,10 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="K7">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="L7">
         <v>5269</v>
@@ -1021,23 +1015,22 @@
         <v>1983</v>
       </c>
       <c r="O7">
-        <v>34810</v>
+        <v>34968</v>
       </c>
       <c r="P7">
         <v>77581</v>
       </c>
-      <c r="Q7" s="3">
-        <v>20905</v>
-      </c>
-      <c r="R7" s="3">
-        <v>0</v>
-      </c>
-      <c r="S7" s="3">
+      <c r="Q7">
+        <v>20511</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
         <v>8</v>
       </c>
-      <c r="T7" s="3"/>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
@@ -1057,16 +1050,16 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>40131</v>
+        <v>40434</v>
       </c>
       <c r="H8">
-        <v>421</v>
+        <v>118</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>112</v>
+        <v>158</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -1078,26 +1071,25 @@
         <v>163</v>
       </c>
       <c r="N8">
-        <v>1778</v>
+        <v>1848</v>
       </c>
       <c r="O8">
-        <v>32521</v>
+        <v>33126</v>
       </c>
       <c r="P8">
         <v>73458</v>
       </c>
-      <c r="Q8" s="3">
-        <v>20902</v>
-      </c>
-      <c r="R8" s="3">
-        <v>0</v>
-      </c>
-      <c r="S8" s="3">
+      <c r="Q8">
+        <v>20788</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
         <v>110</v>
       </c>
-      <c r="T8" s="3"/>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6</v>
       </c>
@@ -1117,47 +1109,46 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>43268</v>
+        <v>43273</v>
       </c>
       <c r="H9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>1546</v>
+        <v>478</v>
       </c>
       <c r="K9">
-        <v>898</v>
+        <v>380</v>
       </c>
       <c r="L9">
-        <v>6050</v>
+        <v>7111</v>
       </c>
       <c r="M9">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="N9">
         <v>1280</v>
       </c>
       <c r="O9">
-        <v>39546</v>
+        <v>40165</v>
       </c>
       <c r="P9">
         <v>72762</v>
       </c>
-      <c r="Q9" s="3">
-        <v>18214</v>
-      </c>
-      <c r="R9" s="3">
-        <v>0</v>
-      </c>
-      <c r="S9" s="3">
+      <c r="Q9">
+        <v>18141</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
         <v>110</v>
       </c>
-      <c r="T9" s="3"/>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>7</v>
       </c>
@@ -1186,38 +1177,37 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>1492</v>
+        <v>117</v>
       </c>
       <c r="K10">
-        <v>1240</v>
+        <v>112</v>
       </c>
       <c r="L10">
-        <v>9504</v>
+        <v>10789</v>
       </c>
       <c r="M10">
-        <v>111</v>
+        <v>166</v>
       </c>
       <c r="N10">
-        <v>770</v>
+        <v>775</v>
       </c>
       <c r="O10">
-        <v>34257</v>
+        <v>35268</v>
       </c>
       <c r="P10">
         <v>53124</v>
       </c>
-      <c r="Q10" s="3">
-        <v>9511</v>
-      </c>
-      <c r="R10" s="3">
-        <v>0</v>
-      </c>
-      <c r="S10" s="3">
+      <c r="Q10">
+        <v>9498</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
         <v>2</v>
       </c>
-      <c r="T10" s="3"/>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>8</v>
       </c>
@@ -1246,16 +1236,16 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>310</v>
+        <v>3</v>
       </c>
       <c r="K11">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="L11">
-        <v>9623</v>
+        <v>9923</v>
       </c>
       <c r="M11">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="N11">
         <v>1611</v>
@@ -1266,18 +1256,17 @@
       <c r="P11">
         <v>84438</v>
       </c>
-      <c r="Q11" s="3">
-        <v>23805</v>
-      </c>
-      <c r="R11" s="3">
-        <v>0</v>
-      </c>
-      <c r="S11" s="3">
+      <c r="Q11">
+        <v>23477</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
         <v>23</v>
       </c>
-      <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
@@ -1306,38 +1295,37 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>929</v>
+        <v>547</v>
       </c>
       <c r="K12">
-        <v>845</v>
+        <v>517</v>
       </c>
       <c r="L12">
-        <v>9012</v>
+        <v>9371</v>
       </c>
       <c r="M12">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="N12">
         <v>1028</v>
       </c>
       <c r="O12">
-        <v>34114</v>
+        <v>34616</v>
       </c>
       <c r="P12">
         <v>66685</v>
       </c>
-      <c r="Q12" s="3">
-        <v>17907</v>
-      </c>
-      <c r="R12" s="3">
-        <v>0</v>
-      </c>
-      <c r="S12" s="3">
+      <c r="Q12">
+        <v>17786</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
         <v>3</v>
       </c>
-      <c r="T12" s="3"/>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
@@ -1386,18 +1374,17 @@
       <c r="P13">
         <v>56565</v>
       </c>
-      <c r="Q13" s="3">
-        <v>16822</v>
-      </c>
-      <c r="R13" s="3">
-        <v>0</v>
-      </c>
-      <c r="S13" s="3">
-        <v>109</v>
-      </c>
-      <c r="T13" s="3"/>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="Q13">
+        <v>16237</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>11</v>
       </c>
@@ -1417,47 +1404,46 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>47335</v>
+        <v>47795</v>
       </c>
       <c r="H14">
-        <v>1566</v>
+        <v>1108</v>
       </c>
       <c r="I14">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="J14">
-        <v>7843</v>
+        <v>5924</v>
       </c>
       <c r="K14">
-        <v>4911</v>
+        <v>4228</v>
       </c>
       <c r="L14">
-        <v>7518</v>
+        <v>9466</v>
       </c>
       <c r="M14">
-        <v>950</v>
+        <v>971</v>
       </c>
       <c r="N14">
-        <v>4093</v>
+        <v>4467</v>
       </c>
       <c r="O14">
-        <v>28880</v>
+        <v>28883</v>
       </c>
       <c r="P14">
         <v>77955</v>
       </c>
-      <c r="Q14" s="3">
-        <v>20044</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3">
+      <c r="Q14">
+        <v>19716</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
         <v>174</v>
       </c>
-      <c r="T14" s="3"/>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12</v>
       </c>
@@ -1506,18 +1492,17 @@
       <c r="P15">
         <v>67178</v>
       </c>
-      <c r="Q15" s="3">
-        <v>4892</v>
-      </c>
-      <c r="R15" s="3">
-        <v>0</v>
-      </c>
-      <c r="S15" s="3">
+      <c r="Q15">
+        <v>4859</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
         <v>50</v>
       </c>
-      <c r="T15" s="3"/>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13</v>
       </c>
@@ -1566,18 +1551,17 @@
       <c r="P16">
         <v>71673</v>
       </c>
-      <c r="Q16" s="3">
-        <v>5208</v>
-      </c>
-      <c r="R16" s="3">
-        <v>0</v>
-      </c>
-      <c r="S16" s="3">
+      <c r="Q16">
+        <v>5197</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
         <v>47</v>
       </c>
-      <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>14</v>
       </c>
@@ -1618,26 +1602,25 @@
         <v>2</v>
       </c>
       <c r="N17">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="O17">
-        <v>27285</v>
+        <v>27282</v>
       </c>
       <c r="P17">
-        <v>65458</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>5418</v>
-      </c>
-      <c r="R17" s="3">
-        <v>0</v>
-      </c>
-      <c r="S17" s="3">
+        <v>65457</v>
+      </c>
+      <c r="Q17">
+        <v>5417</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
         <v>105</v>
       </c>
-      <c r="T17" s="1"/>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>15</v>
       </c>
@@ -1681,23 +1664,22 @@
         <v>1969</v>
       </c>
       <c r="O18">
-        <v>44492</v>
+        <v>44978</v>
       </c>
       <c r="P18">
         <v>71475</v>
       </c>
-      <c r="Q18" s="3">
-        <v>6857</v>
-      </c>
-      <c r="R18" s="3">
-        <v>0</v>
-      </c>
-      <c r="S18" s="3">
+      <c r="Q18">
+        <v>6819</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
         <v>32</v>
       </c>
-      <c r="T18" s="1"/>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>16</v>
       </c>
@@ -1746,18 +1728,17 @@
       <c r="P19">
         <v>106227</v>
       </c>
-      <c r="Q19" s="3">
-        <v>6151</v>
-      </c>
-      <c r="R19" s="3">
-        <v>0</v>
-      </c>
-      <c r="S19" s="3">
-        <v>37</v>
-      </c>
-      <c r="T19" s="1"/>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="Q19">
+        <v>6135</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>17</v>
       </c>
@@ -1806,18 +1787,17 @@
       <c r="P20">
         <v>75812</v>
       </c>
-      <c r="Q20" s="3">
-        <v>9010</v>
-      </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3">
-        <v>72</v>
-      </c>
-      <c r="T20" s="1"/>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="Q20">
+        <v>8984</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>18</v>
       </c>
@@ -1866,18 +1846,17 @@
       <c r="P21">
         <v>62460</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21">
         <v>3868</v>
       </c>
-      <c r="R21" s="3">
-        <v>0</v>
-      </c>
-      <c r="S21" s="3">
-        <v>0</v>
-      </c>
-      <c r="T21" s="1"/>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>19</v>
       </c>
@@ -1926,18 +1905,17 @@
       <c r="P22">
         <v>64099</v>
       </c>
-      <c r="Q22" s="3">
-        <v>4866</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
-      <c r="S22" s="3">
-        <v>0</v>
-      </c>
-      <c r="T22" s="1"/>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="Q22">
+        <v>4848</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>20</v>
       </c>
@@ -1986,18 +1964,17 @@
       <c r="P23">
         <v>57094</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23">
         <v>3541</v>
       </c>
-      <c r="R23" s="3">
-        <v>0</v>
-      </c>
-      <c r="S23" s="3">
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
         <v>28</v>
       </c>
-      <c r="T23" s="1"/>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>21</v>
       </c>
@@ -2046,18 +2023,17 @@
       <c r="P24">
         <v>65629</v>
       </c>
-      <c r="Q24" s="3">
-        <v>3496</v>
-      </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
-      <c r="T24" s="1"/>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="Q24">
+        <v>3492</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>22</v>
       </c>
@@ -2106,18 +2082,17 @@
       <c r="P25">
         <v>57533</v>
       </c>
-      <c r="Q25" s="3">
-        <v>3232</v>
-      </c>
-      <c r="R25" s="3">
-        <v>0</v>
-      </c>
-      <c r="S25" s="3">
+      <c r="Q25">
+        <v>3231</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
         <v>13</v>
       </c>
-      <c r="T25" s="1"/>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23</v>
       </c>
@@ -2166,18 +2141,17 @@
       <c r="P26">
         <v>66594</v>
       </c>
-      <c r="Q26" s="3">
-        <v>3340</v>
-      </c>
-      <c r="R26" s="3">
-        <v>0</v>
-      </c>
-      <c r="S26" s="3">
+      <c r="Q26">
+        <v>3333</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
         <v>2</v>
       </c>
-      <c r="T26" s="1"/>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>24</v>
       </c>
@@ -2197,16 +2171,16 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>43069</v>
+        <v>43381</v>
       </c>
       <c r="H27">
-        <v>1207</v>
+        <v>895</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27">
-        <v>269</v>
+        <v>313</v>
       </c>
       <c r="K27">
         <v>0</v>
@@ -2218,26 +2192,25 @@
         <v>26</v>
       </c>
       <c r="N27">
-        <v>1468</v>
+        <v>1734</v>
       </c>
       <c r="O27">
-        <v>40009</v>
+        <v>40080</v>
       </c>
       <c r="P27">
-        <v>63059</v>
-      </c>
-      <c r="Q27" s="3">
+        <v>63296</v>
+      </c>
+      <c r="Q27">
         <v>12669</v>
       </c>
-      <c r="R27" s="3">
-        <v>0</v>
-      </c>
-      <c r="S27" s="3">
-        <v>0</v>
-      </c>
-      <c r="T27" s="1"/>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25</v>
       </c>
@@ -2257,16 +2230,16 @@
         <v>0</v>
       </c>
       <c r="G28">
-        <v>53475</v>
+        <v>53519</v>
       </c>
       <c r="H28">
-        <v>874</v>
+        <v>830</v>
       </c>
       <c r="I28">
         <v>0</v>
       </c>
       <c r="J28">
-        <v>489</v>
+        <v>526</v>
       </c>
       <c r="K28">
         <v>0</v>
@@ -2281,23 +2254,22 @@
         <v>2677</v>
       </c>
       <c r="O28">
-        <v>49400</v>
+        <v>49418</v>
       </c>
       <c r="P28">
         <v>80620</v>
       </c>
-      <c r="Q28" s="3">
-        <v>14114</v>
-      </c>
-      <c r="R28" s="3">
-        <v>0</v>
-      </c>
-      <c r="S28" s="3">
-        <v>134</v>
-      </c>
-      <c r="T28" s="1"/>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="Q28">
+        <v>13995</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26</v>
       </c>
@@ -2326,7 +2298,7 @@
         <v>0</v>
       </c>
       <c r="J29">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="K29">
         <v>0</v>
@@ -2341,23 +2313,22 @@
         <v>4228</v>
       </c>
       <c r="O29">
-        <v>42161</v>
+        <v>42187</v>
       </c>
       <c r="P29">
         <v>83836</v>
       </c>
-      <c r="Q29" s="3">
-        <v>14644</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
-      <c r="S29" s="3">
+      <c r="Q29">
+        <v>14229</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
         <v>22</v>
       </c>
-      <c r="T29" s="1"/>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>27</v>
       </c>
@@ -2377,19 +2348,19 @@
         <v>0</v>
       </c>
       <c r="G30">
-        <v>52316</v>
+        <v>52458</v>
       </c>
       <c r="H30">
         <v>0</v>
       </c>
       <c r="I30">
-        <v>337</v>
+        <v>195</v>
       </c>
       <c r="J30">
-        <v>257</v>
+        <v>361</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L30">
         <v>11270</v>
@@ -2398,26 +2369,25 @@
         <v>246</v>
       </c>
       <c r="N30">
-        <v>5276</v>
+        <v>5284</v>
       </c>
       <c r="O30">
-        <v>46217</v>
+        <v>46247</v>
       </c>
       <c r="P30">
         <v>86933</v>
       </c>
-      <c r="Q30" s="3">
+      <c r="Q30">
         <v>12564</v>
       </c>
-      <c r="R30" s="3">
-        <v>0</v>
-      </c>
-      <c r="S30" s="3">
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
         <v>8</v>
       </c>
-      <c r="T30" s="1"/>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>28</v>
       </c>
@@ -2466,18 +2436,17 @@
       <c r="P31">
         <v>81643</v>
       </c>
-      <c r="Q31" s="3">
-        <v>14710</v>
-      </c>
-      <c r="R31" s="3">
-        <v>0</v>
-      </c>
-      <c r="S31" s="3">
+      <c r="Q31">
+        <v>14581</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
         <v>39</v>
       </c>
-      <c r="T31" s="1"/>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>29</v>
       </c>
@@ -2497,16 +2466,16 @@
         <v>0</v>
       </c>
       <c r="G32">
-        <v>44991</v>
+        <v>45894</v>
       </c>
       <c r="H32">
-        <v>1581</v>
+        <v>750</v>
       </c>
       <c r="I32">
-        <v>156</v>
+        <v>84</v>
       </c>
       <c r="J32">
-        <v>171</v>
+        <v>277</v>
       </c>
       <c r="K32">
         <v>0</v>
@@ -2518,26 +2487,25 @@
         <v>157</v>
       </c>
       <c r="N32">
-        <v>3871</v>
+        <v>4116</v>
       </c>
       <c r="O32">
-        <v>40272</v>
+        <v>41162</v>
       </c>
       <c r="P32">
         <v>74810</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32">
         <v>11379</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32" s="1"/>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>30</v>
       </c>
@@ -2557,16 +2525,16 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <v>39744</v>
+        <v>39910</v>
       </c>
       <c r="H33">
-        <v>482</v>
+        <v>317</v>
       </c>
       <c r="I33">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J33">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="K33">
         <v>2</v>
@@ -2578,26 +2546,25 @@
         <v>56</v>
       </c>
       <c r="N33">
-        <v>844</v>
+        <v>961</v>
       </c>
       <c r="O33">
-        <v>36858</v>
+        <v>37169</v>
       </c>
       <c r="P33">
         <v>76969</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33">
         <v>6678</v>
       </c>
-      <c r="R33" s="3">
-        <v>0</v>
-      </c>
-      <c r="S33" s="3">
+      <c r="R33">
+        <v>0</v>
+      </c>
+      <c r="S33">
         <v>19</v>
       </c>
-      <c r="T33" s="1"/>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>31</v>
       </c>
@@ -2617,19 +2584,19 @@
         <v>0</v>
       </c>
       <c r="G34">
-        <v>36418</v>
+        <v>36482</v>
       </c>
       <c r="H34">
-        <v>124</v>
+        <v>60</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
       <c r="J34">
-        <v>328</v>
+        <v>509</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L34">
         <v>11568</v>
@@ -2638,26 +2605,25 @@
         <v>54</v>
       </c>
       <c r="N34">
-        <v>1210</v>
+        <v>1267</v>
       </c>
       <c r="O34">
-        <v>33770</v>
+        <v>33780</v>
       </c>
       <c r="P34">
         <v>74624</v>
       </c>
-      <c r="Q34" s="3">
-        <v>7152</v>
-      </c>
-      <c r="R34" s="3">
-        <v>0</v>
-      </c>
-      <c r="S34" s="3">
-        <v>0</v>
-      </c>
-      <c r="T34" s="1"/>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="Q34">
+        <v>7137</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32</v>
       </c>
@@ -2677,16 +2643,16 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>32211</v>
+        <v>32586</v>
       </c>
       <c r="H35">
-        <v>1353</v>
+        <v>978</v>
       </c>
       <c r="I35">
         <v>0</v>
       </c>
       <c r="J35">
-        <v>215</v>
+        <v>547</v>
       </c>
       <c r="K35">
         <v>0</v>
@@ -2698,26 +2664,25 @@
         <v>8</v>
       </c>
       <c r="N35">
-        <v>986</v>
+        <v>1004</v>
       </c>
       <c r="O35">
-        <v>30713</v>
+        <v>30786</v>
       </c>
       <c r="P35">
         <v>76465</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35">
         <v>8879</v>
       </c>
-      <c r="R35" s="3">
-        <v>0</v>
-      </c>
-      <c r="S35" s="3">
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
         <v>35</v>
       </c>
-      <c r="T35" s="1"/>
-    </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>33</v>
       </c>
@@ -2766,18 +2731,17 @@
       <c r="P36">
         <v>60419</v>
       </c>
-      <c r="Q36" s="3">
-        <v>3869</v>
-      </c>
-      <c r="R36" s="3">
-        <v>0</v>
-      </c>
-      <c r="S36" s="3">
+      <c r="Q36">
+        <v>3855</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36">
         <v>2</v>
       </c>
-      <c r="T36" s="1"/>
-    </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>34</v>
       </c>
@@ -2826,18 +2790,17 @@
       <c r="P37">
         <v>57832</v>
       </c>
-      <c r="Q37" s="3">
-        <v>4044</v>
-      </c>
-      <c r="R37" s="3">
-        <v>0</v>
-      </c>
-      <c r="S37" s="3">
+      <c r="Q37">
+        <v>4036</v>
+      </c>
+      <c r="R37">
+        <v>0</v>
+      </c>
+      <c r="S37">
         <v>1</v>
       </c>
-      <c r="T37" s="1"/>
-    </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>35</v>
       </c>
@@ -2886,18 +2849,17 @@
       <c r="P38">
         <v>63038</v>
       </c>
-      <c r="Q38" s="3">
-        <v>5160</v>
-      </c>
-      <c r="R38" s="3">
-        <v>0</v>
-      </c>
-      <c r="S38" s="3">
-        <v>0</v>
-      </c>
-      <c r="T38" s="1"/>
-    </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="Q38">
+        <v>5135</v>
+      </c>
+      <c r="R38">
+        <v>0</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>36</v>
       </c>
@@ -2946,18 +2908,17 @@
       <c r="P39">
         <v>71133</v>
       </c>
-      <c r="Q39" s="3">
+      <c r="Q39">
         <v>5903</v>
       </c>
-      <c r="R39" s="3">
-        <v>0</v>
-      </c>
-      <c r="S39" s="3">
+      <c r="R39">
+        <v>0</v>
+      </c>
+      <c r="S39">
         <v>26</v>
       </c>
-      <c r="T39" s="1"/>
-    </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>37</v>
       </c>
@@ -3006,18 +2967,17 @@
       <c r="P40">
         <v>73242</v>
       </c>
-      <c r="Q40" s="3">
+      <c r="Q40">
         <v>3824</v>
       </c>
-      <c r="R40" s="3">
-        <v>0</v>
-      </c>
-      <c r="S40" s="3">
+      <c r="R40">
+        <v>0</v>
+      </c>
+      <c r="S40">
         <v>61</v>
       </c>
-      <c r="T40" s="1"/>
-    </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>38</v>
       </c>
@@ -3066,18 +3026,17 @@
       <c r="P41">
         <v>85251</v>
       </c>
-      <c r="Q41" s="3">
-        <v>6018</v>
-      </c>
-      <c r="R41" s="3">
-        <v>0</v>
-      </c>
-      <c r="S41" s="3">
+      <c r="Q41">
+        <v>6015</v>
+      </c>
+      <c r="R41">
+        <v>0</v>
+      </c>
+      <c r="S41">
         <v>27</v>
       </c>
-      <c r="T41" s="1"/>
-    </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>39</v>
       </c>
@@ -3126,18 +3085,17 @@
       <c r="P42">
         <v>68615</v>
       </c>
-      <c r="Q42" s="3">
-        <v>4713</v>
-      </c>
-      <c r="R42" s="3">
-        <v>0</v>
-      </c>
-      <c r="S42" s="3">
+      <c r="Q42">
+        <v>4708</v>
+      </c>
+      <c r="R42">
+        <v>0</v>
+      </c>
+      <c r="S42">
         <v>8</v>
       </c>
-      <c r="T42" s="1"/>
-    </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>40</v>
       </c>
@@ -3186,18 +3144,17 @@
       <c r="P43">
         <v>63043</v>
       </c>
-      <c r="Q43" s="3">
-        <v>5260</v>
-      </c>
-      <c r="R43" s="3">
-        <v>0</v>
-      </c>
-      <c r="S43" s="3">
+      <c r="Q43">
+        <v>5219</v>
+      </c>
+      <c r="R43">
+        <v>0</v>
+      </c>
+      <c r="S43">
         <v>121</v>
       </c>
-      <c r="T43" s="1"/>
-    </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>41</v>
       </c>
@@ -3246,18 +3203,17 @@
       <c r="P44">
         <v>68393</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="Q44">
         <v>7659</v>
       </c>
-      <c r="R44" s="3">
-        <v>0</v>
-      </c>
-      <c r="S44" s="3">
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
         <v>20</v>
       </c>
-      <c r="T44" s="1"/>
-    </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>42</v>
       </c>
@@ -3277,22 +3233,22 @@
         <v>0</v>
       </c>
       <c r="G45">
-        <v>19914</v>
+        <v>19932</v>
       </c>
       <c r="H45">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="I45">
         <v>0</v>
       </c>
       <c r="J45">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K45">
         <v>0</v>
       </c>
       <c r="L45">
-        <v>2243</v>
+        <v>2247</v>
       </c>
       <c r="M45">
         <v>13</v>
@@ -3301,23 +3257,22 @@
         <v>142</v>
       </c>
       <c r="O45">
-        <v>19464</v>
+        <v>19601</v>
       </c>
       <c r="P45">
         <v>76002</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45">
         <v>6998</v>
       </c>
-      <c r="R45" s="3">
-        <v>0</v>
-      </c>
-      <c r="S45" s="3">
+      <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45">
         <v>129</v>
       </c>
-      <c r="T45" s="1"/>
-    </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>43</v>
       </c>
@@ -3366,18 +3321,17 @@
       <c r="P46">
         <v>64160</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="Q46">
         <v>7548</v>
       </c>
-      <c r="R46" s="3">
-        <v>0</v>
-      </c>
-      <c r="S46" s="3">
+      <c r="R46">
+        <v>0</v>
+      </c>
+      <c r="S46">
         <v>152</v>
       </c>
-      <c r="T46" s="1"/>
-    </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>44</v>
       </c>
@@ -3426,18 +3380,17 @@
       <c r="P47">
         <v>49875</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="Q47">
         <v>5046</v>
       </c>
-      <c r="R47" s="3">
-        <v>0</v>
-      </c>
-      <c r="S47" s="3">
-        <v>0</v>
-      </c>
-      <c r="T47" s="1"/>
-    </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="R47">
+        <v>0</v>
+      </c>
+      <c r="S47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>45</v>
       </c>
@@ -3457,47 +3410,46 @@
         <v>2</v>
       </c>
       <c r="G48">
-        <v>19619</v>
+        <v>19638</v>
       </c>
       <c r="H48">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="I48">
         <v>1</v>
       </c>
       <c r="J48">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K48">
         <v>0</v>
       </c>
       <c r="L48">
-        <v>3786</v>
+        <v>3793</v>
       </c>
       <c r="M48">
         <v>4</v>
       </c>
       <c r="N48">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="O48">
-        <v>19342</v>
+        <v>19347</v>
       </c>
       <c r="P48">
         <v>54142</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="Q48">
         <v>4623</v>
       </c>
-      <c r="R48" s="3">
-        <v>0</v>
-      </c>
-      <c r="S48" s="3">
+      <c r="R48">
+        <v>0</v>
+      </c>
+      <c r="S48">
         <v>9</v>
       </c>
-      <c r="T48" s="1"/>
-    </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>46</v>
       </c>
@@ -3517,28 +3469,28 @@
         <v>0</v>
       </c>
       <c r="G49">
-        <v>21517</v>
+        <v>21565</v>
       </c>
       <c r="H49">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I49">
-        <v>109</v>
+        <v>69</v>
       </c>
       <c r="J49">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K49">
         <v>0</v>
       </c>
       <c r="L49">
-        <v>3604</v>
+        <v>3615</v>
       </c>
       <c r="M49">
         <v>0</v>
       </c>
       <c r="N49">
-        <v>506</v>
+        <v>554</v>
       </c>
       <c r="O49">
         <v>20144</v>
@@ -3546,18 +3498,17 @@
       <c r="P49">
         <v>55376</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="Q49">
         <v>5057</v>
       </c>
-      <c r="R49" s="3">
-        <v>0</v>
-      </c>
-      <c r="S49" s="3">
+      <c r="R49">
+        <v>0</v>
+      </c>
+      <c r="S49">
         <v>4</v>
       </c>
-      <c r="T49" s="1"/>
-    </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>47</v>
       </c>
@@ -3606,18 +3557,17 @@
       <c r="P50">
         <v>63298</v>
       </c>
-      <c r="Q50" s="3">
+      <c r="Q50">
         <v>7292</v>
       </c>
-      <c r="R50" s="3">
-        <v>0</v>
-      </c>
-      <c r="S50" s="3">
+      <c r="R50">
+        <v>0</v>
+      </c>
+      <c r="S50">
         <v>1</v>
       </c>
-      <c r="T50" s="1"/>
-    </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>48</v>
       </c>
@@ -3666,18 +3616,17 @@
       <c r="P51">
         <v>71754</v>
       </c>
-      <c r="Q51" s="3">
-        <v>7716</v>
-      </c>
-      <c r="R51" s="3">
-        <v>0</v>
-      </c>
-      <c r="S51" s="3">
+      <c r="Q51">
+        <v>7715</v>
+      </c>
+      <c r="R51">
+        <v>0</v>
+      </c>
+      <c r="S51">
         <v>40</v>
       </c>
-      <c r="T51" s="1"/>
-    </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>49</v>
       </c>
@@ -3726,18 +3675,17 @@
       <c r="P52">
         <v>63987</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="Q52">
         <v>5655</v>
       </c>
-      <c r="R52" s="3">
-        <v>0</v>
-      </c>
-      <c r="S52" s="3">
+      <c r="R52">
+        <v>0</v>
+      </c>
+      <c r="S52">
         <v>2</v>
       </c>
-      <c r="T52" s="1"/>
-    </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>50</v>
       </c>
@@ -3786,18 +3734,17 @@
       <c r="P53">
         <v>56306</v>
       </c>
-      <c r="Q53" s="3">
+      <c r="Q53">
         <v>6551</v>
       </c>
-      <c r="R53" s="3">
-        <v>0</v>
-      </c>
-      <c r="S53" s="3">
+      <c r="R53">
+        <v>0</v>
+      </c>
+      <c r="S53">
         <v>5</v>
       </c>
-      <c r="T53" s="1"/>
-    </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>51</v>
       </c>
@@ -3826,7 +3773,7 @@
         <v>0</v>
       </c>
       <c r="J54">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K54">
         <v>0</v>
@@ -3846,18 +3793,17 @@
       <c r="P54">
         <v>58440</v>
       </c>
-      <c r="Q54" s="3">
-        <v>7378</v>
-      </c>
-      <c r="R54" s="3">
-        <v>0</v>
-      </c>
-      <c r="S54" s="3">
+      <c r="Q54">
+        <v>7347</v>
+      </c>
+      <c r="R54">
+        <v>0</v>
+      </c>
+      <c r="S54">
         <v>1</v>
       </c>
-      <c r="T54" s="1"/>
-    </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>52</v>
       </c>
@@ -3886,7 +3832,7 @@
         <v>0</v>
       </c>
       <c r="J55">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="K55">
         <v>4</v>
@@ -3906,18 +3852,17 @@
       <c r="P55">
         <v>58215</v>
       </c>
-      <c r="Q55" s="3">
+      <c r="Q55">
         <v>5098</v>
       </c>
-      <c r="R55" s="3">
-        <v>0</v>
-      </c>
-      <c r="S55" s="3">
-        <v>0</v>
-      </c>
-      <c r="T55" s="1"/>
-    </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="R55">
+        <v>0</v>
+      </c>
+      <c r="S55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>53</v>
       </c>
@@ -3946,38 +3891,37 @@
         <v>0</v>
       </c>
       <c r="J56">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="K56">
         <v>0</v>
       </c>
       <c r="L56">
-        <v>3895</v>
+        <v>3984</v>
       </c>
       <c r="M56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N56">
         <v>425</v>
       </c>
       <c r="O56">
-        <v>18561</v>
+        <v>18700</v>
       </c>
       <c r="P56">
         <v>46365</v>
       </c>
-      <c r="Q56" s="3">
+      <c r="Q56">
         <v>4882</v>
       </c>
-      <c r="R56" s="3">
-        <v>0</v>
-      </c>
-      <c r="S56" s="3">
+      <c r="R56">
+        <v>0</v>
+      </c>
+      <c r="S56">
         <v>30</v>
       </c>
-      <c r="T56" s="1"/>
-    </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>54</v>
       </c>
@@ -4026,18 +3970,17 @@
       <c r="P57">
         <v>61556</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="Q57">
         <v>6870</v>
       </c>
-      <c r="R57" s="3">
-        <v>0</v>
-      </c>
-      <c r="S57" s="3">
-        <v>0</v>
-      </c>
-      <c r="T57" s="1"/>
-    </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="R57">
+        <v>0</v>
+      </c>
+      <c r="S57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>55</v>
       </c>
@@ -4086,18 +4029,17 @@
       <c r="P58">
         <v>57577</v>
       </c>
-      <c r="Q58" s="3">
-        <v>8916</v>
-      </c>
-      <c r="R58" s="3">
-        <v>0</v>
-      </c>
-      <c r="S58" s="3">
+      <c r="Q58">
+        <v>8884</v>
+      </c>
+      <c r="R58">
+        <v>0</v>
+      </c>
+      <c r="S58">
         <v>64</v>
       </c>
-      <c r="T58" s="1"/>
-    </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="59" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>56</v>
       </c>
@@ -4146,18 +4088,17 @@
       <c r="P59">
         <v>60495</v>
       </c>
-      <c r="Q59" s="3">
-        <v>8042</v>
-      </c>
-      <c r="R59" s="3">
-        <v>0</v>
-      </c>
-      <c r="S59" s="3">
+      <c r="Q59">
+        <v>8028</v>
+      </c>
+      <c r="R59">
+        <v>0</v>
+      </c>
+      <c r="S59">
         <v>27</v>
       </c>
-      <c r="T59" s="1"/>
-    </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>57</v>
       </c>
@@ -4206,18 +4147,17 @@
       <c r="P60">
         <v>70140</v>
       </c>
-      <c r="Q60" s="3">
-        <v>7432</v>
-      </c>
-      <c r="R60" s="3">
-        <v>0</v>
-      </c>
-      <c r="S60" s="3">
+      <c r="Q60">
+        <v>7415</v>
+      </c>
+      <c r="R60">
+        <v>0</v>
+      </c>
+      <c r="S60">
         <v>32</v>
       </c>
-      <c r="T60" s="1"/>
-    </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>58</v>
       </c>
@@ -4258,7 +4198,7 @@
         <v>37</v>
       </c>
       <c r="N61">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O61">
         <v>22032</v>
@@ -4266,18 +4206,17 @@
       <c r="P61">
         <v>55240</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="Q61">
         <v>7927</v>
       </c>
-      <c r="R61" s="3">
+      <c r="R61">
         <v>1</v>
       </c>
-      <c r="S61" s="3">
+      <c r="S61">
         <v>268</v>
       </c>
-      <c r="T61" s="1"/>
-    </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>59</v>
       </c>
@@ -4306,7 +4245,7 @@
         <v>0</v>
       </c>
       <c r="J62">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K62">
         <v>0</v>
@@ -4326,18 +4265,17 @@
       <c r="P62">
         <v>51334</v>
       </c>
-      <c r="Q62" s="3">
-        <v>6956</v>
-      </c>
-      <c r="R62" s="3">
-        <v>0</v>
-      </c>
-      <c r="S62" s="3">
+      <c r="Q62">
+        <v>6917</v>
+      </c>
+      <c r="R62">
+        <v>0</v>
+      </c>
+      <c r="S62">
         <v>100</v>
       </c>
-      <c r="T62" s="1"/>
-    </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>60</v>
       </c>
@@ -4386,18 +4324,17 @@
       <c r="P63">
         <v>68691</v>
       </c>
-      <c r="Q63" s="3">
-        <v>9804</v>
-      </c>
-      <c r="R63" s="3">
-        <v>0</v>
-      </c>
-      <c r="S63" s="3">
+      <c r="Q63">
+        <v>9766</v>
+      </c>
+      <c r="R63">
+        <v>0</v>
+      </c>
+      <c r="S63">
         <v>153</v>
       </c>
-      <c r="T63" s="1"/>
-    </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>61</v>
       </c>
@@ -4426,13 +4363,13 @@
         <v>0</v>
       </c>
       <c r="J64">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="K64">
         <v>0</v>
       </c>
       <c r="L64">
-        <v>9767</v>
+        <v>9784</v>
       </c>
       <c r="M64">
         <v>8</v>
@@ -4441,23 +4378,22 @@
         <v>478</v>
       </c>
       <c r="O64">
-        <v>41296</v>
+        <v>41375</v>
       </c>
       <c r="P64">
         <v>60527</v>
       </c>
-      <c r="Q64" s="3">
-        <v>6002</v>
-      </c>
-      <c r="R64" s="3">
-        <v>0</v>
-      </c>
-      <c r="S64" s="3">
+      <c r="Q64">
+        <v>5985</v>
+      </c>
+      <c r="R64">
+        <v>0</v>
+      </c>
+      <c r="S64">
         <v>101</v>
       </c>
-      <c r="T64" s="1"/>
-    </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>62</v>
       </c>
@@ -4477,16 +4413,16 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>41057</v>
+        <v>41089</v>
       </c>
       <c r="H65">
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="I65">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="J65">
-        <v>177</v>
+        <v>241</v>
       </c>
       <c r="K65">
         <v>0</v>
@@ -4498,26 +4434,25 @@
         <v>2</v>
       </c>
       <c r="N65">
-        <v>2285</v>
+        <v>2293</v>
       </c>
       <c r="O65">
-        <v>34206</v>
+        <v>34230</v>
       </c>
       <c r="P65">
         <v>58103</v>
       </c>
-      <c r="Q65" s="3">
-        <v>13284</v>
-      </c>
-      <c r="R65" s="3">
-        <v>0</v>
-      </c>
-      <c r="S65" s="3">
+      <c r="Q65">
+        <v>13282</v>
+      </c>
+      <c r="R65">
+        <v>0</v>
+      </c>
+      <c r="S65">
         <v>138</v>
       </c>
-      <c r="T65" s="1"/>
-    </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="66" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>63</v>
       </c>
@@ -4537,47 +4472,46 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>67274</v>
+        <v>67338</v>
       </c>
       <c r="H66">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="I66">
         <v>0</v>
       </c>
       <c r="J66">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="K66">
         <v>0</v>
       </c>
       <c r="L66">
-        <v>13690</v>
+        <v>13714</v>
       </c>
       <c r="M66">
         <v>2</v>
       </c>
       <c r="N66">
-        <v>4001</v>
+        <v>4014</v>
       </c>
       <c r="O66">
-        <v>63005</v>
+        <v>63126</v>
       </c>
       <c r="P66">
         <v>93809</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="Q66">
         <v>17742</v>
       </c>
-      <c r="R66" s="3">
-        <v>0</v>
-      </c>
-      <c r="S66" s="3">
+      <c r="R66">
+        <v>0</v>
+      </c>
+      <c r="S66">
         <v>52</v>
       </c>
-      <c r="T66" s="1"/>
-    </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="67" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>64</v>
       </c>
@@ -4597,47 +4531,46 @@
         <v>0</v>
       </c>
       <c r="G67">
-        <v>68810</v>
+        <v>68812</v>
       </c>
       <c r="H67">
         <v>0</v>
       </c>
       <c r="I67">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J67">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K67">
         <v>0</v>
       </c>
       <c r="L67">
-        <v>19419</v>
+        <v>19422</v>
       </c>
       <c r="M67">
         <v>10</v>
       </c>
       <c r="N67">
-        <v>3628</v>
+        <v>3632</v>
       </c>
       <c r="O67">
-        <v>65109</v>
+        <v>65105</v>
       </c>
       <c r="P67">
         <v>78022</v>
       </c>
-      <c r="Q67" s="3">
-        <v>9810</v>
-      </c>
-      <c r="R67" s="3">
-        <v>0</v>
-      </c>
-      <c r="S67" s="3">
+      <c r="Q67">
+        <v>9807</v>
+      </c>
+      <c r="R67">
+        <v>0</v>
+      </c>
+      <c r="S67">
         <v>116</v>
       </c>
-      <c r="T67" s="1"/>
-    </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="68" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>65</v>
       </c>
@@ -4657,16 +4590,16 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>63884</v>
+        <v>63903</v>
       </c>
       <c r="H68">
-        <v>884</v>
+        <v>869</v>
       </c>
       <c r="I68">
-        <v>565</v>
+        <v>625</v>
       </c>
       <c r="J68">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="K68">
         <v>0</v>
@@ -4678,26 +4611,25 @@
         <v>2</v>
       </c>
       <c r="N68">
-        <v>950</v>
+        <v>974</v>
       </c>
       <c r="O68">
-        <v>56492</v>
+        <v>56500</v>
       </c>
       <c r="P68">
         <v>71326</v>
       </c>
-      <c r="Q68" s="3">
+      <c r="Q68">
         <v>7850</v>
       </c>
-      <c r="R68" s="3">
-        <v>0</v>
-      </c>
-      <c r="S68" s="3">
+      <c r="R68">
+        <v>0</v>
+      </c>
+      <c r="S68">
         <v>26</v>
       </c>
-      <c r="T68" s="1"/>
-    </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="69" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>66</v>
       </c>
@@ -4717,47 +4649,46 @@
         <v>0</v>
       </c>
       <c r="G69">
-        <v>43309</v>
+        <v>43549</v>
       </c>
       <c r="H69">
-        <v>625</v>
+        <v>385</v>
       </c>
       <c r="I69">
         <v>4</v>
       </c>
       <c r="J69">
-        <v>67</v>
+        <v>171</v>
       </c>
       <c r="K69">
         <v>0</v>
       </c>
       <c r="L69">
-        <v>17705</v>
+        <v>17718</v>
       </c>
       <c r="M69">
         <v>2</v>
       </c>
       <c r="N69">
-        <v>2381</v>
+        <v>2463</v>
       </c>
       <c r="O69">
-        <v>40679</v>
+        <v>40737</v>
       </c>
       <c r="P69">
         <v>36117</v>
       </c>
-      <c r="Q69" s="3">
+      <c r="Q69">
         <v>6528</v>
       </c>
-      <c r="R69" s="3">
-        <v>0</v>
-      </c>
-      <c r="S69" s="3">
+      <c r="R69">
+        <v>0</v>
+      </c>
+      <c r="S69">
         <v>47</v>
       </c>
-      <c r="T69" s="1"/>
-    </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="70" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>67</v>
       </c>
@@ -4801,23 +4732,22 @@
         <v>3246</v>
       </c>
       <c r="O70">
-        <v>44449</v>
+        <v>44451</v>
       </c>
       <c r="P70">
         <v>42039</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="Q70">
         <v>5798</v>
       </c>
-      <c r="R70" s="3">
-        <v>0</v>
-      </c>
-      <c r="S70" s="3">
+      <c r="R70">
+        <v>0</v>
+      </c>
+      <c r="S70">
         <v>29</v>
       </c>
-      <c r="T70" s="1"/>
-    </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>68</v>
       </c>
@@ -4866,18 +4796,17 @@
       <c r="P71">
         <v>48896</v>
       </c>
-      <c r="Q71" s="3">
+      <c r="Q71">
         <v>6782</v>
       </c>
-      <c r="R71" s="3">
-        <v>0</v>
-      </c>
-      <c r="S71" s="3">
+      <c r="R71">
+        <v>0</v>
+      </c>
+      <c r="S71">
         <v>235</v>
       </c>
-      <c r="T71" s="1"/>
-    </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>69</v>
       </c>
@@ -4906,7 +4835,7 @@
         <v>61</v>
       </c>
       <c r="J72">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K72">
         <v>0</v>
@@ -4921,23 +4850,22 @@
         <v>3631</v>
       </c>
       <c r="O72">
-        <v>56402</v>
+        <v>56744</v>
       </c>
       <c r="P72">
         <v>85505</v>
       </c>
-      <c r="Q72" s="3">
-        <v>12373</v>
-      </c>
-      <c r="R72" s="3">
-        <v>0</v>
-      </c>
-      <c r="S72" s="3">
+      <c r="Q72">
+        <v>12340</v>
+      </c>
+      <c r="R72">
+        <v>0</v>
+      </c>
+      <c r="S72">
         <v>79</v>
       </c>
-      <c r="T72" s="1"/>
-    </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>70</v>
       </c>
@@ -4957,16 +4885,16 @@
         <v>0</v>
       </c>
       <c r="G73">
-        <v>58442</v>
+        <v>58748</v>
       </c>
       <c r="H73">
-        <v>473</v>
+        <v>167</v>
       </c>
       <c r="I73">
         <v>0</v>
       </c>
       <c r="J73">
-        <v>126</v>
+        <v>177</v>
       </c>
       <c r="K73">
         <v>0</v>
@@ -4978,30 +4906,29 @@
         <v>7</v>
       </c>
       <c r="N73">
-        <v>3265</v>
+        <v>3524</v>
       </c>
       <c r="O73">
-        <v>50304</v>
+        <v>50370</v>
       </c>
       <c r="P73">
         <v>67550</v>
       </c>
-      <c r="Q73" s="3">
-        <v>10016</v>
-      </c>
-      <c r="R73" s="3">
-        <v>0</v>
-      </c>
-      <c r="S73" s="3">
+      <c r="Q73">
+        <v>10010</v>
+      </c>
+      <c r="R73">
+        <v>0</v>
+      </c>
+      <c r="S73">
         <v>74</v>
       </c>
-      <c r="T73" s="1"/>
-    </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A74" s="2" t="s">
+    </row>
+    <row r="74" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B74" s="2"/>
+      <c r="B74" s="1"/>
       <c r="C74">
         <v>2430387</v>
       </c>
@@ -5015,49 +4942,49 @@
         <v>2</v>
       </c>
       <c r="G74">
-        <v>2416279</v>
+        <v>2421060</v>
       </c>
       <c r="H74">
-        <v>12412</v>
+        <v>7910</v>
       </c>
       <c r="I74">
-        <v>1582</v>
+        <v>1373</v>
       </c>
       <c r="J74">
-        <v>18853</v>
+        <v>13505</v>
       </c>
       <c r="K74">
-        <v>8781</v>
+        <v>5850</v>
       </c>
       <c r="L74">
-        <v>601246</v>
+        <v>608169</v>
       </c>
       <c r="M74">
-        <v>4750</v>
+        <v>5013</v>
       </c>
       <c r="N74">
-        <v>87066</v>
+        <v>88874</v>
       </c>
       <c r="O74">
-        <v>2250952</v>
+        <v>2260402</v>
       </c>
       <c r="P74">
-        <v>4689221</v>
-      </c>
-      <c r="Q74" s="3">
-        <v>629442</v>
-      </c>
-      <c r="R74" s="3">
+        <v>4689457</v>
+      </c>
+      <c r="Q74">
+        <v>626236</v>
+      </c>
+      <c r="R74">
         <v>1</v>
       </c>
-      <c r="S74" s="3">
-        <v>3457</v>
-      </c>
-      <c r="T74" s="1"/>
+      <c r="S74">
+        <v>3445</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="A74:B74"/>
+    <mergeCell ref="Q2:S2"/>
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
@@ -5068,7 +4995,6 @@
     <mergeCell ref="G2:I2"/>
     <mergeCell ref="J2:M2"/>
     <mergeCell ref="N2:P2"/>
-    <mergeCell ref="Q2:S2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B58BC206-27B9-46AD-B5FB-121DC723EE0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E51B67D4-4E24-4242-A31C-0CB4AE009F72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
   <si>
     <t>S. No.</t>
   </si>
@@ -292,19 +292,7 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Notice &amp; Hearing Report Last Updated On : 05-09-2026 09:56:58</t>
-  </si>
-  <si>
-    <t>DSE with UP</t>
-  </si>
-  <si>
-    <t>Electors having DSE with UP</t>
-  </si>
-  <si>
-    <t>Form 7 Generated</t>
-  </si>
-  <si>
-    <t>No Action Required</t>
+    <t>Notice &amp; Hearing Report Last Updated On : 07-09-2026 07:56:57</t>
   </si>
 </sst>
 </file>
@@ -682,10 +670,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S74"/>
+  <dimension ref="A1:Q74"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>90</v>
       </c>
@@ -706,7 +694,7 @@
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
     </row>
-    <row r="2" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -741,13 +729,8 @@
       </c>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
-      <c r="Q2" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-    </row>
-    <row r="3" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -784,17 +767,8 @@
       <c r="P3" t="s">
         <v>18</v>
       </c>
-      <c r="Q3" t="s">
-        <v>92</v>
-      </c>
-      <c r="R3" t="s">
-        <v>93</v>
-      </c>
-      <c r="S3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -814,46 +788,37 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>51274</v>
+        <v>51528</v>
       </c>
       <c r="H4">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>1828</v>
+        <v>3</v>
       </c>
       <c r="K4">
-        <v>365</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>16111</v>
+        <v>17792</v>
       </c>
       <c r="M4">
-        <v>671</v>
+        <v>948</v>
       </c>
       <c r="N4">
-        <v>632</v>
+        <v>854</v>
       </c>
       <c r="O4">
-        <v>46109</v>
+        <v>50323</v>
       </c>
       <c r="P4">
         <v>53812</v>
       </c>
-      <c r="Q4">
-        <v>12212</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
@@ -873,46 +838,37 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>53706</v>
+        <v>53911</v>
       </c>
       <c r="H5">
-        <v>205</v>
+        <v>0</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>11353</v>
+        <v>11380</v>
       </c>
       <c r="M5">
-        <v>688</v>
+        <v>749</v>
       </c>
       <c r="N5">
-        <v>722</v>
+        <v>854</v>
       </c>
       <c r="O5">
-        <v>51753</v>
+        <v>52482</v>
       </c>
       <c r="P5">
         <v>74848</v>
       </c>
-      <c r="Q5">
-        <v>16108</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
@@ -932,46 +888,37 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>38898</v>
+        <v>39665</v>
       </c>
       <c r="H6">
-        <v>738</v>
+        <v>63</v>
       </c>
       <c r="I6">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>5797</v>
+        <v>5875</v>
       </c>
       <c r="M6">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="N6">
-        <v>1295</v>
+        <v>1742</v>
       </c>
       <c r="O6">
-        <v>32659</v>
+        <v>33211</v>
       </c>
       <c r="P6">
         <v>71989</v>
       </c>
-      <c r="Q6">
-        <v>17830</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4</v>
       </c>
@@ -1000,37 +947,28 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>369</v>
+        <v>11</v>
       </c>
       <c r="K7">
-        <v>236</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>5269</v>
+        <v>5605</v>
       </c>
       <c r="M7">
-        <v>218</v>
+        <v>257</v>
       </c>
       <c r="N7">
-        <v>1983</v>
+        <v>1985</v>
       </c>
       <c r="O7">
-        <v>34968</v>
+        <v>35002</v>
       </c>
       <c r="P7">
         <v>77581</v>
       </c>
-      <c r="Q7">
-        <v>20511</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
@@ -1050,46 +988,37 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>40434</v>
+        <v>40552</v>
       </c>
       <c r="H8">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>14027</v>
+        <v>14223</v>
       </c>
       <c r="M8">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N8">
-        <v>1848</v>
+        <v>1871</v>
       </c>
       <c r="O8">
-        <v>33126</v>
+        <v>34519</v>
       </c>
       <c r="P8">
         <v>73458</v>
       </c>
-      <c r="Q8">
-        <v>20788</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6</v>
       </c>
@@ -1118,37 +1047,28 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <v>478</v>
+        <v>1</v>
       </c>
       <c r="K9">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="L9">
-        <v>7111</v>
+        <v>7741</v>
       </c>
       <c r="M9">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="N9">
-        <v>1280</v>
+        <v>1335</v>
       </c>
       <c r="O9">
-        <v>40165</v>
+        <v>41894</v>
       </c>
       <c r="P9">
         <v>72762</v>
       </c>
-      <c r="Q9">
-        <v>18141</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>7</v>
       </c>
@@ -1177,37 +1097,28 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>117</v>
+        <v>19</v>
       </c>
       <c r="K10">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="L10">
-        <v>10789</v>
+        <v>10912</v>
       </c>
       <c r="M10">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="N10">
-        <v>775</v>
+        <v>781</v>
       </c>
       <c r="O10">
-        <v>35268</v>
+        <v>35600</v>
       </c>
       <c r="P10">
         <v>53124</v>
       </c>
-      <c r="Q10">
-        <v>9498</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>8</v>
       </c>
@@ -1236,37 +1147,28 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>9923</v>
+        <v>9958</v>
       </c>
       <c r="M11">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="N11">
-        <v>1611</v>
+        <v>1703</v>
       </c>
       <c r="O11">
-        <v>48965</v>
+        <v>49300</v>
       </c>
       <c r="P11">
         <v>84438</v>
       </c>
-      <c r="Q11">
-        <v>23477</v>
-      </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
@@ -1295,37 +1197,28 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>547</v>
+        <v>51</v>
       </c>
       <c r="K12">
-        <v>517</v>
+        <v>0</v>
       </c>
       <c r="L12">
-        <v>9371</v>
+        <v>9922</v>
       </c>
       <c r="M12">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="N12">
-        <v>1028</v>
+        <v>1037</v>
       </c>
       <c r="O12">
-        <v>34616</v>
+        <v>38588</v>
       </c>
       <c r="P12">
         <v>66685</v>
       </c>
-      <c r="Q12">
-        <v>17786</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
@@ -1366,25 +1259,16 @@
         <v>258</v>
       </c>
       <c r="N13">
-        <v>3821</v>
+        <v>3822</v>
       </c>
       <c r="O13">
-        <v>33160</v>
+        <v>33195</v>
       </c>
       <c r="P13">
-        <v>56565</v>
-      </c>
-      <c r="Q13">
-        <v>16237</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>56564</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>11</v>
       </c>
@@ -1404,46 +1288,37 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>47795</v>
+        <v>48966</v>
       </c>
       <c r="H14">
-        <v>1108</v>
+        <v>0</v>
       </c>
       <c r="I14">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="J14">
-        <v>5924</v>
+        <v>18</v>
       </c>
       <c r="K14">
-        <v>4228</v>
+        <v>0</v>
       </c>
       <c r="L14">
-        <v>9466</v>
+        <v>14957</v>
       </c>
       <c r="M14">
-        <v>971</v>
+        <v>1407</v>
       </c>
       <c r="N14">
-        <v>4467</v>
+        <v>5545</v>
       </c>
       <c r="O14">
-        <v>28883</v>
+        <v>30269</v>
       </c>
       <c r="P14">
         <v>77955</v>
       </c>
-      <c r="Q14">
-        <v>19716</v>
-      </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12</v>
       </c>
@@ -1492,17 +1367,8 @@
       <c r="P15">
         <v>67178</v>
       </c>
-      <c r="Q15">
-        <v>4859</v>
-      </c>
-      <c r="R15">
-        <v>0</v>
-      </c>
-      <c r="S15">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13</v>
       </c>
@@ -1551,17 +1417,8 @@
       <c r="P16">
         <v>71673</v>
       </c>
-      <c r="Q16">
-        <v>5197</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>14</v>
       </c>
@@ -1610,17 +1467,8 @@
       <c r="P17">
         <v>65457</v>
       </c>
-      <c r="Q17">
-        <v>5417</v>
-      </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>15</v>
       </c>
@@ -1664,22 +1512,13 @@
         <v>1969</v>
       </c>
       <c r="O18">
-        <v>44978</v>
+        <v>45401</v>
       </c>
       <c r="P18">
         <v>71475</v>
       </c>
-      <c r="Q18">
-        <v>6819</v>
-      </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
-      <c r="S18">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>16</v>
       </c>
@@ -1714,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>15283</v>
+        <v>15284</v>
       </c>
       <c r="M19">
         <v>1</v>
@@ -1728,17 +1567,8 @@
       <c r="P19">
         <v>106227</v>
       </c>
-      <c r="Q19">
-        <v>6135</v>
-      </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>17</v>
       </c>
@@ -1787,17 +1617,8 @@
       <c r="P20">
         <v>75812</v>
       </c>
-      <c r="Q20">
-        <v>8984</v>
-      </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>18</v>
       </c>
@@ -1846,17 +1667,8 @@
       <c r="P21">
         <v>62460</v>
       </c>
-      <c r="Q21">
-        <v>3868</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>19</v>
       </c>
@@ -1905,17 +1717,8 @@
       <c r="P22">
         <v>64099</v>
       </c>
-      <c r="Q22">
-        <v>4848</v>
-      </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>20</v>
       </c>
@@ -1964,17 +1767,8 @@
       <c r="P23">
         <v>57094</v>
       </c>
-      <c r="Q23">
-        <v>3541</v>
-      </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
-      <c r="S23">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>21</v>
       </c>
@@ -2023,17 +1817,8 @@
       <c r="P24">
         <v>65629</v>
       </c>
-      <c r="Q24">
-        <v>3492</v>
-      </c>
-      <c r="R24">
-        <v>0</v>
-      </c>
-      <c r="S24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>22</v>
       </c>
@@ -2082,17 +1867,8 @@
       <c r="P25">
         <v>57533</v>
       </c>
-      <c r="Q25">
-        <v>3231</v>
-      </c>
-      <c r="R25">
-        <v>0</v>
-      </c>
-      <c r="S25">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23</v>
       </c>
@@ -2141,17 +1917,8 @@
       <c r="P26">
         <v>66594</v>
       </c>
-      <c r="Q26">
-        <v>3333</v>
-      </c>
-      <c r="R26">
-        <v>0</v>
-      </c>
-      <c r="S26">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>24</v>
       </c>
@@ -2171,46 +1938,37 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>43381</v>
+        <v>44071</v>
       </c>
       <c r="H27">
-        <v>895</v>
+        <v>205</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27">
-        <v>313</v>
+        <v>5</v>
       </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="L27">
-        <v>9404</v>
+        <v>9654</v>
       </c>
       <c r="M27">
-        <v>26</v>
+        <v>193</v>
       </c>
       <c r="N27">
-        <v>1734</v>
+        <v>2638</v>
       </c>
       <c r="O27">
-        <v>40080</v>
+        <v>40096</v>
       </c>
       <c r="P27">
-        <v>63296</v>
-      </c>
-      <c r="Q27">
-        <v>12669</v>
-      </c>
-      <c r="R27">
-        <v>0</v>
-      </c>
-      <c r="S27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>63288</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25</v>
       </c>
@@ -2230,46 +1988,37 @@
         <v>0</v>
       </c>
       <c r="G28">
-        <v>53519</v>
+        <v>54335</v>
       </c>
       <c r="H28">
-        <v>830</v>
+        <v>14</v>
       </c>
       <c r="I28">
         <v>0</v>
       </c>
       <c r="J28">
-        <v>526</v>
+        <v>75</v>
       </c>
       <c r="K28">
         <v>0</v>
       </c>
       <c r="L28">
-        <v>8311</v>
+        <v>8798</v>
       </c>
       <c r="M28">
-        <v>263</v>
+        <v>802</v>
       </c>
       <c r="N28">
-        <v>2677</v>
+        <v>3202</v>
       </c>
       <c r="O28">
-        <v>49418</v>
+        <v>50536</v>
       </c>
       <c r="P28">
         <v>80620</v>
       </c>
-      <c r="Q28">
-        <v>13995</v>
-      </c>
-      <c r="R28">
-        <v>0</v>
-      </c>
-      <c r="S28">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26</v>
       </c>
@@ -2298,16 +2047,16 @@
         <v>0</v>
       </c>
       <c r="J29">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="K29">
         <v>0</v>
       </c>
       <c r="L29">
-        <v>8651</v>
+        <v>8796</v>
       </c>
       <c r="M29">
-        <v>37</v>
+        <v>270</v>
       </c>
       <c r="N29">
         <v>4228</v>
@@ -2318,17 +2067,8 @@
       <c r="P29">
         <v>83836</v>
       </c>
-      <c r="Q29">
-        <v>14229</v>
-      </c>
-      <c r="R29">
-        <v>0</v>
-      </c>
-      <c r="S29">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>27</v>
       </c>
@@ -2348,46 +2088,37 @@
         <v>0</v>
       </c>
       <c r="G30">
-        <v>52458</v>
+        <v>52592</v>
       </c>
       <c r="H30">
         <v>0</v>
       </c>
       <c r="I30">
-        <v>195</v>
+        <v>61</v>
       </c>
       <c r="J30">
-        <v>361</v>
+        <v>0</v>
       </c>
       <c r="K30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L30">
-        <v>11270</v>
+        <v>11601</v>
       </c>
       <c r="M30">
-        <v>246</v>
+        <v>389</v>
       </c>
       <c r="N30">
         <v>5284</v>
       </c>
       <c r="O30">
-        <v>46247</v>
+        <v>47059</v>
       </c>
       <c r="P30">
         <v>86933</v>
       </c>
-      <c r="Q30">
-        <v>12564</v>
-      </c>
-      <c r="R30">
-        <v>0</v>
-      </c>
-      <c r="S30">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>28</v>
       </c>
@@ -2436,17 +2167,8 @@
       <c r="P31">
         <v>81643</v>
       </c>
-      <c r="Q31">
-        <v>14581</v>
-      </c>
-      <c r="R31">
-        <v>0</v>
-      </c>
-      <c r="S31">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>29</v>
       </c>
@@ -2466,46 +2188,37 @@
         <v>0</v>
       </c>
       <c r="G32">
-        <v>45894</v>
+        <v>46727</v>
       </c>
       <c r="H32">
-        <v>750</v>
+        <v>1</v>
       </c>
       <c r="I32">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="J32">
-        <v>277</v>
+        <v>13</v>
       </c>
       <c r="K32">
         <v>0</v>
       </c>
       <c r="L32">
-        <v>10301</v>
+        <v>10555</v>
       </c>
       <c r="M32">
-        <v>157</v>
+        <v>303</v>
       </c>
       <c r="N32">
-        <v>4116</v>
+        <v>4331</v>
       </c>
       <c r="O32">
-        <v>41162</v>
+        <v>41961</v>
       </c>
       <c r="P32">
         <v>74810</v>
       </c>
-      <c r="Q32">
-        <v>11379</v>
-      </c>
-      <c r="R32">
-        <v>0</v>
-      </c>
-      <c r="S32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>30</v>
       </c>
@@ -2525,46 +2238,37 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <v>39910</v>
+        <v>40199</v>
       </c>
       <c r="H33">
-        <v>317</v>
+        <v>31</v>
       </c>
       <c r="I33">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J33">
-        <v>234</v>
+        <v>0</v>
       </c>
       <c r="K33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L33">
-        <v>4921</v>
+        <v>5037</v>
       </c>
       <c r="M33">
-        <v>56</v>
+        <v>258</v>
       </c>
       <c r="N33">
-        <v>961</v>
+        <v>1200</v>
       </c>
       <c r="O33">
-        <v>37169</v>
+        <v>37505</v>
       </c>
       <c r="P33">
         <v>76969</v>
       </c>
-      <c r="Q33">
-        <v>6678</v>
-      </c>
-      <c r="R33">
-        <v>0</v>
-      </c>
-      <c r="S33">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>31</v>
       </c>
@@ -2584,46 +2288,37 @@
         <v>0</v>
       </c>
       <c r="G34">
-        <v>36482</v>
+        <v>36542</v>
       </c>
       <c r="H34">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
       <c r="J34">
-        <v>509</v>
+        <v>0</v>
       </c>
       <c r="K34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L34">
-        <v>11568</v>
+        <v>11887</v>
       </c>
       <c r="M34">
-        <v>54</v>
+        <v>339</v>
       </c>
       <c r="N34">
-        <v>1267</v>
+        <v>1301</v>
       </c>
       <c r="O34">
-        <v>33780</v>
+        <v>33815</v>
       </c>
       <c r="P34">
         <v>74624</v>
       </c>
-      <c r="Q34">
-        <v>7137</v>
-      </c>
-      <c r="R34">
-        <v>0</v>
-      </c>
-      <c r="S34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32</v>
       </c>
@@ -2643,46 +2338,37 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>32586</v>
+        <v>33282</v>
       </c>
       <c r="H35">
-        <v>978</v>
+        <v>282</v>
       </c>
       <c r="I35">
         <v>0</v>
       </c>
       <c r="J35">
-        <v>547</v>
+        <v>135</v>
       </c>
       <c r="K35">
         <v>0</v>
       </c>
       <c r="L35">
-        <v>6720</v>
+        <v>7593</v>
       </c>
       <c r="M35">
-        <v>8</v>
+        <v>234</v>
       </c>
       <c r="N35">
         <v>1004</v>
       </c>
       <c r="O35">
-        <v>30786</v>
+        <v>31854</v>
       </c>
       <c r="P35">
         <v>76465</v>
       </c>
-      <c r="Q35">
-        <v>8879</v>
-      </c>
-      <c r="R35">
-        <v>0</v>
-      </c>
-      <c r="S35">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>33</v>
       </c>
@@ -2731,17 +2417,8 @@
       <c r="P36">
         <v>60419</v>
       </c>
-      <c r="Q36">
-        <v>3855</v>
-      </c>
-      <c r="R36">
-        <v>0</v>
-      </c>
-      <c r="S36">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>34</v>
       </c>
@@ -2790,17 +2467,8 @@
       <c r="P37">
         <v>57832</v>
       </c>
-      <c r="Q37">
-        <v>4036</v>
-      </c>
-      <c r="R37">
-        <v>0</v>
-      </c>
-      <c r="S37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>35</v>
       </c>
@@ -2835,7 +2503,7 @@
         <v>0</v>
       </c>
       <c r="L38">
-        <v>5385</v>
+        <v>5386</v>
       </c>
       <c r="M38">
         <v>2</v>
@@ -2844,22 +2512,13 @@
         <v>635</v>
       </c>
       <c r="O38">
-        <v>28474</v>
+        <v>28475</v>
       </c>
       <c r="P38">
         <v>63038</v>
       </c>
-      <c r="Q38">
-        <v>5135</v>
-      </c>
-      <c r="R38">
-        <v>0</v>
-      </c>
-      <c r="S38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>36</v>
       </c>
@@ -2908,17 +2567,8 @@
       <c r="P39">
         <v>71133</v>
       </c>
-      <c r="Q39">
-        <v>5903</v>
-      </c>
-      <c r="R39">
-        <v>0</v>
-      </c>
-      <c r="S39">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="40" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>37</v>
       </c>
@@ -2967,17 +2617,8 @@
       <c r="P40">
         <v>73242</v>
       </c>
-      <c r="Q40">
-        <v>3824</v>
-      </c>
-      <c r="R40">
-        <v>0</v>
-      </c>
-      <c r="S40">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="41" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>38</v>
       </c>
@@ -3026,17 +2667,8 @@
       <c r="P41">
         <v>85251</v>
       </c>
-      <c r="Q41">
-        <v>6015</v>
-      </c>
-      <c r="R41">
-        <v>0</v>
-      </c>
-      <c r="S41">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="42" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>39</v>
       </c>
@@ -3085,17 +2717,8 @@
       <c r="P42">
         <v>68615</v>
       </c>
-      <c r="Q42">
-        <v>4708</v>
-      </c>
-      <c r="R42">
-        <v>0</v>
-      </c>
-      <c r="S42">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>40</v>
       </c>
@@ -3144,17 +2767,8 @@
       <c r="P43">
         <v>63043</v>
       </c>
-      <c r="Q43">
-        <v>5219</v>
-      </c>
-      <c r="R43">
-        <v>0</v>
-      </c>
-      <c r="S43">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="44" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>41</v>
       </c>
@@ -3203,17 +2817,8 @@
       <c r="P44">
         <v>68393</v>
       </c>
-      <c r="Q44">
-        <v>7659</v>
-      </c>
-      <c r="R44">
-        <v>0</v>
-      </c>
-      <c r="S44">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="45" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>42</v>
       </c>
@@ -3233,10 +2838,10 @@
         <v>0</v>
       </c>
       <c r="G45">
-        <v>19932</v>
+        <v>19935</v>
       </c>
       <c r="H45">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -3248,31 +2853,22 @@
         <v>0</v>
       </c>
       <c r="L45">
-        <v>2247</v>
+        <v>2254</v>
       </c>
       <c r="M45">
         <v>13</v>
       </c>
       <c r="N45">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="O45">
-        <v>19601</v>
+        <v>19786</v>
       </c>
       <c r="P45">
-        <v>76002</v>
-      </c>
-      <c r="Q45">
-        <v>6998</v>
-      </c>
-      <c r="R45">
-        <v>0</v>
-      </c>
-      <c r="S45">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="46" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>76287</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>43</v>
       </c>
@@ -3307,7 +2903,7 @@
         <v>0</v>
       </c>
       <c r="L46">
-        <v>8299</v>
+        <v>8303</v>
       </c>
       <c r="M46">
         <v>32</v>
@@ -3316,22 +2912,13 @@
         <v>276</v>
       </c>
       <c r="O46">
-        <v>21232</v>
+        <v>21236</v>
       </c>
       <c r="P46">
         <v>64160</v>
       </c>
-      <c r="Q46">
-        <v>7548</v>
-      </c>
-      <c r="R46">
-        <v>0</v>
-      </c>
-      <c r="S46">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="47" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>44</v>
       </c>
@@ -3380,17 +2967,8 @@
       <c r="P47">
         <v>49875</v>
       </c>
-      <c r="Q47">
-        <v>5046</v>
-      </c>
-      <c r="R47">
-        <v>0</v>
-      </c>
-      <c r="S47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>45</v>
       </c>
@@ -3404,22 +2982,22 @@
         <v>0</v>
       </c>
       <c r="E48">
-        <v>19639</v>
+        <v>19640</v>
       </c>
       <c r="F48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G48">
-        <v>19638</v>
+        <v>19641</v>
       </c>
       <c r="H48">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J48">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K48">
         <v>0</v>
@@ -3431,7 +3009,7 @@
         <v>4</v>
       </c>
       <c r="N48">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O48">
         <v>19347</v>
@@ -3439,17 +3017,8 @@
       <c r="P48">
         <v>54142</v>
       </c>
-      <c r="Q48">
-        <v>4623</v>
-      </c>
-      <c r="R48">
-        <v>0</v>
-      </c>
-      <c r="S48">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>46</v>
       </c>
@@ -3469,16 +3038,16 @@
         <v>0</v>
       </c>
       <c r="G49">
-        <v>21565</v>
+        <v>21649</v>
       </c>
       <c r="H49">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I49">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="J49">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K49">
         <v>0</v>
@@ -3490,25 +3059,16 @@
         <v>0</v>
       </c>
       <c r="N49">
-        <v>554</v>
+        <v>626</v>
       </c>
       <c r="O49">
-        <v>20144</v>
+        <v>21015</v>
       </c>
       <c r="P49">
         <v>55376</v>
       </c>
-      <c r="Q49">
-        <v>5057</v>
-      </c>
-      <c r="R49">
-        <v>0</v>
-      </c>
-      <c r="S49">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="50" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>47</v>
       </c>
@@ -3557,17 +3117,8 @@
       <c r="P50">
         <v>63298</v>
       </c>
-      <c r="Q50">
-        <v>7292</v>
-      </c>
-      <c r="R50">
-        <v>0</v>
-      </c>
-      <c r="S50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>48</v>
       </c>
@@ -3616,17 +3167,8 @@
       <c r="P51">
         <v>71754</v>
       </c>
-      <c r="Q51">
-        <v>7715</v>
-      </c>
-      <c r="R51">
-        <v>0</v>
-      </c>
-      <c r="S51">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="52" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>49</v>
       </c>
@@ -3675,17 +3217,8 @@
       <c r="P52">
         <v>63987</v>
       </c>
-      <c r="Q52">
-        <v>5655</v>
-      </c>
-      <c r="R52">
-        <v>0</v>
-      </c>
-      <c r="S52">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>50</v>
       </c>
@@ -3734,17 +3267,8 @@
       <c r="P53">
         <v>56306</v>
       </c>
-      <c r="Q53">
-        <v>6551</v>
-      </c>
-      <c r="R53">
-        <v>0</v>
-      </c>
-      <c r="S53">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>51</v>
       </c>
@@ -3773,13 +3297,13 @@
         <v>0</v>
       </c>
       <c r="J54">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K54">
         <v>0</v>
       </c>
       <c r="L54">
-        <v>2587</v>
+        <v>2599</v>
       </c>
       <c r="M54">
         <v>5</v>
@@ -3788,22 +3312,13 @@
         <v>391</v>
       </c>
       <c r="O54">
-        <v>20346</v>
+        <v>20354</v>
       </c>
       <c r="P54">
         <v>58440</v>
       </c>
-      <c r="Q54">
-        <v>7347</v>
-      </c>
-      <c r="R54">
-        <v>0</v>
-      </c>
-      <c r="S54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>52</v>
       </c>
@@ -3832,37 +3347,28 @@
         <v>0</v>
       </c>
       <c r="J55">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="K55">
         <v>4</v>
       </c>
       <c r="L55">
-        <v>2064</v>
+        <v>2090</v>
       </c>
       <c r="M55">
         <v>1</v>
       </c>
       <c r="N55">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="O55">
-        <v>15851</v>
+        <v>15874</v>
       </c>
       <c r="P55">
         <v>58215</v>
       </c>
-      <c r="Q55">
-        <v>5098</v>
-      </c>
-      <c r="R55">
-        <v>0</v>
-      </c>
-      <c r="S55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>53</v>
       </c>
@@ -3891,37 +3397,28 @@
         <v>0</v>
       </c>
       <c r="J56">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="K56">
         <v>0</v>
       </c>
       <c r="L56">
-        <v>3984</v>
+        <v>4033</v>
       </c>
       <c r="M56">
         <v>3</v>
       </c>
       <c r="N56">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="O56">
-        <v>18700</v>
+        <v>18747</v>
       </c>
       <c r="P56">
         <v>46365</v>
       </c>
-      <c r="Q56">
-        <v>4882</v>
-      </c>
-      <c r="R56">
-        <v>0</v>
-      </c>
-      <c r="S56">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="57" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>54</v>
       </c>
@@ -3970,17 +3467,8 @@
       <c r="P57">
         <v>61556</v>
       </c>
-      <c r="Q57">
-        <v>6870</v>
-      </c>
-      <c r="R57">
-        <v>0</v>
-      </c>
-      <c r="S57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>55</v>
       </c>
@@ -4009,13 +3497,13 @@
         <v>0</v>
       </c>
       <c r="J58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K58">
         <v>0</v>
       </c>
       <c r="L58">
-        <v>8098</v>
+        <v>8122</v>
       </c>
       <c r="M58">
         <v>10</v>
@@ -4024,22 +3512,13 @@
         <v>552</v>
       </c>
       <c r="O58">
-        <v>22242</v>
+        <v>22243</v>
       </c>
       <c r="P58">
         <v>57577</v>
       </c>
-      <c r="Q58">
-        <v>8884</v>
-      </c>
-      <c r="R58">
-        <v>0</v>
-      </c>
-      <c r="S58">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="59" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="59" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>56</v>
       </c>
@@ -4088,17 +3567,8 @@
       <c r="P59">
         <v>60495</v>
       </c>
-      <c r="Q59">
-        <v>8028</v>
-      </c>
-      <c r="R59">
-        <v>0</v>
-      </c>
-      <c r="S59">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="60" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>57</v>
       </c>
@@ -4127,13 +3597,13 @@
         <v>0</v>
       </c>
       <c r="J60">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K60">
         <v>0</v>
       </c>
       <c r="L60">
-        <v>5764</v>
+        <v>5790</v>
       </c>
       <c r="M60">
         <v>9</v>
@@ -4142,22 +3612,13 @@
         <v>324</v>
       </c>
       <c r="O60">
-        <v>23374</v>
+        <v>23400</v>
       </c>
       <c r="P60">
         <v>70140</v>
       </c>
-      <c r="Q60">
-        <v>7415</v>
-      </c>
-      <c r="R60">
-        <v>0</v>
-      </c>
-      <c r="S60">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="61" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>58</v>
       </c>
@@ -4186,13 +3647,13 @@
         <v>0</v>
       </c>
       <c r="J61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K61">
         <v>0</v>
       </c>
       <c r="L61">
-        <v>9976</v>
+        <v>9977</v>
       </c>
       <c r="M61">
         <v>37</v>
@@ -4201,22 +3662,13 @@
         <v>36</v>
       </c>
       <c r="O61">
-        <v>22032</v>
+        <v>22033</v>
       </c>
       <c r="P61">
         <v>55240</v>
       </c>
-      <c r="Q61">
-        <v>7927</v>
-      </c>
-      <c r="R61">
-        <v>1</v>
-      </c>
-      <c r="S61">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="62" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>59</v>
       </c>
@@ -4245,13 +3697,13 @@
         <v>0</v>
       </c>
       <c r="J62">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K62">
         <v>0</v>
       </c>
       <c r="L62">
-        <v>4197</v>
+        <v>4214</v>
       </c>
       <c r="M62">
         <v>19</v>
@@ -4260,22 +3712,13 @@
         <v>494</v>
       </c>
       <c r="O62">
-        <v>15289</v>
+        <v>15306</v>
       </c>
       <c r="P62">
         <v>51334</v>
       </c>
-      <c r="Q62">
-        <v>6917</v>
-      </c>
-      <c r="R62">
-        <v>0</v>
-      </c>
-      <c r="S62">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="63" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>60</v>
       </c>
@@ -4324,17 +3767,8 @@
       <c r="P63">
         <v>68691</v>
       </c>
-      <c r="Q63">
-        <v>9766</v>
-      </c>
-      <c r="R63">
-        <v>0</v>
-      </c>
-      <c r="S63">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="64" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>61</v>
       </c>
@@ -4363,37 +3797,28 @@
         <v>0</v>
       </c>
       <c r="J64">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="K64">
         <v>0</v>
       </c>
       <c r="L64">
-        <v>9784</v>
+        <v>9820</v>
       </c>
       <c r="M64">
         <v>8</v>
       </c>
       <c r="N64">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="O64">
-        <v>41375</v>
+        <v>41401</v>
       </c>
       <c r="P64">
         <v>60527</v>
       </c>
-      <c r="Q64">
-        <v>5985</v>
-      </c>
-      <c r="R64">
-        <v>0</v>
-      </c>
-      <c r="S64">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="65" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>62</v>
       </c>
@@ -4413,46 +3838,37 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>41089</v>
+        <v>41272</v>
       </c>
       <c r="H65">
-        <v>148</v>
+        <v>104</v>
       </c>
       <c r="I65">
-        <v>152</v>
+        <v>13</v>
       </c>
       <c r="J65">
-        <v>241</v>
+        <v>23</v>
       </c>
       <c r="K65">
         <v>0</v>
       </c>
       <c r="L65">
-        <v>13163</v>
+        <v>13402</v>
       </c>
       <c r="M65">
         <v>2</v>
       </c>
       <c r="N65">
-        <v>2293</v>
+        <v>2395</v>
       </c>
       <c r="O65">
-        <v>34230</v>
+        <v>34543</v>
       </c>
       <c r="P65">
         <v>58103</v>
       </c>
-      <c r="Q65">
-        <v>13282</v>
-      </c>
-      <c r="R65">
-        <v>0</v>
-      </c>
-      <c r="S65">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="66" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="66" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>63</v>
       </c>
@@ -4472,46 +3888,37 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>67338</v>
+        <v>67362</v>
       </c>
       <c r="H66">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="I66">
         <v>0</v>
       </c>
       <c r="J66">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K66">
         <v>0</v>
       </c>
       <c r="L66">
-        <v>13714</v>
+        <v>13731</v>
       </c>
       <c r="M66">
         <v>2</v>
       </c>
       <c r="N66">
-        <v>4014</v>
+        <v>4021</v>
       </c>
       <c r="O66">
-        <v>63126</v>
+        <v>63158</v>
       </c>
       <c r="P66">
         <v>93809</v>
       </c>
-      <c r="Q66">
-        <v>17742</v>
-      </c>
-      <c r="R66">
-        <v>0</v>
-      </c>
-      <c r="S66">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="67" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="67" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>64</v>
       </c>
@@ -4531,46 +3938,37 @@
         <v>0</v>
       </c>
       <c r="G67">
-        <v>68812</v>
+        <v>68828</v>
       </c>
       <c r="H67">
         <v>0</v>
       </c>
       <c r="I67">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J67">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K67">
         <v>0</v>
       </c>
       <c r="L67">
-        <v>19422</v>
+        <v>19450</v>
       </c>
       <c r="M67">
         <v>10</v>
       </c>
       <c r="N67">
-        <v>3632</v>
+        <v>3638</v>
       </c>
       <c r="O67">
-        <v>65105</v>
+        <v>65129</v>
       </c>
       <c r="P67">
         <v>78022</v>
       </c>
-      <c r="Q67">
-        <v>9807</v>
-      </c>
-      <c r="R67">
-        <v>0</v>
-      </c>
-      <c r="S67">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="68" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="68" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>65</v>
       </c>
@@ -4590,46 +3988,37 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>63903</v>
+        <v>65358</v>
       </c>
       <c r="H68">
-        <v>869</v>
+        <v>38</v>
       </c>
       <c r="I68">
-        <v>625</v>
+        <v>1</v>
       </c>
       <c r="J68">
-        <v>89</v>
+        <v>163</v>
       </c>
       <c r="K68">
         <v>0</v>
       </c>
       <c r="L68">
-        <v>17627</v>
+        <v>18453</v>
       </c>
       <c r="M68">
         <v>2</v>
       </c>
       <c r="N68">
-        <v>974</v>
+        <v>1525</v>
       </c>
       <c r="O68">
-        <v>56500</v>
+        <v>58256</v>
       </c>
       <c r="P68">
-        <v>71326</v>
-      </c>
-      <c r="Q68">
-        <v>7850</v>
-      </c>
-      <c r="R68">
-        <v>0</v>
-      </c>
-      <c r="S68">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="69" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>71325</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>66</v>
       </c>
@@ -4649,46 +4038,37 @@
         <v>0</v>
       </c>
       <c r="G69">
-        <v>43549</v>
+        <v>43938</v>
       </c>
       <c r="H69">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="I69">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J69">
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="K69">
         <v>0</v>
       </c>
       <c r="L69">
-        <v>17718</v>
+        <v>18012</v>
       </c>
       <c r="M69">
         <v>2</v>
       </c>
       <c r="N69">
-        <v>2463</v>
+        <v>2619</v>
       </c>
       <c r="O69">
-        <v>40737</v>
+        <v>40997</v>
       </c>
       <c r="P69">
         <v>36117</v>
       </c>
-      <c r="Q69">
-        <v>6528</v>
-      </c>
-      <c r="R69">
-        <v>0</v>
-      </c>
-      <c r="S69">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="70" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="70" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>67</v>
       </c>
@@ -4723,7 +4103,7 @@
         <v>0</v>
       </c>
       <c r="L70">
-        <v>18266</v>
+        <v>18275</v>
       </c>
       <c r="M70">
         <v>2</v>
@@ -4732,22 +4112,13 @@
         <v>3246</v>
       </c>
       <c r="O70">
-        <v>44451</v>
+        <v>44466</v>
       </c>
       <c r="P70">
-        <v>42039</v>
-      </c>
-      <c r="Q70">
-        <v>5798</v>
-      </c>
-      <c r="R70">
-        <v>0</v>
-      </c>
-      <c r="S70">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="71" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>42051</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>68</v>
       </c>
@@ -4767,46 +4138,37 @@
         <v>0</v>
       </c>
       <c r="G71">
-        <v>50962</v>
+        <v>50963</v>
       </c>
       <c r="H71">
         <v>0</v>
       </c>
       <c r="I71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J71">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K71">
         <v>0</v>
       </c>
       <c r="L71">
-        <v>22777</v>
+        <v>22816</v>
       </c>
       <c r="M71">
         <v>1</v>
       </c>
       <c r="N71">
-        <v>4387</v>
+        <v>4388</v>
       </c>
       <c r="O71">
-        <v>46185</v>
+        <v>46419</v>
       </c>
       <c r="P71">
         <v>48896</v>
       </c>
-      <c r="Q71">
-        <v>6782</v>
-      </c>
-      <c r="R71">
-        <v>0</v>
-      </c>
-      <c r="S71">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="72" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>69</v>
       </c>
@@ -4826,46 +4188,37 @@
         <v>0</v>
       </c>
       <c r="G72">
-        <v>61437</v>
+        <v>61543</v>
       </c>
       <c r="H72">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="I72">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="J72">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="K72">
         <v>0</v>
       </c>
       <c r="L72">
-        <v>17105</v>
+        <v>17203</v>
       </c>
       <c r="M72">
         <v>9</v>
       </c>
       <c r="N72">
-        <v>3631</v>
+        <v>3665</v>
       </c>
       <c r="O72">
-        <v>56744</v>
+        <v>57835</v>
       </c>
       <c r="P72">
         <v>85505</v>
       </c>
-      <c r="Q72">
-        <v>12340</v>
-      </c>
-      <c r="R72">
-        <v>0</v>
-      </c>
-      <c r="S72">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="73" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>70</v>
       </c>
@@ -4885,46 +4238,37 @@
         <v>0</v>
       </c>
       <c r="G73">
-        <v>58748</v>
+        <v>58915</v>
       </c>
       <c r="H73">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="I73">
         <v>0</v>
       </c>
       <c r="J73">
-        <v>177</v>
+        <v>51</v>
       </c>
       <c r="K73">
         <v>0</v>
       </c>
       <c r="L73">
-        <v>14508</v>
+        <v>14837</v>
       </c>
       <c r="M73">
         <v>7</v>
       </c>
       <c r="N73">
-        <v>3524</v>
+        <v>3783</v>
       </c>
       <c r="O73">
-        <v>50370</v>
+        <v>53849</v>
       </c>
       <c r="P73">
-        <v>67550</v>
-      </c>
-      <c r="Q73">
-        <v>10010</v>
-      </c>
-      <c r="R73">
-        <v>0</v>
-      </c>
-      <c r="S73">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="74" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>67666</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>89</v>
       </c>
@@ -4936,55 +4280,45 @@
         <v>0</v>
       </c>
       <c r="E74">
-        <v>2430385</v>
+        <v>2430386</v>
       </c>
       <c r="F74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G74">
-        <v>2421060</v>
+        <v>2429524</v>
       </c>
       <c r="H74">
-        <v>7910</v>
+        <v>740</v>
       </c>
       <c r="I74">
-        <v>1373</v>
+        <v>79</v>
       </c>
       <c r="J74">
-        <v>13505</v>
+        <v>736</v>
       </c>
       <c r="K74">
-        <v>5850</v>
+        <v>6</v>
       </c>
       <c r="L74">
-        <v>608169</v>
+        <v>622175</v>
       </c>
       <c r="M74">
-        <v>5013</v>
+        <v>7807</v>
       </c>
       <c r="N74">
-        <v>88874</v>
+        <v>94070</v>
       </c>
       <c r="O74">
-        <v>2260402</v>
+        <v>2288134</v>
       </c>
       <c r="P74">
-        <v>4689457</v>
-      </c>
-      <c r="Q74">
-        <v>626236</v>
-      </c>
-      <c r="R74">
-        <v>1</v>
-      </c>
-      <c r="S74">
-        <v>3445</v>
+        <v>4689860</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="11">
     <mergeCell ref="A74:B74"/>
-    <mergeCell ref="Q2:S2"/>
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>

--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\New folder (13)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E51B67D4-4E24-4242-A31C-0CB4AE009F72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{600F57FA-A87D-4182-AA36-14A323BA7F90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
   <si>
     <t>S. No.</t>
   </si>
@@ -293,6 +293,18 @@
   </si>
   <si>
     <t>Notice &amp; Hearing Report Last Updated On : 07-09-2026 07:56:57</t>
+  </si>
+  <si>
+    <t>DSE with UP</t>
+  </si>
+  <si>
+    <t>Electors having DSE with UP</t>
+  </si>
+  <si>
+    <t>Form 7 Generated</t>
+  </si>
+  <si>
+    <t>No Action Required</t>
   </si>
 </sst>
 </file>
@@ -328,7 +340,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
@@ -670,10 +683,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q74"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:S74"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>90</v>
       </c>
@@ -694,7 +707,7 @@
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
     </row>
-    <row r="2" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -729,8 +742,13 @@
       </c>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
-    </row>
-    <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -767,8 +785,17 @@
       <c r="P3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q3" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -817,8 +844,17 @@
       <c r="P4">
         <v>53812</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q4" s="2">
+        <v>12212</v>
+      </c>
+      <c r="R4" s="2">
+        <v>0</v>
+      </c>
+      <c r="S4" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
@@ -867,8 +903,17 @@
       <c r="P5">
         <v>74848</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q5" s="2">
+        <v>16108</v>
+      </c>
+      <c r="R5" s="2">
+        <v>0</v>
+      </c>
+      <c r="S5" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
@@ -917,8 +962,17 @@
       <c r="P6">
         <v>71989</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q6" s="2">
+        <v>17830</v>
+      </c>
+      <c r="R6" s="2">
+        <v>0</v>
+      </c>
+      <c r="S6" s="2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4</v>
       </c>
@@ -967,8 +1021,17 @@
       <c r="P7">
         <v>77581</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q7" s="2">
+        <v>20511</v>
+      </c>
+      <c r="R7" s="2">
+        <v>0</v>
+      </c>
+      <c r="S7" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
@@ -1017,8 +1080,17 @@
       <c r="P8">
         <v>73458</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q8" s="2">
+        <v>20788</v>
+      </c>
+      <c r="R8" s="2">
+        <v>0</v>
+      </c>
+      <c r="S8" s="2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6</v>
       </c>
@@ -1067,8 +1139,17 @@
       <c r="P9">
         <v>72762</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q9" s="2">
+        <v>18141</v>
+      </c>
+      <c r="R9" s="2">
+        <v>0</v>
+      </c>
+      <c r="S9" s="2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>7</v>
       </c>
@@ -1117,8 +1198,17 @@
       <c r="P10">
         <v>53124</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q10" s="2">
+        <v>9498</v>
+      </c>
+      <c r="R10" s="2">
+        <v>0</v>
+      </c>
+      <c r="S10" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>8</v>
       </c>
@@ -1167,8 +1257,17 @@
       <c r="P11">
         <v>84438</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q11" s="2">
+        <v>23477</v>
+      </c>
+      <c r="R11" s="2">
+        <v>0</v>
+      </c>
+      <c r="S11" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
@@ -1217,8 +1316,17 @@
       <c r="P12">
         <v>66685</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q12" s="2">
+        <v>17786</v>
+      </c>
+      <c r="R12" s="2">
+        <v>0</v>
+      </c>
+      <c r="S12" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
@@ -1267,8 +1375,17 @@
       <c r="P13">
         <v>56564</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q13" s="2">
+        <v>16237</v>
+      </c>
+      <c r="R13" s="2">
+        <v>0</v>
+      </c>
+      <c r="S13" s="2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>11</v>
       </c>
@@ -1317,8 +1434,17 @@
       <c r="P14">
         <v>77955</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q14" s="2">
+        <v>19716</v>
+      </c>
+      <c r="R14" s="2">
+        <v>0</v>
+      </c>
+      <c r="S14" s="2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12</v>
       </c>
@@ -1367,8 +1493,17 @@
       <c r="P15">
         <v>67178</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q15" s="2">
+        <v>4859</v>
+      </c>
+      <c r="R15" s="2">
+        <v>0</v>
+      </c>
+      <c r="S15" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13</v>
       </c>
@@ -1417,8 +1552,17 @@
       <c r="P16">
         <v>71673</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q16" s="2">
+        <v>5197</v>
+      </c>
+      <c r="R16" s="2">
+        <v>0</v>
+      </c>
+      <c r="S16" s="2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>14</v>
       </c>
@@ -1467,8 +1611,17 @@
       <c r="P17">
         <v>65457</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q17" s="2">
+        <v>5417</v>
+      </c>
+      <c r="R17" s="2">
+        <v>0</v>
+      </c>
+      <c r="S17" s="2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>15</v>
       </c>
@@ -1517,8 +1670,17 @@
       <c r="P18">
         <v>71475</v>
       </c>
-    </row>
-    <row r="19" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q18" s="2">
+        <v>6819</v>
+      </c>
+      <c r="R18" s="2">
+        <v>0</v>
+      </c>
+      <c r="S18" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>16</v>
       </c>
@@ -1567,8 +1729,17 @@
       <c r="P19">
         <v>106227</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q19" s="2">
+        <v>6135</v>
+      </c>
+      <c r="R19" s="2">
+        <v>0</v>
+      </c>
+      <c r="S19" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>17</v>
       </c>
@@ -1617,8 +1788,17 @@
       <c r="P20">
         <v>75812</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q20" s="2">
+        <v>8984</v>
+      </c>
+      <c r="R20" s="2">
+        <v>0</v>
+      </c>
+      <c r="S20" s="2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>18</v>
       </c>
@@ -1667,8 +1847,17 @@
       <c r="P21">
         <v>62460</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q21" s="2">
+        <v>3868</v>
+      </c>
+      <c r="R21" s="2">
+        <v>0</v>
+      </c>
+      <c r="S21" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>19</v>
       </c>
@@ -1717,8 +1906,17 @@
       <c r="P22">
         <v>64099</v>
       </c>
-    </row>
-    <row r="23" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q22" s="2">
+        <v>4848</v>
+      </c>
+      <c r="R22" s="2">
+        <v>0</v>
+      </c>
+      <c r="S22" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>20</v>
       </c>
@@ -1767,8 +1965,17 @@
       <c r="P23">
         <v>57094</v>
       </c>
-    </row>
-    <row r="24" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q23" s="2">
+        <v>3541</v>
+      </c>
+      <c r="R23" s="2">
+        <v>0</v>
+      </c>
+      <c r="S23" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>21</v>
       </c>
@@ -1817,8 +2024,17 @@
       <c r="P24">
         <v>65629</v>
       </c>
-    </row>
-    <row r="25" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q24" s="2">
+        <v>3492</v>
+      </c>
+      <c r="R24" s="2">
+        <v>0</v>
+      </c>
+      <c r="S24" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>22</v>
       </c>
@@ -1867,8 +2083,17 @@
       <c r="P25">
         <v>57533</v>
       </c>
-    </row>
-    <row r="26" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q25" s="2">
+        <v>3231</v>
+      </c>
+      <c r="R25" s="2">
+        <v>0</v>
+      </c>
+      <c r="S25" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23</v>
       </c>
@@ -1917,8 +2142,17 @@
       <c r="P26">
         <v>66594</v>
       </c>
-    </row>
-    <row r="27" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q26" s="2">
+        <v>3333</v>
+      </c>
+      <c r="R26" s="2">
+        <v>0</v>
+      </c>
+      <c r="S26" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>24</v>
       </c>
@@ -1967,8 +2201,17 @@
       <c r="P27">
         <v>63288</v>
       </c>
-    </row>
-    <row r="28" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q27" s="2">
+        <v>12669</v>
+      </c>
+      <c r="R27" s="2">
+        <v>0</v>
+      </c>
+      <c r="S27" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25</v>
       </c>
@@ -2017,8 +2260,17 @@
       <c r="P28">
         <v>80620</v>
       </c>
-    </row>
-    <row r="29" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q28" s="2">
+        <v>13995</v>
+      </c>
+      <c r="R28" s="2">
+        <v>0</v>
+      </c>
+      <c r="S28" s="2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26</v>
       </c>
@@ -2067,8 +2319,17 @@
       <c r="P29">
         <v>83836</v>
       </c>
-    </row>
-    <row r="30" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q29" s="2">
+        <v>14229</v>
+      </c>
+      <c r="R29" s="2">
+        <v>0</v>
+      </c>
+      <c r="S29" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>27</v>
       </c>
@@ -2117,8 +2378,17 @@
       <c r="P30">
         <v>86933</v>
       </c>
-    </row>
-    <row r="31" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q30" s="2">
+        <v>12564</v>
+      </c>
+      <c r="R30" s="2">
+        <v>0</v>
+      </c>
+      <c r="S30" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>28</v>
       </c>
@@ -2167,8 +2437,17 @@
       <c r="P31">
         <v>81643</v>
       </c>
-    </row>
-    <row r="32" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q31" s="2">
+        <v>14581</v>
+      </c>
+      <c r="R31" s="2">
+        <v>0</v>
+      </c>
+      <c r="S31" s="2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>29</v>
       </c>
@@ -2217,8 +2496,17 @@
       <c r="P32">
         <v>74810</v>
       </c>
-    </row>
-    <row r="33" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q32" s="2">
+        <v>11379</v>
+      </c>
+      <c r="R32" s="2">
+        <v>0</v>
+      </c>
+      <c r="S32" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>30</v>
       </c>
@@ -2267,8 +2555,17 @@
       <c r="P33">
         <v>76969</v>
       </c>
-    </row>
-    <row r="34" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q33" s="2">
+        <v>6678</v>
+      </c>
+      <c r="R33" s="2">
+        <v>0</v>
+      </c>
+      <c r="S33" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>31</v>
       </c>
@@ -2317,8 +2614,17 @@
       <c r="P34">
         <v>74624</v>
       </c>
-    </row>
-    <row r="35" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q34" s="2">
+        <v>7137</v>
+      </c>
+      <c r="R34" s="2">
+        <v>0</v>
+      </c>
+      <c r="S34" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32</v>
       </c>
@@ -2367,8 +2673,17 @@
       <c r="P35">
         <v>76465</v>
       </c>
-    </row>
-    <row r="36" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q35" s="2">
+        <v>8879</v>
+      </c>
+      <c r="R35" s="2">
+        <v>0</v>
+      </c>
+      <c r="S35" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>33</v>
       </c>
@@ -2417,8 +2732,17 @@
       <c r="P36">
         <v>60419</v>
       </c>
-    </row>
-    <row r="37" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q36" s="2">
+        <v>3855</v>
+      </c>
+      <c r="R36" s="2">
+        <v>0</v>
+      </c>
+      <c r="S36" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>34</v>
       </c>
@@ -2467,8 +2791,17 @@
       <c r="P37">
         <v>57832</v>
       </c>
-    </row>
-    <row r="38" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q37" s="2">
+        <v>4036</v>
+      </c>
+      <c r="R37" s="2">
+        <v>0</v>
+      </c>
+      <c r="S37" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>35</v>
       </c>
@@ -2517,8 +2850,17 @@
       <c r="P38">
         <v>63038</v>
       </c>
-    </row>
-    <row r="39" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q38" s="2">
+        <v>5135</v>
+      </c>
+      <c r="R38" s="2">
+        <v>0</v>
+      </c>
+      <c r="S38" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>36</v>
       </c>
@@ -2567,8 +2909,17 @@
       <c r="P39">
         <v>71133</v>
       </c>
-    </row>
-    <row r="40" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q39" s="2">
+        <v>5903</v>
+      </c>
+      <c r="R39" s="2">
+        <v>0</v>
+      </c>
+      <c r="S39" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>37</v>
       </c>
@@ -2617,8 +2968,17 @@
       <c r="P40">
         <v>73242</v>
       </c>
-    </row>
-    <row r="41" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q40" s="2">
+        <v>3824</v>
+      </c>
+      <c r="R40" s="2">
+        <v>0</v>
+      </c>
+      <c r="S40" s="2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>38</v>
       </c>
@@ -2667,8 +3027,17 @@
       <c r="P41">
         <v>85251</v>
       </c>
-    </row>
-    <row r="42" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q41" s="2">
+        <v>6015</v>
+      </c>
+      <c r="R41" s="2">
+        <v>0</v>
+      </c>
+      <c r="S41" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>39</v>
       </c>
@@ -2717,8 +3086,17 @@
       <c r="P42">
         <v>68615</v>
       </c>
-    </row>
-    <row r="43" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q42" s="2">
+        <v>4708</v>
+      </c>
+      <c r="R42" s="2">
+        <v>0</v>
+      </c>
+      <c r="S42" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>40</v>
       </c>
@@ -2767,8 +3145,17 @@
       <c r="P43">
         <v>63043</v>
       </c>
-    </row>
-    <row r="44" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q43" s="2">
+        <v>5219</v>
+      </c>
+      <c r="R43" s="2">
+        <v>0</v>
+      </c>
+      <c r="S43" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>41</v>
       </c>
@@ -2817,8 +3204,17 @@
       <c r="P44">
         <v>68393</v>
       </c>
-    </row>
-    <row r="45" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q44" s="2">
+        <v>7659</v>
+      </c>
+      <c r="R44" s="2">
+        <v>0</v>
+      </c>
+      <c r="S44" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>42</v>
       </c>
@@ -2867,8 +3263,17 @@
       <c r="P45">
         <v>76287</v>
       </c>
-    </row>
-    <row r="46" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q45" s="2">
+        <v>6998</v>
+      </c>
+      <c r="R45" s="2">
+        <v>0</v>
+      </c>
+      <c r="S45" s="2">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>43</v>
       </c>
@@ -2917,8 +3322,17 @@
       <c r="P46">
         <v>64160</v>
       </c>
-    </row>
-    <row r="47" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q46" s="2">
+        <v>7548</v>
+      </c>
+      <c r="R46" s="2">
+        <v>0</v>
+      </c>
+      <c r="S46" s="2">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>44</v>
       </c>
@@ -2967,8 +3381,17 @@
       <c r="P47">
         <v>49875</v>
       </c>
-    </row>
-    <row r="48" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q47" s="2">
+        <v>5046</v>
+      </c>
+      <c r="R47" s="2">
+        <v>0</v>
+      </c>
+      <c r="S47" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>45</v>
       </c>
@@ -3017,8 +3440,17 @@
       <c r="P48">
         <v>54142</v>
       </c>
-    </row>
-    <row r="49" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q48" s="2">
+        <v>4623</v>
+      </c>
+      <c r="R48" s="2">
+        <v>0</v>
+      </c>
+      <c r="S48" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>46</v>
       </c>
@@ -3067,8 +3499,17 @@
       <c r="P49">
         <v>55376</v>
       </c>
-    </row>
-    <row r="50" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q49" s="2">
+        <v>5057</v>
+      </c>
+      <c r="R49" s="2">
+        <v>0</v>
+      </c>
+      <c r="S49" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>47</v>
       </c>
@@ -3117,8 +3558,17 @@
       <c r="P50">
         <v>63298</v>
       </c>
-    </row>
-    <row r="51" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q50" s="2">
+        <v>7292</v>
+      </c>
+      <c r="R50" s="2">
+        <v>0</v>
+      </c>
+      <c r="S50" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>48</v>
       </c>
@@ -3167,8 +3617,17 @@
       <c r="P51">
         <v>71754</v>
       </c>
-    </row>
-    <row r="52" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q51" s="2">
+        <v>7715</v>
+      </c>
+      <c r="R51" s="2">
+        <v>0</v>
+      </c>
+      <c r="S51" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>49</v>
       </c>
@@ -3217,8 +3676,17 @@
       <c r="P52">
         <v>63987</v>
       </c>
-    </row>
-    <row r="53" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q52" s="2">
+        <v>5655</v>
+      </c>
+      <c r="R52" s="2">
+        <v>0</v>
+      </c>
+      <c r="S52" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>50</v>
       </c>
@@ -3267,8 +3735,17 @@
       <c r="P53">
         <v>56306</v>
       </c>
-    </row>
-    <row r="54" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q53" s="2">
+        <v>6551</v>
+      </c>
+      <c r="R53" s="2">
+        <v>0</v>
+      </c>
+      <c r="S53" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>51</v>
       </c>
@@ -3317,8 +3794,17 @@
       <c r="P54">
         <v>58440</v>
       </c>
-    </row>
-    <row r="55" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q54" s="2">
+        <v>7347</v>
+      </c>
+      <c r="R54" s="2">
+        <v>0</v>
+      </c>
+      <c r="S54" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>52</v>
       </c>
@@ -3367,8 +3853,17 @@
       <c r="P55">
         <v>58215</v>
       </c>
-    </row>
-    <row r="56" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q55" s="2">
+        <v>5098</v>
+      </c>
+      <c r="R55" s="2">
+        <v>0</v>
+      </c>
+      <c r="S55" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>53</v>
       </c>
@@ -3417,8 +3912,17 @@
       <c r="P56">
         <v>46365</v>
       </c>
-    </row>
-    <row r="57" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q56" s="2">
+        <v>4882</v>
+      </c>
+      <c r="R56" s="2">
+        <v>0</v>
+      </c>
+      <c r="S56" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>54</v>
       </c>
@@ -3467,8 +3971,17 @@
       <c r="P57">
         <v>61556</v>
       </c>
-    </row>
-    <row r="58" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q57" s="2">
+        <v>6870</v>
+      </c>
+      <c r="R57" s="2">
+        <v>0</v>
+      </c>
+      <c r="S57" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>55</v>
       </c>
@@ -3517,8 +4030,17 @@
       <c r="P58">
         <v>57577</v>
       </c>
-    </row>
-    <row r="59" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q58" s="2">
+        <v>8884</v>
+      </c>
+      <c r="R58" s="2">
+        <v>0</v>
+      </c>
+      <c r="S58" s="2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>56</v>
       </c>
@@ -3567,8 +4089,17 @@
       <c r="P59">
         <v>60495</v>
       </c>
-    </row>
-    <row r="60" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q59" s="2">
+        <v>8028</v>
+      </c>
+      <c r="R59" s="2">
+        <v>0</v>
+      </c>
+      <c r="S59" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>57</v>
       </c>
@@ -3617,8 +4148,17 @@
       <c r="P60">
         <v>70140</v>
       </c>
-    </row>
-    <row r="61" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q60" s="2">
+        <v>7415</v>
+      </c>
+      <c r="R60" s="2">
+        <v>0</v>
+      </c>
+      <c r="S60" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>58</v>
       </c>
@@ -3667,8 +4207,17 @@
       <c r="P61">
         <v>55240</v>
       </c>
-    </row>
-    <row r="62" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q61" s="2">
+        <v>7927</v>
+      </c>
+      <c r="R61" s="2">
+        <v>1</v>
+      </c>
+      <c r="S61" s="2">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>59</v>
       </c>
@@ -3717,8 +4266,17 @@
       <c r="P62">
         <v>51334</v>
       </c>
-    </row>
-    <row r="63" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q62" s="2">
+        <v>6917</v>
+      </c>
+      <c r="R62" s="2">
+        <v>0</v>
+      </c>
+      <c r="S62" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>60</v>
       </c>
@@ -3767,8 +4325,17 @@
       <c r="P63">
         <v>68691</v>
       </c>
-    </row>
-    <row r="64" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q63" s="2">
+        <v>9766</v>
+      </c>
+      <c r="R63" s="2">
+        <v>0</v>
+      </c>
+      <c r="S63" s="2">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>61</v>
       </c>
@@ -3817,8 +4384,17 @@
       <c r="P64">
         <v>60527</v>
       </c>
-    </row>
-    <row r="65" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q64" s="2">
+        <v>5985</v>
+      </c>
+      <c r="R64" s="2">
+        <v>0</v>
+      </c>
+      <c r="S64" s="2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>62</v>
       </c>
@@ -3867,8 +4443,17 @@
       <c r="P65">
         <v>58103</v>
       </c>
-    </row>
-    <row r="66" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q65" s="2">
+        <v>13282</v>
+      </c>
+      <c r="R65" s="2">
+        <v>0</v>
+      </c>
+      <c r="S65" s="2">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>63</v>
       </c>
@@ -3917,8 +4502,17 @@
       <c r="P66">
         <v>93809</v>
       </c>
-    </row>
-    <row r="67" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q66" s="2">
+        <v>17742</v>
+      </c>
+      <c r="R66" s="2">
+        <v>0</v>
+      </c>
+      <c r="S66" s="2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>64</v>
       </c>
@@ -3967,8 +4561,17 @@
       <c r="P67">
         <v>78022</v>
       </c>
-    </row>
-    <row r="68" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q67" s="2">
+        <v>9807</v>
+      </c>
+      <c r="R67" s="2">
+        <v>0</v>
+      </c>
+      <c r="S67" s="2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>65</v>
       </c>
@@ -4017,8 +4620,17 @@
       <c r="P68">
         <v>71325</v>
       </c>
-    </row>
-    <row r="69" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q68" s="2">
+        <v>7850</v>
+      </c>
+      <c r="R68" s="2">
+        <v>0</v>
+      </c>
+      <c r="S68" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>66</v>
       </c>
@@ -4067,8 +4679,17 @@
       <c r="P69">
         <v>36117</v>
       </c>
-    </row>
-    <row r="70" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q69" s="2">
+        <v>6528</v>
+      </c>
+      <c r="R69" s="2">
+        <v>0</v>
+      </c>
+      <c r="S69" s="2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>67</v>
       </c>
@@ -4117,8 +4738,17 @@
       <c r="P70">
         <v>42051</v>
       </c>
-    </row>
-    <row r="71" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q70" s="2">
+        <v>5798</v>
+      </c>
+      <c r="R70" s="2">
+        <v>0</v>
+      </c>
+      <c r="S70" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>68</v>
       </c>
@@ -4167,8 +4797,17 @@
       <c r="P71">
         <v>48896</v>
       </c>
-    </row>
-    <row r="72" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q71" s="2">
+        <v>6782</v>
+      </c>
+      <c r="R71" s="2">
+        <v>0</v>
+      </c>
+      <c r="S71" s="2">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>69</v>
       </c>
@@ -4217,8 +4856,17 @@
       <c r="P72">
         <v>85505</v>
       </c>
-    </row>
-    <row r="73" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q72" s="2">
+        <v>12340</v>
+      </c>
+      <c r="R72" s="2">
+        <v>0</v>
+      </c>
+      <c r="S72" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>70</v>
       </c>
@@ -4267,8 +4915,17 @@
       <c r="P73">
         <v>67666</v>
       </c>
-    </row>
-    <row r="74" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q73" s="2">
+        <v>10010</v>
+      </c>
+      <c r="R73" s="2">
+        <v>0</v>
+      </c>
+      <c r="S73" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>89</v>
       </c>
@@ -4315,9 +4972,18 @@
       <c r="P74">
         <v>4689860</v>
       </c>
+      <c r="Q74" s="2">
+        <v>626236</v>
+      </c>
+      <c r="R74" s="2">
+        <v>1</v>
+      </c>
+      <c r="S74" s="2">
+        <v>3445</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="A74:B74"/>
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A2:A3"/>
@@ -4329,6 +4995,7 @@
     <mergeCell ref="G2:I2"/>
     <mergeCell ref="J2:M2"/>
     <mergeCell ref="N2:P2"/>
+    <mergeCell ref="Q2:S2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\New folder (13)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{600F57FA-A87D-4182-AA36-14A323BA7F90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{011F85E2-12D9-4F12-9642-5F00A55289F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
   <si>
     <t>S. No.</t>
   </si>
@@ -292,19 +292,7 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Notice &amp; Hearing Report Last Updated On : 07-09-2026 07:56:57</t>
-  </si>
-  <si>
-    <t>DSE with UP</t>
-  </si>
-  <si>
-    <t>Electors having DSE with UP</t>
-  </si>
-  <si>
-    <t>Form 7 Generated</t>
-  </si>
-  <si>
-    <t>No Action Required</t>
+    <t>Notice &amp; Hearing Report Last Updated On : 07-09-2026 11:56:56</t>
   </si>
 </sst>
 </file>
@@ -340,8 +328,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
@@ -683,10 +670,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S74"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Q74"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>90</v>
       </c>
@@ -707,7 +694,7 @@
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -742,13 +729,8 @@
       </c>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
-      <c r="Q2" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -785,17 +767,8 @@
       <c r="P3" t="s">
         <v>18</v>
       </c>
-      <c r="Q3" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -824,37 +797,28 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>17792</v>
+        <v>17795</v>
       </c>
       <c r="M4">
         <v>948</v>
       </c>
       <c r="N4">
-        <v>854</v>
+        <v>861</v>
       </c>
       <c r="O4">
-        <v>50323</v>
+        <v>50436</v>
       </c>
       <c r="P4">
         <v>53812</v>
       </c>
-      <c r="Q4" s="2">
-        <v>12212</v>
-      </c>
-      <c r="R4" s="2">
-        <v>0</v>
-      </c>
-      <c r="S4" s="2">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
@@ -883,13 +847,13 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>11380</v>
+        <v>11383</v>
       </c>
       <c r="M5">
         <v>749</v>
@@ -898,22 +862,13 @@
         <v>854</v>
       </c>
       <c r="O5">
-        <v>52482</v>
+        <v>52854</v>
       </c>
       <c r="P5">
         <v>74848</v>
       </c>
-      <c r="Q5" s="2">
-        <v>16108</v>
-      </c>
-      <c r="R5" s="2">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
@@ -933,46 +888,37 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>39665</v>
+        <v>39673</v>
       </c>
       <c r="H6">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="I6">
         <v>3</v>
       </c>
       <c r="J6">
-        <v>93</v>
+        <v>2</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>5875</v>
+        <v>5967</v>
       </c>
       <c r="M6">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N6">
-        <v>1742</v>
+        <v>1746</v>
       </c>
       <c r="O6">
-        <v>33211</v>
+        <v>33213</v>
       </c>
       <c r="P6">
         <v>71989</v>
       </c>
-      <c r="Q6" s="2">
-        <v>17830</v>
-      </c>
-      <c r="R6" s="2">
-        <v>0</v>
-      </c>
-      <c r="S6" s="2">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4</v>
       </c>
@@ -1001,13 +947,13 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>5605</v>
+        <v>5616</v>
       </c>
       <c r="M7">
         <v>257</v>
@@ -1016,22 +962,13 @@
         <v>1985</v>
       </c>
       <c r="O7">
-        <v>35002</v>
+        <v>35013</v>
       </c>
       <c r="P7">
         <v>77581</v>
       </c>
-      <c r="Q7" s="2">
-        <v>20511</v>
-      </c>
-      <c r="R7" s="2">
-        <v>0</v>
-      </c>
-      <c r="S7" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
@@ -1080,17 +1017,8 @@
       <c r="P8">
         <v>73458</v>
       </c>
-      <c r="Q8" s="2">
-        <v>20788</v>
-      </c>
-      <c r="R8" s="2">
-        <v>0</v>
-      </c>
-      <c r="S8" s="2">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6</v>
       </c>
@@ -1131,25 +1059,16 @@
         <v>49</v>
       </c>
       <c r="N9">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="O9">
-        <v>41894</v>
+        <v>41898</v>
       </c>
       <c r="P9">
         <v>72762</v>
       </c>
-      <c r="Q9" s="2">
-        <v>18141</v>
-      </c>
-      <c r="R9" s="2">
-        <v>0</v>
-      </c>
-      <c r="S9" s="2">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>7</v>
       </c>
@@ -1178,37 +1097,28 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>10912</v>
+        <v>10927</v>
       </c>
       <c r="M10">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="N10">
         <v>781</v>
       </c>
       <c r="O10">
-        <v>35600</v>
+        <v>35722</v>
       </c>
       <c r="P10">
         <v>53124</v>
       </c>
-      <c r="Q10" s="2">
-        <v>9498</v>
-      </c>
-      <c r="R10" s="2">
-        <v>0</v>
-      </c>
-      <c r="S10" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>8</v>
       </c>
@@ -1257,17 +1167,8 @@
       <c r="P11">
         <v>84438</v>
       </c>
-      <c r="Q11" s="2">
-        <v>23477</v>
-      </c>
-      <c r="R11" s="2">
-        <v>0</v>
-      </c>
-      <c r="S11" s="2">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
@@ -1296,37 +1197,28 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="L12">
-        <v>9922</v>
+        <v>9972</v>
       </c>
       <c r="M12">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N12">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="O12">
-        <v>38588</v>
+        <v>39300</v>
       </c>
       <c r="P12">
         <v>66685</v>
       </c>
-      <c r="Q12" s="2">
-        <v>17786</v>
-      </c>
-      <c r="R12" s="2">
-        <v>0</v>
-      </c>
-      <c r="S12" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
@@ -1375,17 +1267,8 @@
       <c r="P13">
         <v>56564</v>
       </c>
-      <c r="Q13" s="2">
-        <v>16237</v>
-      </c>
-      <c r="R13" s="2">
-        <v>0</v>
-      </c>
-      <c r="S13" s="2">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>11</v>
       </c>
@@ -1414,37 +1297,28 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>14957</v>
+        <v>14971</v>
       </c>
       <c r="M14">
-        <v>1407</v>
+        <v>1411</v>
       </c>
       <c r="N14">
         <v>5545</v>
       </c>
       <c r="O14">
-        <v>30269</v>
+        <v>30281</v>
       </c>
       <c r="P14">
         <v>77955</v>
       </c>
-      <c r="Q14" s="2">
-        <v>19716</v>
-      </c>
-      <c r="R14" s="2">
-        <v>0</v>
-      </c>
-      <c r="S14" s="2">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12</v>
       </c>
@@ -1493,17 +1367,8 @@
       <c r="P15">
         <v>67178</v>
       </c>
-      <c r="Q15" s="2">
-        <v>4859</v>
-      </c>
-      <c r="R15" s="2">
-        <v>0</v>
-      </c>
-      <c r="S15" s="2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13</v>
       </c>
@@ -1552,17 +1417,8 @@
       <c r="P16">
         <v>71673</v>
       </c>
-      <c r="Q16" s="2">
-        <v>5197</v>
-      </c>
-      <c r="R16" s="2">
-        <v>0</v>
-      </c>
-      <c r="S16" s="2">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>14</v>
       </c>
@@ -1611,17 +1467,8 @@
       <c r="P17">
         <v>65457</v>
       </c>
-      <c r="Q17" s="2">
-        <v>5417</v>
-      </c>
-      <c r="R17" s="2">
-        <v>0</v>
-      </c>
-      <c r="S17" s="2">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>15</v>
       </c>
@@ -1670,17 +1517,8 @@
       <c r="P18">
         <v>71475</v>
       </c>
-      <c r="Q18" s="2">
-        <v>6819</v>
-      </c>
-      <c r="R18" s="2">
-        <v>0</v>
-      </c>
-      <c r="S18" s="2">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>16</v>
       </c>
@@ -1729,17 +1567,8 @@
       <c r="P19">
         <v>106227</v>
       </c>
-      <c r="Q19" s="2">
-        <v>6135</v>
-      </c>
-      <c r="R19" s="2">
-        <v>0</v>
-      </c>
-      <c r="S19" s="2">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>17</v>
       </c>
@@ -1788,17 +1617,8 @@
       <c r="P20">
         <v>75812</v>
       </c>
-      <c r="Q20" s="2">
-        <v>8984</v>
-      </c>
-      <c r="R20" s="2">
-        <v>0</v>
-      </c>
-      <c r="S20" s="2">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>18</v>
       </c>
@@ -1847,17 +1667,8 @@
       <c r="P21">
         <v>62460</v>
       </c>
-      <c r="Q21" s="2">
-        <v>3868</v>
-      </c>
-      <c r="R21" s="2">
-        <v>0</v>
-      </c>
-      <c r="S21" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>19</v>
       </c>
@@ -1906,17 +1717,8 @@
       <c r="P22">
         <v>64099</v>
       </c>
-      <c r="Q22" s="2">
-        <v>4848</v>
-      </c>
-      <c r="R22" s="2">
-        <v>0</v>
-      </c>
-      <c r="S22" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>20</v>
       </c>
@@ -1965,17 +1767,8 @@
       <c r="P23">
         <v>57094</v>
       </c>
-      <c r="Q23" s="2">
-        <v>3541</v>
-      </c>
-      <c r="R23" s="2">
-        <v>0</v>
-      </c>
-      <c r="S23" s="2">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>21</v>
       </c>
@@ -2024,17 +1817,8 @@
       <c r="P24">
         <v>65629</v>
       </c>
-      <c r="Q24" s="2">
-        <v>3492</v>
-      </c>
-      <c r="R24" s="2">
-        <v>0</v>
-      </c>
-      <c r="S24" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>22</v>
       </c>
@@ -2083,17 +1867,8 @@
       <c r="P25">
         <v>57533</v>
       </c>
-      <c r="Q25" s="2">
-        <v>3231</v>
-      </c>
-      <c r="R25" s="2">
-        <v>0</v>
-      </c>
-      <c r="S25" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23</v>
       </c>
@@ -2142,17 +1917,8 @@
       <c r="P26">
         <v>66594</v>
       </c>
-      <c r="Q26" s="2">
-        <v>3333</v>
-      </c>
-      <c r="R26" s="2">
-        <v>0</v>
-      </c>
-      <c r="S26" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>24</v>
       </c>
@@ -2172,46 +1938,37 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>44071</v>
+        <v>44132</v>
       </c>
       <c r="H27">
-        <v>205</v>
+        <v>144</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="L27">
-        <v>9654</v>
+        <v>9658</v>
       </c>
       <c r="M27">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N27">
-        <v>2638</v>
+        <v>2760</v>
       </c>
       <c r="O27">
-        <v>40096</v>
+        <v>40059</v>
       </c>
       <c r="P27">
         <v>63288</v>
       </c>
-      <c r="Q27" s="2">
-        <v>12669</v>
-      </c>
-      <c r="R27" s="2">
-        <v>0</v>
-      </c>
-      <c r="S27" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25</v>
       </c>
@@ -2231,46 +1988,37 @@
         <v>0</v>
       </c>
       <c r="G28">
-        <v>54335</v>
+        <v>54336</v>
       </c>
       <c r="H28">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I28">
         <v>0</v>
       </c>
       <c r="J28">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="K28">
         <v>0</v>
       </c>
       <c r="L28">
-        <v>8798</v>
+        <v>8827</v>
       </c>
       <c r="M28">
-        <v>802</v>
+        <v>850</v>
       </c>
       <c r="N28">
-        <v>3202</v>
+        <v>3215</v>
       </c>
       <c r="O28">
-        <v>50536</v>
+        <v>50591</v>
       </c>
       <c r="P28">
         <v>80620</v>
       </c>
-      <c r="Q28" s="2">
-        <v>13995</v>
-      </c>
-      <c r="R28" s="2">
-        <v>0</v>
-      </c>
-      <c r="S28" s="2">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26</v>
       </c>
@@ -2319,17 +2067,8 @@
       <c r="P29">
         <v>83836</v>
       </c>
-      <c r="Q29" s="2">
-        <v>14229</v>
-      </c>
-      <c r="R29" s="2">
-        <v>0</v>
-      </c>
-      <c r="S29" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>27</v>
       </c>
@@ -2378,17 +2117,8 @@
       <c r="P30">
         <v>86933</v>
       </c>
-      <c r="Q30" s="2">
-        <v>12564</v>
-      </c>
-      <c r="R30" s="2">
-        <v>0</v>
-      </c>
-      <c r="S30" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>28</v>
       </c>
@@ -2437,17 +2167,8 @@
       <c r="P31">
         <v>81643</v>
       </c>
-      <c r="Q31" s="2">
-        <v>14581</v>
-      </c>
-      <c r="R31" s="2">
-        <v>0</v>
-      </c>
-      <c r="S31" s="2">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>29</v>
       </c>
@@ -2476,37 +2197,28 @@
         <v>0</v>
       </c>
       <c r="J32">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K32">
         <v>0</v>
       </c>
       <c r="L32">
-        <v>10555</v>
+        <v>10557</v>
       </c>
       <c r="M32">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="N32">
-        <v>4331</v>
+        <v>4332</v>
       </c>
       <c r="O32">
-        <v>41961</v>
+        <v>42262</v>
       </c>
       <c r="P32">
         <v>74810</v>
       </c>
-      <c r="Q32" s="2">
-        <v>11379</v>
-      </c>
-      <c r="R32" s="2">
-        <v>0</v>
-      </c>
-      <c r="S32" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>30</v>
       </c>
@@ -2526,16 +2238,16 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <v>40199</v>
+        <v>40200</v>
       </c>
       <c r="H33">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I33">
         <v>0</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K33">
         <v>0</v>
@@ -2547,25 +2259,16 @@
         <v>258</v>
       </c>
       <c r="N33">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="O33">
-        <v>37505</v>
+        <v>37515</v>
       </c>
       <c r="P33">
         <v>76969</v>
       </c>
-      <c r="Q33" s="2">
-        <v>6678</v>
-      </c>
-      <c r="R33" s="2">
-        <v>0</v>
-      </c>
-      <c r="S33" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>31</v>
       </c>
@@ -2600,31 +2303,22 @@
         <v>0</v>
       </c>
       <c r="L34">
-        <v>11887</v>
+        <v>11888</v>
       </c>
       <c r="M34">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N34">
-        <v>1301</v>
+        <v>1306</v>
       </c>
       <c r="O34">
-        <v>33815</v>
+        <v>33842</v>
       </c>
       <c r="P34">
         <v>74624</v>
       </c>
-      <c r="Q34" s="2">
-        <v>7137</v>
-      </c>
-      <c r="R34" s="2">
-        <v>0</v>
-      </c>
-      <c r="S34" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32</v>
       </c>
@@ -2644,46 +2338,37 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>33282</v>
+        <v>33283</v>
       </c>
       <c r="H35">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I35">
         <v>0</v>
       </c>
       <c r="J35">
-        <v>135</v>
+        <v>2</v>
       </c>
       <c r="K35">
         <v>0</v>
       </c>
       <c r="L35">
-        <v>7593</v>
+        <v>7714</v>
       </c>
       <c r="M35">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="N35">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="O35">
-        <v>31854</v>
+        <v>31866</v>
       </c>
       <c r="P35">
         <v>76465</v>
       </c>
-      <c r="Q35" s="2">
-        <v>8879</v>
-      </c>
-      <c r="R35" s="2">
-        <v>0</v>
-      </c>
-      <c r="S35" s="2">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>33</v>
       </c>
@@ -2732,17 +2417,8 @@
       <c r="P36">
         <v>60419</v>
       </c>
-      <c r="Q36" s="2">
-        <v>3855</v>
-      </c>
-      <c r="R36" s="2">
-        <v>0</v>
-      </c>
-      <c r="S36" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>34</v>
       </c>
@@ -2791,17 +2467,8 @@
       <c r="P37">
         <v>57832</v>
       </c>
-      <c r="Q37" s="2">
-        <v>4036</v>
-      </c>
-      <c r="R37" s="2">
-        <v>0</v>
-      </c>
-      <c r="S37" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>35</v>
       </c>
@@ -2850,17 +2517,8 @@
       <c r="P38">
         <v>63038</v>
       </c>
-      <c r="Q38" s="2">
-        <v>5135</v>
-      </c>
-      <c r="R38" s="2">
-        <v>0</v>
-      </c>
-      <c r="S38" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>36</v>
       </c>
@@ -2909,17 +2567,8 @@
       <c r="P39">
         <v>71133</v>
       </c>
-      <c r="Q39" s="2">
-        <v>5903</v>
-      </c>
-      <c r="R39" s="2">
-        <v>0</v>
-      </c>
-      <c r="S39" s="2">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>37</v>
       </c>
@@ -2968,17 +2617,8 @@
       <c r="P40">
         <v>73242</v>
       </c>
-      <c r="Q40" s="2">
-        <v>3824</v>
-      </c>
-      <c r="R40" s="2">
-        <v>0</v>
-      </c>
-      <c r="S40" s="2">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>38</v>
       </c>
@@ -3027,17 +2667,8 @@
       <c r="P41">
         <v>85251</v>
       </c>
-      <c r="Q41" s="2">
-        <v>6015</v>
-      </c>
-      <c r="R41" s="2">
-        <v>0</v>
-      </c>
-      <c r="S41" s="2">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>39</v>
       </c>
@@ -3086,17 +2717,8 @@
       <c r="P42">
         <v>68615</v>
       </c>
-      <c r="Q42" s="2">
-        <v>4708</v>
-      </c>
-      <c r="R42" s="2">
-        <v>0</v>
-      </c>
-      <c r="S42" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>40</v>
       </c>
@@ -3145,17 +2767,8 @@
       <c r="P43">
         <v>63043</v>
       </c>
-      <c r="Q43" s="2">
-        <v>5219</v>
-      </c>
-      <c r="R43" s="2">
-        <v>0</v>
-      </c>
-      <c r="S43" s="2">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>41</v>
       </c>
@@ -3204,17 +2817,8 @@
       <c r="P44">
         <v>68393</v>
       </c>
-      <c r="Q44" s="2">
-        <v>7659</v>
-      </c>
-      <c r="R44" s="2">
-        <v>0</v>
-      </c>
-      <c r="S44" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>42</v>
       </c>
@@ -3263,17 +2867,8 @@
       <c r="P45">
         <v>76287</v>
       </c>
-      <c r="Q45" s="2">
-        <v>6998</v>
-      </c>
-      <c r="R45" s="2">
-        <v>0</v>
-      </c>
-      <c r="S45" s="2">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>43</v>
       </c>
@@ -3322,17 +2917,8 @@
       <c r="P46">
         <v>64160</v>
       </c>
-      <c r="Q46" s="2">
-        <v>7548</v>
-      </c>
-      <c r="R46" s="2">
-        <v>0</v>
-      </c>
-      <c r="S46" s="2">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>44</v>
       </c>
@@ -3381,17 +2967,8 @@
       <c r="P47">
         <v>49875</v>
       </c>
-      <c r="Q47" s="2">
-        <v>5046</v>
-      </c>
-      <c r="R47" s="2">
-        <v>0</v>
-      </c>
-      <c r="S47" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>45</v>
       </c>
@@ -3405,10 +2982,10 @@
         <v>0</v>
       </c>
       <c r="E48">
-        <v>19640</v>
+        <v>19641</v>
       </c>
       <c r="F48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48">
         <v>19641</v>
@@ -3420,13 +2997,13 @@
         <v>0</v>
       </c>
       <c r="J48">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K48">
         <v>0</v>
       </c>
       <c r="L48">
-        <v>3793</v>
+        <v>3799</v>
       </c>
       <c r="M48">
         <v>4</v>
@@ -3440,17 +3017,8 @@
       <c r="P48">
         <v>54142</v>
       </c>
-      <c r="Q48" s="2">
-        <v>4623</v>
-      </c>
-      <c r="R48" s="2">
-        <v>0</v>
-      </c>
-      <c r="S48" s="2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>46</v>
       </c>
@@ -3470,46 +3038,37 @@
         <v>0</v>
       </c>
       <c r="G49">
-        <v>21649</v>
+        <v>21651</v>
       </c>
       <c r="H49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K49">
         <v>0</v>
       </c>
       <c r="L49">
-        <v>3615</v>
+        <v>3627</v>
       </c>
       <c r="M49">
         <v>0</v>
       </c>
       <c r="N49">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="O49">
-        <v>21015</v>
+        <v>21024</v>
       </c>
       <c r="P49">
         <v>55376</v>
       </c>
-      <c r="Q49" s="2">
-        <v>5057</v>
-      </c>
-      <c r="R49" s="2">
-        <v>0</v>
-      </c>
-      <c r="S49" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>47</v>
       </c>
@@ -3558,17 +3117,8 @@
       <c r="P50">
         <v>63298</v>
       </c>
-      <c r="Q50" s="2">
-        <v>7292</v>
-      </c>
-      <c r="R50" s="2">
-        <v>0</v>
-      </c>
-      <c r="S50" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>48</v>
       </c>
@@ -3617,17 +3167,8 @@
       <c r="P51">
         <v>71754</v>
       </c>
-      <c r="Q51" s="2">
-        <v>7715</v>
-      </c>
-      <c r="R51" s="2">
-        <v>0</v>
-      </c>
-      <c r="S51" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>49</v>
       </c>
@@ -3676,17 +3217,8 @@
       <c r="P52">
         <v>63987</v>
       </c>
-      <c r="Q52" s="2">
-        <v>5655</v>
-      </c>
-      <c r="R52" s="2">
-        <v>0</v>
-      </c>
-      <c r="S52" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>50</v>
       </c>
@@ -3735,17 +3267,8 @@
       <c r="P53">
         <v>56306</v>
       </c>
-      <c r="Q53" s="2">
-        <v>6551</v>
-      </c>
-      <c r="R53" s="2">
-        <v>0</v>
-      </c>
-      <c r="S53" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>51</v>
       </c>
@@ -3774,13 +3297,13 @@
         <v>0</v>
       </c>
       <c r="J54">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K54">
         <v>0</v>
       </c>
       <c r="L54">
-        <v>2599</v>
+        <v>2602</v>
       </c>
       <c r="M54">
         <v>5</v>
@@ -3789,22 +3312,13 @@
         <v>391</v>
       </c>
       <c r="O54">
-        <v>20354</v>
+        <v>20366</v>
       </c>
       <c r="P54">
         <v>58440</v>
       </c>
-      <c r="Q54" s="2">
-        <v>7347</v>
-      </c>
-      <c r="R54" s="2">
-        <v>0</v>
-      </c>
-      <c r="S54" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>52</v>
       </c>
@@ -3833,13 +3347,13 @@
         <v>0</v>
       </c>
       <c r="J55">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="K55">
         <v>4</v>
       </c>
       <c r="L55">
-        <v>2090</v>
+        <v>2105</v>
       </c>
       <c r="M55">
         <v>1</v>
@@ -3848,22 +3362,13 @@
         <v>129</v>
       </c>
       <c r="O55">
-        <v>15874</v>
+        <v>15889</v>
       </c>
       <c r="P55">
         <v>58215</v>
       </c>
-      <c r="Q55" s="2">
-        <v>5098</v>
-      </c>
-      <c r="R55" s="2">
-        <v>0</v>
-      </c>
-      <c r="S55" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>53</v>
       </c>
@@ -3892,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="J56">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="K56">
         <v>0</v>
@@ -3904,7 +3409,7 @@
         <v>3</v>
       </c>
       <c r="N56">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O56">
         <v>18747</v>
@@ -3912,17 +3417,8 @@
       <c r="P56">
         <v>46365</v>
       </c>
-      <c r="Q56" s="2">
-        <v>4882</v>
-      </c>
-      <c r="R56" s="2">
-        <v>0</v>
-      </c>
-      <c r="S56" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>54</v>
       </c>
@@ -3971,17 +3467,8 @@
       <c r="P57">
         <v>61556</v>
       </c>
-      <c r="Q57" s="2">
-        <v>6870</v>
-      </c>
-      <c r="R57" s="2">
-        <v>0</v>
-      </c>
-      <c r="S57" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>55</v>
       </c>
@@ -4030,17 +3517,8 @@
       <c r="P58">
         <v>57577</v>
       </c>
-      <c r="Q58" s="2">
-        <v>8884</v>
-      </c>
-      <c r="R58" s="2">
-        <v>0</v>
-      </c>
-      <c r="S58" s="2">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="59" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>56</v>
       </c>
@@ -4089,17 +3567,8 @@
       <c r="P59">
         <v>60495</v>
       </c>
-      <c r="Q59" s="2">
-        <v>8028</v>
-      </c>
-      <c r="R59" s="2">
-        <v>0</v>
-      </c>
-      <c r="S59" s="2">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>57</v>
       </c>
@@ -4148,17 +3617,8 @@
       <c r="P60">
         <v>70140</v>
       </c>
-      <c r="Q60" s="2">
-        <v>7415</v>
-      </c>
-      <c r="R60" s="2">
-        <v>0</v>
-      </c>
-      <c r="S60" s="2">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>58</v>
       </c>
@@ -4207,17 +3667,8 @@
       <c r="P61">
         <v>55240</v>
       </c>
-      <c r="Q61" s="2">
-        <v>7927</v>
-      </c>
-      <c r="R61" s="2">
-        <v>1</v>
-      </c>
-      <c r="S61" s="2">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>59</v>
       </c>
@@ -4266,17 +3717,8 @@
       <c r="P62">
         <v>51334</v>
       </c>
-      <c r="Q62" s="2">
-        <v>6917</v>
-      </c>
-      <c r="R62" s="2">
-        <v>0</v>
-      </c>
-      <c r="S62" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>60</v>
       </c>
@@ -4325,17 +3767,8 @@
       <c r="P63">
         <v>68691</v>
       </c>
-      <c r="Q63" s="2">
-        <v>9766</v>
-      </c>
-      <c r="R63" s="2">
-        <v>0</v>
-      </c>
-      <c r="S63" s="2">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>61</v>
       </c>
@@ -4364,13 +3797,13 @@
         <v>0</v>
       </c>
       <c r="J64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K64">
         <v>0</v>
       </c>
       <c r="L64">
-        <v>9820</v>
+        <v>9822</v>
       </c>
       <c r="M64">
         <v>8</v>
@@ -4379,22 +3812,13 @@
         <v>484</v>
       </c>
       <c r="O64">
-        <v>41401</v>
+        <v>41404</v>
       </c>
       <c r="P64">
         <v>60527</v>
       </c>
-      <c r="Q64" s="2">
-        <v>5985</v>
-      </c>
-      <c r="R64" s="2">
-        <v>0</v>
-      </c>
-      <c r="S64" s="2">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>62</v>
       </c>
@@ -4414,46 +3838,37 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>41272</v>
+        <v>41294</v>
       </c>
       <c r="H65">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="I65">
         <v>13</v>
       </c>
       <c r="J65">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="K65">
         <v>0</v>
       </c>
       <c r="L65">
-        <v>13402</v>
+        <v>13427</v>
       </c>
       <c r="M65">
         <v>2</v>
       </c>
       <c r="N65">
-        <v>2395</v>
+        <v>2447</v>
       </c>
       <c r="O65">
-        <v>34543</v>
+        <v>35927</v>
       </c>
       <c r="P65">
         <v>58103</v>
       </c>
-      <c r="Q65" s="2">
-        <v>13282</v>
-      </c>
-      <c r="R65" s="2">
-        <v>0</v>
-      </c>
-      <c r="S65" s="2">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="66" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>63</v>
       </c>
@@ -4488,7 +3903,7 @@
         <v>0</v>
       </c>
       <c r="L66">
-        <v>13731</v>
+        <v>13733</v>
       </c>
       <c r="M66">
         <v>2</v>
@@ -4497,22 +3912,13 @@
         <v>4021</v>
       </c>
       <c r="O66">
-        <v>63158</v>
+        <v>63161</v>
       </c>
       <c r="P66">
-        <v>93809</v>
-      </c>
-      <c r="Q66" s="2">
-        <v>17742</v>
-      </c>
-      <c r="R66" s="2">
-        <v>0</v>
-      </c>
-      <c r="S66" s="2">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+        <v>93810</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>64</v>
       </c>
@@ -4541,7 +3947,7 @@
         <v>0</v>
       </c>
       <c r="J67">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K67">
         <v>0</v>
@@ -4556,22 +3962,13 @@
         <v>3638</v>
       </c>
       <c r="O67">
-        <v>65129</v>
+        <v>65130</v>
       </c>
       <c r="P67">
         <v>78022</v>
       </c>
-      <c r="Q67" s="2">
-        <v>9807</v>
-      </c>
-      <c r="R67" s="2">
-        <v>0</v>
-      </c>
-      <c r="S67" s="2">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="68" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>65</v>
       </c>
@@ -4591,46 +3988,37 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>65358</v>
+        <v>65387</v>
       </c>
       <c r="H68">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="I68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J68">
-        <v>163</v>
+        <v>3</v>
       </c>
       <c r="K68">
         <v>0</v>
       </c>
       <c r="L68">
-        <v>18453</v>
+        <v>18625</v>
       </c>
       <c r="M68">
         <v>2</v>
       </c>
       <c r="N68">
-        <v>1525</v>
+        <v>1550</v>
       </c>
       <c r="O68">
-        <v>58256</v>
+        <v>58846</v>
       </c>
       <c r="P68">
         <v>71325</v>
       </c>
-      <c r="Q68" s="2">
-        <v>7850</v>
-      </c>
-      <c r="R68" s="2">
-        <v>0</v>
-      </c>
-      <c r="S68" s="2">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="69" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>66</v>
       </c>
@@ -4659,7 +4047,7 @@
         <v>0</v>
       </c>
       <c r="J69">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="K69">
         <v>0</v>
@@ -4674,22 +4062,13 @@
         <v>2619</v>
       </c>
       <c r="O69">
-        <v>40997</v>
+        <v>41118</v>
       </c>
       <c r="P69">
-        <v>36117</v>
-      </c>
-      <c r="Q69" s="2">
-        <v>6528</v>
-      </c>
-      <c r="R69" s="2">
-        <v>0</v>
-      </c>
-      <c r="S69" s="2">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+        <v>36118</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>67</v>
       </c>
@@ -4738,17 +4117,8 @@
       <c r="P70">
         <v>42051</v>
       </c>
-      <c r="Q70" s="2">
-        <v>5798</v>
-      </c>
-      <c r="R70" s="2">
-        <v>0</v>
-      </c>
-      <c r="S70" s="2">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>68</v>
       </c>
@@ -4789,25 +4159,16 @@
         <v>1</v>
       </c>
       <c r="N71">
-        <v>4388</v>
+        <v>4389</v>
       </c>
       <c r="O71">
-        <v>46419</v>
+        <v>46421</v>
       </c>
       <c r="P71">
-        <v>48896</v>
-      </c>
-      <c r="Q71" s="2">
-        <v>6782</v>
-      </c>
-      <c r="R71" s="2">
-        <v>0</v>
-      </c>
-      <c r="S71" s="2">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+        <v>49140</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>69</v>
       </c>
@@ -4836,37 +4197,28 @@
         <v>0</v>
       </c>
       <c r="J72">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K72">
         <v>0</v>
       </c>
       <c r="L72">
-        <v>17203</v>
+        <v>17217</v>
       </c>
       <c r="M72">
         <v>9</v>
       </c>
       <c r="N72">
-        <v>3665</v>
+        <v>3666</v>
       </c>
       <c r="O72">
-        <v>57835</v>
+        <v>57848</v>
       </c>
       <c r="P72">
         <v>85505</v>
       </c>
-      <c r="Q72" s="2">
-        <v>12340</v>
-      </c>
-      <c r="R72" s="2">
-        <v>0</v>
-      </c>
-      <c r="S72" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>70</v>
       </c>
@@ -4895,13 +4247,13 @@
         <v>0</v>
       </c>
       <c r="J73">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="K73">
         <v>0</v>
       </c>
       <c r="L73">
-        <v>14837</v>
+        <v>14879</v>
       </c>
       <c r="M73">
         <v>7</v>
@@ -4910,22 +4262,13 @@
         <v>3783</v>
       </c>
       <c r="O73">
-        <v>53849</v>
+        <v>53997</v>
       </c>
       <c r="P73">
         <v>67666</v>
       </c>
-      <c r="Q73" s="2">
-        <v>10010</v>
-      </c>
-      <c r="R73" s="2">
-        <v>0</v>
-      </c>
-      <c r="S73" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="74" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>89</v>
       </c>
@@ -4937,53 +4280,44 @@
         <v>0</v>
       </c>
       <c r="E74">
-        <v>2430386</v>
+        <v>2430387</v>
       </c>
       <c r="F74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G74">
-        <v>2429524</v>
+        <v>2429649</v>
       </c>
       <c r="H74">
-        <v>740</v>
+        <v>617</v>
       </c>
       <c r="I74">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J74">
-        <v>736</v>
+        <v>293</v>
       </c>
       <c r="K74">
         <v>6</v>
       </c>
       <c r="L74">
-        <v>622175</v>
+        <v>622813</v>
       </c>
       <c r="M74">
-        <v>7807</v>
+        <v>7890</v>
       </c>
       <c r="N74">
-        <v>94070</v>
+        <v>94311</v>
       </c>
       <c r="O74">
-        <v>2288134</v>
+        <v>2292151</v>
       </c>
       <c r="P74">
-        <v>4689860</v>
-      </c>
-      <c r="Q74" s="2">
-        <v>626236</v>
-      </c>
-      <c r="R74" s="2">
-        <v>1</v>
-      </c>
-      <c r="S74" s="2">
-        <v>3445</v>
+        <v>4690106</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="11">
     <mergeCell ref="A74:B74"/>
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A2:A3"/>
@@ -4995,7 +4329,6 @@
     <mergeCell ref="G2:I2"/>
     <mergeCell ref="J2:M2"/>
     <mergeCell ref="N2:P2"/>
-    <mergeCell ref="Q2:S2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\New folder (13)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{011F85E2-12D9-4F12-9642-5F00A55289F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89FDD9BB-97F8-4CFF-8482-43D8406B2618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
   <si>
     <t>S. No.</t>
   </si>
@@ -293,6 +293,18 @@
   </si>
   <si>
     <t>Notice &amp; Hearing Report Last Updated On : 07-09-2026 11:56:56</t>
+  </si>
+  <si>
+    <t>DSE with UP</t>
+  </si>
+  <si>
+    <t>Electors having DSE with UP</t>
+  </si>
+  <si>
+    <t>Form 7 Generated</t>
+  </si>
+  <si>
+    <t>No Action Required</t>
   </si>
 </sst>
 </file>
@@ -328,7 +340,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
@@ -670,10 +683,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q74"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:S74"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>90</v>
       </c>
@@ -694,7 +707,7 @@
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
     </row>
-    <row r="2" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -729,8 +742,13 @@
       </c>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
-    </row>
-    <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -767,8 +785,17 @@
       <c r="P3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q3" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -817,8 +844,17 @@
       <c r="P4">
         <v>53812</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q4" s="2">
+        <v>12212</v>
+      </c>
+      <c r="R4" s="2">
+        <v>0</v>
+      </c>
+      <c r="S4" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
@@ -867,8 +903,17 @@
       <c r="P5">
         <v>74848</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q5" s="2">
+        <v>16108</v>
+      </c>
+      <c r="R5" s="2">
+        <v>0</v>
+      </c>
+      <c r="S5" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
@@ -917,8 +962,17 @@
       <c r="P6">
         <v>71989</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q6" s="2">
+        <v>17830</v>
+      </c>
+      <c r="R6" s="2">
+        <v>0</v>
+      </c>
+      <c r="S6" s="2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4</v>
       </c>
@@ -967,8 +1021,17 @@
       <c r="P7">
         <v>77581</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q7" s="2">
+        <v>20511</v>
+      </c>
+      <c r="R7" s="2">
+        <v>0</v>
+      </c>
+      <c r="S7" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
@@ -1017,8 +1080,17 @@
       <c r="P8">
         <v>73458</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q8" s="2">
+        <v>20788</v>
+      </c>
+      <c r="R8" s="2">
+        <v>0</v>
+      </c>
+      <c r="S8" s="2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6</v>
       </c>
@@ -1067,8 +1139,17 @@
       <c r="P9">
         <v>72762</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q9" s="2">
+        <v>18141</v>
+      </c>
+      <c r="R9" s="2">
+        <v>0</v>
+      </c>
+      <c r="S9" s="2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>7</v>
       </c>
@@ -1117,8 +1198,17 @@
       <c r="P10">
         <v>53124</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q10" s="2">
+        <v>9498</v>
+      </c>
+      <c r="R10" s="2">
+        <v>0</v>
+      </c>
+      <c r="S10" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>8</v>
       </c>
@@ -1167,8 +1257,17 @@
       <c r="P11">
         <v>84438</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q11" s="2">
+        <v>23477</v>
+      </c>
+      <c r="R11" s="2">
+        <v>0</v>
+      </c>
+      <c r="S11" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
@@ -1217,8 +1316,17 @@
       <c r="P12">
         <v>66685</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q12" s="2">
+        <v>17786</v>
+      </c>
+      <c r="R12" s="2">
+        <v>0</v>
+      </c>
+      <c r="S12" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
@@ -1267,8 +1375,17 @@
       <c r="P13">
         <v>56564</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q13" s="2">
+        <v>16237</v>
+      </c>
+      <c r="R13" s="2">
+        <v>0</v>
+      </c>
+      <c r="S13" s="2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>11</v>
       </c>
@@ -1317,8 +1434,17 @@
       <c r="P14">
         <v>77955</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q14" s="2">
+        <v>19716</v>
+      </c>
+      <c r="R14" s="2">
+        <v>0</v>
+      </c>
+      <c r="S14" s="2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12</v>
       </c>
@@ -1367,8 +1493,17 @@
       <c r="P15">
         <v>67178</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q15" s="2">
+        <v>4859</v>
+      </c>
+      <c r="R15" s="2">
+        <v>0</v>
+      </c>
+      <c r="S15" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13</v>
       </c>
@@ -1417,8 +1552,17 @@
       <c r="P16">
         <v>71673</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q16" s="2">
+        <v>5197</v>
+      </c>
+      <c r="R16" s="2">
+        <v>0</v>
+      </c>
+      <c r="S16" s="2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>14</v>
       </c>
@@ -1467,8 +1611,17 @@
       <c r="P17">
         <v>65457</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q17" s="2">
+        <v>5417</v>
+      </c>
+      <c r="R17" s="2">
+        <v>0</v>
+      </c>
+      <c r="S17" s="2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>15</v>
       </c>
@@ -1517,8 +1670,17 @@
       <c r="P18">
         <v>71475</v>
       </c>
-    </row>
-    <row r="19" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q18" s="2">
+        <v>6819</v>
+      </c>
+      <c r="R18" s="2">
+        <v>0</v>
+      </c>
+      <c r="S18" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>16</v>
       </c>
@@ -1567,8 +1729,17 @@
       <c r="P19">
         <v>106227</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q19" s="2">
+        <v>6135</v>
+      </c>
+      <c r="R19" s="2">
+        <v>0</v>
+      </c>
+      <c r="S19" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>17</v>
       </c>
@@ -1617,8 +1788,17 @@
       <c r="P20">
         <v>75812</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q20" s="2">
+        <v>8984</v>
+      </c>
+      <c r="R20" s="2">
+        <v>0</v>
+      </c>
+      <c r="S20" s="2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>18</v>
       </c>
@@ -1667,8 +1847,17 @@
       <c r="P21">
         <v>62460</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q21" s="2">
+        <v>3868</v>
+      </c>
+      <c r="R21" s="2">
+        <v>0</v>
+      </c>
+      <c r="S21" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>19</v>
       </c>
@@ -1717,8 +1906,17 @@
       <c r="P22">
         <v>64099</v>
       </c>
-    </row>
-    <row r="23" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q22" s="2">
+        <v>4848</v>
+      </c>
+      <c r="R22" s="2">
+        <v>0</v>
+      </c>
+      <c r="S22" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>20</v>
       </c>
@@ -1767,8 +1965,17 @@
       <c r="P23">
         <v>57094</v>
       </c>
-    </row>
-    <row r="24" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q23" s="2">
+        <v>3541</v>
+      </c>
+      <c r="R23" s="2">
+        <v>0</v>
+      </c>
+      <c r="S23" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>21</v>
       </c>
@@ -1817,8 +2024,17 @@
       <c r="P24">
         <v>65629</v>
       </c>
-    </row>
-    <row r="25" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q24" s="2">
+        <v>3492</v>
+      </c>
+      <c r="R24" s="2">
+        <v>0</v>
+      </c>
+      <c r="S24" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>22</v>
       </c>
@@ -1867,8 +2083,17 @@
       <c r="P25">
         <v>57533</v>
       </c>
-    </row>
-    <row r="26" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q25" s="2">
+        <v>3231</v>
+      </c>
+      <c r="R25" s="2">
+        <v>0</v>
+      </c>
+      <c r="S25" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23</v>
       </c>
@@ -1917,8 +2142,17 @@
       <c r="P26">
         <v>66594</v>
       </c>
-    </row>
-    <row r="27" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q26" s="2">
+        <v>3333</v>
+      </c>
+      <c r="R26" s="2">
+        <v>0</v>
+      </c>
+      <c r="S26" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>24</v>
       </c>
@@ -1967,8 +2201,17 @@
       <c r="P27">
         <v>63288</v>
       </c>
-    </row>
-    <row r="28" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q27" s="2">
+        <v>12669</v>
+      </c>
+      <c r="R27" s="2">
+        <v>0</v>
+      </c>
+      <c r="S27" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25</v>
       </c>
@@ -2017,8 +2260,17 @@
       <c r="P28">
         <v>80620</v>
       </c>
-    </row>
-    <row r="29" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q28" s="2">
+        <v>13995</v>
+      </c>
+      <c r="R28" s="2">
+        <v>0</v>
+      </c>
+      <c r="S28" s="2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26</v>
       </c>
@@ -2067,8 +2319,17 @@
       <c r="P29">
         <v>83836</v>
       </c>
-    </row>
-    <row r="30" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q29" s="2">
+        <v>14229</v>
+      </c>
+      <c r="R29" s="2">
+        <v>0</v>
+      </c>
+      <c r="S29" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>27</v>
       </c>
@@ -2117,8 +2378,17 @@
       <c r="P30">
         <v>86933</v>
       </c>
-    </row>
-    <row r="31" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q30" s="2">
+        <v>12564</v>
+      </c>
+      <c r="R30" s="2">
+        <v>0</v>
+      </c>
+      <c r="S30" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>28</v>
       </c>
@@ -2167,8 +2437,17 @@
       <c r="P31">
         <v>81643</v>
       </c>
-    </row>
-    <row r="32" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q31" s="2">
+        <v>14581</v>
+      </c>
+      <c r="R31" s="2">
+        <v>0</v>
+      </c>
+      <c r="S31" s="2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>29</v>
       </c>
@@ -2217,8 +2496,17 @@
       <c r="P32">
         <v>74810</v>
       </c>
-    </row>
-    <row r="33" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q32" s="2">
+        <v>11379</v>
+      </c>
+      <c r="R32" s="2">
+        <v>0</v>
+      </c>
+      <c r="S32" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>30</v>
       </c>
@@ -2267,8 +2555,17 @@
       <c r="P33">
         <v>76969</v>
       </c>
-    </row>
-    <row r="34" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q33" s="2">
+        <v>6678</v>
+      </c>
+      <c r="R33" s="2">
+        <v>0</v>
+      </c>
+      <c r="S33" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>31</v>
       </c>
@@ -2317,8 +2614,17 @@
       <c r="P34">
         <v>74624</v>
       </c>
-    </row>
-    <row r="35" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q34" s="2">
+        <v>7137</v>
+      </c>
+      <c r="R34" s="2">
+        <v>0</v>
+      </c>
+      <c r="S34" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32</v>
       </c>
@@ -2367,8 +2673,17 @@
       <c r="P35">
         <v>76465</v>
       </c>
-    </row>
-    <row r="36" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q35" s="2">
+        <v>8879</v>
+      </c>
+      <c r="R35" s="2">
+        <v>0</v>
+      </c>
+      <c r="S35" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>33</v>
       </c>
@@ -2417,8 +2732,17 @@
       <c r="P36">
         <v>60419</v>
       </c>
-    </row>
-    <row r="37" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q36" s="2">
+        <v>3855</v>
+      </c>
+      <c r="R36" s="2">
+        <v>0</v>
+      </c>
+      <c r="S36" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>34</v>
       </c>
@@ -2467,8 +2791,17 @@
       <c r="P37">
         <v>57832</v>
       </c>
-    </row>
-    <row r="38" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q37" s="2">
+        <v>4036</v>
+      </c>
+      <c r="R37" s="2">
+        <v>0</v>
+      </c>
+      <c r="S37" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>35</v>
       </c>
@@ -2517,8 +2850,17 @@
       <c r="P38">
         <v>63038</v>
       </c>
-    </row>
-    <row r="39" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q38" s="2">
+        <v>5135</v>
+      </c>
+      <c r="R38" s="2">
+        <v>0</v>
+      </c>
+      <c r="S38" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>36</v>
       </c>
@@ -2567,8 +2909,17 @@
       <c r="P39">
         <v>71133</v>
       </c>
-    </row>
-    <row r="40" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q39" s="2">
+        <v>5903</v>
+      </c>
+      <c r="R39" s="2">
+        <v>0</v>
+      </c>
+      <c r="S39" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>37</v>
       </c>
@@ -2617,8 +2968,17 @@
       <c r="P40">
         <v>73242</v>
       </c>
-    </row>
-    <row r="41" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q40" s="2">
+        <v>3824</v>
+      </c>
+      <c r="R40" s="2">
+        <v>0</v>
+      </c>
+      <c r="S40" s="2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>38</v>
       </c>
@@ -2667,8 +3027,17 @@
       <c r="P41">
         <v>85251</v>
       </c>
-    </row>
-    <row r="42" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q41" s="2">
+        <v>6015</v>
+      </c>
+      <c r="R41" s="2">
+        <v>0</v>
+      </c>
+      <c r="S41" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>39</v>
       </c>
@@ -2717,8 +3086,17 @@
       <c r="P42">
         <v>68615</v>
       </c>
-    </row>
-    <row r="43" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q42" s="2">
+        <v>4708</v>
+      </c>
+      <c r="R42" s="2">
+        <v>0</v>
+      </c>
+      <c r="S42" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>40</v>
       </c>
@@ -2767,8 +3145,17 @@
       <c r="P43">
         <v>63043</v>
       </c>
-    </row>
-    <row r="44" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q43" s="2">
+        <v>5219</v>
+      </c>
+      <c r="R43" s="2">
+        <v>0</v>
+      </c>
+      <c r="S43" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>41</v>
       </c>
@@ -2817,8 +3204,17 @@
       <c r="P44">
         <v>68393</v>
       </c>
-    </row>
-    <row r="45" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q44" s="2">
+        <v>7659</v>
+      </c>
+      <c r="R44" s="2">
+        <v>0</v>
+      </c>
+      <c r="S44" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>42</v>
       </c>
@@ -2867,8 +3263,17 @@
       <c r="P45">
         <v>76287</v>
       </c>
-    </row>
-    <row r="46" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q45" s="2">
+        <v>6998</v>
+      </c>
+      <c r="R45" s="2">
+        <v>0</v>
+      </c>
+      <c r="S45" s="2">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>43</v>
       </c>
@@ -2917,8 +3322,17 @@
       <c r="P46">
         <v>64160</v>
       </c>
-    </row>
-    <row r="47" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q46" s="2">
+        <v>7548</v>
+      </c>
+      <c r="R46" s="2">
+        <v>0</v>
+      </c>
+      <c r="S46" s="2">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>44</v>
       </c>
@@ -2967,8 +3381,17 @@
       <c r="P47">
         <v>49875</v>
       </c>
-    </row>
-    <row r="48" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q47" s="2">
+        <v>5046</v>
+      </c>
+      <c r="R47" s="2">
+        <v>0</v>
+      </c>
+      <c r="S47" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>45</v>
       </c>
@@ -3017,8 +3440,17 @@
       <c r="P48">
         <v>54142</v>
       </c>
-    </row>
-    <row r="49" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q48" s="2">
+        <v>4623</v>
+      </c>
+      <c r="R48" s="2">
+        <v>0</v>
+      </c>
+      <c r="S48" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>46</v>
       </c>
@@ -3067,8 +3499,17 @@
       <c r="P49">
         <v>55376</v>
       </c>
-    </row>
-    <row r="50" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q49" s="2">
+        <v>5057</v>
+      </c>
+      <c r="R49" s="2">
+        <v>0</v>
+      </c>
+      <c r="S49" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>47</v>
       </c>
@@ -3117,8 +3558,17 @@
       <c r="P50">
         <v>63298</v>
       </c>
-    </row>
-    <row r="51" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q50" s="2">
+        <v>7292</v>
+      </c>
+      <c r="R50" s="2">
+        <v>0</v>
+      </c>
+      <c r="S50" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>48</v>
       </c>
@@ -3167,8 +3617,17 @@
       <c r="P51">
         <v>71754</v>
       </c>
-    </row>
-    <row r="52" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q51" s="2">
+        <v>7715</v>
+      </c>
+      <c r="R51" s="2">
+        <v>0</v>
+      </c>
+      <c r="S51" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>49</v>
       </c>
@@ -3217,8 +3676,17 @@
       <c r="P52">
         <v>63987</v>
       </c>
-    </row>
-    <row r="53" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q52" s="2">
+        <v>5655</v>
+      </c>
+      <c r="R52" s="2">
+        <v>0</v>
+      </c>
+      <c r="S52" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>50</v>
       </c>
@@ -3267,8 +3735,17 @@
       <c r="P53">
         <v>56306</v>
       </c>
-    </row>
-    <row r="54" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q53" s="2">
+        <v>6551</v>
+      </c>
+      <c r="R53" s="2">
+        <v>0</v>
+      </c>
+      <c r="S53" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>51</v>
       </c>
@@ -3317,8 +3794,17 @@
       <c r="P54">
         <v>58440</v>
       </c>
-    </row>
-    <row r="55" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q54" s="2">
+        <v>7347</v>
+      </c>
+      <c r="R54" s="2">
+        <v>0</v>
+      </c>
+      <c r="S54" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>52</v>
       </c>
@@ -3367,8 +3853,17 @@
       <c r="P55">
         <v>58215</v>
       </c>
-    </row>
-    <row r="56" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q55" s="2">
+        <v>5098</v>
+      </c>
+      <c r="R55" s="2">
+        <v>0</v>
+      </c>
+      <c r="S55" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>53</v>
       </c>
@@ -3417,8 +3912,17 @@
       <c r="P56">
         <v>46365</v>
       </c>
-    </row>
-    <row r="57" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q56" s="2">
+        <v>4882</v>
+      </c>
+      <c r="R56" s="2">
+        <v>0</v>
+      </c>
+      <c r="S56" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>54</v>
       </c>
@@ -3467,8 +3971,17 @@
       <c r="P57">
         <v>61556</v>
       </c>
-    </row>
-    <row r="58" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q57" s="2">
+        <v>6870</v>
+      </c>
+      <c r="R57" s="2">
+        <v>0</v>
+      </c>
+      <c r="S57" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>55</v>
       </c>
@@ -3517,8 +4030,17 @@
       <c r="P58">
         <v>57577</v>
       </c>
-    </row>
-    <row r="59" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q58" s="2">
+        <v>8884</v>
+      </c>
+      <c r="R58" s="2">
+        <v>0</v>
+      </c>
+      <c r="S58" s="2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>56</v>
       </c>
@@ -3567,8 +4089,17 @@
       <c r="P59">
         <v>60495</v>
       </c>
-    </row>
-    <row r="60" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q59" s="2">
+        <v>8028</v>
+      </c>
+      <c r="R59" s="2">
+        <v>0</v>
+      </c>
+      <c r="S59" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>57</v>
       </c>
@@ -3617,8 +4148,17 @@
       <c r="P60">
         <v>70140</v>
       </c>
-    </row>
-    <row r="61" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q60" s="2">
+        <v>7415</v>
+      </c>
+      <c r="R60" s="2">
+        <v>0</v>
+      </c>
+      <c r="S60" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>58</v>
       </c>
@@ -3667,8 +4207,17 @@
       <c r="P61">
         <v>55240</v>
       </c>
-    </row>
-    <row r="62" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q61" s="2">
+        <v>7927</v>
+      </c>
+      <c r="R61" s="2">
+        <v>1</v>
+      </c>
+      <c r="S61" s="2">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>59</v>
       </c>
@@ -3717,8 +4266,17 @@
       <c r="P62">
         <v>51334</v>
       </c>
-    </row>
-    <row r="63" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q62" s="2">
+        <v>6917</v>
+      </c>
+      <c r="R62" s="2">
+        <v>0</v>
+      </c>
+      <c r="S62" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>60</v>
       </c>
@@ -3767,8 +4325,17 @@
       <c r="P63">
         <v>68691</v>
       </c>
-    </row>
-    <row r="64" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q63" s="2">
+        <v>9766</v>
+      </c>
+      <c r="R63" s="2">
+        <v>0</v>
+      </c>
+      <c r="S63" s="2">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>61</v>
       </c>
@@ -3817,8 +4384,17 @@
       <c r="P64">
         <v>60527</v>
       </c>
-    </row>
-    <row r="65" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q64" s="2">
+        <v>5985</v>
+      </c>
+      <c r="R64" s="2">
+        <v>0</v>
+      </c>
+      <c r="S64" s="2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>62</v>
       </c>
@@ -3867,8 +4443,17 @@
       <c r="P65">
         <v>58103</v>
       </c>
-    </row>
-    <row r="66" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q65" s="2">
+        <v>13282</v>
+      </c>
+      <c r="R65" s="2">
+        <v>0</v>
+      </c>
+      <c r="S65" s="2">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>63</v>
       </c>
@@ -3917,8 +4502,17 @@
       <c r="P66">
         <v>93810</v>
       </c>
-    </row>
-    <row r="67" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q66" s="2">
+        <v>17742</v>
+      </c>
+      <c r="R66" s="2">
+        <v>0</v>
+      </c>
+      <c r="S66" s="2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>64</v>
       </c>
@@ -3967,8 +4561,17 @@
       <c r="P67">
         <v>78022</v>
       </c>
-    </row>
-    <row r="68" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q67" s="2">
+        <v>9807</v>
+      </c>
+      <c r="R67" s="2">
+        <v>0</v>
+      </c>
+      <c r="S67" s="2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>65</v>
       </c>
@@ -4017,8 +4620,17 @@
       <c r="P68">
         <v>71325</v>
       </c>
-    </row>
-    <row r="69" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q68" s="2">
+        <v>7850</v>
+      </c>
+      <c r="R68" s="2">
+        <v>0</v>
+      </c>
+      <c r="S68" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>66</v>
       </c>
@@ -4067,8 +4679,17 @@
       <c r="P69">
         <v>36118</v>
       </c>
-    </row>
-    <row r="70" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q69" s="2">
+        <v>6528</v>
+      </c>
+      <c r="R69" s="2">
+        <v>0</v>
+      </c>
+      <c r="S69" s="2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>67</v>
       </c>
@@ -4117,8 +4738,17 @@
       <c r="P70">
         <v>42051</v>
       </c>
-    </row>
-    <row r="71" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q70" s="2">
+        <v>5798</v>
+      </c>
+      <c r="R70" s="2">
+        <v>0</v>
+      </c>
+      <c r="S70" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>68</v>
       </c>
@@ -4167,8 +4797,17 @@
       <c r="P71">
         <v>49140</v>
       </c>
-    </row>
-    <row r="72" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q71" s="2">
+        <v>6782</v>
+      </c>
+      <c r="R71" s="2">
+        <v>0</v>
+      </c>
+      <c r="S71" s="2">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>69</v>
       </c>
@@ -4217,8 +4856,17 @@
       <c r="P72">
         <v>85505</v>
       </c>
-    </row>
-    <row r="73" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q72" s="2">
+        <v>12340</v>
+      </c>
+      <c r="R72" s="2">
+        <v>0</v>
+      </c>
+      <c r="S72" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>70</v>
       </c>
@@ -4267,8 +4915,17 @@
       <c r="P73">
         <v>67666</v>
       </c>
-    </row>
-    <row r="74" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="Q73" s="2">
+        <v>10010</v>
+      </c>
+      <c r="R73" s="2">
+        <v>0</v>
+      </c>
+      <c r="S73" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>89</v>
       </c>
@@ -4315,9 +4972,18 @@
       <c r="P74">
         <v>4690106</v>
       </c>
+      <c r="Q74" s="2">
+        <v>626236</v>
+      </c>
+      <c r="R74" s="2">
+        <v>1</v>
+      </c>
+      <c r="S74" s="2">
+        <v>3445</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="A74:B74"/>
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A2:A3"/>
@@ -4329,6 +4995,7 @@
     <mergeCell ref="G2:I2"/>
     <mergeCell ref="J2:M2"/>
     <mergeCell ref="N2:P2"/>
+    <mergeCell ref="Q2:S2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\New folder (13)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89FDD9BB-97F8-4CFF-8482-43D8406B2618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{600F57FA-A87D-4182-AA36-14A323BA7F90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -292,7 +292,7 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Notice &amp; Hearing Report Last Updated On : 07-09-2026 11:56:56</t>
+    <t>Notice &amp; Hearing Report Last Updated On : 07-09-2026 07:56:57</t>
   </si>
   <si>
     <t>DSE with UP</t>
@@ -824,22 +824,22 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>17795</v>
+        <v>17792</v>
       </c>
       <c r="M4">
         <v>948</v>
       </c>
       <c r="N4">
-        <v>861</v>
+        <v>854</v>
       </c>
       <c r="O4">
-        <v>50436</v>
+        <v>50323</v>
       </c>
       <c r="P4">
         <v>53812</v>
@@ -883,13 +883,13 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>11383</v>
+        <v>11380</v>
       </c>
       <c r="M5">
         <v>749</v>
@@ -898,7 +898,7 @@
         <v>854</v>
       </c>
       <c r="O5">
-        <v>52854</v>
+        <v>52482</v>
       </c>
       <c r="P5">
         <v>74848</v>
@@ -933,31 +933,31 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>39673</v>
+        <v>39665</v>
       </c>
       <c r="H6">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="I6">
         <v>3</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>93</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>5967</v>
+        <v>5875</v>
       </c>
       <c r="M6">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N6">
-        <v>1746</v>
+        <v>1742</v>
       </c>
       <c r="O6">
-        <v>33213</v>
+        <v>33211</v>
       </c>
       <c r="P6">
         <v>71989</v>
@@ -1001,13 +1001,13 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>5616</v>
+        <v>5605</v>
       </c>
       <c r="M7">
         <v>257</v>
@@ -1016,7 +1016,7 @@
         <v>1985</v>
       </c>
       <c r="O7">
-        <v>35013</v>
+        <v>35002</v>
       </c>
       <c r="P7">
         <v>77581</v>
@@ -1131,10 +1131,10 @@
         <v>49</v>
       </c>
       <c r="N9">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="O9">
-        <v>41898</v>
+        <v>41894</v>
       </c>
       <c r="P9">
         <v>72762</v>
@@ -1178,22 +1178,22 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>10927</v>
+        <v>10912</v>
       </c>
       <c r="M10">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="N10">
         <v>781</v>
       </c>
       <c r="O10">
-        <v>35722</v>
+        <v>35600</v>
       </c>
       <c r="P10">
         <v>53124</v>
@@ -1296,22 +1296,22 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="L12">
-        <v>9972</v>
+        <v>9922</v>
       </c>
       <c r="M12">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="N12">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="O12">
-        <v>39300</v>
+        <v>38588</v>
       </c>
       <c r="P12">
         <v>66685</v>
@@ -1414,22 +1414,22 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>14971</v>
+        <v>14957</v>
       </c>
       <c r="M14">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="N14">
         <v>5545</v>
       </c>
       <c r="O14">
-        <v>30281</v>
+        <v>30269</v>
       </c>
       <c r="P14">
         <v>77955</v>
@@ -2172,31 +2172,31 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>44132</v>
+        <v>44071</v>
       </c>
       <c r="H27">
-        <v>144</v>
+        <v>205</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="L27">
-        <v>9658</v>
+        <v>9654</v>
       </c>
       <c r="M27">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N27">
-        <v>2760</v>
+        <v>2638</v>
       </c>
       <c r="O27">
-        <v>40059</v>
+        <v>40096</v>
       </c>
       <c r="P27">
         <v>63288</v>
@@ -2231,31 +2231,31 @@
         <v>0</v>
       </c>
       <c r="G28">
-        <v>54336</v>
+        <v>54335</v>
       </c>
       <c r="H28">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I28">
         <v>0</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="K28">
         <v>0</v>
       </c>
       <c r="L28">
-        <v>8827</v>
+        <v>8798</v>
       </c>
       <c r="M28">
-        <v>850</v>
+        <v>802</v>
       </c>
       <c r="N28">
-        <v>3215</v>
+        <v>3202</v>
       </c>
       <c r="O28">
-        <v>50591</v>
+        <v>50536</v>
       </c>
       <c r="P28">
         <v>80620</v>
@@ -2476,22 +2476,22 @@
         <v>0</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K32">
         <v>0</v>
       </c>
       <c r="L32">
-        <v>10557</v>
+        <v>10555</v>
       </c>
       <c r="M32">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="N32">
-        <v>4332</v>
+        <v>4331</v>
       </c>
       <c r="O32">
-        <v>42262</v>
+        <v>41961</v>
       </c>
       <c r="P32">
         <v>74810</v>
@@ -2526,16 +2526,16 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <v>40200</v>
+        <v>40199</v>
       </c>
       <c r="H33">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I33">
         <v>0</v>
       </c>
       <c r="J33">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K33">
         <v>0</v>
@@ -2547,10 +2547,10 @@
         <v>258</v>
       </c>
       <c r="N33">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="O33">
-        <v>37515</v>
+        <v>37505</v>
       </c>
       <c r="P33">
         <v>76969</v>
@@ -2600,16 +2600,16 @@
         <v>0</v>
       </c>
       <c r="L34">
-        <v>11888</v>
+        <v>11887</v>
       </c>
       <c r="M34">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="N34">
-        <v>1306</v>
+        <v>1301</v>
       </c>
       <c r="O34">
-        <v>33842</v>
+        <v>33815</v>
       </c>
       <c r="P34">
         <v>74624</v>
@@ -2644,31 +2644,31 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>33283</v>
+        <v>33282</v>
       </c>
       <c r="H35">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="I35">
         <v>0</v>
       </c>
       <c r="J35">
-        <v>2</v>
+        <v>135</v>
       </c>
       <c r="K35">
         <v>0</v>
       </c>
       <c r="L35">
-        <v>7714</v>
+        <v>7593</v>
       </c>
       <c r="M35">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="N35">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="O35">
-        <v>31866</v>
+        <v>31854</v>
       </c>
       <c r="P35">
         <v>76465</v>
@@ -3405,10 +3405,10 @@
         <v>0</v>
       </c>
       <c r="E48">
-        <v>19641</v>
+        <v>19640</v>
       </c>
       <c r="F48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48">
         <v>19641</v>
@@ -3420,13 +3420,13 @@
         <v>0</v>
       </c>
       <c r="J48">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K48">
         <v>0</v>
       </c>
       <c r="L48">
-        <v>3799</v>
+        <v>3793</v>
       </c>
       <c r="M48">
         <v>4</v>
@@ -3470,31 +3470,31 @@
         <v>0</v>
       </c>
       <c r="G49">
-        <v>21651</v>
+        <v>21649</v>
       </c>
       <c r="H49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K49">
         <v>0</v>
       </c>
       <c r="L49">
-        <v>3627</v>
+        <v>3615</v>
       </c>
       <c r="M49">
         <v>0</v>
       </c>
       <c r="N49">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="O49">
-        <v>21024</v>
+        <v>21015</v>
       </c>
       <c r="P49">
         <v>55376</v>
@@ -3774,13 +3774,13 @@
         <v>0</v>
       </c>
       <c r="J54">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K54">
         <v>0</v>
       </c>
       <c r="L54">
-        <v>2602</v>
+        <v>2599</v>
       </c>
       <c r="M54">
         <v>5</v>
@@ -3789,7 +3789,7 @@
         <v>391</v>
       </c>
       <c r="O54">
-        <v>20366</v>
+        <v>20354</v>
       </c>
       <c r="P54">
         <v>58440</v>
@@ -3833,13 +3833,13 @@
         <v>0</v>
       </c>
       <c r="J55">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="K55">
         <v>4</v>
       </c>
       <c r="L55">
-        <v>2105</v>
+        <v>2090</v>
       </c>
       <c r="M55">
         <v>1</v>
@@ -3848,7 +3848,7 @@
         <v>129</v>
       </c>
       <c r="O55">
-        <v>15889</v>
+        <v>15874</v>
       </c>
       <c r="P55">
         <v>58215</v>
@@ -3892,7 +3892,7 @@
         <v>0</v>
       </c>
       <c r="J56">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K56">
         <v>0</v>
@@ -3904,7 +3904,7 @@
         <v>3</v>
       </c>
       <c r="N56">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="O56">
         <v>18747</v>
@@ -4364,13 +4364,13 @@
         <v>0</v>
       </c>
       <c r="J64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K64">
         <v>0</v>
       </c>
       <c r="L64">
-        <v>9822</v>
+        <v>9820</v>
       </c>
       <c r="M64">
         <v>8</v>
@@ -4379,7 +4379,7 @@
         <v>484</v>
       </c>
       <c r="O64">
-        <v>41404</v>
+        <v>41401</v>
       </c>
       <c r="P64">
         <v>60527</v>
@@ -4414,31 +4414,31 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>41294</v>
+        <v>41272</v>
       </c>
       <c r="H65">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="I65">
         <v>13</v>
       </c>
       <c r="J65">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="K65">
         <v>0</v>
       </c>
       <c r="L65">
-        <v>13427</v>
+        <v>13402</v>
       </c>
       <c r="M65">
         <v>2</v>
       </c>
       <c r="N65">
-        <v>2447</v>
+        <v>2395</v>
       </c>
       <c r="O65">
-        <v>35927</v>
+        <v>34543</v>
       </c>
       <c r="P65">
         <v>58103</v>
@@ -4488,7 +4488,7 @@
         <v>0</v>
       </c>
       <c r="L66">
-        <v>13733</v>
+        <v>13731</v>
       </c>
       <c r="M66">
         <v>2</v>
@@ -4497,10 +4497,10 @@
         <v>4021</v>
       </c>
       <c r="O66">
-        <v>63161</v>
+        <v>63158</v>
       </c>
       <c r="P66">
-        <v>93810</v>
+        <v>93809</v>
       </c>
       <c r="Q66" s="2">
         <v>17742</v>
@@ -4541,7 +4541,7 @@
         <v>0</v>
       </c>
       <c r="J67">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K67">
         <v>0</v>
@@ -4556,7 +4556,7 @@
         <v>3638</v>
       </c>
       <c r="O67">
-        <v>65130</v>
+        <v>65129</v>
       </c>
       <c r="P67">
         <v>78022</v>
@@ -4591,31 +4591,31 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>65387</v>
+        <v>65358</v>
       </c>
       <c r="H68">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="I68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68">
-        <v>3</v>
+        <v>163</v>
       </c>
       <c r="K68">
         <v>0</v>
       </c>
       <c r="L68">
-        <v>18625</v>
+        <v>18453</v>
       </c>
       <c r="M68">
         <v>2</v>
       </c>
       <c r="N68">
-        <v>1550</v>
+        <v>1525</v>
       </c>
       <c r="O68">
-        <v>58846</v>
+        <v>58256</v>
       </c>
       <c r="P68">
         <v>71325</v>
@@ -4659,7 +4659,7 @@
         <v>0</v>
       </c>
       <c r="J69">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="K69">
         <v>0</v>
@@ -4674,10 +4674,10 @@
         <v>2619</v>
       </c>
       <c r="O69">
-        <v>41118</v>
+        <v>40997</v>
       </c>
       <c r="P69">
-        <v>36118</v>
+        <v>36117</v>
       </c>
       <c r="Q69" s="2">
         <v>6528</v>
@@ -4789,13 +4789,13 @@
         <v>1</v>
       </c>
       <c r="N71">
-        <v>4389</v>
+        <v>4388</v>
       </c>
       <c r="O71">
-        <v>46421</v>
+        <v>46419</v>
       </c>
       <c r="P71">
-        <v>49140</v>
+        <v>48896</v>
       </c>
       <c r="Q71" s="2">
         <v>6782</v>
@@ -4836,22 +4836,22 @@
         <v>0</v>
       </c>
       <c r="J72">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="K72">
         <v>0</v>
       </c>
       <c r="L72">
-        <v>17217</v>
+        <v>17203</v>
       </c>
       <c r="M72">
         <v>9</v>
       </c>
       <c r="N72">
-        <v>3666</v>
+        <v>3665</v>
       </c>
       <c r="O72">
-        <v>57848</v>
+        <v>57835</v>
       </c>
       <c r="P72">
         <v>85505</v>
@@ -4895,13 +4895,13 @@
         <v>0</v>
       </c>
       <c r="J73">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="K73">
         <v>0</v>
       </c>
       <c r="L73">
-        <v>14879</v>
+        <v>14837</v>
       </c>
       <c r="M73">
         <v>7</v>
@@ -4910,7 +4910,7 @@
         <v>3783</v>
       </c>
       <c r="O73">
-        <v>53997</v>
+        <v>53849</v>
       </c>
       <c r="P73">
         <v>67666</v>
@@ -4937,40 +4937,40 @@
         <v>0</v>
       </c>
       <c r="E74">
-        <v>2430387</v>
+        <v>2430386</v>
       </c>
       <c r="F74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G74">
-        <v>2429649</v>
+        <v>2429524</v>
       </c>
       <c r="H74">
-        <v>617</v>
+        <v>740</v>
       </c>
       <c r="I74">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J74">
-        <v>293</v>
+        <v>736</v>
       </c>
       <c r="K74">
         <v>6</v>
       </c>
       <c r="L74">
-        <v>622813</v>
+        <v>622175</v>
       </c>
       <c r="M74">
-        <v>7890</v>
+        <v>7807</v>
       </c>
       <c r="N74">
-        <v>94311</v>
+        <v>94070</v>
       </c>
       <c r="O74">
-        <v>2292151</v>
+        <v>2288134</v>
       </c>
       <c r="P74">
-        <v>4690106</v>
+        <v>4689860</v>
       </c>
       <c r="Q74" s="2">
         <v>626236</v>

--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\New folder (13)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{600F57FA-A87D-4182-AA36-14A323BA7F90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89FDD9BB-97F8-4CFF-8482-43D8406B2618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -292,7 +292,7 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Notice &amp; Hearing Report Last Updated On : 07-09-2026 07:56:57</t>
+    <t>Notice &amp; Hearing Report Last Updated On : 07-09-2026 11:56:56</t>
   </si>
   <si>
     <t>DSE with UP</t>
@@ -824,22 +824,22 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>17792</v>
+        <v>17795</v>
       </c>
       <c r="M4">
         <v>948</v>
       </c>
       <c r="N4">
-        <v>854</v>
+        <v>861</v>
       </c>
       <c r="O4">
-        <v>50323</v>
+        <v>50436</v>
       </c>
       <c r="P4">
         <v>53812</v>
@@ -883,13 +883,13 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>11380</v>
+        <v>11383</v>
       </c>
       <c r="M5">
         <v>749</v>
@@ -898,7 +898,7 @@
         <v>854</v>
       </c>
       <c r="O5">
-        <v>52482</v>
+        <v>52854</v>
       </c>
       <c r="P5">
         <v>74848</v>
@@ -933,31 +933,31 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>39665</v>
+        <v>39673</v>
       </c>
       <c r="H6">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="I6">
         <v>3</v>
       </c>
       <c r="J6">
-        <v>93</v>
+        <v>2</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>5875</v>
+        <v>5967</v>
       </c>
       <c r="M6">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N6">
-        <v>1742</v>
+        <v>1746</v>
       </c>
       <c r="O6">
-        <v>33211</v>
+        <v>33213</v>
       </c>
       <c r="P6">
         <v>71989</v>
@@ -1001,13 +1001,13 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>5605</v>
+        <v>5616</v>
       </c>
       <c r="M7">
         <v>257</v>
@@ -1016,7 +1016,7 @@
         <v>1985</v>
       </c>
       <c r="O7">
-        <v>35002</v>
+        <v>35013</v>
       </c>
       <c r="P7">
         <v>77581</v>
@@ -1131,10 +1131,10 @@
         <v>49</v>
       </c>
       <c r="N9">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="O9">
-        <v>41894</v>
+        <v>41898</v>
       </c>
       <c r="P9">
         <v>72762</v>
@@ -1178,22 +1178,22 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>10912</v>
+        <v>10927</v>
       </c>
       <c r="M10">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="N10">
         <v>781</v>
       </c>
       <c r="O10">
-        <v>35600</v>
+        <v>35722</v>
       </c>
       <c r="P10">
         <v>53124</v>
@@ -1296,22 +1296,22 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="L12">
-        <v>9922</v>
+        <v>9972</v>
       </c>
       <c r="M12">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N12">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="O12">
-        <v>38588</v>
+        <v>39300</v>
       </c>
       <c r="P12">
         <v>66685</v>
@@ -1414,22 +1414,22 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>14957</v>
+        <v>14971</v>
       </c>
       <c r="M14">
-        <v>1407</v>
+        <v>1411</v>
       </c>
       <c r="N14">
         <v>5545</v>
       </c>
       <c r="O14">
-        <v>30269</v>
+        <v>30281</v>
       </c>
       <c r="P14">
         <v>77955</v>
@@ -2172,31 +2172,31 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>44071</v>
+        <v>44132</v>
       </c>
       <c r="H27">
-        <v>205</v>
+        <v>144</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="L27">
-        <v>9654</v>
+        <v>9658</v>
       </c>
       <c r="M27">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N27">
-        <v>2638</v>
+        <v>2760</v>
       </c>
       <c r="O27">
-        <v>40096</v>
+        <v>40059</v>
       </c>
       <c r="P27">
         <v>63288</v>
@@ -2231,31 +2231,31 @@
         <v>0</v>
       </c>
       <c r="G28">
-        <v>54335</v>
+        <v>54336</v>
       </c>
       <c r="H28">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I28">
         <v>0</v>
       </c>
       <c r="J28">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="K28">
         <v>0</v>
       </c>
       <c r="L28">
-        <v>8798</v>
+        <v>8827</v>
       </c>
       <c r="M28">
-        <v>802</v>
+        <v>850</v>
       </c>
       <c r="N28">
-        <v>3202</v>
+        <v>3215</v>
       </c>
       <c r="O28">
-        <v>50536</v>
+        <v>50591</v>
       </c>
       <c r="P28">
         <v>80620</v>
@@ -2476,22 +2476,22 @@
         <v>0</v>
       </c>
       <c r="J32">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K32">
         <v>0</v>
       </c>
       <c r="L32">
-        <v>10555</v>
+        <v>10557</v>
       </c>
       <c r="M32">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="N32">
-        <v>4331</v>
+        <v>4332</v>
       </c>
       <c r="O32">
-        <v>41961</v>
+        <v>42262</v>
       </c>
       <c r="P32">
         <v>74810</v>
@@ -2526,16 +2526,16 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <v>40199</v>
+        <v>40200</v>
       </c>
       <c r="H33">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I33">
         <v>0</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K33">
         <v>0</v>
@@ -2547,10 +2547,10 @@
         <v>258</v>
       </c>
       <c r="N33">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="O33">
-        <v>37505</v>
+        <v>37515</v>
       </c>
       <c r="P33">
         <v>76969</v>
@@ -2600,16 +2600,16 @@
         <v>0</v>
       </c>
       <c r="L34">
-        <v>11887</v>
+        <v>11888</v>
       </c>
       <c r="M34">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N34">
-        <v>1301</v>
+        <v>1306</v>
       </c>
       <c r="O34">
-        <v>33815</v>
+        <v>33842</v>
       </c>
       <c r="P34">
         <v>74624</v>
@@ -2644,31 +2644,31 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>33282</v>
+        <v>33283</v>
       </c>
       <c r="H35">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I35">
         <v>0</v>
       </c>
       <c r="J35">
-        <v>135</v>
+        <v>2</v>
       </c>
       <c r="K35">
         <v>0</v>
       </c>
       <c r="L35">
-        <v>7593</v>
+        <v>7714</v>
       </c>
       <c r="M35">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="N35">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="O35">
-        <v>31854</v>
+        <v>31866</v>
       </c>
       <c r="P35">
         <v>76465</v>
@@ -3405,10 +3405,10 @@
         <v>0</v>
       </c>
       <c r="E48">
-        <v>19640</v>
+        <v>19641</v>
       </c>
       <c r="F48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48">
         <v>19641</v>
@@ -3420,13 +3420,13 @@
         <v>0</v>
       </c>
       <c r="J48">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K48">
         <v>0</v>
       </c>
       <c r="L48">
-        <v>3793</v>
+        <v>3799</v>
       </c>
       <c r="M48">
         <v>4</v>
@@ -3470,31 +3470,31 @@
         <v>0</v>
       </c>
       <c r="G49">
-        <v>21649</v>
+        <v>21651</v>
       </c>
       <c r="H49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K49">
         <v>0</v>
       </c>
       <c r="L49">
-        <v>3615</v>
+        <v>3627</v>
       </c>
       <c r="M49">
         <v>0</v>
       </c>
       <c r="N49">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="O49">
-        <v>21015</v>
+        <v>21024</v>
       </c>
       <c r="P49">
         <v>55376</v>
@@ -3774,13 +3774,13 @@
         <v>0</v>
       </c>
       <c r="J54">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K54">
         <v>0</v>
       </c>
       <c r="L54">
-        <v>2599</v>
+        <v>2602</v>
       </c>
       <c r="M54">
         <v>5</v>
@@ -3789,7 +3789,7 @@
         <v>391</v>
       </c>
       <c r="O54">
-        <v>20354</v>
+        <v>20366</v>
       </c>
       <c r="P54">
         <v>58440</v>
@@ -3833,13 +3833,13 @@
         <v>0</v>
       </c>
       <c r="J55">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="K55">
         <v>4</v>
       </c>
       <c r="L55">
-        <v>2090</v>
+        <v>2105</v>
       </c>
       <c r="M55">
         <v>1</v>
@@ -3848,7 +3848,7 @@
         <v>129</v>
       </c>
       <c r="O55">
-        <v>15874</v>
+        <v>15889</v>
       </c>
       <c r="P55">
         <v>58215</v>
@@ -3892,7 +3892,7 @@
         <v>0</v>
       </c>
       <c r="J56">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="K56">
         <v>0</v>
@@ -3904,7 +3904,7 @@
         <v>3</v>
       </c>
       <c r="N56">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O56">
         <v>18747</v>
@@ -4364,13 +4364,13 @@
         <v>0</v>
       </c>
       <c r="J64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K64">
         <v>0</v>
       </c>
       <c r="L64">
-        <v>9820</v>
+        <v>9822</v>
       </c>
       <c r="M64">
         <v>8</v>
@@ -4379,7 +4379,7 @@
         <v>484</v>
       </c>
       <c r="O64">
-        <v>41401</v>
+        <v>41404</v>
       </c>
       <c r="P64">
         <v>60527</v>
@@ -4414,31 +4414,31 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>41272</v>
+        <v>41294</v>
       </c>
       <c r="H65">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="I65">
         <v>13</v>
       </c>
       <c r="J65">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="K65">
         <v>0</v>
       </c>
       <c r="L65">
-        <v>13402</v>
+        <v>13427</v>
       </c>
       <c r="M65">
         <v>2</v>
       </c>
       <c r="N65">
-        <v>2395</v>
+        <v>2447</v>
       </c>
       <c r="O65">
-        <v>34543</v>
+        <v>35927</v>
       </c>
       <c r="P65">
         <v>58103</v>
@@ -4488,7 +4488,7 @@
         <v>0</v>
       </c>
       <c r="L66">
-        <v>13731</v>
+        <v>13733</v>
       </c>
       <c r="M66">
         <v>2</v>
@@ -4497,10 +4497,10 @@
         <v>4021</v>
       </c>
       <c r="O66">
-        <v>63158</v>
+        <v>63161</v>
       </c>
       <c r="P66">
-        <v>93809</v>
+        <v>93810</v>
       </c>
       <c r="Q66" s="2">
         <v>17742</v>
@@ -4541,7 +4541,7 @@
         <v>0</v>
       </c>
       <c r="J67">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K67">
         <v>0</v>
@@ -4556,7 +4556,7 @@
         <v>3638</v>
       </c>
       <c r="O67">
-        <v>65129</v>
+        <v>65130</v>
       </c>
       <c r="P67">
         <v>78022</v>
@@ -4591,31 +4591,31 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>65358</v>
+        <v>65387</v>
       </c>
       <c r="H68">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="I68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J68">
-        <v>163</v>
+        <v>3</v>
       </c>
       <c r="K68">
         <v>0</v>
       </c>
       <c r="L68">
-        <v>18453</v>
+        <v>18625</v>
       </c>
       <c r="M68">
         <v>2</v>
       </c>
       <c r="N68">
-        <v>1525</v>
+        <v>1550</v>
       </c>
       <c r="O68">
-        <v>58256</v>
+        <v>58846</v>
       </c>
       <c r="P68">
         <v>71325</v>
@@ -4659,7 +4659,7 @@
         <v>0</v>
       </c>
       <c r="J69">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="K69">
         <v>0</v>
@@ -4674,10 +4674,10 @@
         <v>2619</v>
       </c>
       <c r="O69">
-        <v>40997</v>
+        <v>41118</v>
       </c>
       <c r="P69">
-        <v>36117</v>
+        <v>36118</v>
       </c>
       <c r="Q69" s="2">
         <v>6528</v>
@@ -4789,13 +4789,13 @@
         <v>1</v>
       </c>
       <c r="N71">
-        <v>4388</v>
+        <v>4389</v>
       </c>
       <c r="O71">
-        <v>46419</v>
+        <v>46421</v>
       </c>
       <c r="P71">
-        <v>48896</v>
+        <v>49140</v>
       </c>
       <c r="Q71" s="2">
         <v>6782</v>
@@ -4836,22 +4836,22 @@
         <v>0</v>
       </c>
       <c r="J72">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K72">
         <v>0</v>
       </c>
       <c r="L72">
-        <v>17203</v>
+        <v>17217</v>
       </c>
       <c r="M72">
         <v>9</v>
       </c>
       <c r="N72">
-        <v>3665</v>
+        <v>3666</v>
       </c>
       <c r="O72">
-        <v>57835</v>
+        <v>57848</v>
       </c>
       <c r="P72">
         <v>85505</v>
@@ -4895,13 +4895,13 @@
         <v>0</v>
       </c>
       <c r="J73">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="K73">
         <v>0</v>
       </c>
       <c r="L73">
-        <v>14837</v>
+        <v>14879</v>
       </c>
       <c r="M73">
         <v>7</v>
@@ -4910,7 +4910,7 @@
         <v>3783</v>
       </c>
       <c r="O73">
-        <v>53849</v>
+        <v>53997</v>
       </c>
       <c r="P73">
         <v>67666</v>
@@ -4937,40 +4937,40 @@
         <v>0</v>
       </c>
       <c r="E74">
-        <v>2430386</v>
+        <v>2430387</v>
       </c>
       <c r="F74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G74">
-        <v>2429524</v>
+        <v>2429649</v>
       </c>
       <c r="H74">
-        <v>740</v>
+        <v>617</v>
       </c>
       <c r="I74">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J74">
-        <v>736</v>
+        <v>293</v>
       </c>
       <c r="K74">
         <v>6</v>
       </c>
       <c r="L74">
-        <v>622175</v>
+        <v>622813</v>
       </c>
       <c r="M74">
-        <v>7807</v>
+        <v>7890</v>
       </c>
       <c r="N74">
-        <v>94070</v>
+        <v>94311</v>
       </c>
       <c r="O74">
-        <v>2288134</v>
+        <v>2292151</v>
       </c>
       <c r="P74">
-        <v>4689860</v>
+        <v>4690106</v>
       </c>
       <c r="Q74" s="2">
         <v>626236</v>

--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\New folder (13)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89FDD9BB-97F8-4CFF-8482-43D8406B2618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C30A3056-7237-4D83-B4D2-BF53828ABCF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -292,7 +292,7 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Notice &amp; Hearing Report Last Updated On : 07-09-2026 11:56:56</t>
+    <t>Notice &amp; Hearing Report Last Updated On : 08-09-2026 07:56:56</t>
   </si>
   <si>
     <t>DSE with UP</t>
@@ -340,8 +340,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
@@ -684,9 +683,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S74"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>90</v>
       </c>
@@ -707,7 +706,7 @@
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -748,7 +747,7 @@
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -785,17 +784,17 @@
       <c r="P3" t="s">
         <v>18</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="Q3" t="s">
         <v>92</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="R3" t="s">
         <v>93</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="S3" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -824,37 +823,37 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>17795</v>
+        <v>17801</v>
       </c>
       <c r="M4">
-        <v>948</v>
+        <v>967</v>
       </c>
       <c r="N4">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="O4">
-        <v>50436</v>
+        <v>50447</v>
       </c>
       <c r="P4">
         <v>53812</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="Q4">
         <v>12212</v>
       </c>
-      <c r="R4" s="2">
-        <v>0</v>
-      </c>
-      <c r="S4" s="2">
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
@@ -883,7 +882,7 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -892,28 +891,28 @@
         <v>11383</v>
       </c>
       <c r="M5">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="N5">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="O5">
-        <v>52854</v>
+        <v>52926</v>
       </c>
       <c r="P5">
         <v>74848</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="Q5">
         <v>16108</v>
       </c>
-      <c r="R5" s="2">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2">
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
@@ -933,46 +932,46 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>39673</v>
+        <v>39773</v>
       </c>
       <c r="H6">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>5967</v>
+        <v>6011</v>
       </c>
       <c r="M6">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="N6">
-        <v>1746</v>
+        <v>1778</v>
       </c>
       <c r="O6">
-        <v>33213</v>
+        <v>33319</v>
       </c>
       <c r="P6">
         <v>71989</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="Q6">
         <v>17830</v>
       </c>
-      <c r="R6" s="2">
-        <v>0</v>
-      </c>
-      <c r="S6" s="2">
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4</v>
       </c>
@@ -1016,22 +1015,22 @@
         <v>1985</v>
       </c>
       <c r="O7">
-        <v>35013</v>
+        <v>35071</v>
       </c>
       <c r="P7">
         <v>77581</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="Q7">
         <v>20511</v>
       </c>
-      <c r="R7" s="2">
-        <v>0</v>
-      </c>
-      <c r="S7" s="2">
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
@@ -1060,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -1080,17 +1079,17 @@
       <c r="P8">
         <v>73458</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="Q8">
         <v>20788</v>
       </c>
-      <c r="R8" s="2">
-        <v>0</v>
-      </c>
-      <c r="S8" s="2">
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
         <v>110</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6</v>
       </c>
@@ -1119,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -1134,22 +1133,22 @@
         <v>1336</v>
       </c>
       <c r="O9">
-        <v>41898</v>
+        <v>41904</v>
       </c>
       <c r="P9">
         <v>72762</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="Q9">
         <v>18141</v>
       </c>
-      <c r="R9" s="2">
-        <v>0</v>
-      </c>
-      <c r="S9" s="2">
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
         <v>110</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>7</v>
       </c>
@@ -1178,7 +1177,7 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -1190,25 +1189,25 @@
         <v>172</v>
       </c>
       <c r="N10">
-        <v>781</v>
+        <v>813</v>
       </c>
       <c r="O10">
-        <v>35722</v>
+        <v>35727</v>
       </c>
       <c r="P10">
         <v>53124</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="Q10">
         <v>9498</v>
       </c>
-      <c r="R10" s="2">
-        <v>0</v>
-      </c>
-      <c r="S10" s="2">
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>8</v>
       </c>
@@ -1257,17 +1256,17 @@
       <c r="P11">
         <v>84438</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="Q11">
         <v>23477</v>
       </c>
-      <c r="R11" s="2">
-        <v>0</v>
-      </c>
-      <c r="S11" s="2">
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
@@ -1296,7 +1295,7 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -1308,25 +1307,25 @@
         <v>206</v>
       </c>
       <c r="N12">
-        <v>1039</v>
+        <v>1052</v>
       </c>
       <c r="O12">
-        <v>39300</v>
+        <v>39466</v>
       </c>
       <c r="P12">
         <v>66685</v>
       </c>
-      <c r="Q12" s="2">
+      <c r="Q12">
         <v>17786</v>
       </c>
-      <c r="R12" s="2">
-        <v>0</v>
-      </c>
-      <c r="S12" s="2">
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
@@ -1375,17 +1374,17 @@
       <c r="P13">
         <v>56564</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="Q13">
         <v>16237</v>
       </c>
-      <c r="R13" s="2">
-        <v>0</v>
-      </c>
-      <c r="S13" s="2">
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
         <v>106</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>11</v>
       </c>
@@ -1414,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -1426,25 +1425,25 @@
         <v>1411</v>
       </c>
       <c r="N14">
-        <v>5545</v>
+        <v>5602</v>
       </c>
       <c r="O14">
-        <v>30281</v>
+        <v>30590</v>
       </c>
       <c r="P14">
         <v>77955</v>
       </c>
-      <c r="Q14" s="2">
+      <c r="Q14">
         <v>19716</v>
       </c>
-      <c r="R14" s="2">
-        <v>0</v>
-      </c>
-      <c r="S14" s="2">
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
         <v>174</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12</v>
       </c>
@@ -1493,17 +1492,17 @@
       <c r="P15">
         <v>67178</v>
       </c>
-      <c r="Q15" s="2">
+      <c r="Q15">
         <v>4859</v>
       </c>
-      <c r="R15" s="2">
-        <v>0</v>
-      </c>
-      <c r="S15" s="2">
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13</v>
       </c>
@@ -1552,17 +1551,17 @@
       <c r="P16">
         <v>71673</v>
       </c>
-      <c r="Q16" s="2">
+      <c r="Q16">
         <v>5197</v>
       </c>
-      <c r="R16" s="2">
-        <v>0</v>
-      </c>
-      <c r="S16" s="2">
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>14</v>
       </c>
@@ -1611,17 +1610,17 @@
       <c r="P17">
         <v>65457</v>
       </c>
-      <c r="Q17" s="2">
+      <c r="Q17">
         <v>5417</v>
       </c>
-      <c r="R17" s="2">
-        <v>0</v>
-      </c>
-      <c r="S17" s="2">
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
         <v>105</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>15</v>
       </c>
@@ -1670,17 +1669,17 @@
       <c r="P18">
         <v>71475</v>
       </c>
-      <c r="Q18" s="2">
+      <c r="Q18">
         <v>6819</v>
       </c>
-      <c r="R18" s="2">
-        <v>0</v>
-      </c>
-      <c r="S18" s="2">
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>16</v>
       </c>
@@ -1709,7 +1708,7 @@
         <v>0</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19">
         <v>0</v>
@@ -1729,17 +1728,17 @@
       <c r="P19">
         <v>106227</v>
       </c>
-      <c r="Q19" s="2">
+      <c r="Q19">
         <v>6135</v>
       </c>
-      <c r="R19" s="2">
-        <v>0</v>
-      </c>
-      <c r="S19" s="2">
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>17</v>
       </c>
@@ -1788,17 +1787,17 @@
       <c r="P20">
         <v>75812</v>
       </c>
-      <c r="Q20" s="2">
+      <c r="Q20">
         <v>8984</v>
       </c>
-      <c r="R20" s="2">
-        <v>0</v>
-      </c>
-      <c r="S20" s="2">
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>18</v>
       </c>
@@ -1847,17 +1846,17 @@
       <c r="P21">
         <v>62460</v>
       </c>
-      <c r="Q21" s="2">
+      <c r="Q21">
         <v>3868</v>
       </c>
-      <c r="R21" s="2">
-        <v>0</v>
-      </c>
-      <c r="S21" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>19</v>
       </c>
@@ -1906,17 +1905,17 @@
       <c r="P22">
         <v>64099</v>
       </c>
-      <c r="Q22" s="2">
+      <c r="Q22">
         <v>4848</v>
       </c>
-      <c r="R22" s="2">
-        <v>0</v>
-      </c>
-      <c r="S22" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>20</v>
       </c>
@@ -1965,17 +1964,17 @@
       <c r="P23">
         <v>57094</v>
       </c>
-      <c r="Q23" s="2">
+      <c r="Q23">
         <v>3541</v>
       </c>
-      <c r="R23" s="2">
-        <v>0</v>
-      </c>
-      <c r="S23" s="2">
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>21</v>
       </c>
@@ -2024,17 +2023,17 @@
       <c r="P24">
         <v>65629</v>
       </c>
-      <c r="Q24" s="2">
+      <c r="Q24">
         <v>3492</v>
       </c>
-      <c r="R24" s="2">
-        <v>0</v>
-      </c>
-      <c r="S24" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>22</v>
       </c>
@@ -2083,17 +2082,17 @@
       <c r="P25">
         <v>57533</v>
       </c>
-      <c r="Q25" s="2">
+      <c r="Q25">
         <v>3231</v>
       </c>
-      <c r="R25" s="2">
-        <v>0</v>
-      </c>
-      <c r="S25" s="2">
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23</v>
       </c>
@@ -2142,17 +2141,17 @@
       <c r="P26">
         <v>66594</v>
       </c>
-      <c r="Q26" s="2">
+      <c r="Q26">
         <v>3333</v>
       </c>
-      <c r="R26" s="2">
-        <v>0</v>
-      </c>
-      <c r="S26" s="2">
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>24</v>
       </c>
@@ -2172,46 +2171,46 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>44132</v>
+        <v>44256</v>
       </c>
       <c r="H27">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="L27">
-        <v>9658</v>
+        <v>9664</v>
       </c>
       <c r="M27">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="N27">
-        <v>2760</v>
+        <v>3057</v>
       </c>
       <c r="O27">
-        <v>40059</v>
+        <v>40522</v>
       </c>
       <c r="P27">
-        <v>63288</v>
-      </c>
-      <c r="Q27" s="2">
+        <v>68986</v>
+      </c>
+      <c r="Q27">
         <v>12669</v>
       </c>
-      <c r="R27" s="2">
-        <v>0</v>
-      </c>
-      <c r="S27" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25</v>
       </c>
@@ -2231,46 +2230,46 @@
         <v>0</v>
       </c>
       <c r="G28">
-        <v>54336</v>
+        <v>54346</v>
       </c>
       <c r="H28">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I28">
         <v>0</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28">
         <v>0</v>
       </c>
       <c r="L28">
-        <v>8827</v>
+        <v>8878</v>
       </c>
       <c r="M28">
-        <v>850</v>
+        <v>855</v>
       </c>
       <c r="N28">
-        <v>3215</v>
+        <v>3220</v>
       </c>
       <c r="O28">
-        <v>50591</v>
+        <v>50675</v>
       </c>
       <c r="P28">
         <v>80620</v>
       </c>
-      <c r="Q28" s="2">
+      <c r="Q28">
         <v>13995</v>
       </c>
-      <c r="R28" s="2">
-        <v>0</v>
-      </c>
-      <c r="S28" s="2">
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
         <v>127</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26</v>
       </c>
@@ -2299,37 +2298,37 @@
         <v>0</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="K29">
         <v>0</v>
       </c>
       <c r="L29">
-        <v>8796</v>
+        <v>8797</v>
       </c>
       <c r="M29">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="N29">
-        <v>4228</v>
+        <v>4546</v>
       </c>
       <c r="O29">
-        <v>42187</v>
+        <v>42501</v>
       </c>
       <c r="P29">
         <v>83836</v>
       </c>
-      <c r="Q29" s="2">
+      <c r="Q29">
         <v>14229</v>
       </c>
-      <c r="R29" s="2">
-        <v>0</v>
-      </c>
-      <c r="S29" s="2">
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>27</v>
       </c>
@@ -2349,46 +2348,46 @@
         <v>0</v>
       </c>
       <c r="G30">
-        <v>52592</v>
+        <v>52653</v>
       </c>
       <c r="H30">
         <v>0</v>
       </c>
       <c r="I30">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K30">
         <v>0</v>
       </c>
       <c r="L30">
-        <v>11601</v>
+        <v>11652</v>
       </c>
       <c r="M30">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="N30">
-        <v>5284</v>
+        <v>5340</v>
       </c>
       <c r="O30">
-        <v>47059</v>
+        <v>47199</v>
       </c>
       <c r="P30">
         <v>86933</v>
       </c>
-      <c r="Q30" s="2">
+      <c r="Q30">
         <v>12564</v>
       </c>
-      <c r="R30" s="2">
-        <v>0</v>
-      </c>
-      <c r="S30" s="2">
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>28</v>
       </c>
@@ -2429,25 +2428,25 @@
         <v>42</v>
       </c>
       <c r="N31">
-        <v>1894</v>
+        <v>1898</v>
       </c>
       <c r="O31">
-        <v>89268</v>
+        <v>89265</v>
       </c>
       <c r="P31">
-        <v>81643</v>
-      </c>
-      <c r="Q31" s="2">
+        <v>81642</v>
+      </c>
+      <c r="Q31">
         <v>14581</v>
       </c>
-      <c r="R31" s="2">
-        <v>0</v>
-      </c>
-      <c r="S31" s="2">
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>29</v>
       </c>
@@ -2467,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="G32">
-        <v>46727</v>
+        <v>46728</v>
       </c>
       <c r="H32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -2485,28 +2484,28 @@
         <v>10557</v>
       </c>
       <c r="M32">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="N32">
-        <v>4332</v>
+        <v>4376</v>
       </c>
       <c r="O32">
-        <v>42262</v>
+        <v>42298</v>
       </c>
       <c r="P32">
         <v>74810</v>
       </c>
-      <c r="Q32" s="2">
+      <c r="Q32">
         <v>11379</v>
       </c>
-      <c r="R32" s="2">
-        <v>0</v>
-      </c>
-      <c r="S32" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>30</v>
       </c>
@@ -2526,46 +2525,46 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <v>40200</v>
+        <v>40230</v>
       </c>
       <c r="H33">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I33">
         <v>0</v>
       </c>
       <c r="J33">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K33">
         <v>0</v>
       </c>
       <c r="L33">
-        <v>5037</v>
+        <v>5057</v>
       </c>
       <c r="M33">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="N33">
-        <v>1201</v>
+        <v>1227</v>
       </c>
       <c r="O33">
-        <v>37515</v>
+        <v>37698</v>
       </c>
       <c r="P33">
         <v>76969</v>
       </c>
-      <c r="Q33" s="2">
+      <c r="Q33">
         <v>6678</v>
       </c>
-      <c r="R33" s="2">
-        <v>0</v>
-      </c>
-      <c r="S33" s="2">
+      <c r="R33">
+        <v>0</v>
+      </c>
+      <c r="S33">
         <v>19</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>31</v>
       </c>
@@ -2609,22 +2608,22 @@
         <v>1306</v>
       </c>
       <c r="O34">
-        <v>33842</v>
+        <v>33870</v>
       </c>
       <c r="P34">
         <v>74624</v>
       </c>
-      <c r="Q34" s="2">
+      <c r="Q34">
         <v>7137</v>
       </c>
-      <c r="R34" s="2">
-        <v>0</v>
-      </c>
-      <c r="S34" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32</v>
       </c>
@@ -2644,46 +2643,46 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>33283</v>
+        <v>33435</v>
       </c>
       <c r="H35">
-        <v>281</v>
+        <v>129</v>
       </c>
       <c r="I35">
         <v>0</v>
       </c>
       <c r="J35">
-        <v>2</v>
+        <v>97</v>
       </c>
       <c r="K35">
         <v>0</v>
       </c>
       <c r="L35">
-        <v>7714</v>
+        <v>7765</v>
       </c>
       <c r="M35">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="N35">
-        <v>1007</v>
+        <v>1011</v>
       </c>
       <c r="O35">
-        <v>31866</v>
+        <v>32070</v>
       </c>
       <c r="P35">
         <v>76465</v>
       </c>
-      <c r="Q35" s="2">
+      <c r="Q35">
         <v>8879</v>
       </c>
-      <c r="R35" s="2">
-        <v>0</v>
-      </c>
-      <c r="S35" s="2">
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>33</v>
       </c>
@@ -2732,17 +2731,17 @@
       <c r="P36">
         <v>60419</v>
       </c>
-      <c r="Q36" s="2">
+      <c r="Q36">
         <v>3855</v>
       </c>
-      <c r="R36" s="2">
-        <v>0</v>
-      </c>
-      <c r="S36" s="2">
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36">
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>34</v>
       </c>
@@ -2791,17 +2790,17 @@
       <c r="P37">
         <v>57832</v>
       </c>
-      <c r="Q37" s="2">
+      <c r="Q37">
         <v>4036</v>
       </c>
-      <c r="R37" s="2">
-        <v>0</v>
-      </c>
-      <c r="S37" s="2">
+      <c r="R37">
+        <v>0</v>
+      </c>
+      <c r="S37">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>35</v>
       </c>
@@ -2850,17 +2849,17 @@
       <c r="P38">
         <v>63038</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="Q38">
         <v>5135</v>
       </c>
-      <c r="R38" s="2">
-        <v>0</v>
-      </c>
-      <c r="S38" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R38">
+        <v>0</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>36</v>
       </c>
@@ -2909,17 +2908,17 @@
       <c r="P39">
         <v>71133</v>
       </c>
-      <c r="Q39" s="2">
+      <c r="Q39">
         <v>5903</v>
       </c>
-      <c r="R39" s="2">
-        <v>0</v>
-      </c>
-      <c r="S39" s="2">
+      <c r="R39">
+        <v>0</v>
+      </c>
+      <c r="S39">
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>37</v>
       </c>
@@ -2968,17 +2967,17 @@
       <c r="P40">
         <v>73242</v>
       </c>
-      <c r="Q40" s="2">
+      <c r="Q40">
         <v>3824</v>
       </c>
-      <c r="R40" s="2">
-        <v>0</v>
-      </c>
-      <c r="S40" s="2">
+      <c r="R40">
+        <v>0</v>
+      </c>
+      <c r="S40">
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>38</v>
       </c>
@@ -3027,17 +3026,17 @@
       <c r="P41">
         <v>85251</v>
       </c>
-      <c r="Q41" s="2">
+      <c r="Q41">
         <v>6015</v>
       </c>
-      <c r="R41" s="2">
-        <v>0</v>
-      </c>
-      <c r="S41" s="2">
+      <c r="R41">
+        <v>0</v>
+      </c>
+      <c r="S41">
         <v>27</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>39</v>
       </c>
@@ -3086,17 +3085,17 @@
       <c r="P42">
         <v>68615</v>
       </c>
-      <c r="Q42" s="2">
+      <c r="Q42">
         <v>4708</v>
       </c>
-      <c r="R42" s="2">
-        <v>0</v>
-      </c>
-      <c r="S42" s="2">
+      <c r="R42">
+        <v>0</v>
+      </c>
+      <c r="S42">
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>40</v>
       </c>
@@ -3145,17 +3144,17 @@
       <c r="P43">
         <v>63043</v>
       </c>
-      <c r="Q43" s="2">
+      <c r="Q43">
         <v>5219</v>
       </c>
-      <c r="R43" s="2">
-        <v>0</v>
-      </c>
-      <c r="S43" s="2">
+      <c r="R43">
+        <v>0</v>
+      </c>
+      <c r="S43">
         <v>121</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>41</v>
       </c>
@@ -3204,17 +3203,17 @@
       <c r="P44">
         <v>68393</v>
       </c>
-      <c r="Q44" s="2">
+      <c r="Q44">
         <v>7659</v>
       </c>
-      <c r="R44" s="2">
-        <v>0</v>
-      </c>
-      <c r="S44" s="2">
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>42</v>
       </c>
@@ -3263,17 +3262,17 @@
       <c r="P45">
         <v>76287</v>
       </c>
-      <c r="Q45" s="2">
+      <c r="Q45">
         <v>6998</v>
       </c>
-      <c r="R45" s="2">
-        <v>0</v>
-      </c>
-      <c r="S45" s="2">
+      <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45">
         <v>129</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>43</v>
       </c>
@@ -3322,17 +3321,17 @@
       <c r="P46">
         <v>64160</v>
       </c>
-      <c r="Q46" s="2">
+      <c r="Q46">
         <v>7548</v>
       </c>
-      <c r="R46" s="2">
-        <v>0</v>
-      </c>
-      <c r="S46" s="2">
+      <c r="R46">
+        <v>0</v>
+      </c>
+      <c r="S46">
         <v>152</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>44</v>
       </c>
@@ -3376,22 +3375,22 @@
         <v>137</v>
       </c>
       <c r="O47">
-        <v>21232</v>
+        <v>21624</v>
       </c>
       <c r="P47">
         <v>49875</v>
       </c>
-      <c r="Q47" s="2">
+      <c r="Q47">
         <v>5046</v>
       </c>
-      <c r="R47" s="2">
-        <v>0</v>
-      </c>
-      <c r="S47" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R47">
+        <v>0</v>
+      </c>
+      <c r="S47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>45</v>
       </c>
@@ -3440,17 +3439,17 @@
       <c r="P48">
         <v>54142</v>
       </c>
-      <c r="Q48" s="2">
+      <c r="Q48">
         <v>4623</v>
       </c>
-      <c r="R48" s="2">
-        <v>0</v>
-      </c>
-      <c r="S48" s="2">
+      <c r="R48">
+        <v>0</v>
+      </c>
+      <c r="S48">
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>46</v>
       </c>
@@ -3499,17 +3498,17 @@
       <c r="P49">
         <v>55376</v>
       </c>
-      <c r="Q49" s="2">
+      <c r="Q49">
         <v>5057</v>
       </c>
-      <c r="R49" s="2">
-        <v>0</v>
-      </c>
-      <c r="S49" s="2">
+      <c r="R49">
+        <v>0</v>
+      </c>
+      <c r="S49">
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>47</v>
       </c>
@@ -3558,17 +3557,17 @@
       <c r="P50">
         <v>63298</v>
       </c>
-      <c r="Q50" s="2">
+      <c r="Q50">
         <v>7292</v>
       </c>
-      <c r="R50" s="2">
-        <v>0</v>
-      </c>
-      <c r="S50" s="2">
+      <c r="R50">
+        <v>0</v>
+      </c>
+      <c r="S50">
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>48</v>
       </c>
@@ -3617,17 +3616,17 @@
       <c r="P51">
         <v>71754</v>
       </c>
-      <c r="Q51" s="2">
+      <c r="Q51">
         <v>7715</v>
       </c>
-      <c r="R51" s="2">
-        <v>0</v>
-      </c>
-      <c r="S51" s="2">
+      <c r="R51">
+        <v>0</v>
+      </c>
+      <c r="S51">
         <v>40</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>49</v>
       </c>
@@ -3676,17 +3675,17 @@
       <c r="P52">
         <v>63987</v>
       </c>
-      <c r="Q52" s="2">
+      <c r="Q52">
         <v>5655</v>
       </c>
-      <c r="R52" s="2">
-        <v>0</v>
-      </c>
-      <c r="S52" s="2">
+      <c r="R52">
+        <v>0</v>
+      </c>
+      <c r="S52">
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>50</v>
       </c>
@@ -3735,17 +3734,17 @@
       <c r="P53">
         <v>56306</v>
       </c>
-      <c r="Q53" s="2">
+      <c r="Q53">
         <v>6551</v>
       </c>
-      <c r="R53" s="2">
-        <v>0</v>
-      </c>
-      <c r="S53" s="2">
+      <c r="R53">
+        <v>0</v>
+      </c>
+      <c r="S53">
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>51</v>
       </c>
@@ -3780,7 +3779,7 @@
         <v>0</v>
       </c>
       <c r="L54">
-        <v>2602</v>
+        <v>2603</v>
       </c>
       <c r="M54">
         <v>5</v>
@@ -3789,22 +3788,22 @@
         <v>391</v>
       </c>
       <c r="O54">
-        <v>20366</v>
+        <v>20367</v>
       </c>
       <c r="P54">
         <v>58440</v>
       </c>
-      <c r="Q54" s="2">
+      <c r="Q54">
         <v>7347</v>
       </c>
-      <c r="R54" s="2">
-        <v>0</v>
-      </c>
-      <c r="S54" s="2">
+      <c r="R54">
+        <v>0</v>
+      </c>
+      <c r="S54">
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>52</v>
       </c>
@@ -3853,17 +3852,17 @@
       <c r="P55">
         <v>58215</v>
       </c>
-      <c r="Q55" s="2">
+      <c r="Q55">
         <v>5098</v>
       </c>
-      <c r="R55" s="2">
-        <v>0</v>
-      </c>
-      <c r="S55" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R55">
+        <v>0</v>
+      </c>
+      <c r="S55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>53</v>
       </c>
@@ -3892,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="J56">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="K56">
         <v>0</v>
       </c>
       <c r="L56">
-        <v>4033</v>
+        <v>4070</v>
       </c>
       <c r="M56">
         <v>3</v>
@@ -3907,22 +3906,22 @@
         <v>431</v>
       </c>
       <c r="O56">
-        <v>18747</v>
+        <v>18751</v>
       </c>
       <c r="P56">
         <v>46365</v>
       </c>
-      <c r="Q56" s="2">
+      <c r="Q56">
         <v>4882</v>
       </c>
-      <c r="R56" s="2">
-        <v>0</v>
-      </c>
-      <c r="S56" s="2">
+      <c r="R56">
+        <v>0</v>
+      </c>
+      <c r="S56">
         <v>30</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>54</v>
       </c>
@@ -3971,17 +3970,17 @@
       <c r="P57">
         <v>61556</v>
       </c>
-      <c r="Q57" s="2">
+      <c r="Q57">
         <v>6870</v>
       </c>
-      <c r="R57" s="2">
-        <v>0</v>
-      </c>
-      <c r="S57" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R57">
+        <v>0</v>
+      </c>
+      <c r="S57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>55</v>
       </c>
@@ -4010,13 +4009,13 @@
         <v>0</v>
       </c>
       <c r="J58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K58">
         <v>0</v>
       </c>
       <c r="L58">
-        <v>8122</v>
+        <v>8123</v>
       </c>
       <c r="M58">
         <v>10</v>
@@ -4025,22 +4024,22 @@
         <v>552</v>
       </c>
       <c r="O58">
-        <v>22243</v>
+        <v>22244</v>
       </c>
       <c r="P58">
         <v>57577</v>
       </c>
-      <c r="Q58" s="2">
+      <c r="Q58">
         <v>8884</v>
       </c>
-      <c r="R58" s="2">
-        <v>0</v>
-      </c>
-      <c r="S58" s="2">
+      <c r="R58">
+        <v>0</v>
+      </c>
+      <c r="S58">
         <v>64</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>56</v>
       </c>
@@ -4089,17 +4088,17 @@
       <c r="P59">
         <v>60495</v>
       </c>
-      <c r="Q59" s="2">
+      <c r="Q59">
         <v>8028</v>
       </c>
-      <c r="R59" s="2">
-        <v>0</v>
-      </c>
-      <c r="S59" s="2">
+      <c r="R59">
+        <v>0</v>
+      </c>
+      <c r="S59">
         <v>27</v>
       </c>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>57</v>
       </c>
@@ -4128,13 +4127,13 @@
         <v>0</v>
       </c>
       <c r="J60">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K60">
         <v>0</v>
       </c>
       <c r="L60">
-        <v>5790</v>
+        <v>5814</v>
       </c>
       <c r="M60">
         <v>9</v>
@@ -4143,22 +4142,22 @@
         <v>324</v>
       </c>
       <c r="O60">
-        <v>23400</v>
+        <v>23424</v>
       </c>
       <c r="P60">
         <v>70140</v>
       </c>
-      <c r="Q60" s="2">
+      <c r="Q60">
         <v>7415</v>
       </c>
-      <c r="R60" s="2">
-        <v>0</v>
-      </c>
-      <c r="S60" s="2">
+      <c r="R60">
+        <v>0</v>
+      </c>
+      <c r="S60">
         <v>32</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>58</v>
       </c>
@@ -4207,17 +4206,17 @@
       <c r="P61">
         <v>55240</v>
       </c>
-      <c r="Q61" s="2">
+      <c r="Q61">
         <v>7927</v>
       </c>
-      <c r="R61" s="2">
+      <c r="R61">
         <v>1</v>
       </c>
-      <c r="S61" s="2">
+      <c r="S61">
         <v>268</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>59</v>
       </c>
@@ -4266,17 +4265,17 @@
       <c r="P62">
         <v>51334</v>
       </c>
-      <c r="Q62" s="2">
+      <c r="Q62">
         <v>6917</v>
       </c>
-      <c r="R62" s="2">
-        <v>0</v>
-      </c>
-      <c r="S62" s="2">
+      <c r="R62">
+        <v>0</v>
+      </c>
+      <c r="S62">
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>60</v>
       </c>
@@ -4325,17 +4324,17 @@
       <c r="P63">
         <v>68691</v>
       </c>
-      <c r="Q63" s="2">
+      <c r="Q63">
         <v>9766</v>
       </c>
-      <c r="R63" s="2">
-        <v>0</v>
-      </c>
-      <c r="S63" s="2">
+      <c r="R63">
+        <v>0</v>
+      </c>
+      <c r="S63">
         <v>153</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>61</v>
       </c>
@@ -4364,37 +4363,37 @@
         <v>0</v>
       </c>
       <c r="J64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K64">
         <v>0</v>
       </c>
       <c r="L64">
-        <v>9822</v>
+        <v>9887</v>
       </c>
       <c r="M64">
         <v>8</v>
       </c>
       <c r="N64">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="O64">
-        <v>41404</v>
+        <v>41555</v>
       </c>
       <c r="P64">
         <v>60527</v>
       </c>
-      <c r="Q64" s="2">
+      <c r="Q64">
         <v>5985</v>
       </c>
-      <c r="R64" s="2">
-        <v>0</v>
-      </c>
-      <c r="S64" s="2">
+      <c r="R64">
+        <v>0</v>
+      </c>
+      <c r="S64">
         <v>101</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>62</v>
       </c>
@@ -4414,46 +4413,46 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>41294</v>
+        <v>41354</v>
       </c>
       <c r="H65">
-        <v>82</v>
+        <v>35</v>
       </c>
       <c r="I65">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J65">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K65">
         <v>0</v>
       </c>
       <c r="L65">
-        <v>13427</v>
+        <v>13492</v>
       </c>
       <c r="M65">
         <v>2</v>
       </c>
       <c r="N65">
-        <v>2447</v>
+        <v>2514</v>
       </c>
       <c r="O65">
-        <v>35927</v>
+        <v>38619</v>
       </c>
       <c r="P65">
-        <v>58103</v>
-      </c>
-      <c r="Q65" s="2">
+        <v>58527</v>
+      </c>
+      <c r="Q65">
         <v>13282</v>
       </c>
-      <c r="R65" s="2">
-        <v>0</v>
-      </c>
-      <c r="S65" s="2">
+      <c r="R65">
+        <v>0</v>
+      </c>
+      <c r="S65">
         <v>138</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>63</v>
       </c>
@@ -4497,22 +4496,22 @@
         <v>4021</v>
       </c>
       <c r="O66">
-        <v>63161</v>
+        <v>63342</v>
       </c>
       <c r="P66">
         <v>93810</v>
       </c>
-      <c r="Q66" s="2">
+      <c r="Q66">
         <v>17742</v>
       </c>
-      <c r="R66" s="2">
-        <v>0</v>
-      </c>
-      <c r="S66" s="2">
+      <c r="R66">
+        <v>0</v>
+      </c>
+      <c r="S66">
         <v>52</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>64</v>
       </c>
@@ -4541,37 +4540,37 @@
         <v>0</v>
       </c>
       <c r="J67">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K67">
         <v>0</v>
       </c>
       <c r="L67">
-        <v>19450</v>
+        <v>19491</v>
       </c>
       <c r="M67">
         <v>10</v>
       </c>
       <c r="N67">
-        <v>3638</v>
+        <v>3643</v>
       </c>
       <c r="O67">
-        <v>65130</v>
+        <v>65182</v>
       </c>
       <c r="P67">
-        <v>78022</v>
-      </c>
-      <c r="Q67" s="2">
+        <v>78032</v>
+      </c>
+      <c r="Q67">
         <v>9807</v>
       </c>
-      <c r="R67" s="2">
-        <v>0</v>
-      </c>
-      <c r="S67" s="2">
+      <c r="R67">
+        <v>0</v>
+      </c>
+      <c r="S67">
         <v>116</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>65</v>
       </c>
@@ -4591,46 +4590,46 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>65387</v>
+        <v>65397</v>
       </c>
       <c r="H68">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I68">
         <v>0</v>
       </c>
       <c r="J68">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K68">
         <v>0</v>
       </c>
       <c r="L68">
-        <v>18625</v>
+        <v>18664</v>
       </c>
       <c r="M68">
         <v>2</v>
       </c>
       <c r="N68">
-        <v>1550</v>
+        <v>1593</v>
       </c>
       <c r="O68">
-        <v>58846</v>
+        <v>63773</v>
       </c>
       <c r="P68">
         <v>71325</v>
       </c>
-      <c r="Q68" s="2">
+      <c r="Q68">
         <v>7850</v>
       </c>
-      <c r="R68" s="2">
-        <v>0</v>
-      </c>
-      <c r="S68" s="2">
+      <c r="R68">
+        <v>0</v>
+      </c>
+      <c r="S68">
         <v>26</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>66</v>
       </c>
@@ -4659,13 +4658,13 @@
         <v>0</v>
       </c>
       <c r="J69">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="K69">
         <v>0</v>
       </c>
       <c r="L69">
-        <v>18012</v>
+        <v>18216</v>
       </c>
       <c r="M69">
         <v>2</v>
@@ -4674,22 +4673,22 @@
         <v>2619</v>
       </c>
       <c r="O69">
-        <v>41118</v>
+        <v>41322</v>
       </c>
       <c r="P69">
         <v>36118</v>
       </c>
-      <c r="Q69" s="2">
+      <c r="Q69">
         <v>6528</v>
       </c>
-      <c r="R69" s="2">
-        <v>0</v>
-      </c>
-      <c r="S69" s="2">
+      <c r="R69">
+        <v>0</v>
+      </c>
+      <c r="S69">
         <v>47</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>67</v>
       </c>
@@ -4738,17 +4737,17 @@
       <c r="P70">
         <v>42051</v>
       </c>
-      <c r="Q70" s="2">
+      <c r="Q70">
         <v>5798</v>
       </c>
-      <c r="R70" s="2">
-        <v>0</v>
-      </c>
-      <c r="S70" s="2">
+      <c r="R70">
+        <v>0</v>
+      </c>
+      <c r="S70">
         <v>29</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>68</v>
       </c>
@@ -4783,31 +4782,31 @@
         <v>0</v>
       </c>
       <c r="L71">
-        <v>22816</v>
+        <v>22851</v>
       </c>
       <c r="M71">
         <v>1</v>
       </c>
       <c r="N71">
-        <v>4389</v>
+        <v>4442</v>
       </c>
       <c r="O71">
-        <v>46421</v>
+        <v>46521</v>
       </c>
       <c r="P71">
         <v>49140</v>
       </c>
-      <c r="Q71" s="2">
+      <c r="Q71">
         <v>6782</v>
       </c>
-      <c r="R71" s="2">
-        <v>0</v>
-      </c>
-      <c r="S71" s="2">
+      <c r="R71">
+        <v>0</v>
+      </c>
+      <c r="S71">
         <v>235</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>69</v>
       </c>
@@ -4836,37 +4835,37 @@
         <v>0</v>
       </c>
       <c r="J72">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K72">
         <v>0</v>
       </c>
       <c r="L72">
-        <v>17217</v>
+        <v>17245</v>
       </c>
       <c r="M72">
         <v>9</v>
       </c>
       <c r="N72">
-        <v>3666</v>
+        <v>3667</v>
       </c>
       <c r="O72">
-        <v>57848</v>
+        <v>57877</v>
       </c>
       <c r="P72">
         <v>85505</v>
       </c>
-      <c r="Q72" s="2">
+      <c r="Q72">
         <v>12340</v>
       </c>
-      <c r="R72" s="2">
-        <v>0</v>
-      </c>
-      <c r="S72" s="2">
+      <c r="R72">
+        <v>0</v>
+      </c>
+      <c r="S72">
         <v>79</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>70</v>
       </c>
@@ -4895,37 +4894,37 @@
         <v>0</v>
       </c>
       <c r="J73">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K73">
         <v>0</v>
       </c>
       <c r="L73">
-        <v>14879</v>
+        <v>15107</v>
       </c>
       <c r="M73">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N73">
-        <v>3783</v>
+        <v>3826</v>
       </c>
       <c r="O73">
-        <v>53997</v>
+        <v>55024</v>
       </c>
       <c r="P73">
         <v>67666</v>
       </c>
-      <c r="Q73" s="2">
+      <c r="Q73">
         <v>10010</v>
       </c>
-      <c r="R73" s="2">
-        <v>0</v>
-      </c>
-      <c r="S73" s="2">
+      <c r="R73">
+        <v>0</v>
+      </c>
+      <c r="S73">
         <v>74</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>89</v>
       </c>
@@ -4943,48 +4942,49 @@
         <v>0</v>
       </c>
       <c r="G74">
-        <v>2429649</v>
+        <v>2430197</v>
       </c>
       <c r="H74">
-        <v>617</v>
+        <v>188</v>
       </c>
       <c r="I74">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="J74">
-        <v>293</v>
+        <v>375</v>
       </c>
       <c r="K74">
         <v>6</v>
       </c>
       <c r="L74">
-        <v>622813</v>
+        <v>623811</v>
       </c>
       <c r="M74">
-        <v>7890</v>
+        <v>7956</v>
       </c>
       <c r="N74">
-        <v>94311</v>
+        <v>95425</v>
       </c>
       <c r="O74">
-        <v>2292151</v>
+        <v>2304118</v>
       </c>
       <c r="P74">
-        <v>4690106</v>
-      </c>
-      <c r="Q74" s="2">
+        <v>4696237</v>
+      </c>
+      <c r="Q74">
         <v>626236</v>
       </c>
-      <c r="R74" s="2">
+      <c r="R74">
         <v>1</v>
       </c>
-      <c r="S74" s="2">
+      <c r="S74">
         <v>3445</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="A74:B74"/>
+    <mergeCell ref="Q2:S2"/>
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
@@ -4995,7 +4995,6 @@
     <mergeCell ref="G2:I2"/>
     <mergeCell ref="J2:M2"/>
     <mergeCell ref="N2:P2"/>
-    <mergeCell ref="Q2:S2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C30A3056-7237-4D83-B4D2-BF53828ABCF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF87C3B4-2BAC-4913-AA1A-D428FB87B87B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -292,9 +292,6 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Notice &amp; Hearing Report Last Updated On : 08-09-2026 07:56:56</t>
-  </si>
-  <si>
     <t>DSE with UP</t>
   </si>
   <si>
@@ -305,6 +302,9 @@
   </si>
   <si>
     <t>No Action Required</t>
+  </si>
+  <si>
+    <t>Notice &amp; Hearing Report Last Updated On : 09-09-2026 07:56:55</t>
   </si>
 </sst>
 </file>
@@ -687,7 +687,7 @@
   <sheetData>
     <row r="1" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -742,7 +742,7 @@
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
@@ -785,13 +785,13 @@
         <v>18</v>
       </c>
       <c r="Q3" t="s">
+        <v>91</v>
+      </c>
+      <c r="R3" t="s">
         <v>92</v>
       </c>
-      <c r="R3" t="s">
+      <c r="S3" t="s">
         <v>93</v>
-      </c>
-      <c r="S3" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
@@ -829,16 +829,16 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>17801</v>
+        <v>17975</v>
       </c>
       <c r="M4">
         <v>967</v>
       </c>
       <c r="N4">
-        <v>862</v>
+        <v>869</v>
       </c>
       <c r="O4">
-        <v>50447</v>
+        <v>50485</v>
       </c>
       <c r="P4">
         <v>53812</v>
@@ -882,7 +882,7 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -894,10 +894,10 @@
         <v>751</v>
       </c>
       <c r="N5">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="O5">
-        <v>52926</v>
+        <v>52986</v>
       </c>
       <c r="P5">
         <v>74848</v>
@@ -1000,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>1985</v>
       </c>
       <c r="O7">
-        <v>35071</v>
+        <v>35212</v>
       </c>
       <c r="P7">
         <v>77581</v>
@@ -1059,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -1118,13 +1118,13 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>7741</v>
+        <v>7755</v>
       </c>
       <c r="M9">
         <v>49</v>
@@ -1133,7 +1133,7 @@
         <v>1336</v>
       </c>
       <c r="O9">
-        <v>41904</v>
+        <v>41917</v>
       </c>
       <c r="P9">
         <v>72762</v>
@@ -1177,13 +1177,13 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>10927</v>
+        <v>10960</v>
       </c>
       <c r="M10">
         <v>172</v>
@@ -1192,7 +1192,7 @@
         <v>813</v>
       </c>
       <c r="O10">
-        <v>35727</v>
+        <v>35763</v>
       </c>
       <c r="P10">
         <v>53124</v>
@@ -1295,22 +1295,22 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="L12">
-        <v>9972</v>
+        <v>9978</v>
       </c>
       <c r="M12">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N12">
         <v>1052</v>
       </c>
       <c r="O12">
-        <v>39466</v>
+        <v>39500</v>
       </c>
       <c r="P12">
         <v>66685</v>
@@ -1413,22 +1413,22 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>14971</v>
+        <v>14997</v>
       </c>
       <c r="M14">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="N14">
-        <v>5602</v>
+        <v>5619</v>
       </c>
       <c r="O14">
-        <v>30590</v>
+        <v>32052</v>
       </c>
       <c r="P14">
         <v>77955</v>
@@ -2171,34 +2171,34 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>44256</v>
+        <v>44276</v>
       </c>
       <c r="H27">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="L27">
-        <v>9664</v>
+        <v>9677</v>
       </c>
       <c r="M27">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="N27">
-        <v>3057</v>
+        <v>3242</v>
       </c>
       <c r="O27">
-        <v>40522</v>
+        <v>40981</v>
       </c>
       <c r="P27">
-        <v>68986</v>
+        <v>71316</v>
       </c>
       <c r="Q27">
         <v>12669</v>
@@ -2230,31 +2230,31 @@
         <v>0</v>
       </c>
       <c r="G28">
-        <v>54346</v>
+        <v>54349</v>
       </c>
       <c r="H28">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I28">
         <v>0</v>
       </c>
       <c r="J28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28">
         <v>0</v>
       </c>
       <c r="L28">
-        <v>8878</v>
+        <v>8879</v>
       </c>
       <c r="M28">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="N28">
-        <v>3220</v>
+        <v>3326</v>
       </c>
       <c r="O28">
-        <v>50675</v>
+        <v>50677</v>
       </c>
       <c r="P28">
         <v>80620</v>
@@ -2298,22 +2298,22 @@
         <v>0</v>
       </c>
       <c r="J29">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="K29">
         <v>0</v>
       </c>
       <c r="L29">
-        <v>8797</v>
+        <v>8816</v>
       </c>
       <c r="M29">
-        <v>272</v>
+        <v>318</v>
       </c>
       <c r="N29">
-        <v>4546</v>
+        <v>4559</v>
       </c>
       <c r="O29">
-        <v>42501</v>
+        <v>42502</v>
       </c>
       <c r="P29">
         <v>83836</v>
@@ -2357,22 +2357,22 @@
         <v>0</v>
       </c>
       <c r="J30">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K30">
         <v>0</v>
       </c>
       <c r="L30">
-        <v>11652</v>
+        <v>11658</v>
       </c>
       <c r="M30">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="N30">
-        <v>5340</v>
+        <v>5373</v>
       </c>
       <c r="O30">
-        <v>47199</v>
+        <v>47202</v>
       </c>
       <c r="P30">
         <v>86933</v>
@@ -2428,10 +2428,10 @@
         <v>42</v>
       </c>
       <c r="N31">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="O31">
-        <v>89265</v>
+        <v>89264</v>
       </c>
       <c r="P31">
         <v>81642</v>
@@ -2490,7 +2490,7 @@
         <v>4376</v>
       </c>
       <c r="O32">
-        <v>42298</v>
+        <v>42299</v>
       </c>
       <c r="P32">
         <v>74810</v>
@@ -2540,16 +2540,16 @@
         <v>0</v>
       </c>
       <c r="L33">
-        <v>5057</v>
+        <v>5060</v>
       </c>
       <c r="M33">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="N33">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="O33">
-        <v>37698</v>
+        <v>38415</v>
       </c>
       <c r="P33">
         <v>76969</v>
@@ -2599,16 +2599,16 @@
         <v>0</v>
       </c>
       <c r="L34">
-        <v>11888</v>
+        <v>11992</v>
       </c>
       <c r="M34">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="N34">
-        <v>1306</v>
+        <v>1315</v>
       </c>
       <c r="O34">
-        <v>33870</v>
+        <v>33862</v>
       </c>
       <c r="P34">
         <v>74624</v>
@@ -2643,31 +2643,31 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>33435</v>
+        <v>33519</v>
       </c>
       <c r="H35">
-        <v>129</v>
+        <v>45</v>
       </c>
       <c r="I35">
         <v>0</v>
       </c>
       <c r="J35">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="K35">
         <v>0</v>
       </c>
       <c r="L35">
-        <v>7765</v>
+        <v>7881</v>
       </c>
       <c r="M35">
-        <v>248</v>
+        <v>271</v>
       </c>
       <c r="N35">
-        <v>1011</v>
+        <v>1048</v>
       </c>
       <c r="O35">
-        <v>32070</v>
+        <v>32234</v>
       </c>
       <c r="P35">
         <v>76465</v>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="J56">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K56">
         <v>0</v>
       </c>
       <c r="L56">
-        <v>4070</v>
+        <v>4078</v>
       </c>
       <c r="M56">
         <v>3</v>
@@ -3906,7 +3906,7 @@
         <v>431</v>
       </c>
       <c r="O56">
-        <v>18751</v>
+        <v>18764</v>
       </c>
       <c r="P56">
         <v>46365</v>
@@ -4024,7 +4024,7 @@
         <v>552</v>
       </c>
       <c r="O58">
-        <v>22244</v>
+        <v>22267</v>
       </c>
       <c r="P58">
         <v>57577</v>
@@ -4133,7 +4133,7 @@
         <v>0</v>
       </c>
       <c r="L60">
-        <v>5814</v>
+        <v>5815</v>
       </c>
       <c r="M60">
         <v>9</v>
@@ -4142,7 +4142,7 @@
         <v>324</v>
       </c>
       <c r="O60">
-        <v>23424</v>
+        <v>23425</v>
       </c>
       <c r="P60">
         <v>70140</v>
@@ -4316,10 +4316,10 @@
         <v>68</v>
       </c>
       <c r="N63">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="O63">
-        <v>35820</v>
+        <v>35823</v>
       </c>
       <c r="P63">
         <v>68691</v>
@@ -4413,10 +4413,10 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>41354</v>
+        <v>41389</v>
       </c>
       <c r="H65">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -4428,16 +4428,16 @@
         <v>0</v>
       </c>
       <c r="L65">
-        <v>13492</v>
+        <v>13526</v>
       </c>
       <c r="M65">
         <v>2</v>
       </c>
       <c r="N65">
-        <v>2514</v>
+        <v>2524</v>
       </c>
       <c r="O65">
-        <v>38619</v>
+        <v>38681</v>
       </c>
       <c r="P65">
         <v>58527</v>
@@ -4546,16 +4546,16 @@
         <v>0</v>
       </c>
       <c r="L67">
-        <v>19491</v>
+        <v>19495</v>
       </c>
       <c r="M67">
         <v>10</v>
       </c>
       <c r="N67">
-        <v>3643</v>
+        <v>3644</v>
       </c>
       <c r="O67">
-        <v>65182</v>
+        <v>65185</v>
       </c>
       <c r="P67">
         <v>78032</v>
@@ -4599,22 +4599,22 @@
         <v>0</v>
       </c>
       <c r="J68">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K68">
         <v>0</v>
       </c>
       <c r="L68">
-        <v>18664</v>
+        <v>18676</v>
       </c>
       <c r="M68">
         <v>2</v>
       </c>
       <c r="N68">
-        <v>1593</v>
+        <v>1602</v>
       </c>
       <c r="O68">
-        <v>63773</v>
+        <v>63794</v>
       </c>
       <c r="P68">
         <v>71325</v>
@@ -4894,22 +4894,22 @@
         <v>0</v>
       </c>
       <c r="J73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K73">
         <v>0</v>
       </c>
       <c r="L73">
-        <v>15107</v>
+        <v>15131</v>
       </c>
       <c r="M73">
         <v>8</v>
       </c>
       <c r="N73">
-        <v>3826</v>
+        <v>3863</v>
       </c>
       <c r="O73">
-        <v>55024</v>
+        <v>55049</v>
       </c>
       <c r="P73">
         <v>67666</v>
@@ -4942,34 +4942,34 @@
         <v>0</v>
       </c>
       <c r="G74">
-        <v>2430197</v>
+        <v>2430339</v>
       </c>
       <c r="H74">
-        <v>188</v>
+        <v>46</v>
       </c>
       <c r="I74">
         <v>0</v>
       </c>
       <c r="J74">
-        <v>375</v>
+        <v>129</v>
       </c>
       <c r="K74">
         <v>6</v>
       </c>
       <c r="L74">
-        <v>623811</v>
+        <v>624409</v>
       </c>
       <c r="M74">
-        <v>7956</v>
+        <v>8073</v>
       </c>
       <c r="N74">
-        <v>95425</v>
+        <v>95894</v>
       </c>
       <c r="O74">
-        <v>2304118</v>
+        <v>2307391</v>
       </c>
       <c r="P74">
-        <v>4696237</v>
+        <v>4698567</v>
       </c>
       <c r="Q74">
         <v>626236</v>

--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF87C3B4-2BAC-4913-AA1A-D428FB87B87B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DD7FB89-0D14-4FBD-8C04-26B908F71D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -292,6 +292,9 @@
     <t>Total</t>
   </si>
   <si>
+    <t>Notice &amp; Hearing Report Last Updated On : 10-09-2026 07:56:54</t>
+  </si>
+  <si>
     <t>DSE with UP</t>
   </si>
   <si>
@@ -302,9 +305,6 @@
   </si>
   <si>
     <t>No Action Required</t>
-  </si>
-  <si>
-    <t>Notice &amp; Hearing Report Last Updated On : 09-09-2026 07:56:55</t>
   </si>
 </sst>
 </file>
@@ -687,7 +687,7 @@
   <sheetData>
     <row r="1" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -742,7 +742,7 @@
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
@@ -785,13 +785,13 @@
         <v>18</v>
       </c>
       <c r="Q3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="R3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="S3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
@@ -882,22 +882,22 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>11383</v>
+        <v>11399</v>
       </c>
       <c r="M5">
-        <v>751</v>
+        <v>757</v>
       </c>
       <c r="N5">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="O5">
-        <v>52986</v>
+        <v>52995</v>
       </c>
       <c r="P5">
         <v>74848</v>
@@ -941,13 +941,13 @@
         <v>0</v>
       </c>
       <c r="J6">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>6011</v>
+        <v>6024</v>
       </c>
       <c r="M6">
         <v>201</v>
@@ -956,7 +956,7 @@
         <v>1778</v>
       </c>
       <c r="O6">
-        <v>33319</v>
+        <v>33326</v>
       </c>
       <c r="P6">
         <v>71989</v>
@@ -1000,22 +1000,22 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>5616</v>
+        <v>5627</v>
       </c>
       <c r="M7">
         <v>257</v>
       </c>
       <c r="N7">
-        <v>1985</v>
+        <v>1991</v>
       </c>
       <c r="O7">
-        <v>35212</v>
+        <v>35384</v>
       </c>
       <c r="P7">
         <v>77581</v>
@@ -1059,13 +1059,13 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>14223</v>
+        <v>14241</v>
       </c>
       <c r="M8">
         <v>164</v>
@@ -1074,7 +1074,7 @@
         <v>1871</v>
       </c>
       <c r="O8">
-        <v>34519</v>
+        <v>34536</v>
       </c>
       <c r="P8">
         <v>73458</v>
@@ -1124,7 +1124,7 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>7755</v>
+        <v>7757</v>
       </c>
       <c r="M9">
         <v>49</v>
@@ -1133,10 +1133,10 @@
         <v>1336</v>
       </c>
       <c r="O9">
-        <v>41917</v>
+        <v>41918</v>
       </c>
       <c r="P9">
-        <v>72762</v>
+        <v>72913</v>
       </c>
       <c r="Q9">
         <v>18141</v>
@@ -1189,10 +1189,10 @@
         <v>172</v>
       </c>
       <c r="N10">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="O10">
-        <v>35763</v>
+        <v>35761</v>
       </c>
       <c r="P10">
         <v>53124</v>
@@ -1295,22 +1295,22 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="L12">
-        <v>9978</v>
+        <v>9980</v>
       </c>
       <c r="M12">
         <v>207</v>
       </c>
       <c r="N12">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="O12">
-        <v>39500</v>
+        <v>39505</v>
       </c>
       <c r="P12">
         <v>66685</v>
@@ -1413,22 +1413,22 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>14997</v>
+        <v>15071</v>
       </c>
       <c r="M14">
         <v>1412</v>
       </c>
       <c r="N14">
-        <v>5619</v>
+        <v>5627</v>
       </c>
       <c r="O14">
-        <v>32052</v>
+        <v>32057</v>
       </c>
       <c r="P14">
         <v>77955</v>
@@ -1708,13 +1708,13 @@
         <v>0</v>
       </c>
       <c r="J19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19">
         <v>0</v>
       </c>
       <c r="L19">
-        <v>15284</v>
+        <v>15285</v>
       </c>
       <c r="M19">
         <v>1</v>
@@ -2180,7 +2180,7 @@
         <v>0</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K27">
         <v>0</v>
@@ -2189,16 +2189,16 @@
         <v>9677</v>
       </c>
       <c r="M27">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N27">
-        <v>3242</v>
+        <v>3256</v>
       </c>
       <c r="O27">
-        <v>40981</v>
+        <v>41027</v>
       </c>
       <c r="P27">
-        <v>71316</v>
+        <v>73109</v>
       </c>
       <c r="Q27">
         <v>12669</v>
@@ -2251,10 +2251,10 @@
         <v>856</v>
       </c>
       <c r="N28">
-        <v>3326</v>
+        <v>3340</v>
       </c>
       <c r="O28">
-        <v>50677</v>
+        <v>50752</v>
       </c>
       <c r="P28">
         <v>80620</v>
@@ -2310,10 +2310,10 @@
         <v>318</v>
       </c>
       <c r="N29">
-        <v>4559</v>
+        <v>4592</v>
       </c>
       <c r="O29">
-        <v>42502</v>
+        <v>42520</v>
       </c>
       <c r="P29">
         <v>83836</v>
@@ -2369,10 +2369,10 @@
         <v>411</v>
       </c>
       <c r="N30">
-        <v>5373</v>
+        <v>5374</v>
       </c>
       <c r="O30">
-        <v>47202</v>
+        <v>47204</v>
       </c>
       <c r="P30">
         <v>86933</v>
@@ -2487,10 +2487,10 @@
         <v>316</v>
       </c>
       <c r="N32">
-        <v>4376</v>
+        <v>4377</v>
       </c>
       <c r="O32">
-        <v>42299</v>
+        <v>42336</v>
       </c>
       <c r="P32">
         <v>74810</v>
@@ -2534,22 +2534,22 @@
         <v>0</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K33">
         <v>0</v>
       </c>
       <c r="L33">
-        <v>5060</v>
+        <v>5076</v>
       </c>
       <c r="M33">
         <v>279</v>
       </c>
       <c r="N33">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="O33">
-        <v>38415</v>
+        <v>38465</v>
       </c>
       <c r="P33">
         <v>76969</v>
@@ -2593,22 +2593,22 @@
         <v>0</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="K34">
         <v>0</v>
       </c>
       <c r="L34">
-        <v>11992</v>
+        <v>12006</v>
       </c>
       <c r="M34">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="N34">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="O34">
-        <v>33862</v>
+        <v>34330</v>
       </c>
       <c r="P34">
         <v>74624</v>
@@ -2643,31 +2643,31 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>33519</v>
+        <v>33564</v>
       </c>
       <c r="H35">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="I35">
         <v>0</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K35">
         <v>0</v>
       </c>
       <c r="L35">
-        <v>7881</v>
+        <v>7883</v>
       </c>
       <c r="M35">
         <v>271</v>
       </c>
       <c r="N35">
-        <v>1048</v>
+        <v>1098</v>
       </c>
       <c r="O35">
-        <v>32234</v>
+        <v>32429</v>
       </c>
       <c r="P35">
         <v>76465</v>
@@ -3136,13 +3136,13 @@
         <v>1</v>
       </c>
       <c r="N43">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="O43">
         <v>28789</v>
       </c>
       <c r="P43">
-        <v>63043</v>
+        <v>63042</v>
       </c>
       <c r="Q43">
         <v>5219</v>
@@ -3655,13 +3655,13 @@
         <v>0</v>
       </c>
       <c r="J52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52">
-        <v>2941</v>
+        <v>2942</v>
       </c>
       <c r="M52">
         <v>1</v>
@@ -3670,7 +3670,7 @@
         <v>45</v>
       </c>
       <c r="O52">
-        <v>21048</v>
+        <v>21049</v>
       </c>
       <c r="P52">
         <v>63987</v>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="J56">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K56">
         <v>0</v>
       </c>
       <c r="L56">
-        <v>4078</v>
+        <v>4083</v>
       </c>
       <c r="M56">
         <v>3</v>
@@ -3906,10 +3906,10 @@
         <v>431</v>
       </c>
       <c r="O56">
-        <v>18764</v>
+        <v>18795</v>
       </c>
       <c r="P56">
-        <v>46365</v>
+        <v>47621</v>
       </c>
       <c r="Q56">
         <v>4882</v>
@@ -4422,22 +4422,22 @@
         <v>0</v>
       </c>
       <c r="J65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K65">
         <v>0</v>
       </c>
       <c r="L65">
-        <v>13526</v>
+        <v>13573</v>
       </c>
       <c r="M65">
         <v>2</v>
       </c>
       <c r="N65">
-        <v>2524</v>
+        <v>2635</v>
       </c>
       <c r="O65">
-        <v>38681</v>
+        <v>38745</v>
       </c>
       <c r="P65">
         <v>58527</v>
@@ -4599,13 +4599,13 @@
         <v>0</v>
       </c>
       <c r="J68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K68">
         <v>0</v>
       </c>
       <c r="L68">
-        <v>18676</v>
+        <v>18679</v>
       </c>
       <c r="M68">
         <v>2</v>
@@ -4614,7 +4614,7 @@
         <v>1602</v>
       </c>
       <c r="O68">
-        <v>63794</v>
+        <v>63795</v>
       </c>
       <c r="P68">
         <v>71325</v>
@@ -4906,7 +4906,7 @@
         <v>8</v>
       </c>
       <c r="N73">
-        <v>3863</v>
+        <v>3866</v>
       </c>
       <c r="O73">
         <v>55049</v>
@@ -4942,34 +4942,34 @@
         <v>0</v>
       </c>
       <c r="G74">
-        <v>2430339</v>
+        <v>2430384</v>
       </c>
       <c r="H74">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="I74">
         <v>0</v>
       </c>
       <c r="J74">
-        <v>129</v>
+        <v>60</v>
       </c>
       <c r="K74">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L74">
-        <v>624409</v>
+        <v>624634</v>
       </c>
       <c r="M74">
-        <v>8073</v>
+        <v>8088</v>
       </c>
       <c r="N74">
-        <v>95894</v>
+        <v>96145</v>
       </c>
       <c r="O74">
-        <v>2307391</v>
+        <v>2308593</v>
       </c>
       <c r="P74">
-        <v>4698567</v>
+        <v>4701766</v>
       </c>
       <c r="Q74">
         <v>626236</v>

--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -1,317 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DD7FB89-0D14-4FBD-8C04-26B908F71D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
-  <si>
-    <t>S. No.</t>
-  </si>
-  <si>
-    <t>AC No. - AC Name</t>
-  </si>
-  <si>
-    <t>Notice Generated</t>
-  </si>
-  <si>
-    <t>Pending for Notice Generation</t>
-  </si>
-  <si>
-    <t>Notice Delivered</t>
-  </si>
-  <si>
-    <t>Notices pending delivery</t>
-  </si>
-  <si>
-    <t>Hearing</t>
-  </si>
-  <si>
-    <t>DEO Status</t>
-  </si>
-  <si>
-    <t>ERO/AERO Status</t>
-  </si>
-  <si>
-    <t>Hearing Held</t>
-  </si>
-  <si>
-    <t>Hearing Date Lapsed</t>
-  </si>
-  <si>
-    <t>Reschedule Date Lapsed</t>
-  </si>
-  <si>
-    <t>Total Pending</t>
-  </si>
-  <si>
-    <t>Pending &gt; 5 days</t>
-  </si>
-  <si>
-    <t>Verified</t>
-  </si>
-  <si>
-    <t>Not Verified</t>
-  </si>
-  <si>
-    <t>Found Ineligible for Final</t>
-  </si>
-  <si>
-    <t>Parked for Final Publication w.r.t. Notices Generated</t>
-  </si>
-  <si>
-    <t>Parked For Final Publication w.r.t. Others</t>
-  </si>
-  <si>
-    <t>25 - Haridwar</t>
-  </si>
-  <si>
-    <t>26 - BHEL Ranipur</t>
-  </si>
-  <si>
-    <t>27 - Jwalapur</t>
-  </si>
-  <si>
-    <t>28 - Bhagwanpur</t>
-  </si>
-  <si>
-    <t>29 - Jhabrera</t>
-  </si>
-  <si>
-    <t>30 - Piran Kaliyar</t>
-  </si>
-  <si>
-    <t>31 - Roorkee</t>
-  </si>
-  <si>
-    <t>32 - Khanpur</t>
-  </si>
-  <si>
-    <t>33 - Manglore</t>
-  </si>
-  <si>
-    <t>34 - Laksar</t>
-  </si>
-  <si>
-    <t>35 - Haridwar Rural</t>
-  </si>
-  <si>
-    <t>56 - Lalkuan</t>
-  </si>
-  <si>
-    <t>57 - Bhimtal</t>
-  </si>
-  <si>
-    <t>58 - Nainital</t>
-  </si>
-  <si>
-    <t>59 - Haldwani</t>
-  </si>
-  <si>
-    <t>60 - Kaladhungi</t>
-  </si>
-  <si>
-    <t>61 - Ramnagar</t>
-  </si>
-  <si>
-    <t>48 - Dwarahat</t>
-  </si>
-  <si>
-    <t>49 - Salt</t>
-  </si>
-  <si>
-    <t>50 - Ranikhet</t>
-  </si>
-  <si>
-    <t>51 - Someshwar</t>
-  </si>
-  <si>
-    <t>52 - Almora</t>
-  </si>
-  <si>
-    <t>53 - Jageshwar</t>
-  </si>
-  <si>
-    <t>62 - Jaspur</t>
-  </si>
-  <si>
-    <t>63 - Kashipur</t>
-  </si>
-  <si>
-    <t>64 - Bajpur</t>
-  </si>
-  <si>
-    <t>65 - Gadarpur</t>
-  </si>
-  <si>
-    <t>66 - Rudrapur</t>
-  </si>
-  <si>
-    <t>67 - Kichha</t>
-  </si>
-  <si>
-    <t>68 - Sitarganj</t>
-  </si>
-  <si>
-    <t>69 - Nanakmatta</t>
-  </si>
-  <si>
-    <t>70 - Khatima</t>
-  </si>
-  <si>
-    <t>42 - Dharchula</t>
-  </si>
-  <si>
-    <t>43 - Didihat</t>
-  </si>
-  <si>
-    <t>44 - Pithoragarh</t>
-  </si>
-  <si>
-    <t>45 - Gangolihat</t>
-  </si>
-  <si>
-    <t>46 - Kapkot</t>
-  </si>
-  <si>
-    <t>47 - Bageshwar</t>
-  </si>
-  <si>
-    <t>54 - Lohaghat</t>
-  </si>
-  <si>
-    <t>55 - Champawat</t>
-  </si>
-  <si>
-    <t>4 - Badrinath</t>
-  </si>
-  <si>
-    <t>5 - Tharali</t>
-  </si>
-  <si>
-    <t>6 - Karanprayag</t>
-  </si>
-  <si>
-    <t>1 - Purola</t>
-  </si>
-  <si>
-    <t>2 - Yamunotri</t>
-  </si>
-  <si>
-    <t>3 - Gangotri</t>
-  </si>
-  <si>
-    <t>7 - Kedarnath</t>
-  </si>
-  <si>
-    <t>8 - Rudraprayag</t>
-  </si>
-  <si>
-    <t>9 - Ghansali</t>
-  </si>
-  <si>
-    <t>10 - Devprayag</t>
-  </si>
-  <si>
-    <t>11 - Narendranagar</t>
-  </si>
-  <si>
-    <t>12 - Pratapnagar</t>
-  </si>
-  <si>
-    <t>13 - Tehri</t>
-  </si>
-  <si>
-    <t>14 - Dhanolti</t>
-  </si>
-  <si>
-    <t>36 - Yamkeshwar</t>
-  </si>
-  <si>
-    <t>37 - Pauri</t>
-  </si>
-  <si>
-    <t>38 - Srinagar</t>
-  </si>
-  <si>
-    <t>39 - Chaubattakhal</t>
-  </si>
-  <si>
-    <t>40 - Lansdowne</t>
-  </si>
-  <si>
-    <t>41 - Kotdwar</t>
-  </si>
-  <si>
-    <t>15 - Chakrata</t>
-  </si>
-  <si>
-    <t>16 - Vikasnagar</t>
-  </si>
-  <si>
-    <t>17 - Sahaspur</t>
-  </si>
-  <si>
-    <t>18 - Dharmpur</t>
-  </si>
-  <si>
-    <t>19 - Raipur</t>
-  </si>
-  <si>
-    <t>20 - Rajpur Road</t>
-  </si>
-  <si>
-    <t>21 - Dehradun Cantonment</t>
-  </si>
-  <si>
-    <t>22 - Mussoorie</t>
-  </si>
-  <si>
-    <t>23 - Doiwala</t>
-  </si>
-  <si>
-    <t>24 - Rishikesh</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Notice &amp; Hearing Report Last Updated On : 10-09-2026 07:56:54</t>
-  </si>
-  <si>
-    <t>DSE with UP</t>
-  </si>
-  <si>
-    <t>Electors having DSE with UP</t>
-  </si>
-  <si>
-    <t>Form 7 Generated</t>
-  </si>
-  <si>
-    <t>No Action Required</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -340,23 +64,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -681,125 +396,81 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S74"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P74"/>
   <sheetData>
-    <row r="1" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-    </row>
-    <row r="2" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-    </row>
-    <row r="3" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L3" t="s">
-        <v>14</v>
-      </c>
-      <c r="M3" t="s">
-        <v>15</v>
-      </c>
-      <c r="N3" t="s">
-        <v>16</v>
-      </c>
-      <c r="O3" t="s">
-        <v>17</v>
-      </c>
-      <c r="P3" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>92</v>
-      </c>
-      <c r="R3" t="s">
-        <v>93</v>
-      </c>
-      <c r="S3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Notice &amp; Hearing Report</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>S. No.</v>
+      </c>
+      <c r="B2" t="str">
+        <v>AC No. - AC Name</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Notice Generated</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Pending for Notice Generation</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Notice Delivered</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Notices pending delivery</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Hearing</v>
+      </c>
+      <c r="J2" t="str">
+        <v>DEO Status</v>
+      </c>
+      <c r="N2" t="str">
+        <v>ERO/AERO Status</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="G3" t="str">
+        <v>Hearing Held</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Hearing Date Lapsed</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Reschedule Date Lapsed</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Total Pending</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Pending &gt; 5 days</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Verified</v>
+      </c>
+      <c r="M3" t="str">
+        <v>Not Verified</v>
+      </c>
+      <c r="N3" t="str">
+        <v>Found Ineligible for Final</v>
+      </c>
+      <c r="O3" t="str">
+        <v>Parked for Final Publication w.r.t. Notices Generated</v>
+      </c>
+      <c r="P3" t="str">
+        <v>Parked For Final Publication w.r.t. Others</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" t="s">
-        <v>19</v>
+      <c r="B4" t="str">
+        <v>25 - Haridwar</v>
       </c>
       <c r="C4">
         <v>51528</v>
@@ -838,27 +509,18 @@
         <v>869</v>
       </c>
       <c r="O4">
-        <v>50485</v>
+        <v>50659</v>
       </c>
       <c r="P4">
         <v>53812</v>
       </c>
-      <c r="Q4">
-        <v>12212</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5">
       <c r="A5">
         <v>2</v>
       </c>
-      <c r="B5" t="s">
-        <v>20</v>
+      <c r="B5" t="str">
+        <v>26 - BHEL Ranipur</v>
       </c>
       <c r="C5">
         <v>53911</v>
@@ -882,42 +544,33 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>11399</v>
+        <v>11412</v>
       </c>
       <c r="M5">
         <v>757</v>
       </c>
       <c r="N5">
-        <v>861</v>
+        <v>877</v>
       </c>
       <c r="O5">
-        <v>52995</v>
+        <v>53032</v>
       </c>
       <c r="P5">
         <v>74848</v>
       </c>
-      <c r="Q5">
-        <v>16108</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6">
       <c r="A6">
         <v>3</v>
       </c>
-      <c r="B6" t="s">
-        <v>21</v>
+      <c r="B6" t="str">
+        <v>27 - Jwalapur</v>
       </c>
       <c r="C6">
         <v>39773</v>
@@ -941,13 +594,13 @@
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>6024</v>
+        <v>6026</v>
       </c>
       <c r="M6">
         <v>201</v>
@@ -956,27 +609,18 @@
         <v>1778</v>
       </c>
       <c r="O6">
-        <v>33326</v>
+        <v>35153</v>
       </c>
       <c r="P6">
         <v>71989</v>
       </c>
-      <c r="Q6">
-        <v>17830</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7">
       <c r="A7">
         <v>4</v>
       </c>
-      <c r="B7" t="s">
-        <v>22</v>
+      <c r="B7" t="str">
+        <v>28 - Bhagwanpur</v>
       </c>
       <c r="C7">
         <v>39463</v>
@@ -1015,27 +659,18 @@
         <v>1991</v>
       </c>
       <c r="O7">
-        <v>35384</v>
+        <v>35405</v>
       </c>
       <c r="P7">
         <v>77581</v>
       </c>
-      <c r="Q7">
-        <v>20511</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8">
       <c r="A8">
         <v>5</v>
       </c>
-      <c r="B8" t="s">
-        <v>23</v>
+      <c r="B8" t="str">
+        <v>29 - Jhabrera</v>
       </c>
       <c r="C8">
         <v>40552</v>
@@ -1079,22 +714,13 @@
       <c r="P8">
         <v>73458</v>
       </c>
-      <c r="Q8">
-        <v>20788</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9">
       <c r="A9">
         <v>6</v>
       </c>
-      <c r="B9" t="s">
-        <v>24</v>
+      <c r="B9" t="str">
+        <v>30 - Piran Kaliyar</v>
       </c>
       <c r="C9">
         <v>43273</v>
@@ -1124,36 +750,27 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>7757</v>
+        <v>7759</v>
       </c>
       <c r="M9">
         <v>49</v>
       </c>
       <c r="N9">
-        <v>1336</v>
+        <v>1350</v>
       </c>
       <c r="O9">
-        <v>41918</v>
+        <v>41923</v>
       </c>
       <c r="P9">
         <v>72913</v>
       </c>
-      <c r="Q9">
-        <v>18141</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10">
       <c r="A10">
         <v>7</v>
       </c>
-      <c r="B10" t="s">
-        <v>25</v>
+      <c r="B10" t="str">
+        <v>31 - Roorkee</v>
       </c>
       <c r="C10">
         <v>36576</v>
@@ -1197,22 +814,13 @@
       <c r="P10">
         <v>53124</v>
       </c>
-      <c r="Q10">
-        <v>9498</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11">
       <c r="A11">
         <v>8</v>
       </c>
-      <c r="B11" t="s">
-        <v>26</v>
+      <c r="B11" t="str">
+        <v>32 - Khanpur</v>
       </c>
       <c r="C11">
         <v>50998</v>
@@ -1256,22 +864,13 @@
       <c r="P11">
         <v>84438</v>
       </c>
-      <c r="Q11">
-        <v>23477</v>
-      </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12">
       <c r="A12">
         <v>9</v>
       </c>
-      <c r="B12" t="s">
-        <v>27</v>
+      <c r="B12" t="str">
+        <v>33 - Manglore</v>
       </c>
       <c r="C12">
         <v>40739</v>
@@ -1307,30 +906,21 @@
         <v>207</v>
       </c>
       <c r="N12">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="O12">
-        <v>39505</v>
+        <v>39509</v>
       </c>
       <c r="P12">
         <v>66685</v>
       </c>
-      <c r="Q12">
-        <v>17786</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13">
       <c r="A13">
         <v>10</v>
       </c>
-      <c r="B13" t="s">
-        <v>28</v>
+      <c r="B13" t="str">
+        <v>34 - Laksar</v>
       </c>
       <c r="C13">
         <v>37031</v>
@@ -1374,22 +964,13 @@
       <c r="P13">
         <v>56564</v>
       </c>
-      <c r="Q13">
-        <v>16237</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14">
       <c r="A14">
         <v>11</v>
       </c>
-      <c r="B14" t="s">
-        <v>29</v>
+      <c r="B14" t="str">
+        <v>35 - Haridwar Rural</v>
       </c>
       <c r="C14">
         <v>48966</v>
@@ -1413,42 +994,33 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>3</v>
+        <v>71</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>15071</v>
+        <v>15097</v>
       </c>
       <c r="M14">
-        <v>1412</v>
+        <v>1425</v>
       </c>
       <c r="N14">
-        <v>5627</v>
+        <v>5630</v>
       </c>
       <c r="O14">
-        <v>32057</v>
+        <v>37550</v>
       </c>
       <c r="P14">
         <v>77955</v>
       </c>
-      <c r="Q14">
-        <v>19716</v>
-      </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15">
       <c r="A15">
         <v>12</v>
       </c>
-      <c r="B15" t="s">
-        <v>30</v>
+      <c r="B15" t="str">
+        <v>56 - Lalkuan</v>
       </c>
       <c r="C15">
         <v>42703</v>
@@ -1492,22 +1064,13 @@
       <c r="P15">
         <v>67178</v>
       </c>
-      <c r="Q15">
-        <v>4859</v>
-      </c>
-      <c r="R15">
-        <v>0</v>
-      </c>
-      <c r="S15">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16">
       <c r="A16">
         <v>13</v>
       </c>
-      <c r="B16" t="s">
-        <v>31</v>
+      <c r="B16" t="str">
+        <v>57 - Bhimtal</v>
       </c>
       <c r="C16">
         <v>25549</v>
@@ -1551,22 +1114,13 @@
       <c r="P16">
         <v>71673</v>
       </c>
-      <c r="Q16">
-        <v>5197</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17">
       <c r="A17">
         <v>14</v>
       </c>
-      <c r="B17" t="s">
-        <v>32</v>
+      <c r="B17" t="str">
+        <v>58 - Nainital</v>
       </c>
       <c r="C17">
         <v>27707</v>
@@ -1610,22 +1164,13 @@
       <c r="P17">
         <v>65457</v>
       </c>
-      <c r="Q17">
-        <v>5417</v>
-      </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18">
       <c r="A18">
         <v>15</v>
       </c>
-      <c r="B18" t="s">
-        <v>33</v>
+      <c r="B18" t="str">
+        <v>59 - Haldwani</v>
       </c>
       <c r="C18">
         <v>47836</v>
@@ -1669,22 +1214,13 @@
       <c r="P18">
         <v>71475</v>
       </c>
-      <c r="Q18">
-        <v>6819</v>
-      </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
-      <c r="S18">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19">
       <c r="A19">
         <v>16</v>
       </c>
-      <c r="B19" t="s">
-        <v>34</v>
+      <c r="B19" t="str">
+        <v>60 - Kaladhungi</v>
       </c>
       <c r="C19">
         <v>56490</v>
@@ -1708,7 +1244,7 @@
         <v>0</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19">
         <v>0</v>
@@ -1723,27 +1259,18 @@
         <v>910</v>
       </c>
       <c r="O19">
-        <v>55575</v>
+        <v>55579</v>
       </c>
       <c r="P19">
-        <v>106227</v>
-      </c>
-      <c r="Q19">
-        <v>6135</v>
-      </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>106392</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20">
         <v>17</v>
       </c>
-      <c r="B20" t="s">
-        <v>35</v>
+      <c r="B20" t="str">
+        <v>61 - Ramnagar</v>
       </c>
       <c r="C20">
         <v>35022</v>
@@ -1787,22 +1314,13 @@
       <c r="P20">
         <v>75812</v>
       </c>
-      <c r="Q20">
-        <v>8984</v>
-      </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21">
       <c r="A21">
         <v>18</v>
       </c>
-      <c r="B21" t="s">
-        <v>36</v>
+      <c r="B21" t="str">
+        <v>48 - Dwarahat</v>
       </c>
       <c r="C21">
         <v>16962</v>
@@ -1846,22 +1364,13 @@
       <c r="P21">
         <v>62460</v>
       </c>
-      <c r="Q21">
-        <v>3868</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22">
       <c r="A22">
         <v>19</v>
       </c>
-      <c r="B22" t="s">
-        <v>37</v>
+      <c r="B22" t="str">
+        <v>49 - Salt</v>
       </c>
       <c r="C22">
         <v>18668</v>
@@ -1905,22 +1414,13 @@
       <c r="P22">
         <v>64099</v>
       </c>
-      <c r="Q22">
-        <v>4848</v>
-      </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23">
       <c r="A23">
         <v>20</v>
       </c>
-      <c r="B23" t="s">
-        <v>38</v>
+      <c r="B23" t="str">
+        <v>50 - Ranikhet</v>
       </c>
       <c r="C23">
         <v>12020</v>
@@ -1964,22 +1464,13 @@
       <c r="P23">
         <v>57094</v>
       </c>
-      <c r="Q23">
-        <v>3541</v>
-      </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
-      <c r="S23">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24">
       <c r="A24">
         <v>21</v>
       </c>
-      <c r="B24" t="s">
-        <v>39</v>
+      <c r="B24" t="str">
+        <v>51 - Someshwar</v>
       </c>
       <c r="C24">
         <v>14056</v>
@@ -2023,22 +1514,13 @@
       <c r="P24">
         <v>65629</v>
       </c>
-      <c r="Q24">
-        <v>3492</v>
-      </c>
-      <c r="R24">
-        <v>0</v>
-      </c>
-      <c r="S24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25">
       <c r="A25">
         <v>22</v>
       </c>
-      <c r="B25" t="s">
-        <v>40</v>
+      <c r="B25" t="str">
+        <v>52 - Almora</v>
       </c>
       <c r="C25">
         <v>19266</v>
@@ -2082,22 +1564,13 @@
       <c r="P25">
         <v>57533</v>
       </c>
-      <c r="Q25">
-        <v>3231</v>
-      </c>
-      <c r="R25">
-        <v>0</v>
-      </c>
-      <c r="S25">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26">
       <c r="A26">
         <v>23</v>
       </c>
-      <c r="B26" t="s">
-        <v>41</v>
+      <c r="B26" t="str">
+        <v>53 - Jageshwar</v>
       </c>
       <c r="C26">
         <v>17557</v>
@@ -2141,22 +1614,13 @@
       <c r="P26">
         <v>66594</v>
       </c>
-      <c r="Q26">
-        <v>3333</v>
-      </c>
-      <c r="R26">
-        <v>0</v>
-      </c>
-      <c r="S26">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27">
       <c r="A27">
         <v>24</v>
       </c>
-      <c r="B27" t="s">
-        <v>42</v>
+      <c r="B27" t="str">
+        <v>62 - Jaspur</v>
       </c>
       <c r="C27">
         <v>44276</v>
@@ -2180,13 +1644,13 @@
         <v>0</v>
       </c>
       <c r="J27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="L27">
-        <v>9677</v>
+        <v>9679</v>
       </c>
       <c r="M27">
         <v>215</v>
@@ -2200,22 +1664,13 @@
       <c r="P27">
         <v>73109</v>
       </c>
-      <c r="Q27">
-        <v>12669</v>
-      </c>
-      <c r="R27">
-        <v>0</v>
-      </c>
-      <c r="S27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28">
       <c r="A28">
         <v>25</v>
       </c>
-      <c r="B28" t="s">
-        <v>43</v>
+      <c r="B28" t="str">
+        <v>63 - Kashipur</v>
       </c>
       <c r="C28">
         <v>54349</v>
@@ -2251,30 +1706,21 @@
         <v>856</v>
       </c>
       <c r="N28">
-        <v>3340</v>
+        <v>3456</v>
       </c>
       <c r="O28">
-        <v>50752</v>
+        <v>50785</v>
       </c>
       <c r="P28">
         <v>80620</v>
       </c>
-      <c r="Q28">
-        <v>13995</v>
-      </c>
-      <c r="R28">
-        <v>0</v>
-      </c>
-      <c r="S28">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29">
       <c r="A29">
         <v>26</v>
       </c>
-      <c r="B29" t="s">
-        <v>44</v>
+      <c r="B29" t="str">
+        <v>64 - Bajpur</v>
       </c>
       <c r="C29">
         <v>47111</v>
@@ -2318,22 +1764,13 @@
       <c r="P29">
         <v>83836</v>
       </c>
-      <c r="Q29">
-        <v>14229</v>
-      </c>
-      <c r="R29">
-        <v>0</v>
-      </c>
-      <c r="S29">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30">
       <c r="A30">
         <v>27</v>
       </c>
-      <c r="B30" t="s">
-        <v>45</v>
+      <c r="B30" t="str">
+        <v>65 - Gadarpur</v>
       </c>
       <c r="C30">
         <v>52653</v>
@@ -2363,36 +1800,27 @@
         <v>0</v>
       </c>
       <c r="L30">
-        <v>11658</v>
+        <v>11659</v>
       </c>
       <c r="M30">
         <v>411</v>
       </c>
       <c r="N30">
-        <v>5374</v>
+        <v>5383</v>
       </c>
       <c r="O30">
-        <v>47204</v>
+        <v>47260</v>
       </c>
       <c r="P30">
         <v>86933</v>
       </c>
-      <c r="Q30">
-        <v>12564</v>
-      </c>
-      <c r="R30">
-        <v>0</v>
-      </c>
-      <c r="S30">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31">
       <c r="A31">
         <v>28</v>
       </c>
-      <c r="B31" t="s">
-        <v>46</v>
+      <c r="B31" t="str">
+        <v>66 - Rudrapur</v>
       </c>
       <c r="C31">
         <v>91162</v>
@@ -2436,22 +1864,13 @@
       <c r="P31">
         <v>81642</v>
       </c>
-      <c r="Q31">
-        <v>14581</v>
-      </c>
-      <c r="R31">
-        <v>0</v>
-      </c>
-      <c r="S31">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32">
       <c r="A32">
         <v>29</v>
       </c>
-      <c r="B32" t="s">
-        <v>47</v>
+      <c r="B32" t="str">
+        <v>67 - Kichha</v>
       </c>
       <c r="C32">
         <v>46728</v>
@@ -2495,22 +1914,13 @@
       <c r="P32">
         <v>74810</v>
       </c>
-      <c r="Q32">
-        <v>11379</v>
-      </c>
-      <c r="R32">
-        <v>0</v>
-      </c>
-      <c r="S32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33">
       <c r="A33">
         <v>30</v>
       </c>
-      <c r="B33" t="s">
-        <v>48</v>
+      <c r="B33" t="str">
+        <v>68 - Sitarganj</v>
       </c>
       <c r="C33">
         <v>40230</v>
@@ -2534,42 +1944,33 @@
         <v>0</v>
       </c>
       <c r="J33">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="K33">
         <v>0</v>
       </c>
       <c r="L33">
-        <v>5076</v>
+        <v>5089</v>
       </c>
       <c r="M33">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="N33">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="O33">
-        <v>38465</v>
+        <v>38583</v>
       </c>
       <c r="P33">
         <v>76969</v>
       </c>
-      <c r="Q33">
-        <v>6678</v>
-      </c>
-      <c r="R33">
-        <v>0</v>
-      </c>
-      <c r="S33">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34">
       <c r="A34">
         <v>31</v>
       </c>
-      <c r="B34" t="s">
-        <v>49</v>
+      <c r="B34" t="str">
+        <v>69 - Nanakmatta</v>
       </c>
       <c r="C34">
         <v>36542</v>
@@ -2593,42 +1994,33 @@
         <v>0</v>
       </c>
       <c r="J34">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K34">
         <v>0</v>
       </c>
       <c r="L34">
-        <v>12006</v>
+        <v>12131</v>
       </c>
       <c r="M34">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N34">
-        <v>1316</v>
+        <v>1357</v>
       </c>
       <c r="O34">
-        <v>34330</v>
+        <v>34723</v>
       </c>
       <c r="P34">
         <v>74624</v>
       </c>
-      <c r="Q34">
-        <v>7137</v>
-      </c>
-      <c r="R34">
-        <v>0</v>
-      </c>
-      <c r="S34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35">
       <c r="A35">
         <v>32</v>
       </c>
-      <c r="B35" t="s">
-        <v>50</v>
+      <c r="B35" t="str">
+        <v>70 - Khatima</v>
       </c>
       <c r="C35">
         <v>33564</v>
@@ -2652,13 +2044,13 @@
         <v>0</v>
       </c>
       <c r="J35">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K35">
         <v>0</v>
       </c>
       <c r="L35">
-        <v>7883</v>
+        <v>7886</v>
       </c>
       <c r="M35">
         <v>271</v>
@@ -2667,27 +2059,18 @@
         <v>1098</v>
       </c>
       <c r="O35">
-        <v>32429</v>
+        <v>32434</v>
       </c>
       <c r="P35">
         <v>76465</v>
       </c>
-      <c r="Q35">
-        <v>8879</v>
-      </c>
-      <c r="R35">
-        <v>0</v>
-      </c>
-      <c r="S35">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36">
       <c r="A36">
         <v>33</v>
       </c>
-      <c r="B36" t="s">
-        <v>51</v>
+      <c r="B36" t="str">
+        <v>42 - Dharchula</v>
       </c>
       <c r="C36">
         <v>20905</v>
@@ -2731,22 +2114,13 @@
       <c r="P36">
         <v>60419</v>
       </c>
-      <c r="Q36">
-        <v>3855</v>
-      </c>
-      <c r="R36">
-        <v>0</v>
-      </c>
-      <c r="S36">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37">
       <c r="A37">
         <v>34</v>
       </c>
-      <c r="B37" t="s">
-        <v>52</v>
+      <c r="B37" t="str">
+        <v>43 - Didihat</v>
       </c>
       <c r="C37">
         <v>17692</v>
@@ -2790,22 +2164,13 @@
       <c r="P37">
         <v>57832</v>
       </c>
-      <c r="Q37">
-        <v>4036</v>
-      </c>
-      <c r="R37">
-        <v>0</v>
-      </c>
-      <c r="S37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38">
       <c r="A38">
         <v>35</v>
       </c>
-      <c r="B38" t="s">
-        <v>53</v>
+      <c r="B38" t="str">
+        <v>44 - Pithoragarh</v>
       </c>
       <c r="C38">
         <v>29110</v>
@@ -2849,22 +2214,13 @@
       <c r="P38">
         <v>63038</v>
       </c>
-      <c r="Q38">
-        <v>5135</v>
-      </c>
-      <c r="R38">
-        <v>0</v>
-      </c>
-      <c r="S38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39">
       <c r="A39">
         <v>36</v>
       </c>
-      <c r="B39" t="s">
-        <v>54</v>
+      <c r="B39" t="str">
+        <v>45 - Gangolihat</v>
       </c>
       <c r="C39">
         <v>21367</v>
@@ -2908,22 +2264,13 @@
       <c r="P39">
         <v>71133</v>
       </c>
-      <c r="Q39">
-        <v>5903</v>
-      </c>
-      <c r="R39">
-        <v>0</v>
-      </c>
-      <c r="S39">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="40" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40">
       <c r="A40">
         <v>37</v>
       </c>
-      <c r="B40" t="s">
-        <v>55</v>
+      <c r="B40" t="str">
+        <v>46 - Kapkot</v>
       </c>
       <c r="C40">
         <v>18905</v>
@@ -2967,22 +2314,13 @@
       <c r="P40">
         <v>73242</v>
       </c>
-      <c r="Q40">
-        <v>3824</v>
-      </c>
-      <c r="R40">
-        <v>0</v>
-      </c>
-      <c r="S40">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="41" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41">
       <c r="A41">
         <v>38</v>
       </c>
-      <c r="B41" t="s">
-        <v>56</v>
+      <c r="B41" t="str">
+        <v>47 - Bageshwar</v>
       </c>
       <c r="C41">
         <v>23521</v>
@@ -3026,22 +2364,13 @@
       <c r="P41">
         <v>85251</v>
       </c>
-      <c r="Q41">
-        <v>6015</v>
-      </c>
-      <c r="R41">
-        <v>0</v>
-      </c>
-      <c r="S41">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="42" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42">
       <c r="A42">
         <v>39</v>
       </c>
-      <c r="B42" t="s">
-        <v>57</v>
+      <c r="B42" t="str">
+        <v>54 - Lohaghat</v>
       </c>
       <c r="C42">
         <v>27565</v>
@@ -3085,22 +2414,13 @@
       <c r="P42">
         <v>68615</v>
       </c>
-      <c r="Q42">
-        <v>4708</v>
-      </c>
-      <c r="R42">
-        <v>0</v>
-      </c>
-      <c r="S42">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43">
       <c r="A43">
         <v>40</v>
       </c>
-      <c r="B43" t="s">
-        <v>58</v>
+      <c r="B43" t="str">
+        <v>55 - Champawat</v>
       </c>
       <c r="C43">
         <v>29700</v>
@@ -3136,30 +2456,21 @@
         <v>1</v>
       </c>
       <c r="N43">
-        <v>912</v>
+        <v>957</v>
       </c>
       <c r="O43">
-        <v>28789</v>
+        <v>28774</v>
       </c>
       <c r="P43">
-        <v>63042</v>
-      </c>
-      <c r="Q43">
-        <v>5219</v>
-      </c>
-      <c r="R43">
-        <v>0</v>
-      </c>
-      <c r="S43">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="44" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>63012</v>
+      </c>
+    </row>
+    <row r="44">
       <c r="A44">
         <v>41</v>
       </c>
-      <c r="B44" t="s">
-        <v>59</v>
+      <c r="B44" t="str">
+        <v>4 - Badrinath</v>
       </c>
       <c r="C44">
         <v>21900</v>
@@ -3203,22 +2514,13 @@
       <c r="P44">
         <v>68393</v>
       </c>
-      <c r="Q44">
-        <v>7659</v>
-      </c>
-      <c r="R44">
-        <v>0</v>
-      </c>
-      <c r="S44">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="45" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45">
       <c r="A45">
         <v>42</v>
       </c>
-      <c r="B45" t="s">
-        <v>60</v>
+      <c r="B45" t="str">
+        <v>5 - Tharali</v>
       </c>
       <c r="C45">
         <v>19935</v>
@@ -3262,22 +2564,13 @@
       <c r="P45">
         <v>76287</v>
       </c>
-      <c r="Q45">
-        <v>6998</v>
-      </c>
-      <c r="R45">
-        <v>0</v>
-      </c>
-      <c r="S45">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="46" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46">
       <c r="A46">
         <v>43</v>
       </c>
-      <c r="B46" t="s">
-        <v>61</v>
+      <c r="B46" t="str">
+        <v>6 - Karanprayag</v>
       </c>
       <c r="C46">
         <v>21512</v>
@@ -3321,22 +2614,13 @@
       <c r="P46">
         <v>64160</v>
       </c>
-      <c r="Q46">
-        <v>7548</v>
-      </c>
-      <c r="R46">
-        <v>0</v>
-      </c>
-      <c r="S46">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="47" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47">
       <c r="A47">
         <v>44</v>
       </c>
-      <c r="B47" t="s">
-        <v>62</v>
+      <c r="B47" t="str">
+        <v>1 - Purola</v>
       </c>
       <c r="C47">
         <v>22426</v>
@@ -3380,22 +2664,13 @@
       <c r="P47">
         <v>49875</v>
       </c>
-      <c r="Q47">
-        <v>5046</v>
-      </c>
-      <c r="R47">
-        <v>0</v>
-      </c>
-      <c r="S47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48">
       <c r="A48">
         <v>45</v>
       </c>
-      <c r="B48" t="s">
-        <v>63</v>
+      <c r="B48" t="str">
+        <v>2 - Yamunotri</v>
       </c>
       <c r="C48">
         <v>19641</v>
@@ -3439,22 +2714,13 @@
       <c r="P48">
         <v>54142</v>
       </c>
-      <c r="Q48">
-        <v>4623</v>
-      </c>
-      <c r="R48">
-        <v>0</v>
-      </c>
-      <c r="S48">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49">
       <c r="A49">
         <v>46</v>
       </c>
-      <c r="B49" t="s">
-        <v>64</v>
+      <c r="B49" t="str">
+        <v>3 - Gangotri</v>
       </c>
       <c r="C49">
         <v>21651</v>
@@ -3498,22 +2764,13 @@
       <c r="P49">
         <v>55376</v>
       </c>
-      <c r="Q49">
-        <v>5057</v>
-      </c>
-      <c r="R49">
-        <v>0</v>
-      </c>
-      <c r="S49">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="50" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50">
       <c r="A50">
         <v>47</v>
       </c>
-      <c r="B50" t="s">
-        <v>65</v>
+      <c r="B50" t="str">
+        <v>7 - Kedarnath</v>
       </c>
       <c r="C50">
         <v>21936</v>
@@ -3557,22 +2814,13 @@
       <c r="P50">
         <v>63298</v>
       </c>
-      <c r="Q50">
-        <v>7292</v>
-      </c>
-      <c r="R50">
-        <v>0</v>
-      </c>
-      <c r="S50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51">
       <c r="A51">
         <v>48</v>
       </c>
-      <c r="B51" t="s">
-        <v>66</v>
+      <c r="B51" t="str">
+        <v>8 - Rudraprayag</v>
       </c>
       <c r="C51">
         <v>23798</v>
@@ -3616,22 +2864,13 @@
       <c r="P51">
         <v>71754</v>
       </c>
-      <c r="Q51">
-        <v>7715</v>
-      </c>
-      <c r="R51">
-        <v>0</v>
-      </c>
-      <c r="S51">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="52" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52">
       <c r="A52">
         <v>49</v>
       </c>
-      <c r="B52" t="s">
-        <v>67</v>
+      <c r="B52" t="str">
+        <v>9 - Ghansali</v>
       </c>
       <c r="C52">
         <v>21094</v>
@@ -3675,22 +2914,13 @@
       <c r="P52">
         <v>63987</v>
       </c>
-      <c r="Q52">
-        <v>5655</v>
-      </c>
-      <c r="R52">
-        <v>0</v>
-      </c>
-      <c r="S52">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53">
       <c r="A53">
         <v>50</v>
       </c>
-      <c r="B53" t="s">
-        <v>68</v>
+      <c r="B53" t="str">
+        <v>10 - Devprayag</v>
       </c>
       <c r="C53">
         <v>19131</v>
@@ -3734,22 +2964,13 @@
       <c r="P53">
         <v>56306</v>
       </c>
-      <c r="Q53">
-        <v>6551</v>
-      </c>
-      <c r="R53">
-        <v>0</v>
-      </c>
-      <c r="S53">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54">
       <c r="A54">
         <v>51</v>
       </c>
-      <c r="B54" t="s">
-        <v>69</v>
+      <c r="B54" t="str">
+        <v>11 - Narendranagar</v>
       </c>
       <c r="C54">
         <v>20758</v>
@@ -3793,22 +3014,13 @@
       <c r="P54">
         <v>58440</v>
       </c>
-      <c r="Q54">
-        <v>7347</v>
-      </c>
-      <c r="R54">
-        <v>0</v>
-      </c>
-      <c r="S54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55">
       <c r="A55">
         <v>52</v>
       </c>
-      <c r="B55" t="s">
-        <v>70</v>
+      <c r="B55" t="str">
+        <v>12 - Pratapnagar</v>
       </c>
       <c r="C55">
         <v>16022</v>
@@ -3852,22 +3064,13 @@
       <c r="P55">
         <v>58215</v>
       </c>
-      <c r="Q55">
-        <v>5098</v>
-      </c>
-      <c r="R55">
-        <v>0</v>
-      </c>
-      <c r="S55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56">
       <c r="A56">
         <v>53</v>
       </c>
-      <c r="B56" t="s">
-        <v>71</v>
+      <c r="B56" t="str">
+        <v>13 - Tehri</v>
       </c>
       <c r="C56">
         <v>19256</v>
@@ -3882,51 +3085,42 @@
         <v>0</v>
       </c>
       <c r="G56">
-        <v>19255</v>
+        <v>19256</v>
       </c>
       <c r="H56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I56">
         <v>0</v>
       </c>
       <c r="J56">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K56">
         <v>0</v>
       </c>
       <c r="L56">
-        <v>4083</v>
+        <v>4088</v>
       </c>
       <c r="M56">
         <v>3</v>
       </c>
       <c r="N56">
-        <v>431</v>
+        <v>444</v>
       </c>
       <c r="O56">
-        <v>18795</v>
+        <v>18802</v>
       </c>
       <c r="P56">
         <v>47621</v>
       </c>
-      <c r="Q56">
-        <v>4882</v>
-      </c>
-      <c r="R56">
-        <v>0</v>
-      </c>
-      <c r="S56">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="57" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57">
       <c r="A57">
         <v>54</v>
       </c>
-      <c r="B57" t="s">
-        <v>72</v>
+      <c r="B57" t="str">
+        <v>14 - Dhanolti</v>
       </c>
       <c r="C57">
         <v>21240</v>
@@ -3970,22 +3164,13 @@
       <c r="P57">
         <v>61556</v>
       </c>
-      <c r="Q57">
-        <v>6870</v>
-      </c>
-      <c r="R57">
-        <v>0</v>
-      </c>
-      <c r="S57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58">
       <c r="A58">
         <v>55</v>
       </c>
-      <c r="B58" t="s">
-        <v>73</v>
+      <c r="B58" t="str">
+        <v>36 - Yamkeshwar</v>
       </c>
       <c r="C58">
         <v>22819</v>
@@ -4029,22 +3214,13 @@
       <c r="P58">
         <v>57577</v>
       </c>
-      <c r="Q58">
-        <v>8884</v>
-      </c>
-      <c r="R58">
-        <v>0</v>
-      </c>
-      <c r="S58">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="59" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="59">
       <c r="A59">
         <v>56</v>
       </c>
-      <c r="B59" t="s">
-        <v>74</v>
+      <c r="B59" t="str">
+        <v>37 - Pauri</v>
       </c>
       <c r="C59">
         <v>18776</v>
@@ -4088,22 +3264,13 @@
       <c r="P59">
         <v>60495</v>
       </c>
-      <c r="Q59">
-        <v>8028</v>
-      </c>
-      <c r="R59">
-        <v>0</v>
-      </c>
-      <c r="S59">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="60" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60">
       <c r="A60">
         <v>57</v>
       </c>
-      <c r="B60" t="s">
-        <v>75</v>
+      <c r="B60" t="str">
+        <v>38 - Srinagar</v>
       </c>
       <c r="C60">
         <v>23749</v>
@@ -4147,22 +3314,13 @@
       <c r="P60">
         <v>70140</v>
       </c>
-      <c r="Q60">
-        <v>7415</v>
-      </c>
-      <c r="R60">
-        <v>0</v>
-      </c>
-      <c r="S60">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="61" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61">
       <c r="A61">
         <v>58</v>
       </c>
-      <c r="B61" t="s">
-        <v>76</v>
+      <c r="B61" t="str">
+        <v>39 - Chaubattakhal</v>
       </c>
       <c r="C61">
         <v>22069</v>
@@ -4206,22 +3364,13 @@
       <c r="P61">
         <v>55240</v>
       </c>
-      <c r="Q61">
-        <v>7927</v>
-      </c>
-      <c r="R61">
-        <v>1</v>
-      </c>
-      <c r="S61">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="62" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62">
       <c r="A62">
         <v>59</v>
       </c>
-      <c r="B62" t="s">
-        <v>77</v>
+      <c r="B62" t="str">
+        <v>40 - Lansdowne</v>
       </c>
       <c r="C62">
         <v>15800</v>
@@ -4265,22 +3414,13 @@
       <c r="P62">
         <v>51334</v>
       </c>
-      <c r="Q62">
-        <v>6917</v>
-      </c>
-      <c r="R62">
-        <v>0</v>
-      </c>
-      <c r="S62">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="63" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63">
       <c r="A63">
         <v>60</v>
       </c>
-      <c r="B63" t="s">
-        <v>78</v>
+      <c r="B63" t="str">
+        <v>41 - Kotdwar</v>
       </c>
       <c r="C63">
         <v>36754</v>
@@ -4324,22 +3464,13 @@
       <c r="P63">
         <v>68691</v>
       </c>
-      <c r="Q63">
-        <v>9766</v>
-      </c>
-      <c r="R63">
-        <v>0</v>
-      </c>
-      <c r="S63">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="64" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64">
       <c r="A64">
         <v>61</v>
       </c>
-      <c r="B64" t="s">
-        <v>79</v>
+      <c r="B64" t="str">
+        <v>15 - Chakrata</v>
       </c>
       <c r="C64">
         <v>42048</v>
@@ -4383,22 +3514,13 @@
       <c r="P64">
         <v>60527</v>
       </c>
-      <c r="Q64">
-        <v>5985</v>
-      </c>
-      <c r="R64">
-        <v>0</v>
-      </c>
-      <c r="S64">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="65" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65">
       <c r="A65">
         <v>62</v>
       </c>
-      <c r="B65" t="s">
-        <v>80</v>
+      <c r="B65" t="str">
+        <v>16 - Vikasnagar</v>
       </c>
       <c r="C65">
         <v>41389</v>
@@ -4422,13 +3544,13 @@
         <v>0</v>
       </c>
       <c r="J65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K65">
         <v>0</v>
       </c>
       <c r="L65">
-        <v>13573</v>
+        <v>13582</v>
       </c>
       <c r="M65">
         <v>2</v>
@@ -4437,27 +3559,18 @@
         <v>2635</v>
       </c>
       <c r="O65">
-        <v>38745</v>
+        <v>38754</v>
       </c>
       <c r="P65">
         <v>58527</v>
       </c>
-      <c r="Q65">
-        <v>13282</v>
-      </c>
-      <c r="R65">
-        <v>0</v>
-      </c>
-      <c r="S65">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="66" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="66">
       <c r="A66">
         <v>63</v>
       </c>
-      <c r="B66" t="s">
-        <v>81</v>
+      <c r="B66" t="str">
+        <v>17 - Sahaspur</v>
       </c>
       <c r="C66">
         <v>67362</v>
@@ -4493,30 +3606,21 @@
         <v>2</v>
       </c>
       <c r="N66">
-        <v>4021</v>
+        <v>4022</v>
       </c>
       <c r="O66">
-        <v>63342</v>
+        <v>63341</v>
       </c>
       <c r="P66">
         <v>93810</v>
       </c>
-      <c r="Q66">
-        <v>17742</v>
-      </c>
-      <c r="R66">
-        <v>0</v>
-      </c>
-      <c r="S66">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="67" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="67">
       <c r="A67">
         <v>64</v>
       </c>
-      <c r="B67" t="s">
-        <v>82</v>
+      <c r="B67" t="str">
+        <v>18 - Dharmpur</v>
       </c>
       <c r="C67">
         <v>68828</v>
@@ -4560,22 +3664,13 @@
       <c r="P67">
         <v>78032</v>
       </c>
-      <c r="Q67">
-        <v>9807</v>
-      </c>
-      <c r="R67">
-        <v>0</v>
-      </c>
-      <c r="S67">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="68" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="68">
       <c r="A68">
         <v>65</v>
       </c>
-      <c r="B68" t="s">
-        <v>83</v>
+      <c r="B68" t="str">
+        <v>19 - Raipur</v>
       </c>
       <c r="C68">
         <v>65397</v>
@@ -4614,27 +3709,18 @@
         <v>1602</v>
       </c>
       <c r="O68">
-        <v>63795</v>
+        <v>63796</v>
       </c>
       <c r="P68">
         <v>71325</v>
       </c>
-      <c r="Q68">
-        <v>7850</v>
-      </c>
-      <c r="R68">
-        <v>0</v>
-      </c>
-      <c r="S68">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="69" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="69">
       <c r="A69">
         <v>66</v>
       </c>
-      <c r="B69" t="s">
-        <v>84</v>
+      <c r="B69" t="str">
+        <v>20 - Rajpur Road</v>
       </c>
       <c r="C69">
         <v>43938</v>
@@ -4678,22 +3764,13 @@
       <c r="P69">
         <v>36118</v>
       </c>
-      <c r="Q69">
-        <v>6528</v>
-      </c>
-      <c r="R69">
-        <v>0</v>
-      </c>
-      <c r="S69">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="70" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="70">
       <c r="A70">
         <v>67</v>
       </c>
-      <c r="B70" t="s">
-        <v>85</v>
+      <c r="B70" t="str">
+        <v>21 - Dehradun Cantonment</v>
       </c>
       <c r="C70">
         <v>47711</v>
@@ -4737,22 +3814,13 @@
       <c r="P70">
         <v>42051</v>
       </c>
-      <c r="Q70">
-        <v>5798</v>
-      </c>
-      <c r="R70">
-        <v>0</v>
-      </c>
-      <c r="S70">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="71" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71">
       <c r="A71">
         <v>68</v>
       </c>
-      <c r="B71" t="s">
-        <v>86</v>
+      <c r="B71" t="str">
+        <v>22 - Mussoorie</v>
       </c>
       <c r="C71">
         <v>50963</v>
@@ -4796,22 +3864,13 @@
       <c r="P71">
         <v>49140</v>
       </c>
-      <c r="Q71">
-        <v>6782</v>
-      </c>
-      <c r="R71">
-        <v>0</v>
-      </c>
-      <c r="S71">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="72" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72">
       <c r="A72">
         <v>69</v>
       </c>
-      <c r="B72" t="s">
-        <v>87</v>
+      <c r="B72" t="str">
+        <v>23 - Doiwala</v>
       </c>
       <c r="C72">
         <v>61543</v>
@@ -4855,22 +3914,13 @@
       <c r="P72">
         <v>85505</v>
       </c>
-      <c r="Q72">
-        <v>12340</v>
-      </c>
-      <c r="R72">
-        <v>0</v>
-      </c>
-      <c r="S72">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="73" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73">
       <c r="A73">
         <v>70</v>
       </c>
-      <c r="B73" t="s">
-        <v>88</v>
+      <c r="B73" t="str">
+        <v>24 - Rishikesh</v>
       </c>
       <c r="C73">
         <v>58915</v>
@@ -4914,21 +3964,11 @@
       <c r="P73">
         <v>67666</v>
       </c>
-      <c r="Q73">
-        <v>10010</v>
-      </c>
-      <c r="R73">
-        <v>0</v>
-      </c>
-      <c r="S73">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="74" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B74" s="1"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>Total</v>
+      </c>
       <c r="C74">
         <v>2430387</v>
       </c>
@@ -4942,49 +3982,38 @@
         <v>0</v>
       </c>
       <c r="G74">
-        <v>2430384</v>
+        <v>2430385</v>
       </c>
       <c r="H74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I74">
         <v>0</v>
       </c>
       <c r="J74">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="K74">
         <v>5</v>
       </c>
       <c r="L74">
-        <v>624634</v>
+        <v>624835</v>
       </c>
       <c r="M74">
-        <v>8088</v>
+        <v>8105</v>
       </c>
       <c r="N74">
-        <v>96145</v>
+        <v>96407</v>
       </c>
       <c r="O74">
-        <v>2308593</v>
+        <v>2316764</v>
       </c>
       <c r="P74">
-        <v>4701766</v>
-      </c>
-      <c r="Q74">
-        <v>626236</v>
-      </c>
-      <c r="R74">
-        <v>1</v>
-      </c>
-      <c r="S74">
-        <v>3445</v>
+        <v>4701901</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="Q2:S2"/>
+  <mergeCells count="11">
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
@@ -4995,10 +4024,10 @@
     <mergeCell ref="G2:I2"/>
     <mergeCell ref="J2:M2"/>
     <mergeCell ref="N2:P2"/>
+    <mergeCell ref="A74:B74"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A2:P74 B1:P1" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P74"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -1,41 +1,317 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\New folder (13)\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C36331EC-C675-4CC8-BA7B-9838FBA432EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
+  <si>
+    <t>S. No.</t>
+  </si>
+  <si>
+    <t>AC No. - AC Name</t>
+  </si>
+  <si>
+    <t>Notice Generated</t>
+  </si>
+  <si>
+    <t>Pending for Notice Generation</t>
+  </si>
+  <si>
+    <t>Notice Delivered</t>
+  </si>
+  <si>
+    <t>Notices pending delivery</t>
+  </si>
+  <si>
+    <t>Hearing</t>
+  </si>
+  <si>
+    <t>DEO Status</t>
+  </si>
+  <si>
+    <t>ERO/AERO Status</t>
+  </si>
+  <si>
+    <t>Hearing Held</t>
+  </si>
+  <si>
+    <t>Hearing Date Lapsed</t>
+  </si>
+  <si>
+    <t>Reschedule Date Lapsed</t>
+  </si>
+  <si>
+    <t>Total Pending</t>
+  </si>
+  <si>
+    <t>Pending &gt; 5 days</t>
+  </si>
+  <si>
+    <t>Verified</t>
+  </si>
+  <si>
+    <t>Not Verified</t>
+  </si>
+  <si>
+    <t>Found Ineligible for Final</t>
+  </si>
+  <si>
+    <t>Parked for Final Publication w.r.t. Notices Generated</t>
+  </si>
+  <si>
+    <t>Parked For Final Publication w.r.t. Others</t>
+  </si>
+  <si>
+    <t>25 - Haridwar</t>
+  </si>
+  <si>
+    <t>26 - BHEL Ranipur</t>
+  </si>
+  <si>
+    <t>27 - Jwalapur</t>
+  </si>
+  <si>
+    <t>28 - Bhagwanpur</t>
+  </si>
+  <si>
+    <t>29 - Jhabrera</t>
+  </si>
+  <si>
+    <t>30 - Piran Kaliyar</t>
+  </si>
+  <si>
+    <t>31 - Roorkee</t>
+  </si>
+  <si>
+    <t>32 - Khanpur</t>
+  </si>
+  <si>
+    <t>33 - Manglore</t>
+  </si>
+  <si>
+    <t>34 - Laksar</t>
+  </si>
+  <si>
+    <t>35 - Haridwar Rural</t>
+  </si>
+  <si>
+    <t>56 - Lalkuan</t>
+  </si>
+  <si>
+    <t>57 - Bhimtal</t>
+  </si>
+  <si>
+    <t>58 - Nainital</t>
+  </si>
+  <si>
+    <t>59 - Haldwani</t>
+  </si>
+  <si>
+    <t>60 - Kaladhungi</t>
+  </si>
+  <si>
+    <t>61 - Ramnagar</t>
+  </si>
+  <si>
+    <t>48 - Dwarahat</t>
+  </si>
+  <si>
+    <t>49 - Salt</t>
+  </si>
+  <si>
+    <t>50 - Ranikhet</t>
+  </si>
+  <si>
+    <t>51 - Someshwar</t>
+  </si>
+  <si>
+    <t>52 - Almora</t>
+  </si>
+  <si>
+    <t>53 - Jageshwar</t>
+  </si>
+  <si>
+    <t>62 - Jaspur</t>
+  </si>
+  <si>
+    <t>63 - Kashipur</t>
+  </si>
+  <si>
+    <t>64 - Bajpur</t>
+  </si>
+  <si>
+    <t>65 - Gadarpur</t>
+  </si>
+  <si>
+    <t>66 - Rudrapur</t>
+  </si>
+  <si>
+    <t>67 - Kichha</t>
+  </si>
+  <si>
+    <t>68 - Sitarganj</t>
+  </si>
+  <si>
+    <t>69 - Nanakmatta</t>
+  </si>
+  <si>
+    <t>70 - Khatima</t>
+  </si>
+  <si>
+    <t>42 - Dharchula</t>
+  </si>
+  <si>
+    <t>43 - Didihat</t>
+  </si>
+  <si>
+    <t>44 - Pithoragarh</t>
+  </si>
+  <si>
+    <t>45 - Gangolihat</t>
+  </si>
+  <si>
+    <t>46 - Kapkot</t>
+  </si>
+  <si>
+    <t>47 - Bageshwar</t>
+  </si>
+  <si>
+    <t>54 - Lohaghat</t>
+  </si>
+  <si>
+    <t>55 - Champawat</t>
+  </si>
+  <si>
+    <t>4 - Badrinath</t>
+  </si>
+  <si>
+    <t>5 - Tharali</t>
+  </si>
+  <si>
+    <t>6 - Karanprayag</t>
+  </si>
+  <si>
+    <t>1 - Purola</t>
+  </si>
+  <si>
+    <t>2 - Yamunotri</t>
+  </si>
+  <si>
+    <t>3 - Gangotri</t>
+  </si>
+  <si>
+    <t>7 - Kedarnath</t>
+  </si>
+  <si>
+    <t>8 - Rudraprayag</t>
+  </si>
+  <si>
+    <t>9 - Ghansali</t>
+  </si>
+  <si>
+    <t>10 - Devprayag</t>
+  </si>
+  <si>
+    <t>11 - Narendranagar</t>
+  </si>
+  <si>
+    <t>12 - Pratapnagar</t>
+  </si>
+  <si>
+    <t>13 - Tehri</t>
+  </si>
+  <si>
+    <t>14 - Dhanolti</t>
+  </si>
+  <si>
+    <t>36 - Yamkeshwar</t>
+  </si>
+  <si>
+    <t>37 - Pauri</t>
+  </si>
+  <si>
+    <t>38 - Srinagar</t>
+  </si>
+  <si>
+    <t>39 - Chaubattakhal</t>
+  </si>
+  <si>
+    <t>40 - Lansdowne</t>
+  </si>
+  <si>
+    <t>41 - Kotdwar</t>
+  </si>
+  <si>
+    <t>15 - Chakrata</t>
+  </si>
+  <si>
+    <t>16 - Vikasnagar</t>
+  </si>
+  <si>
+    <t>17 - Sahaspur</t>
+  </si>
+  <si>
+    <t>18 - Dharmpur</t>
+  </si>
+  <si>
+    <t>19 - Raipur</t>
+  </si>
+  <si>
+    <t>20 - Rajpur Road</t>
+  </si>
+  <si>
+    <t>21 - Dehradun Cantonment</t>
+  </si>
+  <si>
+    <t>22 - Mussoorie</t>
+  </si>
+  <si>
+    <t>23 - Doiwala</t>
+  </si>
+  <si>
+    <t>24 - Rishikesh</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>DSE with UP</t>
+  </si>
+  <si>
+    <t>Electors having DSE with UP</t>
+  </si>
+  <si>
+    <t>Form 7 Generated</t>
+  </si>
+  <si>
+    <t>No Action Required</t>
+  </si>
+  <si>
+    <t>Notice &amp; Hearing Report Last Updated On : 11-09-2026 07:56:53</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -64,14 +340,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,81 +682,125 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P74"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:S76"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Notice &amp; Hearing Report</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>S. No.</v>
-      </c>
-      <c r="B2" t="str">
-        <v>AC No. - AC Name</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Notice Generated</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Pending for Notice Generation</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Notice Delivered</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Notices pending delivery</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Hearing</v>
-      </c>
-      <c r="J2" t="str">
-        <v>DEO Status</v>
-      </c>
-      <c r="N2" t="str">
-        <v>ERO/AERO Status</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="G3" t="str">
-        <v>Hearing Held</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Hearing Date Lapsed</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Reschedule Date Lapsed</v>
-      </c>
-      <c r="J3" t="str">
-        <v>Total Pending</v>
-      </c>
-      <c r="K3" t="str">
-        <v>Pending &gt; 5 days</v>
-      </c>
-      <c r="L3" t="str">
-        <v>Verified</v>
-      </c>
-      <c r="M3" t="str">
-        <v>Not Verified</v>
-      </c>
-      <c r="N3" t="str">
-        <v>Found Ineligible for Final</v>
-      </c>
-      <c r="O3" t="str">
-        <v>Parked for Final Publication w.r.t. Notices Generated</v>
-      </c>
-      <c r="P3" t="str">
-        <v>Parked For Final Publication w.r.t. Others</v>
-      </c>
-    </row>
-    <row r="4">
+    <row r="1" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+    </row>
+    <row r="3" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L3" t="s">
+        <v>14</v>
+      </c>
+      <c r="M3" t="s">
+        <v>15</v>
+      </c>
+      <c r="N3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" t="str">
-        <v>25 - Haridwar</v>
+      <c r="B4" t="s">
+        <v>19</v>
       </c>
       <c r="C4">
         <v>51528</v>
@@ -514,13 +844,22 @@
       <c r="P4">
         <v>53812</v>
       </c>
-    </row>
-    <row r="5">
+      <c r="Q4" s="2">
+        <v>12212</v>
+      </c>
+      <c r="R4" s="2">
+        <v>0</v>
+      </c>
+      <c r="S4" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
-      <c r="B5" t="str">
-        <v>26 - BHEL Ranipur</v>
+      <c r="B5" t="s">
+        <v>20</v>
       </c>
       <c r="C5">
         <v>53911</v>
@@ -564,13 +903,22 @@
       <c r="P5">
         <v>74848</v>
       </c>
-    </row>
-    <row r="6">
+      <c r="Q5" s="2">
+        <v>16108</v>
+      </c>
+      <c r="R5" s="2">
+        <v>0</v>
+      </c>
+      <c r="S5" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
-      <c r="B6" t="str">
-        <v>27 - Jwalapur</v>
+      <c r="B6" t="s">
+        <v>21</v>
       </c>
       <c r="C6">
         <v>39773</v>
@@ -614,13 +962,22 @@
       <c r="P6">
         <v>71989</v>
       </c>
-    </row>
-    <row r="7">
+      <c r="Q6" s="2">
+        <v>17830</v>
+      </c>
+      <c r="R6" s="2">
+        <v>0</v>
+      </c>
+      <c r="S6" s="2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4</v>
       </c>
-      <c r="B7" t="str">
-        <v>28 - Bhagwanpur</v>
+      <c r="B7" t="s">
+        <v>22</v>
       </c>
       <c r="C7">
         <v>39463</v>
@@ -664,13 +1021,22 @@
       <c r="P7">
         <v>77581</v>
       </c>
-    </row>
-    <row r="8">
+      <c r="Q7" s="2">
+        <v>20511</v>
+      </c>
+      <c r="R7" s="2">
+        <v>0</v>
+      </c>
+      <c r="S7" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
-      <c r="B8" t="str">
-        <v>29 - Jhabrera</v>
+      <c r="B8" t="s">
+        <v>23</v>
       </c>
       <c r="C8">
         <v>40552</v>
@@ -714,13 +1080,22 @@
       <c r="P8">
         <v>73458</v>
       </c>
-    </row>
-    <row r="9">
+      <c r="Q8" s="2">
+        <v>20788</v>
+      </c>
+      <c r="R8" s="2">
+        <v>0</v>
+      </c>
+      <c r="S8" s="2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6</v>
       </c>
-      <c r="B9" t="str">
-        <v>30 - Piran Kaliyar</v>
+      <c r="B9" t="s">
+        <v>24</v>
       </c>
       <c r="C9">
         <v>43273</v>
@@ -764,13 +1139,22 @@
       <c r="P9">
         <v>72913</v>
       </c>
-    </row>
-    <row r="10">
+      <c r="Q9" s="2">
+        <v>18141</v>
+      </c>
+      <c r="R9" s="2">
+        <v>0</v>
+      </c>
+      <c r="S9" s="2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>7</v>
       </c>
-      <c r="B10" t="str">
-        <v>31 - Roorkee</v>
+      <c r="B10" t="s">
+        <v>25</v>
       </c>
       <c r="C10">
         <v>36576</v>
@@ -814,13 +1198,22 @@
       <c r="P10">
         <v>53124</v>
       </c>
-    </row>
-    <row r="11">
+      <c r="Q10" s="2">
+        <v>9498</v>
+      </c>
+      <c r="R10" s="2">
+        <v>0</v>
+      </c>
+      <c r="S10" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>8</v>
       </c>
-      <c r="B11" t="str">
-        <v>32 - Khanpur</v>
+      <c r="B11" t="s">
+        <v>26</v>
       </c>
       <c r="C11">
         <v>50998</v>
@@ -864,13 +1257,22 @@
       <c r="P11">
         <v>84438</v>
       </c>
-    </row>
-    <row r="12">
+      <c r="Q11" s="2">
+        <v>23477</v>
+      </c>
+      <c r="R11" s="2">
+        <v>0</v>
+      </c>
+      <c r="S11" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
-      <c r="B12" t="str">
-        <v>33 - Manglore</v>
+      <c r="B12" t="s">
+        <v>27</v>
       </c>
       <c r="C12">
         <v>40739</v>
@@ -914,13 +1316,22 @@
       <c r="P12">
         <v>66685</v>
       </c>
-    </row>
-    <row r="13">
+      <c r="Q12" s="2">
+        <v>17786</v>
+      </c>
+      <c r="R12" s="2">
+        <v>0</v>
+      </c>
+      <c r="S12" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
-      <c r="B13" t="str">
-        <v>34 - Laksar</v>
+      <c r="B13" t="s">
+        <v>28</v>
       </c>
       <c r="C13">
         <v>37031</v>
@@ -964,13 +1375,22 @@
       <c r="P13">
         <v>56564</v>
       </c>
-    </row>
-    <row r="14">
+      <c r="Q13" s="2">
+        <v>16237</v>
+      </c>
+      <c r="R13" s="2">
+        <v>0</v>
+      </c>
+      <c r="S13" s="2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>11</v>
       </c>
-      <c r="B14" t="str">
-        <v>35 - Haridwar Rural</v>
+      <c r="B14" t="s">
+        <v>29</v>
       </c>
       <c r="C14">
         <v>48966</v>
@@ -1014,13 +1434,22 @@
       <c r="P14">
         <v>77955</v>
       </c>
-    </row>
-    <row r="15">
+      <c r="Q14" s="2">
+        <v>19716</v>
+      </c>
+      <c r="R14" s="2">
+        <v>0</v>
+      </c>
+      <c r="S14" s="2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12</v>
       </c>
-      <c r="B15" t="str">
-        <v>56 - Lalkuan</v>
+      <c r="B15" t="s">
+        <v>30</v>
       </c>
       <c r="C15">
         <v>42703</v>
@@ -1064,13 +1493,22 @@
       <c r="P15">
         <v>67178</v>
       </c>
-    </row>
-    <row r="16">
+      <c r="Q15" s="2">
+        <v>4859</v>
+      </c>
+      <c r="R15" s="2">
+        <v>0</v>
+      </c>
+      <c r="S15" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13</v>
       </c>
-      <c r="B16" t="str">
-        <v>57 - Bhimtal</v>
+      <c r="B16" t="s">
+        <v>31</v>
       </c>
       <c r="C16">
         <v>25549</v>
@@ -1114,13 +1552,22 @@
       <c r="P16">
         <v>71673</v>
       </c>
-    </row>
-    <row r="17">
+      <c r="Q16" s="2">
+        <v>5197</v>
+      </c>
+      <c r="R16" s="2">
+        <v>0</v>
+      </c>
+      <c r="S16" s="2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>14</v>
       </c>
-      <c r="B17" t="str">
-        <v>58 - Nainital</v>
+      <c r="B17" t="s">
+        <v>32</v>
       </c>
       <c r="C17">
         <v>27707</v>
@@ -1164,13 +1611,22 @@
       <c r="P17">
         <v>65457</v>
       </c>
-    </row>
-    <row r="18">
+      <c r="Q17" s="2">
+        <v>5417</v>
+      </c>
+      <c r="R17" s="2">
+        <v>0</v>
+      </c>
+      <c r="S17" s="2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>15</v>
       </c>
-      <c r="B18" t="str">
-        <v>59 - Haldwani</v>
+      <c r="B18" t="s">
+        <v>33</v>
       </c>
       <c r="C18">
         <v>47836</v>
@@ -1214,13 +1670,22 @@
       <c r="P18">
         <v>71475</v>
       </c>
-    </row>
-    <row r="19">
+      <c r="Q18" s="2">
+        <v>6819</v>
+      </c>
+      <c r="R18" s="2">
+        <v>0</v>
+      </c>
+      <c r="S18" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>16</v>
       </c>
-      <c r="B19" t="str">
-        <v>60 - Kaladhungi</v>
+      <c r="B19" t="s">
+        <v>34</v>
       </c>
       <c r="C19">
         <v>56490</v>
@@ -1264,13 +1729,22 @@
       <c r="P19">
         <v>106392</v>
       </c>
-    </row>
-    <row r="20">
+      <c r="Q19" s="2">
+        <v>6135</v>
+      </c>
+      <c r="R19" s="2">
+        <v>0</v>
+      </c>
+      <c r="S19" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>17</v>
       </c>
-      <c r="B20" t="str">
-        <v>61 - Ramnagar</v>
+      <c r="B20" t="s">
+        <v>35</v>
       </c>
       <c r="C20">
         <v>35022</v>
@@ -1314,13 +1788,22 @@
       <c r="P20">
         <v>75812</v>
       </c>
-    </row>
-    <row r="21">
+      <c r="Q20" s="2">
+        <v>8984</v>
+      </c>
+      <c r="R20" s="2">
+        <v>0</v>
+      </c>
+      <c r="S20" s="2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>18</v>
       </c>
-      <c r="B21" t="str">
-        <v>48 - Dwarahat</v>
+      <c r="B21" t="s">
+        <v>36</v>
       </c>
       <c r="C21">
         <v>16962</v>
@@ -1364,13 +1847,22 @@
       <c r="P21">
         <v>62460</v>
       </c>
-    </row>
-    <row r="22">
+      <c r="Q21" s="2">
+        <v>3868</v>
+      </c>
+      <c r="R21" s="2">
+        <v>0</v>
+      </c>
+      <c r="S21" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>19</v>
       </c>
-      <c r="B22" t="str">
-        <v>49 - Salt</v>
+      <c r="B22" t="s">
+        <v>37</v>
       </c>
       <c r="C22">
         <v>18668</v>
@@ -1414,13 +1906,22 @@
       <c r="P22">
         <v>64099</v>
       </c>
-    </row>
-    <row r="23">
+      <c r="Q22" s="2">
+        <v>4848</v>
+      </c>
+      <c r="R22" s="2">
+        <v>0</v>
+      </c>
+      <c r="S22" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>20</v>
       </c>
-      <c r="B23" t="str">
-        <v>50 - Ranikhet</v>
+      <c r="B23" t="s">
+        <v>38</v>
       </c>
       <c r="C23">
         <v>12020</v>
@@ -1464,13 +1965,22 @@
       <c r="P23">
         <v>57094</v>
       </c>
-    </row>
-    <row r="24">
+      <c r="Q23" s="2">
+        <v>3541</v>
+      </c>
+      <c r="R23" s="2">
+        <v>0</v>
+      </c>
+      <c r="S23" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>21</v>
       </c>
-      <c r="B24" t="str">
-        <v>51 - Someshwar</v>
+      <c r="B24" t="s">
+        <v>39</v>
       </c>
       <c r="C24">
         <v>14056</v>
@@ -1514,13 +2024,22 @@
       <c r="P24">
         <v>65629</v>
       </c>
-    </row>
-    <row r="25">
+      <c r="Q24" s="2">
+        <v>3492</v>
+      </c>
+      <c r="R24" s="2">
+        <v>0</v>
+      </c>
+      <c r="S24" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>22</v>
       </c>
-      <c r="B25" t="str">
-        <v>52 - Almora</v>
+      <c r="B25" t="s">
+        <v>40</v>
       </c>
       <c r="C25">
         <v>19266</v>
@@ -1564,13 +2083,22 @@
       <c r="P25">
         <v>57533</v>
       </c>
-    </row>
-    <row r="26">
+      <c r="Q25" s="2">
+        <v>3231</v>
+      </c>
+      <c r="R25" s="2">
+        <v>0</v>
+      </c>
+      <c r="S25" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23</v>
       </c>
-      <c r="B26" t="str">
-        <v>53 - Jageshwar</v>
+      <c r="B26" t="s">
+        <v>41</v>
       </c>
       <c r="C26">
         <v>17557</v>
@@ -1614,13 +2142,22 @@
       <c r="P26">
         <v>66594</v>
       </c>
-    </row>
-    <row r="27">
+      <c r="Q26" s="2">
+        <v>3333</v>
+      </c>
+      <c r="R26" s="2">
+        <v>0</v>
+      </c>
+      <c r="S26" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>24</v>
       </c>
-      <c r="B27" t="str">
-        <v>62 - Jaspur</v>
+      <c r="B27" t="s">
+        <v>42</v>
       </c>
       <c r="C27">
         <v>44276</v>
@@ -1664,13 +2201,22 @@
       <c r="P27">
         <v>73109</v>
       </c>
-    </row>
-    <row r="28">
+      <c r="Q27" s="2">
+        <v>12669</v>
+      </c>
+      <c r="R27" s="2">
+        <v>0</v>
+      </c>
+      <c r="S27" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25</v>
       </c>
-      <c r="B28" t="str">
-        <v>63 - Kashipur</v>
+      <c r="B28" t="s">
+        <v>43</v>
       </c>
       <c r="C28">
         <v>54349</v>
@@ -1714,13 +2260,22 @@
       <c r="P28">
         <v>80620</v>
       </c>
-    </row>
-    <row r="29">
+      <c r="Q28" s="2">
+        <v>13995</v>
+      </c>
+      <c r="R28" s="2">
+        <v>0</v>
+      </c>
+      <c r="S28" s="2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26</v>
       </c>
-      <c r="B29" t="str">
-        <v>64 - Bajpur</v>
+      <c r="B29" t="s">
+        <v>44</v>
       </c>
       <c r="C29">
         <v>47111</v>
@@ -1764,13 +2319,22 @@
       <c r="P29">
         <v>83836</v>
       </c>
-    </row>
-    <row r="30">
+      <c r="Q29" s="2">
+        <v>14229</v>
+      </c>
+      <c r="R29" s="2">
+        <v>0</v>
+      </c>
+      <c r="S29" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>27</v>
       </c>
-      <c r="B30" t="str">
-        <v>65 - Gadarpur</v>
+      <c r="B30" t="s">
+        <v>45</v>
       </c>
       <c r="C30">
         <v>52653</v>
@@ -1814,13 +2378,22 @@
       <c r="P30">
         <v>86933</v>
       </c>
-    </row>
-    <row r="31">
+      <c r="Q30" s="2">
+        <v>12564</v>
+      </c>
+      <c r="R30" s="2">
+        <v>0</v>
+      </c>
+      <c r="S30" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>28</v>
       </c>
-      <c r="B31" t="str">
-        <v>66 - Rudrapur</v>
+      <c r="B31" t="s">
+        <v>46</v>
       </c>
       <c r="C31">
         <v>91162</v>
@@ -1864,13 +2437,22 @@
       <c r="P31">
         <v>81642</v>
       </c>
-    </row>
-    <row r="32">
+      <c r="Q31" s="2">
+        <v>14581</v>
+      </c>
+      <c r="R31" s="2">
+        <v>0</v>
+      </c>
+      <c r="S31" s="2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>29</v>
       </c>
-      <c r="B32" t="str">
-        <v>67 - Kichha</v>
+      <c r="B32" t="s">
+        <v>47</v>
       </c>
       <c r="C32">
         <v>46728</v>
@@ -1914,13 +2496,22 @@
       <c r="P32">
         <v>74810</v>
       </c>
-    </row>
-    <row r="33">
+      <c r="Q32" s="2">
+        <v>11379</v>
+      </c>
+      <c r="R32" s="2">
+        <v>0</v>
+      </c>
+      <c r="S32" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>30</v>
       </c>
-      <c r="B33" t="str">
-        <v>68 - Sitarganj</v>
+      <c r="B33" t="s">
+        <v>48</v>
       </c>
       <c r="C33">
         <v>40230</v>
@@ -1964,13 +2555,22 @@
       <c r="P33">
         <v>76969</v>
       </c>
-    </row>
-    <row r="34">
+      <c r="Q33" s="2">
+        <v>6678</v>
+      </c>
+      <c r="R33" s="2">
+        <v>0</v>
+      </c>
+      <c r="S33" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>31</v>
       </c>
-      <c r="B34" t="str">
-        <v>69 - Nanakmatta</v>
+      <c r="B34" t="s">
+        <v>49</v>
       </c>
       <c r="C34">
         <v>36542</v>
@@ -2014,13 +2614,22 @@
       <c r="P34">
         <v>74624</v>
       </c>
-    </row>
-    <row r="35">
+      <c r="Q34" s="2">
+        <v>7137</v>
+      </c>
+      <c r="R34" s="2">
+        <v>0</v>
+      </c>
+      <c r="S34" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32</v>
       </c>
-      <c r="B35" t="str">
-        <v>70 - Khatima</v>
+      <c r="B35" t="s">
+        <v>50</v>
       </c>
       <c r="C35">
         <v>33564</v>
@@ -2064,13 +2673,22 @@
       <c r="P35">
         <v>76465</v>
       </c>
-    </row>
-    <row r="36">
+      <c r="Q35" s="2">
+        <v>8879</v>
+      </c>
+      <c r="R35" s="2">
+        <v>0</v>
+      </c>
+      <c r="S35" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>33</v>
       </c>
-      <c r="B36" t="str">
-        <v>42 - Dharchula</v>
+      <c r="B36" t="s">
+        <v>51</v>
       </c>
       <c r="C36">
         <v>20905</v>
@@ -2114,13 +2732,22 @@
       <c r="P36">
         <v>60419</v>
       </c>
-    </row>
-    <row r="37">
+      <c r="Q36" s="2">
+        <v>3855</v>
+      </c>
+      <c r="R36" s="2">
+        <v>0</v>
+      </c>
+      <c r="S36" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>34</v>
       </c>
-      <c r="B37" t="str">
-        <v>43 - Didihat</v>
+      <c r="B37" t="s">
+        <v>52</v>
       </c>
       <c r="C37">
         <v>17692</v>
@@ -2164,13 +2791,22 @@
       <c r="P37">
         <v>57832</v>
       </c>
-    </row>
-    <row r="38">
+      <c r="Q37" s="2">
+        <v>4036</v>
+      </c>
+      <c r="R37" s="2">
+        <v>0</v>
+      </c>
+      <c r="S37" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>35</v>
       </c>
-      <c r="B38" t="str">
-        <v>44 - Pithoragarh</v>
+      <c r="B38" t="s">
+        <v>53</v>
       </c>
       <c r="C38">
         <v>29110</v>
@@ -2214,13 +2850,22 @@
       <c r="P38">
         <v>63038</v>
       </c>
-    </row>
-    <row r="39">
+      <c r="Q38" s="2">
+        <v>5135</v>
+      </c>
+      <c r="R38" s="2">
+        <v>0</v>
+      </c>
+      <c r="S38" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>36</v>
       </c>
-      <c r="B39" t="str">
-        <v>45 - Gangolihat</v>
+      <c r="B39" t="s">
+        <v>54</v>
       </c>
       <c r="C39">
         <v>21367</v>
@@ -2264,13 +2909,22 @@
       <c r="P39">
         <v>71133</v>
       </c>
-    </row>
-    <row r="40">
+      <c r="Q39" s="2">
+        <v>5903</v>
+      </c>
+      <c r="R39" s="2">
+        <v>0</v>
+      </c>
+      <c r="S39" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>37</v>
       </c>
-      <c r="B40" t="str">
-        <v>46 - Kapkot</v>
+      <c r="B40" t="s">
+        <v>55</v>
       </c>
       <c r="C40">
         <v>18905</v>
@@ -2314,13 +2968,22 @@
       <c r="P40">
         <v>73242</v>
       </c>
-    </row>
-    <row r="41">
+      <c r="Q40" s="2">
+        <v>3824</v>
+      </c>
+      <c r="R40" s="2">
+        <v>0</v>
+      </c>
+      <c r="S40" s="2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>38</v>
       </c>
-      <c r="B41" t="str">
-        <v>47 - Bageshwar</v>
+      <c r="B41" t="s">
+        <v>56</v>
       </c>
       <c r="C41">
         <v>23521</v>
@@ -2364,13 +3027,22 @@
       <c r="P41">
         <v>85251</v>
       </c>
-    </row>
-    <row r="42">
+      <c r="Q41" s="2">
+        <v>6015</v>
+      </c>
+      <c r="R41" s="2">
+        <v>0</v>
+      </c>
+      <c r="S41" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>39</v>
       </c>
-      <c r="B42" t="str">
-        <v>54 - Lohaghat</v>
+      <c r="B42" t="s">
+        <v>57</v>
       </c>
       <c r="C42">
         <v>27565</v>
@@ -2414,13 +3086,22 @@
       <c r="P42">
         <v>68615</v>
       </c>
-    </row>
-    <row r="43">
+      <c r="Q42" s="2">
+        <v>4708</v>
+      </c>
+      <c r="R42" s="2">
+        <v>0</v>
+      </c>
+      <c r="S42" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>40</v>
       </c>
-      <c r="B43" t="str">
-        <v>55 - Champawat</v>
+      <c r="B43" t="s">
+        <v>58</v>
       </c>
       <c r="C43">
         <v>29700</v>
@@ -2464,13 +3145,22 @@
       <c r="P43">
         <v>63012</v>
       </c>
-    </row>
-    <row r="44">
+      <c r="Q43" s="2">
+        <v>5219</v>
+      </c>
+      <c r="R43" s="2">
+        <v>0</v>
+      </c>
+      <c r="S43" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>41</v>
       </c>
-      <c r="B44" t="str">
-        <v>4 - Badrinath</v>
+      <c r="B44" t="s">
+        <v>59</v>
       </c>
       <c r="C44">
         <v>21900</v>
@@ -2514,13 +3204,22 @@
       <c r="P44">
         <v>68393</v>
       </c>
-    </row>
-    <row r="45">
+      <c r="Q44" s="2">
+        <v>7659</v>
+      </c>
+      <c r="R44" s="2">
+        <v>0</v>
+      </c>
+      <c r="S44" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>42</v>
       </c>
-      <c r="B45" t="str">
-        <v>5 - Tharali</v>
+      <c r="B45" t="s">
+        <v>60</v>
       </c>
       <c r="C45">
         <v>19935</v>
@@ -2564,13 +3263,22 @@
       <c r="P45">
         <v>76287</v>
       </c>
-    </row>
-    <row r="46">
+      <c r="Q45" s="2">
+        <v>6998</v>
+      </c>
+      <c r="R45" s="2">
+        <v>0</v>
+      </c>
+      <c r="S45" s="2">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>43</v>
       </c>
-      <c r="B46" t="str">
-        <v>6 - Karanprayag</v>
+      <c r="B46" t="s">
+        <v>61</v>
       </c>
       <c r="C46">
         <v>21512</v>
@@ -2614,13 +3322,22 @@
       <c r="P46">
         <v>64160</v>
       </c>
-    </row>
-    <row r="47">
+      <c r="Q46" s="2">
+        <v>7548</v>
+      </c>
+      <c r="R46" s="2">
+        <v>0</v>
+      </c>
+      <c r="S46" s="2">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>44</v>
       </c>
-      <c r="B47" t="str">
-        <v>1 - Purola</v>
+      <c r="B47" t="s">
+        <v>62</v>
       </c>
       <c r="C47">
         <v>22426</v>
@@ -2664,13 +3381,22 @@
       <c r="P47">
         <v>49875</v>
       </c>
-    </row>
-    <row r="48">
+      <c r="Q47" s="2">
+        <v>5046</v>
+      </c>
+      <c r="R47" s="2">
+        <v>0</v>
+      </c>
+      <c r="S47" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>45</v>
       </c>
-      <c r="B48" t="str">
-        <v>2 - Yamunotri</v>
+      <c r="B48" t="s">
+        <v>63</v>
       </c>
       <c r="C48">
         <v>19641</v>
@@ -2714,13 +3440,22 @@
       <c r="P48">
         <v>54142</v>
       </c>
-    </row>
-    <row r="49">
+      <c r="Q48" s="2">
+        <v>4623</v>
+      </c>
+      <c r="R48" s="2">
+        <v>0</v>
+      </c>
+      <c r="S48" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>46</v>
       </c>
-      <c r="B49" t="str">
-        <v>3 - Gangotri</v>
+      <c r="B49" t="s">
+        <v>64</v>
       </c>
       <c r="C49">
         <v>21651</v>
@@ -2764,13 +3499,22 @@
       <c r="P49">
         <v>55376</v>
       </c>
-    </row>
-    <row r="50">
+      <c r="Q49" s="2">
+        <v>5057</v>
+      </c>
+      <c r="R49" s="2">
+        <v>0</v>
+      </c>
+      <c r="S49" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>47</v>
       </c>
-      <c r="B50" t="str">
-        <v>7 - Kedarnath</v>
+      <c r="B50" t="s">
+        <v>65</v>
       </c>
       <c r="C50">
         <v>21936</v>
@@ -2814,13 +3558,22 @@
       <c r="P50">
         <v>63298</v>
       </c>
-    </row>
-    <row r="51">
+      <c r="Q50" s="2">
+        <v>7292</v>
+      </c>
+      <c r="R50" s="2">
+        <v>0</v>
+      </c>
+      <c r="S50" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>48</v>
       </c>
-      <c r="B51" t="str">
-        <v>8 - Rudraprayag</v>
+      <c r="B51" t="s">
+        <v>66</v>
       </c>
       <c r="C51">
         <v>23798</v>
@@ -2864,13 +3617,22 @@
       <c r="P51">
         <v>71754</v>
       </c>
-    </row>
-    <row r="52">
+      <c r="Q51" s="2">
+        <v>7715</v>
+      </c>
+      <c r="R51" s="2">
+        <v>0</v>
+      </c>
+      <c r="S51" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>49</v>
       </c>
-      <c r="B52" t="str">
-        <v>9 - Ghansali</v>
+      <c r="B52" t="s">
+        <v>67</v>
       </c>
       <c r="C52">
         <v>21094</v>
@@ -2914,13 +3676,22 @@
       <c r="P52">
         <v>63987</v>
       </c>
-    </row>
-    <row r="53">
+      <c r="Q52" s="2">
+        <v>5655</v>
+      </c>
+      <c r="R52" s="2">
+        <v>0</v>
+      </c>
+      <c r="S52" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>50</v>
       </c>
-      <c r="B53" t="str">
-        <v>10 - Devprayag</v>
+      <c r="B53" t="s">
+        <v>68</v>
       </c>
       <c r="C53">
         <v>19131</v>
@@ -2964,13 +3735,22 @@
       <c r="P53">
         <v>56306</v>
       </c>
-    </row>
-    <row r="54">
+      <c r="Q53" s="2">
+        <v>6551</v>
+      </c>
+      <c r="R53" s="2">
+        <v>0</v>
+      </c>
+      <c r="S53" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>51</v>
       </c>
-      <c r="B54" t="str">
-        <v>11 - Narendranagar</v>
+      <c r="B54" t="s">
+        <v>69</v>
       </c>
       <c r="C54">
         <v>20758</v>
@@ -3014,13 +3794,22 @@
       <c r="P54">
         <v>58440</v>
       </c>
-    </row>
-    <row r="55">
+      <c r="Q54" s="2">
+        <v>7347</v>
+      </c>
+      <c r="R54" s="2">
+        <v>0</v>
+      </c>
+      <c r="S54" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>52</v>
       </c>
-      <c r="B55" t="str">
-        <v>12 - Pratapnagar</v>
+      <c r="B55" t="s">
+        <v>70</v>
       </c>
       <c r="C55">
         <v>16022</v>
@@ -3064,13 +3853,22 @@
       <c r="P55">
         <v>58215</v>
       </c>
-    </row>
-    <row r="56">
+      <c r="Q55" s="2">
+        <v>5098</v>
+      </c>
+      <c r="R55" s="2">
+        <v>0</v>
+      </c>
+      <c r="S55" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>53</v>
       </c>
-      <c r="B56" t="str">
-        <v>13 - Tehri</v>
+      <c r="B56" t="s">
+        <v>71</v>
       </c>
       <c r="C56">
         <v>19256</v>
@@ -3114,13 +3912,22 @@
       <c r="P56">
         <v>47621</v>
       </c>
-    </row>
-    <row r="57">
+      <c r="Q56" s="2">
+        <v>4882</v>
+      </c>
+      <c r="R56" s="2">
+        <v>0</v>
+      </c>
+      <c r="S56" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>54</v>
       </c>
-      <c r="B57" t="str">
-        <v>14 - Dhanolti</v>
+      <c r="B57" t="s">
+        <v>72</v>
       </c>
       <c r="C57">
         <v>21240</v>
@@ -3164,13 +3971,22 @@
       <c r="P57">
         <v>61556</v>
       </c>
-    </row>
-    <row r="58">
+      <c r="Q57" s="2">
+        <v>6870</v>
+      </c>
+      <c r="R57" s="2">
+        <v>0</v>
+      </c>
+      <c r="S57" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>55</v>
       </c>
-      <c r="B58" t="str">
-        <v>36 - Yamkeshwar</v>
+      <c r="B58" t="s">
+        <v>73</v>
       </c>
       <c r="C58">
         <v>22819</v>
@@ -3214,13 +4030,22 @@
       <c r="P58">
         <v>57577</v>
       </c>
-    </row>
-    <row r="59">
+      <c r="Q58" s="2">
+        <v>8884</v>
+      </c>
+      <c r="R58" s="2">
+        <v>0</v>
+      </c>
+      <c r="S58" s="2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>56</v>
       </c>
-      <c r="B59" t="str">
-        <v>37 - Pauri</v>
+      <c r="B59" t="s">
+        <v>74</v>
       </c>
       <c r="C59">
         <v>18776</v>
@@ -3264,13 +4089,22 @@
       <c r="P59">
         <v>60495</v>
       </c>
-    </row>
-    <row r="60">
+      <c r="Q59" s="2">
+        <v>8028</v>
+      </c>
+      <c r="R59" s="2">
+        <v>0</v>
+      </c>
+      <c r="S59" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>57</v>
       </c>
-      <c r="B60" t="str">
-        <v>38 - Srinagar</v>
+      <c r="B60" t="s">
+        <v>75</v>
       </c>
       <c r="C60">
         <v>23749</v>
@@ -3314,13 +4148,22 @@
       <c r="P60">
         <v>70140</v>
       </c>
-    </row>
-    <row r="61">
+      <c r="Q60" s="2">
+        <v>7415</v>
+      </c>
+      <c r="R60" s="2">
+        <v>0</v>
+      </c>
+      <c r="S60" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>58</v>
       </c>
-      <c r="B61" t="str">
-        <v>39 - Chaubattakhal</v>
+      <c r="B61" t="s">
+        <v>76</v>
       </c>
       <c r="C61">
         <v>22069</v>
@@ -3364,13 +4207,22 @@
       <c r="P61">
         <v>55240</v>
       </c>
-    </row>
-    <row r="62">
+      <c r="Q61" s="2">
+        <v>7927</v>
+      </c>
+      <c r="R61" s="2">
+        <v>1</v>
+      </c>
+      <c r="S61" s="2">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>59</v>
       </c>
-      <c r="B62" t="str">
-        <v>40 - Lansdowne</v>
+      <c r="B62" t="s">
+        <v>77</v>
       </c>
       <c r="C62">
         <v>15800</v>
@@ -3414,13 +4266,22 @@
       <c r="P62">
         <v>51334</v>
       </c>
-    </row>
-    <row r="63">
+      <c r="Q62" s="2">
+        <v>6917</v>
+      </c>
+      <c r="R62" s="2">
+        <v>0</v>
+      </c>
+      <c r="S62" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>60</v>
       </c>
-      <c r="B63" t="str">
-        <v>41 - Kotdwar</v>
+      <c r="B63" t="s">
+        <v>78</v>
       </c>
       <c r="C63">
         <v>36754</v>
@@ -3464,13 +4325,22 @@
       <c r="P63">
         <v>68691</v>
       </c>
-    </row>
-    <row r="64">
+      <c r="Q63" s="2">
+        <v>9766</v>
+      </c>
+      <c r="R63" s="2">
+        <v>0</v>
+      </c>
+      <c r="S63" s="2">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>61</v>
       </c>
-      <c r="B64" t="str">
-        <v>15 - Chakrata</v>
+      <c r="B64" t="s">
+        <v>79</v>
       </c>
       <c r="C64">
         <v>42048</v>
@@ -3514,13 +4384,22 @@
       <c r="P64">
         <v>60527</v>
       </c>
-    </row>
-    <row r="65">
+      <c r="Q64" s="2">
+        <v>5985</v>
+      </c>
+      <c r="R64" s="2">
+        <v>0</v>
+      </c>
+      <c r="S64" s="2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>62</v>
       </c>
-      <c r="B65" t="str">
-        <v>16 - Vikasnagar</v>
+      <c r="B65" t="s">
+        <v>80</v>
       </c>
       <c r="C65">
         <v>41389</v>
@@ -3564,13 +4443,22 @@
       <c r="P65">
         <v>58527</v>
       </c>
-    </row>
-    <row r="66">
+      <c r="Q65" s="2">
+        <v>13282</v>
+      </c>
+      <c r="R65" s="2">
+        <v>0</v>
+      </c>
+      <c r="S65" s="2">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>63</v>
       </c>
-      <c r="B66" t="str">
-        <v>17 - Sahaspur</v>
+      <c r="B66" t="s">
+        <v>81</v>
       </c>
       <c r="C66">
         <v>67362</v>
@@ -3614,13 +4502,22 @@
       <c r="P66">
         <v>93810</v>
       </c>
-    </row>
-    <row r="67">
+      <c r="Q66" s="2">
+        <v>17742</v>
+      </c>
+      <c r="R66" s="2">
+        <v>0</v>
+      </c>
+      <c r="S66" s="2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>64</v>
       </c>
-      <c r="B67" t="str">
-        <v>18 - Dharmpur</v>
+      <c r="B67" t="s">
+        <v>82</v>
       </c>
       <c r="C67">
         <v>68828</v>
@@ -3664,13 +4561,22 @@
       <c r="P67">
         <v>78032</v>
       </c>
-    </row>
-    <row r="68">
+      <c r="Q67" s="2">
+        <v>9807</v>
+      </c>
+      <c r="R67" s="2">
+        <v>0</v>
+      </c>
+      <c r="S67" s="2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>65</v>
       </c>
-      <c r="B68" t="str">
-        <v>19 - Raipur</v>
+      <c r="B68" t="s">
+        <v>83</v>
       </c>
       <c r="C68">
         <v>65397</v>
@@ -3714,13 +4620,22 @@
       <c r="P68">
         <v>71325</v>
       </c>
-    </row>
-    <row r="69">
+      <c r="Q68" s="2">
+        <v>7850</v>
+      </c>
+      <c r="R68" s="2">
+        <v>0</v>
+      </c>
+      <c r="S68" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>66</v>
       </c>
-      <c r="B69" t="str">
-        <v>20 - Rajpur Road</v>
+      <c r="B69" t="s">
+        <v>84</v>
       </c>
       <c r="C69">
         <v>43938</v>
@@ -3764,13 +4679,22 @@
       <c r="P69">
         <v>36118</v>
       </c>
-    </row>
-    <row r="70">
+      <c r="Q69" s="2">
+        <v>6528</v>
+      </c>
+      <c r="R69" s="2">
+        <v>0</v>
+      </c>
+      <c r="S69" s="2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>67</v>
       </c>
-      <c r="B70" t="str">
-        <v>21 - Dehradun Cantonment</v>
+      <c r="B70" t="s">
+        <v>85</v>
       </c>
       <c r="C70">
         <v>47711</v>
@@ -3814,13 +4738,22 @@
       <c r="P70">
         <v>42051</v>
       </c>
-    </row>
-    <row r="71">
+      <c r="Q70" s="2">
+        <v>5798</v>
+      </c>
+      <c r="R70" s="2">
+        <v>0</v>
+      </c>
+      <c r="S70" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>68</v>
       </c>
-      <c r="B71" t="str">
-        <v>22 - Mussoorie</v>
+      <c r="B71" t="s">
+        <v>86</v>
       </c>
       <c r="C71">
         <v>50963</v>
@@ -3864,13 +4797,22 @@
       <c r="P71">
         <v>49140</v>
       </c>
-    </row>
-    <row r="72">
+      <c r="Q71" s="2">
+        <v>6782</v>
+      </c>
+      <c r="R71" s="2">
+        <v>0</v>
+      </c>
+      <c r="S71" s="2">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>69</v>
       </c>
-      <c r="B72" t="str">
-        <v>23 - Doiwala</v>
+      <c r="B72" t="s">
+        <v>87</v>
       </c>
       <c r="C72">
         <v>61543</v>
@@ -3914,13 +4856,22 @@
       <c r="P72">
         <v>85505</v>
       </c>
-    </row>
-    <row r="73">
+      <c r="Q72" s="2">
+        <v>12340</v>
+      </c>
+      <c r="R72" s="2">
+        <v>0</v>
+      </c>
+      <c r="S72" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>70</v>
       </c>
-      <c r="B73" t="str">
-        <v>24 - Rishikesh</v>
+      <c r="B73" t="s">
+        <v>88</v>
       </c>
       <c r="C73">
         <v>58915</v>
@@ -3964,11 +4915,21 @@
       <c r="P73">
         <v>67666</v>
       </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="str">
-        <v>Total</v>
-      </c>
+      <c r="Q73" s="2">
+        <v>10010</v>
+      </c>
+      <c r="R73" s="2">
+        <v>0</v>
+      </c>
+      <c r="S73" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B74" s="1"/>
       <c r="C74">
         <v>2430387</v>
       </c>
@@ -4011,9 +4972,22 @@
       <c r="P74">
         <v>4701901</v>
       </c>
-    </row>
+      <c r="Q74" s="2">
+        <v>626236</v>
+      </c>
+      <c r="R74" s="2">
+        <v>1</v>
+      </c>
+      <c r="S74" s="2">
+        <v>3445</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="1:19" ht="15.75" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="Q2:S2"/>
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
@@ -4024,10 +4998,10 @@
     <mergeCell ref="G2:I2"/>
     <mergeCell ref="J2:M2"/>
     <mergeCell ref="N2:P2"/>
-    <mergeCell ref="A74:B74"/>
   </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P74"/>
+    <ignoredError sqref="A2:P74 B1:P1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Notice.xlsx
+++ b/Notice.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\New folder (13)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C36331EC-C675-4CC8-BA7B-9838FBA432EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D92A034C-1795-4C13-9D46-2BD0B3676EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -292,6 +292,9 @@
     <t>Total</t>
   </si>
   <si>
+    <t>Notice &amp; Hearing Report Last Updated On : 12-09-2026 09:56:54</t>
+  </si>
+  <si>
     <t>DSE with UP</t>
   </si>
   <si>
@@ -302,9 +305,6 @@
   </si>
   <si>
     <t>No Action Required</t>
-  </si>
-  <si>
-    <t>Notice &amp; Hearing Report Last Updated On : 11-09-2026 07:56:53</t>
   </si>
 </sst>
 </file>
@@ -340,8 +340,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
@@ -683,12 +682,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S76"/>
+  <dimension ref="A1:S74"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -743,7 +742,7 @@
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
@@ -785,14 +784,14 @@
       <c r="P3" t="s">
         <v>18</v>
       </c>
-      <c r="Q3" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="R3" s="2" t="s">
+      <c r="Q3" t="s">
         <v>92</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="R3" t="s">
         <v>93</v>
+      </c>
+      <c r="S3" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
@@ -844,13 +843,13 @@
       <c r="P4">
         <v>53812</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="Q4">
         <v>12212</v>
       </c>
-      <c r="R4" s="2">
-        <v>0</v>
-      </c>
-      <c r="S4" s="2">
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
         <v>11</v>
       </c>
     </row>
@@ -883,13 +882,13 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>11412</v>
+        <v>11415</v>
       </c>
       <c r="M5">
         <v>757</v>
@@ -898,18 +897,18 @@
         <v>877</v>
       </c>
       <c r="O5">
-        <v>53032</v>
+        <v>53035</v>
       </c>
       <c r="P5">
         <v>74848</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="Q5">
         <v>16108</v>
       </c>
-      <c r="R5" s="2">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2">
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
         <v>30</v>
       </c>
     </row>
@@ -948,27 +947,27 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>6026</v>
+        <v>6027</v>
       </c>
       <c r="M6">
         <v>201</v>
       </c>
       <c r="N6">
-        <v>1778</v>
+        <v>1804</v>
       </c>
       <c r="O6">
-        <v>35153</v>
+        <v>36928</v>
       </c>
       <c r="P6">
         <v>71989</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="Q6">
         <v>17830</v>
       </c>
-      <c r="R6" s="2">
-        <v>0</v>
-      </c>
-      <c r="S6" s="2">
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
         <v>54</v>
       </c>
     </row>
@@ -1001,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -1016,18 +1015,18 @@
         <v>1991</v>
       </c>
       <c r="O7">
-        <v>35405</v>
+        <v>37230</v>
       </c>
       <c r="P7">
         <v>77581</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="Q7">
         <v>20511</v>
       </c>
-      <c r="R7" s="2">
-        <v>0</v>
-      </c>
-      <c r="S7" s="2">
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
         <v>8</v>
       </c>
     </row>
@@ -1060,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -1072,21 +1071,21 @@
         <v>164</v>
       </c>
       <c r="N8">
-        <v>1871</v>
+        <v>1874</v>
       </c>
       <c r="O8">
-        <v>34536</v>
+        <v>35270</v>
       </c>
       <c r="P8">
         <v>73458</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="Q8">
         <v>20788</v>
       </c>
-      <c r="R8" s="2">
-        <v>0</v>
-      </c>
-      <c r="S8" s="2">
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
         <v>110</v>
       </c>
     </row>
@@ -1134,18 +1133,18 @@
         <v>1350</v>
       </c>
       <c r="O9">
-        <v>41923</v>
+        <v>41924</v>
       </c>
       <c r="P9">
         <v>72913</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="Q9">
         <v>18141</v>
       </c>
-      <c r="R9" s="2">
-        <v>0</v>
-      </c>
-      <c r="S9" s="2">
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
         <v>110</v>
       </c>
     </row>
@@ -1198,13 +1197,13 @@
       <c r="P10">
         <v>53124</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="Q10">
         <v>9498</v>
       </c>
-      <c r="R10" s="2">
-        <v>0</v>
-      </c>
-      <c r="S10" s="2">
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
         <v>2</v>
       </c>
     </row>
@@ -1257,13 +1256,13 @@
       <c r="P11">
         <v>84438</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="Q11">
         <v>23477</v>
       </c>
-      <c r="R11" s="2">
-        <v>0</v>
-      </c>
-      <c r="S11" s="2">
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
         <v>23</v>
       </c>
     </row>
@@ -1296,7 +1295,7 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -1308,21 +1307,21 @@
         <v>207</v>
       </c>
       <c r="N12">
-        <v>1057</v>
+        <v>1062</v>
       </c>
       <c r="O12">
-        <v>39509</v>
+        <v>39510</v>
       </c>
       <c r="P12">
         <v>66685</v>
       </c>
-      <c r="Q12" s="2">
+      <c r="Q12">
         <v>17786</v>
       </c>
-      <c r="R12" s="2">
-        <v>0</v>
-      </c>
-      <c r="S12" s="2">
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
         <v>3</v>
       </c>
     </row>
@@ -1375,13 +1374,13 @@
       <c r="P13">
         <v>56564</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="Q13">
         <v>16237</v>
       </c>
-      <c r="R13" s="2">
-        <v>0</v>
-      </c>
-      <c r="S13" s="2">
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
         <v>106</v>
       </c>
     </row>
@@ -1414,33 +1413,33 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>15097</v>
+        <v>15163</v>
       </c>
       <c r="M14">
-        <v>1425</v>
+        <v>1456</v>
       </c>
       <c r="N14">
-        <v>5630</v>
+        <v>5688</v>
       </c>
       <c r="O14">
-        <v>37550</v>
+        <v>41771</v>
       </c>
       <c r="P14">
         <v>77955</v>
       </c>
-      <c r="Q14" s="2">
+      <c r="Q14">
         <v>19716</v>
       </c>
-      <c r="R14" s="2">
-        <v>0</v>
-      </c>
-      <c r="S14" s="2">
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
         <v>174</v>
       </c>
     </row>
@@ -1493,13 +1492,13 @@
       <c r="P15">
         <v>67178</v>
       </c>
-      <c r="Q15" s="2">
+      <c r="Q15">
         <v>4859</v>
       </c>
-      <c r="R15" s="2">
-        <v>0</v>
-      </c>
-      <c r="S15" s="2">
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
         <v>50</v>
       </c>
     </row>
@@ -1552,13 +1551,13 @@
       <c r="P16">
         <v>71673</v>
       </c>
-      <c r="Q16" s="2">
+      <c r="Q16">
         <v>5197</v>
       </c>
-      <c r="R16" s="2">
-        <v>0</v>
-      </c>
-      <c r="S16" s="2">
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
         <v>47</v>
       </c>
     </row>
@@ -1611,13 +1610,13 @@
       <c r="P17">
         <v>65457</v>
       </c>
-      <c r="Q17" s="2">
+      <c r="Q17">
         <v>5417</v>
       </c>
-      <c r="R17" s="2">
-        <v>0</v>
-      </c>
-      <c r="S17" s="2">
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
         <v>105</v>
       </c>
     </row>
@@ -1670,13 +1669,13 @@
       <c r="P18">
         <v>71475</v>
       </c>
-      <c r="Q18" s="2">
+      <c r="Q18">
         <v>6819</v>
       </c>
-      <c r="R18" s="2">
-        <v>0</v>
-      </c>
-      <c r="S18" s="2">
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
         <v>32</v>
       </c>
     </row>
@@ -1709,13 +1708,13 @@
         <v>0</v>
       </c>
       <c r="J19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19">
         <v>0</v>
       </c>
       <c r="L19">
-        <v>15285</v>
+        <v>15286</v>
       </c>
       <c r="M19">
         <v>1</v>
@@ -1724,18 +1723,18 @@
         <v>910</v>
       </c>
       <c r="O19">
-        <v>55579</v>
+        <v>55580</v>
       </c>
       <c r="P19">
         <v>106392</v>
       </c>
-      <c r="Q19" s="2">
+      <c r="Q19">
         <v>6135</v>
       </c>
-      <c r="R19" s="2">
-        <v>0</v>
-      </c>
-      <c r="S19" s="2">
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
         <v>36</v>
       </c>
     </row>
@@ -1788,13 +1787,13 @@
       <c r="P20">
         <v>75812</v>
       </c>
-      <c r="Q20" s="2">
+      <c r="Q20">
         <v>8984</v>
       </c>
-      <c r="R20" s="2">
-        <v>0</v>
-      </c>
-      <c r="S20" s="2">
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
         <v>71</v>
       </c>
     </row>
@@ -1847,13 +1846,13 @@
       <c r="P21">
         <v>62460</v>
       </c>
-      <c r="Q21" s="2">
+      <c r="Q21">
         <v>3868</v>
       </c>
-      <c r="R21" s="2">
-        <v>0</v>
-      </c>
-      <c r="S21" s="2">
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
         <v>0</v>
       </c>
     </row>
@@ -1906,13 +1905,13 @@
       <c r="P22">
         <v>64099</v>
       </c>
-      <c r="Q22" s="2">
+      <c r="Q22">
         <v>4848</v>
       </c>
-      <c r="R22" s="2">
-        <v>0</v>
-      </c>
-      <c r="S22" s="2">
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
         <v>0</v>
       </c>
     </row>
@@ -1965,13 +1964,13 @@
       <c r="P23">
         <v>57094</v>
       </c>
-      <c r="Q23" s="2">
+      <c r="Q23">
         <v>3541</v>
       </c>
-      <c r="R23" s="2">
-        <v>0</v>
-      </c>
-      <c r="S23" s="2">
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
         <v>28</v>
       </c>
     </row>
@@ -2024,13 +2023,13 @@
       <c r="P24">
         <v>65629</v>
       </c>
-      <c r="Q24" s="2">
+      <c r="Q24">
         <v>3492</v>
       </c>
-      <c r="R24" s="2">
-        <v>0</v>
-      </c>
-      <c r="S24" s="2">
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
         <v>0</v>
       </c>
     </row>
@@ -2083,13 +2082,13 @@
       <c r="P25">
         <v>57533</v>
       </c>
-      <c r="Q25" s="2">
+      <c r="Q25">
         <v>3231</v>
       </c>
-      <c r="R25" s="2">
-        <v>0</v>
-      </c>
-      <c r="S25" s="2">
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
         <v>13</v>
       </c>
     </row>
@@ -2142,13 +2141,13 @@
       <c r="P26">
         <v>66594</v>
       </c>
-      <c r="Q26" s="2">
+      <c r="Q26">
         <v>3333</v>
       </c>
-      <c r="R26" s="2">
-        <v>0</v>
-      </c>
-      <c r="S26" s="2">
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
         <v>2</v>
       </c>
     </row>
@@ -2201,13 +2200,13 @@
       <c r="P27">
         <v>73109</v>
       </c>
-      <c r="Q27" s="2">
+      <c r="Q27">
         <v>12669</v>
       </c>
-      <c r="R27" s="2">
-        <v>0</v>
-      </c>
-      <c r="S27" s="2">
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
         <v>0</v>
       </c>
     </row>
@@ -2252,21 +2251,21 @@
         <v>856</v>
       </c>
       <c r="N28">
-        <v>3456</v>
+        <v>3478</v>
       </c>
       <c r="O28">
-        <v>50785</v>
+        <v>50838</v>
       </c>
       <c r="P28">
         <v>80620</v>
       </c>
-      <c r="Q28" s="2">
+      <c r="Q28">
         <v>13995</v>
       </c>
-      <c r="R28" s="2">
-        <v>0</v>
-      </c>
-      <c r="S28" s="2">
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
         <v>127</v>
       </c>
     </row>
@@ -2319,13 +2318,13 @@
       <c r="P29">
         <v>83836</v>
       </c>
-      <c r="Q29" s="2">
+      <c r="Q29">
         <v>14229</v>
       </c>
-      <c r="R29" s="2">
-        <v>0</v>
-      </c>
-      <c r="S29" s="2">
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
         <v>22</v>
       </c>
     </row>
@@ -2373,18 +2372,18 @@
         <v>5383</v>
       </c>
       <c r="O30">
-        <v>47260</v>
+        <v>47272</v>
       </c>
       <c r="P30">
         <v>86933</v>
       </c>
-      <c r="Q30" s="2">
+      <c r="Q30">
         <v>12564</v>
       </c>
-      <c r="R30" s="2">
-        <v>0</v>
-      </c>
-      <c r="S30" s="2">
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
         <v>8</v>
       </c>
     </row>
@@ -2437,13 +2436,13 @@
       <c r="P31">
         <v>81642</v>
       </c>
-      <c r="Q31" s="2">
+      <c r="Q31">
         <v>14581</v>
       </c>
-      <c r="R31" s="2">
-        <v>0</v>
-      </c>
-      <c r="S31" s="2">
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
         <v>39</v>
       </c>
     </row>
@@ -2496,13 +2495,13 @@
       <c r="P32">
         <v>74810</v>
       </c>
-      <c r="Q32" s="2">
+      <c r="Q32">
         <v>11379</v>
       </c>
-      <c r="R32" s="2">
-        <v>0</v>
-      </c>
-      <c r="S32" s="2">
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
         <v>0</v>
       </c>
     </row>
@@ -2541,27 +2540,27 @@
         <v>0</v>
       </c>
       <c r="L33">
-        <v>5089</v>
+        <v>5095</v>
       </c>
       <c r="M33">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="N33">
-        <v>1232</v>
+        <v>1240</v>
       </c>
       <c r="O33">
-        <v>38583</v>
+        <v>38838</v>
       </c>
       <c r="P33">
         <v>76969</v>
       </c>
-      <c r="Q33" s="2">
+      <c r="Q33">
         <v>6678</v>
       </c>
-      <c r="R33" s="2">
-        <v>0</v>
-      </c>
-      <c r="S33" s="2">
+      <c r="R33">
+        <v>0</v>
+      </c>
+      <c r="S33">
         <v>19</v>
       </c>
     </row>
@@ -2594,33 +2593,33 @@
         <v>0</v>
       </c>
       <c r="J34">
-        <v>35</v>
+        <v>267</v>
       </c>
       <c r="K34">
         <v>0</v>
       </c>
       <c r="L34">
-        <v>12131</v>
+        <v>12300</v>
       </c>
       <c r="M34">
-        <v>360</v>
+        <v>384</v>
       </c>
       <c r="N34">
-        <v>1357</v>
+        <v>1363</v>
       </c>
       <c r="O34">
-        <v>34723</v>
+        <v>34910</v>
       </c>
       <c r="P34">
         <v>74624</v>
       </c>
-      <c r="Q34" s="2">
+      <c r="Q34">
         <v>7137</v>
       </c>
-      <c r="R34" s="2">
-        <v>0</v>
-      </c>
-      <c r="S34" s="2">
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
         <v>0</v>
       </c>
     </row>
@@ -2665,21 +2664,21 @@
         <v>271</v>
       </c>
       <c r="N35">
-        <v>1098</v>
+        <v>1101</v>
       </c>
       <c r="O35">
-        <v>32434</v>
+        <v>32436</v>
       </c>
       <c r="P35">
         <v>76465</v>
       </c>
-      <c r="Q35" s="2">
+      <c r="Q35">
         <v>8879</v>
       </c>
-      <c r="R35" s="2">
-        <v>0</v>
-      </c>
-      <c r="S35" s="2">
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
         <v>35</v>
       </c>
     </row>
@@ -2732,13 +2731,13 @@
       <c r="P36">
         <v>60419</v>
       </c>
-      <c r="Q36" s="2">
+      <c r="Q36">
         <v>3855</v>
       </c>
-      <c r="R36" s="2">
-        <v>0</v>
-      </c>
-      <c r="S36" s="2">
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36">
         <v>2</v>
       </c>
     </row>
@@ -2791,13 +2790,13 @@
       <c r="P37">
         <v>57832</v>
       </c>
-      <c r="Q37" s="2">
+      <c r="Q37">
         <v>4036</v>
       </c>
-      <c r="R37" s="2">
-        <v>0</v>
-      </c>
-      <c r="S37" s="2">
+      <c r="R37">
+        <v>0</v>
+      </c>
+      <c r="S37">
         <v>1</v>
       </c>
     </row>
@@ -2850,13 +2849,13 @@
       <c r="P38">
         <v>63038</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="Q38">
         <v>5135</v>
       </c>
-      <c r="R38" s="2">
-        <v>0</v>
-      </c>
-      <c r="S38" s="2">
+      <c r="R38">
+        <v>0</v>
+      </c>
+      <c r="S38">
         <v>0</v>
       </c>
     </row>
@@ -2909,13 +2908,13 @@
       <c r="P39">
         <v>71133</v>
       </c>
-      <c r="Q39" s="2">
+      <c r="Q39">
         <v>5903</v>
       </c>
-      <c r="R39" s="2">
-        <v>0</v>
-      </c>
-      <c r="S39" s="2">
+      <c r="R39">
+        <v>0</v>
+      </c>
+      <c r="S39">
         <v>26</v>
       </c>
     </row>
@@ -2968,13 +2967,13 @@
       <c r="P40">
         <v>73242</v>
       </c>
-      <c r="Q40" s="2">
+      <c r="Q40">
         <v>3824</v>
       </c>
-      <c r="R40" s="2">
-        <v>0</v>
-      </c>
-      <c r="S40" s="2">
+      <c r="R40">
+        <v>0</v>
+      </c>
+      <c r="S40">
         <v>61</v>
       </c>
     </row>
@@ -3027,13 +3026,13 @@
       <c r="P41">
         <v>85251</v>
       </c>
-      <c r="Q41" s="2">
+      <c r="Q41">
         <v>6015</v>
       </c>
-      <c r="R41" s="2">
-        <v>0</v>
-      </c>
-      <c r="S41" s="2">
+      <c r="R41">
+        <v>0</v>
+      </c>
+      <c r="S41">
         <v>27</v>
       </c>
     </row>
@@ -3086,13 +3085,13 @@
       <c r="P42">
         <v>68615</v>
       </c>
-      <c r="Q42" s="2">
+      <c r="Q42">
         <v>4708</v>
       </c>
-      <c r="R42" s="2">
-        <v>0</v>
-      </c>
-      <c r="S42" s="2">
+      <c r="R42">
+        <v>0</v>
+      </c>
+      <c r="S42">
         <v>8</v>
       </c>
     </row>
@@ -3145,13 +3144,13 @@
       <c r="P43">
         <v>63012</v>
       </c>
-      <c r="Q43" s="2">
+      <c r="Q43">
         <v>5219</v>
       </c>
-      <c r="R43" s="2">
-        <v>0</v>
-      </c>
-      <c r="S43" s="2">
+      <c r="R43">
+        <v>0</v>
+      </c>
+      <c r="S43">
         <v>121</v>
       </c>
     </row>
@@ -3204,13 +3203,13 @@
       <c r="P44">
         <v>68393</v>
       </c>
-      <c r="Q44" s="2">
+      <c r="Q44">
         <v>7659</v>
       </c>
-      <c r="R44" s="2">
-        <v>0</v>
-      </c>
-      <c r="S44" s="2">
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
         <v>20</v>
       </c>
     </row>
@@ -3263,13 +3262,13 @@
       <c r="P45">
         <v>76287</v>
       </c>
-      <c r="Q45" s="2">
+      <c r="Q45">
         <v>6998</v>
       </c>
-      <c r="R45" s="2">
-        <v>0</v>
-      </c>
-      <c r="S45" s="2">
+      <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45">
         <v>129</v>
       </c>
     </row>
@@ -3322,13 +3321,13 @@
       <c r="P46">
         <v>64160</v>
       </c>
-      <c r="Q46" s="2">
+      <c r="Q46">
         <v>7548</v>
       </c>
-      <c r="R46" s="2">
-        <v>0</v>
-      </c>
-      <c r="S46" s="2">
+      <c r="R46">
+        <v>0</v>
+      </c>
+      <c r="S46">
         <v>152</v>
       </c>
     </row>
@@ -3381,13 +3380,13 @@
       <c r="P47">
         <v>49875</v>
       </c>
-      <c r="Q47" s="2">
+      <c r="Q47">
         <v>5046</v>
       </c>
-      <c r="R47" s="2">
-        <v>0</v>
-      </c>
-      <c r="S47" s="2">
+      <c r="R47">
+        <v>0</v>
+      </c>
+      <c r="S47">
         <v>0</v>
       </c>
     </row>
@@ -3440,13 +3439,13 @@
       <c r="P48">
         <v>54142</v>
       </c>
-      <c r="Q48" s="2">
+      <c r="Q48">
         <v>4623</v>
       </c>
-      <c r="R48" s="2">
-        <v>0</v>
-      </c>
-      <c r="S48" s="2">
+      <c r="R48">
+        <v>0</v>
+      </c>
+      <c r="S48">
         <v>9</v>
       </c>
     </row>
@@ -3499,13 +3498,13 @@
       <c r="P49">
         <v>55376</v>
       </c>
-      <c r="Q49" s="2">
+      <c r="Q49">
         <v>5057</v>
       </c>
-      <c r="R49" s="2">
-        <v>0</v>
-      </c>
-      <c r="S49" s="2">
+      <c r="R49">
+        <v>0</v>
+      </c>
+      <c r="S49">
         <v>4</v>
       </c>
     </row>
@@ -3558,13 +3557,13 @@
       <c r="P50">
         <v>63298</v>
       </c>
-      <c r="Q50" s="2">
+      <c r="Q50">
         <v>7292</v>
       </c>
-      <c r="R50" s="2">
-        <v>0</v>
-      </c>
-      <c r="S50" s="2">
+      <c r="R50">
+        <v>0</v>
+      </c>
+      <c r="S50">
         <v>1</v>
       </c>
     </row>
@@ -3617,13 +3616,13 @@
       <c r="P51">
         <v>71754</v>
       </c>
-      <c r="Q51" s="2">
+      <c r="Q51">
         <v>7715</v>
       </c>
-      <c r="R51" s="2">
-        <v>0</v>
-      </c>
-      <c r="S51" s="2">
+      <c r="R51">
+        <v>0</v>
+      </c>
+      <c r="S51">
         <v>40</v>
       </c>
     </row>
@@ -3676,13 +3675,13 @@
       <c r="P52">
         <v>63987</v>
       </c>
-      <c r="Q52" s="2">
+      <c r="Q52">
         <v>5655</v>
       </c>
-      <c r="R52" s="2">
-        <v>0</v>
-      </c>
-      <c r="S52" s="2">
+      <c r="R52">
+        <v>0</v>
+      </c>
+      <c r="S52">
         <v>2</v>
       </c>
     </row>
@@ -3715,13 +3714,13 @@
         <v>0</v>
       </c>
       <c r="J53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53">
-        <v>3512</v>
+        <v>3513</v>
       </c>
       <c r="M53">
         <v>1</v>
@@ -3730,18 +3729,18 @@
         <v>76</v>
       </c>
       <c r="O53">
-        <v>19054</v>
+        <v>19055</v>
       </c>
       <c r="P53">
         <v>56306</v>
       </c>
-      <c r="Q53" s="2">
+      <c r="Q53">
         <v>6551</v>
       </c>
-      <c r="R53" s="2">
-        <v>0</v>
-      </c>
-      <c r="S53" s="2">
+      <c r="R53">
+        <v>0</v>
+      </c>
+      <c r="S53">
         <v>5</v>
       </c>
     </row>
@@ -3794,13 +3793,13 @@
       <c r="P54">
         <v>58440</v>
       </c>
-      <c r="Q54" s="2">
+      <c r="Q54">
         <v>7347</v>
       </c>
-      <c r="R54" s="2">
-        <v>0</v>
-      </c>
-      <c r="S54" s="2">
+      <c r="R54">
+        <v>0</v>
+      </c>
+      <c r="S54">
         <v>1</v>
       </c>
     </row>
@@ -3853,13 +3852,13 @@
       <c r="P55">
         <v>58215</v>
       </c>
-      <c r="Q55" s="2">
+      <c r="Q55">
         <v>5098</v>
       </c>
-      <c r="R55" s="2">
-        <v>0</v>
-      </c>
-      <c r="S55" s="2">
+      <c r="R55">
+        <v>0</v>
+      </c>
+      <c r="S55">
         <v>0</v>
       </c>
     </row>
@@ -3912,13 +3911,13 @@
       <c r="P56">
         <v>47621</v>
       </c>
-      <c r="Q56" s="2">
+      <c r="Q56">
         <v>4882</v>
       </c>
-      <c r="R56" s="2">
-        <v>0</v>
-      </c>
-      <c r="S56" s="2">
+      <c r="R56">
+        <v>0</v>
+      </c>
+      <c r="S56">
         <v>30</v>
       </c>
     </row>
@@ -3971,13 +3970,13 @@
       <c r="P57">
         <v>61556</v>
       </c>
-      <c r="Q57" s="2">
+      <c r="Q57">
         <v>6870</v>
       </c>
-      <c r="R57" s="2">
-        <v>0</v>
-      </c>
-      <c r="S57" s="2">
+      <c r="R57">
+        <v>0</v>
+      </c>
+      <c r="S57">
         <v>0</v>
       </c>
     </row>
@@ -4030,13 +4029,13 @@
       <c r="P58">
         <v>57577</v>
       </c>
-      <c r="Q58" s="2">
+      <c r="Q58">
         <v>8884</v>
       </c>
-      <c r="R58" s="2">
-        <v>0</v>
-      </c>
-      <c r="S58" s="2">
+      <c r="R58">
+        <v>0</v>
+      </c>
+      <c r="S58">
         <v>64</v>
       </c>
     </row>
@@ -4089,13 +4088,13 @@
       <c r="P59">
         <v>60495</v>
       </c>
-      <c r="Q59" s="2">
+      <c r="Q59">
         <v>8028</v>
       </c>
-      <c r="R59" s="2">
-        <v>0</v>
-      </c>
-      <c r="S59" s="2">
+      <c r="R59">
+        <v>0</v>
+      </c>
+      <c r="S59">
         <v>27</v>
       </c>
     </row>
@@ -4148,13 +4147,13 @@
       <c r="P60">
         <v>70140</v>
       </c>
-      <c r="Q60" s="2">
+      <c r="Q60">
         <v>7415</v>
       </c>
-      <c r="R60" s="2">
-        <v>0</v>
-      </c>
-      <c r="S60" s="2">
+      <c r="R60">
+        <v>0</v>
+      </c>
+      <c r="S60">
         <v>32</v>
       </c>
     </row>
@@ -4207,13 +4206,13 @@
       <c r="P61">
         <v>55240</v>
       </c>
-      <c r="Q61" s="2">
+      <c r="Q61">
         <v>7927</v>
       </c>
-      <c r="R61" s="2">
+      <c r="R61">
         <v>1</v>
       </c>
-      <c r="S61" s="2">
+      <c r="S61">
         <v>268</v>
       </c>
     </row>
@@ -4266,13 +4265,13 @@
       <c r="P62">
         <v>51334</v>
       </c>
-      <c r="Q62" s="2">
+      <c r="Q62">
         <v>6917</v>
       </c>
-      <c r="R62" s="2">
-        <v>0</v>
-      </c>
-      <c r="S62" s="2">
+      <c r="R62">
+        <v>0</v>
+      </c>
+      <c r="S62">
         <v>100</v>
       </c>
     </row>
@@ -4325,13 +4324,13 @@
       <c r="P63">
         <v>68691</v>
       </c>
-      <c r="Q63" s="2">
+      <c r="Q63">
         <v>9766</v>
       </c>
-      <c r="R63" s="2">
-        <v>0</v>
-      </c>
-      <c r="S63" s="2">
+      <c r="R63">
+        <v>0</v>
+      </c>
+      <c r="S63">
         <v>153</v>
       </c>
     </row>
@@ -4384,13 +4383,13 @@
       <c r="P64">
         <v>60527</v>
       </c>
-      <c r="Q64" s="2">
+      <c r="Q64">
         <v>5985</v>
       </c>
-      <c r="R64" s="2">
-        <v>0</v>
-      </c>
-      <c r="S64" s="2">
+      <c r="R64">
+        <v>0</v>
+      </c>
+      <c r="S64">
         <v>101</v>
       </c>
     </row>
@@ -4443,13 +4442,13 @@
       <c r="P65">
         <v>58527</v>
       </c>
-      <c r="Q65" s="2">
+      <c r="Q65">
         <v>13282</v>
       </c>
-      <c r="R65" s="2">
-        <v>0</v>
-      </c>
-      <c r="S65" s="2">
+      <c r="R65">
+        <v>0</v>
+      </c>
+      <c r="S65">
         <v>138</v>
       </c>
     </row>
@@ -4502,13 +4501,13 @@
       <c r="P66">
         <v>93810</v>
       </c>
-      <c r="Q66" s="2">
+      <c r="Q66">
         <v>17742</v>
       </c>
-      <c r="R66" s="2">
-        <v>0</v>
-      </c>
-      <c r="S66" s="2">
+      <c r="R66">
+        <v>0</v>
+      </c>
+      <c r="S66">
         <v>52</v>
       </c>
     </row>
@@ -4561,13 +4560,13 @@
       <c r="P67">
         <v>78032</v>
       </c>
-      <c r="Q67" s="2">
+      <c r="Q67">
         <v>9807</v>
       </c>
-      <c r="R67" s="2">
-        <v>0</v>
-      </c>
-      <c r="S67" s="2">
+      <c r="R67">
+        <v>0</v>
+      </c>
+      <c r="S67">
         <v>116</v>
       </c>
     </row>
@@ -4612,21 +4611,21 @@
         <v>2</v>
       </c>
       <c r="N68">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="O68">
-        <v>63796</v>
+        <v>63795</v>
       </c>
       <c r="P68">
         <v>71325</v>
       </c>
-      <c r="Q68" s="2">
+      <c r="Q68">
         <v>7850</v>
       </c>
-      <c r="R68" s="2">
-        <v>0</v>
-      </c>
-      <c r="S68" s="2">
+      <c r="R68">
+        <v>0</v>
+      </c>
+      <c r="S68">
         <v>26</v>
       </c>
     </row>
@@ -4679,13 +4678,13 @@
       <c r="P69">
         <v>36118</v>
       </c>
-      <c r="Q69" s="2">
+      <c r="Q69">
         <v>6528</v>
       </c>
-      <c r="R69" s="2">
-        <v>0</v>
-      </c>
-      <c r="S69" s="2">
+      <c r="R69">
+        <v>0</v>
+      </c>
+      <c r="S69">
         <v>47</v>
       </c>
     </row>
@@ -4738,13 +4737,13 @@
       <c r="P70">
         <v>42051</v>
       </c>
-      <c r="Q70" s="2">
+      <c r="Q70">
         <v>5798</v>
       </c>
-      <c r="R70" s="2">
-        <v>0</v>
-      </c>
-      <c r="S70" s="2">
+      <c r="R70">
+        <v>0</v>
+      </c>
+      <c r="S70">
         <v>29</v>
       </c>
     </row>
@@ -4797,13 +4796,13 @@
       <c r="P71">
         <v>49140</v>
       </c>
-      <c r="Q71" s="2">
+      <c r="Q71">
         <v>6782</v>
       </c>
-      <c r="R71" s="2">
-        <v>0</v>
-      </c>
-      <c r="S71" s="2">
+      <c r="R71">
+        <v>0</v>
+      </c>
+      <c r="S71">
         <v>235</v>
       </c>
     </row>
@@ -4856,13 +4855,13 @@
       <c r="P72">
         <v>85505</v>
       </c>
-      <c r="Q72" s="2">
+      <c r="Q72">
         <v>12340</v>
       </c>
-      <c r="R72" s="2">
-        <v>0</v>
-      </c>
-      <c r="S72" s="2">
+      <c r="R72">
+        <v>0</v>
+      </c>
+      <c r="S72">
         <v>79</v>
       </c>
     </row>
@@ -4915,13 +4914,13 @@
       <c r="P73">
         <v>67666</v>
       </c>
-      <c r="Q73" s="2">
+      <c r="Q73">
         <v>10010</v>
       </c>
-      <c r="R73" s="2">
-        <v>0</v>
-      </c>
-      <c r="S73" s="2">
+      <c r="R73">
+        <v>0</v>
+      </c>
+      <c r="S73">
         <v>74</v>
       </c>
     </row>
@@ -4952,38 +4951,36 @@
         <v>0</v>
       </c>
       <c r="J74">
-        <v>138</v>
+        <v>363</v>
       </c>
       <c r="K74">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L74">
-        <v>624835</v>
+        <v>625082</v>
       </c>
       <c r="M74">
-        <v>8105</v>
+        <v>8174</v>
       </c>
       <c r="N74">
-        <v>96407</v>
+        <v>96539</v>
       </c>
       <c r="O74">
-        <v>2316764</v>
+        <v>2325834</v>
       </c>
       <c r="P74">
         <v>4701901</v>
       </c>
-      <c r="Q74" s="2">
+      <c r="Q74">
         <v>626236</v>
       </c>
-      <c r="R74" s="2">
+      <c r="R74">
         <v>1</v>
       </c>
-      <c r="S74" s="2">
+      <c r="S74">
         <v>3445</v>
       </c>
     </row>
-    <row r="75" spans="1:19" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="1:19" ht="15.75" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="A74:B74"/>
